--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.80000019073486</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="D2" t="n">
-        <v>15.80000019073486</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="E2" t="n">
-        <v>15.89999961853027</v>
+        <v>15.90999984741211</v>
       </c>
       <c r="F2" t="n">
         <v>15.36999988555908</v>
@@ -912,67 +912,67 @@
         <v>15.39999961853027</v>
       </c>
       <c r="H2" t="n">
-        <v>18814600</v>
+        <v>26568100</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01152370720195672</v>
+        <v>0.01600512175618696</v>
       </c>
       <c r="J2" t="n">
-        <v>15.64777776930067</v>
+        <v>15.65555551317003</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.972805363665347</v>
+        <v>1.369765334795389</v>
       </c>
       <c r="M2" t="n">
-        <v>15.58599996566772</v>
+        <v>15.59299993515015</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.373028522639103</v>
+        <v>1.776437834675514</v>
       </c>
       <c r="P2" t="n">
-        <v>15.24346149884737</v>
+        <v>15.24615379480215</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3.650999426406999</v>
+        <v>4.091826037919257</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51299997329712</v>
+        <v>15.5143999671936</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.850062643794001</v>
+        <v>2.292063625518364</v>
       </c>
       <c r="V2" t="n">
-        <v>15.69086667378743</v>
+        <v>15.6913333384196</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.695522555995859</v>
+        <v>1.138632028815726</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.29300000190735</v>
+        <v>15.29335000038147</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.315243502022375</v>
+        <v>3.770592350029451</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.173321781612734</v>
+        <v>0.1764460248019737</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>15.96</v>
+        <v>16.03</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1165,13 +1165,13 @@
         <v>4</v>
       </c>
       <c r="CM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN2" t="n">
         <v>1</v>
       </c>
       <c r="CO2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.28000068664551</v>
+        <v>28.44000053405762</v>
       </c>
       <c r="D3" t="n">
-        <v>28.28000068664551</v>
+        <v>28.44000053405762</v>
       </c>
       <c r="E3" t="n">
-        <v>28.45999908447266</v>
+        <v>28.47999954223633</v>
       </c>
       <c r="F3" t="n">
         <v>27.79999923706055</v>
@@ -1199,67 +1199,67 @@
         <v>27.90999984741211</v>
       </c>
       <c r="H3" t="n">
-        <v>2721300</v>
+        <v>3772200</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01222488593715076</v>
+        <v>-0.006636347617129945</v>
       </c>
       <c r="J3" t="n">
-        <v>28.59999995761448</v>
+        <v>28.61777771843804</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.118878571479755</v>
+        <v>-0.6212124020583372</v>
       </c>
       <c r="M3" t="n">
-        <v>28.40900001525879</v>
+        <v>28.425</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4540790895279513</v>
+        <v>0.0527723273794775</v>
       </c>
       <c r="P3" t="n">
-        <v>26.98999999119685</v>
+        <v>26.99615383148193</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>4.779550558982606</v>
+        <v>5.348342254932338</v>
       </c>
       <c r="S3" t="n">
-        <v>27.17659999847412</v>
+        <v>27.17979999542236</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4.060113068718454</v>
+        <v>4.636533524336076</v>
       </c>
       <c r="V3" t="n">
-        <v>28.95006666819254</v>
+        <v>28.95113333384196</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.314557645849011</v>
+        <v>-1.76550186789013</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.95804999351502</v>
+        <v>28.95884999275208</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2.341488142403761</v>
+        <v>-1.791678394771606</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2667760397813623</v>
+        <v>0.2647488708594864</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1407,13 +1407,13 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CC3" t="n">
         <v>9</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM3" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.689999580383301</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="D4" t="n">
-        <v>9.689999580383301</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="E4" t="n">
         <v>9.819999694824219</v>
@@ -1482,67 +1482,67 @@
         <v>9.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3900900</v>
+        <v>5856400</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01323830127097014</v>
+        <v>-0.01731161726853681</v>
       </c>
       <c r="J4" t="n">
-        <v>9.279999838935005</v>
+        <v>9.275555398729113</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>4.418100738839541</v>
+        <v>4.036892711054965</v>
       </c>
       <c r="M4" t="n">
-        <v>9.195999813079833</v>
+        <v>9.191999816894532</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>5.3718984052265</v>
+        <v>4.982591500860959</v>
       </c>
       <c r="P4" t="n">
-        <v>8.572307641689594</v>
+        <v>8.570769181618324</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>13.03840208974827</v>
+        <v>12.59199045082871</v>
       </c>
       <c r="S4" t="n">
-        <v>8.514799957275391</v>
+        <v>8.51399995803833</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>13.80184653784815</v>
+        <v>13.34272569991513</v>
       </c>
       <c r="V4" t="n">
-        <v>8.689866603215535</v>
+        <v>8.689599936803182</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>11.50918676700612</v>
+        <v>11.05228881319953</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.546049938201904</v>
+        <v>8.545849938392639</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.38571211792012</v>
+        <v>12.92030269777134</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.518963267816177</v>
+        <v>0.5203318511070349</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1692,13 +1692,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>18.63</v>
+        <v>18.56</v>
       </c>
       <c r="CA4" t="n">
         <v>0.92</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CM4" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="CO4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.51000022888184</v>
+        <v>11.5600004196167</v>
       </c>
       <c r="D5" t="n">
-        <v>11.51000022888184</v>
+        <v>11.5600004196167</v>
       </c>
       <c r="E5" t="n">
         <v>11.6899995803833</v>
@@ -1767,73 +1767,73 @@
         <v>11.59000015258789</v>
       </c>
       <c r="H5" t="n">
-        <v>1615300</v>
+        <v>2055600</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02787161481868106</v>
+        <v>-0.02364862579076832</v>
       </c>
       <c r="J5" t="n">
-        <v>11.78555562761095</v>
+        <v>11.79111120435927</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.338077282360344</v>
+        <v>-1.960042448392172</v>
       </c>
       <c r="M5" t="n">
-        <v>11.72600002288818</v>
+        <v>11.73100004196167</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.84205861832452</v>
+        <v>-1.457673017929472</v>
       </c>
       <c r="P5" t="n">
-        <v>10.92615391657903</v>
+        <v>10.93884622133695</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.343566608712124</v>
+        <v>5.678425180419341</v>
       </c>
       <c r="S5" t="n">
-        <v>11.24899997711182</v>
+        <v>11.27619998931885</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.320208483430285</v>
+        <v>2.516809125119066</v>
       </c>
       <c r="V5" t="n">
-        <v>11.96886665344238</v>
+        <v>11.97086665471395</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.833833543701248</v>
+        <v>-3.432217958383621</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.9427999830246</v>
+        <v>11.94854998588562</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.623938730933616</v>
+        <v>-3.251855386033452</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2964960991215612</v>
+        <v>0.3038823503120243</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AE5" t="n">
         <v>11.4</v>
@@ -1975,13 +1975,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54.90999984741211</v>
+        <v>54.97999954223633</v>
       </c>
       <c r="D6" t="n">
-        <v>54.90999984741211</v>
+        <v>54.97999954223633</v>
       </c>
       <c r="E6" t="n">
         <v>55.36999893188477</v>
@@ -2046,67 +2046,67 @@
         <v>53.90000152587891</v>
       </c>
       <c r="H6" t="n">
-        <v>11985100</v>
+        <v>14113300</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002007310435821585</v>
+        <v>0.003284677147477932</v>
       </c>
       <c r="J6" t="n">
-        <v>55.21777809990777</v>
+        <v>55.22555584377713</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5573897811295182</v>
+        <v>-0.4446425170177283</v>
       </c>
       <c r="M6" t="n">
-        <v>55.00800018310547</v>
+        <v>55.01500015258789</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1781565142654563</v>
+        <v>-0.06362012224753805</v>
       </c>
       <c r="P6" t="n">
-        <v>52.81153825613168</v>
+        <v>52.81423055208646</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.973490757082396</v>
+        <v>4.100729987941298</v>
       </c>
       <c r="S6" t="n">
-        <v>52.45659980773926</v>
+        <v>52.45799980163574</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.677009277507317</v>
+        <v>4.807655172018098</v>
       </c>
       <c r="V6" t="n">
-        <v>55.96866663614909</v>
+        <v>55.96913330078125</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.891534768229061</v>
+        <v>-1.767284394470187</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.15650001525879</v>
+        <v>56.15685001373291</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.219689915696275</v>
+        <v>-2.095649010243247</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2482815185295669</v>
+        <v>0.2483356637379966</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.79</v>
+        <v>16.81</v>
       </c>
       <c r="CA6" t="n">
         <v>0.29</v>
@@ -2310,82 +2310,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.85000038146973</v>
+        <v>15.78999996185303</v>
       </c>
       <c r="D7" t="n">
-        <v>15.85000038146973</v>
+        <v>15.78999996185303</v>
       </c>
       <c r="E7" t="n">
         <v>16.20000076293945</v>
       </c>
       <c r="F7" t="n">
-        <v>15.77999973297119</v>
+        <v>15.6899995803833</v>
       </c>
       <c r="G7" t="n">
         <v>16.10000038146973</v>
       </c>
       <c r="H7" t="n">
-        <v>1420000</v>
+        <v>2581600</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03530127285045415</v>
+        <v>-0.03895315468260463</v>
       </c>
       <c r="J7" t="n">
-        <v>16.6199999915229</v>
+        <v>16.61333327823215</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.63296997861559</v>
+        <v>-4.955858662378774</v>
       </c>
       <c r="M7" t="n">
-        <v>16.44399995803833</v>
+        <v>16.43799991607666</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.612257225032633</v>
+        <v>-3.942085153497759</v>
       </c>
       <c r="P7" t="n">
-        <v>15.7650000498845</v>
+        <v>15.76269234143771</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5391711469474233</v>
+        <v>0.1732421075271117</v>
       </c>
       <c r="S7" t="n">
-        <v>16.58</v>
+        <v>16.57879999160767</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.40289275349983</v>
+        <v>-4.757883744022108</v>
       </c>
       <c r="V7" t="n">
-        <v>20.35126669565837</v>
+        <v>20.35086669286092</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-22.11786804970188</v>
+        <v>-22.41116705171012</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.66810000419617</v>
+        <v>21.66780000209808</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-26.8509911879663</v>
+        <v>-27.12688893046784</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5076234707249331</v>
+        <v>0.5098920314615877</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CA7" t="n">
         <v>0.67</v>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3700008392334</v>
+        <v>17.36000061035156</v>
       </c>
       <c r="D8" t="n">
-        <v>17.3700008392334</v>
+        <v>17.36000061035156</v>
       </c>
       <c r="E8" t="n">
-        <v>17.40999984741211</v>
+        <v>17.44000053405762</v>
       </c>
       <c r="F8" t="n">
         <v>16.80999946594238</v>
@@ -2608,67 +2608,67 @@
         <v>16.85000038146973</v>
       </c>
       <c r="H8" t="n">
-        <v>24647000</v>
+        <v>35592700</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005208341956690177</v>
+        <v>0.004629625030506013</v>
       </c>
       <c r="J8" t="n">
-        <v>17.31555599636502</v>
+        <v>17.31444485982259</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3144273442897869</v>
+        <v>0.2631083520019903</v>
       </c>
       <c r="M8" t="n">
-        <v>17.20600032806396</v>
+        <v>17.20500030517578</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9531588285624953</v>
+        <v>0.9009026586832081</v>
       </c>
       <c r="P8" t="n">
-        <v>15.80615399434016</v>
+        <v>15.8057693701524</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>9.893911228836663</v>
+        <v>9.833315948125691</v>
       </c>
       <c r="S8" t="n">
-        <v>15.58600002288818</v>
+        <v>15.58580001831055</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>11.44617486029381</v>
+        <v>11.38344255640805</v>
       </c>
       <c r="V8" t="n">
-        <v>16.61600005467733</v>
+        <v>16.61593338648478</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>4.537799603243391</v>
+        <v>4.478034465833851</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.13960005760193</v>
+        <v>16.13955005645752</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.623489908301277</v>
+        <v>7.561862317256697</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3187402543532048</v>
+        <v>0.3187177795688048</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>17.72</v>
+        <v>17.71</v>
       </c>
       <c r="CA8" t="n">
         <v>-0.01</v>
@@ -2861,13 +2861,13 @@
         <v>9</v>
       </c>
       <c r="CM8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.1299991607666</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="D9" t="n">
-        <v>22.1299991607666</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="E9" t="n">
         <v>22.26000022888184</v>
@@ -2895,88 +2895,88 @@
         <v>21.95000076293945</v>
       </c>
       <c r="H9" t="n">
-        <v>23033600</v>
+        <v>27841000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0160071415747135</v>
+        <v>-0.01289457586171827</v>
       </c>
       <c r="J9" t="n">
-        <v>22.29333326551649</v>
+        <v>22.30111122131348</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.732658964922664</v>
+        <v>-0.4533875346865711</v>
       </c>
       <c r="M9" t="n">
-        <v>22.13799991607666</v>
+        <v>22.14500007629395</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.03614037103797715</v>
+        <v>0.2483661614631657</v>
       </c>
       <c r="P9" t="n">
-        <v>20.17192305051363</v>
+        <v>20.17461541982798</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>9.706938229685095</v>
+        <v>10.03927609505206</v>
       </c>
       <c r="S9" t="n">
-        <v>20.36740001678467</v>
+        <v>20.36880004882812</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>8.654021340619741</v>
+        <v>8.990223821342305</v>
       </c>
       <c r="V9" t="n">
-        <v>21.88459999084473</v>
+        <v>21.88506666819255</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.121332672402218</v>
+        <v>1.439036487856019</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.03229999542236</v>
+        <v>22.03265000343323</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4434360705170916</v>
+        <v>0.7595580172160256</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3637331060927887</v>
+        <v>0.3625449613001165</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -3123,7 +3123,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.1299991607666</v>
+        <v>16.18000030517578</v>
       </c>
       <c r="D10" t="n">
-        <v>16.1299991607666</v>
+        <v>16.18000030517578</v>
       </c>
       <c r="E10" t="n">
-        <v>16.19000053405762</v>
+        <v>16.20000076293945</v>
       </c>
       <c r="F10" t="n">
         <v>15.92000007629395</v>
@@ -3194,67 +3194,67 @@
         <v>15.96000003814697</v>
       </c>
       <c r="H10" t="n">
-        <v>3788100</v>
+        <v>5991300</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01164218980456688</v>
+        <v>-0.008578394133967882</v>
       </c>
       <c r="J10" t="n">
-        <v>15.8800000084771</v>
+        <v>15.88555569118924</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.574301965718149</v>
+        <v>1.853536758237902</v>
       </c>
       <c r="M10" t="n">
-        <v>15.80900001525879</v>
+        <v>15.81400012969971</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.030483554924317</v>
+        <v>2.314406048275556</v>
       </c>
       <c r="P10" t="n">
-        <v>15.06576923223642</v>
+        <v>15.0823077421922</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>7.063893732375997</v>
+        <v>7.278014623139079</v>
       </c>
       <c r="S10" t="n">
-        <v>15.52621776580811</v>
+        <v>15.54341779708862</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>3.888786078269142</v>
+        <v>4.095511787673844</v>
       </c>
       <c r="V10" t="n">
-        <v>16.21020593007406</v>
+        <v>16.23120594024658</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4947917975468255</v>
+        <v>-0.3154764671171616</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29070445537567</v>
+        <v>16.29620446681976</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.9864846240951816</v>
+        <v>-0.713075010077233</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2295906480264004</v>
+        <v>0.2328441944645812</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3422,13 +3422,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.2</v>
+        <v>7.22</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="CC10" t="n">
         <v>2</v>
@@ -3478,13 +3478,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.35000038146973</v>
+        <v>18.42000007629395</v>
       </c>
       <c r="D11" t="n">
-        <v>18.35000038146973</v>
+        <v>18.42000007629395</v>
       </c>
       <c r="E11" t="n">
-        <v>18.42000007629395</v>
+        <v>18.44000053405762</v>
       </c>
       <c r="F11" t="n">
         <v>18.1200008392334</v>
@@ -3493,88 +3493,88 @@
         <v>18.20000076293945</v>
       </c>
       <c r="H11" t="n">
-        <v>14148200</v>
+        <v>19575800</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01291015433825882</v>
+        <v>-0.009144705481364923</v>
       </c>
       <c r="J11" t="n">
-        <v>18.03000005086263</v>
+        <v>18.03777779473199</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.774821573512904</v>
+        <v>2.119009813246441</v>
       </c>
       <c r="M11" t="n">
-        <v>17.94600009918213</v>
+        <v>17.95300006866455</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.251199599101805</v>
+        <v>2.601236594682043</v>
       </c>
       <c r="P11" t="n">
-        <v>17.11846168224628</v>
+        <v>17.12115397820106</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>7.194213604489278</v>
+        <v>7.586206512403313</v>
       </c>
       <c r="S11" t="n">
-        <v>17.72294044494629</v>
+        <v>17.72434043884277</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>3.538125845828501</v>
+        <v>3.92488307168056</v>
       </c>
       <c r="V11" t="n">
-        <v>18.63244682312012</v>
+        <v>18.63291348775228</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.515884866500276</v>
+        <v>-1.142673750931576</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.79323512077331</v>
+        <v>18.79358511924744</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.358480253427219</v>
+        <v>-1.987832766250028</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2651674369052702</v>
+        <v>0.2637896334650086</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.19</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39.90000152587891</v>
+        <v>39.91999816894531</v>
       </c>
       <c r="D12" t="n">
-        <v>39.90000152587891</v>
+        <v>39.91999816894531</v>
       </c>
       <c r="E12" t="n">
         <v>40.11000061035156</v>
@@ -3792,67 +3792,67 @@
         <v>39.06000137329102</v>
       </c>
       <c r="H12" t="n">
-        <v>3253200</v>
+        <v>4465300</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01012662090832683</v>
+        <v>0.01063286503659011</v>
       </c>
       <c r="J12" t="n">
-        <v>41.12222205268012</v>
+        <v>41.12444390190972</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.972165573240365</v>
+        <v>-2.928783027041679</v>
       </c>
       <c r="M12" t="n">
-        <v>41.05</v>
+        <v>41.05199966430664</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.801457915033108</v>
+        <v>-2.757481985330833</v>
       </c>
       <c r="P12" t="n">
-        <v>39.10692302997295</v>
+        <v>39.10769213162936</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>2.027974676755081</v>
+        <v>2.077100419482393</v>
       </c>
       <c r="S12" t="n">
-        <v>39.92039978027343</v>
+        <v>39.92079971313476</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.05109731993367572</v>
+        <v>-0.002007836003311011</v>
       </c>
       <c r="V12" t="n">
-        <v>36.99633323669433</v>
+        <v>36.99646654764811</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>7.848529935676456</v>
+        <v>7.902191463425179</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.66049995422363</v>
+        <v>36.66059993743897</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.836490434392056</v>
+        <v>8.890738932446505</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3179287258733564</v>
+        <v>0.3180849116888456</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.090000152587891</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="D13" t="n">
-        <v>4.090000152587891</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="E13" t="n">
         <v>4.199999809265137</v>
@@ -4091,67 +4091,67 @@
         <v>4.139999866485596</v>
       </c>
       <c r="H13" t="n">
-        <v>13430400</v>
+        <v>23046300</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.009685220519283777</v>
+        <v>-0.002421362858288867</v>
       </c>
       <c r="J13" t="n">
-        <v>3.94888891114129</v>
+        <v>3.952222214804755</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>3.573441659715305</v>
+        <v>4.245147707683112</v>
       </c>
       <c r="M13" t="n">
-        <v>3.93600001335144</v>
+        <v>3.93899998664856</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.912605150255619</v>
+        <v>4.59507234130568</v>
       </c>
       <c r="P13" t="n">
-        <v>3.728846164850088</v>
+        <v>3.730000000733596</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>9.685408616268889</v>
+        <v>10.45576098522207</v>
       </c>
       <c r="S13" t="n">
-        <v>3.653800005912781</v>
+        <v>3.654400000572204</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>11.93826005717956</v>
+        <v>12.7408024549577</v>
       </c>
       <c r="V13" t="n">
-        <v>4.051000005404155</v>
+        <v>4.051200003623962</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9627288850088536</v>
+        <v>1.698259327448055</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.503700007200241</v>
+        <v>4.503850005865097</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-9.185777337543618</v>
+        <v>-8.522711009606214</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5335753427668752</v>
+        <v>0.5323405373351865</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4303,13 +4303,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.76</v>
+        <v>5.8</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CC13" t="n">
         <v>8</v>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.77999877929688</v>
+        <v>60.83000183105469</v>
       </c>
       <c r="D14" t="n">
-        <v>60.77999877929688</v>
+        <v>60.83000183105469</v>
       </c>
       <c r="E14" t="n">
         <v>61</v>
@@ -4378,67 +4378,67 @@
         <v>59.11999893188477</v>
       </c>
       <c r="H14" t="n">
-        <v>5770200</v>
+        <v>7838700</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0006576934516286936</v>
+        <v>0.0001644547234569416</v>
       </c>
       <c r="J14" t="n">
-        <v>59.26000044080946</v>
+        <v>59.26555633544922</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.564965115053666</v>
+        <v>2.639721268708834</v>
       </c>
       <c r="M14" t="n">
-        <v>58.80500030517578</v>
+        <v>58.81000061035157</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35855533351177</v>
+        <v>3.434792041725582</v>
       </c>
       <c r="P14" t="n">
-        <v>54.51615406916692</v>
+        <v>54.51807726346529</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>11.48988738674184</v>
+        <v>11.57767273612062</v>
       </c>
       <c r="S14" t="n">
-        <v>55.33080009460449</v>
+        <v>55.33180015563965</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.848400303945279</v>
+        <v>9.936784380680663</v>
       </c>
       <c r="V14" t="n">
-        <v>56.28519991556804</v>
+        <v>56.28553326924642</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>7.985756238711722</v>
+        <v>8.073954882988193</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.00079992294312</v>
+        <v>56.0010499382019</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.534161767206751</v>
+        <v>8.622966708984233</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3531279762958744</v>
+        <v>0.3530720712105907</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.66</v>
+        <v>13.67</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CC14" t="n">
         <v>6</v>
@@ -4670,82 +4670,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.72999954223633</v>
+        <v>21.69000053405762</v>
       </c>
       <c r="D15" t="n">
-        <v>21.72999954223633</v>
+        <v>21.69000053405762</v>
       </c>
       <c r="E15" t="n">
         <v>22.14999961853027</v>
       </c>
       <c r="F15" t="n">
-        <v>21.72999954223633</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="G15" t="n">
         <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>1188800</v>
+        <v>1790700</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0359361730430553</v>
+        <v>-0.03771075186089179</v>
       </c>
       <c r="J15" t="n">
-        <v>22.49222204420302</v>
+        <v>22.48777770996094</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.38882703749201</v>
+        <v>-3.547603441268213</v>
       </c>
       <c r="M15" t="n">
-        <v>22.44299983978271</v>
+        <v>22.43899993896484</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.176938478083997</v>
+        <v>-3.337935767835205</v>
       </c>
       <c r="P15" t="n">
-        <v>21.6253845508282</v>
+        <v>21.62384612743671</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4837601438357793</v>
+        <v>0.3059326552318041</v>
       </c>
       <c r="S15" t="n">
-        <v>21.59779998779297</v>
+        <v>21.59700000762939</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6120973178660764</v>
+        <v>0.4306178005990189</v>
       </c>
       <c r="V15" t="n">
-        <v>22.66033335367839</v>
+        <v>22.66006669362386</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.1055610123716</v>
+        <v>-4.280950152009937</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.36324997901917</v>
+        <v>22.36304998397827</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.831656567703455</v>
+        <v>-3.009649624728524</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2816128398177731</v>
+        <v>0.2836063496230136</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.92</v>
+        <v>10.9</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
@@ -4961,103 +4961,103 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18.02000045776367</v>
+        <v>17.82999992370605</v>
       </c>
       <c r="D16" t="n">
-        <v>18.02000045776367</v>
+        <v>17.82999992370605</v>
       </c>
       <c r="E16" t="n">
         <v>18.60000038146973</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>17.71999931335449</v>
       </c>
       <c r="G16" t="n">
         <v>18.45000076293945</v>
       </c>
       <c r="H16" t="n">
-        <v>1901800</v>
+        <v>3687600</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01476218940669671</v>
+        <v>-0.02515040835404059</v>
       </c>
       <c r="J16" t="n">
-        <v>18.36111111111111</v>
+        <v>18.33999994066026</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.857788732300726</v>
+        <v>-2.780807080721549</v>
       </c>
       <c r="M16" t="n">
-        <v>18.23799991607666</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.195303538305335</v>
+        <v>-2.135133332768007</v>
       </c>
       <c r="P16" t="n">
-        <v>18.28423067239614</v>
+        <v>18.27692295954778</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.445126236737888</v>
+        <v>-2.445285986218212</v>
       </c>
       <c r="S16" t="n">
-        <v>18.97799991607666</v>
+        <v>18.97419990539551</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.047947426227173</v>
+        <v>-6.03029370089059</v>
       </c>
       <c r="V16" t="n">
-        <v>19.18753323872884</v>
+        <v>19.18626656850179</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.084850858309267</v>
+        <v>-7.068945070440781</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.38319991588592</v>
+        <v>18.38224991321564</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-1.975714020323482</v>
+        <v>-3.004256780953411</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.3958010469906076</v>
+        <v>0.3996478796963019</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AF16" t="n">
         <v>17.8</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>17.9</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
         <v>18</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>18.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>18.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
@@ -5184,10 +5184,10 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>36.04</v>
+        <v>35.66</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CB16" t="n">
         <v>0.73</v>
@@ -5218,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM16" t="n">
         <v>3</v>
@@ -5227,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -5240,82 +5240,82 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.170000076293945</v>
+        <v>5.070000171661377</v>
       </c>
       <c r="D17" t="n">
-        <v>5.170000076293945</v>
+        <v>5.070000171661377</v>
       </c>
       <c r="E17" t="n">
         <v>5.349999904632568</v>
       </c>
       <c r="F17" t="n">
-        <v>5.130000114440918</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="G17" t="n">
         <v>5.210000038146973</v>
       </c>
       <c r="H17" t="n">
-        <v>1883900</v>
+        <v>2983800</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01897531404070085</v>
+        <v>-0.03795062808140182</v>
       </c>
       <c r="J17" t="n">
-        <v>4.952222241295709</v>
+        <v>4.941111140780979</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>4.397577983924584</v>
+        <v>2.608502970447776</v>
       </c>
       <c r="M17" t="n">
-        <v>4.890000009536744</v>
+        <v>4.880000019073487</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>5.725972724153997</v>
+        <v>3.893445734534312</v>
       </c>
       <c r="P17" t="n">
-        <v>4.928846139174241</v>
+        <v>4.924999988996065</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>4.892705722806478</v>
+        <v>2.944166152066719</v>
       </c>
       <c r="S17" t="n">
-        <v>5.502399988174439</v>
+        <v>5.500399990081787</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.040998702291281</v>
+        <v>-7.824882175778098</v>
       </c>
       <c r="V17" t="n">
-        <v>8.327399965922037</v>
+        <v>8.326733299891155</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-37.91579487654037</v>
+        <v>-39.11177422089824</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.301749980449676</v>
+        <v>8.301249980926514</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-37.72397279526473</v>
+        <v>-38.92485850551982</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.070838864942874</v>
+        <v>1.074761045035555</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5467,10 +5467,10 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="CA17" t="n">
-        <v>10.44</v>
+        <v>10.64</v>
       </c>
       <c r="CB17" t="n">
         <v>-0.26</v>
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.380000114440918</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="D18" t="n">
-        <v>9.380000114440918</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="E18" t="n">
-        <v>9.430000305175781</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="F18" t="n">
         <v>9.010000228881836</v>
@@ -5542,67 +5542,67 @@
         <v>9.060000419616699</v>
       </c>
       <c r="H18" t="n">
-        <v>3751600</v>
+        <v>5109700</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003208527459597432</v>
+        <v>0.005347511766912616</v>
       </c>
       <c r="J18" t="n">
-        <v>9.246666696336534</v>
+        <v>9.248888863457573</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.441961979198507</v>
+        <v>1.633826044442378</v>
       </c>
       <c r="M18" t="n">
-        <v>9.153999996185302</v>
+        <v>9.155999946594239</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.468867362353024</v>
+        <v>2.664915611175763</v>
       </c>
       <c r="P18" t="n">
-        <v>8.468076962691088</v>
+        <v>8.468846174386831</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>10.76895209818722</v>
+        <v>10.99504495617858</v>
       </c>
       <c r="S18" t="n">
-        <v>9.113200016021729</v>
+        <v>9.113600006103516</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.927622546966306</v>
+        <v>3.142551924979717</v>
       </c>
       <c r="V18" t="n">
-        <v>10.85493333180746</v>
+        <v>10.85506666183472</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.58767642583896</v>
+        <v>-13.40449661557868</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.38220001220703</v>
+        <v>11.38230000972748</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-17.59062303964805</v>
+        <v>-17.41563998052329</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5218605987318273</v>
+        <v>0.522000863064915</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="CA18" t="n">
         <v>0.05</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.25</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="D19" t="n">
-        <v>11.25</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="E19" t="n">
-        <v>11.30000019073486</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F19" t="n">
         <v>11.13000011444092</v>
@@ -5827,67 +5827,67 @@
         <v>11.21000003814697</v>
       </c>
       <c r="H19" t="n">
-        <v>6849800</v>
+        <v>9893400</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01746723254120064</v>
+        <v>-0.01222702113367302</v>
       </c>
       <c r="J19" t="n">
-        <v>11.26555559370253</v>
+        <v>11.27222230699327</v>
       </c>
       <c r="K19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1380810167163316</v>
+        <v>0.3351434313000459</v>
       </c>
       <c r="M19" t="n">
-        <v>11.20900001525879</v>
+        <v>11.21500005722046</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3657773635953018</v>
+        <v>0.8470830308652259</v>
       </c>
       <c r="P19" t="n">
-        <v>10.67769230329073</v>
+        <v>10.68000001173753</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>5.35984443504603</v>
+        <v>5.898880217104743</v>
       </c>
       <c r="S19" t="n">
-        <v>10.89179996490478</v>
+        <v>10.89299997329712</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.28871294229968</v>
+        <v>3.828150622801861</v>
       </c>
       <c r="V19" t="n">
-        <v>11.5182000541687</v>
+        <v>11.51860005696615</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.328489285716425</v>
+        <v>-1.810980816399575</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43820003032684</v>
+        <v>11.43850003242493</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.645364041788537</v>
+        <v>-1.123395658906035</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2592189334293039</v>
+        <v>0.256606371062407</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6039,13 +6039,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.66</v>
+        <v>6.69</v>
       </c>
       <c r="CA19" t="n">
         <v>0.55</v>
       </c>
       <c r="CB19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CC19" t="n">
         <v>5</v>
@@ -6095,82 +6095,82 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.400000095367432</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="D20" t="n">
-        <v>6.400000095367432</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="E20" t="n">
         <v>6.679999828338623</v>
       </c>
       <c r="F20" t="n">
-        <v>6.380000114440918</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="G20" t="n">
         <v>6.519999980926514</v>
       </c>
       <c r="H20" t="n">
-        <v>8280300</v>
+        <v>11335600</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.04761900369272076</v>
+        <v>-0.07291663488343492</v>
       </c>
       <c r="J20" t="n">
-        <v>6.613333278232151</v>
+        <v>6.594444380866157</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.225804203258704</v>
+        <v>-5.526536289397012</v>
       </c>
       <c r="M20" t="n">
-        <v>6.54399995803833</v>
+        <v>6.526999950408936</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.200486913115209</v>
+        <v>-4.550328383514715</v>
       </c>
       <c r="P20" t="n">
-        <v>6.06115383368272</v>
+        <v>6.054615369209876</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>5.590458037901844</v>
+        <v>2.89671001655218</v>
       </c>
       <c r="S20" t="n">
-        <v>5.770999975204468</v>
+        <v>5.767599973678589</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>10.89932633625905</v>
+        <v>8.017200352055234</v>
       </c>
       <c r="V20" t="n">
-        <v>5.140133320490519</v>
+        <v>5.138999986648559</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>24.51039100201168</v>
+        <v>21.22981193343866</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.260749990940094</v>
+        <v>5.259899990558624</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.65565948561174</v>
+        <v>18.44331698808276</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4852993839405048</v>
+        <v>0.5135189603124447</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6322,13 +6322,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>15.61</v>
+        <v>15.2</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6340,7 +6340,7 @@
         <v>8</v>
       </c>
       <c r="CF20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CG20" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         <v>9</v>
       </c>
       <c r="CI20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
@@ -6360,16 +6360,16 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN20" t="n">
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -6397,7 +6397,7 @@
         <v>2.269999980926514</v>
       </c>
       <c r="H21" t="n">
-        <v>21112400</v>
+        <v>32322200</v>
       </c>
       <c r="I21" t="n">
         <v>0.004291841541072206</v>
@@ -6645,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM21" t="n">
         <v>3</v>
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44.72999954223633</v>
+        <v>44.65999984741211</v>
       </c>
       <c r="D22" t="n">
-        <v>44.72999954223633</v>
+        <v>44.65999984741211</v>
       </c>
       <c r="E22" t="n">
         <v>45.2400016784668</v>
@@ -6682,67 +6682,67 @@
         <v>45.20000076293945</v>
       </c>
       <c r="H22" t="n">
-        <v>953400</v>
+        <v>3749800</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01778659106295355</v>
+        <v>-0.01932369456354555</v>
       </c>
       <c r="J22" t="n">
-        <v>46.07555558946397</v>
+        <v>46.06777784559462</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.920325170284723</v>
+        <v>-3.05588431658449</v>
       </c>
       <c r="M22" t="n">
-        <v>45.92200012207032</v>
+        <v>45.91500015258789</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.595707017693915</v>
+        <v>-2.733312209528652</v>
       </c>
       <c r="P22" t="n">
-        <v>44.2011541219858</v>
+        <v>44.19846182603102</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.196451610270233</v>
+        <v>1.04424000816531</v>
       </c>
       <c r="S22" t="n">
-        <v>45.13940010070801</v>
+        <v>45.13800010681152</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9069694270599304</v>
+        <v>-1.058975271984377</v>
       </c>
       <c r="V22" t="n">
-        <v>46.9013331858317</v>
+        <v>46.90086652119955</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.62957766038793</v>
+        <v>-4.777879045741187</v>
       </c>
       <c r="Y22" t="n">
-        <v>48.01649993896484</v>
+        <v>48.01614994049072</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.844523030429288</v>
+        <v>-6.989627650776016</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.2665562627504393</v>
+        <v>0.2674383510186987</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>8.949999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="CA22" t="n">
         <v>0.5</v>
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.84000015258789</v>
+        <v>15.93000030517578</v>
       </c>
       <c r="D23" t="n">
-        <v>15.84000015258789</v>
+        <v>15.93000030517578</v>
       </c>
       <c r="E23" t="n">
-        <v>15.89000034332275</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
         <v>15.52000045776367</v>
@@ -6965,67 +6965,67 @@
         <v>15.60999965667725</v>
       </c>
       <c r="H23" t="n">
-        <v>12663100</v>
+        <v>18704900</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.007518789804026538</v>
+        <v>-0.001879682512499148</v>
       </c>
       <c r="J23" t="n">
-        <v>15.81666660308838</v>
+        <v>15.82666662004259</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1475250764592559</v>
+        <v>0.6529087116950595</v>
       </c>
       <c r="M23" t="n">
-        <v>15.72999992370606</v>
+        <v>15.73899993896484</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6993021577581741</v>
+        <v>1.213548300092947</v>
       </c>
       <c r="P23" t="n">
-        <v>14.7657691515409</v>
+        <v>14.76923069587121</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7.275144220542582</v>
+        <v>7.859377602037678</v>
       </c>
       <c r="S23" t="n">
-        <v>14.82499998092651</v>
+        <v>14.82679998397827</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>6.846544168413167</v>
+        <v>7.440582744689485</v>
       </c>
       <c r="V23" t="n">
-        <v>14.99519993464152</v>
+        <v>14.99579993565877</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.633804294897956</v>
+        <v>6.229746819278087</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.51869995594025</v>
+        <v>14.51914995670319</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>9.100678439924934</v>
+        <v>9.717169067609463</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1991823404043681</v>
+        <v>0.1974358454563485</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7177,13 +7177,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.41</v>
+        <v>17.51</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
       </c>
       <c r="CB23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="D24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="E24" t="n">
         <v>3.690000057220459</v>
@@ -7248,67 +7248,67 @@
         <v>3.599999904632568</v>
       </c>
       <c r="H24" t="n">
-        <v>18465700</v>
+        <v>24303600</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0189189006326147</v>
+        <v>-0.02702706534118826</v>
       </c>
       <c r="J24" t="n">
-        <v>3.806666665607028</v>
+        <v>3.803333308961657</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.640977702678321</v>
+        <v>-5.346189455706684</v>
       </c>
       <c r="M24" t="n">
-        <v>3.816000008583069</v>
+        <v>3.812999987602234</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.874211051462105</v>
+        <v>-5.586154829851138</v>
       </c>
       <c r="P24" t="n">
-        <v>3.599615399654095</v>
+        <v>3.598461545430697</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8441100343592992</v>
+        <v>0.04275046940059138</v>
       </c>
       <c r="S24" t="n">
-        <v>3.747200021743774</v>
+        <v>3.746600017547607</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.127666167345847</v>
+        <v>-3.912884007591454</v>
       </c>
       <c r="V24" t="n">
-        <v>4.536266670227051</v>
+        <v>4.536066668828329</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-19.97824690806311</v>
+        <v>-20.63608920539846</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.808200011253357</v>
+        <v>4.808050010204315</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-24.50397017709163</v>
+        <v>-25.12557279994705</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5903001610199822</v>
+        <v>0.5926455918284543</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7460,13 +7460,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.91999816894531</v>
+        <v>57.04999923706055</v>
       </c>
       <c r="D25" t="n">
-        <v>56.91999816894531</v>
+        <v>57.04999923706055</v>
       </c>
       <c r="E25" t="n">
-        <v>57.22999954223633</v>
+        <v>57.61999893188477</v>
       </c>
       <c r="F25" t="n">
         <v>54.5</v>
@@ -7535,67 +7535,67 @@
         <v>55.38999938964844</v>
       </c>
       <c r="H25" t="n">
-        <v>1849300</v>
+        <v>2912000</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0173368613544036</v>
+        <v>0.01966038354104405</v>
       </c>
       <c r="J25" t="n">
-        <v>56.33777745564779</v>
+        <v>56.3522220187717</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.033446365107108</v>
+        <v>1.238242598590717</v>
       </c>
       <c r="M25" t="n">
-        <v>56.22599983215332</v>
+        <v>56.23899993896485</v>
       </c>
       <c r="N25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.234301459936197</v>
+        <v>1.442058534070422</v>
       </c>
       <c r="P25" t="n">
-        <v>56.13076928945688</v>
+        <v>56.13576933053824</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.406053915667027</v>
+        <v>1.628604929486485</v>
       </c>
       <c r="S25" t="n">
-        <v>59.88859977722168</v>
+        <v>59.89119979858398</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.956872625707068</v>
+        <v>-4.743936623541496</v>
       </c>
       <c r="V25" t="n">
-        <v>57.19639981587728</v>
+        <v>57.19726648966471</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4832500783646154</v>
+        <v>-0.2574725360883755</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.1389499092102</v>
+        <v>54.13959991455078</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.13687144726461</v>
+        <v>5.37573112306572</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2900229654699051</v>
+        <v>0.291570326925588</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7743,7 +7743,7 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>15.99</v>
+        <v>16.03</v>
       </c>
       <c r="CA25" t="n">
         <v>0.32</v>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.409999847412109</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="D26" t="n">
-        <v>6.409999847412109</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="E26" t="n">
         <v>6.53000020980835</v>
@@ -7818,67 +7818,67 @@
         <v>6.519999980926514</v>
       </c>
       <c r="H26" t="n">
-        <v>18875300</v>
+        <v>27395600</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.03753753839756369</v>
+        <v>-0.04654653902131822</v>
       </c>
       <c r="J26" t="n">
-        <v>6.494444423251682</v>
+        <v>6.487777762942844</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.300258657033708</v>
+        <v>-2.123652556307357</v>
       </c>
       <c r="M26" t="n">
-        <v>6.376999998092652</v>
+        <v>6.371000003814697</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5174823479587242</v>
+        <v>-0.3296201407872402</v>
       </c>
       <c r="P26" t="n">
-        <v>5.358461526724009</v>
+        <v>5.356153836617103</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>19.62388486777057</v>
+        <v>18.55521888152431</v>
       </c>
       <c r="S26" t="n">
-        <v>5.21479998588562</v>
+        <v>5.21359998703003</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>22.91938070034167</v>
+        <v>21.79683751015771</v>
       </c>
       <c r="V26" t="n">
-        <v>6.174333327611287</v>
+        <v>6.173933327992757</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.816873940817774</v>
+        <v>2.851773209819437</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.992900002002716</v>
+        <v>6.992600002288818</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-8.335599742934521</v>
+        <v>-9.189716234961447</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.699241483720031</v>
+        <v>0.705064794406744</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8030,10 +8030,10 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>-4.25</v>
+        <v>-4.21</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="CB26" t="n">
         <v>0.66</v>
@@ -8067,13 +8067,13 @@
         <v>10</v>
       </c>
       <c r="CM26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN26" t="n">
         <v>-1</v>
       </c>
       <c r="CO26" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31.20999908447266</v>
+        <v>30.88999938964844</v>
       </c>
       <c r="D27" t="n">
-        <v>31.20999908447266</v>
+        <v>30.88999938964844</v>
       </c>
       <c r="E27" t="n">
         <v>31.34000015258789</v>
@@ -8101,88 +8101,88 @@
         <v>30.96999931335449</v>
       </c>
       <c r="H27" t="n">
-        <v>3335100</v>
+        <v>4675800</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.01917035248906007</v>
+        <v>-0.02922691119092169</v>
       </c>
       <c r="J27" t="n">
-        <v>32.57111104329427</v>
+        <v>32.53555552164713</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.178893243808587</v>
+        <v>-5.057716413982374</v>
       </c>
       <c r="M27" t="n">
-        <v>32.57399978637695</v>
+        <v>32.54199981689453</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.187390897186491</v>
+        <v>-5.076517843222529</v>
       </c>
       <c r="P27" t="n">
-        <v>31.93961546971248</v>
+        <v>31.92115394885723</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.284361832507654</v>
+        <v>-3.230317302629068</v>
       </c>
       <c r="S27" t="n">
-        <v>31.67540008544922</v>
+        <v>31.7338000869751</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.469282154988012</v>
+        <v>-2.658996700722874</v>
       </c>
       <c r="V27" t="n">
-        <v>33.4092667388916</v>
+        <v>33.4411334101359</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.582807313932417</v>
+        <v>-7.628730728708574</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.68315000534058</v>
+        <v>33.71105000495911</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-7.342397965973479</v>
+        <v>-8.36832615684078</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4346907501476815</v>
+        <v>0.4398009423660922</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AF27" t="n">
         <v>29.5</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>30.9</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>31</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>31.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>31.6</v>
       </c>
       <c r="AJ27" t="n">
         <v>2</v>
@@ -8309,13 +8309,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>9.02</v>
+        <v>8.93</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB27" t="n">
-        <v>6.23</v>
+        <v>6.17</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8347,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="CL27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM27" t="n">
         <v>1</v>
@@ -8356,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="CO27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -8369,13 +8369,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19.95000076293945</v>
+        <v>20.09000015258789</v>
       </c>
       <c r="D28" t="n">
-        <v>19.95000076293945</v>
+        <v>20.09000015258789</v>
       </c>
       <c r="E28" t="n">
-        <v>19.95000076293945</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="F28" t="n">
         <v>19.39999961853027</v>
@@ -8384,67 +8384,67 @@
         <v>19.60000038146973</v>
       </c>
       <c r="H28" t="n">
-        <v>6449400</v>
+        <v>9119800</v>
       </c>
       <c r="I28" t="n">
-        <v>0.006559085273305065</v>
+        <v>0.01362262673667858</v>
       </c>
       <c r="J28" t="n">
-        <v>19.89000002543132</v>
+        <v>19.90555551317003</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3016628327371544</v>
+        <v>0.9265988045188113</v>
       </c>
       <c r="M28" t="n">
-        <v>19.83500003814697</v>
+        <v>19.84899997711182</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5797868644885774</v>
+        <v>1.21416784600723</v>
       </c>
       <c r="P28" t="n">
-        <v>19.06038460364709</v>
+        <v>19.06576919555664</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>4.66735681252803</v>
+        <v>5.372093549049946</v>
       </c>
       <c r="S28" t="n">
-        <v>20.07020004272461</v>
+        <v>20.07300003051758</v>
       </c>
       <c r="T28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5988942787280611</v>
+        <v>0.08469148629735673</v>
       </c>
       <c r="V28" t="n">
-        <v>18.87053342183431</v>
+        <v>18.87146675109863</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>5.720385942329201</v>
+        <v>6.457014802086425</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.28015009403229</v>
+        <v>18.28085009098053</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.134775482244557</v>
+        <v>9.896421953046739</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2464738083144461</v>
+        <v>0.2490389125260893</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8604,13 +8604,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>13.66</v>
+        <v>13.76</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.34000015258789</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="D29" t="n">
-        <v>25.34000015258789</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="E29" t="n">
         <v>25.6200008392334</v>
@@ -8679,67 +8679,67 @@
         <v>25.21999931335449</v>
       </c>
       <c r="H29" t="n">
-        <v>4767500</v>
+        <v>6926800</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.02425872843372157</v>
+        <v>-0.02194839083153577</v>
       </c>
       <c r="J29" t="n">
-        <v>25.46777788798014</v>
+        <v>25.47444449530708</v>
       </c>
       <c r="K29" t="n">
         <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5017231419022238</v>
+        <v>-0.2922335628967937</v>
       </c>
       <c r="M29" t="n">
-        <v>25.35000019073486</v>
+        <v>25.3560001373291</v>
       </c>
       <c r="N29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.03944788193977319</v>
+        <v>0.17352690078431</v>
       </c>
       <c r="P29" t="n">
-        <v>23.44153851729173</v>
+        <v>23.44384618905874</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>8.098707488400366</v>
+        <v>8.343995322680749</v>
       </c>
       <c r="S29" t="n">
-        <v>22.5916000366211</v>
+        <v>22.59280002593994</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>12.16558416186381</v>
+        <v>12.42519559048566</v>
       </c>
       <c r="V29" t="n">
-        <v>24.53033334096273</v>
+        <v>24.53073333740234</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>3.300675944232346</v>
+        <v>3.543580492159805</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.91789999008179</v>
+        <v>25.9181999874115</v>
       </c>
       <c r="Z29" t="n">
         <v>-1</v>
       </c>
       <c r="AA29" t="n">
-        <v>-2.229732492659686</v>
+        <v>-1.999368664231756</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.386148932471657</v>
+        <v>0.3846318719031601</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8887,10 +8887,10 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>5.85</v>
+        <v>5.87</v>
       </c>
       <c r="CA29" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="CB29" t="n">
         <v>1.09</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.19999980926514</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="D30" t="n">
-        <v>10.19999980926514</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="E30" t="n">
         <v>10.3100004196167</v>
@@ -8958,67 +8958,67 @@
         <v>10.19999980926514</v>
       </c>
       <c r="H30" t="n">
-        <v>5621700</v>
+        <v>9469000</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.02578800867980235</v>
+        <v>-0.02769818094143406</v>
       </c>
       <c r="J30" t="n">
-        <v>11.05111122131348</v>
+        <v>11.04888905419244</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.701591224662213</v>
+        <v>-7.864037232656981</v>
       </c>
       <c r="M30" t="n">
-        <v>11.05800008773804</v>
+        <v>11.0560001373291</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-7.759090899486583</v>
+        <v>-7.923297949279366</v>
       </c>
       <c r="P30" t="n">
-        <v>10.89153850995577</v>
+        <v>10.89076929826003</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.349320622229008</v>
+        <v>-6.526343306140954</v>
       </c>
       <c r="S30" t="n">
-        <v>11.48880001068115</v>
+        <v>11.48840002059936</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-11.21788350583018</v>
+        <v>-11.38887671980038</v>
       </c>
       <c r="V30" t="n">
-        <v>13.17946669260661</v>
+        <v>13.17933336257935</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-22.60688503437614</v>
+        <v>-22.75785106035561</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.68830001354218</v>
+        <v>13.68820001602173</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-25.48380880625042</v>
+        <v>-25.62937206308849</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3958993006199691</v>
+        <v>0.3968815520507438</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9166,7 +9166,7 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
@@ -9222,13 +9222,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.27000045776367</v>
+        <v>30.53000068664551</v>
       </c>
       <c r="D31" t="n">
-        <v>30.27000045776367</v>
+        <v>30.53000068664551</v>
       </c>
       <c r="E31" t="n">
-        <v>30.42000007629395</v>
+        <v>30.53000068664551</v>
       </c>
       <c r="F31" t="n">
         <v>30</v>
@@ -9237,88 +9237,88 @@
         <v>30.04000091552734</v>
       </c>
       <c r="H31" t="n">
-        <v>979200</v>
+        <v>1719300</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0156097412109375</v>
+        <v>-0.007154449214780256</v>
       </c>
       <c r="J31" t="n">
-        <v>30.36777771843804</v>
+        <v>30.39666663275825</v>
       </c>
       <c r="K31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3219770033254808</v>
+        <v>0.4386469592148221</v>
       </c>
       <c r="M31" t="n">
-        <v>30.2689998626709</v>
+        <v>30.29499988555908</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.00330567609538598</v>
+        <v>0.7757082091901392</v>
       </c>
       <c r="P31" t="n">
-        <v>29.14999998532809</v>
+        <v>29.18538460364709</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>3.842197162947886</v>
+        <v>4.607155606338639</v>
       </c>
       <c r="S31" t="n">
-        <v>29.9331999206543</v>
+        <v>29.9961999130249</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.125173847106734</v>
+        <v>1.779561328329523</v>
       </c>
       <c r="V31" t="n">
-        <v>32.41853336334228</v>
+        <v>32.44733337402344</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-6.627483364216891</v>
+        <v>-5.909060893468983</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.16327146530151</v>
+        <v>32.17060717582703</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-5.886437919041743</v>
+        <v>-5.099706325761463</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2197317884205117</v>
+        <v>0.2200797256272362</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>30.3</v>
+        <v>31.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>30.4</v>
+        <v>32</v>
       </c>
       <c r="AI31" t="n">
-        <v>31.4</v>
+        <v>39.4</v>
       </c>
       <c r="AJ31" t="n">
         <v>2</v>
@@ -9445,13 +9445,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.45</v>
+        <v>13.57</v>
       </c>
       <c r="CA31" t="n">
         <v>0.71</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CC31" t="n">
         <v>2</v>
@@ -9482,13 +9482,13 @@
         <v>4</v>
       </c>
       <c r="CM31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN31" t="n">
         <v>0</v>
       </c>
       <c r="CO31" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
@@ -9501,13 +9501,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>96.41000366210938</v>
+        <v>96.65000152587891</v>
       </c>
       <c r="D32" t="n">
-        <v>96.41000366210938</v>
+        <v>96.65000152587891</v>
       </c>
       <c r="E32" t="n">
-        <v>96.58000183105469</v>
+        <v>96.84999847412109</v>
       </c>
       <c r="F32" t="n">
         <v>93.65000152587891</v>
@@ -9516,67 +9516,67 @@
         <v>95.11000061035156</v>
       </c>
       <c r="H32" t="n">
-        <v>3617500</v>
+        <v>4482900</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.005467286630379653</v>
+        <v>-0.002991550528406828</v>
       </c>
       <c r="J32" t="n">
-        <v>94.695556640625</v>
+        <v>94.72222306993272</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.810483070489568</v>
+        <v>2.035191313576876</v>
       </c>
       <c r="M32" t="n">
-        <v>94.57500076293945</v>
+        <v>94.5990005493164</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.940262103480726</v>
+        <v>2.168100048259259</v>
       </c>
       <c r="P32" t="n">
-        <v>96.16269243680514</v>
+        <v>96.1719231238732</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2571800134098312</v>
+        <v>0.4971080815238802</v>
       </c>
       <c r="S32" t="n">
-        <v>90.96900009155273</v>
+        <v>90.97380004882812</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>5.981162335609635</v>
+        <v>6.239380430414261</v>
       </c>
       <c r="V32" t="n">
-        <v>83.87739995320638</v>
+        <v>83.87899993896484</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>14.9415739113214</v>
+        <v>15.2255053067001</v>
       </c>
       <c r="Y32" t="n">
-        <v>85.86149990081788</v>
+        <v>85.86269989013672</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.28548741109404</v>
+        <v>12.5634316758555</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2739540204609227</v>
+        <v>0.2733340562953592</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9726,13 +9726,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>42.1</v>
+        <v>42.21</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CC32" t="n">
         <v>8</v>
@@ -9786,10 +9786,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.03000068664551</v>
+        <v>26.89999961853027</v>
       </c>
       <c r="D33" t="n">
-        <v>27.03000068664551</v>
+        <v>26.89999961853027</v>
       </c>
       <c r="E33" t="n">
         <v>27.20000076293945</v>
@@ -9801,67 +9801,67 @@
         <v>26.69000053405762</v>
       </c>
       <c r="H33" t="n">
-        <v>4430200</v>
+        <v>7091800</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.01206140045118276</v>
+        <v>-0.01681290137278901</v>
       </c>
       <c r="J33" t="n">
-        <v>27.36333359612359</v>
+        <v>27.34888903299968</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.218173612901106</v>
+        <v>-1.641344238618848</v>
       </c>
       <c r="M33" t="n">
-        <v>27.2480001449585</v>
+        <v>27.23500003814697</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.8000567276616195</v>
+        <v>-1.230036420589228</v>
       </c>
       <c r="P33" t="n">
-        <v>26.0619231737577</v>
+        <v>26.05692313267635</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>3.714528304122189</v>
+        <v>3.235518182868946</v>
       </c>
       <c r="S33" t="n">
-        <v>26.12080005645752</v>
+        <v>26.11820003509521</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>3.48075337747252</v>
+        <v>2.993313407449786</v>
       </c>
       <c r="V33" t="n">
-        <v>25.01953330993652</v>
+        <v>25.01866663614909</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>8.035591039224244</v>
+        <v>7.51971721651575</v>
       </c>
       <c r="Y33" t="n">
-        <v>23.90760001182556</v>
+        <v>23.90695000648499</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>13.06028490218799</v>
+        <v>12.51957949982492</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2597520528802024</v>
+        <v>0.2621865948013879</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10013,13 +10013,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>40.34</v>
+        <v>40.15</v>
       </c>
       <c r="CA33" t="n">
         <v>0.35</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CC33" t="n">
         <v>10</v>
@@ -10047,16 +10047,16 @@
         <v>0</v>
       </c>
       <c r="CL33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50.88000106811523</v>
+        <v>51.5</v>
       </c>
       <c r="D34" t="n">
-        <v>50.88000106811523</v>
+        <v>51.5</v>
       </c>
       <c r="E34" t="n">
-        <v>51.08000183105469</v>
+        <v>51.5099983215332</v>
       </c>
       <c r="F34" t="n">
         <v>49.86000061035156</v>
@@ -10084,67 +10084,67 @@
         <v>50.20999908447266</v>
       </c>
       <c r="H34" t="n">
-        <v>895900</v>
+        <v>1674400</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.01414453659374515</v>
+        <v>-0.002131381690576806</v>
       </c>
       <c r="J34" t="n">
-        <v>50.9977781507704</v>
+        <v>51.06666692097982</v>
       </c>
       <c r="K34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.2309455174830735</v>
+        <v>0.8485634664402834</v>
       </c>
       <c r="M34" t="n">
-        <v>50.69800033569336</v>
+        <v>50.76000022888184</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3589899625562566</v>
+        <v>1.457840362059559</v>
       </c>
       <c r="P34" t="n">
-        <v>47.43384610689603</v>
+        <v>47.45769221966084</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>7.265181392740132</v>
+        <v>8.517708281365845</v>
       </c>
       <c r="S34" t="n">
-        <v>48.57099990844726</v>
+        <v>48.58339988708496</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>4.753867871817067</v>
+        <v>6.003285319046534</v>
       </c>
       <c r="V34" t="n">
-        <v>50.27780001322429</v>
+        <v>50.28193333943685</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.197747424773069</v>
+        <v>2.422473798571714</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.88671360015869</v>
+        <v>49.88981359481811</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.991086195650663</v>
+        <v>3.227485310446479</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3112862139754534</v>
+        <v>0.3081745133076231</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10292,13 +10292,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>13.46</v>
+        <v>13.62</v>
       </c>
       <c r="CA34" t="n">
         <v>0.26</v>
       </c>
       <c r="CB34" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CC34" t="n">
         <v>5</v>
@@ -10326,16 +10326,16 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.40999984741211</v>
+        <v>39.68000030517578</v>
       </c>
       <c r="D35" t="n">
-        <v>39.40999984741211</v>
+        <v>39.68000030517578</v>
       </c>
       <c r="E35" t="n">
-        <v>39.65999984741211</v>
+        <v>39.79999923706055</v>
       </c>
       <c r="F35" t="n">
         <v>38.31999969482422</v>
@@ -10363,88 +10363,88 @@
         <v>38.59999847412109</v>
       </c>
       <c r="H35" t="n">
-        <v>5620900</v>
+        <v>8168200</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.006053005529146116</v>
+        <v>0.0007565896126711102</v>
       </c>
       <c r="J35" t="n">
-        <v>38.97444449530708</v>
+        <v>39.00444454616971</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.117540885431938</v>
+        <v>1.731996870783316</v>
       </c>
       <c r="M35" t="n">
-        <v>38.7439998626709</v>
+        <v>38.77099990844727</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.718975808129946</v>
+        <v>2.344536893232063</v>
       </c>
       <c r="P35" t="n">
-        <v>36.94576953007625</v>
+        <v>36.95615416306715</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>6.669857871900106</v>
+        <v>7.370480516153803</v>
       </c>
       <c r="S35" t="n">
-        <v>38.0402001953125</v>
+        <v>38.04560020446777</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>3.600926506870492</v>
+        <v>4.295897796129592</v>
       </c>
       <c r="V35" t="n">
-        <v>39.78613342285156</v>
+        <v>39.78793342590332</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.9453886142738807</v>
+        <v>-0.2712709895540067</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.65110006332397</v>
+        <v>39.65245006561279</v>
       </c>
       <c r="Z35" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.6080542923823542</v>
+        <v>0.06947928694797953</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2560727465935089</v>
+        <v>0.2552562375245357</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="AE35" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>39.8</v>
+        <v>41.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>41.2</v>
+        <v>46.3</v>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
@@ -10571,13 +10571,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.04</v>
+        <v>32.26</v>
       </c>
       <c r="CA35" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CC35" t="n">
         <v>8</v>
@@ -10589,7 +10589,7 @@
         <v>2</v>
       </c>
       <c r="CF35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CG35" t="n">
         <v>5</v>
@@ -10598,7 +10598,7 @@
         <v>5</v>
       </c>
       <c r="CI35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CJ35" t="inlineStr"/>
       <c r="CK35" t="n">
@@ -10608,13 +10608,13 @@
         <v>5</v>
       </c>
       <c r="CM35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
@@ -10627,13 +10627,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.3700008392334</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="D36" t="n">
-        <v>21.3700008392334</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="E36" t="n">
-        <v>21.40999984741211</v>
+        <v>21.6299991607666</v>
       </c>
       <c r="F36" t="n">
         <v>20.65999984741211</v>
@@ -10642,67 +10642,67 @@
         <v>20.73999977111816</v>
       </c>
       <c r="H36" t="n">
-        <v>1949900</v>
+        <v>3546400</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01471991363496183</v>
+        <v>0.02374169101041934</v>
       </c>
       <c r="J36" t="n">
-        <v>20.40777778625488</v>
+        <v>20.4288887447781</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>4.714982018407684</v>
+        <v>5.536819624872679</v>
       </c>
       <c r="M36" t="n">
-        <v>20.33500003814697</v>
+        <v>20.35399990081787</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>5.089750671968724</v>
+        <v>5.925123174811704</v>
       </c>
       <c r="P36" t="n">
-        <v>19.20269225193904</v>
+        <v>19.20999989142785</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>11.28648295176166</v>
+        <v>12.23320972304213</v>
       </c>
       <c r="S36" t="n">
-        <v>17.93339992523194</v>
+        <v>17.93719989776611</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>19.16313096417504</v>
+        <v>20.19712992453995</v>
       </c>
       <c r="V36" t="n">
-        <v>16.66099995930989</v>
+        <v>16.66226661682129</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>28.26361497763639</v>
+        <v>29.39415724014774</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.38054999351501</v>
+        <v>16.38149998664856</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>30.45960512738391</v>
+        <v>31.61187610117794</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3712252550422704</v>
+        <v>0.373634587921211</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>16.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -10854,13 +10854,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.42</v>
+        <v>18.59</v>
       </c>
       <c r="CA36" t="n">
         <v>0.27</v>
       </c>
       <c r="CB36" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CC36" t="n">
         <v>9</v>
@@ -10910,82 +10910,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.27000045776367</v>
+        <v>25.34000015258789</v>
       </c>
       <c r="D37" t="n">
-        <v>25.27000045776367</v>
+        <v>25.34000015258789</v>
       </c>
       <c r="E37" t="n">
         <v>25.70000076293945</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>24.98999977111816</v>
       </c>
       <c r="G37" t="n">
         <v>25.3700008392334</v>
       </c>
       <c r="H37" t="n">
-        <v>5637500</v>
+        <v>7548200</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.03180076289559486</v>
+        <v>-0.02911878229018783</v>
       </c>
       <c r="J37" t="n">
-        <v>25.39333343505859</v>
+        <v>25.40111117892795</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4856903785804098</v>
+        <v>-0.2405840670102541</v>
       </c>
       <c r="M37" t="n">
-        <v>25.22800006866455</v>
+        <v>25.23500003814697</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1664832288917376</v>
+        <v>0.4160892184751098</v>
       </c>
       <c r="P37" t="n">
-        <v>24.32769225193904</v>
+        <v>24.33038454789382</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>3.873397427368081</v>
+        <v>4.149608086574493</v>
       </c>
       <c r="S37" t="n">
-        <v>24.18899993896484</v>
+        <v>24.19039993286133</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>4.468975656399494</v>
+        <v>4.752299353946989</v>
       </c>
       <c r="V37" t="n">
-        <v>22.37879998524984</v>
+        <v>22.379266649882</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>12.91937223809794</v>
+        <v>13.2298057350396</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.02079999923706</v>
+        <v>22.02114999771118</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>14.75514267710158</v>
+        <v>15.07119362622598</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.3910419989973974</v>
+        <v>0.3891791026564201</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11137,7 +11137,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>30.45</v>
+        <v>30.53</v>
       </c>
       <c r="CA37" t="n">
         <v>0.16</v>
@@ -11193,82 +11193,82 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.3100004196167</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="D38" t="n">
-        <v>11.3100004196167</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="E38" t="n">
         <v>11.52999973297119</v>
       </c>
       <c r="F38" t="n">
-        <v>11.19999980926514</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="G38" t="n">
         <v>11.35000038146973</v>
       </c>
       <c r="H38" t="n">
-        <v>6387700</v>
+        <v>7998200</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.02751502078034174</v>
+        <v>-0.0352536408751204</v>
       </c>
       <c r="J38" t="n">
-        <v>11.20333353678385</v>
+        <v>11.19333351982964</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9520995021939385</v>
+        <v>0.2382377613596842</v>
       </c>
       <c r="M38" t="n">
-        <v>11.12200021743774</v>
+        <v>11.11300020217896</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.690345248188334</v>
+        <v>0.9628368838585373</v>
       </c>
       <c r="P38" t="n">
-        <v>10.75000003667978</v>
+        <v>10.74653849234948</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>5.209305870010756</v>
+        <v>4.405714221527155</v>
       </c>
       <c r="S38" t="n">
-        <v>10.63980001449585</v>
+        <v>10.63800001144409</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>6.298994381546246</v>
+        <v>5.470955583367322</v>
       </c>
       <c r="V38" t="n">
-        <v>9.876533339818319</v>
+        <v>9.875933338801065</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>14.5138686872974</v>
+        <v>13.60951802850983</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.7020325922966</v>
+        <v>9.701582591533661</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.57351500341096</v>
+        <v>15.651236910772</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3827988392592652</v>
+        <v>0.3885019346684512</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>26.3</v>
+        <v>26.09</v>
       </c>
       <c r="CA38" t="n">
         <v>0.55</v>
@@ -11461,13 +11461,13 @@
         <v>7</v>
       </c>
       <c r="CM38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN38" t="n">
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.78000020980835</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="D39" t="n">
-        <v>6.78000020980835</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="E39" t="n">
         <v>6.829999923706055</v>
@@ -11495,67 +11495,67 @@
         <v>6.619999885559082</v>
       </c>
       <c r="H39" t="n">
-        <v>5734000</v>
+        <v>7299500</v>
       </c>
       <c r="I39" t="n">
-        <v>0.007429448825134966</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>7.00888893339369</v>
+        <v>7.003333356645372</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.26569197715212</v>
+        <v>-3.902903426873484</v>
       </c>
       <c r="M39" t="n">
-        <v>6.969000053405762</v>
+        <v>6.964000034332275</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.712008066423357</v>
+        <v>-3.36013805435349</v>
       </c>
       <c r="P39" t="n">
-        <v>7.231538515824538</v>
+        <v>7.229615431565505</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-6.244014396495326</v>
+        <v>-6.910677576439659</v>
       </c>
       <c r="S39" t="n">
-        <v>8.96640001296997</v>
+        <v>8.965400009155273</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-24.38436607779014</v>
+        <v>-24.93363361142887</v>
       </c>
       <c r="V39" t="n">
-        <v>10.38653332392375</v>
+        <v>10.38619998931885</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-34.72316509887197</v>
+        <v>-35.20247996385002</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.36414999008179</v>
+        <v>11.36389998912811</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-40.33869479260935</v>
+        <v>-40.77737374042271</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.139204453876387</v>
+        <v>1.138202110016387</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11707,10 +11707,10 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>-7.98</v>
+        <v>-7.92</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CB39" t="n">
         <v>0.07000000000000001</v>
@@ -11767,13 +11767,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.35000038146973</v>
+        <v>23.48999977111816</v>
       </c>
       <c r="D40" t="n">
-        <v>23.35000038146973</v>
+        <v>23.48999977111816</v>
       </c>
       <c r="E40" t="n">
-        <v>23.5</v>
+        <v>23.59000015258789</v>
       </c>
       <c r="F40" t="n">
         <v>22</v>
@@ -11782,88 +11782,88 @@
         <v>22.22999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>1588300</v>
+        <v>2951800</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02592267779677759</v>
+        <v>0.03207379327307636</v>
       </c>
       <c r="J40" t="n">
-        <v>22.74666659037272</v>
+        <v>22.76222207811144</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>2.652405303871463</v>
+        <v>3.197305124733728</v>
       </c>
       <c r="M40" t="n">
-        <v>22.6420000076294</v>
+        <v>22.65599994659424</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.126933899839966</v>
+        <v>3.681143301950334</v>
       </c>
       <c r="P40" t="n">
-        <v>21.84538459777832</v>
+        <v>21.85076918968787</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>6.887568295979674</v>
+        <v>7.501935365295512</v>
       </c>
       <c r="S40" t="n">
-        <v>21.41060009002685</v>
+        <v>21.41340007781982</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.058131408218928</v>
+        <v>9.697664479959446</v>
       </c>
       <c r="V40" t="n">
-        <v>22.07306668599447</v>
+        <v>22.07400001525879</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>5.785030751007904</v>
+        <v>6.414785516356599</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.64545001983642</v>
+        <v>22.64615001678467</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.111222612119198</v>
+        <v>3.726239355069452</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2536878735792527</v>
+        <v>0.2590373408228859</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AI40" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AJ40" t="n">
         <v>2</v>
@@ -11990,13 +11990,13 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>9.77</v>
+        <v>9.83</v>
       </c>
       <c r="CA40" t="n">
         <v>0.38</v>
       </c>
       <c r="CB40" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CC40" t="n">
         <v>4</v>
@@ -12046,10 +12046,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.73999977111816</v>
+        <v>25.93000030517578</v>
       </c>
       <c r="D41" t="n">
-        <v>25.73999977111816</v>
+        <v>25.93000030517578</v>
       </c>
       <c r="E41" t="n">
         <v>25.97999954223633</v>
@@ -12061,88 +12061,88 @@
         <v>25.36000061035156</v>
       </c>
       <c r="H41" t="n">
-        <v>872000</v>
+        <v>1451900</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.01265822506977521</v>
+        <v>-0.005370133919726627</v>
       </c>
       <c r="J41" t="n">
-        <v>26.09333335028754</v>
+        <v>26.11444452073839</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.354114380198521</v>
+        <v>-0.7062919351630603</v>
       </c>
       <c r="M41" t="n">
-        <v>25.93700008392334</v>
+        <v>25.9560001373291</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.7595339174451565</v>
+        <v>-0.100168870456773</v>
       </c>
       <c r="P41" t="n">
-        <v>24.63269226367657</v>
+        <v>24.63999997652494</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>4.495276016070853</v>
+        <v>5.23539094918771</v>
       </c>
       <c r="S41" t="n">
-        <v>24.91020000457764</v>
+        <v>24.91400001525879</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>3.331164608827066</v>
+        <v>4.078029578930456</v>
       </c>
       <c r="V41" t="n">
-        <v>26.40479996999105</v>
+        <v>26.4060666402181</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-2.517724806203526</v>
+        <v>-1.802867278677695</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.42519995689392</v>
+        <v>26.42614995956421</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-2.592980135981895</v>
+        <v>-1.877495038617463</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3255535117621575</v>
+        <v>0.3234968555242734</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="AF41" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AG41" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="AH41" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12269,13 +12269,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>10.72</v>
+        <v>10.8</v>
       </c>
       <c r="CA41" t="n">
         <v>0.04</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CC41" t="n">
         <v>7</v>
@@ -12306,13 +12306,13 @@
         <v>5</v>
       </c>
       <c r="CM41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN41" t="n">
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
@@ -12325,10 +12325,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.36000061035156</v>
+        <v>27.32999992370605</v>
       </c>
       <c r="D42" t="n">
-        <v>27.36000061035156</v>
+        <v>27.32999992370605</v>
       </c>
       <c r="E42" t="n">
         <v>27.45999908447266</v>
@@ -12340,67 +12340,67 @@
         <v>27.11000061035156</v>
       </c>
       <c r="H42" t="n">
-        <v>1277400</v>
+        <v>1907300</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.01298696651949394</v>
+        <v>-0.01406924239931528</v>
       </c>
       <c r="J42" t="n">
-        <v>27.63222206963433</v>
+        <v>27.62888866000705</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.9851594945812142</v>
+        <v>-1.081797896321619</v>
       </c>
       <c r="M42" t="n">
-        <v>27.53199977874756</v>
+        <v>27.52899971008301</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.6247245742343954</v>
+        <v>-0.7228732917021476</v>
       </c>
       <c r="P42" t="n">
-        <v>26.55346151498648</v>
+        <v>26.55230764242319</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>3.03741602543941</v>
+        <v>2.928906563436799</v>
       </c>
       <c r="S42" t="n">
-        <v>27.13780006408691</v>
+        <v>27.137200050354</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0.8187861423546263</v>
+        <v>0.7104633970870403</v>
       </c>
       <c r="V42" t="n">
-        <v>28.19033335367839</v>
+        <v>28.19013334910075</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.945452020412094</v>
+        <v>-3.051186082531003</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98115001678467</v>
+        <v>27.98100001335144</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-2.21988519435586</v>
+        <v>-2.326579069135321</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1761097994785612</v>
+        <v>0.1768636732591779</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12548,7 +12548,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.69</v>
+        <v>7.68</v>
       </c>
       <c r="CA42" t="n">
         <v>0.83</v>
@@ -12604,13 +12604,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.02000045776367</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="D43" t="n">
-        <v>14.02000045776367</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="E43" t="n">
-        <v>14.09000015258789</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="F43" t="n">
         <v>13.84000015258789</v>
@@ -12619,67 +12619,67 @@
         <v>13.90999984741211</v>
       </c>
       <c r="H43" t="n">
-        <v>11579500</v>
+        <v>16112800</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01198020631759855</v>
+        <v>-0.007751914019033079</v>
       </c>
       <c r="J43" t="n">
-        <v>13.88999981350369</v>
+        <v>13.89666642083062</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.9359297768571457</v>
+        <v>1.31926245707837</v>
       </c>
       <c r="M43" t="n">
-        <v>13.81099987030029</v>
+        <v>13.81699981689453</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.513290778554143</v>
+        <v>1.903453067213214</v>
       </c>
       <c r="P43" t="n">
-        <v>13.0926921917842</v>
+        <v>13.09499986355121</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>7.082640089571256</v>
+        <v>7.521955482386097</v>
       </c>
       <c r="S43" t="n">
-        <v>13.38219989776611</v>
+        <v>13.38339988708496</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>4.766036711976077</v>
+        <v>5.204955710045815</v>
       </c>
       <c r="V43" t="n">
-        <v>13.55186663945516</v>
+        <v>13.55226663589477</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>3.454386253666184</v>
+        <v>3.894059215257147</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.2309695482254</v>
+        <v>13.23126954555512</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>5.963515422375811</v>
+        <v>6.414580061488206</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2482282951456621</v>
+        <v>0.2466641484070684</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12831,13 +12831,13 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>9.279999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="CA43" t="n">
         <v>0.03</v>
       </c>
       <c r="CB43" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CC43" t="n">
         <v>2</v>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.27999877929688</v>
+        <v>42.5099983215332</v>
       </c>
       <c r="D44" t="n">
-        <v>42.27999877929688</v>
+        <v>42.5099983215332</v>
       </c>
       <c r="E44" t="n">
-        <v>42.5</v>
+        <v>42.58000183105469</v>
       </c>
       <c r="F44" t="n">
         <v>41.65000152587891</v>
@@ -12906,88 +12906,88 @@
         <v>41.86000061035156</v>
       </c>
       <c r="H44" t="n">
-        <v>14423400</v>
+        <v>19844000</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.01053126065434784</v>
+        <v>-0.005148636158670339</v>
       </c>
       <c r="J44" t="n">
-        <v>41.83444383409288</v>
+        <v>41.8599993387858</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.065043309697094</v>
+        <v>1.552792625453138</v>
       </c>
       <c r="M44" t="n">
-        <v>41.60299949645996</v>
+        <v>41.62599945068359</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.627284789632833</v>
+        <v>2.123670019976162</v>
       </c>
       <c r="P44" t="n">
-        <v>39.95769177950346</v>
+        <v>39.96653791574332</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>5.811914793798626</v>
+        <v>6.363974811008051</v>
       </c>
       <c r="S44" t="n">
-        <v>41.24679969787598</v>
+        <v>41.2513996887207</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>2.504919385234393</v>
+        <v>3.051044673174172</v>
       </c>
       <c r="V44" t="n">
-        <v>42.41659985860189</v>
+        <v>42.41813318888347</v>
       </c>
       <c r="W44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.3220462737710799</v>
+        <v>0.2165704281248567</v>
       </c>
       <c r="Y44" t="n">
-        <v>41.99411874771118</v>
+        <v>41.99526874542236</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.6807620688582077</v>
+        <v>1.22568468184156</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2685714365959957</v>
+        <v>0.2672462164201708</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="AE44" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="AF44" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="AG44" t="n">
-        <v>42.3</v>
+        <v>44</v>
       </c>
       <c r="AH44" t="n">
-        <v>42.9</v>
+        <v>44.3</v>
       </c>
       <c r="AI44" t="n">
-        <v>44</v>
+        <v>49.7</v>
       </c>
       <c r="AJ44" t="n">
         <v>3</v>
@@ -13134,13 +13134,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.04</v>
+        <v>10.1</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CC44" t="n">
         <v>10</v>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="CL44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM44" t="n">
         <v>8</v>
@@ -13181,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.29000091552734</v>
+        <v>19.26000022888184</v>
       </c>
       <c r="D45" t="n">
-        <v>19.29000091552734</v>
+        <v>19.26000022888184</v>
       </c>
       <c r="E45" t="n">
         <v>19.43000030517578</v>
@@ -13209,67 +13209,67 @@
         <v>19.25</v>
       </c>
       <c r="H45" t="n">
-        <v>1634300</v>
+        <v>2125700</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.01279426756839808</v>
+        <v>-0.01432961481711126</v>
       </c>
       <c r="J45" t="n">
-        <v>19.45777787102593</v>
+        <v>19.45444446139865</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.8622616447298481</v>
+        <v>-0.9994848884152595</v>
       </c>
       <c r="M45" t="n">
-        <v>19.40200004577637</v>
+        <v>19.39899997711182</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.5772555921285343</v>
+        <v>-0.7165304829835661</v>
       </c>
       <c r="P45" t="n">
-        <v>18.59038463005653</v>
+        <v>18.58923075749324</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>3.763323349102166</v>
+        <v>3.608376700139737</v>
       </c>
       <c r="S45" t="n">
-        <v>18.16240001678467</v>
+        <v>18.16180000305176</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.208435546517029</v>
+        <v>6.04675872240386</v>
       </c>
       <c r="V45" t="n">
-        <v>18.22293333689372</v>
+        <v>18.22273333231608</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>5.855630149693114</v>
+        <v>5.692158677020593</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.31516777038574</v>
+        <v>18.31501776695251</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>5.322545539101392</v>
+        <v>5.159604396532121</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.1959318233179495</v>
+        <v>0.1969816676276432</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13421,7 +13421,7 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.15</v>
+        <v>32.1</v>
       </c>
       <c r="CA45" t="n">
         <v>0.21</v>
@@ -13439,7 +13439,7 @@
         <v>7</v>
       </c>
       <c r="CF45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CG45" t="n">
         <v>3</v>
@@ -13448,7 +13448,7 @@
         <v>3</v>
       </c>
       <c r="CI45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CJ45" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="CO45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46">
@@ -13496,7 +13496,7 @@
         <v>11.03999996185303</v>
       </c>
       <c r="H46" t="n">
-        <v>8469700</v>
+        <v>11247700</v>
       </c>
       <c r="I46" t="n">
         <v>-0.005295628097652938</v>
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.95000076293945</v>
+        <v>17.1299991607666</v>
       </c>
       <c r="D47" t="n">
-        <v>16.95000076293945</v>
+        <v>17.1299991607666</v>
       </c>
       <c r="E47" t="n">
-        <v>17.07999992370605</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="F47" t="n">
         <v>16.80999946594238</v>
@@ -13783,88 +13783,88 @@
         <v>16.86000061035156</v>
       </c>
       <c r="H47" t="n">
-        <v>1169900</v>
+        <v>2127600</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.008191889315298684</v>
+        <v>0.002340491973176206</v>
       </c>
       <c r="J47" t="n">
-        <v>17.6188890669081</v>
+        <v>17.63888888888889</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-3.79642724026768</v>
+        <v>-2.885044127937379</v>
       </c>
       <c r="M47" t="n">
-        <v>17.68300018310547</v>
+        <v>17.70100002288818</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-4.145220904687501</v>
+        <v>-3.225811317910023</v>
       </c>
       <c r="P47" t="n">
-        <v>17.4584615780757</v>
+        <v>17.46538459337675</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.912403322952427</v>
+        <v>-1.920286557774004</v>
       </c>
       <c r="S47" t="n">
-        <v>16.7646000289917</v>
+        <v>16.76819999694824</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1.105906097533699</v>
+        <v>2.157650575996275</v>
       </c>
       <c r="V47" t="n">
-        <v>17.57406671524048</v>
+        <v>17.57526670455933</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-3.551061700248497</v>
+        <v>-2.533489541169887</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.04600006580353</v>
+        <v>18.04690005779266</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-6.073364174152655</v>
+        <v>-5.080655924783837</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4635349406973164</v>
+        <v>0.4630673645230899</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>15.9</v>
+        <v>16.7</v>
       </c>
       <c r="AE47" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AI47" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="AJ47" t="n">
         <v>2</v>
@@ -13991,13 +13991,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>62.78</v>
+        <v>63.44</v>
       </c>
       <c r="CA47" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CC47" t="n">
         <v>7</v>
@@ -14032,13 +14032,13 @@
         <v>4</v>
       </c>
       <c r="CM47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN47" t="n">
         <v>0</v>
       </c>
       <c r="CO47" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
@@ -14051,10 +14051,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.679999828338623</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="D48" t="n">
-        <v>5.679999828338623</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="E48" t="n">
         <v>5.710000038146973</v>
@@ -14066,67 +14066,67 @@
         <v>5.599999904632568</v>
       </c>
       <c r="H48" t="n">
-        <v>12327700</v>
+        <v>17746600</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.01388895787574351</v>
+        <v>-0.03298611973446797</v>
       </c>
       <c r="J48" t="n">
-        <v>5.572222232818604</v>
+        <v>5.560000048743354</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1.934194133271355</v>
+        <v>0.1798583242869446</v>
       </c>
       <c r="M48" t="n">
-        <v>5.496000003814697</v>
+        <v>5.485000038146973</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>3.347886178970413</v>
+        <v>1.549683371435673</v>
       </c>
       <c r="P48" t="n">
-        <v>4.751538487581106</v>
+        <v>4.756923116170443</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>19.54022561711742</v>
+        <v>17.09249940843066</v>
       </c>
       <c r="S48" t="n">
-        <v>4.794800038337708</v>
+        <v>4.795200037956238</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>18.46166227836693</v>
+        <v>16.15782715157316</v>
       </c>
       <c r="V48" t="n">
-        <v>6.785866656303406</v>
+        <v>6.820666654904683</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-16.29661889889246</v>
+        <v>-18.33642584400402</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.415440393686294</v>
+        <v>7.439147533178329</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-23.40306810132642</v>
+        <v>-25.12582729648287</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.843852874127924</v>
+        <v>0.8518453954815262</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14278,13 +14278,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>31.56</v>
+        <v>30.94</v>
       </c>
       <c r="CA48" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="CB48" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="CC48" t="n">
         <v>2</v>
@@ -14319,13 +14319,13 @@
         <v>10</v>
       </c>
       <c r="CM48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CN48" t="n">
         <v>-1</v>
       </c>
       <c r="CO48" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49">
@@ -14338,10 +14338,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.43000030517578</v>
+        <v>16.42000007629395</v>
       </c>
       <c r="D49" t="n">
-        <v>16.43000030517578</v>
+        <v>16.42000007629395</v>
       </c>
       <c r="E49" t="n">
         <v>16.53000068664551</v>
@@ -14353,67 +14353,67 @@
         <v>16.14999961853027</v>
       </c>
       <c r="H49" t="n">
-        <v>6323800</v>
+        <v>9003400</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.006650580668849715</v>
+        <v>-0.007255189394865469</v>
       </c>
       <c r="J49" t="n">
-        <v>16.37777784135606</v>
+        <v>16.37666670481364</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.318861718149874</v>
+        <v>0.2646043438593502</v>
       </c>
       <c r="M49" t="n">
-        <v>16.28600006103516</v>
+        <v>16.28500003814697</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8841965098916466</v>
+        <v>0.8289839596606761</v>
       </c>
       <c r="P49" t="n">
-        <v>15.08076924544114</v>
+        <v>15.08038462125338</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>8.946699188720133</v>
+        <v>8.883165043102366</v>
       </c>
       <c r="S49" t="n">
-        <v>14.90720001220703</v>
+        <v>14.90700000762939</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>10.21519998203403</v>
+        <v>10.1495946058241</v>
       </c>
       <c r="V49" t="n">
-        <v>15.27993336995443</v>
+        <v>15.27986670176188</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>7.52664888894593</v>
+        <v>7.461670947696152</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.41295001506805</v>
+        <v>15.41290001392364</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>6.598673771818087</v>
+        <v>6.534137387905652</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3012672607680366</v>
+        <v>0.3014537018514246</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="CA49" t="n">
         <v>0.93</v>
@@ -14606,13 +14606,13 @@
         <v>9</v>
       </c>
       <c r="CM49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.550000190734863</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="D50" t="n">
-        <v>5.550000190734863</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="E50" t="n">
         <v>5.630000114440918</v>
@@ -14640,67 +14640,67 @@
         <v>5.579999923706055</v>
       </c>
       <c r="H50" t="n">
-        <v>9308400</v>
+        <v>11603900</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.03310097351211017</v>
+        <v>-0.03484317373521018</v>
       </c>
       <c r="J50" t="n">
-        <v>5.648888852861193</v>
+        <v>5.647777716318767</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.750586083424916</v>
+        <v>-1.908321465172482</v>
       </c>
       <c r="M50" t="n">
-        <v>5.634999990463257</v>
+        <v>5.633999967575074</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-1.508425907227121</v>
+        <v>-1.668441715708861</v>
       </c>
       <c r="P50" t="n">
-        <v>5.173846189792339</v>
+        <v>5.173461565604577</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>7.270297321258819</v>
+        <v>7.084973795598619</v>
       </c>
       <c r="S50" t="n">
-        <v>4.965200023651123</v>
+        <v>4.965000019073487</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>11.77797801293233</v>
+        <v>11.58106627533993</v>
       </c>
       <c r="V50" t="n">
-        <v>6.487666670481364</v>
+        <v>6.487600002288819</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-14.45306189994081</v>
+        <v>-14.60632653217644</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.918750014305115</v>
+        <v>6.918700013160706</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-19.78319524105138</v>
+        <v>-19.92715464877974</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.5975202517556031</v>
+        <v>0.5985295977776817</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14848,7 +14848,7 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.11</v>
+        <v>-4.1</v>
       </c>
       <c r="CA50" t="n">
         <v>2.54</v>
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>29.79999923706055</v>
+        <v>30.02000045776367</v>
       </c>
       <c r="D51" t="n">
-        <v>29.79999923706055</v>
+        <v>30.02000045776367</v>
       </c>
       <c r="E51" t="n">
         <v>30.04999923706055</v>
@@ -14923,86 +14923,88 @@
         <v>29.18000030517578</v>
       </c>
       <c r="H51" t="n">
-        <v>1751500</v>
+        <v>3114200</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.008979064200328013</v>
+        <v>-0.001662761475489938</v>
       </c>
       <c r="J51" t="n">
-        <v>29.86444452073839</v>
+        <v>29.88888910081651</v>
       </c>
       <c r="K51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.2157926749084162</v>
+        <v>0.4386625294266188</v>
       </c>
       <c r="M51" t="n">
-        <v>29.67000007629395</v>
+        <v>29.69200019836426</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.4381501868295231</v>
+        <v>1.104675526095015</v>
       </c>
       <c r="P51" t="n">
-        <v>28.09615391951341</v>
+        <v>28.10461550492507</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>6.064336501103019</v>
+        <v>6.815197142629298</v>
       </c>
       <c r="S51" t="n">
-        <v>28.40720008850097</v>
+        <v>28.41160011291504</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>4.902979329959966</v>
+        <v>5.661069205734398</v>
       </c>
       <c r="V51" t="n">
-        <v>30.33226669311523</v>
+        <v>30.33373336791992</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-1.754789582459723</v>
+        <v>-1.034270679282906</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.10380003929138</v>
+        <v>30.1049000453949</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-1.009177585003606</v>
+        <v>-0.2820125212281323</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2648019718610619</v>
+        <v>0.2629948174121735</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="AH51" t="n">
         <v>36</v>
       </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
       <c r="AI51" t="inlineStr">
         <is>
           <t>Foguete</t>
@@ -15012,7 +15014,7 @@
         <v>1</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
@@ -15133,13 +15135,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.52</v>
+        <v>12.61</v>
       </c>
       <c r="CA51" t="n">
         <v>0.29</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CC51" t="n">
         <v>8</v>
@@ -15174,13 +15176,13 @@
         <v>7</v>
       </c>
       <c r="CM51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -15193,10 +15195,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.090000152587891</v>
+        <v>8.069999694824219</v>
       </c>
       <c r="D52" t="n">
-        <v>8.090000152587891</v>
+        <v>8.069999694824219</v>
       </c>
       <c r="E52" t="n">
         <v>8.239999771118164</v>
@@ -15208,67 +15210,67 @@
         <v>8.220000267028809</v>
       </c>
       <c r="H52" t="n">
-        <v>5591800</v>
+        <v>7150200</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.02881149739691558</v>
+        <v>-0.03121251275668202</v>
       </c>
       <c r="J52" t="n">
-        <v>8.75</v>
+        <v>8.747777726915148</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.542855398995536</v>
+        <v>-7.748002444158391</v>
       </c>
       <c r="M52" t="n">
-        <v>8.748999977111817</v>
+        <v>8.746999931335449</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-7.532287418538461</v>
+        <v>-7.739799266328207</v>
       </c>
       <c r="P52" t="n">
-        <v>8.3873076072106</v>
+        <v>8.386538358835073</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.544730544604241</v>
+        <v>-3.774366138531838</v>
       </c>
       <c r="S52" t="n">
-        <v>8.423400039672851</v>
+        <v>8.423000030517578</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.95802034231665</v>
+        <v>-4.190909823274307</v>
       </c>
       <c r="V52" t="n">
-        <v>9.116066643397014</v>
+        <v>9.115933307011922</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-11.25558347637057</v>
+        <v>-11.47368653282245</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.811149973869323</v>
+        <v>8.811049971580506</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-8.184514205524836</v>
+        <v>-8.410465031369682</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4411671550595475</v>
+        <v>0.4425442582303413</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15420,7 +15422,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>-4.79</v>
+        <v>-4.78</v>
       </c>
       <c r="CA52" t="n">
         <v>0.36</v>
@@ -15480,82 +15482,82 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.34999847412109</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="D53" t="n">
-        <v>54.34999847412109</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="E53" t="n">
         <v>55.2599983215332</v>
       </c>
       <c r="F53" t="n">
-        <v>54.18999862670898</v>
+        <v>54.13000106811523</v>
       </c>
       <c r="G53" t="n">
         <v>55.06000137329102</v>
       </c>
       <c r="H53" t="n">
-        <v>5827200</v>
+        <v>7637400</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.003118158147747629</v>
+        <v>0.001650773144391549</v>
       </c>
       <c r="J53" t="n">
-        <v>53.43777762518989</v>
+        <v>53.46666675143771</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1.707071082426894</v>
+        <v>2.138404969640462</v>
       </c>
       <c r="M53" t="n">
-        <v>53.12299995422363</v>
+        <v>53.14900016784668</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>2.309731229325857</v>
+        <v>2.748876625883807</v>
       </c>
       <c r="P53" t="n">
-        <v>49.49346131544847</v>
+        <v>49.50346139761118</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>9.812482355435392</v>
+        <v>10.31551949817151</v>
       </c>
       <c r="S53" t="n">
-        <v>47.93079971313477</v>
+        <v>47.93599975585938</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>13.39263855267417</v>
+        <v>13.92273216055414</v>
       </c>
       <c r="V53" t="n">
-        <v>47.87139994303386</v>
+        <v>47.87313329060873</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>13.53333835817766</v>
+        <v>14.07233422313807</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.51659998893738</v>
+        <v>44.51789999961853</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>22.08928464354279</v>
+        <v>22.6697589302719</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3402477601971097</v>
+        <v>0.3397031450879363</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15707,13 +15709,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>6.51</v>
+        <v>6.54</v>
       </c>
       <c r="CA53" t="n">
         <v>0.46</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CC53" t="n">
         <v>1</v>
@@ -15741,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CM53" t="n">
         <v>9</v>
@@ -15750,7 +15752,7 @@
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54">
@@ -15763,82 +15765,82 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>48.88999938964844</v>
+        <v>49.11000061035156</v>
       </c>
       <c r="D54" t="n">
-        <v>48.88999938964844</v>
+        <v>49.11000061035156</v>
       </c>
       <c r="E54" t="n">
         <v>49.72999954223633</v>
       </c>
       <c r="F54" t="n">
-        <v>48.7400016784668</v>
+        <v>48.61000061035156</v>
       </c>
       <c r="G54" t="n">
         <v>49.5099983215332</v>
       </c>
       <c r="H54" t="n">
-        <v>24134900</v>
+        <v>29994300</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.002244910415338031</v>
+        <v>0.00224491041533792</v>
       </c>
       <c r="J54" t="n">
-        <v>48.13999981350369</v>
+        <v>48.16444439358182</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1.557955087349966</v>
+        <v>1.963183067249803</v>
       </c>
       <c r="M54" t="n">
-        <v>47.82799987792968</v>
+        <v>47.85</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>2.22045562103636</v>
+        <v>2.633230115677244</v>
       </c>
       <c r="P54" t="n">
-        <v>44.47846148564265</v>
+        <v>44.48692307105431</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>9.918368928812427</v>
+        <v>10.39199211847781</v>
       </c>
       <c r="S54" t="n">
-        <v>42.89</v>
+        <v>42.89440002441406</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>13.98927346618894</v>
+        <v>14.49047097616423</v>
       </c>
       <c r="V54" t="n">
-        <v>43.23599995930989</v>
+        <v>43.23746663411458</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>13.07706410320015</v>
+        <v>13.58204916567318</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.56180003166199</v>
+        <v>40.5629000377655</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>20.53212468747829</v>
+        <v>21.07122657558608</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3224959779048094</v>
+        <v>0.3219829447687988</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -15990,7 +15992,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="CA54" t="n">
         <v>0.51</v>
@@ -16046,10 +16048,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.429999828338623</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="D55" t="n">
-        <v>4.429999828338623</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="E55" t="n">
         <v>4.480000019073486</v>
@@ -16061,67 +16063,67 @@
         <v>4.440000057220459</v>
       </c>
       <c r="H55" t="n">
-        <v>7808000</v>
+        <v>11198700</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.01555559370252824</v>
+        <v>-0.008888880411783817</v>
       </c>
       <c r="J55" t="n">
-        <v>4.529999944898817</v>
+        <v>4.533333301544189</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-2.207508118687795</v>
+        <v>-1.61764552745851</v>
       </c>
       <c r="M55" t="n">
-        <v>4.516999959945679</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.926060048229487</v>
+        <v>-1.327432367980722</v>
       </c>
       <c r="P55" t="n">
-        <v>4.408846139907837</v>
+        <v>4.409999994131235</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4798010127708456</v>
+        <v>1.133787847670678</v>
       </c>
       <c r="S55" t="n">
-        <v>4.845799980163574</v>
+        <v>4.846399984359741</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-8.580629690186163</v>
+        <v>-7.972927275085734</v>
       </c>
       <c r="V55" t="n">
-        <v>5.774733320871989</v>
+        <v>5.774933322270711</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-23.28650377105743</v>
+        <v>-22.76967041425</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.829254477024079</v>
+        <v>5.82940447807312</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-24.00400693091368</v>
+        <v>-23.49132651674905</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4610393875331076</v>
+        <v>0.4601931059511786</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16273,13 +16275,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="CA55" t="n">
         <v>0.28</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CC55" t="n">
         <v>9</v>
@@ -16333,10 +16335,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>64</v>
+        <v>64.01000213623047</v>
       </c>
       <c r="D56" t="n">
-        <v>64</v>
+        <v>64.01000213623047</v>
       </c>
       <c r="E56" t="n">
         <v>65.34999847412109</v>
@@ -16348,67 +16350,67 @@
         <v>65.19999694824219</v>
       </c>
       <c r="H56" t="n">
-        <v>5364200</v>
+        <v>6671300</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.002960000532476803</v>
+        <v>-0.002804179752759595</v>
       </c>
       <c r="J56" t="n">
-        <v>62.9988899230957</v>
+        <v>63.00000127156576</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1.589091614354438</v>
+        <v>1.603175943300436</v>
       </c>
       <c r="M56" t="n">
-        <v>62.96700096130371</v>
+        <v>62.96800117492675</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>1.640540319414478</v>
+        <v>1.654810287544316</v>
       </c>
       <c r="P56" t="n">
-        <v>61.4938465998723</v>
+        <v>61.49423129741962</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>4.075453949782522</v>
+        <v>4.091068033102497</v>
       </c>
       <c r="S56" t="n">
-        <v>59.68980018615723</v>
+        <v>59.69000022888184</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>7.220998898304837</v>
+        <v>7.237396365862871</v>
       </c>
       <c r="V56" t="n">
-        <v>60.73800003051758</v>
+        <v>60.73806671142578</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>5.370608133036066</v>
+        <v>5.386960109135621</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.1904999923706</v>
+        <v>56.19055000305175</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.89825683823733</v>
+        <v>13.91595585512873</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3824950610177792</v>
+        <v>0.3824779041433548</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16616,10 +16618,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50.06000137329102</v>
+        <v>50.20999908447266</v>
       </c>
       <c r="D57" t="n">
-        <v>50.06000137329102</v>
+        <v>50.20999908447266</v>
       </c>
       <c r="E57" t="n">
         <v>50.29000091552734</v>
@@ -16631,91 +16633,91 @@
         <v>50.0099983215332</v>
       </c>
       <c r="H57" t="n">
-        <v>619800</v>
+        <v>893000</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.01203861886121305</v>
+        <v>-0.00907833236817801</v>
       </c>
       <c r="J57" t="n">
-        <v>50.81000010172526</v>
+        <v>50.82666651407877</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.476084878828363</v>
+        <v>-1.213275376686966</v>
       </c>
       <c r="M57" t="n">
-        <v>50.63700027465821</v>
+        <v>50.65200004577637</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.139480810943604</v>
+        <v>-0.8726229189454657</v>
       </c>
       <c r="P57" t="n">
-        <v>48.95230777447041</v>
+        <v>48.95807691720816</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.262801590323172</v>
+        <v>2.557131011051745</v>
       </c>
       <c r="S57" t="n">
-        <v>51.43840019226074</v>
+        <v>51.44140014648438</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.679707793822713</v>
+        <v>-2.393793828521747</v>
       </c>
       <c r="V57" t="n">
-        <v>50.91180010477702</v>
+        <v>50.91280008951823</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-1.673087044129236</v>
+        <v>-1.380401399667394</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.23495008468628</v>
+        <v>50.23570007324219</v>
       </c>
       <c r="Z57" t="n">
         <v>-1</v>
       </c>
       <c r="AA57" t="n">
-        <v>-0.348260944024703</v>
+        <v>-0.05116080542733094</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.257059538270494</v>
+        <v>0.2562793193561825</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="AE57" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="AG57" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="AH57" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="AI57" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK57" t="n">
         <v>0</v>
@@ -16839,13 +16841,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.779999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="CA57" t="n">
         <v>-0.4</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CC57" t="n">
         <v>7</v>
@@ -16877,7 +16879,7 @@
         <v>0</v>
       </c>
       <c r="CL57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM57" t="n">
         <v>4</v>
@@ -16886,7 +16888,7 @@
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
@@ -16899,13 +16901,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>19.6200008392334</v>
+        <v>19.6299991607666</v>
       </c>
       <c r="D58" t="n">
-        <v>19.6200008392334</v>
+        <v>19.6299991607666</v>
       </c>
       <c r="E58" t="n">
-        <v>19.73999977111816</v>
+        <v>19.77000045776367</v>
       </c>
       <c r="F58" t="n">
         <v>18.90999984741211</v>
@@ -16914,67 +16916,67 @@
         <v>18.90999984741211</v>
       </c>
       <c r="H58" t="n">
-        <v>4289400</v>
+        <v>6234300</v>
       </c>
       <c r="I58" t="n">
-        <v>0.003067554955483942</v>
+        <v>0.003578716602017362</v>
       </c>
       <c r="J58" t="n">
-        <v>19.90000004238552</v>
+        <v>19.90111096700032</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.407031168621853</v>
+        <v>-1.36229483209895</v>
       </c>
       <c r="M58" t="n">
-        <v>19.87000007629394</v>
+        <v>19.87099990844727</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.258174313541194</v>
+        <v>-1.212826474717132</v>
       </c>
       <c r="P58" t="n">
-        <v>19.01884614504301</v>
+        <v>19.01923069587121</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>3.160836833138134</v>
+        <v>3.211320555820285</v>
       </c>
       <c r="S58" t="n">
-        <v>18.747200050354</v>
+        <v>18.74740001678467</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>4.655632769347411</v>
+        <v>4.707848251980211</v>
       </c>
       <c r="V58" t="n">
-        <v>20.59060006459554</v>
+        <v>20.59066672007243</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-4.713797666494615</v>
+        <v>-4.66554858259804</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.4369068813324</v>
+        <v>21.43695687294006</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-8.475597958962961</v>
+        <v>-8.42917081413915</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.4641563872605222</v>
+        <v>0.464165062821851</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17122,7 +17124,7 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>26.51</v>
+        <v>26.53</v>
       </c>
       <c r="CA58" t="n">
         <v>0.09</v>
@@ -17182,10 +17184,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.65999984741211</v>
+        <v>14.60999965667725</v>
       </c>
       <c r="D59" t="n">
-        <v>14.65999984741211</v>
+        <v>14.60999965667725</v>
       </c>
       <c r="E59" t="n">
         <v>14.85000038146973</v>
@@ -17197,67 +17199,67 @@
         <v>14.56999969482422</v>
       </c>
       <c r="H59" t="n">
-        <v>2446000</v>
+        <v>4101900</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.01146325537211879</v>
+        <v>-0.01483481241811291</v>
       </c>
       <c r="J59" t="n">
-        <v>14.75666671329074</v>
+        <v>14.75111113654243</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.6550725021902905</v>
+        <v>-0.9566159359725127</v>
       </c>
       <c r="M59" t="n">
-        <v>14.78900003433228</v>
+        <v>14.78400001525879</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.8722711922421763</v>
+        <v>-1.176950476203695</v>
       </c>
       <c r="P59" t="n">
-        <v>14.21807699937087</v>
+        <v>14.21615391511184</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>3.108175937300067</v>
+        <v>2.770409942922402</v>
       </c>
       <c r="S59" t="n">
-        <v>14.04959999084473</v>
+        <v>14.04859998703003</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>4.344606657592701</v>
+        <v>3.996125380219479</v>
       </c>
       <c r="V59" t="n">
-        <v>14.88086668650309</v>
+        <v>14.88053335189819</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-1.484233705899053</v>
+        <v>-1.818037625556197</v>
       </c>
       <c r="Y59" t="n">
-        <v>14.9329500246048</v>
+        <v>14.93270002365112</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-1.827838282073889</v>
+        <v>-2.161031604885708</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3161974231549095</v>
+        <v>0.3174724175226817</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17405,13 +17407,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>26.18</v>
+        <v>26.09</v>
       </c>
       <c r="CA59" t="n">
         <v>0.64</v>
       </c>
       <c r="CB59" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CC59" t="n">
         <v>8</v>
@@ -17443,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="CL59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM59" t="n">
         <v>4</v>
@@ -17452,7 +17454,7 @@
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60">
@@ -17465,10 +17467,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37.09000015258789</v>
+        <v>36.95999908447266</v>
       </c>
       <c r="D60" t="n">
-        <v>37.09000015258789</v>
+        <v>36.95999908447266</v>
       </c>
       <c r="E60" t="n">
         <v>37.27000045776367</v>
@@ -17480,88 +17482,88 @@
         <v>36.4900016784668</v>
       </c>
       <c r="H60" t="n">
-        <v>3018000</v>
+        <v>4331000</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01382612202405942</v>
+        <v>-0.01728267788700866</v>
       </c>
       <c r="J60" t="n">
-        <v>37.16444481743707</v>
+        <v>37.15000025431315</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.2003115214417144</v>
+        <v>-0.5114432531354642</v>
       </c>
       <c r="M60" t="n">
-        <v>36.96600036621093</v>
+        <v>36.95300025939942</v>
       </c>
       <c r="N60" t="n">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.3354427991898711</v>
+        <v>0.01893980197577899</v>
       </c>
       <c r="P60" t="n">
-        <v>35.21538485013522</v>
+        <v>35.21038480905386</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>5.323285008613151</v>
+        <v>4.969029122819765</v>
       </c>
       <c r="S60" t="n">
-        <v>34.97320014953613</v>
+        <v>34.97060012817383</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>6.052634571617358</v>
+        <v>5.688775568641392</v>
       </c>
       <c r="V60" t="n">
-        <v>36.72120002746582</v>
+        <v>36.72033335367838</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1.004324817397648</v>
+        <v>0.6526785268692659</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.32624998092651</v>
+        <v>38.32559997558594</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-3.225595587759969</v>
+        <v>-3.563155937501807</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3398075372842329</v>
+        <v>0.3413944581970529</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AE60" t="n">
         <v>36.5</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AF60" t="n">
         <v>36.8</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AG60" t="n">
         <v>37</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AH60" t="n">
         <v>37.1</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AI60" t="n">
         <v>37.7</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>38.4</v>
       </c>
       <c r="AJ60" t="n">
         <v>2</v>
@@ -17688,13 +17690,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>18.36</v>
+        <v>18.3</v>
       </c>
       <c r="CA60" t="n">
         <v>0.09</v>
       </c>
       <c r="CB60" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CC60" t="n">
         <v>9</v>
@@ -17729,13 +17731,13 @@
         <v>7</v>
       </c>
       <c r="CM60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN60" t="n">
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -17748,82 +17750,82 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.38000011444092</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="D61" t="n">
-        <v>11.38000011444092</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="E61" t="n">
         <v>11.56999969482422</v>
       </c>
       <c r="F61" t="n">
-        <v>11.3100004196167</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="G61" t="n">
         <v>11.47999954223633</v>
       </c>
       <c r="H61" t="n">
-        <v>1081000</v>
+        <v>1502600</v>
       </c>
       <c r="I61" t="n">
-        <v>0.00176060372958875</v>
+        <v>0.005281727238559464</v>
       </c>
       <c r="J61" t="n">
-        <v>11.39777766333686</v>
+        <v>11.40222210354275</v>
       </c>
       <c r="K61" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.1559738171865514</v>
+        <v>0.1559167378933114</v>
       </c>
       <c r="M61" t="n">
-        <v>11.34699993133545</v>
+        <v>11.35099992752075</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.2908273843761642</v>
+        <v>0.6078772726083922</v>
       </c>
       <c r="P61" t="n">
-        <v>10.83769222406241</v>
+        <v>10.83923068413368</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>5.003905620925932</v>
+        <v>5.358031479211817</v>
       </c>
       <c r="S61" t="n">
-        <v>10.56759998321533</v>
+        <v>10.56839998245239</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>7.687650294446533</v>
+        <v>8.057985080575454</v>
       </c>
       <c r="V61" t="n">
-        <v>11.58920001983643</v>
+        <v>11.58946668624878</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-1.805128093720316</v>
+        <v>-1.462246836223361</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.39974999904633</v>
+        <v>11.39994999885559</v>
       </c>
       <c r="Z61" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-0.1732484011233643</v>
+        <v>0.1758786436814778</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3705376703777531</v>
+        <v>0.3706242802259763</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17971,7 +17973,7 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
       <c r="CA61" t="n">
         <v>0.45</v>
@@ -18031,13 +18033,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>35.66999816894531</v>
+        <v>35.84000015258789</v>
       </c>
       <c r="D62" t="n">
-        <v>35.66999816894531</v>
+        <v>35.84000015258789</v>
       </c>
       <c r="E62" t="n">
-        <v>35.90000152587891</v>
+        <v>35.95000076293945</v>
       </c>
       <c r="F62" t="n">
         <v>34.54999923706055</v>
@@ -18046,67 +18048,67 @@
         <v>34.59999847412109</v>
       </c>
       <c r="H62" t="n">
-        <v>2852200</v>
+        <v>3672300</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.003631314829209753</v>
+        <v>0.001117344032955492</v>
       </c>
       <c r="J62" t="n">
-        <v>36.13777754041884</v>
+        <v>36.15666664971246</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-1.29443314811026</v>
+        <v>-0.8758177300812754</v>
       </c>
       <c r="M62" t="n">
-        <v>36.03099975585938</v>
+        <v>36.04799995422363</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-1.001919428714596</v>
+        <v>-0.5770078836547848</v>
       </c>
       <c r="P62" t="n">
-        <v>34.99192296541654</v>
+        <v>34.99846150324895</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>1.937804916291484</v>
+        <v>2.404501835775902</v>
       </c>
       <c r="S62" t="n">
-        <v>36.71699989318848</v>
+        <v>36.72039993286133</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.851544862839952</v>
+        <v>-2.397576774444552</v>
       </c>
       <c r="V62" t="n">
-        <v>42.85513333638509</v>
+        <v>42.85626668294271</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-16.76610153337084</v>
+        <v>-16.37162327335287</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.42795000076294</v>
+        <v>43.42880001068115</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-17.86396049475358</v>
+        <v>-17.47411822621584</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4090830536728336</v>
+        <v>0.4090941839161074</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18120,19 +18122,19 @@
         <v>26.7</v>
       </c>
       <c r="AF62" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="AG62" t="n">
-        <v>35.7</v>
+        <v>36.5</v>
       </c>
       <c r="AH62" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="AI62" t="n">
-        <v>37.6</v>
+        <v>38.1</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK62" t="n">
         <v>0</v>
@@ -18256,13 +18258,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>17.83</v>
+        <v>17.92</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="CB62" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CC62" t="n">
         <v>10</v>
@@ -18312,13 +18314,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30.23999977111816</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="D63" t="n">
-        <v>30.23999977111816</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="E63" t="n">
-        <v>30.3700008392334</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="F63" t="n">
         <v>29.8799991607666</v>
@@ -18327,67 +18329,67 @@
         <v>29.88999938964844</v>
       </c>
       <c r="H63" t="n">
-        <v>1018100</v>
+        <v>1414500</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.01241022396146829</v>
+        <v>-0.009144372272085088</v>
       </c>
       <c r="J63" t="n">
-        <v>30.14000002543132</v>
+        <v>30.15111117892795</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.331784159264999</v>
+        <v>0.626474336348671</v>
       </c>
       <c r="M63" t="n">
-        <v>30.08199996948242</v>
+        <v>30.09200000762939</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.5252303762915713</v>
+        <v>0.8241397876366451</v>
       </c>
       <c r="P63" t="n">
-        <v>29.72538463885968</v>
+        <v>29.72923080737774</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.731231196873183</v>
+        <v>2.054440456826675</v>
       </c>
       <c r="S63" t="n">
-        <v>28.51380004882812</v>
+        <v>28.51580005645752</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>6.053909753642201</v>
+        <v>6.397155585740877</v>
       </c>
       <c r="V63" t="n">
-        <v>29.41293333689372</v>
+        <v>29.41360000610351</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>2.811914149300524</v>
+        <v>3.149563964601891</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.55154997825623</v>
+        <v>30.55204998016357</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-1.01975254073785</v>
+        <v>-0.6940608820467363</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.1825098020486434</v>
+        <v>0.1805191279316638</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18557,7 +18559,7 @@
         <v>18881600000</v>
       </c>
       <c r="BZ63" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="CA63" t="n">
         <v>0</v>
@@ -18617,13 +18619,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>26.82999992370605</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="D64" t="n">
-        <v>26.82999992370605</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E64" t="n">
-        <v>26.95999908447266</v>
+        <v>27.06999969482422</v>
       </c>
       <c r="F64" t="n">
         <v>26.04000091552734</v>
@@ -18632,67 +18634,67 @@
         <v>26.20000076293945</v>
       </c>
       <c r="H64" t="n">
-        <v>7010500</v>
+        <v>10230000</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.007766308606176775</v>
+        <v>-0.002218985623501202</v>
       </c>
       <c r="J64" t="n">
-        <v>26.52444479200575</v>
+        <v>26.54111141628689</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1.151975598721652</v>
+        <v>1.653616229801565</v>
       </c>
       <c r="M64" t="n">
-        <v>26.40000038146973</v>
+        <v>26.41500034332275</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.628786121299248</v>
+        <v>2.138933149991033</v>
       </c>
       <c r="P64" t="n">
-        <v>25.38230778620793</v>
+        <v>25.38807700230525</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>5.703548115844534</v>
+        <v>6.270354937817971</v>
       </c>
       <c r="S64" t="n">
-        <v>27.0446000289917</v>
+        <v>27.0476000213623</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-0.793504452110934</v>
+        <v>-0.2499315246919648</v>
       </c>
       <c r="V64" t="n">
-        <v>29.16892787933349</v>
+        <v>29.16992787679036</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-8.018559904920593</v>
+        <v>-7.507486284518709</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.57399991035462</v>
+        <v>28.57474990844727</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-6.103450661860512</v>
+        <v>-5.580977510986013</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3243782088909398</v>
+        <v>0.3237495052502448</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18710,10 +18712,10 @@
         <v>27</v>
       </c>
       <c r="AH64" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AI64" t="n">
         <v>27.4</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>28.4</v>
       </c>
       <c r="AJ64" t="n">
         <v>1</v>
@@ -18840,13 +18842,13 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.82</v>
+        <v>10.88</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
       </c>
       <c r="CB64" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CC64" t="n">
         <v>9</v>
@@ -18900,82 +18902,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.55999946594238</v>
+        <v>17.42000007629395</v>
       </c>
       <c r="D65" t="n">
-        <v>17.55999946594238</v>
+        <v>17.42000007629395</v>
       </c>
       <c r="E65" t="n">
         <v>17.97999954223633</v>
       </c>
       <c r="F65" t="n">
-        <v>17.53000068664551</v>
+        <v>17.3700008392334</v>
       </c>
       <c r="G65" t="n">
         <v>17.8700008392334</v>
       </c>
       <c r="H65" t="n">
-        <v>3181600</v>
+        <v>4063900</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.02118177574152424</v>
+        <v>-0.0289855318998733</v>
       </c>
       <c r="J65" t="n">
-        <v>17.13888867696126</v>
+        <v>17.12333318922255</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>2.457048393967305</v>
+        <v>1.732530014998006</v>
       </c>
       <c r="M65" t="n">
-        <v>17.03199977874756</v>
+        <v>17.01799983978271</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>3.100045174106098</v>
+        <v>2.362206136419637</v>
       </c>
       <c r="P65" t="n">
-        <v>15.48846145776602</v>
+        <v>15.48307686585646</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>13.37471777829605</v>
+        <v>12.50993731555267</v>
       </c>
       <c r="S65" t="n">
-        <v>14.53199998855591</v>
+        <v>14.52920000076294</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>20.83677043607937</v>
+        <v>19.8964848400408</v>
       </c>
       <c r="V65" t="n">
-        <v>15.79479996999105</v>
+        <v>15.79386664072672</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>11.17582685000812</v>
+        <v>10.29598053825531</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.59519992351532</v>
+        <v>15.59449992656708</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>12.59874546054666</v>
+        <v>11.70605122525867</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.3640333625118002</v>
+        <v>0.3703688281474487</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19127,13 +19129,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>27.02</v>
+        <v>26.8</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CC65" t="n">
         <v>3</v>
@@ -19187,13 +19189,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.1200008392334</v>
+        <v>17.13999938964844</v>
       </c>
       <c r="D66" t="n">
-        <v>17.1200008392334</v>
+        <v>17.13999938964844</v>
       </c>
       <c r="E66" t="n">
-        <v>17.20000076293945</v>
+        <v>17.26000022888184</v>
       </c>
       <c r="F66" t="n">
         <v>16.82999992370605</v>
@@ -19202,67 +19204,67 @@
         <v>16.94000053405762</v>
       </c>
       <c r="H66" t="n">
-        <v>4589700</v>
+        <v>7410300</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.01325645747431647</v>
+        <v>-0.01210380329706362</v>
       </c>
       <c r="J66" t="n">
-        <v>17.61222224765354</v>
+        <v>17.61444430881076</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.794771730101904</v>
+        <v>-2.693499214874516</v>
       </c>
       <c r="M66" t="n">
-        <v>17.53199996948242</v>
+        <v>17.53399982452392</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-2.349983635444787</v>
+        <v>-2.24706535199355</v>
       </c>
       <c r="P66" t="n">
-        <v>17.35192320897029</v>
+        <v>17.37038465646597</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-1.336580198885375</v>
+        <v>-1.326310679779753</v>
       </c>
       <c r="S66" t="n">
-        <v>18.66080013275146</v>
+        <v>18.70580009460449</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-8.256876889291679</v>
+        <v>-8.370669509120297</v>
       </c>
       <c r="V66" t="n">
-        <v>18.97940003712972</v>
+        <v>19.00653335571289</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-9.796933487142635</v>
+        <v>-9.820486098815167</v>
       </c>
       <c r="Y66" t="n">
-        <v>20.08254096984863</v>
+        <v>20.11294095993042</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-14.75181917996886</v>
+        <v>-14.78123749383425</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3378182000137312</v>
+        <v>0.3448458100735897</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19414,7 +19416,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.29</v>
+        <v>15.3</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
@@ -19432,7 +19434,7 @@
         <v>5</v>
       </c>
       <c r="CF66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CG66" t="n">
         <v>5</v>
@@ -19441,7 +19443,7 @@
         <v>6</v>
       </c>
       <c r="CI66" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CJ66" t="inlineStr">
         <is>
@@ -19461,7 +19463,7 @@
         <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -19474,10 +19476,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>47.41999816894531</v>
+        <v>47.34999847412109</v>
       </c>
       <c r="D67" t="n">
-        <v>47.41999816894531</v>
+        <v>47.34999847412109</v>
       </c>
       <c r="E67" t="n">
         <v>47.54000091552734</v>
@@ -19489,67 +19491,67 @@
         <v>46.84000015258789</v>
       </c>
       <c r="H67" t="n">
-        <v>3037900</v>
+        <v>5143400</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.008157356058215437</v>
+        <v>-0.009621478476403045</v>
       </c>
       <c r="J67" t="n">
-        <v>47.08666610717773</v>
+        <v>47.07888836330838</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.7079117918623806</v>
+        <v>0.5758634501319438</v>
       </c>
       <c r="M67" t="n">
-        <v>46.90799942016601</v>
+        <v>46.90099945068359</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>1.09149559799642</v>
+        <v>0.9573335935188844</v>
       </c>
       <c r="P67" t="n">
-        <v>44.71423090421236</v>
+        <v>44.71153860825758</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>6.051244111811499</v>
+        <v>5.901071508588666</v>
       </c>
       <c r="S67" t="n">
-        <v>43.40060005187988</v>
+        <v>43.3992000579834</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>9.261157938509491</v>
+        <v>9.103389949259984</v>
       </c>
       <c r="V67" t="n">
-        <v>46.15340009053548</v>
+        <v>46.15293342590332</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>2.744322359620835</v>
+        <v>2.593692230071601</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.20380002975464</v>
+        <v>47.20345003128052</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.4580100310873156</v>
+        <v>0.3104612962473336</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2713179501581395</v>
+        <v>0.2718812080935407</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19697,7 +19699,7 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="CA67" t="n">
         <v>1.14</v>
@@ -19757,10 +19759,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40.58000183105469</v>
+        <v>40.68000030517578</v>
       </c>
       <c r="D68" t="n">
-        <v>40.58000183105469</v>
+        <v>40.68000030517578</v>
       </c>
       <c r="E68" t="n">
         <v>40.77999877929688</v>
@@ -19772,67 +19774,67 @@
         <v>40.4900016784668</v>
       </c>
       <c r="H68" t="n">
-        <v>702700</v>
+        <v>1028100</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.003682732945432421</v>
+        <v>-0.001227577648477474</v>
       </c>
       <c r="J68" t="n">
-        <v>41</v>
+        <v>41.01111094156901</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-1.024385777915396</v>
+        <v>-0.8073681224217018</v>
       </c>
       <c r="M68" t="n">
-        <v>40.80999984741211</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.5635824974696866</v>
+        <v>-0.3429676401153642</v>
       </c>
       <c r="P68" t="n">
-        <v>39.12730745168832</v>
+        <v>39.13115354684683</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>3.712737916249538</v>
+        <v>3.958091234071873</v>
       </c>
       <c r="S68" t="n">
-        <v>39.77419982910156</v>
+        <v>39.77619979858398</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>2.025941453040986</v>
+        <v>2.272214317024762</v>
       </c>
       <c r="V68" t="n">
-        <v>41.05799997965494</v>
+        <v>41.05866663614909</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-1.164202223286849</v>
+        <v>-0.9222567657370602</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.20495006561279</v>
+        <v>41.2054500579834</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-1.51668242180361</v>
+        <v>-1.27519479114587</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2077076795672926</v>
+        <v>0.2073639924084216</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -19982,7 +19984,7 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>8.92</v>
+        <v>8.94</v>
       </c>
       <c r="CA68" t="n">
         <v>0.24</v>
@@ -20019,13 +20021,13 @@
         <v>4</v>
       </c>
       <c r="CM68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN68" t="n">
         <v>0</v>
       </c>
       <c r="CO68" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
@@ -20038,13 +20040,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.54000091552734</v>
+        <v>19.71999931335449</v>
       </c>
       <c r="D69" t="n">
-        <v>19.54000091552734</v>
+        <v>19.71999931335449</v>
       </c>
       <c r="E69" t="n">
-        <v>19.63999938964844</v>
+        <v>19.71999931335449</v>
       </c>
       <c r="F69" t="n">
         <v>19.04999923706055</v>
@@ -20053,88 +20055,88 @@
         <v>19.14999961853027</v>
       </c>
       <c r="H69" t="n">
-        <v>3081200</v>
+        <v>4761800</v>
       </c>
       <c r="I69" t="n">
-        <v>0.008776461999403518</v>
+        <v>0.01806909958476521</v>
       </c>
       <c r="J69" t="n">
-        <v>19.16222233242459</v>
+        <v>19.18222215440538</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.971475836931051</v>
+        <v>2.803518563283901</v>
       </c>
       <c r="M69" t="n">
-        <v>19.10700016021729</v>
+        <v>19.125</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>2.26618910179113</v>
+        <v>3.111107520807802</v>
       </c>
       <c r="P69" t="n">
-        <v>18.69269231649546</v>
+        <v>18.6996153317965</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>4.53283339117595</v>
+        <v>5.456711079093418</v>
       </c>
       <c r="S69" t="n">
-        <v>19.94900005340576</v>
+        <v>19.9526000213623</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-2.050223754491353</v>
+        <v>-1.16576640517415</v>
       </c>
       <c r="V69" t="n">
-        <v>23.29233334859212</v>
+        <v>23.29353333791097</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-16.10973180276756</v>
+        <v>-15.34131371448245</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.33170001029968</v>
+        <v>23.33260000228882</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-16.25127655978137</v>
+        <v>-15.4830609901166</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2147302296403928</v>
+        <v>0.2195609651448596</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AE69" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF69" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AG69" t="n">
-        <v>19.6</v>
+        <v>21.9</v>
       </c>
       <c r="AH69" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="AI69" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AJ69" t="n">
         <v>1</v>
@@ -20261,13 +20263,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>1954</v>
+        <v>1972</v>
       </c>
       <c r="CA69" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CC69" t="n">
         <v>1</v>
@@ -20302,13 +20304,13 @@
         <v>3</v>
       </c>
       <c r="CM69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN69" t="n">
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70">
@@ -20321,13 +20323,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>33.72000122070312</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="D70" t="n">
-        <v>33.72000122070312</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="E70" t="n">
-        <v>33.77999877929688</v>
+        <v>34.54999923706055</v>
       </c>
       <c r="F70" t="n">
         <v>32.02999877929688</v>
@@ -20336,67 +20338,67 @@
         <v>32.02999877929688</v>
       </c>
       <c r="H70" t="n">
-        <v>2521000</v>
+        <v>4584500</v>
       </c>
       <c r="I70" t="n">
-        <v>0.02367949685831761</v>
+        <v>0.04766240923735809</v>
       </c>
       <c r="J70" t="n">
-        <v>34.01888910929362</v>
+        <v>34.10666656494141</v>
       </c>
       <c r="K70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.8785939118418752</v>
+        <v>1.182559884073766</v>
       </c>
       <c r="M70" t="n">
-        <v>34.1620002746582</v>
+        <v>34.24099998474121</v>
       </c>
       <c r="N70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>-1.293832475854641</v>
+        <v>0.7856030399575612</v>
       </c>
       <c r="P70" t="n">
-        <v>32.6519231062669</v>
+        <v>32.68230761014498</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>3.27110323934099</v>
+        <v>5.59229395056818</v>
       </c>
       <c r="S70" t="n">
-        <v>31.22559989929199</v>
+        <v>31.24139984130859</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>7.988321535714323</v>
+        <v>10.46239444079821</v>
       </c>
       <c r="V70" t="n">
-        <v>32.77799996693929</v>
+        <v>32.78326661427815</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>2.873882649075478</v>
+        <v>5.267113029251947</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.57349997520447</v>
+        <v>35.57744996070862</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-5.210335659390489</v>
+        <v>-3.000360172958713</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3649367304112825</v>
+        <v>0.3829243547603716</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20411,13 +20413,13 @@
         <v>33.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="AH70" t="n">
-        <v>34.7</v>
+        <v>35.2</v>
       </c>
       <c r="AI70" t="n">
-        <v>35.2</v>
+        <v>35.5</v>
       </c>
       <c r="AJ70" t="n">
         <v>3</v>
@@ -20544,13 +20546,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>21.9</v>
+        <v>22.41</v>
       </c>
       <c r="CA70" t="n">
         <v>0.17</v>
       </c>
       <c r="CB70" t="n">
-        <v>4.07</v>
+        <v>4.17</v>
       </c>
       <c r="CC70" t="n">
         <v>7</v>
@@ -20582,16 +20584,16 @@
         <v>0</v>
       </c>
       <c r="CL70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71">
@@ -20619,7 +20621,7 @@
         <v>37.29999923706055</v>
       </c>
       <c r="H71" t="n">
-        <v>2610200</v>
+        <v>3701000</v>
       </c>
       <c r="I71" t="n">
         <v>0.009468716623280526</v>
@@ -20887,82 +20889,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7.21999979019165</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="D72" t="n">
-        <v>7.21999979019165</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E72" t="n">
         <v>7.349999904632568</v>
       </c>
       <c r="F72" t="n">
-        <v>7.099999904632568</v>
+        <v>7.019999980926514</v>
       </c>
       <c r="G72" t="n">
         <v>7.230000019073486</v>
       </c>
       <c r="H72" t="n">
-        <v>5258400</v>
+        <v>8808500</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.02168026040218951</v>
+        <v>-0.04742546059690445</v>
       </c>
       <c r="J72" t="n">
-        <v>7.584444469875759</v>
+        <v>7.563333405388726</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-4.80515983908415</v>
+        <v>-7.051562677382267</v>
       </c>
       <c r="M72" t="n">
-        <v>7.573000001907348</v>
+        <v>7.554000043869019</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-4.661299506494003</v>
+        <v>-6.936720029356609</v>
       </c>
       <c r="P72" t="n">
-        <v>7.037692290086013</v>
+        <v>7.030384613917424</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>2.590444318835222</v>
+        <v>-0.0054677536178265</v>
       </c>
       <c r="S72" t="n">
-        <v>7.574199953079224</v>
+        <v>7.570399961471558</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-4.676403647669432</v>
+        <v>-7.138324981685161</v>
       </c>
       <c r="V72" t="n">
-        <v>7.901199998855591</v>
+        <v>7.899933334986369</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-8.621477861117372</v>
+        <v>-11.01190463627527</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.454649999141693</v>
+        <v>7.453700001239777</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-3.147702561180731</v>
+        <v>-5.684422385673598</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.5028476368533048</v>
+        <v>0.5177369597831084</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21114,13 +21116,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>-3.47</v>
+        <v>-3.38</v>
       </c>
       <c r="CA72" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="CB72" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="CC72" t="n">
         <v>1</v>
@@ -21152,7 +21154,7 @@
         <v>-1</v>
       </c>
       <c r="CL72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM72" t="n">
         <v>1</v>
@@ -21161,7 +21163,7 @@
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
@@ -21174,94 +21176,94 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>75.66999816894531</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D73" t="n">
-        <v>75.66999816894531</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="E73" t="n">
         <v>76.88999938964844</v>
       </c>
       <c r="F73" t="n">
-        <v>75.56999969482422</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="G73" t="n">
         <v>76.5</v>
       </c>
       <c r="H73" t="n">
-        <v>12712700</v>
+        <v>17248500</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.03235292682903035</v>
+        <v>-0.03196931071051912</v>
       </c>
       <c r="J73" t="n">
-        <v>78.48777770996094</v>
+        <v>78.49111090766058</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-3.590087046964535</v>
+        <v>-3.555961849873613</v>
       </c>
       <c r="M73" t="n">
-        <v>78.42399978637695</v>
+        <v>78.42699966430663</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-3.511682169914061</v>
+        <v>-3.477122327434322</v>
       </c>
       <c r="P73" t="n">
-        <v>76.23192302997296</v>
+        <v>76.23307682917668</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.7371253914278278</v>
+        <v>-0.699276354972555</v>
       </c>
       <c r="S73" t="n">
-        <v>75.50920013427735</v>
+        <v>75.50980010986328</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>0.2129515799161119</v>
+        <v>0.25188364702619</v>
       </c>
       <c r="V73" t="n">
-        <v>80.10773345947266</v>
+        <v>80.10793345133463</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-5.539708963020954</v>
+        <v>-5.502496835435474</v>
       </c>
       <c r="Y73" t="n">
-        <v>78.90265007019043</v>
+        <v>78.90280006408692</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-4.09701308938218</v>
+        <v>-4.059175483307728</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2629337644581474</v>
+        <v>0.2625273404041317</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
       </c>
       <c r="AD73" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE73" t="n">
         <v>65.3</v>
       </c>
-      <c r="AE73" t="n">
+      <c r="AF73" t="n">
         <v>66.40000000000001</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>75.59999999999999</v>
       </c>
       <c r="AG73" t="n">
         <v>77.2</v>
@@ -21397,7 +21399,7 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="CA73" t="n">
         <v>0.21</v>
@@ -21468,7 +21470,7 @@
         <v>3.140000104904175</v>
       </c>
       <c r="H74" t="n">
-        <v>9852200</v>
+        <v>15012400</v>
       </c>
       <c r="I74" t="n">
         <v>-0.01223240430774986</v>
@@ -21736,10 +21738,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>37.70999908447266</v>
+        <v>37.81999969482422</v>
       </c>
       <c r="D75" t="n">
-        <v>37.70999908447266</v>
+        <v>37.81999969482422</v>
       </c>
       <c r="E75" t="n">
         <v>38.22000122070312</v>
@@ -21751,67 +21753,67 @@
         <v>36.7400016784668</v>
       </c>
       <c r="H75" t="n">
-        <v>5311700</v>
+        <v>9334300</v>
       </c>
       <c r="I75" t="n">
-        <v>0.004260981375844963</v>
+        <v>0.007190425119827815</v>
       </c>
       <c r="J75" t="n">
-        <v>37.11000018649631</v>
+        <v>37.12222247653537</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1.616811896957839</v>
+        <v>1.87967522345923</v>
       </c>
       <c r="M75" t="n">
-        <v>36.84099998474121</v>
+        <v>36.85200004577636</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>2.358782606583341</v>
+        <v>2.626722153059363</v>
       </c>
       <c r="P75" t="n">
-        <v>35.01115388136644</v>
+        <v>35.01538467407227</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>7.708529722416804</v>
+        <v>8.009665028265927</v>
       </c>
       <c r="S75" t="n">
-        <v>34.56959983825683</v>
+        <v>34.57179985046387</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>9.084280005869386</v>
+        <v>9.395518481566031</v>
       </c>
       <c r="V75" t="n">
-        <v>32.33286652882894</v>
+        <v>32.33359986623128</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>16.63054697253431</v>
+        <v>16.96810701960486</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.77794505119324</v>
+        <v>30.778495054245</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>22.52279683308703</v>
+        <v>22.87800176119415</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2790151740563562</v>
+        <v>0.2793823096974768</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21963,13 +21965,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.02</v>
+        <v>15.07</v>
       </c>
       <c r="CA75" t="n">
         <v>0.4</v>
       </c>
       <c r="CB75" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CC75" t="n">
         <v>5</v>
@@ -22019,10 +22021,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.51000022888184</v>
+        <v>22.45999908447266</v>
       </c>
       <c r="D76" t="n">
-        <v>22.51000022888184</v>
+        <v>22.45999908447266</v>
       </c>
       <c r="E76" t="n">
         <v>22.65999984741211</v>
@@ -22034,67 +22036,67 @@
         <v>22.18000030517578</v>
       </c>
       <c r="H76" t="n">
-        <v>1364400</v>
+        <v>1835200</v>
       </c>
       <c r="I76" t="n">
-        <v>0.008060918306797227</v>
+        <v>0.005821726879120748</v>
       </c>
       <c r="J76" t="n">
-        <v>22.82555537753635</v>
+        <v>22.81999969482422</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.382464274955019</v>
+        <v>-1.577566236485156</v>
       </c>
       <c r="M76" t="n">
-        <v>22.77099990844727</v>
+        <v>22.76599979400635</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-1.146193318759831</v>
+        <v>-1.344112765977679</v>
       </c>
       <c r="P76" t="n">
-        <v>21.95000002934383</v>
+        <v>21.94807690840501</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>2.551253753026762</v>
+        <v>2.332423830133407</v>
       </c>
       <c r="S76" t="n">
-        <v>22.1734001159668</v>
+        <v>22.17240009307861</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>1.518035624462746</v>
+        <v>1.297103562026283</v>
       </c>
       <c r="V76" t="n">
-        <v>24.40880002339681</v>
+        <v>24.40846668243408</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-7.779160764539427</v>
+        <v>-7.982752965648879</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.17620001792908</v>
+        <v>26.17595001220703</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-14.00585182928049</v>
+        <v>-14.19604990841387</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3160126910185264</v>
+        <v>0.3156247775556806</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22242,7 +22244,7 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.08</v>
+        <v>9.06</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
@@ -22302,13 +22304,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30.40999984741211</v>
+        <v>30.61000061035156</v>
       </c>
       <c r="D77" t="n">
-        <v>30.40999984741211</v>
+        <v>30.61000061035156</v>
       </c>
       <c r="E77" t="n">
-        <v>30.60000038146973</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="F77" t="n">
         <v>29.79000091552734</v>
@@ -22317,88 +22319,88 @@
         <v>29.88999938964844</v>
       </c>
       <c r="H77" t="n">
-        <v>3080600</v>
+        <v>4559700</v>
       </c>
       <c r="I77" t="n">
-        <v>0.004625021061488876</v>
+        <v>0.01123224801606137</v>
       </c>
       <c r="J77" t="n">
-        <v>30.21444447835286</v>
+        <v>30.23666678534614</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>0.6472247709182659</v>
+        <v>1.234705622996635</v>
       </c>
       <c r="M77" t="n">
-        <v>30.17800006866455</v>
+        <v>30.1980001449585</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7687712181711308</v>
+        <v>1.364330298083828</v>
       </c>
       <c r="P77" t="n">
-        <v>29.93038463592529</v>
+        <v>29.93807697296143</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>1.602435843444313</v>
+        <v>2.2443780807865</v>
       </c>
       <c r="S77" t="n">
-        <v>31.98160018920898</v>
+        <v>31.98560020446777</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-4.914076633123418</v>
+        <v>-4.300684011938801</v>
       </c>
       <c r="V77" t="n">
-        <v>36.14153345743815</v>
+        <v>36.14286679585775</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-15.8585789304589</v>
+        <v>-15.3083213259118</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.7171501159668</v>
+        <v>35.71815011978149</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-14.8588290256176</v>
+        <v>-14.30127118089725</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1690982723838805</v>
+        <v>0.1724966135420725</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="AE77" t="n">
-        <v>27.4</v>
+        <v>28.1</v>
       </c>
       <c r="AF77" t="n">
-        <v>28.1</v>
+        <v>30.6</v>
       </c>
       <c r="AG77" t="n">
-        <v>30.6</v>
+        <v>32</v>
       </c>
       <c r="AH77" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="AI77" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AJ77" t="n">
         <v>1</v>
@@ -22525,13 +22527,13 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.44</v>
+        <v>15.54</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
       </c>
       <c r="CB77" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CC77" t="n">
         <v>5</v>
@@ -22585,10 +22587,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.90999984741211</v>
+        <v>50.84999847412109</v>
       </c>
       <c r="D78" t="n">
-        <v>50.90999984741211</v>
+        <v>50.84999847412109</v>
       </c>
       <c r="E78" t="n">
         <v>51.29000091552734</v>
@@ -22600,67 +22602,67 @@
         <v>50.06999969482422</v>
       </c>
       <c r="H78" t="n">
-        <v>5389400</v>
+        <v>7573200</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.01126435836371797</v>
+        <v>-0.01242965980739819</v>
       </c>
       <c r="J78" t="n">
-        <v>51.47222264607748</v>
+        <v>51.46555582682291</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.092283895590065</v>
+        <v>-1.196056941021131</v>
       </c>
       <c r="M78" t="n">
-        <v>51.34000053405762</v>
+        <v>51.33400039672851</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.8375548932070135</v>
+        <v>-0.9428486361220043</v>
       </c>
       <c r="P78" t="n">
-        <v>49.65730799161471</v>
+        <v>49.65500024648813</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2.52267371402601</v>
+        <v>2.406601997182513</v>
       </c>
       <c r="S78" t="n">
-        <v>47.84240020751953</v>
+        <v>47.84120018005371</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>6.411884910846162</v>
+        <v>6.289136315024621</v>
       </c>
       <c r="V78" t="n">
-        <v>47.23606676737467</v>
+        <v>47.2356667582194</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>7.777813292818387</v>
+        <v>7.651700428834886</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.45410005569458</v>
+        <v>47.45380004882813</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>7.282615806982968</v>
+        <v>7.15685239495764</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.1917733120043124</v>
+        <v>0.1925333796987556</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22808,13 +22810,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>33.94</v>
+        <v>33.9</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12.04</v>
+        <v>12.02</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22868,10 +22870,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9.880000114440918</v>
+        <v>9.859999656677246</v>
       </c>
       <c r="D79" t="n">
-        <v>9.880000114440918</v>
+        <v>9.859999656677246</v>
       </c>
       <c r="E79" t="n">
         <v>9.930000305175781</v>
@@ -22883,67 +22885,67 @@
         <v>9.689999580383301</v>
       </c>
       <c r="H79" t="n">
-        <v>2040400</v>
+        <v>2796300</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.003027218308083612</v>
+        <v>-0.005045428002495966</v>
       </c>
       <c r="J79" t="n">
-        <v>9.698888884650337</v>
+        <v>9.696666611565483</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1.86733998032714</v>
+        <v>1.684424675557589</v>
       </c>
       <c r="M79" t="n">
-        <v>9.601999950408935</v>
+        <v>9.599999904632568</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.895231883646735</v>
+        <v>2.708330777370242</v>
       </c>
       <c r="P79" t="n">
-        <v>8.570384575770451</v>
+        <v>8.569615327394926</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>15.28070913378746</v>
+        <v>15.05766921832865</v>
       </c>
       <c r="S79" t="n">
-        <v>8.459399995803834</v>
+        <v>8.458999986648559</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>16.79315458947151</v>
+        <v>16.56223752500278</v>
       </c>
       <c r="V79" t="n">
-        <v>9.949533303578695</v>
+        <v>9.949399967193603</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-0.6988588008722706</v>
+        <v>-0.8985497699473214</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.7109499835968</v>
+        <v>10.71084998130798</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-7.757947431632443</v>
+        <v>-7.943817027739136</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5474049224920204</v>
+        <v>0.5477426718129479</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23091,10 +23093,10 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>22.98</v>
+        <v>22.93</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CB79" t="n">
         <v>0.9</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -912,7 +912,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="H2" t="n">
-        <v>26568100</v>
+        <v>29297200</v>
       </c>
       <c r="I2" t="n">
         <v>0.01600512175618696</v>
@@ -1199,7 +1199,7 @@
         <v>27.90999984741211</v>
       </c>
       <c r="H3" t="n">
-        <v>3772200</v>
+        <v>4292700</v>
       </c>
       <c r="I3" t="n">
         <v>-0.006636347617129945</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.649999618530273</v>
+        <v>9.630000114440918</v>
       </c>
       <c r="D4" t="n">
-        <v>9.649999618530273</v>
+        <v>9.630000114440918</v>
       </c>
       <c r="E4" t="n">
         <v>9.819999694824219</v>
@@ -1482,67 +1482,67 @@
         <v>9.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5856400</v>
+        <v>6287000</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01731161726853681</v>
+        <v>-0.01934822670956327</v>
       </c>
       <c r="J4" t="n">
-        <v>9.275555398729113</v>
+        <v>9.273333231608072</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>4.036892711054965</v>
+        <v>3.846156219396385</v>
       </c>
       <c r="M4" t="n">
-        <v>9.191999816894532</v>
+        <v>9.189999866485596</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.982591500860959</v>
+        <v>4.787815607701251</v>
       </c>
       <c r="P4" t="n">
-        <v>8.570769181618324</v>
+        <v>8.569999969922579</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>12.59199045082871</v>
+        <v>12.36872985109141</v>
       </c>
       <c r="S4" t="n">
-        <v>8.51399995803833</v>
+        <v>8.513599967956543</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>13.34272569991513</v>
+        <v>13.11313839840112</v>
       </c>
       <c r="V4" t="n">
-        <v>8.689599936803182</v>
+        <v>8.68946660677592</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>11.05228881319953</v>
+        <v>10.82383476716032</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.545849938392639</v>
+        <v>8.545749940872192</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.92030269777134</v>
+        <v>12.68759536694408</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5203318511070349</v>
+        <v>0.5211150784183726</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1692,13 +1692,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>18.56</v>
+        <v>18.52</v>
       </c>
       <c r="CA4" t="n">
         <v>0.92</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.5600004196167</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="D5" t="n">
-        <v>11.5600004196167</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="E5" t="n">
         <v>11.6899995803833</v>
@@ -1767,73 +1767,73 @@
         <v>11.59000015258789</v>
       </c>
       <c r="H5" t="n">
-        <v>2055600</v>
+        <v>2354300</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02364862579076832</v>
+        <v>-0.02618246753560571</v>
       </c>
       <c r="J5" t="n">
-        <v>11.79111120435927</v>
+        <v>11.78777779473199</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.960042448392172</v>
+        <v>-2.186824915176106</v>
       </c>
       <c r="M5" t="n">
-        <v>11.73100004196167</v>
+        <v>11.72799997329712</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.457673017929472</v>
+        <v>-1.688269447277839</v>
       </c>
       <c r="P5" t="n">
-        <v>10.93884622133695</v>
+        <v>10.92692312827477</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.678425180419341</v>
+        <v>5.519180446468823</v>
       </c>
       <c r="S5" t="n">
-        <v>11.27619998931885</v>
+        <v>11.2493999671936</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.516809125119066</v>
+        <v>2.49435317968865</v>
       </c>
       <c r="V5" t="n">
-        <v>11.97086665471395</v>
+        <v>11.96899998346965</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.432217958383621</v>
+        <v>-3.667810603264735</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.94854998588562</v>
+        <v>11.94289998054504</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.251855386033452</v>
+        <v>-3.457286322806565</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3038823503120243</v>
+        <v>0.2950671581733426</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="AE5" t="n">
         <v>11.4</v>
@@ -1975,7 +1975,7 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.4</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="CA5" t="n">
         <v>1.67</v>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54.97999954223633</v>
+        <v>55.06999969482422</v>
       </c>
       <c r="D6" t="n">
-        <v>54.97999954223633</v>
+        <v>55.06999969482422</v>
       </c>
       <c r="E6" t="n">
         <v>55.36999893188477</v>
@@ -2046,67 +2046,67 @@
         <v>53.90000152587891</v>
       </c>
       <c r="H6" t="n">
-        <v>14113300</v>
+        <v>15419700</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003284677147477932</v>
+        <v>0.004927015721216899</v>
       </c>
       <c r="J6" t="n">
-        <v>55.22555584377713</v>
+        <v>55.23555586073134</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4446425170177283</v>
+        <v>-0.2997275275450222</v>
       </c>
       <c r="M6" t="n">
-        <v>55.01500015258789</v>
+        <v>55.02400016784668</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.06362012224753805</v>
+        <v>0.08359902376639444</v>
       </c>
       <c r="P6" t="n">
-        <v>52.81423055208646</v>
+        <v>52.81769209641676</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.100729987941298</v>
+        <v>4.264305214805582</v>
       </c>
       <c r="S6" t="n">
-        <v>52.45799980163574</v>
+        <v>52.4597998046875</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.807655172018098</v>
+        <v>4.975619235785737</v>
       </c>
       <c r="V6" t="n">
-        <v>55.96913330078125</v>
+        <v>55.96973330179851</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.767284394470187</v>
+        <v>-1.607535991145013</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.15685001373291</v>
+        <v>56.15730001449585</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.095649010243247</v>
+        <v>-1.936169152347014</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2483356637379966</v>
+        <v>0.2484863244657854</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2254,13 +2254,13 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.81</v>
+        <v>16.84</v>
       </c>
       <c r="CA6" t="n">
         <v>0.29</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.78999996185303</v>
+        <v>15.77000045776367</v>
       </c>
       <c r="D7" t="n">
-        <v>15.78999996185303</v>
+        <v>15.77000045776367</v>
       </c>
       <c r="E7" t="n">
         <v>16.20000076293945</v>
@@ -2325,67 +2325,67 @@
         <v>16.10000038146973</v>
       </c>
       <c r="H7" t="n">
-        <v>2581600</v>
+        <v>2726000</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03895315468260463</v>
+        <v>-0.04017040993019316</v>
       </c>
       <c r="J7" t="n">
-        <v>16.61333327823215</v>
+        <v>16.61111111111111</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.955858662378774</v>
+        <v>-5.063542394733746</v>
       </c>
       <c r="M7" t="n">
-        <v>16.43799991607666</v>
+        <v>16.43599996566773</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.942085153497759</v>
+        <v>-4.052077812699103</v>
       </c>
       <c r="P7" t="n">
-        <v>15.76269234143771</v>
+        <v>15.76192312974196</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1732421075271117</v>
+        <v>0.05124582803267164</v>
       </c>
       <c r="S7" t="n">
-        <v>16.57879999160767</v>
+        <v>16.57840000152588</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.757883744022108</v>
+        <v>-4.876221732421713</v>
       </c>
       <c r="V7" t="n">
-        <v>20.35086669286092</v>
+        <v>20.35073336283366</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-22.41116705171012</v>
+        <v>-22.50893283991295</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.66780000209808</v>
+        <v>21.66770000457764</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-27.12688893046784</v>
+        <v>-27.21885361883349</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5098920314615877</v>
+        <v>0.5106947012146335</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CA7" t="n">
         <v>0.67</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.36000061035156</v>
+        <v>17.3700008392334</v>
       </c>
       <c r="D8" t="n">
-        <v>17.36000061035156</v>
+        <v>17.3700008392334</v>
       </c>
       <c r="E8" t="n">
         <v>17.44000053405762</v>
@@ -2608,67 +2608,67 @@
         <v>16.85000038146973</v>
       </c>
       <c r="H8" t="n">
-        <v>35592700</v>
+        <v>38205800</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004629625030506013</v>
+        <v>0.005208341956690177</v>
       </c>
       <c r="J8" t="n">
-        <v>17.31444485982259</v>
+        <v>17.31555599636502</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2631083520019903</v>
+        <v>0.3144273442897869</v>
       </c>
       <c r="M8" t="n">
-        <v>17.20500030517578</v>
+        <v>17.20600032806396</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9009026586832081</v>
+        <v>0.9531588285624953</v>
       </c>
       <c r="P8" t="n">
-        <v>15.8057693701524</v>
+        <v>15.80615399434016</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>9.833315948125691</v>
+        <v>9.893911228836663</v>
       </c>
       <c r="S8" t="n">
-        <v>15.58580001831055</v>
+        <v>15.58600002288818</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>11.38344255640805</v>
+        <v>11.44617486029381</v>
       </c>
       <c r="V8" t="n">
-        <v>16.61593338648478</v>
+        <v>16.61600005467733</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>4.478034465833851</v>
+        <v>4.537799603243391</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.13955005645752</v>
+        <v>16.13960005760193</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.561862317256697</v>
+        <v>7.623489908301277</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3187177795688048</v>
+        <v>0.3187402543532048</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>17.71</v>
+        <v>17.72</v>
       </c>
       <c r="CA8" t="n">
         <v>-0.01</v>
@@ -2861,13 +2861,13 @@
         <v>9</v>
       </c>
       <c r="CM8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.20000076293945</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="D9" t="n">
-        <v>22.20000076293945</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="E9" t="n">
         <v>22.26000022888184</v>
@@ -2895,88 +2895,88 @@
         <v>21.95000076293945</v>
       </c>
       <c r="H9" t="n">
-        <v>27841000</v>
+        <v>29606200</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01289457586171827</v>
+        <v>-0.01645170901068316</v>
       </c>
       <c r="J9" t="n">
-        <v>22.30111122131348</v>
+        <v>22.29222234090169</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4533875346865711</v>
+        <v>-0.7725631793663823</v>
       </c>
       <c r="M9" t="n">
-        <v>22.14500007629395</v>
+        <v>22.13700008392334</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2483661614631657</v>
+        <v>-0.07679109466276259</v>
       </c>
       <c r="P9" t="n">
-        <v>20.17461541982798</v>
+        <v>20.17153849968543</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>10.03927609505206</v>
+        <v>9.659463206429947</v>
       </c>
       <c r="S9" t="n">
-        <v>20.36880004882812</v>
+        <v>20.367200050354</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>8.990223821342305</v>
+        <v>8.605997803065369</v>
       </c>
       <c r="V9" t="n">
-        <v>21.88506666819255</v>
+        <v>21.88453333536784</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.439036487856019</v>
+        <v>1.075953963729348</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.03265000343323</v>
+        <v>22.0322500038147</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7595580172160256</v>
+        <v>0.3982835861226591</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3625449613001165</v>
+        <v>0.3639207432678676</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AE9" t="n">
         <v>22</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>22.1</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>22.2</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>22.3</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>22.4</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>22.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -3123,7 +3123,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.84</v>
+        <v>8.81</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.18000030517578</v>
+        <v>16.17000007629395</v>
       </c>
       <c r="D10" t="n">
-        <v>16.18000030517578</v>
+        <v>16.17000007629395</v>
       </c>
       <c r="E10" t="n">
         <v>16.20000076293945</v>
@@ -3194,67 +3194,67 @@
         <v>15.96000003814697</v>
       </c>
       <c r="H10" t="n">
-        <v>5991300</v>
+        <v>6488400</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008578394133967882</v>
+        <v>-0.009191153268087726</v>
       </c>
       <c r="J10" t="n">
-        <v>15.88555569118924</v>
+        <v>15.88444455464681</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.853536758237902</v>
+        <v>1.797705425989219</v>
       </c>
       <c r="M10" t="n">
-        <v>15.81400012969971</v>
+        <v>15.81300010681152</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.314406048275556</v>
+        <v>2.257635913937938</v>
       </c>
       <c r="P10" t="n">
-        <v>15.0823077421922</v>
+        <v>15.06730772898747</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>7.278014623139079</v>
+        <v>7.318443129591354</v>
       </c>
       <c r="S10" t="n">
-        <v>15.54341779708862</v>
+        <v>15.52701778411865</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>4.095511787673844</v>
+        <v>4.14105465141509</v>
       </c>
       <c r="V10" t="n">
-        <v>16.23120594024658</v>
+        <v>16.21047260284424</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3154764671171616</v>
+        <v>-0.2496690105332979</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29620446681976</v>
+        <v>16.29090445995331</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.713075010077233</v>
+        <v>-0.7421588160225945</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2328441944645812</v>
+        <v>0.2285765158263853</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3456,16 +3456,16 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.42000007629395</v>
+        <v>18.32999992370605</v>
       </c>
       <c r="D11" t="n">
-        <v>18.42000007629395</v>
+        <v>18.32999992370605</v>
       </c>
       <c r="E11" t="n">
         <v>18.44000053405762</v>
@@ -3493,88 +3493,88 @@
         <v>18.20000076293945</v>
       </c>
       <c r="H11" t="n">
-        <v>19575800</v>
+        <v>21504500</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.009144705481364923</v>
+        <v>-0.01398602618331024</v>
       </c>
       <c r="J11" t="n">
-        <v>18.03777779473199</v>
+        <v>18.02777777777778</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>2.119009813246441</v>
+        <v>1.676424846443442</v>
       </c>
       <c r="M11" t="n">
-        <v>17.95300006866455</v>
+        <v>17.94400005340576</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.601236594682043</v>
+        <v>2.151136141058078</v>
       </c>
       <c r="P11" t="n">
-        <v>17.12115397820106</v>
+        <v>17.11769243387075</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>7.586206512403313</v>
+        <v>7.082189930206417</v>
       </c>
       <c r="S11" t="n">
-        <v>17.72434043884277</v>
+        <v>17.72254043579101</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>3.92488307168056</v>
+        <v>3.427609546813414</v>
       </c>
       <c r="V11" t="n">
-        <v>18.63291348775228</v>
+        <v>18.63231348673503</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.142673750931576</v>
+        <v>-1.622522953170566</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.79358511924744</v>
+        <v>18.7931351184845</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.987832766250028</v>
+        <v>-2.464384956839439</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2637896334650086</v>
+        <v>0.2656421579851223</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AE11" t="n">
         <v>18.2</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>18.3</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>18.4</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>18.6</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>18.7</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.220000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39.91999816894531</v>
+        <v>39.77000045776367</v>
       </c>
       <c r="D12" t="n">
-        <v>39.91999816894531</v>
+        <v>39.77000045776367</v>
       </c>
       <c r="E12" t="n">
         <v>40.11000061035156</v>
@@ -3792,67 +3792,67 @@
         <v>39.06000137329102</v>
       </c>
       <c r="H12" t="n">
-        <v>4465300</v>
+        <v>5314600</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01063286503659011</v>
+        <v>0.006835454626928472</v>
       </c>
       <c r="J12" t="n">
-        <v>41.12444390190972</v>
+        <v>41.10777748955621</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.928783027041679</v>
+        <v>-3.254316125780353</v>
       </c>
       <c r="M12" t="n">
-        <v>41.05199966430664</v>
+        <v>41.03699989318848</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.757481985330833</v>
+        <v>-3.087456292425291</v>
       </c>
       <c r="P12" t="n">
-        <v>39.10769213162936</v>
+        <v>39.1019229888916</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>2.077100419482393</v>
+        <v>1.708553998896329</v>
       </c>
       <c r="S12" t="n">
-        <v>39.92079971313476</v>
+        <v>39.91779975891113</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.002007836003311011</v>
+        <v>-0.3702591376281049</v>
       </c>
       <c r="V12" t="n">
-        <v>36.99646654764811</v>
+        <v>36.9954665629069</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>7.902191463425179</v>
+        <v>7.499659154558763</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.66059993743897</v>
+        <v>36.65984994888306</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.890738932446505</v>
+        <v>8.483805889051037</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3180849116888456</v>
+        <v>0.3170770528833803</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="n">
-        <v>8.44</v>
+        <v>8.41</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.119999885559082</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="D13" t="n">
-        <v>4.119999885559082</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="E13" t="n">
         <v>4.199999809265137</v>
@@ -4091,67 +4091,67 @@
         <v>4.139999866485596</v>
       </c>
       <c r="H13" t="n">
-        <v>23046300</v>
+        <v>24266800</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.002421362858288867</v>
+        <v>-0.01210658337757253</v>
       </c>
       <c r="J13" t="n">
-        <v>3.952222214804755</v>
+        <v>3.947777774598864</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>4.245147707683112</v>
+        <v>3.349280447292307</v>
       </c>
       <c r="M13" t="n">
-        <v>3.93899998664856</v>
+        <v>3.934999990463257</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>4.59507234130568</v>
+        <v>3.684877600869513</v>
       </c>
       <c r="P13" t="n">
-        <v>3.730000000733596</v>
+        <v>3.728461540662325</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>10.45576098522207</v>
+        <v>9.428510371097509</v>
       </c>
       <c r="S13" t="n">
-        <v>3.654400000572204</v>
+        <v>3.653600001335144</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>12.7408024549577</v>
+        <v>11.67067884319823</v>
       </c>
       <c r="V13" t="n">
-        <v>4.051200003623962</v>
+        <v>4.050933337211609</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.698259327448055</v>
+        <v>0.7175281367245023</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.503850005865097</v>
+        <v>4.503650006055832</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-8.522711009606214</v>
+        <v>-9.406816288568519</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5323405373351865</v>
+        <v>0.5341707454561956</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4303,13 +4303,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CC13" t="n">
         <v>8</v>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.83000183105469</v>
+        <v>60.47999954223633</v>
       </c>
       <c r="D14" t="n">
-        <v>60.83000183105469</v>
+        <v>60.47999954223633</v>
       </c>
       <c r="E14" t="n">
         <v>61</v>
@@ -4378,67 +4378,67 @@
         <v>59.11999893188477</v>
       </c>
       <c r="H14" t="n">
-        <v>7838700</v>
+        <v>8454000</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001644547234569416</v>
+        <v>-0.005590268896644268</v>
       </c>
       <c r="J14" t="n">
-        <v>59.26555633544922</v>
+        <v>59.22666719224718</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.639721268708834</v>
+        <v>2.116162211054167</v>
       </c>
       <c r="M14" t="n">
-        <v>58.81000061035157</v>
+        <v>58.77500038146972</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.434792041725582</v>
+        <v>2.900891790217917</v>
       </c>
       <c r="P14" t="n">
-        <v>54.51807726346529</v>
+        <v>54.50461563697228</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>11.57767273612062</v>
+        <v>10.96307869605587</v>
       </c>
       <c r="S14" t="n">
-        <v>55.33180015563965</v>
+        <v>55.32480010986328</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.936784380680663</v>
+        <v>9.318062464095517</v>
       </c>
       <c r="V14" t="n">
-        <v>56.28553326924642</v>
+        <v>56.2831999206543</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>8.073954882988193</v>
+        <v>7.456576078649585</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.0010499382019</v>
+        <v>55.99929992675781</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.622966708984233</v>
+        <v>8.001349340686181</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3530720712105907</v>
+        <v>0.3538003289106529</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.67</v>
+        <v>13.59</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CC14" t="n">
         <v>6</v>
@@ -4648,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM14" t="n">
         <v>10</v>
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.69000053405762</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="D15" t="n">
-        <v>21.69000053405762</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="E15" t="n">
         <v>22.14999961853027</v>
@@ -4685,67 +4685,67 @@
         <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>1790700</v>
+        <v>1978300</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03771075186089179</v>
+        <v>-0.03992908115895033</v>
       </c>
       <c r="J15" t="n">
-        <v>22.48777770996094</v>
+        <v>22.48222202724881</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.547603441268213</v>
+        <v>-3.746171693258707</v>
       </c>
       <c r="M15" t="n">
-        <v>22.43899993896484</v>
+        <v>22.43399982452393</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.337935767835205</v>
+        <v>-3.539272715904724</v>
       </c>
       <c r="P15" t="n">
-        <v>21.62384612743671</v>
+        <v>21.6219230064979</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3059326552318041</v>
+        <v>0.08360210673725514</v>
       </c>
       <c r="S15" t="n">
-        <v>21.59700000762939</v>
+        <v>21.59599998474121</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4306178005990189</v>
+        <v>0.2037386781733352</v>
       </c>
       <c r="V15" t="n">
-        <v>22.66006669362386</v>
+        <v>22.65973335266113</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.280950152009937</v>
+        <v>-4.500202836203886</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.36304998397827</v>
+        <v>22.36279997825623</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3.009649624728524</v>
+        <v>-3.232156032833913</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2836063496230136</v>
+        <v>0.2862088309586095</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.9</v>
+        <v>10.87</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.82999992370605</v>
+        <v>17.75</v>
       </c>
       <c r="D16" t="n">
-        <v>17.82999992370605</v>
+        <v>17.75</v>
       </c>
       <c r="E16" t="n">
         <v>18.60000038146973</v>
@@ -4976,88 +4976,88 @@
         <v>18.45000076293945</v>
       </c>
       <c r="H16" t="n">
-        <v>3687600</v>
+        <v>4134700</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.02515040835404059</v>
+        <v>-0.02952437881339354</v>
       </c>
       <c r="J16" t="n">
-        <v>18.33999994066026</v>
+        <v>18.33111106024848</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.780807080721549</v>
+        <v>-3.170080953296044</v>
       </c>
       <c r="M16" t="n">
-        <v>18.2189998626709</v>
+        <v>18.21099987030029</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.135133332768007</v>
+        <v>-2.531436349368827</v>
       </c>
       <c r="P16" t="n">
-        <v>18.27692295954778</v>
+        <v>18.27384603940524</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-2.445285986218212</v>
+        <v>-2.866643607895282</v>
       </c>
       <c r="S16" t="n">
-        <v>18.97419990539551</v>
+        <v>18.97259990692139</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.03029370089059</v>
+        <v>-6.444029352431409</v>
       </c>
       <c r="V16" t="n">
-        <v>19.18626656850179</v>
+        <v>19.18573323567708</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.068945070440781</v>
+        <v>-7.483337842972023</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.38224991321564</v>
+        <v>18.38184991359711</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.004256780953411</v>
+        <v>-3.437357592228663</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.3996478796963019</v>
+        <v>0.4019318467823466</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AE16" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AF16" t="n">
         <v>17.6</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>17.9</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>18</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>18.3</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
@@ -5184,13 +5184,13 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>35.66</v>
+        <v>35.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="CC16" t="n">
         <v>10</v>
@@ -5221,13 +5221,13 @@
         <v>2</v>
       </c>
       <c r="CM16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.070000171661377</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="D17" t="n">
-        <v>5.070000171661377</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="E17" t="n">
         <v>5.349999904632568</v>
@@ -5255,67 +5255,67 @@
         <v>5.210000038146973</v>
       </c>
       <c r="H17" t="n">
-        <v>2983800</v>
+        <v>3116400</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.03795062808140182</v>
+        <v>-0.03415556527326158</v>
       </c>
       <c r="J17" t="n">
-        <v>4.941111140780979</v>
+        <v>4.943333360883924</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.608502970447776</v>
+        <v>2.966961380038113</v>
       </c>
       <c r="M17" t="n">
-        <v>4.880000019073487</v>
+        <v>4.882000017166138</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.893445734534312</v>
+        <v>4.260551714264255</v>
       </c>
       <c r="P17" t="n">
-        <v>4.924999988996065</v>
+        <v>4.925769219031701</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.944166152066719</v>
+        <v>3.334117500301279</v>
       </c>
       <c r="S17" t="n">
-        <v>5.500399990081787</v>
+        <v>5.500799989700317</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.824882175778098</v>
+        <v>-7.468001706690061</v>
       </c>
       <c r="V17" t="n">
-        <v>8.326733299891155</v>
+        <v>8.32686663309733</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-39.11177422089824</v>
+        <v>-38.87256303161695</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.301249980926514</v>
+        <v>8.301349980831146</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-38.92485850551982</v>
+        <v>-38.68466979056013</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.074761045035555</v>
+        <v>1.073752436093836</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5470,7 +5470,7 @@
         <v>-0.44</v>
       </c>
       <c r="CA17" t="n">
-        <v>10.64</v>
+        <v>10.6</v>
       </c>
       <c r="CB17" t="n">
         <v>-0.26</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.399999618530273</v>
+        <v>9.350000381469727</v>
       </c>
       <c r="D18" t="n">
-        <v>9.399999618530273</v>
+        <v>9.350000381469727</v>
       </c>
       <c r="E18" t="n">
         <v>9.449999809265137</v>
@@ -5542,67 +5542,67 @@
         <v>9.060000419616699</v>
       </c>
       <c r="H18" t="n">
-        <v>5109700</v>
+        <v>5578200</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005347511766912616</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>9.248888863457573</v>
+        <v>9.243333392673069</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.633826044442378</v>
+        <v>1.153988331538593</v>
       </c>
       <c r="M18" t="n">
-        <v>9.155999946594239</v>
+        <v>9.151000022888184</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.664915611175763</v>
+        <v>2.174629637021197</v>
       </c>
       <c r="P18" t="n">
-        <v>8.468846174386831</v>
+        <v>8.466923126807579</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>10.99504495617858</v>
+        <v>10.42973039245141</v>
       </c>
       <c r="S18" t="n">
-        <v>9.113600006103516</v>
+        <v>9.112600021362304</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3.142551924979717</v>
+        <v>2.605187976547791</v>
       </c>
       <c r="V18" t="n">
-        <v>10.85506666183472</v>
+        <v>10.85473333358765</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.40449661557868</v>
+        <v>-13.86245894647495</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.38230000972748</v>
+        <v>11.38205001354217</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-17.41563998052329</v>
+        <v>-17.85310756546272</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.522000863064915</v>
+        <v>0.5217882524379458</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>4.95</v>
+        <v>4.92</v>
       </c>
       <c r="CA18" t="n">
         <v>0.05</v>
@@ -5790,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="CL18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM18" t="n">
         <v>9</v>
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="CO18" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.3100004196167</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="D19" t="n">
-        <v>11.3100004196167</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="E19" t="n">
         <v>11.31999969482422</v>
@@ -5827,67 +5827,67 @@
         <v>11.21000003814697</v>
       </c>
       <c r="H19" t="n">
-        <v>9893400</v>
+        <v>12209400</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01222702113367302</v>
+        <v>-0.02008729659979702</v>
       </c>
       <c r="J19" t="n">
-        <v>11.27222230699327</v>
+        <v>11.26222229003906</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3351434313000459</v>
+        <v>-0.3748995706433305</v>
       </c>
       <c r="M19" t="n">
-        <v>11.21500005722046</v>
+        <v>11.20600004196167</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8470830308652259</v>
+        <v>0.1249350795530478</v>
       </c>
       <c r="P19" t="n">
-        <v>10.68000001173753</v>
+        <v>10.67653846740723</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>5.898880217104743</v>
+        <v>5.090243446231506</v>
       </c>
       <c r="S19" t="n">
-        <v>10.89299997329712</v>
+        <v>10.89119997024536</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.828150622801861</v>
+        <v>3.018953813002476</v>
       </c>
       <c r="V19" t="n">
-        <v>11.51860005696615</v>
+        <v>11.51800005594889</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.810980816399575</v>
+        <v>-2.58725288654753</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43850003242493</v>
+        <v>11.43805003166199</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.123395658906035</v>
+        <v>-1.906354352617702</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.256606371062407</v>
+        <v>0.2608471790139753</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6039,13 +6039,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="CA19" t="n">
         <v>0.55</v>
       </c>
       <c r="CB19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="CC19" t="n">
         <v>5</v>
@@ -6076,13 +6076,13 @@
         <v>5</v>
       </c>
       <c r="CM19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN19" t="n">
         <v>0</v>
       </c>
       <c r="CO19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.230000019073486</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="D20" t="n">
-        <v>6.230000019073486</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="E20" t="n">
         <v>6.679999828338623</v>
@@ -6110,67 +6110,67 @@
         <v>6.519999980926514</v>
       </c>
       <c r="H20" t="n">
-        <v>11335600</v>
+        <v>11974600</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07291663488343492</v>
+        <v>-0.06845231780828609</v>
       </c>
       <c r="J20" t="n">
-        <v>6.594444380866157</v>
+        <v>6.597777737511529</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.526536289397012</v>
+        <v>-5.11956483028014</v>
       </c>
       <c r="M20" t="n">
-        <v>6.526999950408936</v>
+        <v>6.529999971389771</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.550328383514715</v>
+        <v>-4.134758708895843</v>
       </c>
       <c r="P20" t="n">
-        <v>6.054615369209876</v>
+        <v>6.055769223433274</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.89671001655218</v>
+        <v>3.372503110889261</v>
       </c>
       <c r="S20" t="n">
-        <v>5.767599973678589</v>
+        <v>5.768199977874755</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>8.017200352055234</v>
+        <v>8.526061039726299</v>
       </c>
       <c r="V20" t="n">
-        <v>5.138999986648559</v>
+        <v>5.139199988047282</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>21.22981193343866</v>
+        <v>21.80884658003783</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.259899990558624</v>
+        <v>5.260049991607666</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.44331698808276</v>
+        <v>19.01028010892627</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5135189603124447</v>
+        <v>0.5078842334566656</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6322,13 +6322,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>15.2</v>
+        <v>15.27</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6340,7 +6340,7 @@
         <v>8</v>
       </c>
       <c r="CF20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CG20" t="n">
         <v>1</v>
@@ -6349,7 +6349,7 @@
         <v>9</v>
       </c>
       <c r="CI20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -6397,7 +6397,7 @@
         <v>2.269999980926514</v>
       </c>
       <c r="H21" t="n">
-        <v>32322200</v>
+        <v>33197100</v>
       </c>
       <c r="I21" t="n">
         <v>0.004291841541072206</v>
@@ -6645,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM21" t="n">
         <v>3</v>
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44.65999984741211</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="D22" t="n">
-        <v>44.65999984741211</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="E22" t="n">
         <v>45.2400016784668</v>
@@ -6682,67 +6682,67 @@
         <v>45.20000076293945</v>
       </c>
       <c r="H22" t="n">
-        <v>3749800</v>
+        <v>3973900</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01932369456354555</v>
+        <v>-0.01778659106295355</v>
       </c>
       <c r="J22" t="n">
-        <v>46.06777784559462</v>
+        <v>46.07555558946397</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.05588431658449</v>
+        <v>-2.920325170284723</v>
       </c>
       <c r="M22" t="n">
-        <v>45.91500015258789</v>
+        <v>45.92200012207032</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.733312209528652</v>
+        <v>-2.595707017693915</v>
       </c>
       <c r="P22" t="n">
-        <v>44.19846182603102</v>
+        <v>44.2011541219858</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.04424000816531</v>
+        <v>1.196451610270233</v>
       </c>
       <c r="S22" t="n">
-        <v>45.13800010681152</v>
+        <v>45.13940010070801</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.058975271984377</v>
+        <v>-0.9069694270599304</v>
       </c>
       <c r="V22" t="n">
-        <v>46.90086652119955</v>
+        <v>46.9013331858317</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.777879045741187</v>
+        <v>-4.62957766038793</v>
       </c>
       <c r="Y22" t="n">
-        <v>48.01614994049072</v>
+        <v>48.01649993896484</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.989627650776016</v>
+        <v>-6.844523030429288</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.2674383510186987</v>
+        <v>0.2665562627504393</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>8.93</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="CA22" t="n">
         <v>0.5</v>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.93000030517578</v>
+        <v>15.92000007629395</v>
       </c>
       <c r="D23" t="n">
-        <v>15.93000030517578</v>
+        <v>15.92000007629395</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
@@ -6965,67 +6965,67 @@
         <v>15.60999965667725</v>
       </c>
       <c r="H23" t="n">
-        <v>18704900</v>
+        <v>19836500</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.001879682512499148</v>
+        <v>-0.002506263268008846</v>
       </c>
       <c r="J23" t="n">
-        <v>15.82666662004259</v>
+        <v>15.82555548350016</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6529087116950595</v>
+        <v>0.5967853254329792</v>
       </c>
       <c r="M23" t="n">
-        <v>15.73899993896484</v>
+        <v>15.73799991607666</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.213548300092947</v>
+        <v>1.156437674341125</v>
       </c>
       <c r="P23" t="n">
-        <v>14.76923069587121</v>
+        <v>14.76884607168344</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7.859377602037678</v>
+        <v>7.794474930696374</v>
       </c>
       <c r="S23" t="n">
-        <v>14.82679998397827</v>
+        <v>14.82659997940064</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.440582744689485</v>
+        <v>7.374584182566656</v>
       </c>
       <c r="V23" t="n">
-        <v>14.99579993565877</v>
+        <v>14.99573326746623</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>6.229746819278087</v>
+        <v>6.163531935000126</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.51914995670319</v>
+        <v>14.51909995555878</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>9.717169067609463</v>
+        <v>9.648670544476962</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1974358454563485</v>
+        <v>0.1975639089499049</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7177,7 +7177,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.51</v>
+        <v>17.49</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.599999904632568</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="D24" t="n">
-        <v>3.599999904632568</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="E24" t="n">
         <v>3.690000057220459</v>
@@ -7248,67 +7248,67 @@
         <v>3.599999904632568</v>
       </c>
       <c r="H24" t="n">
-        <v>24303600</v>
+        <v>25935800</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.02702706534118826</v>
+        <v>-0.02432436525081472</v>
       </c>
       <c r="J24" t="n">
-        <v>3.803333308961657</v>
+        <v>3.804444419013129</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.346189455706684</v>
+        <v>-5.110983431524092</v>
       </c>
       <c r="M24" t="n">
-        <v>3.812999987602234</v>
+        <v>3.81399998664856</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.586154829851138</v>
+        <v>-5.348717678732704</v>
       </c>
       <c r="P24" t="n">
-        <v>3.598461545430697</v>
+        <v>3.598846160448514</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.04275046940059138</v>
+        <v>0.3099252968879523</v>
       </c>
       <c r="S24" t="n">
-        <v>3.746600017547607</v>
+        <v>3.746800017356873</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.912884007591454</v>
+        <v>-3.651118864826718</v>
       </c>
       <c r="V24" t="n">
-        <v>4.536066668828329</v>
+        <v>4.536133335431416</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-20.63608920539846</v>
+        <v>-20.41680373682203</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.808050010204315</v>
+        <v>4.808100010156632</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-25.12557279994705</v>
+        <v>-24.91836926290924</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5926455918284543</v>
+        <v>0.5917611403160902</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7463,10 +7463,10 @@
         <v>-1.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.04999923706055</v>
+        <v>56.86999893188477</v>
       </c>
       <c r="D25" t="n">
-        <v>57.04999923706055</v>
+        <v>56.86999893188477</v>
       </c>
       <c r="E25" t="n">
         <v>57.61999893188477</v>
@@ -7535,67 +7535,67 @@
         <v>55.38999938964844</v>
       </c>
       <c r="H25" t="n">
-        <v>2912000</v>
+        <v>3148800</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01966038354104405</v>
+        <v>0.01644321995353226</v>
       </c>
       <c r="J25" t="n">
-        <v>56.3522220187717</v>
+        <v>56.33222198486328</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.238242598590717</v>
+        <v>0.9546524672255738</v>
       </c>
       <c r="M25" t="n">
-        <v>56.23899993896485</v>
+        <v>56.22099990844727</v>
       </c>
       <c r="N25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.442058534070422</v>
+        <v>1.154371186023649</v>
       </c>
       <c r="P25" t="n">
-        <v>56.13576933053824</v>
+        <v>56.12884624187763</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.628604929486485</v>
+        <v>1.320448823788865</v>
       </c>
       <c r="S25" t="n">
-        <v>59.89119979858398</v>
+        <v>59.88759979248047</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.743936623541496</v>
+        <v>-5.038774088546121</v>
       </c>
       <c r="V25" t="n">
-        <v>57.19726648966471</v>
+        <v>57.19606648763021</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2574725360883755</v>
+        <v>-0.5700873779772335</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.13959991455078</v>
+        <v>54.1386999130249</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.37573112306572</v>
+        <v>5.045002970606537</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.291570326925588</v>
+        <v>0.2894673551252709</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7743,7 +7743,7 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>16.03</v>
+        <v>15.97</v>
       </c>
       <c r="CA25" t="n">
         <v>0.32</v>
@@ -7818,7 +7818,7 @@
         <v>6.519999980926514</v>
       </c>
       <c r="H26" t="n">
-        <v>27395600</v>
+        <v>28450400</v>
       </c>
       <c r="I26" t="n">
         <v>-0.04654653902131822</v>
@@ -8067,13 +8067,13 @@
         <v>10</v>
       </c>
       <c r="CM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN26" t="n">
         <v>-1</v>
       </c>
       <c r="CO26" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30.88999938964844</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="D27" t="n">
-        <v>30.88999938964844</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="E27" t="n">
         <v>31.34000015258789</v>
@@ -8101,67 +8101,67 @@
         <v>30.96999931335449</v>
       </c>
       <c r="H27" t="n">
-        <v>4675800</v>
+        <v>4965200</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.02922691119092169</v>
+        <v>-0.03205532581854753</v>
       </c>
       <c r="J27" t="n">
-        <v>32.53555552164713</v>
+        <v>32.52555550469292</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-5.057716413982374</v>
+        <v>-5.305232273076496</v>
       </c>
       <c r="M27" t="n">
-        <v>32.54199981689453</v>
+        <v>32.53299980163574</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.076517843222529</v>
+        <v>-5.326900609048841</v>
       </c>
       <c r="P27" t="n">
-        <v>31.92115394885723</v>
+        <v>31.92384624481201</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-3.230317302629068</v>
+        <v>-3.520399763653487</v>
       </c>
       <c r="S27" t="n">
-        <v>31.7338000869751</v>
+        <v>31.66720008850098</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.658996700722874</v>
+        <v>-2.738482875078458</v>
       </c>
       <c r="V27" t="n">
-        <v>33.4411334101359</v>
+        <v>33.40653340657552</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.628730728708574</v>
+        <v>-7.802468271077537</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.71105000495911</v>
+        <v>33.68110000610351</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-8.36832615684078</v>
+        <v>-8.554057820323173</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4398009423660922</v>
+        <v>0.441584248230227</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8309,13 +8309,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>8.93</v>
+        <v>8.9</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB27" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20.09000015258789</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="D28" t="n">
-        <v>20.09000015258789</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="E28" t="n">
         <v>20.10000038146973</v>
@@ -8384,67 +8384,67 @@
         <v>19.60000038146973</v>
       </c>
       <c r="H28" t="n">
-        <v>9119800</v>
+        <v>8565400</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01362262673667858</v>
+        <v>0.01210896946586915</v>
       </c>
       <c r="J28" t="n">
-        <v>19.90555551317003</v>
+        <v>19.90222210354275</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9265988045188113</v>
+        <v>0.7927625446986941</v>
       </c>
       <c r="M28" t="n">
-        <v>19.84899997711182</v>
+        <v>19.84599990844726</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21416784600723</v>
+        <v>1.078300707862197</v>
       </c>
       <c r="P28" t="n">
-        <v>19.06576919555664</v>
+        <v>19.06461532299335</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>5.372093549049946</v>
+        <v>5.221107932602889</v>
       </c>
       <c r="S28" t="n">
-        <v>20.07300003051758</v>
+        <v>20.07240001678467</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08469148629735673</v>
+        <v>-0.06177911376774796</v>
       </c>
       <c r="V28" t="n">
-        <v>18.87146675109863</v>
+        <v>18.87126674652099</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>6.457014802086425</v>
+        <v>6.299167593720418</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.28085009098053</v>
+        <v>18.2807000875473</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.896421953046739</v>
+        <v>9.733212458351788</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2490389125260893</v>
+        <v>0.2483494336782166</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8604,13 +8604,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>13.76</v>
+        <v>13.74</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.39999961853027</v>
+        <v>25.32999992370605</v>
       </c>
       <c r="D29" t="n">
-        <v>25.39999961853027</v>
+        <v>25.32999992370605</v>
       </c>
       <c r="E29" t="n">
         <v>25.6200008392334</v>
@@ -8679,67 +8679,67 @@
         <v>25.21999931335449</v>
       </c>
       <c r="H29" t="n">
-        <v>6926800</v>
+        <v>7443200</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.02194839083153577</v>
+        <v>-0.02464379694147056</v>
       </c>
       <c r="J29" t="n">
-        <v>25.47444449530708</v>
+        <v>25.46666675143772</v>
       </c>
       <c r="K29" t="n">
         <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.2922335628967937</v>
+        <v>-0.5366498453275091</v>
       </c>
       <c r="M29" t="n">
-        <v>25.3560001373291</v>
+        <v>25.34900016784668</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.17352690078431</v>
+        <v>-0.07495460970774179</v>
       </c>
       <c r="P29" t="n">
-        <v>23.44384618905874</v>
+        <v>23.44115389310397</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>8.343995322680749</v>
+        <v>8.057820187587945</v>
       </c>
       <c r="S29" t="n">
-        <v>22.59280002593994</v>
+        <v>22.59140003204346</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>12.42519559048566</v>
+        <v>12.12231153349589</v>
       </c>
       <c r="V29" t="n">
-        <v>24.53073333740234</v>
+        <v>24.53026667277018</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>3.543580492159805</v>
+        <v>3.260189795749822</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.9181999874115</v>
+        <v>25.91784998893738</v>
       </c>
       <c r="Z29" t="n">
         <v>-1</v>
       </c>
       <c r="AA29" t="n">
-        <v>-1.999368664231756</v>
+        <v>-2.26812820308103</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.3846318719031601</v>
+        <v>0.3864124863402995</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8887,10 +8887,10 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>5.87</v>
+        <v>5.85</v>
       </c>
       <c r="CA29" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="CB29" t="n">
         <v>1.09</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.18000030517578</v>
+        <v>10.13000011444092</v>
       </c>
       <c r="D30" t="n">
-        <v>10.18000030517578</v>
+        <v>10.13000011444092</v>
       </c>
       <c r="E30" t="n">
         <v>10.3100004196167</v>
@@ -8958,67 +8958,67 @@
         <v>10.19999980926514</v>
       </c>
       <c r="H30" t="n">
-        <v>9469000</v>
+        <v>10630900</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.02769818094143406</v>
+        <v>-0.03247374822506821</v>
       </c>
       <c r="J30" t="n">
-        <v>11.04888905419244</v>
+        <v>11.04333347744412</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.864037232656981</v>
+        <v>-8.270449904176791</v>
       </c>
       <c r="M30" t="n">
-        <v>11.0560001373291</v>
+        <v>11.05100011825562</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-7.923297949279366</v>
+        <v>-8.33408735824062</v>
       </c>
       <c r="P30" t="n">
-        <v>10.89076929826003</v>
+        <v>10.888846214001</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.526343306140954</v>
+        <v>-6.969022104328603</v>
       </c>
       <c r="S30" t="n">
-        <v>11.48840002059936</v>
+        <v>11.48740001678467</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-11.38887671980038</v>
+        <v>-11.81642408517509</v>
       </c>
       <c r="V30" t="n">
-        <v>13.17933336257935</v>
+        <v>13.17900002797445</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-22.75785106035561</v>
+        <v>-23.13529028804582</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.68820001602173</v>
+        <v>13.68795001506805</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-25.62937206308849</v>
+        <v>-25.9932999222707</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3968815520507438</v>
+        <v>0.3996623502986902</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9166,13 +9166,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.32</v>
+        <v>6.29</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CC30" t="n">
         <v>9</v>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.53000068664551</v>
+        <v>30.45999908447266</v>
       </c>
       <c r="D31" t="n">
-        <v>30.53000068664551</v>
+        <v>30.45999908447266</v>
       </c>
       <c r="E31" t="n">
         <v>30.53000068664551</v>
@@ -9237,67 +9237,67 @@
         <v>30.04000091552734</v>
       </c>
       <c r="H31" t="n">
-        <v>1719300</v>
+        <v>1924100</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.007154449214780256</v>
+        <v>-0.00943092408219004</v>
       </c>
       <c r="J31" t="n">
-        <v>30.39666663275825</v>
+        <v>30.38888867696126</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4386469592148221</v>
+        <v>0.234001342620026</v>
       </c>
       <c r="M31" t="n">
-        <v>30.29499988555908</v>
+        <v>30.2879997253418</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7757082091901392</v>
+        <v>0.5678795585399687</v>
       </c>
       <c r="P31" t="n">
-        <v>29.18538460364709</v>
+        <v>29.15730762481689</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>4.607155606338639</v>
+        <v>4.467804354291586</v>
       </c>
       <c r="S31" t="n">
-        <v>29.9961999130249</v>
+        <v>29.93699989318848</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.779561328329523</v>
+        <v>1.746999342453068</v>
       </c>
       <c r="V31" t="n">
-        <v>32.44733337402344</v>
+        <v>32.41980002085368</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-5.909060893468983</v>
+        <v>-6.045074106318983</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.17060717582703</v>
+        <v>32.16422145843506</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-5.099706325761463</v>
+        <v>-5.298503419909361</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2200797256272362</v>
+        <v>0.2164731917799287</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.57</v>
+        <v>13.54</v>
       </c>
       <c r="CA31" t="n">
         <v>0.71</v>
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>96.65000152587891</v>
+        <v>96.51999664306641</v>
       </c>
       <c r="D32" t="n">
-        <v>96.65000152587891</v>
+        <v>96.51999664306641</v>
       </c>
       <c r="E32" t="n">
         <v>96.84999847412109</v>
@@ -9516,67 +9516,67 @@
         <v>95.11000061035156</v>
       </c>
       <c r="H32" t="n">
-        <v>4482900</v>
+        <v>4769200</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.002991550528406828</v>
+        <v>-0.004332636556242164</v>
       </c>
       <c r="J32" t="n">
-        <v>94.72222306993272</v>
+        <v>94.70777808295355</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>2.035191313576876</v>
+        <v>1.913484400959708</v>
       </c>
       <c r="M32" t="n">
-        <v>94.5990005493164</v>
+        <v>94.58600006103515</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>2.168100048259259</v>
+        <v>2.044696446390874</v>
       </c>
       <c r="P32" t="n">
-        <v>96.1719231238732</v>
+        <v>96.16692293607272</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4971080815238802</v>
+        <v>0.3671467238567988</v>
       </c>
       <c r="S32" t="n">
-        <v>90.97380004882812</v>
+        <v>90.97119995117187</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>6.239380430414261</v>
+        <v>6.099509179688532</v>
       </c>
       <c r="V32" t="n">
-        <v>83.87899993896484</v>
+        <v>83.87813323974609</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>15.2255053067001</v>
+        <v>15.07170333319948</v>
       </c>
       <c r="Y32" t="n">
-        <v>85.86269989013672</v>
+        <v>85.86204986572265</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.5634316758555</v>
+        <v>12.41287250189278</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2733340562953592</v>
+        <v>0.2736467062723927</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9726,7 +9726,7 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>42.21</v>
+        <v>42.15</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
@@ -9767,13 +9767,13 @@
         <v>7</v>
       </c>
       <c r="CM32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
@@ -9786,10 +9786,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26.89999961853027</v>
+        <v>26.94000053405762</v>
       </c>
       <c r="D33" t="n">
-        <v>26.89999961853027</v>
+        <v>26.94000053405762</v>
       </c>
       <c r="E33" t="n">
         <v>27.20000076293945</v>
@@ -9801,67 +9801,67 @@
         <v>26.69000053405762</v>
       </c>
       <c r="H33" t="n">
-        <v>7091800</v>
+        <v>8129000</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.01681290137278901</v>
+        <v>-0.01535087963905379</v>
       </c>
       <c r="J33" t="n">
-        <v>27.34888903299968</v>
+        <v>27.35333357916938</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.641344238618848</v>
+        <v>-1.511088379467328</v>
       </c>
       <c r="M33" t="n">
-        <v>27.23500003814697</v>
+        <v>27.23900012969971</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.230036420589228</v>
+        <v>-1.097689321261393</v>
       </c>
       <c r="P33" t="n">
-        <v>26.05692313267635</v>
+        <v>26.05846162942739</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>3.235518182868946</v>
+        <v>3.382927653851656</v>
       </c>
       <c r="S33" t="n">
-        <v>26.11820003509521</v>
+        <v>26.11900005340576</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2.993313407449786</v>
+        <v>3.143307473383922</v>
       </c>
       <c r="V33" t="n">
-        <v>25.01866663614909</v>
+        <v>25.01893330891927</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>7.51971721651575</v>
+        <v>7.678453759071678</v>
       </c>
       <c r="Y33" t="n">
-        <v>23.90695000648499</v>
+        <v>23.90715001106262</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.51957949982492</v>
+        <v>12.68595596543961</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2621865948013879</v>
+        <v>0.2613626365646027</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>40.15</v>
+        <v>40.21</v>
       </c>
       <c r="CA33" t="n">
         <v>0.35</v>
@@ -10047,16 +10047,16 @@
         <v>0</v>
       </c>
       <c r="CL33" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM33" t="n">
         <v>4</v>
       </c>
-      <c r="CM33" t="n">
-        <v>3</v>
-      </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>51.5</v>
+        <v>51.34999847412109</v>
       </c>
       <c r="D34" t="n">
-        <v>51.5</v>
+        <v>51.34999847412109</v>
       </c>
       <c r="E34" t="n">
         <v>51.5099983215332</v>
@@ -10084,67 +10084,67 @@
         <v>50.20999908447266</v>
       </c>
       <c r="H34" t="n">
-        <v>1674400</v>
+        <v>1885600</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.002131381690576806</v>
+        <v>-0.005037824707530003</v>
       </c>
       <c r="J34" t="n">
-        <v>51.06666692097982</v>
+        <v>51.05000008477105</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8485634664402834</v>
+        <v>0.5876560016687209</v>
       </c>
       <c r="M34" t="n">
-        <v>50.76000022888184</v>
+        <v>50.74500007629395</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.457840362059559</v>
+        <v>1.192232529150743</v>
       </c>
       <c r="P34" t="n">
-        <v>47.45769221966084</v>
+        <v>47.45192293020395</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>8.517708281365845</v>
+        <v>8.21478941886242</v>
       </c>
       <c r="S34" t="n">
-        <v>48.58339988708496</v>
+        <v>48.58039985656738</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>6.003285319046534</v>
+        <v>5.701061798031497</v>
       </c>
       <c r="V34" t="n">
-        <v>50.28193333943685</v>
+        <v>50.28093332926432</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>2.422473798571714</v>
+        <v>2.126183970882177</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.88981359481811</v>
+        <v>49.88906358718872</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.227485310446479</v>
+        <v>2.928367024526659</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3081745133076231</v>
+        <v>0.3085701750814533</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10292,7 +10292,7 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>13.62</v>
+        <v>13.58</v>
       </c>
       <c r="CA34" t="n">
         <v>0.26</v>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.68000030517578</v>
+        <v>39.47999954223633</v>
       </c>
       <c r="D35" t="n">
-        <v>39.68000030517578</v>
+        <v>39.47999954223633</v>
       </c>
       <c r="E35" t="n">
         <v>39.79999923706055</v>
@@ -10363,88 +10363,88 @@
         <v>38.59999847412109</v>
       </c>
       <c r="H35" t="n">
-        <v>8168200</v>
+        <v>11507800</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0007565896126711102</v>
+        <v>-0.004287565626740819</v>
       </c>
       <c r="J35" t="n">
-        <v>39.00444454616971</v>
+        <v>38.98222223917643</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.731996870783316</v>
+        <v>1.276934136811834</v>
       </c>
       <c r="M35" t="n">
-        <v>38.77099990844727</v>
+        <v>38.75099983215332</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>2.344536893232063</v>
+        <v>1.881241034400686</v>
       </c>
       <c r="P35" t="n">
-        <v>36.95615416306715</v>
+        <v>36.94846182603102</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>7.370480516153803</v>
+        <v>6.851537495998769</v>
       </c>
       <c r="S35" t="n">
-        <v>38.04560020446777</v>
+        <v>38.04160018920899</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>4.295897796129592</v>
+        <v>3.781122102837736</v>
       </c>
       <c r="V35" t="n">
-        <v>39.78793342590332</v>
+        <v>39.78660008748373</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.2712709895540067</v>
+        <v>-0.7706125795449678</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.65245006561279</v>
+        <v>39.65145006179809</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.06947928694797953</v>
+        <v>-0.4323940720819916</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2552562375245357</v>
+        <v>0.2557150893978988</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AE35" t="n">
         <v>39</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AF35" t="n">
         <v>39.2</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
         <v>39.5</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>39.8</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>41.2</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>46.3</v>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
@@ -10571,13 +10571,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.26</v>
+        <v>32.1</v>
       </c>
       <c r="CA35" t="n">
         <v>0.92</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC35" t="n">
         <v>8</v>
@@ -10608,13 +10608,13 @@
         <v>5</v>
       </c>
       <c r="CM35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.55999946594238</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="D36" t="n">
-        <v>21.55999946594238</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="E36" t="n">
         <v>21.6299991607666</v>
@@ -10642,67 +10642,67 @@
         <v>20.73999977111816</v>
       </c>
       <c r="H36" t="n">
-        <v>3546400</v>
+        <v>4001100</v>
       </c>
       <c r="I36" t="n">
-        <v>0.02374169101041934</v>
+        <v>0.0161443571324742</v>
       </c>
       <c r="J36" t="n">
-        <v>20.4288887447781</v>
+        <v>20.41111098395454</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>5.536819624872679</v>
+        <v>4.844854527287204</v>
       </c>
       <c r="M36" t="n">
-        <v>20.35399990081787</v>
+        <v>20.33799991607666</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>5.925123174811704</v>
+        <v>5.221750943238664</v>
       </c>
       <c r="P36" t="n">
-        <v>19.20999989142785</v>
+        <v>19.20384605114277</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>12.23320972304213</v>
+        <v>11.4360090241237</v>
       </c>
       <c r="S36" t="n">
-        <v>17.93719989776611</v>
+        <v>17.93399990081787</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>20.19712992453995</v>
+        <v>19.32641762507392</v>
       </c>
       <c r="V36" t="n">
-        <v>16.66226661682129</v>
+        <v>16.66119995117187</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>29.39415724014774</v>
+        <v>28.44212710516744</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.38149998664856</v>
+        <v>16.3806999874115</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>31.61187610117794</v>
+        <v>30.64154544662978</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.373634587921211</v>
+        <v>0.3714843687686921</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10854,13 +10854,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.59</v>
+        <v>18.45</v>
       </c>
       <c r="CA36" t="n">
         <v>0.27</v>
       </c>
       <c r="CB36" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CC36" t="n">
         <v>9</v>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.34000015258789</v>
+        <v>25.05999946594238</v>
       </c>
       <c r="D37" t="n">
-        <v>25.34000015258789</v>
+        <v>25.05999946594238</v>
       </c>
       <c r="E37" t="n">
         <v>25.70000076293945</v>
@@ -10925,67 +10925,67 @@
         <v>25.3700008392334</v>
       </c>
       <c r="H37" t="n">
-        <v>7548200</v>
+        <v>8431100</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.02911878229018783</v>
+        <v>-0.03984677779030665</v>
       </c>
       <c r="J37" t="n">
-        <v>25.40111117892795</v>
+        <v>25.3699999915229</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.2405840670102541</v>
+        <v>-1.221917720473379</v>
       </c>
       <c r="M37" t="n">
-        <v>25.23500003814697</v>
+        <v>25.20699996948242</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.4160892184751098</v>
+        <v>-0.5831733396199814</v>
       </c>
       <c r="P37" t="n">
-        <v>24.33038454789382</v>
+        <v>24.31961529071515</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>4.149608086574493</v>
+        <v>3.044390983889885</v>
       </c>
       <c r="S37" t="n">
-        <v>24.19039993286133</v>
+        <v>24.18479991912842</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>4.752299353946989</v>
+        <v>3.618800030351891</v>
       </c>
       <c r="V37" t="n">
-        <v>22.379266649882</v>
+        <v>22.37739997863769</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>13.2298057350396</v>
+        <v>11.9879856009438</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.02114999771118</v>
+        <v>22.01974999427796</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>15.07119362622598</v>
+        <v>13.80692093440873</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.3891791026564201</v>
+        <v>0.3974913403177197</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11137,13 +11137,13 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>30.53</v>
+        <v>30.19</v>
       </c>
       <c r="CA37" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CC37" t="n">
         <v>1</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="CL37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM37" t="n">
         <v>5</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.22000026702881</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D38" t="n">
-        <v>11.22000026702881</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="E38" t="n">
         <v>11.52999973297119</v>
@@ -11208,67 +11208,67 @@
         <v>11.35000038146973</v>
       </c>
       <c r="H38" t="n">
-        <v>7998200</v>
+        <v>8782900</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0352536408751204</v>
+        <v>-0.03611350577481365</v>
       </c>
       <c r="J38" t="n">
-        <v>11.19333351982964</v>
+        <v>11.19222238328722</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2382377613596842</v>
+        <v>0.1588393640775138</v>
       </c>
       <c r="M38" t="n">
-        <v>11.11300020217896</v>
+        <v>11.11200017929077</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9628368838585373</v>
+        <v>0.8819281612219769</v>
       </c>
       <c r="P38" t="n">
-        <v>10.74653849234948</v>
+        <v>10.74615386816171</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>4.405714221527155</v>
+        <v>4.316392410493241</v>
       </c>
       <c r="S38" t="n">
-        <v>10.63800001144409</v>
+        <v>10.63780000686645</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>5.470955583367322</v>
+        <v>5.378932024583808</v>
       </c>
       <c r="V38" t="n">
-        <v>9.875933338801065</v>
+        <v>9.87586667060852</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>13.60951802850983</v>
+        <v>13.50902570919629</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.701582591533661</v>
+        <v>9.701532590389252</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>15.651236910772</v>
+        <v>15.54875411388167</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3885019346684512</v>
+        <v>0.3892102581688434</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>26.09</v>
+        <v>26.07</v>
       </c>
       <c r="CA38" t="n">
         <v>0.55</v>
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.730000019073486</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="D39" t="n">
-        <v>6.730000019073486</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="E39" t="n">
         <v>6.829999923706055</v>
@@ -11495,67 +11495,67 @@
         <v>6.619999885559082</v>
       </c>
       <c r="H39" t="n">
-        <v>7299500</v>
+        <v>7701500</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-0.001485918106016948</v>
       </c>
       <c r="J39" t="n">
-        <v>7.003333356645372</v>
+        <v>7.002222220102946</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.902903426873484</v>
+        <v>-4.030469485830552</v>
       </c>
       <c r="M39" t="n">
-        <v>6.964000034332275</v>
+        <v>6.963000011444092</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-3.36013805435349</v>
+        <v>-3.48987822566504</v>
       </c>
       <c r="P39" t="n">
-        <v>7.229615431565505</v>
+        <v>7.229230807377742</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-6.910677576439659</v>
+        <v>-7.044055318670961</v>
       </c>
       <c r="S39" t="n">
-        <v>8.965400009155273</v>
+        <v>8.965200004577637</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-24.93363361142887</v>
+        <v>-25.04350391781094</v>
       </c>
       <c r="V39" t="n">
-        <v>10.38619998931885</v>
+        <v>10.3861333211263</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-35.20247996385002</v>
+        <v>-35.29834845733605</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.36389998912811</v>
+        <v>11.3638499879837</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-40.77737374042271</v>
+        <v>-40.86511351964807</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.138202110016387</v>
+        <v>1.138050422733464</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11707,7 +11707,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>-7.92</v>
+        <v>-7.91</v>
       </c>
       <c r="CA39" t="n">
         <v>1.47</v>
@@ -11767,10 +11767,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.48999977111816</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="D40" t="n">
-        <v>23.48999977111816</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="E40" t="n">
         <v>23.59000015258789</v>
@@ -11782,67 +11782,67 @@
         <v>22.22999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>2951800</v>
+        <v>3131100</v>
       </c>
       <c r="I40" t="n">
-        <v>0.03207379327307636</v>
+        <v>0.03383130272496926</v>
       </c>
       <c r="J40" t="n">
-        <v>22.76222207811144</v>
+        <v>22.76666662428114</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>3.197305124733728</v>
+        <v>3.352858259672729</v>
       </c>
       <c r="M40" t="n">
-        <v>22.65599994659424</v>
+        <v>22.66000003814697</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.681143301950334</v>
+        <v>3.839367374377464</v>
       </c>
       <c r="P40" t="n">
-        <v>21.85076918968787</v>
+        <v>21.85230768643893</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>7.501935365295512</v>
+        <v>7.677417983857702</v>
       </c>
       <c r="S40" t="n">
-        <v>21.41340007781982</v>
+        <v>21.41420009613037</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.697664479959446</v>
+        <v>9.880362474512735</v>
       </c>
       <c r="V40" t="n">
-        <v>22.07400001525879</v>
+        <v>22.07426668802897</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6.414785516356599</v>
+        <v>6.594710570412706</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.64615001678467</v>
+        <v>22.64635002136231</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.726239355069452</v>
+        <v>3.901956228927197</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2590373408228859</v>
+        <v>0.2607695918235784</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="CA40" t="n">
         <v>0.38</v>
@@ -12024,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="CL40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM40" t="n">
         <v>10</v>
@@ -12033,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="CO40" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
@@ -12046,10 +12046,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.93000030517578</v>
+        <v>25.76000022888184</v>
       </c>
       <c r="D41" t="n">
-        <v>25.93000030517578</v>
+        <v>25.76000022888184</v>
       </c>
       <c r="E41" t="n">
         <v>25.97999954223633</v>
@@ -12061,88 +12061,88 @@
         <v>25.36000061035156</v>
       </c>
       <c r="H41" t="n">
-        <v>1451900</v>
+        <v>1802500</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.005370133919726627</v>
+        <v>-0.01189104217764636</v>
       </c>
       <c r="J41" t="n">
-        <v>26.11444452073839</v>
+        <v>26.09555562337239</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.7062919351630603</v>
+        <v>-1.285871814087835</v>
       </c>
       <c r="M41" t="n">
-        <v>25.9560001373291</v>
+        <v>25.93900012969971</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.100168870456773</v>
+        <v>-0.6900801878362278</v>
       </c>
       <c r="P41" t="n">
-        <v>24.63999997652494</v>
+        <v>24.6334615120521</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>5.23539094918771</v>
+        <v>4.57320509453603</v>
       </c>
       <c r="S41" t="n">
-        <v>24.91400001525879</v>
+        <v>24.91060001373291</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>4.078029578930456</v>
+        <v>3.409794283078936</v>
       </c>
       <c r="V41" t="n">
-        <v>26.4060666402181</v>
+        <v>26.40493330637614</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.802867278677695</v>
+        <v>-2.442471904818517</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.42614995956421</v>
+        <v>26.42529995918274</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.877495038617463</v>
+        <v>-2.517661980482879</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3234968555242734</v>
+        <v>0.3252730395763057</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AE41" t="n">
         <v>25.4</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AF41" t="n">
         <v>25.7</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AG41" t="n">
         <v>25.8</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>26</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>26.2</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>26.4</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12269,13 +12269,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="CA41" t="n">
         <v>0.04</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CC41" t="n">
         <v>7</v>
@@ -12325,10 +12325,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.32999992370605</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="D42" t="n">
-        <v>27.32999992370605</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="E42" t="n">
         <v>27.45999908447266</v>
@@ -12340,67 +12340,67 @@
         <v>27.11000061035156</v>
       </c>
       <c r="H42" t="n">
-        <v>1907300</v>
+        <v>2129000</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.01406924239931528</v>
+        <v>-0.01587296672467842</v>
       </c>
       <c r="J42" t="n">
-        <v>27.62888866000705</v>
+        <v>27.62333318922255</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.081797896321619</v>
+        <v>-1.242907581880797</v>
       </c>
       <c r="M42" t="n">
-        <v>27.52899971008301</v>
+        <v>27.52399978637695</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.7228732917021476</v>
+        <v>-0.886495791400981</v>
       </c>
       <c r="P42" t="n">
-        <v>26.55230764242319</v>
+        <v>26.55038459484394</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.928906563436799</v>
+        <v>2.748043401010702</v>
       </c>
       <c r="S42" t="n">
-        <v>27.137200050354</v>
+        <v>27.13620006561279</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0.7104633970870403</v>
+        <v>0.5299217306955926</v>
       </c>
       <c r="V42" t="n">
-        <v>28.19013334910075</v>
+        <v>28.18980002085368</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-3.051186082531003</v>
+        <v>-3.227406131065623</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98100001335144</v>
+        <v>27.98075001716614</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-2.326579069135321</v>
+        <v>-2.504397952487768</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1768636732591779</v>
+        <v>0.1782356988785002</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12548,7 +12548,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.68</v>
+        <v>7.66</v>
       </c>
       <c r="CA42" t="n">
         <v>0.83</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.07999992370605</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="D43" t="n">
-        <v>14.07999992370605</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="E43" t="n">
         <v>14.10000038146973</v>
@@ -12619,67 +12619,67 @@
         <v>13.90999984741211</v>
       </c>
       <c r="H43" t="n">
-        <v>16112800</v>
+        <v>17898700</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.007751914019033079</v>
+        <v>-0.009866060168315816</v>
       </c>
       <c r="J43" t="n">
-        <v>13.89666642083062</v>
+        <v>13.89333311716715</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.31926245707837</v>
+        <v>1.127642101765521</v>
       </c>
       <c r="M43" t="n">
-        <v>13.81699981689453</v>
+        <v>13.81399984359741</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.903453067213214</v>
+        <v>1.708414288471522</v>
       </c>
       <c r="P43" t="n">
-        <v>13.09499986355121</v>
+        <v>13.09384602766771</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>7.521955482386097</v>
+        <v>7.302317142318415</v>
       </c>
       <c r="S43" t="n">
-        <v>13.38339988708496</v>
+        <v>13.38279989242554</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>5.204955710045815</v>
+        <v>4.985506050097575</v>
       </c>
       <c r="V43" t="n">
-        <v>13.55226663589477</v>
+        <v>13.55206663767497</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>3.894059215257147</v>
+        <v>3.67422597875687</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.23126954555512</v>
+        <v>13.23111954689026</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.414580061488206</v>
+        <v>6.189050298748663</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2466641484070684</v>
+        <v>0.2473715819431421</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12831,7 +12831,7 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="CA43" t="n">
         <v>0.03</v>
@@ -12891,10 +12891,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.5099983215332</v>
+        <v>42.34999847412109</v>
       </c>
       <c r="D44" t="n">
-        <v>42.5099983215332</v>
+        <v>42.34999847412109</v>
       </c>
       <c r="E44" t="n">
         <v>42.58000183105469</v>
@@ -12906,67 +12906,67 @@
         <v>41.86000061035156</v>
       </c>
       <c r="H44" t="n">
-        <v>19844000</v>
+        <v>21563100</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.005148636158670339</v>
+        <v>-0.008893074471943874</v>
       </c>
       <c r="J44" t="n">
-        <v>41.8599993387858</v>
+        <v>41.84222157796224</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.552792625453138</v>
+        <v>1.213551472673935</v>
       </c>
       <c r="M44" t="n">
-        <v>41.62599945068359</v>
+        <v>41.60999946594238</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>2.123670019976162</v>
+        <v>1.778416288576019</v>
       </c>
       <c r="P44" t="n">
-        <v>39.96653791574332</v>
+        <v>39.96038407545824</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>6.363974811008051</v>
+        <v>5.979958536310577</v>
       </c>
       <c r="S44" t="n">
-        <v>41.2513996887207</v>
+        <v>41.24819969177246</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>3.051044673174172</v>
+        <v>2.671143930115331</v>
       </c>
       <c r="V44" t="n">
-        <v>42.41813318888347</v>
+        <v>42.41706652323405</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.2165704281248567</v>
+        <v>-0.1581157175879143</v>
       </c>
       <c r="Y44" t="n">
-        <v>41.99526874542236</v>
+        <v>41.99446874618531</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.22568468184156</v>
+        <v>0.8466108479300251</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2672462164201708</v>
+        <v>0.2680727150191796</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13134,13 +13134,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.1</v>
+        <v>10.06</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CC44" t="n">
         <v>10</v>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.26000022888184</v>
+        <v>19.21999931335449</v>
       </c>
       <c r="D45" t="n">
-        <v>19.26000022888184</v>
+        <v>19.21999931335449</v>
       </c>
       <c r="E45" t="n">
         <v>19.43000030517578</v>
@@ -13209,67 +13209,67 @@
         <v>19.25</v>
       </c>
       <c r="H45" t="n">
-        <v>2125700</v>
+        <v>2483800</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.01432961481711126</v>
+        <v>-0.01637674448206217</v>
       </c>
       <c r="J45" t="n">
-        <v>19.45444446139865</v>
+        <v>19.44999991522895</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.9994848884152595</v>
+        <v>-1.182522379829794</v>
       </c>
       <c r="M45" t="n">
-        <v>19.39899997711182</v>
+        <v>19.39499988555908</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.7165304829835661</v>
+        <v>-0.9022973613672896</v>
       </c>
       <c r="P45" t="n">
-        <v>18.58923075749324</v>
+        <v>18.58769226074219</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>3.608376700139737</v>
+        <v>3.401751243470701</v>
       </c>
       <c r="S45" t="n">
-        <v>18.16180000305176</v>
+        <v>18.16099998474121</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.04675872240386</v>
+        <v>5.831173005357904</v>
       </c>
       <c r="V45" t="n">
-        <v>18.22273333231608</v>
+        <v>18.2224666595459</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>5.692158677020593</v>
+        <v>5.474191131451646</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.31501776695251</v>
+        <v>18.31481776237488</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>5.159604396532121</v>
+        <v>4.94234538789229</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.1969816676276432</v>
+        <v>0.1985280297110362</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13421,13 +13421,13 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.1</v>
+        <v>32.03</v>
       </c>
       <c r="CA45" t="n">
         <v>0.21</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CC45" t="n">
         <v>4</v>
@@ -13481,10 +13481,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.27000045776367</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D46" t="n">
-        <v>11.27000045776367</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="E46" t="n">
         <v>11.32999992370605</v>
@@ -13496,67 +13496,67 @@
         <v>11.03999996185303</v>
       </c>
       <c r="H46" t="n">
-        <v>11247700</v>
+        <v>12426400</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.005295628097652938</v>
+        <v>-0.01059134036779674</v>
       </c>
       <c r="J46" t="n">
-        <v>11.35111120012071</v>
+        <v>11.34444448682997</v>
       </c>
       <c r="K46" t="n">
         <v>-1</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.7145621334075181</v>
+        <v>-1.185112667606391</v>
       </c>
       <c r="M46" t="n">
-        <v>11.30600004196167</v>
+        <v>11.3</v>
       </c>
       <c r="N46" t="n">
         <v>-1</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.318411321991757</v>
+        <v>-0.7964598394073279</v>
       </c>
       <c r="P46" t="n">
-        <v>11.22307693041288</v>
+        <v>11.22076922196608</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.418098598465775</v>
+        <v>-0.09597545057810121</v>
       </c>
       <c r="S46" t="n">
-        <v>12.42340000152588</v>
+        <v>12.42219999313354</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-9.284089247875325</v>
+        <v>-9.758335525564098</v>
       </c>
       <c r="V46" t="n">
-        <v>14.06746671676636</v>
+        <v>14.06706671396891</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-19.88606986123888</v>
+        <v>-20.31032292599287</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.12370004177093</v>
+        <v>14.12340003967285</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-20.20504241500052</v>
+        <v>-20.62817730392181</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.403019672492954</v>
+        <v>0.403239536922926</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13708,7 +13708,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>7.61</v>
+        <v>7.57</v>
       </c>
       <c r="CA46" t="n">
         <v>-0.13</v>
@@ -13749,13 +13749,13 @@
         <v>1</v>
       </c>
       <c r="CM46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN46" t="n">
         <v>0</v>
       </c>
       <c r="CO46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.1299991607666</v>
+        <v>17.20999908447266</v>
       </c>
       <c r="D47" t="n">
-        <v>17.1299991607666</v>
+        <v>17.20999908447266</v>
       </c>
       <c r="E47" t="n">
-        <v>17.20000076293945</v>
+        <v>17.20999908447266</v>
       </c>
       <c r="F47" t="n">
         <v>16.80999946594238</v>
@@ -13783,67 +13783,67 @@
         <v>16.86000061035156</v>
       </c>
       <c r="H47" t="n">
-        <v>2127600</v>
+        <v>2551900</v>
       </c>
       <c r="I47" t="n">
-        <v>0.002340491973176206</v>
+        <v>0.007021587525649853</v>
       </c>
       <c r="J47" t="n">
-        <v>17.63888888888889</v>
+        <v>17.64777776930067</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.885044127937379</v>
+        <v>-2.480644818576304</v>
       </c>
       <c r="M47" t="n">
-        <v>17.70100002288818</v>
+        <v>17.70900001525879</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-3.225811317910023</v>
+        <v>-2.817781525530364</v>
       </c>
       <c r="P47" t="n">
-        <v>17.46538459337675</v>
+        <v>17.46846151351929</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.920286557774004</v>
+        <v>-1.479594690388734</v>
       </c>
       <c r="S47" t="n">
-        <v>16.76819999694824</v>
+        <v>16.76979999542236</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>2.157650575996275</v>
+        <v>2.624951336154593</v>
       </c>
       <c r="V47" t="n">
-        <v>17.57526670455933</v>
+        <v>17.57580003738403</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.533489541169887</v>
+        <v>-2.081276255608924</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.04690005779266</v>
+        <v>18.04730005741119</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-5.080655924783837</v>
+        <v>-4.639480533237409</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4630673645230899</v>
+        <v>0.4635051628877302</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -13991,13 +13991,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>63.44</v>
+        <v>63.74</v>
       </c>
       <c r="CA47" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CC47" t="n">
         <v>7</v>
@@ -14066,7 +14066,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="H48" t="n">
-        <v>17746600</v>
+        <v>18372000</v>
       </c>
       <c r="I48" t="n">
         <v>-0.03298611973446797</v>
@@ -14090,43 +14090,43 @@
         <v>1.549683371435673</v>
       </c>
       <c r="P48" t="n">
-        <v>4.756923116170443</v>
+        <v>4.747307731555058</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>17.09249940843066</v>
+        <v>17.32966318231138</v>
       </c>
       <c r="S48" t="n">
-        <v>4.795200037956238</v>
+        <v>4.792600045204162</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>16.15782715157316</v>
+        <v>16.22084294797643</v>
       </c>
       <c r="V48" t="n">
-        <v>6.820666654904683</v>
+        <v>6.785133325258891</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-18.33642584400402</v>
+        <v>-17.90875868384133</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.439147533178329</v>
+        <v>7.414890395402908</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-25.12582729648287</v>
+        <v>-24.88088326815091</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.8518453954815262</v>
+        <v>0.8494373233129683</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14338,10 +14338,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.42000007629395</v>
+        <v>16.3799991607666</v>
       </c>
       <c r="D49" t="n">
-        <v>16.42000007629395</v>
+        <v>16.3799991607666</v>
       </c>
       <c r="E49" t="n">
         <v>16.53000068664551</v>
@@ -14353,67 +14353,67 @@
         <v>16.14999961853027</v>
       </c>
       <c r="H49" t="n">
-        <v>9003400</v>
+        <v>9769200</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.007255189394865469</v>
+        <v>-0.009673624298928374</v>
       </c>
       <c r="J49" t="n">
-        <v>16.37666670481364</v>
+        <v>16.37222215864394</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2646043438593502</v>
+        <v>0.04750120079795978</v>
       </c>
       <c r="M49" t="n">
-        <v>16.28500003814697</v>
+        <v>16.28099994659424</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8289839596606761</v>
+        <v>0.6080659326644851</v>
       </c>
       <c r="P49" t="n">
-        <v>15.08038462125338</v>
+        <v>15.07884612450233</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>8.883165043102366</v>
+        <v>8.628996048643058</v>
       </c>
       <c r="S49" t="n">
-        <v>14.90700000762939</v>
+        <v>14.90619998931885</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>10.1495946058241</v>
+        <v>9.887155495725372</v>
       </c>
       <c r="V49" t="n">
-        <v>15.27986670176188</v>
+        <v>15.2796000289917</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>7.461670947696152</v>
+        <v>7.201753512441365</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.41290001392364</v>
+        <v>15.41270000934601</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>6.534137387905652</v>
+        <v>6.275987664938912</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3014537018514246</v>
+        <v>0.3022999087735194</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14565,13 +14565,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>9.890000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="CA49" t="n">
         <v>0.93</v>
       </c>
       <c r="CB49" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CC49" t="n">
         <v>5</v>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.539999961853027</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="D50" t="n">
-        <v>5.539999961853027</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="E50" t="n">
         <v>5.630000114440918</v>
@@ -14640,67 +14640,67 @@
         <v>5.579999923706055</v>
       </c>
       <c r="H50" t="n">
-        <v>11603900</v>
+        <v>12104100</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.03484317373521018</v>
+        <v>-0.03310097351211017</v>
       </c>
       <c r="J50" t="n">
-        <v>5.647777716318767</v>
+        <v>5.648888852861193</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.908321465172482</v>
+        <v>-1.750586083424916</v>
       </c>
       <c r="M50" t="n">
-        <v>5.633999967575074</v>
+        <v>5.634999990463257</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-1.668441715708861</v>
+        <v>-1.508425907227121</v>
       </c>
       <c r="P50" t="n">
-        <v>5.173461565604577</v>
+        <v>5.173846189792339</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>7.084973795598619</v>
+        <v>7.270297321258819</v>
       </c>
       <c r="S50" t="n">
-        <v>4.965000019073487</v>
+        <v>4.965200023651123</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>11.58106627533993</v>
+        <v>11.77797801293233</v>
       </c>
       <c r="V50" t="n">
-        <v>6.487600002288819</v>
+        <v>6.487666670481364</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-14.60632653217644</v>
+        <v>-14.45306189994081</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.918700013160706</v>
+        <v>6.918750014305115</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-19.92715464877974</v>
+        <v>-19.78319524105138</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.5985295977776817</v>
+        <v>0.5975202517556031</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14848,7 +14848,7 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.1</v>
+        <v>-4.11</v>
       </c>
       <c r="CA50" t="n">
         <v>2.54</v>
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30.02000045776367</v>
+        <v>29.82999992370605</v>
       </c>
       <c r="D51" t="n">
-        <v>30.02000045776367</v>
+        <v>29.82999992370605</v>
       </c>
       <c r="E51" t="n">
         <v>30.04999923706055</v>
@@ -14923,67 +14923,67 @@
         <v>29.18000030517578</v>
       </c>
       <c r="H51" t="n">
-        <v>3114200</v>
+        <v>3676600</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.001662761475489938</v>
+        <v>-0.007981369256863435</v>
       </c>
       <c r="J51" t="n">
-        <v>29.88888910081651</v>
+        <v>29.86777793036567</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4386625294266188</v>
+        <v>-0.1264841554255924</v>
       </c>
       <c r="M51" t="n">
-        <v>29.69200019836426</v>
+        <v>29.6730001449585</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>1.104675526095015</v>
+        <v>0.5290997808802035</v>
       </c>
       <c r="P51" t="n">
-        <v>28.10461550492507</v>
+        <v>28.0973077920767</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>6.815197142629298</v>
+        <v>6.166754994647448</v>
       </c>
       <c r="S51" t="n">
-        <v>28.41160011291504</v>
+        <v>28.40780010223389</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>5.661069205734398</v>
+        <v>5.006370843057054</v>
       </c>
       <c r="V51" t="n">
-        <v>30.33373336791992</v>
+        <v>30.33246669769287</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-1.034270679282906</v>
+        <v>-1.656531198054644</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.1049000453949</v>
+        <v>30.10395004272461</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.2820125212281323</v>
+        <v>-0.9100138640602128</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2629948174121735</v>
+        <v>0.2644561646884099</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15135,13 +15135,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.61</v>
+        <v>12.53</v>
       </c>
       <c r="CA51" t="n">
         <v>0.29</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CC51" t="n">
         <v>8</v>
@@ -15173,16 +15173,16 @@
         <v>0</v>
       </c>
       <c r="CL51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -15195,10 +15195,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.069999694824219</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="D52" t="n">
-        <v>8.069999694824219</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="E52" t="n">
         <v>8.239999771118164</v>
@@ -15210,67 +15210,67 @@
         <v>8.220000267028809</v>
       </c>
       <c r="H52" t="n">
-        <v>7150200</v>
+        <v>7663600</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.03121251275668202</v>
+        <v>-0.03601442898950136</v>
       </c>
       <c r="J52" t="n">
-        <v>8.747777726915148</v>
+        <v>8.743333286709255</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.748002444158391</v>
+        <v>-8.158599590643565</v>
       </c>
       <c r="M52" t="n">
-        <v>8.746999931335449</v>
+        <v>8.742999935150147</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-7.739799266328207</v>
+        <v>-8.155097877931196</v>
       </c>
       <c r="P52" t="n">
-        <v>8.386538358835073</v>
+        <v>8.384999898763803</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.774366138531838</v>
+        <v>-4.233752773747196</v>
       </c>
       <c r="S52" t="n">
-        <v>8.423000030517578</v>
+        <v>8.422200031280518</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-4.190909823274307</v>
+        <v>-4.656744043749528</v>
       </c>
       <c r="V52" t="n">
-        <v>9.115933307011922</v>
+        <v>9.115666640599569</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-11.47368653282245</v>
+        <v>-11.90990138661948</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.811049971580506</v>
+        <v>8.810849971771241</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-8.410465031369682</v>
+        <v>-8.862371295638747</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4425442582303413</v>
+        <v>0.4456117415262858</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>-4.78</v>
+        <v>-4.75</v>
       </c>
       <c r="CA52" t="n">
         <v>0.36</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.61000061035156</v>
+        <v>54.2599983215332</v>
       </c>
       <c r="D53" t="n">
-        <v>54.61000061035156</v>
+        <v>54.2599983215332</v>
       </c>
       <c r="E53" t="n">
         <v>55.2599983215332</v>
@@ -15497,67 +15497,67 @@
         <v>55.06000137329102</v>
       </c>
       <c r="H53" t="n">
-        <v>7637400</v>
+        <v>9063000</v>
       </c>
       <c r="I53" t="n">
-        <v>0.001650773144391549</v>
+        <v>-0.004768931292139178</v>
       </c>
       <c r="J53" t="n">
-        <v>53.46666675143771</v>
+        <v>53.42777760823568</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>2.138404969640462</v>
+        <v>1.557655494113684</v>
       </c>
       <c r="M53" t="n">
-        <v>53.14900016784668</v>
+        <v>53.11399993896485</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>2.748876625883807</v>
+        <v>2.157620182786582</v>
       </c>
       <c r="P53" t="n">
-        <v>49.50346139761118</v>
+        <v>49.48999977111816</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>10.31551949817151</v>
+        <v>9.638307885381643</v>
       </c>
       <c r="S53" t="n">
-        <v>47.93599975585938</v>
+        <v>47.928999710083</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>13.92273216055414</v>
+        <v>13.2091190088374</v>
       </c>
       <c r="V53" t="n">
-        <v>47.87313329060873</v>
+        <v>47.8707999420166</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>14.07233422313807</v>
+        <v>13.34675498896092</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.51789999961853</v>
+        <v>44.51614998817444</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>22.6697589302719</v>
+        <v>21.88834464783496</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3397031450879363</v>
+        <v>0.3405667938035418</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15709,13 +15709,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
       <c r="CA53" t="n">
         <v>0.46</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CC53" t="n">
         <v>1</v>
@@ -15765,10 +15765,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>49.11000061035156</v>
+        <v>48.91999816894531</v>
       </c>
       <c r="D54" t="n">
-        <v>49.11000061035156</v>
+        <v>48.91999816894531</v>
       </c>
       <c r="E54" t="n">
         <v>49.72999954223633</v>
@@ -15780,67 +15780,67 @@
         <v>49.5099983215332</v>
       </c>
       <c r="H54" t="n">
-        <v>29994300</v>
+        <v>32056200</v>
       </c>
       <c r="I54" t="n">
-        <v>0.00224491041533792</v>
+        <v>-0.0016326904296875</v>
       </c>
       <c r="J54" t="n">
-        <v>48.16444439358182</v>
+        <v>48.14333301120334</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1.963183067249803</v>
+        <v>1.613235123461929</v>
       </c>
       <c r="M54" t="n">
-        <v>47.85</v>
+        <v>47.83099975585937</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>2.633230115677244</v>
+        <v>2.276762807895385</v>
       </c>
       <c r="P54" t="n">
-        <v>44.48692307105431</v>
+        <v>44.47961528484638</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>10.39199211847781</v>
+        <v>9.982961533418907</v>
       </c>
       <c r="S54" t="n">
-        <v>42.89440002441406</v>
+        <v>42.89059997558594</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>14.49047097616423</v>
+        <v>14.05762147601436</v>
       </c>
       <c r="V54" t="n">
-        <v>43.23746663411458</v>
+        <v>43.23619995117188</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>13.58204916567318</v>
+        <v>13.14592453590358</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.5629000377655</v>
+        <v>40.56195002555847</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>21.07122657558608</v>
+        <v>20.60563690384794</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3219829447687988</v>
+        <v>0.3223951450806589</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -15992,7 +15992,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.88</v>
+        <v>5.86</v>
       </c>
       <c r="CA54" t="n">
         <v>0.51</v>
@@ -16048,10 +16048,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.460000038146973</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="D55" t="n">
-        <v>4.460000038146973</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="E55" t="n">
         <v>4.480000019073486</v>
@@ -16063,67 +16063,67 @@
         <v>4.440000057220459</v>
       </c>
       <c r="H55" t="n">
-        <v>11198700</v>
+        <v>11767300</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.008888880411783817</v>
+        <v>-0.01555559370252824</v>
       </c>
       <c r="J55" t="n">
-        <v>4.533333301544189</v>
+        <v>4.529999944898817</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.61764552745851</v>
+        <v>-2.207508118687795</v>
       </c>
       <c r="M55" t="n">
-        <v>4.519999980926514</v>
+        <v>4.516999959945679</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.327432367980722</v>
+        <v>-1.926060048229487</v>
       </c>
       <c r="P55" t="n">
-        <v>4.409999994131235</v>
+        <v>4.408846139907837</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>1.133787847670678</v>
+        <v>0.4798010127708456</v>
       </c>
       <c r="S55" t="n">
-        <v>4.846399984359741</v>
+        <v>4.845799980163574</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-7.972927275085734</v>
+        <v>-8.580629690186163</v>
       </c>
       <c r="V55" t="n">
-        <v>5.774933322270711</v>
+        <v>5.774733320871989</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-22.76967041425</v>
+        <v>-23.28650377105743</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.82940447807312</v>
+        <v>5.829254477024079</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-23.49132651674905</v>
+        <v>-24.00400693091368</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4601931059511786</v>
+        <v>0.4610393875331076</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16275,13 +16275,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="CA55" t="n">
         <v>0.28</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CC55" t="n">
         <v>9</v>
@@ -16335,10 +16335,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>64.01000213623047</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="D56" t="n">
-        <v>64.01000213623047</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="E56" t="n">
         <v>65.34999847412109</v>
@@ -16350,67 +16350,67 @@
         <v>65.19999694824219</v>
       </c>
       <c r="H56" t="n">
-        <v>6671300</v>
+        <v>7113800</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.002804179752759595</v>
+        <v>-0.0043620904088566</v>
       </c>
       <c r="J56" t="n">
-        <v>63.00000127156576</v>
+        <v>62.98888990614149</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1.603175943300436</v>
+        <v>1.462337156033616</v>
       </c>
       <c r="M56" t="n">
-        <v>62.96800117492675</v>
+        <v>62.95800094604492</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>1.654810287544316</v>
+        <v>1.51211742282455</v>
       </c>
       <c r="P56" t="n">
-        <v>61.49423129741962</v>
+        <v>61.49038505554199</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>4.091068033102497</v>
+        <v>3.934948186915025</v>
       </c>
       <c r="S56" t="n">
-        <v>59.69000022888184</v>
+        <v>59.68800018310547</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>7.237396365862871</v>
+        <v>7.073448015270698</v>
       </c>
       <c r="V56" t="n">
-        <v>60.73806671142578</v>
+        <v>60.73740002950033</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>5.386960109135621</v>
+        <v>5.223469915358313</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.19055000305175</v>
+        <v>56.19004999160767</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>13.91595585512873</v>
+        <v>13.73899802003641</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3824779041433548</v>
+        <v>0.3826733802599127</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16562,13 +16562,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>21.55</v>
+        <v>21.52</v>
       </c>
       <c r="CA56" t="n">
         <v>0.43</v>
       </c>
       <c r="CB56" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CC56" t="n">
         <v>10</v>
@@ -16618,10 +16618,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50.20999908447266</v>
+        <v>50.04000091552734</v>
       </c>
       <c r="D57" t="n">
-        <v>50.20999908447266</v>
+        <v>50.04000091552734</v>
       </c>
       <c r="E57" t="n">
         <v>50.29000091552734</v>
@@ -16633,91 +16633,91 @@
         <v>50.0099983215332</v>
       </c>
       <c r="H57" t="n">
-        <v>893000</v>
+        <v>994600</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.00907833236817801</v>
+        <v>-0.01243333878397657</v>
       </c>
       <c r="J57" t="n">
-        <v>50.82666651407877</v>
+        <v>50.80777782864041</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.213275376686966</v>
+        <v>-1.511140510223753</v>
       </c>
       <c r="M57" t="n">
-        <v>50.65200004577637</v>
+        <v>50.63500022888184</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.8726229189454657</v>
+        <v>-1.175075166712666</v>
       </c>
       <c r="P57" t="n">
-        <v>48.95807691720816</v>
+        <v>48.95153852609488</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.557131011051745</v>
+        <v>2.22355092854177</v>
       </c>
       <c r="S57" t="n">
-        <v>51.44140014648438</v>
+        <v>51.43800018310547</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.393793828521747</v>
+        <v>-2.717833630004316</v>
       </c>
       <c r="V57" t="n">
-        <v>50.91280008951823</v>
+        <v>50.91166676839192</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-1.380401399667394</v>
+        <v>-1.71211415416819</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.23570007324219</v>
+        <v>50.23485008239746</v>
       </c>
       <c r="Z57" t="n">
         <v>-1</v>
       </c>
       <c r="AA57" t="n">
-        <v>-0.05116080542733094</v>
+        <v>-0.3878764772872088</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.2562793193561825</v>
+        <v>0.2571850199680428</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
       <c r="AD57" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AF57" t="n">
         <v>49.7</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>50.1</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AH57" t="n">
         <v>50.2</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>50.4</v>
       </c>
-      <c r="AH57" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>50.8</v>
-      </c>
       <c r="AJ57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK57" t="n">
         <v>0</v>
@@ -16841,13 +16841,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.81</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="CA57" t="n">
         <v>-0.4</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CC57" t="n">
         <v>7</v>
@@ -16901,10 +16901,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>19.6299991607666</v>
+        <v>19.54000091552734</v>
       </c>
       <c r="D58" t="n">
-        <v>19.6299991607666</v>
+        <v>19.54000091552734</v>
       </c>
       <c r="E58" t="n">
         <v>19.77000045776367</v>
@@ -16916,88 +16916,88 @@
         <v>18.90999984741211</v>
       </c>
       <c r="H58" t="n">
-        <v>6234300</v>
+        <v>6761800</v>
       </c>
       <c r="I58" t="n">
-        <v>0.003578716602017362</v>
+        <v>-0.001022420805780744</v>
       </c>
       <c r="J58" t="n">
-        <v>19.90111096700032</v>
+        <v>19.89111116197374</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.36229483209895</v>
+        <v>-1.765161551746897</v>
       </c>
       <c r="M58" t="n">
-        <v>19.87099990844727</v>
+        <v>19.86200008392334</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.212826474717132</v>
+        <v>-1.621181990914548</v>
       </c>
       <c r="P58" t="n">
-        <v>19.01923069587121</v>
+        <v>19.01576922490047</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>3.211320555820285</v>
+        <v>2.756826107988386</v>
       </c>
       <c r="S58" t="n">
-        <v>18.74740001678467</v>
+        <v>18.74560005187988</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>4.707848251980211</v>
+        <v>4.237799064574596</v>
       </c>
       <c r="V58" t="n">
-        <v>20.59066672007243</v>
+        <v>20.59006673177083</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-4.66554858259804</v>
+        <v>-5.099866017545339</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.43695687294006</v>
+        <v>21.43650688171387</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-8.42917081413915</v>
+        <v>-8.847084912907679</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.464165062821851</v>
+        <v>0.4642572424234797</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
       <c r="AD58" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AE58" t="n">
         <v>19.3</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AF58" t="n">
         <v>19.4</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AG58" t="n">
         <v>19.6</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
         <v>19.7</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>19.9</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>20.1</v>
       </c>
       <c r="AJ58" t="n">
         <v>2</v>
@@ -17124,13 +17124,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>26.53</v>
+        <v>26.41</v>
       </c>
       <c r="CA58" t="n">
         <v>0.09</v>
       </c>
       <c r="CB58" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17184,10 +17184,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.60999965667725</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="D59" t="n">
-        <v>14.60999965667725</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="E59" t="n">
         <v>14.85000038146973</v>
@@ -17199,88 +17199,88 @@
         <v>14.56999969482422</v>
       </c>
       <c r="H59" t="n">
-        <v>4101900</v>
+        <v>5622400</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.01483481241811291</v>
+        <v>-0.01955495369824356</v>
       </c>
       <c r="J59" t="n">
-        <v>14.75111113654243</v>
+        <v>14.74333339267307</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.9566159359725127</v>
+        <v>-1.379155075751671</v>
       </c>
       <c r="M59" t="n">
-        <v>14.78400001525879</v>
+        <v>14.77700004577637</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.176950476203695</v>
+        <v>-1.603844374292196</v>
       </c>
       <c r="P59" t="n">
-        <v>14.21615391511184</v>
+        <v>14.21346161915706</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>2.770409942922402</v>
+        <v>2.297387866836454</v>
       </c>
       <c r="S59" t="n">
-        <v>14.04859998703003</v>
+        <v>14.04719999313354</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>3.996125380219479</v>
+        <v>3.508172226211417</v>
       </c>
       <c r="V59" t="n">
-        <v>14.88053335189819</v>
+        <v>14.88006668726603</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-1.818037625556197</v>
+        <v>-2.285384417692326</v>
       </c>
       <c r="Y59" t="n">
-        <v>14.93270002365112</v>
+        <v>14.932350025177</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-2.161031604885708</v>
+        <v>-2.627517186929345</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3174724175226817</v>
+        <v>0.3197509211384504</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
       </c>
       <c r="AD59" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AE59" t="n">
         <v>14.4</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AF59" t="n">
         <v>14.5</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AG59" t="n">
         <v>14.6</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
         <v>14.7</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AI59" t="n">
         <v>14.8</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>15.1</v>
       </c>
       <c r="AJ59" t="n">
         <v>2</v>
@@ -17407,13 +17407,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>26.09</v>
+        <v>25.96</v>
       </c>
       <c r="CA59" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="CB59" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC59" t="n">
         <v>8</v>
@@ -17448,13 +17448,13 @@
         <v>5</v>
       </c>
       <c r="CM59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
@@ -17467,10 +17467,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36.95999908447266</v>
+        <v>37.04999923706055</v>
       </c>
       <c r="D60" t="n">
-        <v>36.95999908447266</v>
+        <v>37.04999923706055</v>
       </c>
       <c r="E60" t="n">
         <v>37.27000045776367</v>
@@ -17482,88 +17482,88 @@
         <v>36.4900016784668</v>
       </c>
       <c r="H60" t="n">
-        <v>4331000</v>
+        <v>4662800</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01728267788700866</v>
+        <v>-0.01488969327846501</v>
       </c>
       <c r="J60" t="n">
-        <v>37.15000025431315</v>
+        <v>37.16000027126736</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.5114432531354642</v>
+        <v>-0.2960200037777496</v>
       </c>
       <c r="M60" t="n">
-        <v>36.95300025939942</v>
+        <v>36.9620002746582</v>
       </c>
       <c r="N60" t="n">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.01893980197577899</v>
+        <v>0.2380795458807428</v>
       </c>
       <c r="P60" t="n">
-        <v>35.21038480905386</v>
+        <v>35.21384635338416</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>4.969029122819765</v>
+        <v>5.214292313455056</v>
       </c>
       <c r="S60" t="n">
-        <v>34.97060012817383</v>
+        <v>34.97240013122558</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>5.688775568641392</v>
+        <v>5.940682075120004</v>
       </c>
       <c r="V60" t="n">
-        <v>36.72033335367838</v>
+        <v>36.72093335469564</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>0.6526785268692659</v>
+        <v>0.8961261392415815</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.32559997558594</v>
+        <v>38.32604997634888</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-3.563155937501807</v>
+        <v>-3.329460615105873</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3413944581970529</v>
+        <v>0.3402652023819016</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="AE60" t="n">
-        <v>36.5</v>
+        <v>36.8</v>
       </c>
       <c r="AF60" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="AG60" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="AH60" t="n">
-        <v>37.1</v>
+        <v>37.7</v>
       </c>
       <c r="AI60" t="n">
-        <v>37.7</v>
+        <v>38.4</v>
       </c>
       <c r="AJ60" t="n">
         <v>2</v>
@@ -17690,13 +17690,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>18.3</v>
+        <v>18.34</v>
       </c>
       <c r="CA60" t="n">
         <v>0.09</v>
       </c>
       <c r="CB60" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="CC60" t="n">
         <v>9</v>
@@ -17731,13 +17731,13 @@
         <v>7</v>
       </c>
       <c r="CM60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN60" t="n">
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.42000007629395</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="D61" t="n">
-        <v>11.42000007629395</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="E61" t="n">
         <v>11.56999969482422</v>
@@ -17765,67 +17765,67 @@
         <v>11.47999954223633</v>
       </c>
       <c r="H61" t="n">
-        <v>1502600</v>
+        <v>1623300</v>
       </c>
       <c r="I61" t="n">
-        <v>0.005281727238559464</v>
+        <v>0.000880301864794264</v>
       </c>
       <c r="J61" t="n">
-        <v>11.40222210354275</v>
+        <v>11.39666652679443</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1559167378933114</v>
+        <v>-0.2339863254983925</v>
       </c>
       <c r="M61" t="n">
-        <v>11.35099992752075</v>
+        <v>11.34599990844726</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6078772726083922</v>
+        <v>0.2115280918868048</v>
       </c>
       <c r="P61" t="n">
-        <v>10.83923068413368</v>
+        <v>10.83730759987464</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>5.358031479211817</v>
+        <v>4.915356335282025</v>
       </c>
       <c r="S61" t="n">
-        <v>10.56839998245239</v>
+        <v>10.5673999786377</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>8.057985080575454</v>
+        <v>7.595055629046554</v>
       </c>
       <c r="V61" t="n">
-        <v>11.58946668624878</v>
+        <v>11.58913335164388</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-1.462246836223361</v>
+        <v>-1.89085291743334</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.39994999885559</v>
+        <v>11.39969999790192</v>
       </c>
       <c r="Z61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.1758786436814778</v>
+        <v>-0.2605341574629156</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3706242802259763</v>
+        <v>0.3705599321327734</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17973,7 +17973,7 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="CA61" t="n">
         <v>0.45</v>
@@ -18033,10 +18033,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>35.84000015258789</v>
+        <v>35.59000015258789</v>
       </c>
       <c r="D62" t="n">
-        <v>35.84000015258789</v>
+        <v>35.59000015258789</v>
       </c>
       <c r="E62" t="n">
         <v>35.95000076293945</v>
@@ -18048,67 +18048,67 @@
         <v>34.59999847412109</v>
       </c>
       <c r="H62" t="n">
-        <v>3672300</v>
+        <v>4373500</v>
       </c>
       <c r="I62" t="n">
-        <v>0.001117344032955492</v>
+        <v>-0.005865896339329102</v>
       </c>
       <c r="J62" t="n">
-        <v>36.15666664971246</v>
+        <v>36.12888887193468</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.8758177300812754</v>
+        <v>-1.491572910689211</v>
       </c>
       <c r="M62" t="n">
-        <v>36.04799995422363</v>
+        <v>36.02299995422364</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.5770078836547848</v>
+        <v>-1.202009277922386</v>
       </c>
       <c r="P62" t="n">
-        <v>34.99846150324895</v>
+        <v>34.98884611863356</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>2.404501835775902</v>
+        <v>1.718130491974645</v>
       </c>
       <c r="S62" t="n">
-        <v>36.72039993286133</v>
+        <v>36.71539993286133</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.397576774444552</v>
+        <v>-3.065198206560118</v>
       </c>
       <c r="V62" t="n">
-        <v>42.85626668294271</v>
+        <v>42.85460001627604</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-16.37162327335287</v>
+        <v>-16.95173881200403</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.42880001068115</v>
+        <v>43.42755001068115</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-17.47411822621584</v>
+        <v>-18.04741427081562</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4090941839161074</v>
+        <v>0.4092379971944728</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18118,26 +18118,28 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE62" t="n">
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
         <v>26.7</v>
       </c>
-      <c r="AF62" t="n">
+      <c r="AG62" t="n">
         <v>35.7</v>
       </c>
-      <c r="AG62" t="n">
+      <c r="AH62" t="n">
         <v>36.5</v>
       </c>
-      <c r="AH62" t="n">
+      <c r="AI62" t="n">
         <v>37.6</v>
       </c>
-      <c r="AI62" t="n">
-        <v>38.1</v>
-      </c>
       <c r="AJ62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
@@ -18258,13 +18260,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>17.92</v>
+        <v>17.8</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CB62" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CC62" t="n">
         <v>10</v>
@@ -18314,10 +18316,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30.34000015258789</v>
+        <v>30.3700008392334</v>
       </c>
       <c r="D63" t="n">
-        <v>30.34000015258789</v>
+        <v>30.3700008392334</v>
       </c>
       <c r="E63" t="n">
         <v>30.39999961853027</v>
@@ -18329,67 +18331,67 @@
         <v>29.88999938964844</v>
       </c>
       <c r="H63" t="n">
-        <v>1414500</v>
+        <v>1675500</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.009144372272085088</v>
+        <v>-0.008164598077988083</v>
       </c>
       <c r="J63" t="n">
-        <v>30.15111117892795</v>
+        <v>30.15444458855523</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.626474336348671</v>
+        <v>0.7148407261992187</v>
       </c>
       <c r="M63" t="n">
-        <v>30.09200000762939</v>
+        <v>30.09500007629395</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8241397876366451</v>
+        <v>0.9137755847891575</v>
       </c>
       <c r="P63" t="n">
-        <v>29.72923080737774</v>
+        <v>29.73038467994103</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>2.054440456826675</v>
+        <v>2.151388776761817</v>
       </c>
       <c r="S63" t="n">
-        <v>28.51580005645752</v>
+        <v>28.51640007019043</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>6.397155585740877</v>
+        <v>6.50012191048136</v>
       </c>
       <c r="V63" t="n">
-        <v>29.41360000610351</v>
+        <v>29.41380001068115</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>3.149563964601891</v>
+        <v>3.250857856533381</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.55204998016357</v>
+        <v>30.5521999835968</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.6940608820467363</v>
+        <v>-0.5963535996138509</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.1805191279316638</v>
+        <v>0.1800146984692386</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18600,13 +18602,13 @@
         <v>7</v>
       </c>
       <c r="CM63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN63" t="n">
         <v>1</v>
       </c>
       <c r="CO63" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64">
@@ -18619,10 +18621,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>26.97999954223633</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="D64" t="n">
-        <v>26.97999954223633</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="E64" t="n">
         <v>27.06999969482422</v>
@@ -18634,67 +18636,67 @@
         <v>26.20000076293945</v>
       </c>
       <c r="H64" t="n">
-        <v>10230000</v>
+        <v>11088800</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.002218985623501202</v>
+        <v>-0.007396477668926593</v>
       </c>
       <c r="J64" t="n">
-        <v>26.54111141628689</v>
+        <v>26.52555592854818</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1.653616229801565</v>
+        <v>1.185438770394605</v>
       </c>
       <c r="M64" t="n">
-        <v>26.41500034332275</v>
+        <v>26.40100040435791</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>2.138933149991033</v>
+        <v>1.662814823325854</v>
       </c>
       <c r="P64" t="n">
-        <v>25.38807700230525</v>
+        <v>25.38269241039569</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>6.270354937817971</v>
+        <v>5.74134421451423</v>
       </c>
       <c r="S64" t="n">
-        <v>27.0476000213623</v>
+        <v>27.04480003356933</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-0.2499315246919648</v>
+        <v>-0.7572615834734813</v>
       </c>
       <c r="V64" t="n">
-        <v>29.16992787679036</v>
+        <v>29.16899454752604</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-7.507486284518709</v>
+        <v>-7.984486373513628</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.57474990844727</v>
+        <v>28.57404991149902</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-5.580977510986013</v>
+        <v>-6.068617379342163</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3237495052502448</v>
+        <v>0.3243115355173587</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18842,13 +18844,13 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.88</v>
+        <v>10.82</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
       </c>
       <c r="CB64" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CC64" t="n">
         <v>9</v>
@@ -18902,82 +18904,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.42000007629395</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="D65" t="n">
-        <v>17.42000007629395</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="E65" t="n">
         <v>17.97999954223633</v>
       </c>
       <c r="F65" t="n">
-        <v>17.3700008392334</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="G65" t="n">
         <v>17.8700008392334</v>
       </c>
       <c r="H65" t="n">
-        <v>4063900</v>
+        <v>4523800</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0289855318998733</v>
+        <v>-0.03288740997904782</v>
       </c>
       <c r="J65" t="n">
-        <v>17.12333318922255</v>
+        <v>17.11555544535319</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1.732530014998006</v>
+        <v>1.369776966135132</v>
       </c>
       <c r="M65" t="n">
-        <v>17.01799983978271</v>
+        <v>17.01099987030029</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>2.362206136419637</v>
+        <v>1.992831190136562</v>
       </c>
       <c r="P65" t="n">
-        <v>15.48307686585646</v>
+        <v>15.48038456990169</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>12.50993731555267</v>
+        <v>12.07732148465556</v>
       </c>
       <c r="S65" t="n">
-        <v>14.52920000076294</v>
+        <v>14.52780000686646</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>19.8964848400408</v>
+        <v>19.42620612390988</v>
       </c>
       <c r="V65" t="n">
-        <v>15.79386664072672</v>
+        <v>15.79339997609456</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>10.29598053825531</v>
+        <v>9.85601838572623</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.59449992656708</v>
+        <v>15.59414992809296</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>11.70605122525867</v>
+        <v>11.2596740538809</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.3703688281474487</v>
+        <v>0.3740095186332498</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19129,7 +19131,7 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>26.8</v>
+        <v>26.69</v>
       </c>
       <c r="CA65" t="n">
         <v>0.73</v>
@@ -19170,13 +19172,13 @@
         <v>10</v>
       </c>
       <c r="CM65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66">
@@ -19189,10 +19191,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.13999938964844</v>
+        <v>17.09000015258789</v>
       </c>
       <c r="D66" t="n">
-        <v>17.13999938964844</v>
+        <v>17.09000015258789</v>
       </c>
       <c r="E66" t="n">
         <v>17.26000022888184</v>
@@ -19204,67 +19206,67 @@
         <v>16.94000053405762</v>
       </c>
       <c r="H66" t="n">
-        <v>7410300</v>
+        <v>8559500</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.01210380329706362</v>
+        <v>-0.01498560364065027</v>
       </c>
       <c r="J66" t="n">
-        <v>17.61444430881076</v>
+        <v>17.60888883802626</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.693499214874516</v>
+        <v>-2.946742921778423</v>
       </c>
       <c r="M66" t="n">
-        <v>17.53399982452392</v>
+        <v>17.52899990081787</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-2.24706535199355</v>
+        <v>-2.504419822659129</v>
       </c>
       <c r="P66" t="n">
-        <v>17.37038465646597</v>
+        <v>17.350769336407</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-1.326310679779753</v>
+        <v>-1.502925770973974</v>
       </c>
       <c r="S66" t="n">
-        <v>18.70580009460449</v>
+        <v>18.66020011901855</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-8.370669509120297</v>
+        <v>-8.414700573496582</v>
       </c>
       <c r="V66" t="n">
-        <v>19.00653335571289</v>
+        <v>18.97920003255208</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-9.820486098815167</v>
+        <v>-9.954054315903409</v>
       </c>
       <c r="Y66" t="n">
-        <v>20.11294095993042</v>
+        <v>20.08239096641541</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-14.78123749383425</v>
+        <v>-14.9005704491652</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3448458100735897</v>
+        <v>0.3382470286062177</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19416,7 +19418,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.3</v>
+        <v>15.26</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
@@ -19434,7 +19436,7 @@
         <v>5</v>
       </c>
       <c r="CF66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CG66" t="n">
         <v>5</v>
@@ -19443,7 +19445,7 @@
         <v>6</v>
       </c>
       <c r="CI66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CJ66" t="inlineStr">
         <is>
@@ -19463,7 +19465,7 @@
         <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -19476,10 +19478,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>47.34999847412109</v>
+        <v>47.29999923706055</v>
       </c>
       <c r="D67" t="n">
-        <v>47.34999847412109</v>
+        <v>47.29999923706055</v>
       </c>
       <c r="E67" t="n">
         <v>47.54000091552734</v>
@@ -19491,88 +19493,88 @@
         <v>46.84000015258789</v>
       </c>
       <c r="H67" t="n">
-        <v>5143400</v>
+        <v>5604400</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.009621478476403045</v>
+        <v>-0.010667268805296</v>
       </c>
       <c r="J67" t="n">
-        <v>47.07888836330838</v>
+        <v>47.07333289252387</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5758634501319438</v>
+        <v>0.4815175187492904</v>
       </c>
       <c r="M67" t="n">
-        <v>46.90099945068359</v>
+        <v>46.89599952697754</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.9573335935188844</v>
+        <v>0.8614801137794285</v>
       </c>
       <c r="P67" t="n">
-        <v>44.71153860825758</v>
+        <v>44.70961556067834</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>5.901071508588666</v>
+        <v>5.793795459651473</v>
       </c>
       <c r="S67" t="n">
-        <v>43.3992000579834</v>
+        <v>43.39820007324219</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>9.103389949259984</v>
+        <v>8.990693524693143</v>
       </c>
       <c r="V67" t="n">
-        <v>46.15293342590332</v>
+        <v>46.15260009765625</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>2.593692230071601</v>
+        <v>2.486098588110896</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.20345003128052</v>
+        <v>47.20320003509521</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.3104612962473336</v>
+        <v>0.2050691518654728</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2718812080935407</v>
+        <v>0.2723233029866185</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
       </c>
       <c r="AD67" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AE67" t="n">
         <v>42.7</v>
       </c>
-      <c r="AE67" t="n">
+      <c r="AF67" t="n">
         <v>47.1</v>
       </c>
-      <c r="AF67" t="n">
+      <c r="AG67" t="n">
         <v>47.3</v>
       </c>
-      <c r="AG67" t="n">
+      <c r="AH67" t="n">
         <v>48.8</v>
       </c>
-      <c r="AH67" t="n">
+      <c r="AI67" t="n">
         <v>48.9</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>49.4</v>
       </c>
       <c r="AJ67" t="n">
         <v>1</v>
@@ -19705,7 +19707,7 @@
         <v>1.14</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CC67" t="n">
         <v>3</v>
@@ -19740,13 +19742,13 @@
         <v>8</v>
       </c>
       <c r="CM67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN67" t="n">
         <v>0</v>
       </c>
       <c r="CO67" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68">
@@ -19759,10 +19761,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40.68000030517578</v>
+        <v>40.5099983215332</v>
       </c>
       <c r="D68" t="n">
-        <v>40.68000030517578</v>
+        <v>40.5099983215332</v>
       </c>
       <c r="E68" t="n">
         <v>40.77999877929688</v>
@@ -19774,67 +19776,67 @@
         <v>40.4900016784668</v>
       </c>
       <c r="H68" t="n">
-        <v>1028100</v>
+        <v>1180600</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.001227577648477474</v>
+        <v>-0.005401454043106213</v>
       </c>
       <c r="J68" t="n">
-        <v>41.01111094156901</v>
+        <v>40.99222183227539</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.8073681224217018</v>
+        <v>-1.176378076590391</v>
       </c>
       <c r="M68" t="n">
-        <v>40.81999969482422</v>
+        <v>40.80299949645996</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.3429676401153642</v>
+        <v>-0.7180873429468791</v>
       </c>
       <c r="P68" t="n">
-        <v>39.13115354684683</v>
+        <v>39.12461500901442</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>3.958091234071873</v>
+        <v>3.540950657788165</v>
       </c>
       <c r="S68" t="n">
-        <v>39.77619979858398</v>
+        <v>39.77279975891113</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>2.272214317024762</v>
+        <v>1.853524436526244</v>
       </c>
       <c r="V68" t="n">
-        <v>41.05866663614909</v>
+        <v>41.05753328959147</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-0.9222567657370602</v>
+        <v>-1.333579794471168</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.2054500579834</v>
+        <v>41.20460004806519</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-1.27519479114587</v>
+        <v>-1.685738305241968</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2073639924084216</v>
+        <v>0.2080927782774584</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -19984,13 +19986,13 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="CA68" t="n">
         <v>0.24</v>
       </c>
       <c r="CB68" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CC68" t="n">
         <v>6</v>
@@ -20040,10 +20042,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.71999931335449</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="D69" t="n">
-        <v>19.71999931335449</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="E69" t="n">
         <v>19.71999931335449</v>
@@ -20055,67 +20057,67 @@
         <v>19.14999961853027</v>
       </c>
       <c r="H69" t="n">
-        <v>4761800</v>
+        <v>5066200</v>
       </c>
       <c r="I69" t="n">
-        <v>0.01806909958476521</v>
+        <v>0.01187400786119075</v>
       </c>
       <c r="J69" t="n">
-        <v>19.18222215440538</v>
+        <v>19.16888893975152</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>2.803518563283901</v>
+        <v>2.249016325741186</v>
       </c>
       <c r="M69" t="n">
-        <v>19.125</v>
+        <v>19.11300010681152</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>3.111107520807802</v>
+        <v>2.548005399134832</v>
       </c>
       <c r="P69" t="n">
-        <v>18.6996153317965</v>
+        <v>18.69499998826247</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>5.456711079093418</v>
+        <v>4.840868648170392</v>
       </c>
       <c r="S69" t="n">
-        <v>19.9526000213623</v>
+        <v>19.95020004272461</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-1.16576640517415</v>
+        <v>-1.755369171762233</v>
       </c>
       <c r="V69" t="n">
-        <v>23.29353333791097</v>
+        <v>23.29273334503174</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-15.34131371448245</v>
+        <v>-15.85358364285598</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.33260000228882</v>
+        <v>23.33200000762939</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-15.4830609901166</v>
+        <v>-15.99519811820388</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2195609651448596</v>
+        <v>0.2159796155687953</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20263,13 +20265,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>1972</v>
+        <v>1960</v>
       </c>
       <c r="CA69" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CC69" t="n">
         <v>1</v>
@@ -20304,13 +20306,13 @@
         <v>3</v>
       </c>
       <c r="CM69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN69" t="n">
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70">
@@ -20323,10 +20325,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>34.5099983215332</v>
+        <v>34.36999893188477</v>
       </c>
       <c r="D70" t="n">
-        <v>34.5099983215332</v>
+        <v>34.36999893188477</v>
       </c>
       <c r="E70" t="n">
         <v>34.54999923706055</v>
@@ -20338,67 +20340,67 @@
         <v>32.02999877929688</v>
       </c>
       <c r="H70" t="n">
-        <v>4584500</v>
+        <v>5137900</v>
       </c>
       <c r="I70" t="n">
-        <v>0.04766240923735809</v>
+        <v>0.04341227579822315</v>
       </c>
       <c r="J70" t="n">
-        <v>34.10666656494141</v>
+        <v>34.09111107720269</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>1.182559884073766</v>
+        <v>0.818066193414777</v>
       </c>
       <c r="M70" t="n">
-        <v>34.24099998474121</v>
+        <v>34.22700004577636</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.7856030399575612</v>
+        <v>0.4177955588194982</v>
       </c>
       <c r="P70" t="n">
-        <v>32.68230761014498</v>
+        <v>32.67692301823543</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>5.59229395056818</v>
+        <v>5.181258690435795</v>
       </c>
       <c r="S70" t="n">
-        <v>31.24139984130859</v>
+        <v>31.23859985351562</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>10.46239444079821</v>
+        <v>10.02413390181677</v>
       </c>
       <c r="V70" t="n">
-        <v>32.78326661427815</v>
+        <v>32.78233328501383</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>5.267113029251947</v>
+        <v>4.843052607230734</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.57744996070862</v>
+        <v>35.57674996376038</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-3.000360172958713</v>
+        <v>-3.39196535126128</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3829243547603716</v>
+        <v>0.3788702136154615</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20546,13 +20548,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>22.41</v>
+        <v>22.32</v>
       </c>
       <c r="CA70" t="n">
         <v>0.17</v>
       </c>
       <c r="CB70" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CC70" t="n">
         <v>7</v>
@@ -20606,10 +20608,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.38000106811523</v>
+        <v>38.36999893188477</v>
       </c>
       <c r="D71" t="n">
-        <v>38.38000106811523</v>
+        <v>38.36999893188477</v>
       </c>
       <c r="E71" t="n">
         <v>38.68000030517578</v>
@@ -20621,67 +20623,67 @@
         <v>37.29999923706055</v>
       </c>
       <c r="H71" t="n">
-        <v>3701000</v>
+        <v>4172900</v>
       </c>
       <c r="I71" t="n">
-        <v>0.009468716623280526</v>
+        <v>0.009205640975988638</v>
       </c>
       <c r="J71" t="n">
-        <v>37.47333357069228</v>
+        <v>37.47222222222222</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>2.419500511510561</v>
+        <v>2.395845926453046</v>
       </c>
       <c r="M71" t="n">
-        <v>37.20800018310547</v>
+        <v>37.20699996948242</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>3.149862608154684</v>
+        <v>3.125753119994208</v>
       </c>
       <c r="P71" t="n">
-        <v>34.56461546971248</v>
+        <v>34.56423077216515</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>11.03841470982374</v>
+        <v>11.01071273596642</v>
       </c>
       <c r="S71" t="n">
-        <v>33.14020000457764</v>
+        <v>33.13999996185303</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>15.81101219308824</v>
+        <v>15.78152980100155</v>
       </c>
       <c r="V71" t="n">
-        <v>29.36940004984538</v>
+        <v>29.36933336893717</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>30.68023522093464</v>
+        <v>30.64647552561494</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.61070001602173</v>
+        <v>27.61065000534058</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>39.00408553873817</v>
+        <v>38.96811166873314</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3428131134694355</v>
+        <v>0.3427856290892249</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20833,7 +20835,7 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>14.27</v>
+        <v>14.26</v>
       </c>
       <c r="CA71" t="n">
         <v>0.33</v>
@@ -20904,7 +20906,7 @@
         <v>7.230000019073486</v>
       </c>
       <c r="H72" t="n">
-        <v>8808500</v>
+        <v>9815800</v>
       </c>
       <c r="I72" t="n">
         <v>-0.04742546059690445</v>
@@ -21176,10 +21178,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>75.69999694824219</v>
+        <v>75.48000335693359</v>
       </c>
       <c r="D73" t="n">
-        <v>75.69999694824219</v>
+        <v>75.48000335693359</v>
       </c>
       <c r="E73" t="n">
         <v>76.88999938964844</v>
@@ -21191,67 +21193,67 @@
         <v>76.5</v>
       </c>
       <c r="H73" t="n">
-        <v>17248500</v>
+        <v>18562600</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.03196931071051912</v>
+        <v>-0.034782528100466</v>
       </c>
       <c r="J73" t="n">
-        <v>78.49111090766058</v>
+        <v>78.46666717529297</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-3.555961849873613</v>
+        <v>-3.806283516142246</v>
       </c>
       <c r="M73" t="n">
-        <v>78.42699966430663</v>
+        <v>78.40500030517578</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-3.477122327434322</v>
+        <v>-3.730625517323151</v>
       </c>
       <c r="P73" t="n">
-        <v>76.23307682917668</v>
+        <v>76.22461553720328</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.699276354972555</v>
+        <v>-0.9768657736374644</v>
       </c>
       <c r="S73" t="n">
-        <v>75.50980010986328</v>
+        <v>75.50540023803711</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>0.25188364702619</v>
+        <v>-0.03363584726847629</v>
       </c>
       <c r="V73" t="n">
-        <v>80.10793345133463</v>
+        <v>80.10646682739258</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-5.502496835435474</v>
+        <v>-5.775393240632799</v>
       </c>
       <c r="Y73" t="n">
-        <v>78.90280006408692</v>
+        <v>78.90170009613037</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-4.059175483307728</v>
+        <v>-4.33665780968969</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2625273404041317</v>
+        <v>0.2656014748450375</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21399,13 +21401,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>21.57</v>
+        <v>21.5</v>
       </c>
       <c r="CA73" t="n">
         <v>0.21</v>
       </c>
       <c r="CB73" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21455,10 +21457,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.230000019073486</v>
+        <v>3.240000009536743</v>
       </c>
       <c r="D74" t="n">
-        <v>3.230000019073486</v>
+        <v>3.240000009536743</v>
       </c>
       <c r="E74" t="n">
         <v>3.269999980926514</v>
@@ -21470,67 +21472,67 @@
         <v>3.140000104904175</v>
       </c>
       <c r="H74" t="n">
-        <v>15012400</v>
+        <v>15724600</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.01223240430774986</v>
+        <v>-0.009174303230812364</v>
       </c>
       <c r="J74" t="n">
-        <v>3.351111120647854</v>
+        <v>3.352222230699327</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-3.614058060568107</v>
+        <v>-3.347696347063868</v>
       </c>
       <c r="M74" t="n">
-        <v>3.315000009536743</v>
+        <v>3.316000008583069</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>-2.564102269041483</v>
+        <v>-2.291917938769864</v>
       </c>
       <c r="P74" t="n">
-        <v>3.026538454569303</v>
+        <v>3.026923069587121</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>6.722583160871724</v>
+        <v>7.039390663426634</v>
       </c>
       <c r="S74" t="n">
-        <v>3.085199990272522</v>
+        <v>3.085399990081787</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>4.693375770047693</v>
+        <v>5.010696180460481</v>
       </c>
       <c r="V74" t="n">
-        <v>3.464728128115336</v>
+        <v>3.464794794718424</v>
       </c>
       <c r="W74" t="n">
         <v>-1</v>
       </c>
       <c r="X74" t="n">
-        <v>-6.7747915669658</v>
+        <v>-6.487968220350253</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.518696091175079</v>
+        <v>3.518746091127396</v>
       </c>
       <c r="Z74" t="n">
         <v>-1</v>
       </c>
       <c r="AA74" t="n">
-        <v>-8.204632188203046</v>
+        <v>-7.921744688925338</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.7650389560453665</v>
+        <v>0.7646665446417946</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21682,10 +21684,10 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>12.92</v>
+        <v>12.96</v>
       </c>
       <c r="CA74" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CB74" t="n">
         <v>1.52</v>
@@ -21719,13 +21721,13 @@
         <v>6</v>
       </c>
       <c r="CM74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN74" t="n">
         <v>-1</v>
       </c>
       <c r="CO74" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75">
@@ -21738,10 +21740,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>37.81999969482422</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="D75" t="n">
-        <v>37.81999969482422</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="E75" t="n">
         <v>38.22000122070312</v>
@@ -21753,67 +21755,67 @@
         <v>36.7400016784668</v>
       </c>
       <c r="H75" t="n">
-        <v>9334300</v>
+        <v>9824500</v>
       </c>
       <c r="I75" t="n">
-        <v>0.007190425119827815</v>
+        <v>0.003994714485396234</v>
       </c>
       <c r="J75" t="n">
-        <v>37.12222247653537</v>
+        <v>37.10888926188151</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1.87967522345923</v>
+        <v>1.592910789882193</v>
       </c>
       <c r="M75" t="n">
-        <v>36.85200004577636</v>
+        <v>36.84000015258789</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>2.626722153059363</v>
+        <v>2.334420756757652</v>
       </c>
       <c r="P75" t="n">
-        <v>35.01538467407227</v>
+        <v>35.01076933053824</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>8.009665028265927</v>
+        <v>7.68115492410938</v>
       </c>
       <c r="S75" t="n">
-        <v>34.57179985046387</v>
+        <v>34.56939987182617</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>9.395518481566031</v>
+        <v>9.055988541081678</v>
       </c>
       <c r="V75" t="n">
-        <v>32.33359986623128</v>
+        <v>32.33279987335205</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>16.96810701960486</v>
+        <v>16.59986425738195</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.778495054245</v>
+        <v>30.77789505958557</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>22.87800176119415</v>
+        <v>22.4905104457364</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2793823096974768</v>
+        <v>0.2789945898925284</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21965,13 +21967,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.07</v>
+        <v>15.02</v>
       </c>
       <c r="CA75" t="n">
         <v>0.4</v>
       </c>
       <c r="CB75" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CC75" t="n">
         <v>5</v>
@@ -22021,10 +22023,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.45999908447266</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="D76" t="n">
-        <v>22.45999908447266</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="E76" t="n">
         <v>22.65999984741211</v>
@@ -22036,67 +22038,67 @@
         <v>22.18000030517578</v>
       </c>
       <c r="H76" t="n">
-        <v>1835200</v>
+        <v>2103700</v>
       </c>
       <c r="I76" t="n">
-        <v>0.005821726879120748</v>
+        <v>0.003134782582328022</v>
       </c>
       <c r="J76" t="n">
-        <v>22.81999969482422</v>
+        <v>22.81333308749729</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.577566236485156</v>
+        <v>-1.811806575486943</v>
       </c>
       <c r="M76" t="n">
-        <v>22.76599979400635</v>
+        <v>22.75999984741211</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-1.344112765977679</v>
+        <v>-1.581723336095587</v>
       </c>
       <c r="P76" t="n">
-        <v>21.94807690840501</v>
+        <v>21.945769236638</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>2.332423830133407</v>
+        <v>2.069785647494866</v>
       </c>
       <c r="S76" t="n">
-        <v>22.17240009307861</v>
+        <v>22.17120010375977</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>1.297103562026283</v>
+        <v>1.031967208359226</v>
       </c>
       <c r="V76" t="n">
-        <v>24.40846668243408</v>
+        <v>24.40806668599447</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-7.982752965648879</v>
+        <v>-8.227063180782102</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.17595001220703</v>
+        <v>26.17565001487732</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-14.19604990841387</v>
+        <v>-14.4242851436396</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3156247775556806</v>
+        <v>0.3153350111542571</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22244,7 +22246,7 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.06</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
@@ -22304,10 +22306,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30.61000061035156</v>
+        <v>30.51000022888184</v>
       </c>
       <c r="D77" t="n">
-        <v>30.61000061035156</v>
+        <v>30.51000022888184</v>
       </c>
       <c r="E77" t="n">
         <v>30.6299991607666</v>
@@ -22319,88 +22321,88 @@
         <v>29.88999938964844</v>
       </c>
       <c r="H77" t="n">
-        <v>4559700</v>
+        <v>5327100</v>
       </c>
       <c r="I77" t="n">
-        <v>0.01123224801606137</v>
+        <v>0.007928634538775237</v>
       </c>
       <c r="J77" t="n">
-        <v>30.23666678534614</v>
+        <v>30.2255556318495</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1.234705622996635</v>
+        <v>0.9410731782631198</v>
       </c>
       <c r="M77" t="n">
-        <v>30.1980001449585</v>
+        <v>30.18800010681152</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1.364330298083828</v>
+        <v>1.066649400195473</v>
       </c>
       <c r="P77" t="n">
-        <v>29.93807697296143</v>
+        <v>29.93423080444336</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>2.2443780807865</v>
+        <v>1.923448202828084</v>
       </c>
       <c r="S77" t="n">
-        <v>31.98560020446777</v>
+        <v>31.98360019683838</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-4.300684011938801</v>
+        <v>-4.607361144109753</v>
       </c>
       <c r="V77" t="n">
-        <v>36.14286679585775</v>
+        <v>36.14220012664795</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-15.3083213259118</v>
+        <v>-15.58344505323417</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.71815011978149</v>
+        <v>35.71765011787414</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-14.30127118089725</v>
+        <v>-14.58004620070526</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1724966135420725</v>
+        <v>0.1705373192661557</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
       </c>
       <c r="AD77" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AE77" t="n">
         <v>27.4</v>
       </c>
-      <c r="AE77" t="n">
+      <c r="AF77" t="n">
         <v>28.1</v>
       </c>
-      <c r="AF77" t="n">
+      <c r="AG77" t="n">
         <v>30.6</v>
       </c>
-      <c r="AG77" t="n">
+      <c r="AH77" t="n">
         <v>32</v>
       </c>
-      <c r="AH77" t="n">
+      <c r="AI77" t="n">
         <v>32.1</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>32.2</v>
       </c>
       <c r="AJ77" t="n">
         <v>1</v>
@@ -22527,7 +22529,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.54</v>
+        <v>15.49</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
@@ -22587,10 +22589,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.84999847412109</v>
+        <v>50.7400016784668</v>
       </c>
       <c r="D78" t="n">
-        <v>50.84999847412109</v>
+        <v>50.7400016784668</v>
       </c>
       <c r="E78" t="n">
         <v>51.29000091552734</v>
@@ -22602,67 +22604,67 @@
         <v>50.06999969482422</v>
       </c>
       <c r="H78" t="n">
-        <v>7573200</v>
+        <v>8260500</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.01242965980739819</v>
+        <v>-0.01456593465821643</v>
       </c>
       <c r="J78" t="n">
-        <v>51.46555582682291</v>
+        <v>51.45333396063911</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.196056941021131</v>
+        <v>-1.386367465941073</v>
       </c>
       <c r="M78" t="n">
-        <v>51.33400039672851</v>
+        <v>51.32300071716308</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.9428486361220043</v>
+        <v>-1.135941060635069</v>
       </c>
       <c r="P78" t="n">
-        <v>49.65500024648813</v>
+        <v>49.65076960050143</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2.406601997182513</v>
+        <v>2.193786897422774</v>
       </c>
       <c r="S78" t="n">
-        <v>47.84120018005371</v>
+        <v>47.83900024414063</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>6.289136315024621</v>
+        <v>6.064092935724522</v>
       </c>
       <c r="V78" t="n">
-        <v>47.2356667582194</v>
+        <v>47.23493344624837</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>7.651700428834886</v>
+        <v>7.420499991192042</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.45380004882813</v>
+        <v>47.45325006484985</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>7.15685239495764</v>
+        <v>6.926294003309049</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.1925333796987556</v>
+        <v>0.1940717271677031</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22810,13 +22812,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>33.9</v>
+        <v>33.83</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12.02</v>
+        <v>12</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22870,10 +22872,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9.859999656677246</v>
+        <v>9.920000076293945</v>
       </c>
       <c r="D79" t="n">
-        <v>9.859999656677246</v>
+        <v>9.920000076293945</v>
       </c>
       <c r="E79" t="n">
         <v>9.930000305175781</v>
@@ -22885,67 +22887,67 @@
         <v>9.689999580383301</v>
       </c>
       <c r="H79" t="n">
-        <v>2796300</v>
+        <v>3204200</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.005045428002495966</v>
+        <v>0.001009104847206066</v>
       </c>
       <c r="J79" t="n">
-        <v>9.696666611565483</v>
+        <v>9.703333324856228</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1.684424675557589</v>
+        <v>2.232910528619068</v>
       </c>
       <c r="M79" t="n">
-        <v>9.599999904632568</v>
+        <v>9.605999946594238</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.708330777370242</v>
+        <v>3.268791707739227</v>
       </c>
       <c r="P79" t="n">
-        <v>8.569615327394926</v>
+        <v>8.571923035841722</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>15.05766921832865</v>
+        <v>15.72665824011155</v>
       </c>
       <c r="S79" t="n">
-        <v>8.458999986648559</v>
+        <v>8.460199995040893</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>16.56223752500278</v>
+        <v>17.25491220194252</v>
       </c>
       <c r="V79" t="n">
-        <v>9.949399967193603</v>
+        <v>9.949799969991048</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-0.8985497699473214</v>
+        <v>-0.2995024401192006</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.71084998130798</v>
+        <v>10.71114998340607</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-7.943817027739136</v>
+        <v>-7.386227513738366</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5477426718129479</v>
+        <v>0.5469165162276194</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23093,13 +23095,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>22.93</v>
+        <v>23.07</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="CC79" t="n">
         <v>5</v>
@@ -23134,13 +23136,13 @@
         <v>10</v>
       </c>
       <c r="CM79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.85999965667725</v>
+        <v>15.82999992370605</v>
       </c>
       <c r="D2" t="n">
-        <v>15.85999965667725</v>
+        <v>15.82999992370605</v>
       </c>
       <c r="E2" t="n">
         <v>15.94999980926514</v>
@@ -912,67 +912,67 @@
         <v>15.94999980926514</v>
       </c>
       <c r="H2" t="n">
-        <v>12185700</v>
+        <v>17209100</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0006301341495872359</v>
+        <v>-0.002520476505448843</v>
       </c>
       <c r="J2" t="n">
-        <v>15.73222213321262</v>
+        <v>15.72888882954915</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8122026397966537</v>
+        <v>0.6428368542280469</v>
       </c>
       <c r="M2" t="n">
-        <v>15.67599992752075</v>
+        <v>15.67299995422363</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.173767096244138</v>
+        <v>1.001722516052922</v>
       </c>
       <c r="P2" t="n">
-        <v>15.26076918381911</v>
+        <v>15.2596153479356</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3.92660727411758</v>
+        <v>3.73786994472056</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51399995803833</v>
+        <v>15.51339996337891</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2.230241714417708</v>
+        <v>2.040816075615383</v>
       </c>
       <c r="V2" t="n">
-        <v>15.69426666895549</v>
+        <v>15.69406667073568</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.056009759599623</v>
+        <v>0.8661442303150653</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.30379999637604</v>
+        <v>15.30364999771118</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.634389239489001</v>
+        <v>3.439375090737141</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1717133975748477</v>
+        <v>0.1718845368613354</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.02</v>
+        <v>15.99</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.52000045776367</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="D3" t="n">
-        <v>28.52000045776367</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="E3" t="n">
         <v>28.67000007629395</v>
@@ -1199,67 +1199,67 @@
         <v>28.51000022888184</v>
       </c>
       <c r="H3" t="n">
-        <v>1331900</v>
+        <v>2259100</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00281293678634964</v>
+        <v>0.003867746165166386</v>
       </c>
       <c r="J3" t="n">
-        <v>28.75111113654243</v>
+        <v>28.75444433424208</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8038321638464099</v>
+        <v>-0.7110034706463492</v>
       </c>
       <c r="M3" t="n">
-        <v>28.6079999923706</v>
+        <v>28.61099987030029</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3076046372706979</v>
+        <v>-0.2132069257148494</v>
       </c>
       <c r="P3" t="n">
-        <v>27.05692305931678</v>
+        <v>27.05807685852051</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>5.407404955986285</v>
+        <v>5.513778330739855</v>
       </c>
       <c r="S3" t="n">
-        <v>27.19779998779297</v>
+        <v>27.19839996337891</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4.861424345219607</v>
+        <v>4.969407301537924</v>
       </c>
       <c r="V3" t="n">
-        <v>28.93073333740234</v>
+        <v>28.93093332926432</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.419711262927674</v>
+        <v>-1.316701704256644</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.96264999389648</v>
+        <v>28.96279998779297</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.528346115518073</v>
+        <v>-1.425279154316596</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2633010664837896</v>
+        <v>0.2633651728416429</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.39</v>
+        <v>17.41</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1448,13 +1448,13 @@
         <v>6</v>
       </c>
       <c r="CM3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.779999732971191</v>
+        <v>9.659999847412109</v>
       </c>
       <c r="D4" t="n">
-        <v>9.779999732971191</v>
+        <v>9.659999847412109</v>
       </c>
       <c r="E4" t="n">
         <v>9.819999694824219</v>
@@ -1482,98 +1482,96 @@
         <v>9.75</v>
       </c>
       <c r="H4" t="n">
-        <v>3672800</v>
+        <v>6439500</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01557628418979329</v>
+        <v>0.00311523703163874</v>
       </c>
       <c r="J4" t="n">
-        <v>9.415555424160427</v>
+        <v>9.402222103542751</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3.870661818585825</v>
+        <v>2.741668310220278</v>
       </c>
       <c r="M4" t="n">
-        <v>9.323999881744385</v>
+        <v>9.311999893188476</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.890603357037963</v>
+        <v>3.737112953343003</v>
       </c>
       <c r="P4" t="n">
-        <v>8.629230737686157</v>
+        <v>8.624615357472347</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>13.33570778516002</v>
+        <v>12.00499323187448</v>
       </c>
       <c r="S4" t="n">
-        <v>8.535799961090088</v>
+        <v>8.533399963378907</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>14.57625269515113</v>
+        <v>13.20223930517739</v>
       </c>
       <c r="V4" t="n">
-        <v>8.696133273442586</v>
+        <v>8.695333274205526</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>12.4637747082219</v>
+        <v>11.09407244996855</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.547849941253663</v>
+        <v>8.547249941825866</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.41473353165599</v>
+        <v>13.01880620269468</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5220656995514242</v>
+        <v>0.5211213828981155</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE4" t="n">
         <v>8.9</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>9.4</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>12</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Foguete</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1694,13 +1692,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>18.81</v>
+        <v>18.58</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1754,10 +1752,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.5600004196167</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D5" t="n">
-        <v>11.5600004196167</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="E5" t="n">
         <v>11.61999988555908</v>
@@ -1769,67 +1767,67 @@
         <v>11.61999988555908</v>
       </c>
       <c r="H5" t="n">
-        <v>942900</v>
+        <v>1590500</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002601967679124684</v>
+        <v>0.001734645119416456</v>
       </c>
       <c r="J5" t="n">
-        <v>11.82222228580051</v>
+        <v>11.82111114925808</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.218042089250528</v>
+        <v>-2.293447334180895</v>
       </c>
       <c r="M5" t="n">
-        <v>11.76500005722046</v>
+        <v>11.76400003433228</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.742453349823368</v>
+        <v>-1.819107811738105</v>
       </c>
       <c r="P5" t="n">
-        <v>10.95576928212092</v>
+        <v>10.95538465793316</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.515186765404412</v>
+        <v>5.427609813509556</v>
       </c>
       <c r="S5" t="n">
-        <v>11.23579998016357</v>
+        <v>11.23559997558594</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.885423735074411</v>
+        <v>2.79825034561654</v>
       </c>
       <c r="V5" t="n">
-        <v>11.97006665547689</v>
+        <v>11.96999998728434</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.425764013373839</v>
+        <v>-3.508770233881727</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.94034998416901</v>
+        <v>11.9402999830246</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.18541387025163</v>
+        <v>-3.268760356478634</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2899845807552959</v>
+        <v>0.2899594235514774</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1977,7 +1975,7 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.4</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="CA5" t="n">
         <v>1.67</v>
@@ -2011,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM5" t="n">
         <v>2</v>
@@ -2020,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -2033,10 +2031,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.09999847412109</v>
+        <v>54.93000030517578</v>
       </c>
       <c r="D6" t="n">
-        <v>55.09999847412109</v>
+        <v>54.93000030517578</v>
       </c>
       <c r="E6" t="n">
         <v>55.59999847412109</v>
@@ -2048,67 +2046,67 @@
         <v>55.59999847412109</v>
       </c>
       <c r="H6" t="n">
-        <v>4355300</v>
+        <v>6899100</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005447390496298166</v>
+        <v>-0.002542207924900231</v>
       </c>
       <c r="J6" t="n">
-        <v>55.38555569118924</v>
+        <v>55.36666700575087</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5155806663028066</v>
+        <v>-0.7886815735715721</v>
       </c>
       <c r="M6" t="n">
-        <v>55.22200012207031</v>
+        <v>55.20500030517578</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2209294260974421</v>
+        <v>-0.4981432813690534</v>
       </c>
       <c r="P6" t="n">
-        <v>52.8965382209191</v>
+        <v>52.88999982980582</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.165603888858249</v>
+        <v>3.857062737633695</v>
       </c>
       <c r="S6" t="n">
-        <v>52.49099975585938</v>
+        <v>52.48759979248047</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.970373455252171</v>
+        <v>4.653290534053379</v>
       </c>
       <c r="V6" t="n">
-        <v>55.95286661783854</v>
+        <v>55.95173329671224</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.524261749701927</v>
+        <v>-1.826097122171723</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.12489999771118</v>
+        <v>56.12405000686645</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.826108418245529</v>
+        <v>-2.127518775898368</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.245649105028231</v>
+        <v>0.2458684114903697</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2256,13 +2254,13 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.85</v>
+        <v>16.8</v>
       </c>
       <c r="CA6" t="n">
         <v>0.29</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -2312,82 +2310,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.64000034332275</v>
+        <v>15.38000011444092</v>
       </c>
       <c r="D7" t="n">
-        <v>15.64000034332275</v>
+        <v>15.38000011444092</v>
       </c>
       <c r="E7" t="n">
         <v>15.98999977111816</v>
       </c>
       <c r="F7" t="n">
-        <v>15.47000026702881</v>
+        <v>15.30000019073486</v>
       </c>
       <c r="G7" t="n">
         <v>15.81999969482422</v>
       </c>
       <c r="H7" t="n">
-        <v>1221600</v>
+        <v>2141900</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008243507334644296</v>
+        <v>-0.02473052200393278</v>
       </c>
       <c r="J7" t="n">
-        <v>16.67444451649984</v>
+        <v>16.64555560217963</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.203769919612436</v>
+        <v>-7.60296332537557</v>
       </c>
       <c r="M7" t="n">
-        <v>16.51400003433228</v>
+        <v>16.48800001144409</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.29247722655017</v>
+        <v>-6.720038186766908</v>
       </c>
       <c r="P7" t="n">
-        <v>15.70923082645123</v>
+        <v>15.69923081764808</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.4406993817412418</v>
+        <v>-2.033416203093873</v>
       </c>
       <c r="S7" t="n">
-        <v>16.54219999313354</v>
+        <v>16.53699998855591</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.453927834177323</v>
+        <v>-6.996431486458662</v>
       </c>
       <c r="V7" t="n">
-        <v>20.28953336715698</v>
+        <v>20.28780003229777</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-22.91591896026799</v>
+        <v>-24.19089260562374</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.60195000171661</v>
+        <v>21.60065000057221</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-27.59912719879496</v>
+        <v>-28.79843840794838</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5101789351233315</v>
+        <v>0.5145032642434831</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2539,10 +2537,10 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CB7" t="n">
         <v>0.4</v>
@@ -2595,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.55999946594238</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="D8" t="n">
-        <v>17.55999946594238</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="E8" t="n">
         <v>17.61000061035156</v>
@@ -2610,67 +2608,67 @@
         <v>17.55999946594238</v>
       </c>
       <c r="H8" t="n">
-        <v>15329100</v>
+        <v>23165500</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01093831994986649</v>
+        <v>0.009786992981023257</v>
       </c>
       <c r="J8" t="n">
-        <v>17.42000028822157</v>
+        <v>17.41777822706435</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8036692043884158</v>
+        <v>0.7017122785102621</v>
       </c>
       <c r="M8" t="n">
-        <v>17.34000034332275</v>
+        <v>17.33800048828125</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.268737706250083</v>
+        <v>1.165073373845078</v>
       </c>
       <c r="P8" t="n">
-        <v>15.90653859652006</v>
+        <v>15.90576942150409</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>10.39485026480909</v>
+        <v>10.27445734133315</v>
       </c>
       <c r="S8" t="n">
-        <v>15.64560001373291</v>
+        <v>15.64520004272461</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>12.23602450867407</v>
+        <v>12.11106836364079</v>
       </c>
       <c r="V8" t="n">
-        <v>16.61946671168009</v>
+        <v>16.61933338801066</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.659223431045995</v>
+        <v>5.53973800285433</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.15750005722046</v>
+        <v>16.15740006446838</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.680175793006876</v>
+        <v>8.557075058749255</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3178442181751376</v>
+        <v>0.3176464852877336</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2822,7 +2820,7 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>17.92</v>
+        <v>17.9</v>
       </c>
       <c r="CA8" t="n">
         <v>-0.01</v>
@@ -2882,10 +2880,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.30999946594238</v>
+        <v>22.09000015258789</v>
       </c>
       <c r="D9" t="n">
-        <v>22.30999946594238</v>
+        <v>22.09000015258789</v>
       </c>
       <c r="E9" t="n">
         <v>22.32999992370605</v>
@@ -2897,88 +2895,88 @@
         <v>22.28000068664551</v>
       </c>
       <c r="H9" t="n">
-        <v>10280500</v>
+        <v>19332900</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00858944934450423</v>
+        <v>-0.001356269688394307</v>
       </c>
       <c r="J9" t="n">
-        <v>22.41444460550944</v>
+        <v>22.39000023735894</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4659724628705991</v>
+        <v>-1.339884241137626</v>
       </c>
       <c r="M9" t="n">
-        <v>22.29400005340576</v>
+        <v>22.27200012207031</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07176555350451053</v>
+        <v>-0.8171693987289033</v>
       </c>
       <c r="P9" t="n">
-        <v>20.2580769612239</v>
+        <v>20.2496154491718</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>10.12891060018226</v>
+        <v>9.088492115001436</v>
       </c>
       <c r="S9" t="n">
-        <v>20.41800003051758</v>
+        <v>20.41360004425049</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>9.266330848256167</v>
+        <v>8.212172790215726</v>
       </c>
       <c r="V9" t="n">
-        <v>21.87106666564942</v>
+        <v>21.86960000356038</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>2.006910805966098</v>
+        <v>1.007792318979895</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.03460000038147</v>
+        <v>22.0335000038147</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.249850079221519</v>
+        <v>0.2564283875163305</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3641507036508055</v>
+        <v>0.3636908269035047</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG9" t="n">
         <v>22.1</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>22.2</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
         <v>22.3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>22.6</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -3125,13 +3123,13 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.890000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="CC9" t="n">
         <v>1</v>
@@ -3162,13 +3160,13 @@
         <v>8</v>
       </c>
       <c r="CM9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -3181,10 +3179,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.19000053405762</v>
+        <v>16.1299991607666</v>
       </c>
       <c r="D10" t="n">
-        <v>16.19000053405762</v>
+        <v>16.1299991607666</v>
       </c>
       <c r="E10" t="n">
         <v>16.30999946594238</v>
@@ -3196,67 +3194,67 @@
         <v>16.30999946594238</v>
       </c>
       <c r="H10" t="n">
-        <v>2194600</v>
+        <v>3892300</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001236886683321226</v>
+        <v>-0.002473773366642562</v>
       </c>
       <c r="J10" t="n">
-        <v>15.9844446182251</v>
+        <v>15.97777779897054</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28597471317927</v>
+        <v>0.9527067137325463</v>
       </c>
       <c r="M10" t="n">
-        <v>15.91500015258789</v>
+        <v>15.90900001525879</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.727932006491438</v>
+        <v>1.389145422690591</v>
       </c>
       <c r="P10" t="n">
-        <v>15.10730776420006</v>
+        <v>15.10500001907349</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>7.166682421226773</v>
+        <v>6.785826814954131</v>
       </c>
       <c r="S10" t="n">
-        <v>15.53981779098511</v>
+        <v>15.53861776351929</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>4.183979193434884</v>
+        <v>3.80588161860656</v>
       </c>
       <c r="V10" t="n">
-        <v>16.19967260996501</v>
+        <v>16.19927260080973</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0597053788694427</v>
+        <v>-0.4276330286562816</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29145446300507</v>
+        <v>16.29115445613861</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.6227432251542262</v>
+        <v>-0.9892196148891353</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2260513450567614</v>
+        <v>0.2261559777249185</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3424,13 +3422,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.23</v>
+        <v>7.2</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="CC10" t="n">
         <v>2</v>
@@ -3461,13 +3459,13 @@
         <v>5</v>
       </c>
       <c r="CM10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -3480,10 +3478,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.39999961853027</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="D11" t="n">
-        <v>18.39999961853027</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="E11" t="n">
         <v>18.45999908447266</v>
@@ -3495,91 +3493,91 @@
         <v>18.45000076293945</v>
       </c>
       <c r="H11" t="n">
-        <v>7659700</v>
+        <v>16171300</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003818859526217855</v>
+        <v>-0.002727727074121944</v>
       </c>
       <c r="J11" t="n">
-        <v>18.13888888888889</v>
+        <v>18.12555567423503</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.439507851009162</v>
+        <v>0.8520842901937614</v>
       </c>
       <c r="M11" t="n">
-        <v>18.06499996185303</v>
+        <v>18.05300006866455</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.854412717324383</v>
+        <v>1.257412159295182</v>
       </c>
       <c r="P11" t="n">
-        <v>17.1596155166626</v>
+        <v>17.15500017312857</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>7.228507542393468</v>
+        <v>6.55785778002574</v>
       </c>
       <c r="S11" t="n">
-        <v>17.73214042663574</v>
+        <v>17.72974044799805</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>3.766376623610142</v>
+        <v>3.10360007954653</v>
       </c>
       <c r="V11" t="n">
-        <v>18.61758014678955</v>
+        <v>18.61678015391032</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.168683183011817</v>
+        <v>-1.809010282554546</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.79113512039185</v>
+        <v>18.79053512573242</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.081489486162647</v>
+        <v>-2.716976582469811</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.265183881101506</v>
+        <v>0.2650264360026382</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
         <v>18.1</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>18.2</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>18.3</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>18.4</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI11" t="n">
-        <v>18.6</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -3723,7 +3721,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.210000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3760,13 +3758,13 @@
         <v>5</v>
       </c>
       <c r="CM11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN11" t="n">
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -3779,10 +3777,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.38000106811523</v>
+        <v>40.45999908447266</v>
       </c>
       <c r="D12" t="n">
-        <v>40.38000106811523</v>
+        <v>40.45999908447266</v>
       </c>
       <c r="E12" t="n">
         <v>40.59999847412109</v>
@@ -3794,67 +3792,67 @@
         <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>2340800</v>
+        <v>3432500</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01533820978954714</v>
+        <v>0.01734972639594945</v>
       </c>
       <c r="J12" t="n">
-        <v>41.08333333333334</v>
+        <v>41.09222200181749</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.711964945764141</v>
+        <v>-1.538546436639203</v>
       </c>
       <c r="M12" t="n">
-        <v>41.03499984741211</v>
+        <v>41.04299964904785</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.59619539839765</v>
+        <v>-1.420462854957822</v>
       </c>
       <c r="P12" t="n">
-        <v>39.17884606581468</v>
+        <v>39.18192291259766</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.065825369850836</v>
+        <v>3.261902624651627</v>
       </c>
       <c r="S12" t="n">
-        <v>39.95119979858399</v>
+        <v>39.95279975891113</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.073312620629849</v>
+        <v>1.269496327221464</v>
       </c>
       <c r="V12" t="n">
-        <v>37.01646657307943</v>
+        <v>37.01699989318848</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>9.086589851560737</v>
+        <v>9.301129754488095</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.69394994735718</v>
+        <v>36.69434993743896</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.04539202251662</v>
+        <v>10.26220427246656</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3204899069250375</v>
+        <v>0.3214107893149382</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4024,13 +4022,13 @@
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>6.2</v>
+        <v>6.22</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4080,10 +4078,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.010000228881836</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="D13" t="n">
-        <v>4.010000228881836</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="E13" t="n">
         <v>4.119999885559082</v>
@@ -4095,67 +4093,67 @@
         <v>4.099999904632568</v>
       </c>
       <c r="H13" t="n">
-        <v>10759800</v>
+        <v>16322000</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.01715678826793576</v>
+        <v>-0.007352875865728303</v>
       </c>
       <c r="J13" t="n">
-        <v>3.967777808507284</v>
+        <v>3.972222248713175</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.064132681119983</v>
+        <v>1.958046079795374</v>
       </c>
       <c r="M13" t="n">
-        <v>3.954000020027161</v>
+        <v>3.958000016212464</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.416292578933541</v>
+        <v>2.324410665627981</v>
       </c>
       <c r="P13" t="n">
-        <v>3.750384624187763</v>
+        <v>3.751923084259033</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>6.92237278863896</v>
+        <v>7.944648645021392</v>
       </c>
       <c r="S13" t="n">
-        <v>3.663600006103516</v>
+        <v>3.664400005340576</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>9.455186761688543</v>
+        <v>10.52287372645741</v>
       </c>
       <c r="V13" t="n">
-        <v>4.036733339627584</v>
+        <v>4.037000006039937</v>
       </c>
       <c r="W13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6622461405442777</v>
+        <v>0.3220258775198355</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.491900006532669</v>
+        <v>4.492100006341934</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-10.72819468265089</v>
+        <v>-9.841718015692335</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5370705039788262</v>
+        <v>0.5344946852709516</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4307,13 +4305,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CC13" t="n">
         <v>8</v>
@@ -4345,16 +4343,16 @@
         <v>1</v>
       </c>
       <c r="CL13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CN13" t="n">
         <v>0</v>
       </c>
       <c r="CO13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -4367,10 +4365,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.79000091552734</v>
+        <v>60.45999908447266</v>
       </c>
       <c r="D14" t="n">
-        <v>60.79000091552734</v>
+        <v>60.45999908447266</v>
       </c>
       <c r="E14" t="n">
         <v>60.97999954223633</v>
@@ -4382,67 +4380,67 @@
         <v>60.97999954223633</v>
       </c>
       <c r="H14" t="n">
-        <v>2277500</v>
+        <v>3776200</v>
       </c>
       <c r="I14" t="n">
-        <v>0.005125684120988128</v>
+        <v>-0.0003306954020345643</v>
       </c>
       <c r="J14" t="n">
-        <v>59.76222271389432</v>
+        <v>59.72555584377713</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.719779076078565</v>
+        <v>1.229696786107096</v>
       </c>
       <c r="M14" t="n">
-        <v>59.3830005645752</v>
+        <v>59.35000038146973</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.369365538243766</v>
+        <v>1.870258965237503</v>
       </c>
       <c r="P14" t="n">
-        <v>54.76923106266902</v>
+        <v>54.75653868455153</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>10.9929786050294</v>
+        <v>10.41603530270303</v>
       </c>
       <c r="S14" t="n">
-        <v>55.43300010681153</v>
+        <v>55.42640007019043</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.663920044727215</v>
+        <v>9.081591097216879</v>
       </c>
       <c r="V14" t="n">
-        <v>56.28666659037272</v>
+        <v>56.28446657816569</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>8.000712420807803</v>
+        <v>7.418623219086827</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.0472999382019</v>
+        <v>56.04564992904663</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.461961562028451</v>
+        <v>7.87634573069374</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3537622655595773</v>
+        <v>0.3537398803887616</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4614,13 +4612,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.66</v>
+        <v>13.59</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CC14" t="n">
         <v>6</v>
@@ -4674,10 +4672,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.59000015258789</v>
+        <v>21.48999977111816</v>
       </c>
       <c r="D15" t="n">
-        <v>21.59000015258789</v>
+        <v>21.48999977111816</v>
       </c>
       <c r="E15" t="n">
         <v>21.79999923706055</v>
@@ -4689,67 +4687,67 @@
         <v>21.79999923706055</v>
       </c>
       <c r="H15" t="n">
-        <v>548800</v>
+        <v>824300</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.002310500853547337</v>
+        <v>-0.006931590700599899</v>
       </c>
       <c r="J15" t="n">
-        <v>22.40222210354275</v>
+        <v>22.39111095004612</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.625631186052805</v>
+        <v>-4.024414782001229</v>
       </c>
       <c r="M15" t="n">
-        <v>22.39299983978271</v>
+        <v>22.38299980163574</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.585940664225965</v>
+        <v>-3.989635162541156</v>
       </c>
       <c r="P15" t="n">
-        <v>21.63115376692552</v>
+        <v>21.62730759840745</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.1902515916675335</v>
+        <v>-0.6348817422812185</v>
       </c>
       <c r="S15" t="n">
-        <v>21.58299999237061</v>
+        <v>21.58099998474121</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03243367566954983</v>
+        <v>-0.4216681974300955</v>
       </c>
       <c r="V15" t="n">
-        <v>22.64213335673014</v>
+        <v>22.64146668752035</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.646793601847218</v>
+        <v>-5.085655148996395</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.37839998245239</v>
+        <v>22.37789998054505</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3.523039316853357</v>
+        <v>-3.967754839367439</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2783735285891071</v>
+        <v>0.2790697459079771</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4905,7 +4903,7 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.85</v>
+        <v>10.8</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
@@ -4965,13 +4963,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.95999908447266</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="D16" t="n">
-        <v>17.95999908447266</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="E16" t="n">
-        <v>18.02000045776367</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="F16" t="n">
         <v>17.56999969482422</v>
@@ -4980,88 +4978,88 @@
         <v>17.70999908447266</v>
       </c>
       <c r="H16" t="n">
-        <v>1210900</v>
+        <v>2049900</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01183093433648774</v>
+        <v>0.01521129339513649</v>
       </c>
       <c r="J16" t="n">
-        <v>18.32666651407878</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.000731716946137</v>
+        <v>-1.709088412198147</v>
       </c>
       <c r="M16" t="n">
-        <v>18.2939998626709</v>
+        <v>18.3</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.82573948128082</v>
+        <v>-1.530052143367917</v>
       </c>
       <c r="P16" t="n">
-        <v>18.26192290966327</v>
+        <v>18.26423065478985</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.653297008667439</v>
+        <v>-1.337204953454363</v>
       </c>
       <c r="S16" t="n">
-        <v>18.96179988861084</v>
+        <v>18.96299991607666</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.283257971411793</v>
+        <v>-4.972839015379224</v>
       </c>
       <c r="V16" t="n">
-        <v>19.18893323262532</v>
+        <v>19.1893332417806</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.404390141205008</v>
+        <v>-6.093660312652026</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.40219990730286</v>
+        <v>18.40249991416931</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-2.402978040982567</v>
+        <v>-2.078518995732356</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4039455775000541</v>
+        <v>0.4051434855716536</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
@@ -5188,7 +5186,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>35.92</v>
+        <v>36.04</v>
       </c>
       <c r="CA16" t="n">
         <v>1.27</v>
@@ -5225,13 +5223,13 @@
         <v>2</v>
       </c>
       <c r="CM16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -5244,10 +5242,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.53000020980835</v>
+        <v>5.360000133514404</v>
       </c>
       <c r="D17" t="n">
-        <v>5.53000020980835</v>
+        <v>5.360000133514404</v>
       </c>
       <c r="E17" t="n">
         <v>5.539999961853027</v>
@@ -5259,67 +5257,67 @@
         <v>5.139999866485596</v>
       </c>
       <c r="H17" t="n">
-        <v>2773900</v>
+        <v>4100200</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08644401650887001</v>
+        <v>0.0530451813030377</v>
       </c>
       <c r="J17" t="n">
-        <v>5.086666742960612</v>
+        <v>5.067777845594618</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>8.715598824343312</v>
+        <v>5.76628054392347</v>
       </c>
       <c r="M17" t="n">
-        <v>5.002000045776367</v>
+        <v>4.985000038146973</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>10.55578087164992</v>
+        <v>7.522569558631869</v>
       </c>
       <c r="P17" t="n">
-        <v>4.909999994131235</v>
+        <v>4.903461529658391</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>12.62729565006478</v>
+        <v>9.31053707864654</v>
       </c>
       <c r="S17" t="n">
-        <v>5.491399993896485</v>
+        <v>5.487999992370606</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7029212214511404</v>
+        <v>-2.332358947415199</v>
       </c>
       <c r="V17" t="n">
-        <v>8.301333303451537</v>
+        <v>8.300199969609578</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-33.38419254279213</v>
+        <v>-35.42324096841577</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.288699979782104</v>
+        <v>8.287849979400635</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-33.28265924334103</v>
+        <v>-35.32701307532558</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.104719297735589</v>
+        <v>1.086040579929696</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5471,13 +5469,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.76</v>
+        <v>10.07</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="CC17" t="n">
         <v>1</v>
@@ -5509,7 +5507,7 @@
         <v>-1</v>
       </c>
       <c r="CL17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM17" t="n">
         <v>10</v>
@@ -5518,7 +5516,7 @@
         <v>-1</v>
       </c>
       <c r="CO17" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -5531,103 +5529,105 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.300000190734863</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="D18" t="n">
-        <v>9.300000190734863</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="E18" t="n">
         <v>9.439999580383301</v>
       </c>
       <c r="F18" t="n">
-        <v>9.239999771118164</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="G18" t="n">
         <v>9.430000305175781</v>
       </c>
       <c r="H18" t="n">
-        <v>2119600</v>
+        <v>4478100</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.005347613764161596</v>
+        <v>-0.01176477068060522</v>
       </c>
       <c r="J18" t="n">
-        <v>9.30222225189209</v>
+        <v>9.295555538601345</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.02388742277980502</v>
+        <v>-0.5976594648106446</v>
       </c>
       <c r="M18" t="n">
-        <v>9.249000072479248</v>
+        <v>9.243000030517578</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5514122376035874</v>
+        <v>-0.03245980081692219</v>
       </c>
       <c r="P18" t="n">
-        <v>8.471538507021391</v>
+        <v>8.479615431565504</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>9.779353337375801</v>
+        <v>8.96720312010987</v>
       </c>
       <c r="S18" t="n">
-        <v>9.08540002822876</v>
+        <v>9.119200019836425</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.362033172335075</v>
+        <v>1.32467487300389</v>
       </c>
       <c r="V18" t="n">
-        <v>10.82980000178019</v>
+        <v>10.85693333307902</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.12583621852538</v>
+        <v>-14.8930965343074</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.3405500125885</v>
+        <v>11.38370001316071</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-17.99339379120536</v>
+        <v>-18.83131354097708</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5107689270607695</v>
+        <v>0.5352256658246822</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
         <v>7.2</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AG18" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
         <v>9.5</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9.699999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
@@ -5754,7 +5754,7 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>4.89</v>
+        <v>4.86</v>
       </c>
       <c r="CA18" t="n">
         <v>0.05</v>
@@ -5795,13 +5795,13 @@
         <v>4</v>
       </c>
       <c r="CM18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN18" t="n">
         <v>0</v>
       </c>
       <c r="CO18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -5814,113 +5814,109 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.21000003814697</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="D19" t="n">
-        <v>11.21000003814697</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="E19" t="n">
         <v>11.32999992370605</v>
       </c>
       <c r="F19" t="n">
-        <v>11.15999984741211</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="G19" t="n">
         <v>11.31999969482422</v>
       </c>
       <c r="H19" t="n">
-        <v>4391600</v>
+        <v>10164500</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0008912859753865687</v>
+        <v>-0.01426023561534895</v>
       </c>
       <c r="J19" t="n">
-        <v>11.30888896518283</v>
+        <v>11.29222234090169</v>
       </c>
       <c r="K19" t="n">
         <v>-1</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8744353874223679</v>
+        <v>-2.056476699399199</v>
       </c>
       <c r="M19" t="n">
-        <v>11.25700006484985</v>
+        <v>11.24200010299683</v>
       </c>
       <c r="N19" t="n">
         <v>-1</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4175182236130457</v>
+        <v>-1.618926184955385</v>
       </c>
       <c r="P19" t="n">
-        <v>10.68769231209388</v>
+        <v>10.68192309599656</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>4.8870018971454</v>
+        <v>3.539412521719375</v>
       </c>
       <c r="S19" t="n">
-        <v>10.89779996871948</v>
+        <v>10.89479997634888</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>2.864799044978016</v>
+        <v>1.516323784066256</v>
       </c>
       <c r="V19" t="n">
-        <v>11.51706672032674</v>
+        <v>11.51606672286987</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.666188272034755</v>
+        <v>-3.960261035544948</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.4381000328064</v>
+        <v>11.43735003471375</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.994212273062785</v>
+        <v>-3.299274866570876</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2604158801799039</v>
+        <v>0.2636414128008845</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AF19" t="n">
         <v>11</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>11.1</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>11.2</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>13.9</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -6041,13 +6037,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.63</v>
+        <v>6.54</v>
       </c>
       <c r="CA19" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="CB19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="CC19" t="n">
         <v>5</v>
@@ -6078,13 +6074,13 @@
         <v>4</v>
       </c>
       <c r="CM19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN19" t="n">
         <v>0</v>
       </c>
       <c r="CO19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -6097,10 +6093,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.260000228881836</v>
+        <v>6.25</v>
       </c>
       <c r="D20" t="n">
-        <v>6.260000228881836</v>
+        <v>6.25</v>
       </c>
       <c r="E20" t="n">
         <v>6.409999847412109</v>
@@ -6112,67 +6108,67 @@
         <v>6.28000020980835</v>
       </c>
       <c r="H20" t="n">
-        <v>5136100</v>
+        <v>6890700</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.001597480593642397</v>
       </c>
       <c r="J20" t="n">
-        <v>6.617777771419949</v>
+        <v>6.616666634877522</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.406309412250721</v>
+        <v>-5.541561259029784</v>
       </c>
       <c r="M20" t="n">
-        <v>6.563999986648559</v>
+        <v>6.562999963760376</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.631318683501997</v>
+        <v>-4.769159919072095</v>
       </c>
       <c r="P20" t="n">
-        <v>6.086923085726225</v>
+        <v>6.086538461538462</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.843425828091623</v>
+        <v>2.685624012638228</v>
       </c>
       <c r="S20" t="n">
-        <v>5.806799983978271</v>
+        <v>5.806599979400635</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>7.804647071605777</v>
+        <v>7.636138569427228</v>
       </c>
       <c r="V20" t="n">
-        <v>5.141666657129924</v>
+        <v>5.141599988937378</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>21.7504098637185</v>
+        <v>21.5574920928786</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.265149993896484</v>
+        <v>5.265099992752075</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.89500272810102</v>
+        <v>18.70619757656523</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5079896663231357</v>
+        <v>0.5081050952432229</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6324,13 +6320,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>15.27</v>
+        <v>15.24</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6362,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM20" t="n">
         <v>1</v>
@@ -6371,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -6384,13 +6380,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.369999885559082</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="D21" t="n">
-        <v>2.369999885559082</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="E21" t="n">
-        <v>2.369999885559082</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="F21" t="n">
         <v>2.319999933242798</v>
@@ -6399,67 +6395,67 @@
         <v>2.349999904632568</v>
       </c>
       <c r="H21" t="n">
-        <v>10428300</v>
+        <v>20229000</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01282050106417221</v>
+        <v>0.02564110401662978</v>
       </c>
       <c r="J21" t="n">
-        <v>2.387777778837416</v>
+        <v>2.391111135482788</v>
       </c>
       <c r="K21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7445371774499698</v>
+        <v>0.3717501772601126</v>
       </c>
       <c r="M21" t="n">
-        <v>2.382999992370606</v>
+        <v>2.386000013351441</v>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5455353274504644</v>
+        <v>0.5867595112175303</v>
       </c>
       <c r="P21" t="n">
-        <v>2.232692305858319</v>
+        <v>2.233846160081717</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>6.149865762536311</v>
+        <v>7.438020498226118</v>
       </c>
       <c r="S21" t="n">
-        <v>2.230400004386902</v>
+        <v>2.231000008583069</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>6.258961661478015</v>
+        <v>7.575082300949723</v>
       </c>
       <c r="V21" t="n">
-        <v>2.656600000063578</v>
+        <v>2.656800001462301</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-10.78822986138813</v>
+        <v>-9.665759784459743</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.908099956512451</v>
+        <v>2.908249957561493</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-18.5034929679201</v>
+        <v>-17.47614096486459</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4155593809055013</v>
+        <v>0.420389361673026</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6469,28 +6465,26 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AE21" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AJ21" t="n">
         <v>2</v>
       </c>
       <c r="AK21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -6611,10 +6605,10 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>7.18</v>
+        <v>7.27</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CB21" t="n">
         <v>0.36</v>
@@ -6652,13 +6646,13 @@
         <v>7</v>
       </c>
       <c r="CM21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CN21" t="n">
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
@@ -6671,10 +6665,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44.88000106811523</v>
+        <v>44.88999938964844</v>
       </c>
       <c r="D22" t="n">
-        <v>44.88000106811523</v>
+        <v>44.88999938964844</v>
       </c>
       <c r="E22" t="n">
         <v>45.18999862670898</v>
@@ -6686,67 +6680,67 @@
         <v>44.72000122070312</v>
       </c>
       <c r="H22" t="n">
-        <v>927600</v>
+        <v>1369500</v>
       </c>
       <c r="I22" t="n">
-        <v>0.003353488205097399</v>
+        <v>0.003577014286821667</v>
       </c>
       <c r="J22" t="n">
-        <v>46.06111145019531</v>
+        <v>46.06222237481011</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.564224667824575</v>
+        <v>-2.544868494670644</v>
       </c>
       <c r="M22" t="n">
-        <v>45.9560001373291</v>
+        <v>45.95699996948242</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.34136797371069</v>
+        <v>-2.321736798621592</v>
       </c>
       <c r="P22" t="n">
-        <v>44.20423111548791</v>
+        <v>44.20461566631611</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.528744953988254</v>
+        <v>1.550479996265619</v>
       </c>
       <c r="S22" t="n">
-        <v>45.13940010070801</v>
+        <v>45.13960006713867</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5746621178262097</v>
+        <v>-0.5529527889458266</v>
       </c>
       <c r="V22" t="n">
-        <v>46.87179985046387</v>
+        <v>46.87186650594076</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.249460845760374</v>
+        <v>-4.228265832002082</v>
       </c>
       <c r="Y22" t="n">
-        <v>48.00034994125366</v>
+        <v>48.00039993286133</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.500679426206969</v>
+        <v>-6.479947141197657</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.2668408987342984</v>
+        <v>0.2668716520817731</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6954,10 +6948,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.01000022888184</v>
+        <v>15.93000030517578</v>
       </c>
       <c r="D23" t="n">
-        <v>16.01000022888184</v>
+        <v>15.93000030517578</v>
       </c>
       <c r="E23" t="n">
         <v>16.07999992370605</v>
@@ -6969,67 +6963,67 @@
         <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>4883100</v>
+        <v>7855800</v>
       </c>
       <c r="I23" t="n">
-        <v>0.005653275889232479</v>
+        <v>0.0006281550775069089</v>
       </c>
       <c r="J23" t="n">
-        <v>15.91555553012424</v>
+        <v>15.90666664971246</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5934112609442659</v>
+        <v>0.1466910445611636</v>
       </c>
       <c r="M23" t="n">
-        <v>15.84399995803833</v>
+        <v>15.83599996566772</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.047716935642172</v>
+        <v>0.5935863836312728</v>
       </c>
       <c r="P23" t="n">
-        <v>14.82038453909067</v>
+        <v>14.83153838377732</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>8.026888146211064</v>
+        <v>7.40625748303999</v>
       </c>
       <c r="S23" t="n">
-        <v>14.84819997787476</v>
+        <v>14.85919998168945</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.824519152074147</v>
+        <v>7.206312081443435</v>
       </c>
       <c r="V23" t="n">
-        <v>15.01313327153524</v>
+        <v>15.00659993489583</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>6.639966083806435</v>
+        <v>6.153295045420012</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.53339995861053</v>
+        <v>14.52724995613098</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.16004702599867</v>
+        <v>9.655993758493791</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1977827541915861</v>
+        <v>0.2224032662539245</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7181,13 +7175,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.59</v>
+        <v>17.51</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
       </c>
       <c r="CB23" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7215,16 +7209,16 @@
         <v>0</v>
       </c>
       <c r="CL23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
@@ -7237,13 +7231,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="D24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="E24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="F24" t="n">
         <v>3.519999980926514</v>
@@ -7252,67 +7246,67 @@
         <v>3.619999885559082</v>
       </c>
       <c r="H24" t="n">
-        <v>16574500</v>
+        <v>24621300</v>
       </c>
       <c r="I24" t="n">
-        <v>0.005540227126394903</v>
+        <v>-0.01662048324739585</v>
       </c>
       <c r="J24" t="n">
-        <v>3.766666650772095</v>
+        <v>3.757777743869358</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.628315139147308</v>
+        <v>-5.529273036226088</v>
       </c>
       <c r="M24" t="n">
-        <v>3.786999988555908</v>
+        <v>3.778999972343445</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.145758505134261</v>
+        <v>-6.059804755308116</v>
       </c>
       <c r="P24" t="n">
-        <v>3.597307700377244</v>
+        <v>3.594230771064758</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9088022706605152</v>
+        <v>-1.230605978462845</v>
       </c>
       <c r="S24" t="n">
-        <v>3.742600021362305</v>
+        <v>3.741000018119812</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.008601140348427</v>
+        <v>-5.105588475765965</v>
       </c>
       <c r="V24" t="n">
-        <v>4.521866669654846</v>
+        <v>4.521333335240682</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-19.72341557965495</v>
+        <v>-21.48333933606537</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.796700011491776</v>
+        <v>4.796300010681152</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-24.32296983875825</v>
+        <v>-25.98461429830102</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5914972326927517</v>
+        <v>0.5920768148275406</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7464,13 +7458,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>-1.51</v>
+        <v>-1.48</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.29</v>
+        <v>3.37</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7524,10 +7518,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.36999893188477</v>
+        <v>57.43000030517578</v>
       </c>
       <c r="D25" t="n">
-        <v>57.36999893188477</v>
+        <v>57.43000030517578</v>
       </c>
       <c r="E25" t="n">
         <v>57.65000152587891</v>
@@ -7539,67 +7533,67 @@
         <v>57.09999847412109</v>
       </c>
       <c r="H25" t="n">
-        <v>1133900</v>
+        <v>1863500</v>
       </c>
       <c r="I25" t="n">
-        <v>0.008791981877806387</v>
+        <v>0.009847043851042514</v>
       </c>
       <c r="J25" t="n">
-        <v>56.56222195095486</v>
+        <v>56.56888877020942</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.428121019768858</v>
+        <v>1.522235196212383</v>
       </c>
       <c r="M25" t="n">
-        <v>56.43599967956543</v>
+        <v>56.44199981689453</v>
       </c>
       <c r="N25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.654970688252954</v>
+        <v>1.750470379303459</v>
       </c>
       <c r="P25" t="n">
-        <v>55.95307702284593</v>
+        <v>55.9553847679725</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.532339568135453</v>
+        <v>2.635341608887142</v>
       </c>
       <c r="S25" t="n">
-        <v>59.78499977111817</v>
+        <v>59.78619979858399</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.039476203862218</v>
+        <v>-3.941042416721745</v>
       </c>
       <c r="V25" t="n">
-        <v>57.21953315734864</v>
+        <v>57.21993316650391</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2629622547292765</v>
+        <v>0.367122306942585</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.23454990386963</v>
+        <v>54.23484991073608</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.781276019756226</v>
+        <v>5.891323382840603</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2914424140621141</v>
+        <v>0.2918481347211299</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7747,7 +7741,7 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>16.12</v>
+        <v>16.13</v>
       </c>
       <c r="CA25" t="n">
         <v>0.31</v>
@@ -7788,13 +7782,13 @@
         <v>2</v>
       </c>
       <c r="CM25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN25" t="n">
         <v>0</v>
       </c>
       <c r="CO25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
@@ -7807,10 +7801,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.369999885559082</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="D26" t="n">
-        <v>6.369999885559082</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="E26" t="n">
         <v>6.409999847412109</v>
@@ -7822,67 +7816,67 @@
         <v>6.349999904632568</v>
       </c>
       <c r="H26" t="n">
-        <v>13154500</v>
+        <v>18094100</v>
       </c>
       <c r="I26" t="n">
-        <v>0.003149603342816221</v>
+        <v>-0.01102357415362343</v>
       </c>
       <c r="J26" t="n">
-        <v>6.557777775658502</v>
+        <v>6.547777811686198</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.863437837073761</v>
+        <v>-4.089595120346485</v>
       </c>
       <c r="M26" t="n">
-        <v>6.475999975204468</v>
+        <v>6.467000007629395</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.63681423797472</v>
+        <v>-2.891600395862584</v>
       </c>
       <c r="P26" t="n">
-        <v>5.425384594843938</v>
+        <v>5.421923068853525</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>17.41102910221088</v>
+        <v>15.82606632477112</v>
       </c>
       <c r="S26" t="n">
-        <v>5.245799980163574</v>
+        <v>5.24399998664856</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>21.43047599310969</v>
+        <v>19.75591582375074</v>
       </c>
       <c r="V26" t="n">
-        <v>6.152999992370606</v>
+        <v>6.152399994532267</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.526733194499347</v>
+        <v>2.07399088793776</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.983900003433227</v>
+        <v>6.983450005054474</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-8.790219183727674</v>
+        <v>-10.0730984647557</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6654986684029315</v>
+        <v>0.6684746223091828</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8034,13 +8028,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>-4.22</v>
+        <v>-4.16</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="CC26" t="n">
         <v>2</v>
@@ -8071,13 +8065,13 @@
         <v>10</v>
       </c>
       <c r="CM26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN26" t="n">
         <v>-1</v>
       </c>
       <c r="CO26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
@@ -8090,13 +8084,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31.18000030517578</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="D27" t="n">
-        <v>31.18000030517578</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="E27" t="n">
-        <v>31.23999977111816</v>
+        <v>31.3700008392334</v>
       </c>
       <c r="F27" t="n">
         <v>30.69000053405762</v>
@@ -8105,67 +8099,67 @@
         <v>31.09000015258789</v>
       </c>
       <c r="H27" t="n">
-        <v>1078700</v>
+        <v>1991500</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01233769732234258</v>
+        <v>0.01623376663588894</v>
       </c>
       <c r="J27" t="n">
-        <v>32.40111117892795</v>
+        <v>32.41444439358182</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.768731470377214</v>
+        <v>-3.438112783885738</v>
       </c>
       <c r="M27" t="n">
-        <v>32.39099998474121</v>
+        <v>32.40299987792969</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.738691859269277</v>
+        <v>-3.404007792563724</v>
       </c>
       <c r="P27" t="n">
-        <v>31.91692315615141</v>
+        <v>31.92153849968543</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.30887810635843</v>
+        <v>-1.94708429429556</v>
       </c>
       <c r="S27" t="n">
-        <v>31.61480010986328</v>
+        <v>31.61720008850098</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.375304614220384</v>
+        <v>-1.003254084968117</v>
       </c>
       <c r="V27" t="n">
-        <v>33.35773340861002</v>
+        <v>33.35853340148926</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.528420491759622</v>
+        <v>-6.170937252105971</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.64565000534058</v>
+        <v>33.64625</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-7.328286716926032</v>
+        <v>-6.973290524024089</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4229780360026981</v>
+        <v>0.4241105827909596</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8313,13 +8307,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>9.01</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB27" t="n">
-        <v>6.22</v>
+        <v>6.25</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8351,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="CL27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM27" t="n">
         <v>2</v>
@@ -8360,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="CO27" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -8373,13 +8367,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20.26000022888184</v>
+        <v>20.28000068664551</v>
       </c>
       <c r="D28" t="n">
-        <v>20.26000022888184</v>
+        <v>20.28000068664551</v>
       </c>
       <c r="E28" t="n">
-        <v>20.29999923706055</v>
+        <v>20.30999946594238</v>
       </c>
       <c r="F28" t="n">
         <v>20</v>
@@ -8388,67 +8382,67 @@
         <v>20.06999969482422</v>
       </c>
       <c r="H28" t="n">
-        <v>3706000</v>
+        <v>4898000</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01655794875328498</v>
+        <v>0.01756148399951774</v>
       </c>
       <c r="J28" t="n">
-        <v>19.9944445292155</v>
+        <v>19.99666680230035</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.328147422541872</v>
+        <v>1.416905563043975</v>
       </c>
       <c r="M28" t="n">
-        <v>19.925</v>
+        <v>19.92700004577637</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.681306042066927</v>
+        <v>1.771469062368778</v>
       </c>
       <c r="P28" t="n">
-        <v>19.09576922196608</v>
+        <v>19.09653847034161</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>6.096800780230021</v>
+        <v>6.197260399532122</v>
       </c>
       <c r="S28" t="n">
-        <v>20.06340003967285</v>
+        <v>20.06380004882812</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.9798946779719819</v>
+        <v>1.077565751708193</v>
       </c>
       <c r="V28" t="n">
-        <v>18.88426675160726</v>
+        <v>18.88440008799235</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>7.28507754825845</v>
+        <v>7.390229989569804</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.30115008831024</v>
+        <v>18.30125009059906</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>10.70342645745963</v>
+        <v>10.81210620176645</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2439418934832132</v>
+        <v>0.2445219992852302</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8608,13 +8602,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8668,13 +8662,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.67000007629395</v>
+        <v>25.72999954223633</v>
       </c>
       <c r="D29" t="n">
-        <v>25.67000007629395</v>
+        <v>25.72999954223633</v>
       </c>
       <c r="E29" t="n">
-        <v>25.72999954223633</v>
+        <v>25.92000007629395</v>
       </c>
       <c r="F29" t="n">
         <v>25.27000045776367</v>
@@ -8683,88 +8677,90 @@
         <v>25.6299991607666</v>
       </c>
       <c r="H29" t="n">
-        <v>2818300</v>
+        <v>4669000</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01342282485637458</v>
+        <v>0.01579153650750387</v>
       </c>
       <c r="J29" t="n">
-        <v>25.57888899909126</v>
+        <v>25.58555560641819</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3561963821256158</v>
+        <v>0.5645526641676991</v>
       </c>
       <c r="M29" t="n">
-        <v>25.48700008392334</v>
+        <v>25.49300003051758</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7180130724213265</v>
+        <v>0.9296650509357028</v>
       </c>
       <c r="P29" t="n">
-        <v>23.59500004695012</v>
+        <v>23.59730771871714</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>8.794236173828871</v>
+        <v>9.037860797261898</v>
       </c>
       <c r="S29" t="n">
-        <v>22.65300003051758</v>
+        <v>22.65420001983643</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>13.3183244678936</v>
+        <v>13.57717120757597</v>
       </c>
       <c r="V29" t="n">
-        <v>24.4938666788737</v>
+        <v>24.49426667531331</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.801746546757681</v>
+        <v>5.044988214194859</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.87364999771118</v>
+        <v>25.87394999504089</v>
       </c>
       <c r="Z29" t="n">
         <v>-1</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.7870939022335587</v>
+        <v>-0.5563528291279608</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.3870166514107396</v>
+        <v>0.3874607871305794</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AI29" t="n">
         <v>39.1</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AJ29" t="n">
         <v>1</v>
@@ -8891,13 +8887,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>5.93</v>
+        <v>5.94</v>
       </c>
       <c r="CA29" t="n">
         <v>0.42</v>
       </c>
       <c r="CB29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CC29" t="n">
         <v>8</v>
@@ -8928,13 +8924,13 @@
         <v>9</v>
       </c>
       <c r="CM29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -8947,13 +8943,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.27000045776367</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="D30" t="n">
-        <v>10.27000045776367</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="E30" t="n">
-        <v>10.27999973297119</v>
+        <v>10.34000015258789</v>
       </c>
       <c r="F30" t="n">
         <v>10.10000038146973</v>
@@ -8962,67 +8958,67 @@
         <v>10.18000030517578</v>
       </c>
       <c r="H30" t="n">
-        <v>3930900</v>
+        <v>8814300</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01382036937227427</v>
+        <v>0.01875612815763406</v>
       </c>
       <c r="J30" t="n">
-        <v>10.951111263699</v>
+        <v>10.95666673448351</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.219558814940465</v>
+        <v>-5.810773067100143</v>
       </c>
       <c r="M30" t="n">
-        <v>10.96600017547607</v>
+        <v>10.97100009918213</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.34688771270411</v>
+        <v>-5.933829172113867</v>
       </c>
       <c r="P30" t="n">
-        <v>10.83846161915706</v>
+        <v>10.84038466673631</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-5.244850988710667</v>
+        <v>-4.800429024524288</v>
       </c>
       <c r="S30" t="n">
-        <v>11.41520002365112</v>
+        <v>11.41620000839233</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-10.03223389441021</v>
+        <v>-9.602147060863254</v>
       </c>
       <c r="V30" t="n">
-        <v>13.14206669489543</v>
+        <v>13.1424000231425</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.8539922510613</v>
+        <v>-21.4755320439821</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.64740002155304</v>
+        <v>13.64765001773834</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-24.74756773052387</v>
+        <v>-24.38258834736425</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3862247614156276</v>
+        <v>0.3884832620112088</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9170,13 +9166,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.38</v>
+        <v>6.41</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CC30" t="n">
         <v>9</v>
@@ -9226,10 +9222,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.68000030517578</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="D31" t="n">
-        <v>30.68000030517578</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="E31" t="n">
         <v>30.82999992370605</v>
@@ -9241,67 +9237,67 @@
         <v>30.68000030517578</v>
       </c>
       <c r="H31" t="n">
-        <v>1241000</v>
+        <v>1710300</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00722262729204326</v>
+        <v>0.005581092626513184</v>
       </c>
       <c r="J31" t="n">
-        <v>30.5733331044515</v>
+        <v>30.56777742173936</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3488896691762869</v>
+        <v>0.2035533632974755</v>
       </c>
       <c r="M31" t="n">
-        <v>30.41799983978272</v>
+        <v>30.4129997253418</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.861333640519003</v>
+        <v>0.7135088198616176</v>
       </c>
       <c r="P31" t="n">
-        <v>29.19384611569918</v>
+        <v>29.19192299476037</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>5.090641992106041</v>
+        <v>4.926281034190013</v>
       </c>
       <c r="S31" t="n">
-        <v>29.90779991149902</v>
+        <v>29.90679988861084</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.581936471294437</v>
+        <v>2.418176718503307</v>
       </c>
       <c r="V31" t="n">
-        <v>32.40200003306071</v>
+        <v>32.40166669209798</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-5.314485914844519</v>
+        <v>-5.467828393418571</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.16251432418823</v>
+        <v>32.16226431846619</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-4.609446898551414</v>
+        <v>-4.764170652063894</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2155723587544692</v>
+        <v>0.2151945571366529</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9449,13 +9445,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.64</v>
+        <v>13.61</v>
       </c>
       <c r="CA31" t="n">
         <v>0.71</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CC31" t="n">
         <v>2</v>
@@ -9505,13 +9501,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>96.98000335693359</v>
+        <v>96.19999694824219</v>
       </c>
       <c r="D32" t="n">
-        <v>96.98000335693359</v>
+        <v>96.19999694824219</v>
       </c>
       <c r="E32" t="n">
-        <v>97.34999847412109</v>
+        <v>97.52999877929688</v>
       </c>
       <c r="F32" t="n">
         <v>93.80000305175781</v>
@@ -9520,87 +9516,85 @@
         <v>96.68000030517578</v>
       </c>
       <c r="H32" t="n">
-        <v>3344800</v>
+        <v>5606300</v>
       </c>
       <c r="I32" t="n">
-        <v>0.004765921362060332</v>
+        <v>-0.003315372005322281</v>
       </c>
       <c r="J32" t="n">
-        <v>95.24111175537109</v>
+        <v>95.15444437662761</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.825778352975217</v>
+        <v>1.0987953095246</v>
       </c>
       <c r="M32" t="n">
-        <v>94.93500061035157</v>
+        <v>94.85699996948242</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>2.154108319833986</v>
+        <v>1.415812200672426</v>
       </c>
       <c r="P32" t="n">
-        <v>96.33846165583684</v>
+        <v>96.22615344707782</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.6659247927256963</v>
+        <v>-0.02718231779889042</v>
       </c>
       <c r="S32" t="n">
-        <v>91.185</v>
+        <v>91.00199981689452</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>6.355215613240765</v>
+        <v>5.711959233650439</v>
       </c>
       <c r="V32" t="n">
-        <v>83.91299992879232</v>
+        <v>83.88839986165364</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>15.57208470586178</v>
+        <v>14.67616155140935</v>
       </c>
       <c r="Y32" t="n">
-        <v>85.93434989929199</v>
+        <v>85.86974983215332</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.85359518118914</v>
+        <v>12.03013533436519</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2609642309555737</v>
+        <v>0.2568304827548327</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AE32" t="n">
         <v>92.3</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AF32" t="n">
         <v>93.7</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AG32" t="n">
         <v>96.8</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
         <v>105.5</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
@@ -9611,7 +9605,7 @@
         <v>2</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -9732,13 +9726,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>42.35</v>
+        <v>42.01</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC32" t="n">
         <v>8</v>
@@ -9770,16 +9764,16 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
@@ -9792,13 +9786,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.20999908447266</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="D33" t="n">
-        <v>27.20999908447266</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="E33" t="n">
-        <v>27.23999977111816</v>
+        <v>27.26000022888184</v>
       </c>
       <c r="F33" t="n">
         <v>26.82999992370605</v>
@@ -9807,67 +9801,67 @@
         <v>27.06999969482422</v>
       </c>
       <c r="H33" t="n">
-        <v>3020300</v>
+        <v>4808700</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01002221770833689</v>
+        <v>0.005567914460159029</v>
       </c>
       <c r="J33" t="n">
-        <v>27.43000009324815</v>
+        <v>27.41666687859429</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.8020452352446414</v>
+        <v>-1.191489568928774</v>
       </c>
       <c r="M33" t="n">
-        <v>27.33900012969971</v>
+        <v>27.32700023651123</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.4718572172173523</v>
+        <v>-0.8672744240938992</v>
       </c>
       <c r="P33" t="n">
-        <v>26.09807696709266</v>
+        <v>26.09346162355863</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>4.260551912625714</v>
+        <v>3.81911201896466</v>
       </c>
       <c r="S33" t="n">
-        <v>26.14120002746582</v>
+        <v>26.13880004882812</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4.088561565206946</v>
+        <v>3.639035081881703</v>
       </c>
       <c r="V33" t="n">
-        <v>25.05439997355143</v>
+        <v>25.0535999806722</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>8.603674856299778</v>
+        <v>8.128173889128462</v>
       </c>
       <c r="Y33" t="n">
-        <v>23.94770000457764</v>
+        <v>23.94710000991821</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>13.62259874339258</v>
+        <v>13.12434550057409</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2585479996893745</v>
+        <v>0.2574719733044071</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10019,13 +10013,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>40.61</v>
+        <v>40.43</v>
       </c>
       <c r="CA33" t="n">
         <v>0.35</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CC33" t="n">
         <v>10</v>
@@ -10075,13 +10069,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>51.61999893188477</v>
+        <v>51.54000091552734</v>
       </c>
       <c r="D34" t="n">
-        <v>51.61999893188477</v>
+        <v>51.54000091552734</v>
       </c>
       <c r="E34" t="n">
-        <v>51.75</v>
+        <v>51.84999847412109</v>
       </c>
       <c r="F34" t="n">
         <v>50.93999862670898</v>
@@ -10090,91 +10084,91 @@
         <v>51.75</v>
       </c>
       <c r="H34" t="n">
-        <v>920500</v>
+        <v>1906400</v>
       </c>
       <c r="I34" t="n">
-        <v>0.005258042176958355</v>
+        <v>0.003700145025359758</v>
       </c>
       <c r="J34" t="n">
-        <v>51.36555565728082</v>
+        <v>51.35666698879666</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.495357776915014</v>
+        <v>0.3569817464413656</v>
       </c>
       <c r="M34" t="n">
-        <v>51.10699996948242</v>
+        <v>51.09900016784668</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.003774361063396</v>
+        <v>0.8630320480480843</v>
       </c>
       <c r="P34" t="n">
-        <v>47.63423054034893</v>
+        <v>47.63115369356596</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>8.367445734553558</v>
+        <v>8.206492849425558</v>
       </c>
       <c r="S34" t="n">
-        <v>48.65819984436035</v>
+        <v>48.65659988403321</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>6.086947517577953</v>
+        <v>5.926022447861865</v>
       </c>
       <c r="V34" t="n">
-        <v>50.28799997965495</v>
+        <v>50.2874666595459</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>2.648741156476108</v>
+        <v>2.490748369690801</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.90320903778076</v>
+        <v>49.90280904769897</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.440239469979285</v>
+        <v>3.280760941259802</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3082171060633455</v>
+        <v>0.3080683426964306</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AE34" t="n">
         <v>50.1</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AF34" t="n">
         <v>50.5</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AG34" t="n">
         <v>51.6</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AH34" t="n">
         <v>51.7</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>51.8</v>
       </c>
-      <c r="AI34" t="n">
-        <v>59.2</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -10298,7 +10292,7 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>13.66</v>
+        <v>13.63</v>
       </c>
       <c r="CA34" t="n">
         <v>0.26</v>
@@ -10354,10 +10348,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.81999969482422</v>
+        <v>39.72999954223633</v>
       </c>
       <c r="D35" t="n">
-        <v>39.81999969482422</v>
+        <v>39.72999954223633</v>
       </c>
       <c r="E35" t="n">
         <v>40.09000015258789</v>
@@ -10369,90 +10363,88 @@
         <v>39.68999862670898</v>
       </c>
       <c r="H35" t="n">
-        <v>2131000</v>
+        <v>3532400</v>
       </c>
       <c r="I35" t="n">
-        <v>0.008611959385261825</v>
+        <v>0.006332320235529432</v>
       </c>
       <c r="J35" t="n">
-        <v>39.28555552164713</v>
+        <v>39.27555550469292</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.360408847680915</v>
+        <v>1.15706584338216</v>
       </c>
       <c r="M35" t="n">
-        <v>39.06599998474121</v>
+        <v>39.05699996948242</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.930066324623746</v>
+        <v>1.723121523106649</v>
       </c>
       <c r="P35" t="n">
-        <v>37.04615416893592</v>
+        <v>37.04269262460562</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>7.48753976793152</v>
+        <v>7.25462089072235</v>
       </c>
       <c r="S35" t="n">
-        <v>38.05680015563965</v>
+        <v>38.05500015258789</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>4.633073542635402</v>
+        <v>4.401522488325433</v>
       </c>
       <c r="V35" t="n">
-        <v>39.7794667561849</v>
+        <v>39.77886675516764</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>0.1018941226330575</v>
+        <v>-0.1228471721733116</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.65680006027222</v>
+        <v>39.65635005950928</v>
       </c>
       <c r="Z35" t="n">
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.4115300132737956</v>
+        <v>0.1857192671956165</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2562945391560958</v>
+        <v>0.255784188105852</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
+        <v>39</v>
+      </c>
+      <c r="AE35" t="n">
         <v>39.2</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AF35" t="n">
         <v>39.5</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
         <v>39.8</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>41.2</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>46.3</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
@@ -10579,7 +10571,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.37</v>
+        <v>32.3</v>
       </c>
       <c r="CA35" t="n">
         <v>0.92</v>
@@ -10635,10 +10627,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.44000053405762</v>
+        <v>21.3799991607666</v>
       </c>
       <c r="D36" t="n">
-        <v>21.44000053405762</v>
+        <v>21.3799991607666</v>
       </c>
       <c r="E36" t="n">
         <v>21.52000045776367</v>
@@ -10650,67 +10642,67 @@
         <v>21.40999984741211</v>
       </c>
       <c r="H36" t="n">
-        <v>1837400</v>
+        <v>2769700</v>
       </c>
       <c r="I36" t="n">
-        <v>0.001869201693476041</v>
+        <v>-0.0009346008467380207</v>
       </c>
       <c r="J36" t="n">
-        <v>20.65888892279731</v>
+        <v>20.65222210354275</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>3.780995261552242</v>
+        <v>3.523964896247193</v>
       </c>
       <c r="M36" t="n">
-        <v>20.51399993896484</v>
+        <v>20.50799980163574</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>4.513993359890301</v>
+        <v>4.251996135972798</v>
       </c>
       <c r="P36" t="n">
-        <v>19.29961527310885</v>
+        <v>19.29730752798227</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>11.09030014671369</v>
+        <v>10.79265399986137</v>
       </c>
       <c r="S36" t="n">
-        <v>18.04979991912842</v>
+        <v>18.0485998916626</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>18.78248307526339</v>
+        <v>18.45793739736519</v>
       </c>
       <c r="V36" t="n">
-        <v>16.69126661936442</v>
+        <v>16.69086661020915</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>28.45041076261966</v>
+        <v>28.09400290629184</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.41174999237061</v>
+        <v>16.41144998550415</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>30.63811320562715</v>
+        <v>30.27489453796622</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3718665269867579</v>
+        <v>0.3723234044701671</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10862,7 +10854,7 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="CA36" t="n">
         <v>0.27</v>
@@ -10918,13 +10910,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.84000015258789</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="D37" t="n">
-        <v>25.84000015258789</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="E37" t="n">
-        <v>25.84000015258789</v>
+        <v>25.93000030517578</v>
       </c>
       <c r="F37" t="n">
         <v>24.77000045776367</v>
@@ -10933,67 +10925,67 @@
         <v>24.89999961853027</v>
       </c>
       <c r="H37" t="n">
-        <v>6953600</v>
+        <v>8072100</v>
       </c>
       <c r="I37" t="n">
-        <v>0.03112532734510087</v>
+        <v>0.03232248166612472</v>
       </c>
       <c r="J37" t="n">
-        <v>25.55777782864041</v>
+        <v>25.56111123826769</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.104252200014121</v>
+        <v>1.208435729129307</v>
       </c>
       <c r="M37" t="n">
-        <v>25.41700000762939</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.664241038798935</v>
+        <v>1.770262634102478</v>
       </c>
       <c r="P37" t="n">
-        <v>24.34999994131235</v>
+        <v>24.35115381387564</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>6.119097391649666</v>
+        <v>6.23726923564624</v>
       </c>
       <c r="S37" t="n">
-        <v>24.26479991912842</v>
+        <v>24.26539993286133</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>6.491709137142777</v>
+        <v>6.612711559717775</v>
       </c>
       <c r="V37" t="n">
-        <v>22.40319998423259</v>
+        <v>22.40339998881022</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>15.34066638147288</v>
+        <v>15.47354799786922</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.05599999427795</v>
+        <v>22.05614999771118</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>17.1563300657038</v>
+        <v>17.29155288623803</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.4006123075556452</v>
+        <v>0.4014196889373084</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11145,7 +11137,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>31.13</v>
+        <v>31.17</v>
       </c>
       <c r="CA37" t="n">
         <v>0.16</v>
@@ -11201,13 +11193,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.56999969482422</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="D38" t="n">
-        <v>11.56999969482422</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="E38" t="n">
-        <v>11.56999969482422</v>
+        <v>11.64999961853027</v>
       </c>
       <c r="F38" t="n">
         <v>11.10000038146973</v>
@@ -11216,67 +11208,67 @@
         <v>11.25</v>
       </c>
       <c r="H38" t="n">
-        <v>4489800</v>
+        <v>6940800</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03211415302874121</v>
+        <v>0.03568239225415692</v>
       </c>
       <c r="J38" t="n">
-        <v>11.30444452497694</v>
+        <v>11.30888896518283</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>2.349121792411276</v>
+        <v>2.662601891498396</v>
       </c>
       <c r="M38" t="n">
-        <v>11.23000011444092</v>
+        <v>11.23400011062622</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>3.027600863031941</v>
+        <v>3.346978301125061</v>
       </c>
       <c r="P38" t="n">
-        <v>10.7676923091595</v>
+        <v>10.76923076923077</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>7.4510615889557</v>
+        <v>7.807139669145849</v>
       </c>
       <c r="S38" t="n">
-        <v>10.67680000305176</v>
+        <v>10.67760000228882</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>8.365799598354908</v>
+        <v>8.732296154459446</v>
       </c>
       <c r="V38" t="n">
-        <v>9.887133334477742</v>
+        <v>9.887400000890096</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>17.02077137442962</v>
+        <v>17.42217019269045</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.718994085788728</v>
+        <v>9.719194085597993</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>19.04523855757935</v>
+        <v>19.45434523095973</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3931795260017396</v>
+        <v>0.3957309517086102</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11428,10 +11420,10 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>26.91</v>
+        <v>27</v>
       </c>
       <c r="CA38" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="CB38" t="n">
         <v>0.8100000000000001</v>
@@ -11488,10 +11480,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.590000152587891</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="D39" t="n">
-        <v>6.590000152587891</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="E39" t="n">
         <v>6.75</v>
@@ -11503,67 +11495,67 @@
         <v>6.75</v>
       </c>
       <c r="H39" t="n">
-        <v>4401500</v>
+        <v>7385000</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0193451847712115</v>
+        <v>-0.01636899704041639</v>
       </c>
       <c r="J39" t="n">
-        <v>7.001111136542426</v>
+        <v>7.003333356645372</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-5.872081958658452</v>
+        <v>-5.616371563374736</v>
       </c>
       <c r="M39" t="n">
-        <v>6.96100001335144</v>
+        <v>6.963000011444092</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-5.32969199902254</v>
+        <v>-5.069652123359357</v>
       </c>
       <c r="P39" t="n">
-        <v>7.068461564870981</v>
+        <v>7.069230794906616</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-6.768961080031335</v>
+        <v>-6.496189963455258</v>
       </c>
       <c r="S39" t="n">
-        <v>8.889400005340576</v>
+        <v>8.889800004959106</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-25.8667609891697</v>
+        <v>-25.64511991465425</v>
       </c>
       <c r="V39" t="n">
-        <v>10.35159998575846</v>
+        <v>10.35173331896464</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-36.33834226926959</v>
+        <v>-36.1459580744346</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.31114999294281</v>
+        <v>11.31124999284744</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-41.738902262816</v>
+        <v>-41.56260238528746</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.118566242606855</v>
+        <v>1.118537061685585</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11715,7 +11707,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>-7.75</v>
+        <v>-7.78</v>
       </c>
       <c r="CA39" t="n">
         <v>1.5</v>
@@ -11775,13 +11767,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.59000015258789</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="D40" t="n">
-        <v>23.59000015258789</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="E40" t="n">
-        <v>23.65999984741211</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="F40" t="n">
         <v>23.20000076293945</v>
@@ -11790,67 +11782,67 @@
         <v>23.6299991607666</v>
       </c>
       <c r="H40" t="n">
-        <v>1810900</v>
+        <v>2761500</v>
       </c>
       <c r="I40" t="n">
-        <v>0.002549913480301536</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>22.97111108567979</v>
+        <v>22.96444447835286</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>2.694206059949412</v>
+        <v>2.462747177819863</v>
       </c>
       <c r="M40" t="n">
-        <v>22.84899997711182</v>
+        <v>22.84300003051758</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.243031100784915</v>
+        <v>3.007488750208447</v>
       </c>
       <c r="P40" t="n">
-        <v>21.92884613917424</v>
+        <v>21.92653846740723</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>7.575200276708236</v>
+        <v>7.312883525239303</v>
       </c>
       <c r="S40" t="n">
-        <v>21.47220008850098</v>
+        <v>21.47100009918213</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.862985885740985</v>
+        <v>9.589681793824834</v>
       </c>
       <c r="V40" t="n">
-        <v>22.07386669158936</v>
+        <v>22.07346669514974</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6.868454368152076</v>
+        <v>6.598573806332901</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.63775002479553</v>
+        <v>22.63745002746582</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.206469842406338</v>
+        <v>3.942805652124081</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2596006005420882</v>
+        <v>0.2597608384258145</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -11998,13 +11990,13 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>9.869999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="CA40" t="n">
         <v>0.38</v>
       </c>
       <c r="CB40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CC40" t="n">
         <v>4</v>
@@ -12054,10 +12046,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.96999931335449</v>
+        <v>25.94000053405762</v>
       </c>
       <c r="D41" t="n">
-        <v>25.96999931335449</v>
+        <v>25.94000053405762</v>
       </c>
       <c r="E41" t="n">
         <v>26.07999992370605</v>
@@ -12069,67 +12061,67 @@
         <v>25.80999946594238</v>
       </c>
       <c r="H41" t="n">
-        <v>472000</v>
+        <v>914200</v>
       </c>
       <c r="I41" t="n">
-        <v>0.008152138299952538</v>
+        <v>0.006987589424551688</v>
       </c>
       <c r="J41" t="n">
-        <v>26.19555558098687</v>
+        <v>26.19222238328722</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.8610478481169905</v>
+        <v>-0.9629646753096345</v>
       </c>
       <c r="M41" t="n">
-        <v>26.08299999237061</v>
+        <v>26.08000011444092</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.4332349769933183</v>
+        <v>-0.5368082046356282</v>
       </c>
       <c r="P41" t="n">
-        <v>24.69653841165396</v>
+        <v>24.69538461245023</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>5.156434802618354</v>
+        <v>5.039872596193169</v>
       </c>
       <c r="S41" t="n">
-        <v>24.92580001831055</v>
+        <v>24.92520004272461</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>4.189230814163937</v>
+        <v>4.071383537919561</v>
       </c>
       <c r="V41" t="n">
-        <v>26.38713330586751</v>
+        <v>26.38693331400554</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.580823455423496</v>
+        <v>-1.693765526404303</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.42589995384216</v>
+        <v>26.42574995994568</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.725203838976105</v>
+        <v>-1.838167040194992</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3217149941390518</v>
+        <v>0.3215098518237812</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12277,7 +12269,7 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
       <c r="CA41" t="n">
         <v>0.04</v>
@@ -12333,13 +12325,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.43000030517578</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="D42" t="n">
-        <v>27.43000030517578</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="E42" t="n">
-        <v>27.52000045776367</v>
+        <v>27.54000091552734</v>
       </c>
       <c r="F42" t="n">
         <v>27.14999961853027</v>
@@ -12348,67 +12340,67 @@
         <v>27.29999923706055</v>
       </c>
       <c r="H42" t="n">
-        <v>1007900</v>
+        <v>1572100</v>
       </c>
       <c r="I42" t="n">
-        <v>0.005498519602446406</v>
+        <v>0.007331336164105196</v>
       </c>
       <c r="J42" t="n">
-        <v>27.67555554707845</v>
+        <v>27.68111101786296</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.8872640026501292</v>
+        <v>-0.7265296378344392</v>
       </c>
       <c r="M42" t="n">
-        <v>27.60399990081787</v>
+        <v>27.60899982452393</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.6303419659008735</v>
+        <v>-0.467239969240079</v>
       </c>
       <c r="P42" t="n">
-        <v>26.59499997359056</v>
+        <v>26.59692302116981</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>3.139689161174652</v>
+        <v>3.320220614856975</v>
       </c>
       <c r="S42" t="n">
-        <v>27.13320007324219</v>
+        <v>27.1342000579834</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.0938637209486</v>
+        <v>1.274404565139144</v>
       </c>
       <c r="V42" t="n">
-        <v>28.17980002085368</v>
+        <v>28.18013334910075</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.660770179784917</v>
+        <v>-2.484494300261228</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98075001716614</v>
+        <v>27.98100001335144</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-1.968316473477202</v>
+        <v>-1.790502379743593</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1786499065341088</v>
+        <v>0.1791482873269455</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12556,13 +12548,13 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.71</v>
+        <v>7.72</v>
       </c>
       <c r="CA42" t="n">
         <v>0.83</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="CC42" t="n">
         <v>7</v>
@@ -12593,13 +12585,13 @@
         <v>4</v>
       </c>
       <c r="CM42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN42" t="n">
         <v>1</v>
       </c>
       <c r="CO42" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
@@ -12612,13 +12604,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.14999961853027</v>
+        <v>14.17000007629395</v>
       </c>
       <c r="D43" t="n">
-        <v>14.14999961853027</v>
+        <v>14.17000007629395</v>
       </c>
       <c r="E43" t="n">
-        <v>14.15999984741211</v>
+        <v>14.18000030517578</v>
       </c>
       <c r="F43" t="n">
         <v>13.96000003814697</v>
@@ -12627,67 +12619,67 @@
         <v>14.11999988555908</v>
       </c>
       <c r="H43" t="n">
-        <v>9172500</v>
+        <v>13562000</v>
       </c>
       <c r="I43" t="n">
-        <v>0.007117396899492867</v>
+        <v>0.008540917005696258</v>
       </c>
       <c r="J43" t="n">
-        <v>13.99999978807237</v>
+        <v>14.00222206115723</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.071427376632498</v>
+        <v>1.198224213299275</v>
       </c>
       <c r="M43" t="n">
-        <v>13.91899976730347</v>
+        <v>13.92099981307983</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.659600941796399</v>
+        <v>1.788666522214561</v>
       </c>
       <c r="P43" t="n">
-        <v>13.12999985768245</v>
+        <v>13.13076910605797</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>7.768467417393135</v>
+        <v>7.9144714360754</v>
       </c>
       <c r="S43" t="n">
-        <v>13.3965998840332</v>
+        <v>13.39699989318848</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>5.623813064649442</v>
+        <v>5.769949908699259</v>
       </c>
       <c r="V43" t="n">
-        <v>13.55186663309733</v>
+        <v>13.55199996948242</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>4.413657554540414</v>
+        <v>4.560213313187649</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.24397738933563</v>
+        <v>13.24407739162445</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.841013107770714</v>
+        <v>6.991220734296279</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2478601415773774</v>
+        <v>0.2482114870251337</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12839,7 +12831,7 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>9.369999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="CA43" t="n">
         <v>0.03</v>
@@ -12899,13 +12891,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.72999954223633</v>
+        <v>42.79000091552734</v>
       </c>
       <c r="D44" t="n">
-        <v>42.72999954223633</v>
+        <v>42.79000091552734</v>
       </c>
       <c r="E44" t="n">
-        <v>42.75</v>
+        <v>42.79999923706055</v>
       </c>
       <c r="F44" t="n">
         <v>42.09999847412109</v>
@@ -12914,67 +12906,67 @@
         <v>42.65000152587891</v>
       </c>
       <c r="H44" t="n">
-        <v>9462800</v>
+        <v>13953700</v>
       </c>
       <c r="I44" t="n">
-        <v>0.008972870880914918</v>
+        <v>0.01038966841226974</v>
       </c>
       <c r="J44" t="n">
-        <v>42.15888807508681</v>
+        <v>42.16555489434136</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.354664444973849</v>
+        <v>1.480938701626769</v>
       </c>
       <c r="M44" t="n">
-        <v>41.93099937438965</v>
+        <v>41.93699951171875</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.905511864176284</v>
+        <v>2.034006757136334</v>
       </c>
       <c r="P44" t="n">
-        <v>40.03653790400578</v>
+        <v>40.03884564913236</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>6.727508868745255</v>
+        <v>6.87121524557389</v>
       </c>
       <c r="S44" t="n">
-        <v>41.25159965515137</v>
+        <v>41.25279968261719</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>3.583860745871327</v>
+        <v>3.72629553566492</v>
       </c>
       <c r="V44" t="n">
-        <v>42.39026652018229</v>
+        <v>42.39066652933757</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.8014411088740968</v>
+        <v>0.94203375149435</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.01481777191162</v>
+        <v>42.01511777877808</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.702213191087143</v>
+        <v>1.844296000380754</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2687054448620637</v>
+        <v>0.2691568555097344</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13142,7 +13134,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.15</v>
+        <v>10.16</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
@@ -13183,13 +13175,13 @@
         <v>5</v>
       </c>
       <c r="CM44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -13202,13 +13194,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.45999908447266</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="D45" t="n">
-        <v>19.45999908447266</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="E45" t="n">
-        <v>19.47999954223633</v>
+        <v>19.48999977111816</v>
       </c>
       <c r="F45" t="n">
         <v>19.11000061035156</v>
@@ -13217,67 +13209,67 @@
         <v>19.35000038146973</v>
       </c>
       <c r="H45" t="n">
-        <v>1122600</v>
+        <v>1933900</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01248698125350134</v>
+        <v>0.01196677720093109</v>
       </c>
       <c r="J45" t="n">
-        <v>19.4955554538303</v>
+        <v>19.4944445292155</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.1823819251615809</v>
+        <v>-0.2279817011940857</v>
       </c>
       <c r="M45" t="n">
-        <v>19.45099983215332</v>
+        <v>19.45</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.04626627112740176</v>
+        <v>3.922567886043921e-06</v>
       </c>
       <c r="P45" t="n">
-        <v>18.64346144749568</v>
+        <v>18.64307689666748</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.379753401891243</v>
+        <v>4.328276232214723</v>
       </c>
       <c r="S45" t="n">
-        <v>18.21019996643066</v>
+        <v>18.21</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.863181735213869</v>
+        <v>6.80944954936547</v>
       </c>
       <c r="V45" t="n">
-        <v>18.22353332519531</v>
+        <v>18.22346666971842</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>6.784994639693958</v>
+        <v>6.730520133466909</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.32632568359375</v>
+        <v>18.32627569198608</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>6.186037618516197</v>
+        <v>6.131769977927182</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2007684604288034</v>
+        <v>0.2005432296444223</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13429,7 +13421,7 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.43</v>
+        <v>32.42</v>
       </c>
       <c r="CA45" t="n">
         <v>0.2</v>
@@ -13489,10 +13481,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.34000015258789</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="D46" t="n">
-        <v>11.34000015258789</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="E46" t="n">
         <v>11.35999965667725</v>
@@ -13504,67 +13496,67 @@
         <v>11.31999969482422</v>
       </c>
       <c r="H46" t="n">
-        <v>3074000</v>
+        <v>6490100</v>
       </c>
       <c r="I46" t="n">
-        <v>0.01159679875098441</v>
+        <v>0.0008920810747372609</v>
       </c>
       <c r="J46" t="n">
-        <v>11.37555556827121</v>
+        <v>11.36222224765354</v>
       </c>
       <c r="K46" t="n">
         <v>-1</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.3125598171441781</v>
+        <v>-1.251709194951718</v>
       </c>
       <c r="M46" t="n">
-        <v>11.34400005340576</v>
+        <v>11.33200006484985</v>
       </c>
       <c r="N46" t="n">
         <v>-1</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.03526005640902223</v>
+        <v>-0.9883497809751346</v>
       </c>
       <c r="P46" t="n">
-        <v>11.18038459924551</v>
+        <v>11.1757692190317</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.427639200829907</v>
+        <v>0.3957763186607814</v>
       </c>
       <c r="S46" t="n">
-        <v>12.36719999313354</v>
+        <v>12.36479999542236</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-8.305839972798781</v>
+        <v>-9.258538179488358</v>
       </c>
       <c r="V46" t="n">
-        <v>14.03933338165283</v>
+        <v>14.03853338241577</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-19.2269330436482</v>
+        <v>-20.07711944409641</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.10460003852844</v>
+        <v>14.10400003910065</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-19.60069678252987</v>
+        <v>-20.44809815709373</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.4001263071996147</v>
+        <v>0.3971500568518591</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13716,13 +13708,13 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>7.66</v>
+        <v>7.58</v>
       </c>
       <c r="CA46" t="n">
         <v>-0.13</v>
       </c>
       <c r="CB46" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CC46" t="n">
         <v>5</v>
@@ -13757,13 +13749,13 @@
         <v>1</v>
       </c>
       <c r="CM46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN46" t="n">
         <v>0</v>
       </c>
       <c r="CO46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -13776,13 +13768,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.18000030517578</v>
+        <v>17.34000015258789</v>
       </c>
       <c r="D47" t="n">
-        <v>17.18000030517578</v>
+        <v>17.34000015258789</v>
       </c>
       <c r="E47" t="n">
-        <v>17.29999923706055</v>
+        <v>17.40999984741211</v>
       </c>
       <c r="F47" t="n">
         <v>16.89999961853027</v>
@@ -13791,88 +13783,88 @@
         <v>17.29000091552734</v>
       </c>
       <c r="H47" t="n">
-        <v>1794700</v>
+        <v>2934300</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.001743101736939701</v>
+        <v>0.007553810286516915</v>
       </c>
       <c r="J47" t="n">
-        <v>17.5233334435357</v>
+        <v>17.54111120435927</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.95929124710328</v>
+        <v>-1.146512609311763</v>
       </c>
       <c r="M47" t="n">
-        <v>17.60100002288818</v>
+        <v>17.61700000762939</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.391907943667618</v>
+        <v>-1.572344070622366</v>
       </c>
       <c r="P47" t="n">
-        <v>17.51115384468665</v>
+        <v>17.51730768497174</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.891100623339865</v>
+        <v>-1.012184837833042</v>
       </c>
       <c r="S47" t="n">
-        <v>16.78520000457764</v>
+        <v>16.78840000152588</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>2.352073853695376</v>
+        <v>3.285602862761652</v>
       </c>
       <c r="V47" t="n">
-        <v>17.56486670811971</v>
+        <v>17.56593337376912</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.191114850680965</v>
+        <v>-1.286201059595356</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.02920006275177</v>
+        <v>18.03000006198883</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-4.710135528033939</v>
+        <v>-3.826954559227146</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.462669722649194</v>
+        <v>0.4632525127982288</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AE47" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="AG47" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="AI47" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AJ47" t="n">
         <v>2</v>
@@ -13999,13 +13991,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>63.63</v>
+        <v>64.22</v>
       </c>
       <c r="CA47" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CC47" t="n">
         <v>7</v>
@@ -14037,16 +14029,16 @@
         <v>0</v>
       </c>
       <c r="CL47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN47" t="n">
         <v>0</v>
       </c>
       <c r="CO47" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
@@ -14059,10 +14051,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.670000076293945</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="D48" t="n">
-        <v>5.670000076293945</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="E48" t="n">
         <v>5.690000057220459</v>
@@ -14074,67 +14066,67 @@
         <v>5.630000114440918</v>
       </c>
       <c r="H48" t="n">
-        <v>11355400</v>
+        <v>15268600</v>
       </c>
       <c r="I48" t="n">
-        <v>0.01795330368952963</v>
+        <v>0.007181321475811853</v>
       </c>
       <c r="J48" t="n">
-        <v>5.676666736602783</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.1174396986501197</v>
+        <v>-1.058200034783042</v>
       </c>
       <c r="M48" t="n">
-        <v>5.571000051498413</v>
+        <v>5.565000057220459</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1.777060202483831</v>
+        <v>0.8086266995731429</v>
       </c>
       <c r="P48" t="n">
-        <v>4.796153884667617</v>
+        <v>4.793846194560711</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>18.21972798704076</v>
+        <v>17.02503388364304</v>
       </c>
       <c r="S48" t="n">
-        <v>4.81900004863739</v>
+        <v>4.817800049781799</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>17.65926580343535</v>
+        <v>16.44319140576381</v>
       </c>
       <c r="V48" t="n">
-        <v>6.754933327039083</v>
+        <v>6.754533327420552</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-16.06134654804507</v>
+        <v>-16.94466720979563</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.3960975420475</v>
+        <v>7.395797542333603</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-23.33794891076721</v>
+        <v>-24.14610998472146</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.84803993190223</v>
+        <v>0.847126113020642</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14286,10 +14278,10 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>31.5</v>
+        <v>31.17</v>
       </c>
       <c r="CA48" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="CB48" t="n">
         <v>0.39</v>
@@ -14327,13 +14319,13 @@
         <v>10</v>
       </c>
       <c r="CM48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CN48" t="n">
         <v>-1</v>
       </c>
       <c r="CO48" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49">
@@ -14346,10 +14338,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.46999931335449</v>
+        <v>16.40999984741211</v>
       </c>
       <c r="D49" t="n">
-        <v>16.46999931335449</v>
+        <v>16.40999984741211</v>
       </c>
       <c r="E49" t="n">
         <v>16.52000045776367</v>
@@ -14361,67 +14353,67 @@
         <v>16.52000045776367</v>
       </c>
       <c r="H49" t="n">
-        <v>4186800</v>
+        <v>5770800</v>
       </c>
       <c r="I49" t="n">
-        <v>0.005494515091518437</v>
+        <v>0.001831543845091543</v>
       </c>
       <c r="J49" t="n">
-        <v>16.45888879564073</v>
+        <v>16.4522221883138</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.06750466481493556</v>
+        <v>-0.2566360970476227</v>
       </c>
       <c r="M49" t="n">
-        <v>16.38199987411499</v>
+        <v>16.37599992752075</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.5371715292132939</v>
+        <v>0.2076204203825057</v>
       </c>
       <c r="P49" t="n">
-        <v>15.15499995304988</v>
+        <v>15.15269228128287</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>8.677000094876114</v>
+        <v>8.297585292366255</v>
       </c>
       <c r="S49" t="n">
-        <v>14.94219997406006</v>
+        <v>14.94099998474121</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>10.2247282324338</v>
+        <v>9.832004980731835</v>
       </c>
       <c r="V49" t="n">
-        <v>15.27586668650309</v>
+        <v>15.27546669006348</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>7.817118670631423</v>
+        <v>7.427158726918861</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.41535000801086</v>
+        <v>15.41505001068115</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>6.841552769126615</v>
+        <v>6.454405506576701</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3023453215446327</v>
+        <v>0.3023426117704264</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14573,13 +14565,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="CA49" t="n">
         <v>0.93</v>
       </c>
       <c r="CB49" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CC49" t="n">
         <v>5</v>
@@ -14633,13 +14625,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.699999809265137</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="D50" t="n">
-        <v>5.699999809265137</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="E50" t="n">
-        <v>5.71999979019165</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="F50" t="n">
         <v>5.46999979019165</v>
@@ -14648,67 +14640,67 @@
         <v>5.570000171661377</v>
       </c>
       <c r="H50" t="n">
-        <v>4442500</v>
+        <v>6814100</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02702695736491711</v>
+        <v>0.02162160025857451</v>
       </c>
       <c r="J50" t="n">
-        <v>5.66666661368476</v>
+        <v>5.663333310021295</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.588232868682946</v>
+        <v>0.1177180629798683</v>
       </c>
       <c r="M50" t="n">
-        <v>5.653999948501587</v>
+        <v>5.650999975204468</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8135808486475181</v>
+        <v>0.3362254675782385</v>
       </c>
       <c r="P50" t="n">
-        <v>5.2215384886815</v>
+        <v>5.223461572940533</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>9.163225007740092</v>
+        <v>8.548708497572713</v>
       </c>
       <c r="S50" t="n">
-        <v>4.973000020980835</v>
+        <v>4.991000022888183</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>14.61893796937717</v>
+        <v>13.60448908619398</v>
       </c>
       <c r="V50" t="n">
-        <v>6.466066672007243</v>
+        <v>6.496266670227051</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-11.84749402691047</v>
+        <v>-12.71909907454933</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.903700013160705</v>
+        <v>6.92520001411438</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-17.43558094356538</v>
+        <v>-18.12510736530625</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.5978634560593292</v>
+        <v>0.6045750466241533</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14856,10 +14848,10 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.22</v>
+        <v>-4.2</v>
       </c>
       <c r="CA50" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CB50" t="n">
         <v>0.61</v>
@@ -14916,13 +14908,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30.1200008392334</v>
+        <v>30.25</v>
       </c>
       <c r="D51" t="n">
-        <v>30.1200008392334</v>
+        <v>30.25</v>
       </c>
       <c r="E51" t="n">
-        <v>30.13999938964844</v>
+        <v>30.34000015258789</v>
       </c>
       <c r="F51" t="n">
         <v>29.79000091552734</v>
@@ -14931,67 +14923,67 @@
         <v>30.02000045776367</v>
       </c>
       <c r="H51" t="n">
-        <v>1599500</v>
+        <v>3972800</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00972178733721285</v>
+        <v>0.01407978804452381</v>
       </c>
       <c r="J51" t="n">
-        <v>30.06444464789497</v>
+        <v>30.07888899909126</v>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1847903461683343</v>
+        <v>0.5688740728220197</v>
       </c>
       <c r="M51" t="n">
-        <v>29.89300022125244</v>
+        <v>29.9060001373291</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.7593771662289335</v>
+        <v>1.150270384174555</v>
       </c>
       <c r="P51" t="n">
-        <v>28.1869231737577</v>
+        <v>28.19192314147949</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>6.858065541809169</v>
+        <v>7.300235773885206</v>
       </c>
       <c r="S51" t="n">
-        <v>28.43280010223389</v>
+        <v>28.43540008544922</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>5.933994298602171</v>
+        <v>6.381481917250528</v>
       </c>
       <c r="V51" t="n">
-        <v>30.31073336283366</v>
+        <v>30.31160002390544</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.6292573700448059</v>
+        <v>-0.2032226073742616</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.10780004501343</v>
+        <v>30.10845004081726</v>
       </c>
       <c r="Z51" t="n">
         <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.04052369884790802</v>
+        <v>0.4701336634428014</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2594379537679505</v>
+        <v>0.2609097304165432</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15143,13 +15135,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.66</v>
+        <v>12.71</v>
       </c>
       <c r="CA51" t="n">
         <v>0.29</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CC51" t="n">
         <v>8</v>
@@ -15181,16 +15173,16 @@
         <v>0</v>
       </c>
       <c r="CL51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -15203,82 +15195,82 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.909999847412109</v>
+        <v>7.889999866485596</v>
       </c>
       <c r="D52" t="n">
-        <v>7.909999847412109</v>
+        <v>7.889999866485596</v>
       </c>
       <c r="E52" t="n">
         <v>8.130000114440918</v>
       </c>
       <c r="F52" t="n">
-        <v>7.840000152587891</v>
+        <v>7.820000171661377</v>
       </c>
       <c r="G52" t="n">
         <v>8.060000419616699</v>
       </c>
       <c r="H52" t="n">
-        <v>3575900</v>
+        <v>6241200</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01494394639471308</v>
+        <v>-0.01743460412716524</v>
       </c>
       <c r="J52" t="n">
-        <v>8.64555549621582</v>
+        <v>8.643333276112875</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-8.507905005359868</v>
+        <v>-8.715774176025667</v>
       </c>
       <c r="M52" t="n">
-        <v>8.659999942779541</v>
+        <v>8.657999944686889</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-8.660509241605247</v>
+        <v>-8.870409830304839</v>
       </c>
       <c r="P52" t="n">
-        <v>8.370769133934608</v>
+        <v>8.377692204255323</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-5.504503578465297</v>
+        <v>-5.821320787149613</v>
       </c>
       <c r="S52" t="n">
-        <v>8.414200019836425</v>
+        <v>8.418400030136109</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-5.992253229489041</v>
+        <v>-6.27672909055107</v>
       </c>
       <c r="V52" t="n">
-        <v>9.107666641871134</v>
+        <v>9.114399973551432</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-13.15009476689596</v>
+        <v>-13.43368856555401</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.813049972057343</v>
+        <v>8.809899971485137</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-10.2467378207141</v>
+        <v>-10.44166344654273</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.444912948254892</v>
+        <v>0.4411576138944477</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15430,7 +15422,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>-4.68</v>
+        <v>-4.67</v>
       </c>
       <c r="CA52" t="n">
         <v>0.37</v>
@@ -15490,10 +15482,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>56.22000122070312</v>
+        <v>56.16999816894531</v>
       </c>
       <c r="D53" t="n">
-        <v>56.22000122070312</v>
+        <v>56.16999816894531</v>
       </c>
       <c r="E53" t="n">
         <v>56.65000152587891</v>
@@ -15505,67 +15497,67 @@
         <v>54.63999938964844</v>
       </c>
       <c r="H53" t="n">
-        <v>5293500</v>
+        <v>7717800</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0361224283044641</v>
+        <v>0.03520088290629597</v>
       </c>
       <c r="J53" t="n">
-        <v>53.85555564032661</v>
+        <v>53.84999974568685</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>4.390346645325558</v>
+        <v>4.308260787771466</v>
       </c>
       <c r="M53" t="n">
-        <v>53.70699996948242</v>
+        <v>53.70199966430664</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>4.679094443273031</v>
+        <v>4.595729246706323</v>
       </c>
       <c r="P53" t="n">
-        <v>49.89499987088717</v>
+        <v>49.89307667658879</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>12.67662364201444</v>
+        <v>12.58074648922548</v>
       </c>
       <c r="S53" t="n">
-        <v>48.21639976501465</v>
+        <v>48.21539970397949</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>16.59933444781128</v>
+        <v>16.49804525899073</v>
       </c>
       <c r="V53" t="n">
-        <v>47.98646662394206</v>
+        <v>47.98613327026367</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>17.15803470442035</v>
+        <v>17.05464545890608</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.62529999732971</v>
+        <v>44.62504998207092</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>25.98234908015681</v>
+        <v>25.87100337481488</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.351159149317442</v>
+        <v>0.3504609276345493</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15773,10 +15765,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50.56000137329102</v>
+        <v>50.4900016784668</v>
       </c>
       <c r="D54" t="n">
-        <v>50.56000137329102</v>
+        <v>50.4900016784668</v>
       </c>
       <c r="E54" t="n">
         <v>50.70000076293945</v>
@@ -15788,67 +15780,67 @@
         <v>49.06000137329102</v>
       </c>
       <c r="H54" t="n">
-        <v>28034700</v>
+        <v>40518500</v>
       </c>
       <c r="I54" t="n">
-        <v>0.03352418777044819</v>
+        <v>0.03209328635090047</v>
       </c>
       <c r="J54" t="n">
-        <v>48.5533332824707</v>
+        <v>48.54555553860135</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>4.132915198934001</v>
+        <v>4.005405063949279</v>
       </c>
       <c r="M54" t="n">
-        <v>48.38499984741211</v>
+        <v>48.37799987792969</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>4.495197959570182</v>
+        <v>4.365624469523832</v>
       </c>
       <c r="P54" t="n">
-        <v>44.85230768643893</v>
+        <v>44.84961539048415</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>12.72552959092851</v>
+        <v>12.5762199717311</v>
       </c>
       <c r="S54" t="n">
-        <v>43.14639999389649</v>
+        <v>43.145</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>17.18243325154187</v>
+        <v>17.02399276501749</v>
       </c>
       <c r="V54" t="n">
-        <v>43.32893328348796</v>
+        <v>43.32846661885579</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>16.68877477895058</v>
+        <v>16.52847566152833</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.65205002784729</v>
+        <v>40.65170002937317</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>24.3725749098917</v>
+        <v>24.20145194908183</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3309155173648083</v>
+        <v>0.3298900882277963</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16000,7 +15992,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>6.06</v>
+        <v>6.05</v>
       </c>
       <c r="CA54" t="n">
         <v>0.5</v>
@@ -16056,13 +16048,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.460000038146973</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="D55" t="n">
-        <v>4.460000038146973</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="E55" t="n">
-        <v>4.46999979019165</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="F55" t="n">
         <v>4.400000095367432</v>
@@ -16071,67 +16063,67 @@
         <v>4.449999809265137</v>
       </c>
       <c r="H55" t="n">
-        <v>5835700</v>
+        <v>8109700</v>
       </c>
       <c r="I55" t="n">
-        <v>0.006772056652562197</v>
+        <v>0.00902933711129017</v>
       </c>
       <c r="J55" t="n">
-        <v>4.528888861338298</v>
+        <v>4.529999944898817</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.521097675401298</v>
+        <v>-1.324506742538313</v>
       </c>
       <c r="M55" t="n">
-        <v>4.522999954223633</v>
+        <v>4.523999929428101</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.39287898992416</v>
+        <v>-1.193637048603504</v>
       </c>
       <c r="P55" t="n">
-        <v>4.406538449800932</v>
+        <v>4.406923055648804</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>1.213233220476175</v>
+        <v>1.431310094284374</v>
       </c>
       <c r="S55" t="n">
-        <v>4.82019998550415</v>
+        <v>4.820399980545044</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-7.472717904659793</v>
+        <v>-7.269110276483199</v>
       </c>
       <c r="V55" t="n">
-        <v>5.762133321762085</v>
+        <v>5.762199986775716</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-22.59811099297707</v>
+        <v>-22.42546596004431</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.818418116569519</v>
+        <v>5.818468115329742</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-23.34686251842375</v>
+        <v>-23.17565892619267</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4597819564371163</v>
+        <v>0.4603625756069936</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16283,13 +16275,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="CA55" t="n">
         <v>0.28</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CC55" t="n">
         <v>9</v>
@@ -16343,13 +16335,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>65.86000061035156</v>
+        <v>65.51000213623047</v>
       </c>
       <c r="D56" t="n">
-        <v>65.86000061035156</v>
+        <v>65.51000213623047</v>
       </c>
       <c r="E56" t="n">
-        <v>65.94000244140625</v>
+        <v>66.08000183105469</v>
       </c>
       <c r="F56" t="n">
         <v>63.34000015258789</v>
@@ -16358,67 +16350,67 @@
         <v>63.90000152587891</v>
       </c>
       <c r="H56" t="n">
-        <v>4526200</v>
+        <v>7064700</v>
       </c>
       <c r="I56" t="n">
-        <v>0.03051166902824543</v>
+        <v>0.02503524163101911</v>
       </c>
       <c r="J56" t="n">
-        <v>63.1966675652398</v>
+        <v>63.15777884589301</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>4.214356781332378</v>
+        <v>3.724360377012237</v>
       </c>
       <c r="M56" t="n">
-        <v>63.2760009765625</v>
+        <v>63.24100112915039</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>4.083696178502461</v>
+        <v>3.587863832905394</v>
       </c>
       <c r="P56" t="n">
-        <v>61.81384658813477</v>
+        <v>61.80038510836088</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>6.545708195732088</v>
+        <v>6.002579144717534</v>
       </c>
       <c r="S56" t="n">
-        <v>59.93380020141601</v>
+        <v>59.92680023193359</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>9.887910309407571</v>
+        <v>9.31670284862251</v>
       </c>
       <c r="V56" t="n">
-        <v>60.8389333597819</v>
+        <v>60.83660003662109</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>8.25304944265983</v>
+        <v>7.681892309557377</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.32664999008179</v>
+        <v>56.32489999771119</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.92511559261635</v>
+        <v>16.30735631824029</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.371326221857452</v>
+        <v>0.368283430789936</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16570,13 +16562,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>22.18</v>
+        <v>22.06</v>
       </c>
       <c r="CA56" t="n">
         <v>0.42</v>
       </c>
       <c r="CB56" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CC56" t="n">
         <v>10</v>
@@ -16604,16 +16596,16 @@
         <v>0</v>
       </c>
       <c r="CL56" t="n">
+        <v>8</v>
+      </c>
+      <c r="CM56" t="n">
         <v>9</v>
       </c>
-      <c r="CM56" t="n">
-        <v>10</v>
-      </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -16626,13 +16618,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50.5099983215332</v>
+        <v>50.54999923706055</v>
       </c>
       <c r="D57" t="n">
-        <v>50.5099983215332</v>
+        <v>50.54999923706055</v>
       </c>
       <c r="E57" t="n">
-        <v>50.54000091552734</v>
+        <v>50.61999893188477</v>
       </c>
       <c r="F57" t="n">
         <v>49.7400016784668</v>
@@ -16641,67 +16633,67 @@
         <v>50.47000122070312</v>
       </c>
       <c r="H57" t="n">
-        <v>392300</v>
+        <v>618900</v>
       </c>
       <c r="I57" t="n">
-        <v>0.009392434000935923</v>
+        <v>0.01019181279381143</v>
       </c>
       <c r="J57" t="n">
-        <v>50.92888895670573</v>
+        <v>50.93333350287543</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.8225010279109358</v>
+        <v>-0.7526196293302634</v>
       </c>
       <c r="M57" t="n">
-        <v>50.77799987792969</v>
+        <v>50.78199996948242</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.5277906909306395</v>
+        <v>-0.4568562336286381</v>
       </c>
       <c r="P57" t="n">
-        <v>48.95500007042518</v>
+        <v>48.95653856717623</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>3.176382900359619</v>
+        <v>3.254847496413235</v>
       </c>
       <c r="S57" t="n">
-        <v>51.38020011901855</v>
+        <v>51.3810001373291</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-1.693652020563545</v>
+        <v>-1.617331110814289</v>
       </c>
       <c r="V57" t="n">
-        <v>50.90060010274252</v>
+        <v>50.9008667755127</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-0.7673814855245037</v>
+        <v>-0.6893154491839505</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.25490007400513</v>
+        <v>50.25510007858276</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.5076087051261037</v>
+        <v>0.5868044397815462</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.2577570987241232</v>
+        <v>0.2580769263819558</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16716,13 +16708,13 @@
         <v>50.4</v>
       </c>
       <c r="AG57" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="AH57" t="n">
         <v>50.7</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AI57" t="n">
         <v>50.8</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>50.9</v>
       </c>
       <c r="AJ57" t="n">
         <v>2</v>
@@ -16849,7 +16841,7 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.859999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="CA57" t="n">
         <v>-0.4</v>
@@ -16909,103 +16901,103 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>19.67000007629395</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="D58" t="n">
-        <v>19.67000007629395</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="E58" t="n">
         <v>19.78000068664551</v>
       </c>
       <c r="F58" t="n">
-        <v>19.39999961853027</v>
+        <v>19.3700008392334</v>
       </c>
       <c r="G58" t="n">
         <v>19.70999908447266</v>
       </c>
       <c r="H58" t="n">
-        <v>3706300</v>
+        <v>6698000</v>
       </c>
       <c r="I58" t="n">
-        <v>0.006652976186060311</v>
+        <v>-0.004605944133624473</v>
       </c>
       <c r="J58" t="n">
-        <v>19.89222229851617</v>
+        <v>19.86777793036567</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.117131202775659</v>
+        <v>-2.102787583445306</v>
       </c>
       <c r="M58" t="n">
-        <v>19.86900005340576</v>
+        <v>19.84700012207031</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.001560101549786</v>
+        <v>-2.000299071341201</v>
       </c>
       <c r="P58" t="n">
-        <v>18.99461540809045</v>
+        <v>19.01846159421481</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>3.55566382205259</v>
+        <v>2.269054027250641</v>
       </c>
       <c r="S58" t="n">
-        <v>18.79020004272461</v>
+        <v>18.74700008392334</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>4.68222813790631</v>
+        <v>3.749936927876682</v>
       </c>
       <c r="V58" t="n">
-        <v>20.54353340148926</v>
+        <v>20.59053340911865</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-4.252108476782217</v>
+        <v>-5.539111704964899</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.42113139152527</v>
+        <v>21.43685688972473</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-8.17478443703545</v>
+        <v>-9.268411582005902</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.4614239286194887</v>
+        <v>0.5027982282791218</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
       <c r="AD58" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AE58" t="n">
         <v>19.3</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AF58" t="n">
         <v>19.4</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AG58" t="n">
         <v>19.6</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
         <v>19.7</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>19.9</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>20.1</v>
       </c>
       <c r="AJ58" t="n">
         <v>2</v>
@@ -17132,13 +17124,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>26.58</v>
+        <v>26.28</v>
       </c>
       <c r="CA58" t="n">
         <v>0.09</v>
       </c>
       <c r="CB58" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17170,16 +17162,16 @@
         <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -17198,7 +17190,7 @@
         <v>14.71000003814697</v>
       </c>
       <c r="E59" t="n">
-        <v>14.72999954223633</v>
+        <v>14.78999996185303</v>
       </c>
       <c r="F59" t="n">
         <v>14.4399995803833</v>
@@ -17207,7 +17199,7 @@
         <v>14.61999988555908</v>
       </c>
       <c r="H59" t="n">
-        <v>2700700</v>
+        <v>4357900</v>
       </c>
       <c r="I59" t="n">
         <v>0.0116918897345224</v>
@@ -17453,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="CL59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM59" t="n">
         <v>5</v>
@@ -17462,7 +17454,7 @@
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
@@ -17475,10 +17467,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37.25</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="D60" t="n">
-        <v>37.25</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="E60" t="n">
         <v>37.40000152587891</v>
@@ -17490,67 +17482,67 @@
         <v>37.38999938964844</v>
       </c>
       <c r="H60" t="n">
-        <v>1988200</v>
+        <v>2786200</v>
       </c>
       <c r="I60" t="n">
-        <v>0.005398131364585668</v>
+        <v>0.002429153966023945</v>
       </c>
       <c r="J60" t="n">
-        <v>37.33444468180338</v>
+        <v>37.32222239176432</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.2261843788573637</v>
+        <v>-0.4882426351869473</v>
       </c>
       <c r="M60" t="n">
-        <v>37.16900024414063</v>
+        <v>37.15800018310547</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.2179228801617888</v>
+        <v>-0.04844392423793158</v>
       </c>
       <c r="P60" t="n">
-        <v>35.34192334688627</v>
+        <v>35.33576935988206</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>5.398904395738946</v>
+        <v>5.105959378982075</v>
       </c>
       <c r="S60" t="n">
-        <v>35.01740013122559</v>
+        <v>35.03580009460449</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>6.375687116713068</v>
+        <v>6.005854838086014</v>
       </c>
       <c r="V60" t="n">
-        <v>36.69240002950033</v>
+        <v>36.74206667582194</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1.5196606655639</v>
+        <v>1.083043905334694</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.2848999786377</v>
+        <v>38.3418999671936</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-2.703154453100707</v>
+        <v>-3.134692278091453</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3354217520535335</v>
+        <v>0.3393191908587323</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17698,13 +17690,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>18.44</v>
+        <v>18.39</v>
       </c>
       <c r="CA60" t="n">
         <v>0.09</v>
       </c>
       <c r="CB60" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CC60" t="n">
         <v>9</v>
@@ -17758,13 +17750,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.47999954223633</v>
+        <v>11.40999984741211</v>
       </c>
       <c r="D61" t="n">
-        <v>11.47999954223633</v>
+        <v>11.40999984741211</v>
       </c>
       <c r="E61" t="n">
-        <v>11.48999977111816</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="F61" t="n">
         <v>11.27000045776367</v>
@@ -17773,67 +17765,67 @@
         <v>11.35000038146973</v>
       </c>
       <c r="H61" t="n">
-        <v>966000</v>
+        <v>1482300</v>
       </c>
       <c r="I61" t="n">
-        <v>0.009674552135832126</v>
+        <v>0.003518026583609002</v>
       </c>
       <c r="J61" t="n">
-        <v>11.414444287618</v>
+        <v>11.40666654374864</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5743184071557327</v>
+        <v>0.02922241700220746</v>
       </c>
       <c r="M61" t="n">
-        <v>11.40499982833862</v>
+        <v>11.3979998588562</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6576038143494712</v>
+        <v>0.1052815292551931</v>
       </c>
       <c r="P61" t="n">
-        <v>10.88538452295157</v>
+        <v>10.88269222699679</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>5.462508173514957</v>
+        <v>4.845378417550253</v>
       </c>
       <c r="S61" t="n">
-        <v>10.60759996414185</v>
+        <v>10.60619997024536</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>8.224288067456918</v>
+        <v>7.578584973145221</v>
       </c>
       <c r="V61" t="n">
-        <v>11.59393334706624</v>
+        <v>11.59346668243408</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-0.9827019133135344</v>
+        <v>-1.582501938785519</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.40329999446869</v>
+        <v>11.40294999599457</v>
       </c>
       <c r="Z61" t="n">
         <v>1</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.6726083485030029</v>
+        <v>0.06182480340629022</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3564879588243184</v>
+        <v>0.3560479697692505</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17981,7 +17973,7 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>6.31</v>
+        <v>6.27</v>
       </c>
       <c r="CA61" t="n">
         <v>0.45</v>
@@ -18041,13 +18033,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36.20999908447266</v>
+        <v>35.95999908447266</v>
       </c>
       <c r="D62" t="n">
-        <v>36.20999908447266</v>
+        <v>35.95999908447266</v>
       </c>
       <c r="E62" t="n">
-        <v>36.2400016784668</v>
+        <v>36.27999877929688</v>
       </c>
       <c r="F62" t="n">
         <v>35.33000183105469</v>
@@ -18056,67 +18048,67 @@
         <v>35.97000122070312</v>
       </c>
       <c r="H62" t="n">
-        <v>2887800</v>
+        <v>4642900</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01742059368436633</v>
+        <v>0.0103961486456432</v>
       </c>
       <c r="J62" t="n">
-        <v>36.3033332824707</v>
+        <v>36.27555550469292</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.2570953947171399</v>
+        <v>-0.8698872169702409</v>
       </c>
       <c r="M62" t="n">
-        <v>36.13699989318847</v>
+        <v>36.11199989318848</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.2020067839055512</v>
+        <v>-0.420914956705263</v>
       </c>
       <c r="P62" t="n">
-        <v>34.92692301823543</v>
+        <v>34.97576918968787</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>3.673601781546378</v>
+        <v>2.814033594077379</v>
       </c>
       <c r="S62" t="n">
-        <v>36.6331999206543</v>
+        <v>36.70859992980957</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.1552385188798</v>
+        <v>-2.03930644799397</v>
       </c>
       <c r="V62" t="n">
-        <v>42.75600001017253</v>
+        <v>42.85233334859213</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-15.31013407274405</v>
+        <v>-16.08391825026702</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.39375</v>
+        <v>43.42585000991821</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-16.55480550892085</v>
+        <v>-17.19218143971943</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4107899563037127</v>
+        <v>0.4435598109068563</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18134,13 +18126,13 @@
         <v>36.5</v>
       </c>
       <c r="AH62" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AI62" t="n">
         <v>37.6</v>
       </c>
-      <c r="AI62" t="n">
-        <v>38.1</v>
-      </c>
       <c r="AJ62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK62" t="n">
         <v>0</v>
@@ -18264,13 +18256,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>18.1</v>
+        <v>17.98</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="CB62" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CC62" t="n">
         <v>10</v>
@@ -18298,7 +18290,7 @@
         <v>0</v>
       </c>
       <c r="CL62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM62" t="n">
         <v>5</v>
@@ -18307,7 +18299,7 @@
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
@@ -18320,10 +18312,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30.01000022888184</v>
+        <v>30.07999992370605</v>
       </c>
       <c r="D63" t="n">
-        <v>30.01000022888184</v>
+        <v>30.07999992370605</v>
       </c>
       <c r="E63" t="n">
         <v>30.5</v>
@@ -18335,67 +18327,67 @@
         <v>30.48999977111816</v>
       </c>
       <c r="H63" t="n">
-        <v>1373900</v>
+        <v>2196900</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.01185382286478232</v>
+        <v>-0.009548926819676229</v>
       </c>
       <c r="J63" t="n">
-        <v>30.22888904147678</v>
+        <v>30.23666678534614</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.724104720800717</v>
+        <v>-0.5181353578166562</v>
       </c>
       <c r="M63" t="n">
-        <v>30.14000015258789</v>
+        <v>30.14700012207031</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.4313202489977204</v>
+        <v>-0.2222449931766456</v>
       </c>
       <c r="P63" t="n">
-        <v>29.75884620959942</v>
+        <v>29.7615385055542</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>0.8439642367633119</v>
+        <v>1.070043533174278</v>
       </c>
       <c r="S63" t="n">
-        <v>28.58240009307861</v>
+        <v>28.5838000869751</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>4.99468250095947</v>
+        <v>5.234432903176982</v>
       </c>
       <c r="V63" t="n">
-        <v>29.3875333404541</v>
+        <v>29.38800000508626</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>2.118132478886422</v>
+        <v>2.35470232237657</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.53679998397827</v>
+        <v>30.53714998245239</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-1.72513084335238</v>
+        <v>-1.497029221813526</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.1823812344847127</v>
+        <v>0.181055760963719</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18563,7 +18555,7 @@
         <v>18881600000</v>
       </c>
       <c r="BZ63" t="n">
-        <v>7.27</v>
+        <v>7.28</v>
       </c>
       <c r="CA63" t="n">
         <v>0</v>
@@ -18604,13 +18596,13 @@
         <v>6</v>
       </c>
       <c r="CM63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN63" t="n">
         <v>1</v>
       </c>
       <c r="CO63" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -18623,10 +18615,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.1200008392334</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="D64" t="n">
-        <v>27.1200008392334</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="E64" t="n">
         <v>27.35000038146973</v>
@@ -18638,88 +18630,88 @@
         <v>27.13999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>6675900</v>
+        <v>9722900</v>
       </c>
       <c r="I64" t="n">
-        <v>0.01043221628366897</v>
+        <v>0.006706419677811493</v>
       </c>
       <c r="J64" t="n">
-        <v>26.75000042385525</v>
+        <v>26.73888927035862</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1.383179100992411</v>
+        <v>1.051319613775736</v>
       </c>
       <c r="M64" t="n">
-        <v>26.5850004196167</v>
+        <v>26.57500038146973</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>2.012414561490589</v>
+        <v>1.674506377822047</v>
       </c>
       <c r="P64" t="n">
-        <v>25.39153861999512</v>
+        <v>25.38769245147705</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>6.807237029256534</v>
+        <v>6.42952489442046</v>
       </c>
       <c r="S64" t="n">
-        <v>26.99300006866455</v>
+        <v>26.99100006103516</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0.4704952033704483</v>
+        <v>0.1074446914265406</v>
       </c>
       <c r="V64" t="n">
-        <v>29.15830281575521</v>
+        <v>29.15763614654541</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-6.99046851046642</v>
+        <v>-7.331306550496911</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.57329833984375</v>
+        <v>28.5727983379364</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-5.086208401022484</v>
+        <v>-5.434532039205497</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3257122154570699</v>
+        <v>0.3248190307500361</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
       </c>
       <c r="AD64" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AE64" t="n">
         <v>26.6</v>
       </c>
-      <c r="AE64" t="n">
+      <c r="AF64" t="n">
         <v>27</v>
       </c>
-      <c r="AF64" t="n">
+      <c r="AG64" t="n">
         <v>27.1</v>
       </c>
-      <c r="AG64" t="n">
+      <c r="AH64" t="n">
         <v>27.4</v>
       </c>
-      <c r="AH64" t="n">
+      <c r="AI64" t="n">
         <v>28.4</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>29.1</v>
       </c>
       <c r="AJ64" t="n">
         <v>1</v>
@@ -18846,13 +18838,13 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.94</v>
+        <v>10.9</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
       </c>
       <c r="CB64" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CC64" t="n">
         <v>9</v>
@@ -18887,13 +18879,13 @@
         <v>3</v>
       </c>
       <c r="CM64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
@@ -18906,13 +18898,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>18.17000007629395</v>
+        <v>17.96999931335449</v>
       </c>
       <c r="D65" t="n">
-        <v>18.17000007629395</v>
+        <v>17.96999931335449</v>
       </c>
       <c r="E65" t="n">
-        <v>18.17000007629395</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="F65" t="n">
         <v>17.27000045776367</v>
@@ -18921,67 +18913,67 @@
         <v>17.30999946594238</v>
       </c>
       <c r="H65" t="n">
-        <v>1711800</v>
+        <v>2994300</v>
       </c>
       <c r="I65" t="n">
-        <v>0.04726222921009282</v>
+        <v>0.03573480796847361</v>
       </c>
       <c r="J65" t="n">
-        <v>17.3222221798367</v>
+        <v>17.29999987284343</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>4.8941636220558</v>
+        <v>3.872829164367765</v>
       </c>
       <c r="M65" t="n">
-        <v>17.22099990844726</v>
+        <v>17.20099983215332</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>5.510714667509961</v>
+        <v>4.47066733739339</v>
       </c>
       <c r="P65" t="n">
-        <v>15.67076917795035</v>
+        <v>15.66307684091421</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>15.94836137245999</v>
+        <v>14.72841189423438</v>
       </c>
       <c r="S65" t="n">
-        <v>14.63520000457764</v>
+        <v>14.63119998931885</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>24.15272815274601</v>
+        <v>22.81972310181703</v>
       </c>
       <c r="V65" t="n">
-        <v>15.811399974823</v>
+        <v>15.8100666364034</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>14.91708580661183</v>
+        <v>13.66175568152095</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.6126888179779</v>
+        <v>15.61168881416321</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>16.37969787350987</v>
+        <v>15.10605628426171</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.3883667628415573</v>
+        <v>0.3802665659686805</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19133,13 +19125,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>27.95</v>
+        <v>27.65</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CC65" t="n">
         <v>3</v>
@@ -19193,13 +19185,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.20999908447266</v>
+        <v>17.06999969482422</v>
       </c>
       <c r="D66" t="n">
-        <v>17.20999908447266</v>
+        <v>17.06999969482422</v>
       </c>
       <c r="E66" t="n">
-        <v>17.23999977111816</v>
+        <v>17.25</v>
       </c>
       <c r="F66" t="n">
         <v>17</v>
@@ -19208,67 +19200,67 @@
         <v>17.23999977111816</v>
       </c>
       <c r="H66" t="n">
-        <v>1650300</v>
+        <v>2849700</v>
       </c>
       <c r="I66" t="n">
-        <v>0.007021587525649853</v>
+        <v>-0.001170301789648831</v>
       </c>
       <c r="J66" t="n">
-        <v>17.60777770148383</v>
+        <v>17.59222221374512</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.259107445328865</v>
+        <v>-2.968485234985701</v>
       </c>
       <c r="M66" t="n">
-        <v>17.5689998626709</v>
+        <v>17.55499992370606</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-2.043376293496465</v>
+        <v>-2.762746972313563</v>
       </c>
       <c r="P66" t="n">
-        <v>17.31461546971248</v>
+        <v>17.30923087780292</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.6042085394435822</v>
+        <v>-1.38210175060689</v>
       </c>
       <c r="S66" t="n">
-        <v>18.60720008850098</v>
+        <v>18.60440010070801</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-7.508926637983404</v>
+        <v>-8.247513478413083</v>
       </c>
       <c r="V66" t="n">
-        <v>18.94853336334229</v>
+        <v>18.94760003407796</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-9.175033473740964</v>
+        <v>-9.909436212907222</v>
       </c>
       <c r="Y66" t="n">
-        <v>20.04764096260071</v>
+        <v>20.04694096565247</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-14.15449270775416</v>
+        <v>-14.84985303208508</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3398938183130229</v>
+        <v>0.3383835449780145</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19420,13 +19412,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.37</v>
+        <v>15.24</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CC66" t="n">
         <v>10</v>
@@ -19480,10 +19472,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>47.63999938964844</v>
+        <v>47.54000091552734</v>
       </c>
       <c r="D67" t="n">
-        <v>47.63999938964844</v>
+        <v>47.54000091552734</v>
       </c>
       <c r="E67" t="n">
         <v>47.77000045776367</v>
@@ -19495,67 +19487,67 @@
         <v>47.72999954223633</v>
       </c>
       <c r="H67" t="n">
-        <v>778300</v>
+        <v>1623500</v>
       </c>
       <c r="I67" t="n">
-        <v>0.007188164018436138</v>
+        <v>0.005074031339069141</v>
       </c>
       <c r="J67" t="n">
-        <v>47.28222190009223</v>
+        <v>47.27111095852322</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.7566850185513552</v>
+        <v>0.5688251271269051</v>
       </c>
       <c r="M67" t="n">
-        <v>47.12999954223633</v>
+        <v>47.11999969482422</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>1.082112990379017</v>
+        <v>0.8913438527659029</v>
       </c>
       <c r="P67" t="n">
-        <v>44.93807704632099</v>
+        <v>44.93423095116248</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>6.012545531359465</v>
+        <v>5.79907546920517</v>
       </c>
       <c r="S67" t="n">
-        <v>43.5366000366211</v>
+        <v>43.53460006713867</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>9.425171808491569</v>
+        <v>9.200499929278278</v>
       </c>
       <c r="V67" t="n">
-        <v>46.13553342183431</v>
+        <v>46.13486676534017</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>3.260970137828984</v>
+        <v>3.045709782439019</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.20150003433228</v>
+        <v>47.20100004196167</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.9289945340661117</v>
+        <v>0.7182069728698585</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2714509346805017</v>
+        <v>0.271269369018211</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19703,7 +19695,7 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="CA67" t="n">
         <v>1.14</v>
@@ -19763,13 +19755,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40.91999816894531</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="D68" t="n">
-        <v>40.91999816894531</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="E68" t="n">
-        <v>40.95000076293945</v>
+        <v>40.97999954223633</v>
       </c>
       <c r="F68" t="n">
         <v>40.52999877929688</v>
@@ -19778,67 +19770,67 @@
         <v>40.59999847412109</v>
       </c>
       <c r="H68" t="n">
-        <v>311400</v>
+        <v>647800</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0101209544408738</v>
+        <v>0.007652465715512813</v>
       </c>
       <c r="J68" t="n">
-        <v>41.12444390190972</v>
+        <v>41.11333296034071</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.4971392037593363</v>
+        <v>-0.7134747888220437</v>
       </c>
       <c r="M68" t="n">
-        <v>40.98499946594238</v>
+        <v>40.97499961853028</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.1585977744152031</v>
+        <v>-0.3782792560075128</v>
       </c>
       <c r="P68" t="n">
-        <v>39.18884570782001</v>
+        <v>39.18499961266151</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>4.417462239210203</v>
+        <v>4.172515243905754</v>
       </c>
       <c r="S68" t="n">
-        <v>39.78579971313476</v>
+        <v>39.78379974365235</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>2.850761990429734</v>
+        <v>2.604577636748242</v>
       </c>
       <c r="V68" t="n">
-        <v>41.05359995524088</v>
+        <v>41.05293329874674</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-0.3254325721525814</v>
+        <v>-0.567398198388022</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.19450004577637</v>
+        <v>41.19400005340576</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-0.6663556458411186</v>
+        <v>-0.9079000779158839</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2086435530906947</v>
+        <v>0.2078105486096099</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -19988,7 +19980,7 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>8.99</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="CA68" t="n">
         <v>0.24</v>
@@ -20059,7 +20051,7 @@
         <v>19.76000022888184</v>
       </c>
       <c r="H69" t="n">
-        <v>2328800</v>
+        <v>3845200</v>
       </c>
       <c r="I69" t="n">
         <v>0.003061197182379072</v>
@@ -20305,7 +20297,7 @@
         <v>-1</v>
       </c>
       <c r="CL69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM69" t="n">
         <v>9</v>
@@ -20314,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70">
@@ -20327,10 +20319,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>34.20999908447266</v>
+        <v>33.90999984741211</v>
       </c>
       <c r="D70" t="n">
-        <v>34.20999908447266</v>
+        <v>33.90999984741211</v>
       </c>
       <c r="E70" t="n">
         <v>34.54000091552734</v>
@@ -20342,67 +20334,67 @@
         <v>34.36999893188477</v>
       </c>
       <c r="H70" t="n">
-        <v>1789700</v>
+        <v>3017700</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.00465521828293336</v>
+        <v>-0.01338373868978848</v>
       </c>
       <c r="J70" t="n">
-        <v>34.00444412231445</v>
+        <v>33.97111087375217</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.6044944049631251</v>
+        <v>-0.1798911627210729</v>
       </c>
       <c r="M70" t="n">
-        <v>34.10299987792969</v>
+        <v>34.07299995422363</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.3137530625633089</v>
+        <v>-0.4783849588545496</v>
       </c>
       <c r="P70" t="n">
-        <v>32.7538460951585</v>
+        <v>32.75653839111328</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>4.445746569986467</v>
+        <v>3.52131669875031</v>
       </c>
       <c r="S70" t="n">
-        <v>31.35259983062744</v>
+        <v>31.27999984741211</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>9.113755380036796</v>
+        <v>8.407928429761762</v>
       </c>
       <c r="V70" t="n">
-        <v>32.75793328603109</v>
+        <v>32.79613328297933</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>4.432714926679359</v>
+        <v>3.396335033834193</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.53419995307922</v>
+        <v>35.5870999622345</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-3.726553208894797</v>
+        <v>-4.712663062183061</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.375563444883979</v>
+        <v>0.3915529069171073</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20550,13 +20542,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>22.21</v>
+        <v>22.02</v>
       </c>
       <c r="CA70" t="n">
         <v>0.17</v>
       </c>
       <c r="CB70" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC70" t="n">
         <v>7</v>
@@ -20591,13 +20583,13 @@
         <v>8</v>
       </c>
       <c r="CM70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71">
@@ -20610,10 +20602,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.43999862670898</v>
+        <v>38.40999984741211</v>
       </c>
       <c r="D71" t="n">
-        <v>38.43999862670898</v>
+        <v>38.40999984741211</v>
       </c>
       <c r="E71" t="n">
         <v>38.7599983215332</v>
@@ -20625,67 +20617,67 @@
         <v>38.5</v>
       </c>
       <c r="H71" t="n">
-        <v>3099300</v>
+        <v>5293000</v>
       </c>
       <c r="I71" t="n">
-        <v>0.001824334031087282</v>
+        <v>0.001042504994549276</v>
       </c>
       <c r="J71" t="n">
-        <v>37.82222196790907</v>
+        <v>37.81888877020942</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1.633369555400725</v>
+        <v>1.563004880429798</v>
       </c>
       <c r="M71" t="n">
-        <v>37.5689998626709</v>
+        <v>37.56599998474121</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2.318397527807285</v>
+        <v>2.246712088094872</v>
       </c>
       <c r="P71" t="n">
-        <v>34.83961530832144</v>
+        <v>34.84923076629639</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>10.33416496285937</v>
+        <v>10.21764039784613</v>
       </c>
       <c r="S71" t="n">
-        <v>33.34999992370606</v>
+        <v>33.28819995880127</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>15.26236496146083</v>
+        <v>15.38623264384908</v>
       </c>
       <c r="V71" t="n">
-        <v>29.44780002593994</v>
+        <v>29.41873336791992</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>30.53606243199155</v>
+        <v>30.56306458556384</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.69279999732971</v>
+        <v>27.64770000457764</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>38.80863845626147</v>
+        <v>38.92656474517792</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3427576109913911</v>
+        <v>0.3427333549245754</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20837,7 +20829,7 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>14.29</v>
+        <v>14.28</v>
       </c>
       <c r="CA71" t="n">
         <v>0.33</v>
@@ -20893,13 +20885,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7.239999771118164</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="D72" t="n">
-        <v>7.239999771118164</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="E72" t="n">
-        <v>7.239999771118164</v>
+        <v>7.25</v>
       </c>
       <c r="F72" t="n">
         <v>6.929999828338623</v>
@@ -20908,67 +20900,67 @@
         <v>7.050000190734863</v>
       </c>
       <c r="H72" t="n">
-        <v>6878700</v>
+        <v>9435600</v>
       </c>
       <c r="I72" t="n">
-        <v>0.02987191394629263</v>
+        <v>0.02844947415308674</v>
       </c>
       <c r="J72" t="n">
-        <v>7.524444474114312</v>
+        <v>7.523333390553792</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.780275128279547</v>
+        <v>-3.89898142555548</v>
       </c>
       <c r="M72" t="n">
-        <v>7.53100004196167</v>
+        <v>7.530000066757202</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-3.864032256301869</v>
+        <v>-3.984064342949079</v>
       </c>
       <c r="P72" t="n">
-        <v>7.033846139907837</v>
+        <v>7.033461534059965</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>2.930880589506729</v>
+        <v>2.794335108847495</v>
       </c>
       <c r="S72" t="n">
-        <v>7.540999956130982</v>
+        <v>7.540799961090088</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-3.991515538573881</v>
+        <v>-4.121577864686826</v>
       </c>
       <c r="V72" t="n">
-        <v>7.906666666666666</v>
+        <v>7.906600001653035</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-8.431706098842778</v>
+        <v>-8.557407513192672</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.464249999523163</v>
+        <v>7.46420000076294</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-3.00432365501322</v>
+        <v>-3.137643440228226</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.5190710008264982</v>
+        <v>0.5183534011022374</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21161,13 +21153,13 @@
         <v>2</v>
       </c>
       <c r="CM72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN72" t="n">
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
@@ -21180,10 +21172,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>75.27999877929688</v>
+        <v>74.83999633789062</v>
       </c>
       <c r="D73" t="n">
-        <v>75.27999877929688</v>
+        <v>74.83999633789062</v>
       </c>
       <c r="E73" t="n">
         <v>75.94000244140625</v>
@@ -21195,67 +21187,67 @@
         <v>75.83999633789062</v>
       </c>
       <c r="H73" t="n">
-        <v>8220500</v>
+        <v>13231400</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.002649769061229712</v>
+        <v>-0.008479159917580747</v>
       </c>
       <c r="J73" t="n">
-        <v>78.13111114501953</v>
+        <v>78.08222198486328</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-3.649138382827672</v>
+        <v>-4.152322467976362</v>
       </c>
       <c r="M73" t="n">
-        <v>78.14800033569335</v>
+        <v>78.10400009155273</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-3.669961539740827</v>
+        <v>-4.179048127926965</v>
       </c>
       <c r="P73" t="n">
-        <v>76.23653852022611</v>
+        <v>76.2196153494028</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-1.254699858487742</v>
+        <v>-1.810057693400555</v>
       </c>
       <c r="S73" t="n">
-        <v>75.4552001953125</v>
+        <v>75.44640014648438</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-0.2321926329293724</v>
+        <v>-0.8037544633228083</v>
       </c>
       <c r="V73" t="n">
-        <v>80.03746683756511</v>
+        <v>80.03453348795573</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-5.944051262796015</v>
+        <v>-6.490369748762038</v>
       </c>
       <c r="Y73" t="n">
-        <v>78.95265010833741</v>
+        <v>78.95045009613037</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-4.651713810747312</v>
+        <v>-5.206371532061994</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2579850965802324</v>
+        <v>0.2591369895131538</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21403,13 +21395,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>21.45</v>
+        <v>21.32</v>
       </c>
       <c r="CA73" t="n">
         <v>0.21</v>
       </c>
       <c r="CB73" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21440,13 +21432,13 @@
         <v>3</v>
       </c>
       <c r="CM73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN73" t="n">
         <v>0</v>
       </c>
       <c r="CO73" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -21459,13 +21451,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.329999923706055</v>
+        <v>3.309999942779541</v>
       </c>
       <c r="D74" t="n">
-        <v>3.329999923706055</v>
+        <v>3.309999942779541</v>
       </c>
       <c r="E74" t="n">
-        <v>3.329999923706055</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="F74" t="n">
         <v>3.210000038146973</v>
@@ -21474,67 +21466,67 @@
         <v>3.25</v>
       </c>
       <c r="H74" t="n">
-        <v>5376600</v>
+        <v>7365400</v>
       </c>
       <c r="I74" t="n">
-        <v>0.02777775120506232</v>
+        <v>0.02160491760393746</v>
       </c>
       <c r="J74" t="n">
-        <v>3.391111108991835</v>
+        <v>3.388888888888889</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.802099174035855</v>
+        <v>-2.327870540931575</v>
       </c>
       <c r="M74" t="n">
-        <v>3.35</v>
+        <v>3.348000001907349</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.5970172028043402</v>
+        <v>-1.135007739132594</v>
       </c>
       <c r="P74" t="n">
-        <v>3.036538454202505</v>
+        <v>3.03576922416687</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>9.664342274256567</v>
+        <v>9.033319016136025</v>
       </c>
       <c r="S74" t="n">
-        <v>3.094599990844726</v>
+        <v>3.094199991226196</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>7.606796793050844</v>
+        <v>6.97433754008336</v>
       </c>
       <c r="V74" t="n">
-        <v>3.457261460622152</v>
+        <v>3.457128127415975</v>
       </c>
       <c r="W74" t="n">
         <v>-1</v>
       </c>
       <c r="X74" t="n">
-        <v>-3.680992553371877</v>
+        <v>-4.255792068268086</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.517796090841293</v>
+        <v>3.517696090936661</v>
       </c>
       <c r="Z74" t="n">
         <v>-1</v>
       </c>
       <c r="AA74" t="n">
-        <v>-5.338460851217971</v>
+        <v>-5.904323249875071</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.7652449262699454</v>
+        <v>0.7636307973777936</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21684,13 +21676,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>13.32</v>
+        <v>13.24</v>
       </c>
       <c r="CA74" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CC74" t="n">
         <v>6</v>
@@ -21740,13 +21732,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.70999908447266</v>
+        <v>38.77999877929688</v>
       </c>
       <c r="D75" t="n">
-        <v>38.70999908447266</v>
+        <v>38.77999877929688</v>
       </c>
       <c r="E75" t="n">
-        <v>38.84999847412109</v>
+        <v>38.91999816894531</v>
       </c>
       <c r="F75" t="n">
         <v>37.66999816894531</v>
@@ -21755,67 +21747,67 @@
         <v>37.97999954223633</v>
       </c>
       <c r="H75" t="n">
-        <v>3427800</v>
+        <v>6618200</v>
       </c>
       <c r="I75" t="n">
-        <v>0.02679040586455561</v>
+        <v>0.02864716165786141</v>
       </c>
       <c r="J75" t="n">
-        <v>37.54000006781684</v>
+        <v>37.5477778116862</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>3.116672920996766</v>
+        <v>3.28174139569764</v>
       </c>
       <c r="M75" t="n">
-        <v>37.26900024414063</v>
+        <v>37.27600021362305</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>3.866481072452647</v>
+        <v>4.034763807958579</v>
       </c>
       <c r="P75" t="n">
-        <v>35.18307700523963</v>
+        <v>35.18576930119441</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>10.02448443809442</v>
+        <v>10.21500893538927</v>
       </c>
       <c r="S75" t="n">
-        <v>34.74119983673096</v>
+        <v>34.74259983062744</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>11.4238980414994</v>
+        <v>11.6208889615401</v>
       </c>
       <c r="V75" t="n">
-        <v>32.37913319905599</v>
+        <v>32.37959986368815</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>19.5523019300629</v>
+        <v>19.76676346388827</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.84914115905762</v>
+        <v>30.84949115753174</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>25.48161028174041</v>
+        <v>25.70709377755473</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2883682081885301</v>
+        <v>0.2897762823337975</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21830,7 +21822,7 @@
         <v>33.3</v>
       </c>
       <c r="AG75" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -21967,7 +21959,7 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.42</v>
+        <v>15.45</v>
       </c>
       <c r="CA75" t="n">
         <v>0.39</v>
@@ -22023,10 +22015,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.63999938964844</v>
+        <v>22.5</v>
       </c>
       <c r="D76" t="n">
-        <v>22.63999938964844</v>
+        <v>22.5</v>
       </c>
       <c r="E76" t="n">
         <v>22.69000053405762</v>
@@ -22038,67 +22030,67 @@
         <v>22.45999908447266</v>
       </c>
       <c r="H76" t="n">
-        <v>756800</v>
+        <v>1109200</v>
       </c>
       <c r="I76" t="n">
-        <v>0.01071427567880967</v>
+        <v>0.00446430282021093</v>
       </c>
       <c r="J76" t="n">
-        <v>22.828888575236</v>
+        <v>22.81333308749729</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.8274129726686161</v>
+        <v>-1.373464746670481</v>
       </c>
       <c r="M76" t="n">
-        <v>22.7959997177124</v>
+        <v>22.78199977874756</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-0.6843320319167775</v>
+        <v>-1.237818371900014</v>
       </c>
       <c r="P76" t="n">
-        <v>21.9846153992873</v>
+        <v>21.97923080737774</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>2.9811028233061</v>
+        <v>2.369369506995902</v>
       </c>
       <c r="S76" t="n">
-        <v>22.17340007781982</v>
+        <v>22.17060009002686</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>2.104320087090996</v>
+        <v>1.48575098840613</v>
       </c>
       <c r="V76" t="n">
-        <v>24.36466668446859</v>
+        <v>24.36373335520426</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-7.078558952417563</v>
+        <v>-7.649621377941068</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.1253000164032</v>
+        <v>26.12460001945496</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-13.34071043994311</v>
+        <v>-13.87427947894215</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3046406287829193</v>
+        <v>0.3032451029995589</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22246,13 +22238,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.130000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CC76" t="n">
         <v>8</v>
@@ -22306,13 +22298,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30.70999908447266</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="D77" t="n">
-        <v>30.70999908447266</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="E77" t="n">
-        <v>30.79999923706055</v>
+        <v>30.81999969482422</v>
       </c>
       <c r="F77" t="n">
         <v>30.40999984741211</v>
@@ -22321,67 +22313,67 @@
         <v>30.64999961853027</v>
       </c>
       <c r="H77" t="n">
-        <v>1535600</v>
+        <v>2868400</v>
       </c>
       <c r="I77" t="n">
-        <v>0.006555190235675301</v>
+        <v>0.009505047722162541</v>
       </c>
       <c r="J77" t="n">
-        <v>30.30555555555556</v>
+        <v>30.31555557250977</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1.3345524327237</v>
+        <v>1.59800358397547</v>
       </c>
       <c r="M77" t="n">
-        <v>30.27399997711182</v>
+        <v>30.28299999237061</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1.440176744699972</v>
+        <v>1.707225984282245</v>
       </c>
       <c r="P77" t="n">
-        <v>29.93923077216515</v>
+        <v>29.94269231649546</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>2.574442603996677</v>
+        <v>2.863159102405762</v>
       </c>
       <c r="S77" t="n">
-        <v>31.90780017852783</v>
+        <v>31.90960018157959</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-3.753944450426982</v>
+        <v>-3.477326378910829</v>
       </c>
       <c r="V77" t="n">
-        <v>36.08760011037191</v>
+        <v>36.08820011138916</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-14.90152021595274</v>
+        <v>-14.65354564097449</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.69765011787415</v>
+        <v>35.69810011863709</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-13.97193097285731</v>
+        <v>-13.72090073504882</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1706424809658208</v>
+        <v>0.1720794255311011</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22529,7 +22521,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.59</v>
+        <v>15.63</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
@@ -22570,13 +22562,13 @@
         <v>2</v>
       </c>
       <c r="CM77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN77" t="n">
         <v>1</v>
       </c>
       <c r="CO77" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
@@ -22589,10 +22581,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.22999954223633</v>
+        <v>50.75</v>
       </c>
       <c r="D78" t="n">
-        <v>51.22999954223633</v>
+        <v>50.75</v>
       </c>
       <c r="E78" t="n">
         <v>51.29000091552734</v>
@@ -22604,76 +22596,76 @@
         <v>51.13999938964844</v>
       </c>
       <c r="H78" t="n">
-        <v>4238100</v>
+        <v>5825400</v>
       </c>
       <c r="I78" t="n">
-        <v>0.009657032864811343</v>
+        <v>0.0001970500828234467</v>
       </c>
       <c r="J78" t="n">
-        <v>51.62333382500542</v>
+        <v>51.57000054253472</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.7619311920118036</v>
+        <v>-1.590072782447207</v>
       </c>
       <c r="M78" t="n">
-        <v>51.43100051879883</v>
+        <v>51.3830005645752</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.3908167730258877</v>
+        <v>-1.231926040947491</v>
       </c>
       <c r="P78" t="n">
-        <v>49.77038500859187</v>
+        <v>49.77076955942007</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2.932696890716199</v>
+        <v>1.967481011943862</v>
       </c>
       <c r="S78" t="n">
-        <v>47.93840026855469</v>
+        <v>47.90140022277832</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>6.866310213194105</v>
+        <v>5.946798556980592</v>
       </c>
       <c r="V78" t="n">
-        <v>47.23080012003581</v>
+        <v>47.2557334391276</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>8.467354802452343</v>
+        <v>7.394375891707471</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.49345006942749</v>
+        <v>47.46885005950928</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>7.867504818762646</v>
+        <v>6.91221703575568</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.1871717258232193</v>
+        <v>0.1965717927319637</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
       <c r="AD78" t="n">
+        <v>49</v>
+      </c>
+      <c r="AE78" t="n">
         <v>49.1</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>49.5</v>
       </c>
       <c r="AF78" t="n">
         <v>50</v>
@@ -22812,13 +22804,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>34.15</v>
+        <v>33.83</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22853,13 +22845,13 @@
         <v>7</v>
       </c>
       <c r="CM78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO78" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -22872,13 +22864,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10.10999965667725</v>
+        <v>10.21000003814697</v>
       </c>
       <c r="D79" t="n">
-        <v>10.10999965667725</v>
+        <v>10.21000003814697</v>
       </c>
       <c r="E79" t="n">
-        <v>10.13000011444092</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="F79" t="n">
         <v>9.800000190734863</v>
@@ -22887,67 +22879,67 @@
         <v>9.979999542236328</v>
       </c>
       <c r="H79" t="n">
-        <v>2386100</v>
+        <v>3724200</v>
       </c>
       <c r="I79" t="n">
-        <v>0.01915318335907545</v>
+        <v>0.02923386689744567</v>
       </c>
       <c r="J79" t="n">
-        <v>9.84666665395101</v>
+        <v>9.857777807447645</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.674336524031441</v>
+        <v>3.573038848909946</v>
       </c>
       <c r="M79" t="n">
-        <v>9.74399995803833</v>
+        <v>9.753999996185303</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>3.75615455885736</v>
+        <v>4.675005558130064</v>
       </c>
       <c r="P79" t="n">
-        <v>8.654615328862118</v>
+        <v>8.658461497380184</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>16.81627978266803</v>
+        <v>17.91933291192947</v>
       </c>
       <c r="S79" t="n">
-        <v>8.488599996566773</v>
+        <v>8.490600004196168</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>19.10090781478985</v>
+        <v>20.25063049844599</v>
       </c>
       <c r="V79" t="n">
-        <v>9.927199967702229</v>
+        <v>9.927866636912029</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>1.841402304474058</v>
+        <v>2.841833110307562</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.69859998226166</v>
+        <v>10.69909998416901</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-5.501657474438852</v>
+        <v>-4.57141205097376</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5476572339182492</v>
+        <v>0.5504005319419378</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23095,13 +23087,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>23.51</v>
+        <v>23.74</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="CC79" t="n">
         <v>5</v>
@@ -23136,13 +23128,13 @@
         <v>10</v>
       </c>
       <c r="CM79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.82999992370605</v>
+        <v>15.72999954223633</v>
       </c>
       <c r="D2" t="n">
-        <v>15.82999992370605</v>
+        <v>15.72999954223633</v>
       </c>
       <c r="E2" t="n">
         <v>15.94999980926514</v>
@@ -912,67 +912,67 @@
         <v>15.94999980926514</v>
       </c>
       <c r="H2" t="n">
-        <v>17209100</v>
+        <v>20795700</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.002520476505448843</v>
+        <v>-0.00882169781552089</v>
       </c>
       <c r="J2" t="n">
-        <v>15.72888882954915</v>
+        <v>15.71777767605252</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6428368542280469</v>
+        <v>0.07775823297483268</v>
       </c>
       <c r="M2" t="n">
-        <v>15.67299995422363</v>
+        <v>15.66299991607666</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.001722516052922</v>
+        <v>0.4277573039561736</v>
       </c>
       <c r="P2" t="n">
-        <v>15.2596153479356</v>
+        <v>15.25576917941754</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3.73786994472056</v>
+        <v>3.108531318490337</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51339996337891</v>
+        <v>15.51139995574951</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2.040816075615383</v>
+        <v>1.409283411622617</v>
       </c>
       <c r="V2" t="n">
-        <v>15.69406667073568</v>
+        <v>15.69340000152588</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8661442303150653</v>
+        <v>0.2332161335777523</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.30364999771118</v>
+        <v>15.30314999580383</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.439375090737141</v>
+        <v>2.789292051306679</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1718845368613354</v>
+        <v>0.1737063281578304</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1165,13 +1165,13 @@
         <v>4</v>
       </c>
       <c r="CM2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN2" t="n">
         <v>1</v>
       </c>
       <c r="CO2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.54999923706055</v>
+        <v>28.53000068664551</v>
       </c>
       <c r="D3" t="n">
-        <v>28.54999923706055</v>
+        <v>28.53000068664551</v>
       </c>
       <c r="E3" t="n">
         <v>28.67000007629395</v>
@@ -1199,67 +1199,67 @@
         <v>28.51000022888184</v>
       </c>
       <c r="H3" t="n">
-        <v>2259100</v>
+        <v>2869600</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003867746165166386</v>
+        <v>0.003164562267856219</v>
       </c>
       <c r="J3" t="n">
-        <v>28.75444433424208</v>
+        <v>28.75222227308485</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7110034706463492</v>
+        <v>-0.7728849072211343</v>
       </c>
       <c r="M3" t="n">
-        <v>28.61099987030029</v>
+        <v>28.60900001525879</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2132069257148494</v>
+        <v>-0.2761345330880044</v>
       </c>
       <c r="P3" t="n">
-        <v>27.05807685852051</v>
+        <v>27.05730768350454</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>5.513778330739855</v>
+        <v>5.442866010053137</v>
       </c>
       <c r="S3" t="n">
-        <v>27.19839996337891</v>
+        <v>27.1979999923706</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4.969407301537924</v>
+        <v>4.897421481905092</v>
       </c>
       <c r="V3" t="n">
-        <v>28.93093332926432</v>
+        <v>28.93080000559489</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.316701704256644</v>
+        <v>-1.385372401979453</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.96279998779297</v>
+        <v>28.96269999504089</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.425279154316596</v>
+        <v>-1.493988158802438</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2633651728416429</v>
+        <v>0.2633184945711702</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.41</v>
+        <v>17.4</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.659999847412109</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="D4" t="n">
-        <v>9.659999847412109</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="E4" t="n">
         <v>9.819999694824219</v>
@@ -1482,67 +1482,67 @@
         <v>9.75</v>
       </c>
       <c r="H4" t="n">
-        <v>6439500</v>
+        <v>7790900</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00311523703163874</v>
+        <v>0.002076791677225964</v>
       </c>
       <c r="J4" t="n">
-        <v>9.402222103542751</v>
+        <v>9.401110967000326</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2.741668310220278</v>
+        <v>2.647438716589916</v>
       </c>
       <c r="M4" t="n">
-        <v>9.311999893188476</v>
+        <v>9.310999870300293</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.737112953343003</v>
+        <v>3.640852249512997</v>
       </c>
       <c r="P4" t="n">
-        <v>8.624615357472347</v>
+        <v>8.624230733284584</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>12.00499323187448</v>
+        <v>11.89403341548841</v>
       </c>
       <c r="S4" t="n">
-        <v>8.533399963378907</v>
+        <v>8.533199958801269</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>13.20223930517739</v>
+        <v>13.0877005709578</v>
       </c>
       <c r="V4" t="n">
-        <v>8.695333274205526</v>
+        <v>8.69526660601298</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>11.09407244996855</v>
+        <v>10.97991649683372</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.547249941825866</v>
+        <v>8.547199940681457</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.01880620269468</v>
+        <v>12.90246730511012</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5211213828981155</v>
+        <v>0.5211555981230187</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1692,7 +1692,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>18.58</v>
+        <v>18.56</v>
       </c>
       <c r="CA4" t="n">
         <v>0.92</v>
@@ -1733,13 +1733,13 @@
         <v>9</v>
       </c>
       <c r="CM4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN4" t="n">
         <v>0</v>
       </c>
       <c r="CO4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.55000019073486</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="D5" t="n">
-        <v>11.55000019073486</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="E5" t="n">
         <v>11.61999988555908</v>
@@ -1767,73 +1767,73 @@
         <v>11.61999988555908</v>
       </c>
       <c r="H5" t="n">
-        <v>1590500</v>
+        <v>2021900</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001734645119416456</v>
+        <v>0.004336530086109347</v>
       </c>
       <c r="J5" t="n">
-        <v>11.82111114925808</v>
+        <v>11.82444445292155</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.293447334180895</v>
+        <v>-2.067281301787481</v>
       </c>
       <c r="M5" t="n">
-        <v>11.76400003433228</v>
+        <v>11.7670000076294</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.819107811738105</v>
+        <v>-1.589190820107886</v>
       </c>
       <c r="P5" t="n">
-        <v>10.95538465793316</v>
+        <v>10.9607692865225</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.427609813509556</v>
+        <v>5.64951803104705</v>
       </c>
       <c r="S5" t="n">
-        <v>11.23559997558594</v>
+        <v>11.26699996948242</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.79825034561654</v>
+        <v>2.778023920044543</v>
       </c>
       <c r="V5" t="n">
-        <v>11.96999998728434</v>
+        <v>11.97486665089925</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.508770233881727</v>
+        <v>-3.297462416114206</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.9402999830246</v>
+        <v>11.94729998111725</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.268760356478634</v>
+        <v>-3.074335272335283</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2899594235514774</v>
+        <v>0.2994333163756498</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AE5" t="n">
         <v>11.4</v>
@@ -1975,7 +1975,7 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.41</v>
       </c>
       <c r="CA5" t="n">
         <v>1.67</v>
@@ -2009,16 +2009,16 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54.93000030517578</v>
+        <v>54.93999862670898</v>
       </c>
       <c r="D6" t="n">
-        <v>54.93000030517578</v>
+        <v>54.93999862670898</v>
       </c>
       <c r="E6" t="n">
         <v>55.59999847412109</v>
@@ -2046,67 +2046,67 @@
         <v>55.59999847412109</v>
       </c>
       <c r="H6" t="n">
-        <v>6899100</v>
+        <v>8330000</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.002542207924900231</v>
+        <v>-0.002360651331680508</v>
       </c>
       <c r="J6" t="n">
-        <v>55.36666700575087</v>
+        <v>55.36777793036567</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7886815735715721</v>
+        <v>-0.7726141803897016</v>
       </c>
       <c r="M6" t="n">
-        <v>55.20500030517578</v>
+        <v>55.2060001373291</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4981432813690534</v>
+        <v>-0.4818344200963944</v>
       </c>
       <c r="P6" t="n">
-        <v>52.88999982980582</v>
+        <v>52.89038438063402</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.857062737633695</v>
+        <v>3.875211477618679</v>
       </c>
       <c r="S6" t="n">
-        <v>52.48759979248047</v>
+        <v>52.48779975891113</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.653290534053379</v>
+        <v>4.671940677760133</v>
       </c>
       <c r="V6" t="n">
-        <v>55.95173329671224</v>
+        <v>55.95179995218913</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.826097122171723</v>
+        <v>-1.808344550746764</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.12405000686645</v>
+        <v>56.12409999847412</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.127518775898368</v>
+        <v>-2.10979128716065</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2458684114903697</v>
+        <v>0.2458465071190527</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2291,13 +2291,13 @@
         <v>6</v>
       </c>
       <c r="CM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN6" t="n">
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.38000011444092</v>
+        <v>15.30000019073486</v>
       </c>
       <c r="D7" t="n">
-        <v>15.38000011444092</v>
+        <v>15.30000019073486</v>
       </c>
       <c r="E7" t="n">
         <v>15.98999977111816</v>
@@ -2325,67 +2325,67 @@
         <v>15.81999969482422</v>
       </c>
       <c r="H7" t="n">
-        <v>2141900</v>
+        <v>2599200</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02473052200393278</v>
+        <v>-0.02980344029079751</v>
       </c>
       <c r="J7" t="n">
-        <v>16.64555560217963</v>
+        <v>16.63666672176785</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.60296332537557</v>
+        <v>-8.034461189777014</v>
       </c>
       <c r="M7" t="n">
-        <v>16.48800001144409</v>
+        <v>16.48000001907349</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.720038186766908</v>
+        <v>-7.160193124835708</v>
       </c>
       <c r="P7" t="n">
-        <v>15.69923081764808</v>
+        <v>15.69615389750554</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.033416203093873</v>
+        <v>-2.523890306870876</v>
       </c>
       <c r="S7" t="n">
-        <v>16.53699998855591</v>
+        <v>16.53539999008179</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.996431486458662</v>
+        <v>-7.471242304921175</v>
       </c>
       <c r="V7" t="n">
-        <v>20.28780003229777</v>
+        <v>20.28726669947306</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.19089260562374</v>
+        <v>-24.58323530033613</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.60065000057221</v>
+        <v>21.60025000095368</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-28.79843840794838</v>
+        <v>-29.1674856075307</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5145032642434831</v>
+        <v>0.5167162987325872</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2537,13 +2537,13 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CA7" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="CC7" t="n">
         <v>10</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.54000091552734</v>
+        <v>17.42000007629395</v>
       </c>
       <c r="D8" t="n">
-        <v>17.54000091552734</v>
+        <v>17.42000007629395</v>
       </c>
       <c r="E8" t="n">
         <v>17.61000061035156</v>
@@ -2608,67 +2608,67 @@
         <v>17.55999946594238</v>
       </c>
       <c r="H8" t="n">
-        <v>23165500</v>
+        <v>28709500</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009786992981023257</v>
+        <v>0.002878482132690152</v>
       </c>
       <c r="J8" t="n">
-        <v>17.41777822706435</v>
+        <v>17.40444480048286</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7017122785102621</v>
+        <v>0.08937530607501519</v>
       </c>
       <c r="M8" t="n">
-        <v>17.33800048828125</v>
+        <v>17.32600040435791</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.165073373845078</v>
+        <v>0.5425353211488594</v>
       </c>
       <c r="P8" t="n">
-        <v>15.90576942150409</v>
+        <v>15.9011540046105</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>10.27445734133315</v>
+        <v>9.551797757842339</v>
       </c>
       <c r="S8" t="n">
-        <v>15.64520004272461</v>
+        <v>15.64280002593994</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>12.11106836364079</v>
+        <v>11.36113769534183</v>
       </c>
       <c r="V8" t="n">
-        <v>16.61933338801066</v>
+        <v>16.61853338241577</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.53973800285433</v>
+        <v>4.822728188073514</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.15740006446838</v>
+        <v>16.15680006027222</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.557075058749255</v>
+        <v>7.81837994720128</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3176464852877336</v>
+        <v>0.317195538476921</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2820,13 +2820,13 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>17.9</v>
+        <v>17.78</v>
       </c>
       <c r="CA8" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="CC8" t="n">
         <v>4</v>
@@ -2861,13 +2861,13 @@
         <v>9</v>
       </c>
       <c r="CM8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.09000015258789</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="D9" t="n">
-        <v>22.09000015258789</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="E9" t="n">
         <v>22.32999992370605</v>
@@ -2895,67 +2895,67 @@
         <v>22.28000068664551</v>
       </c>
       <c r="H9" t="n">
-        <v>19332900</v>
+        <v>21927800</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.001356269688394307</v>
+        <v>-0.003616632941720432</v>
       </c>
       <c r="J9" t="n">
-        <v>22.39000023735894</v>
+        <v>22.38444476657444</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.339884241137626</v>
+        <v>-1.538764327813183</v>
       </c>
       <c r="M9" t="n">
-        <v>22.27200012207031</v>
+        <v>22.26700019836426</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8171693987289033</v>
+        <v>-1.019442586853659</v>
       </c>
       <c r="P9" t="n">
-        <v>20.2496154491718</v>
+        <v>20.24769240159255</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>9.088492115001436</v>
+        <v>8.85191496584482</v>
       </c>
       <c r="S9" t="n">
-        <v>20.41360004425049</v>
+        <v>20.41260005950928</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>8.212172790215726</v>
+        <v>7.972530943013978</v>
       </c>
       <c r="V9" t="n">
-        <v>21.86960000356038</v>
+        <v>21.86926667531331</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.007792318979895</v>
+        <v>0.7807040023283507</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.0335000038147</v>
+        <v>22.03325000762939</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2564283875163305</v>
+        <v>0.03063963734633546</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3636908269035047</v>
+        <v>0.3639048005627428</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3123,7 +3123,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.1299991607666</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="D10" t="n">
-        <v>16.1299991607666</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="E10" t="n">
         <v>16.30999946594238</v>
@@ -3194,88 +3194,88 @@
         <v>16.30999946594238</v>
       </c>
       <c r="H10" t="n">
-        <v>3892300</v>
+        <v>5016900</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.002473773366642562</v>
+        <v>-0.004947428777278606</v>
       </c>
       <c r="J10" t="n">
-        <v>15.97777779897054</v>
+        <v>15.97333346472846</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9527067137325463</v>
+        <v>0.7303840999566319</v>
       </c>
       <c r="M10" t="n">
-        <v>15.90900001525879</v>
+        <v>15.90500011444092</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.389145422690591</v>
+        <v>1.163156471649452</v>
       </c>
       <c r="P10" t="n">
-        <v>15.10500001907349</v>
+        <v>15.103461595682</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>6.785826814954131</v>
+        <v>6.531870529521125</v>
       </c>
       <c r="S10" t="n">
-        <v>15.53861776351929</v>
+        <v>15.53781778335571</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>3.80588161860656</v>
+        <v>3.55379614390691</v>
       </c>
       <c r="V10" t="n">
-        <v>16.19927260080973</v>
+        <v>16.19900594075521</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4276330286562816</v>
+        <v>-0.6729165268905024</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29115445613861</v>
+        <v>16.29095446109772</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.9892196148891353</v>
+        <v>-1.233533056578715</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2261559777249185</v>
+        <v>0.2265095375441856</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AE10" t="n">
         <v>15.9</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>16</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>16.1</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>16.2</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>16.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>16.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -3422,7 +3422,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.28000068664551</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="D11" t="n">
-        <v>18.28000068664551</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="E11" t="n">
         <v>18.45999908447266</v>
@@ -3493,67 +3493,67 @@
         <v>18.45000076293945</v>
       </c>
       <c r="H11" t="n">
-        <v>16171300</v>
+        <v>24015700</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.002727727074121944</v>
+        <v>-0.007092152826387865</v>
       </c>
       <c r="J11" t="n">
-        <v>18.12555567423503</v>
+        <v>18.11666679382324</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8520842901937614</v>
+        <v>0.4599851068885537</v>
       </c>
       <c r="M11" t="n">
-        <v>18.05300006866455</v>
+        <v>18.04500007629395</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.257412159295182</v>
+        <v>0.8589675034090752</v>
       </c>
       <c r="P11" t="n">
-        <v>17.15500017312857</v>
+        <v>17.15192325298603</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>6.55785778002574</v>
+        <v>6.11055386905934</v>
       </c>
       <c r="S11" t="n">
-        <v>17.72974044799805</v>
+        <v>17.72814044952393</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>3.10360007954653</v>
+        <v>2.661645843561654</v>
       </c>
       <c r="V11" t="n">
-        <v>18.61678015391032</v>
+        <v>18.61624682108561</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.809010282554546</v>
+        <v>-2.235928982606194</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.79053512573242</v>
+        <v>18.79013512611389</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.716976582469811</v>
+        <v>-3.140660560520878</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2650264360026382</v>
+        <v>0.2656753078636565</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3721,13 +3721,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.16</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM11" t="n">
         <v>7</v>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.45999908447266</v>
+        <v>40.15999984741211</v>
       </c>
       <c r="D12" t="n">
-        <v>40.45999908447266</v>
+        <v>40.15999984741211</v>
       </c>
       <c r="E12" t="n">
         <v>40.59999847412109</v>
@@ -3792,90 +3792,88 @@
         <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>3432500</v>
+        <v>5464500</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01734972639594945</v>
+        <v>0.009806371263752611</v>
       </c>
       <c r="J12" t="n">
-        <v>41.09222200181749</v>
+        <v>41.05888875325521</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.538546436639203</v>
+        <v>-2.189267496363589</v>
       </c>
       <c r="M12" t="n">
-        <v>41.04299964904785</v>
+        <v>41.0129997253418</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.420462854957822</v>
+        <v>-2.079828063399675</v>
       </c>
       <c r="P12" t="n">
-        <v>39.18192291259766</v>
+        <v>39.17038448040302</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.261902624651627</v>
+        <v>2.526437715984617</v>
       </c>
       <c r="S12" t="n">
-        <v>39.95279975891113</v>
+        <v>39.94679977416993</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.269496327221464</v>
+        <v>0.5337100204458483</v>
       </c>
       <c r="V12" t="n">
-        <v>37.01699989318848</v>
+        <v>37.01499989827474</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>9.301129754488095</v>
+        <v>8.496555336432568</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.69434993743896</v>
+        <v>36.69284994125366</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.26220427246656</v>
+        <v>9.449115867831081</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3214107893149382</v>
+        <v>0.3184944036596395</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AE12" t="n">
         <v>35.6</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>39.6</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>40.2</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>40.6</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>43</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
       </c>
       <c r="AJ12" t="n">
         <v>1</v>
@@ -4022,13 +4020,13 @@
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>6.22</v>
+        <v>6.17</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4059,13 +4057,13 @@
         <v>3</v>
       </c>
       <c r="CM12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN12" t="n">
         <v>0</v>
       </c>
       <c r="CO12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -4078,10 +4076,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.050000190734863</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="D13" t="n">
-        <v>4.050000190734863</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="E13" t="n">
         <v>4.119999885559082</v>
@@ -4093,67 +4091,67 @@
         <v>4.099999904632568</v>
       </c>
       <c r="H13" t="n">
-        <v>16322000</v>
+        <v>18533800</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.007352875865728303</v>
+        <v>-0.00980391240220746</v>
       </c>
       <c r="J13" t="n">
-        <v>3.972222248713175</v>
+        <v>3.971111112170749</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.958046079795374</v>
+        <v>1.734749991536275</v>
       </c>
       <c r="M13" t="n">
-        <v>3.958000016212464</v>
+        <v>3.95699999332428</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.324410665627981</v>
+        <v>2.097547856173209</v>
       </c>
       <c r="P13" t="n">
-        <v>3.751923084259033</v>
+        <v>3.756923079490662</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>7.944648645021392</v>
+        <v>7.534806445937227</v>
       </c>
       <c r="S13" t="n">
-        <v>3.664400005340576</v>
+        <v>3.668400001525879</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>10.52287372645741</v>
+        <v>10.12975575653092</v>
       </c>
       <c r="V13" t="n">
-        <v>4.037000006039937</v>
+        <v>4.055866670608521</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3220258775198355</v>
+        <v>-0.391203903976281</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.492100006341934</v>
+        <v>4.507350006103516</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-9.841718015692335</v>
+        <v>-10.36862111035615</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5344946852709516</v>
+        <v>0.5412418264737402</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4305,10 +4303,10 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.7</v>
+        <v>5.69</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CB13" t="n">
         <v>3.21</v>
@@ -4365,10 +4363,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.45999908447266</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="D14" t="n">
-        <v>60.45999908447266</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="E14" t="n">
         <v>60.97999954223633</v>
@@ -4380,67 +4378,67 @@
         <v>60.97999954223633</v>
       </c>
       <c r="H14" t="n">
-        <v>3776200</v>
+        <v>5196200</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0003306954020345643</v>
+        <v>-0.004629609481087038</v>
       </c>
       <c r="J14" t="n">
-        <v>59.72555584377713</v>
+        <v>59.69666714138455</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.229696786107096</v>
+        <v>0.8431519641838877</v>
       </c>
       <c r="M14" t="n">
-        <v>59.35000038146973</v>
+        <v>59.32400054931641</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.870258965237503</v>
+        <v>1.476637120746467</v>
       </c>
       <c r="P14" t="n">
-        <v>54.75653868455153</v>
+        <v>54.74653874910795</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>10.41603530270303</v>
+        <v>9.961290957266892</v>
       </c>
       <c r="S14" t="n">
-        <v>55.42640007019043</v>
+        <v>55.42120010375977</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.081591097216879</v>
+        <v>8.622694294300375</v>
       </c>
       <c r="V14" t="n">
-        <v>56.28446657816569</v>
+        <v>56.28273325602213</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>7.418623219086827</v>
+        <v>6.959980939621797</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.04564992904663</v>
+        <v>56.04434993743897</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.87634573069374</v>
+        <v>7.414932691947262</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3537398803887616</v>
+        <v>0.3542198431372929</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4612,13 +4610,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.59</v>
+        <v>13.53</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CC14" t="n">
         <v>6</v>
@@ -4653,13 +4651,13 @@
         <v>8</v>
       </c>
       <c r="CM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN14" t="n">
         <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -4672,10 +4670,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.48999977111816</v>
+        <v>21.47999954223633</v>
       </c>
       <c r="D15" t="n">
-        <v>21.48999977111816</v>
+        <v>21.47999954223633</v>
       </c>
       <c r="E15" t="n">
         <v>21.79999923706055</v>
@@ -4687,67 +4685,67 @@
         <v>21.79999923706055</v>
       </c>
       <c r="H15" t="n">
-        <v>824300</v>
+        <v>1000000</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.006931590700599899</v>
+        <v>-0.007393708499300877</v>
       </c>
       <c r="J15" t="n">
-        <v>22.39111095004612</v>
+        <v>22.38999981350369</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.024414782001229</v>
+        <v>-4.06431567149245</v>
       </c>
       <c r="M15" t="n">
-        <v>22.38299980163574</v>
+        <v>22.38199977874756</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.989635162541156</v>
+        <v>-4.030025223071041</v>
       </c>
       <c r="P15" t="n">
-        <v>21.62730759840745</v>
+        <v>21.62692297421969</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.6348817422812185</v>
+        <v>-0.6793543037005311</v>
       </c>
       <c r="S15" t="n">
-        <v>21.58099998474121</v>
+        <v>21.58079998016358</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4216681974300955</v>
+        <v>-0.4670838802078724</v>
       </c>
       <c r="V15" t="n">
-        <v>22.64146668752035</v>
+        <v>22.6414000193278</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.085655148996395</v>
+        <v>-5.129543562235748</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.37789998054505</v>
+        <v>22.37784997940064</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3.967754839367439</v>
+        <v>-4.012228332886322</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2790697459079771</v>
+        <v>0.2791746154823112</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,7 +4901,7 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
@@ -4963,10 +4961,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18.02000045776367</v>
+        <v>17.90999984741211</v>
       </c>
       <c r="D16" t="n">
-        <v>18.02000045776367</v>
+        <v>17.90999984741211</v>
       </c>
       <c r="E16" t="n">
         <v>18.10000038146973</v>
@@ -4978,88 +4976,88 @@
         <v>17.70999908447266</v>
       </c>
       <c r="H16" t="n">
-        <v>2049900</v>
+        <v>2712800</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01521129339513649</v>
+        <v>0.009014075910541264</v>
       </c>
       <c r="J16" t="n">
-        <v>18.33333333333333</v>
+        <v>18.32111104329427</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.709088412198147</v>
+        <v>-2.243920660219084</v>
       </c>
       <c r="M16" t="n">
-        <v>18.3</v>
+        <v>18.28899993896484</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.530052143367917</v>
+        <v>-2.072284393993958</v>
       </c>
       <c r="P16" t="n">
-        <v>18.26423065478985</v>
+        <v>18.25115372584416</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.337204953454363</v>
+        <v>-1.869218152214503</v>
       </c>
       <c r="S16" t="n">
-        <v>18.96299991607666</v>
+        <v>18.96079990386963</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.972839015379224</v>
+        <v>-5.541960580698207</v>
       </c>
       <c r="V16" t="n">
-        <v>19.1893332417806</v>
+        <v>19.1817999013265</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.093660312652026</v>
+        <v>-6.630243566592709</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.40249991416931</v>
+        <v>18.37889991283417</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-2.078518995732356</v>
+        <v>-2.551295603359921</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4051434855716536</v>
+        <v>0.4056709841130647</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AE16" t="n">
         <v>17.8</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AF16" t="n">
         <v>17.9</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
         <v>18</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>18.3</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>18.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>18.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
@@ -5186,10 +5184,10 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>36.04</v>
+        <v>35.82</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CB16" t="n">
         <v>0.73</v>
@@ -5223,13 +5221,13 @@
         <v>2</v>
       </c>
       <c r="CM16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -5242,10 +5240,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.360000133514404</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="D17" t="n">
-        <v>5.360000133514404</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="E17" t="n">
         <v>5.539999961853027</v>
@@ -5257,67 +5255,67 @@
         <v>5.139999866485596</v>
       </c>
       <c r="H17" t="n">
-        <v>4100200</v>
+        <v>4810600</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0530451813030377</v>
+        <v>0.04911591208359667</v>
       </c>
       <c r="J17" t="n">
-        <v>5.067777845594618</v>
+        <v>5.065555625491672</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>5.76628054392347</v>
+        <v>5.41785634956047</v>
       </c>
       <c r="M17" t="n">
-        <v>4.985000038146973</v>
+        <v>4.983000040054321</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>7.522569558631869</v>
+        <v>7.16436102074921</v>
       </c>
       <c r="P17" t="n">
-        <v>4.903461529658391</v>
+        <v>4.902692299622756</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>9.31053707864654</v>
+        <v>8.919749114150685</v>
       </c>
       <c r="S17" t="n">
-        <v>5.487999992370606</v>
+        <v>5.487599992752076</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.332358947415199</v>
+        <v>-2.689697506362201</v>
       </c>
       <c r="V17" t="n">
-        <v>8.300199969609578</v>
+        <v>8.300066636403402</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-35.42324096841577</v>
+        <v>-35.66316529114243</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.287849979400635</v>
+        <v>8.287749979496002</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-35.32701307532558</v>
+        <v>-35.5675525227098</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.086040579929696</v>
+        <v>1.084390154748174</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5472,7 +5470,7 @@
         <v>-0.47</v>
       </c>
       <c r="CA17" t="n">
-        <v>10.07</v>
+        <v>10.11</v>
       </c>
       <c r="CB17" t="n">
         <v>-0.27</v>
@@ -5529,10 +5527,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.239999771118164</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="D18" t="n">
-        <v>9.239999771118164</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="E18" t="n">
         <v>9.439999580383301</v>
@@ -5544,67 +5542,67 @@
         <v>9.430000305175781</v>
       </c>
       <c r="H18" t="n">
-        <v>4478100</v>
+        <v>5659000</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01176477068060522</v>
+        <v>-0.009625684376041055</v>
       </c>
       <c r="J18" t="n">
-        <v>9.295555538601345</v>
+        <v>9.297777811686197</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5976594648106446</v>
+        <v>-0.4063076529628345</v>
       </c>
       <c r="M18" t="n">
-        <v>9.243000030517578</v>
+        <v>9.245000076293945</v>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.03245980081692219</v>
+        <v>0.1622515139437886</v>
       </c>
       <c r="P18" t="n">
-        <v>8.479615431565504</v>
+        <v>8.470000046950121</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>8.96720312010987</v>
+        <v>9.327038696017228</v>
       </c>
       <c r="S18" t="n">
-        <v>9.119200019836425</v>
+        <v>9.0846000289917</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32467487300389</v>
+        <v>1.930742127670797</v>
       </c>
       <c r="V18" t="n">
-        <v>10.85693333307902</v>
+        <v>10.82953333536784</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.8930965343074</v>
+        <v>-14.4930816303978</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.38370001316071</v>
+        <v>11.34035001277924</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-18.83131354097708</v>
+        <v>-18.34466997538076</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5352256658246822</v>
+        <v>0.5112223980381628</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5754,7 +5752,7 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="CA18" t="n">
         <v>0.05</v>
@@ -5795,13 +5793,13 @@
         <v>4</v>
       </c>
       <c r="CM18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN18" t="n">
         <v>0</v>
       </c>
       <c r="CO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -5814,10 +5812,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.0600004196167</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="D19" t="n">
-        <v>11.0600004196167</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="E19" t="n">
         <v>11.32999992370605</v>
@@ -5829,88 +5827,90 @@
         <v>11.31999969482422</v>
       </c>
       <c r="H19" t="n">
-        <v>10164500</v>
+        <v>13659000</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01426023561534895</v>
+        <v>-0.01069517671151177</v>
       </c>
       <c r="J19" t="n">
-        <v>11.29222234090169</v>
+        <v>11.29666678110758</v>
       </c>
       <c r="K19" t="n">
         <v>-1</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.056476699399199</v>
+        <v>-1.740924145578589</v>
       </c>
       <c r="M19" t="n">
-        <v>11.24200010299683</v>
+        <v>11.24600009918213</v>
       </c>
       <c r="N19" t="n">
         <v>-1</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.618926184955385</v>
+        <v>-1.298236852434502</v>
       </c>
       <c r="P19" t="n">
-        <v>10.68192309599656</v>
+        <v>10.68346155606783</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>3.539412521719375</v>
+        <v>3.898912568888443</v>
       </c>
       <c r="S19" t="n">
-        <v>10.89479997634888</v>
+        <v>10.89559997558594</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.516323784066256</v>
+        <v>1.875990366219336</v>
       </c>
       <c r="V19" t="n">
-        <v>11.51606672286987</v>
+        <v>11.51633338928223</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.960261035544948</v>
+        <v>-3.615152442529708</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43735003471375</v>
+        <v>11.43755003452301</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-3.299274866570876</v>
+        <v>-2.951240886679633</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2636414128008845</v>
+        <v>0.2622259292276338</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AI19" t="n">
         <v>13.9</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -6037,7 +6037,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.54</v>
+        <v>6.57</v>
       </c>
       <c r="CA19" t="n">
         <v>0.5600000000000001</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.25</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="D20" t="n">
-        <v>6.25</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="E20" t="n">
         <v>6.409999847412109</v>
@@ -6108,67 +6108,67 @@
         <v>6.28000020980835</v>
       </c>
       <c r="H20" t="n">
-        <v>6890700</v>
+        <v>7869800</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001597480593642397</v>
+        <v>-0.009584731217720188</v>
       </c>
       <c r="J20" t="n">
-        <v>6.616666634877522</v>
+        <v>6.611111058129205</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.541561259029784</v>
+        <v>-6.218489528451564</v>
       </c>
       <c r="M20" t="n">
-        <v>6.562999963760376</v>
+        <v>6.557999944686889</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.769159919072095</v>
+        <v>-5.458983507796374</v>
       </c>
       <c r="P20" t="n">
-        <v>6.086538461538462</v>
+        <v>6.084615377279428</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.685624012638228</v>
+        <v>1.896330742885827</v>
       </c>
       <c r="S20" t="n">
-        <v>5.806599979400635</v>
+        <v>5.805599975585937</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>7.636138569427228</v>
+        <v>6.793437979498306</v>
       </c>
       <c r="V20" t="n">
-        <v>5.141599988937378</v>
+        <v>5.141266654332479</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>21.5574920928786</v>
+        <v>20.59284659045018</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.265099992752075</v>
+        <v>5.264849991798401</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.70619757656523</v>
+        <v>17.76213603281224</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5081050952432229</v>
+        <v>0.50931353574746</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6320,13 +6320,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>15.24</v>
+        <v>15.12</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM20" t="n">
         <v>1</v>
@@ -6367,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.400000095367432</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="D21" t="n">
-        <v>2.400000095367432</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="E21" t="n">
-        <v>2.410000085830688</v>
+        <v>2.420000076293945</v>
       </c>
       <c r="F21" t="n">
         <v>2.319999933242798</v>
@@ -6395,67 +6395,67 @@
         <v>2.349999904632568</v>
       </c>
       <c r="H21" t="n">
-        <v>20229000</v>
+        <v>28153400</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02564110401662978</v>
+        <v>0.02136760366190571</v>
       </c>
       <c r="J21" t="n">
-        <v>2.391111135482788</v>
+        <v>2.390000025431315</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3717501772601126</v>
+        <v>3.325224226062859e-06</v>
       </c>
       <c r="M21" t="n">
-        <v>2.386000013351441</v>
+        <v>2.385000014305115</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5867595112175303</v>
+        <v>0.2096474033152975</v>
       </c>
       <c r="P21" t="n">
-        <v>2.233846160081717</v>
+        <v>2.233461545063899</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>7.438020498226118</v>
+        <v>7.008786884476994</v>
       </c>
       <c r="S21" t="n">
-        <v>2.231000008583069</v>
+        <v>2.230800008773804</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>7.575082300949723</v>
+        <v>7.136457571464597</v>
       </c>
       <c r="V21" t="n">
-        <v>2.656800001462301</v>
+        <v>2.656733334859212</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-9.665759784459743</v>
+        <v>-10.03989472542123</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.908249957561493</v>
+        <v>2.908199957609177</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-17.47614096486459</v>
+        <v>-17.81857713563178</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.420389361673026</v>
+        <v>0.4184190903879988</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6465,26 +6465,28 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
         <v>0.9</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AG21" t="n">
         <v>2.4</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AH21" t="n">
         <v>2.5</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AI21" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.7</v>
       </c>
       <c r="AJ21" t="n">
         <v>2</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -6605,7 +6607,7 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>7.27</v>
+        <v>7.24</v>
       </c>
       <c r="CA21" t="n">
         <v>1.08</v>
@@ -6665,10 +6667,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44.88999938964844</v>
+        <v>44.72000122070312</v>
       </c>
       <c r="D22" t="n">
-        <v>44.88999938964844</v>
+        <v>44.72000122070312</v>
       </c>
       <c r="E22" t="n">
         <v>45.18999862670898</v>
@@ -6680,67 +6682,67 @@
         <v>44.72000122070312</v>
       </c>
       <c r="H22" t="n">
-        <v>1369500</v>
+        <v>2129100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.003577014286821667</v>
+        <v>-0.0002235260817242679</v>
       </c>
       <c r="J22" t="n">
-        <v>46.06222237481011</v>
+        <v>46.04333368937174</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.544868494670644</v>
+        <v>-2.874102204667436</v>
       </c>
       <c r="M22" t="n">
-        <v>45.95699996948242</v>
+        <v>45.94000015258789</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.321736798621592</v>
+        <v>-2.655635454576815</v>
       </c>
       <c r="P22" t="n">
-        <v>44.20461566631611</v>
+        <v>44.19807727520283</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.550479996265619</v>
+        <v>1.180874774824472</v>
       </c>
       <c r="S22" t="n">
-        <v>45.13960006713867</v>
+        <v>45.13620010375976</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5529527889458266</v>
+        <v>-0.9220955288656845</v>
       </c>
       <c r="V22" t="n">
-        <v>46.87186650594076</v>
+        <v>46.87073318481445</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.228265832002082</v>
+        <v>-4.588645873387235</v>
       </c>
       <c r="Y22" t="n">
-        <v>48.00039993286133</v>
+        <v>47.9995499420166</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-6.479947141197657</v>
+        <v>-6.832457231943145</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.2668716520817731</v>
+        <v>0.2665625644634913</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6888,13 +6890,13 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>8.98</v>
+        <v>8.94</v>
       </c>
       <c r="CA22" t="n">
         <v>0.5</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CC22" t="n">
         <v>3</v>
@@ -6948,10 +6950,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.93000030517578</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="D23" t="n">
-        <v>15.93000030517578</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="E23" t="n">
         <v>16.07999992370605</v>
@@ -6963,67 +6965,67 @@
         <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>7855800</v>
+        <v>10203400</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0006281550775069089</v>
+        <v>0.001256250250848634</v>
       </c>
       <c r="J23" t="n">
-        <v>15.90666664971246</v>
+        <v>15.90777768029107</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1466910445611636</v>
+        <v>0.2025543777378345</v>
       </c>
       <c r="M23" t="n">
-        <v>15.83599996566772</v>
+        <v>15.83699989318848</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5935863836312728</v>
+        <v>0.6503737317010692</v>
       </c>
       <c r="P23" t="n">
-        <v>14.83153838377732</v>
+        <v>14.81769220645611</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7.40625748303999</v>
+        <v>7.574103701777503</v>
       </c>
       <c r="S23" t="n">
-        <v>14.85919998168945</v>
+        <v>14.84679996490478</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.206312081443435</v>
+        <v>7.363200272534468</v>
       </c>
       <c r="V23" t="n">
-        <v>15.00659993489583</v>
+        <v>15.01266660054525</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>6.153295045420012</v>
+        <v>6.177003756310516</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.52724995613098</v>
+        <v>14.53304995536804</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>9.655993758493791</v>
+        <v>9.681034809183849</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2224032662539245</v>
+        <v>0.1975918648376514</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7175,7 +7177,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.51</v>
+        <v>17.52</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
@@ -7209,16 +7211,16 @@
         <v>0</v>
       </c>
       <c r="CL23" t="n">
+        <v>8</v>
+      </c>
+      <c r="CM23" t="n">
         <v>7</v>
       </c>
-      <c r="CM23" t="n">
-        <v>6</v>
-      </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
@@ -7231,82 +7233,82 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.549999952316284</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="D24" t="n">
-        <v>3.549999952316284</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="E24" t="n">
         <v>3.640000104904175</v>
       </c>
       <c r="F24" t="n">
-        <v>3.519999980926514</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="G24" t="n">
         <v>3.619999885559082</v>
       </c>
       <c r="H24" t="n">
-        <v>24621300</v>
+        <v>29904900</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.01662048324739585</v>
+        <v>-0.01939056378862847</v>
       </c>
       <c r="J24" t="n">
-        <v>3.757777743869358</v>
+        <v>3.756666633817884</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.529273036226088</v>
+        <v>-5.76752459253111</v>
       </c>
       <c r="M24" t="n">
-        <v>3.778999972343445</v>
+        <v>3.777999973297119</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.059804755308116</v>
+        <v>-6.299629781002501</v>
       </c>
       <c r="P24" t="n">
-        <v>3.594230771064758</v>
+        <v>3.593846156046941</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.230605978462845</v>
+        <v>-1.498288793005589</v>
       </c>
       <c r="S24" t="n">
-        <v>3.741000018119812</v>
+        <v>3.740800018310547</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.105588475765965</v>
+        <v>-5.367837240019227</v>
       </c>
       <c r="V24" t="n">
-        <v>4.521333335240682</v>
+        <v>4.521266668637594</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-21.48333933606537</v>
+        <v>-21.70335834405128</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.796300010681152</v>
+        <v>4.796250010728836</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-25.98461429830102</v>
+        <v>-26.19233872432996</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5920768148275406</v>
+        <v>0.5926388514156566</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7458,13 +7460,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7518,10 +7520,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.43000030517578</v>
+        <v>57.25</v>
       </c>
       <c r="D25" t="n">
-        <v>57.43000030517578</v>
+        <v>57.25</v>
       </c>
       <c r="E25" t="n">
         <v>57.65000152587891</v>
@@ -7533,67 +7535,67 @@
         <v>57.09999847412109</v>
       </c>
       <c r="H25" t="n">
-        <v>1863500</v>
+        <v>2388600</v>
       </c>
       <c r="I25" t="n">
-        <v>0.009847043851042514</v>
+        <v>0.006681925008832357</v>
       </c>
       <c r="J25" t="n">
-        <v>56.56888877020942</v>
+        <v>56.548888736301</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.522235196212383</v>
+        <v>1.239832080464799</v>
       </c>
       <c r="M25" t="n">
-        <v>56.44199981689453</v>
+        <v>56.42399978637695</v>
       </c>
       <c r="N25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.750470379303459</v>
+        <v>1.463916448231798</v>
       </c>
       <c r="P25" t="n">
-        <v>55.9553847679725</v>
+        <v>55.9484616793119</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.635341608887142</v>
+        <v>2.326316544945101</v>
       </c>
       <c r="S25" t="n">
-        <v>59.78619979858399</v>
+        <v>59.78259979248047</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.941042416721745</v>
+        <v>-4.23634937468715</v>
       </c>
       <c r="V25" t="n">
-        <v>57.21993316650391</v>
+        <v>57.2187331644694</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>0.367122306942585</v>
+        <v>0.05464440367934797</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.23484991073608</v>
+        <v>54.2339499092102</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.891323382840603</v>
+        <v>5.561184637738511</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2918481347211299</v>
+        <v>0.2907257982818814</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7741,13 +7743,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>16.13</v>
+        <v>16.08</v>
       </c>
       <c r="CA25" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CC25" t="n">
         <v>6</v>
@@ -7801,10 +7803,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.28000020980835</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="D26" t="n">
-        <v>6.28000020980835</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="E26" t="n">
         <v>6.409999847412109</v>
@@ -7816,67 +7818,67 @@
         <v>6.349999904632568</v>
       </c>
       <c r="H26" t="n">
-        <v>18094100</v>
+        <v>20851800</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.01102357415362343</v>
+        <v>-0.02204722339971388</v>
       </c>
       <c r="J26" t="n">
-        <v>6.547777811686198</v>
+        <v>6.540000014834934</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.089595120346485</v>
+        <v>-5.045871191734095</v>
       </c>
       <c r="M26" t="n">
-        <v>6.467000007629395</v>
+        <v>6.459999990463257</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.891600395862584</v>
+        <v>-3.869968307822806</v>
       </c>
       <c r="P26" t="n">
-        <v>5.421923068853525</v>
+        <v>5.419230754558857</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>15.82606632477112</v>
+        <v>14.59191016959172</v>
       </c>
       <c r="S26" t="n">
-        <v>5.24399998664856</v>
+        <v>5.242599983215332</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>19.75591582375074</v>
+        <v>18.45267725992564</v>
       </c>
       <c r="V26" t="n">
-        <v>6.152399994532267</v>
+        <v>6.151933326721191</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>2.07399088793776</v>
+        <v>0.943877450257243</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.983450005054474</v>
+        <v>6.983100004196167</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-10.0730984647557</v>
+        <v>-11.07101381312936</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6684746223091828</v>
+        <v>0.6725170535286589</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8028,13 +8030,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>-4.16</v>
+        <v>-4.11</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.44</v>
+        <v>4.49</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="CC26" t="n">
         <v>2</v>
@@ -8084,13 +8086,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31.29999923706055</v>
+        <v>31.25</v>
       </c>
       <c r="D27" t="n">
-        <v>31.29999923706055</v>
+        <v>31.25</v>
       </c>
       <c r="E27" t="n">
-        <v>31.3700008392334</v>
+        <v>31.38999938964844</v>
       </c>
       <c r="F27" t="n">
         <v>30.69000053405762</v>
@@ -8099,67 +8101,67 @@
         <v>31.09000015258789</v>
       </c>
       <c r="H27" t="n">
-        <v>1991500</v>
+        <v>2414300</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01623376663588894</v>
+        <v>0.01461041474306213</v>
       </c>
       <c r="J27" t="n">
-        <v>32.41444439358182</v>
+        <v>32.40888892279731</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.438112783885738</v>
+        <v>-3.575836634072683</v>
       </c>
       <c r="M27" t="n">
-        <v>32.40299987792969</v>
+        <v>32.39799995422364</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.404007792563724</v>
+        <v>-3.543428470416965</v>
       </c>
       <c r="P27" t="n">
-        <v>31.92153849968543</v>
+        <v>31.91961545210618</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.94708429429556</v>
+        <v>-2.097818042673187</v>
       </c>
       <c r="S27" t="n">
-        <v>31.61720008850098</v>
+        <v>31.61620010375977</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.003254084968117</v>
+        <v>-1.158267288788503</v>
       </c>
       <c r="V27" t="n">
-        <v>33.35853340148926</v>
+        <v>33.35820007324219</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.170937252105971</v>
+        <v>-6.319885571203978</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.64625</v>
+        <v>33.6460000038147</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-6.973290524024089</v>
+        <v>-7.121203125313697</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4241105827909596</v>
+        <v>0.4236024803888934</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8307,13 +8309,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>9.050000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB27" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8367,10 +8369,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20.28000068664551</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="D28" t="n">
-        <v>20.28000068664551</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="E28" t="n">
         <v>20.30999946594238</v>
@@ -8382,67 +8384,67 @@
         <v>20.06999969482422</v>
       </c>
       <c r="H28" t="n">
-        <v>4898000</v>
+        <v>5694700</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01756148399951774</v>
+        <v>0.01204213584762659</v>
       </c>
       <c r="J28" t="n">
-        <v>19.99666680230035</v>
+        <v>19.98444451226128</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.416905563043975</v>
+        <v>0.9284999836688748</v>
       </c>
       <c r="M28" t="n">
-        <v>19.92700004577637</v>
+        <v>19.91599998474121</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.771469062368778</v>
+        <v>1.275356957960117</v>
       </c>
       <c r="P28" t="n">
-        <v>19.09653847034161</v>
+        <v>19.09230767763578</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>6.197260399532122</v>
+        <v>5.64464189900179</v>
       </c>
       <c r="S28" t="n">
-        <v>20.06380004882812</v>
+        <v>20.06160003662109</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.077565751708193</v>
+        <v>0.5403359626100328</v>
       </c>
       <c r="V28" t="n">
-        <v>18.88440008799235</v>
+        <v>18.88366675059001</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>7.390229989569804</v>
+        <v>6.81188321470325</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.30125009059906</v>
+        <v>18.3007000875473</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>10.81210620176645</v>
+        <v>10.21436327465203</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2445219992852302</v>
+        <v>0.2417476278747973</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8602,13 +8604,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>13.89</v>
+        <v>13.82</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8643,13 +8645,13 @@
         <v>3</v>
       </c>
       <c r="CM28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN28" t="n">
         <v>0</v>
       </c>
       <c r="CO28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -8662,10 +8664,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.72999954223633</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="D29" t="n">
-        <v>25.72999954223633</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="E29" t="n">
         <v>25.92000007629395</v>
@@ -8677,86 +8679,88 @@
         <v>25.6299991607666</v>
       </c>
       <c r="H29" t="n">
-        <v>4669000</v>
+        <v>5920100</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01579153650750387</v>
+        <v>0.02250294893569116</v>
       </c>
       <c r="J29" t="n">
-        <v>25.58555560641819</v>
+        <v>25.60444450378418</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5645526641676991</v>
+        <v>1.154311762953547</v>
       </c>
       <c r="M29" t="n">
-        <v>25.49300003051758</v>
+        <v>25.51000003814697</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9296650509357028</v>
+        <v>1.528810583301078</v>
       </c>
       <c r="P29" t="n">
-        <v>23.59730771871714</v>
+        <v>23.60384618318998</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>9.037860797261898</v>
+        <v>9.727878319151023</v>
       </c>
       <c r="S29" t="n">
-        <v>22.65420001983643</v>
+        <v>22.65760002136231</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>13.57717120757597</v>
+        <v>14.31042826297106</v>
       </c>
       <c r="V29" t="n">
-        <v>24.49426667531331</v>
+        <v>24.49540000915527</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>5.044988214194859</v>
+        <v>5.734136241294388</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.87394999504089</v>
+        <v>25.87479999542236</v>
       </c>
       <c r="Z29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.5563528291279608</v>
+        <v>0.09739060055485339</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.3874607871305794</v>
+        <v>0.3893743198450477</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AH29" t="n">
         <v>39.1</v>
       </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
       <c r="AI29" t="inlineStr">
         <is>
           <t>Foguete</t>
@@ -8766,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -8887,7 +8891,7 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>5.94</v>
+        <v>5.98</v>
       </c>
       <c r="CA29" t="n">
         <v>0.42</v>
@@ -8924,13 +8928,13 @@
         <v>9</v>
       </c>
       <c r="CM29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -8943,13 +8947,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.31999969482422</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="D30" t="n">
-        <v>10.31999969482422</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="E30" t="n">
-        <v>10.34000015258789</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="F30" t="n">
         <v>10.10000038146973</v>
@@ -8958,67 +8962,67 @@
         <v>10.18000030517578</v>
       </c>
       <c r="H30" t="n">
-        <v>8814300</v>
+        <v>12532700</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01875612815763406</v>
+        <v>0.01382036937227427</v>
       </c>
       <c r="J30" t="n">
-        <v>10.95666673448351</v>
+        <v>10.951111263699</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-5.810773067100143</v>
+        <v>-6.219558814940465</v>
       </c>
       <c r="M30" t="n">
-        <v>10.97100009918213</v>
+        <v>10.96600017547607</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.933829172113867</v>
+        <v>-6.34688771270411</v>
       </c>
       <c r="P30" t="n">
-        <v>10.84038466673631</v>
+        <v>10.83846161915706</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.800429024524288</v>
+        <v>-5.244850988710667</v>
       </c>
       <c r="S30" t="n">
-        <v>11.41620000839233</v>
+        <v>11.41520002365112</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-9.602147060863254</v>
+        <v>-10.03223389441021</v>
       </c>
       <c r="V30" t="n">
-        <v>13.1424000231425</v>
+        <v>13.14206669489543</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.4755320439821</v>
+        <v>-21.8539922510613</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.64765001773834</v>
+        <v>13.64740002155304</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-24.38258834736425</v>
+        <v>-24.74756773052387</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3884832620112088</v>
+        <v>0.3862247614156276</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9166,13 +9170,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.41</v>
+        <v>6.38</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CC30" t="n">
         <v>9</v>
@@ -9222,10 +9226,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.6299991607666</v>
+        <v>30.52000045776367</v>
       </c>
       <c r="D31" t="n">
-        <v>30.6299991607666</v>
+        <v>30.52000045776367</v>
       </c>
       <c r="E31" t="n">
         <v>30.82999992370605</v>
@@ -9237,67 +9241,67 @@
         <v>30.68000030517578</v>
       </c>
       <c r="H31" t="n">
-        <v>1710300</v>
+        <v>2077000</v>
       </c>
       <c r="I31" t="n">
-        <v>0.005581092626513184</v>
+        <v>0.001969841598636224</v>
       </c>
       <c r="J31" t="n">
-        <v>30.56777742173936</v>
+        <v>30.55555534362793</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2035533632974755</v>
+        <v>-0.1163614454537232</v>
       </c>
       <c r="M31" t="n">
-        <v>30.4129997253418</v>
+        <v>30.4019998550415</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7135088198616176</v>
+        <v>0.3881343440721107</v>
       </c>
       <c r="P31" t="n">
-        <v>29.19192299476037</v>
+        <v>29.1876922754141</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>4.926281034190013</v>
+        <v>4.56462323152497</v>
       </c>
       <c r="S31" t="n">
-        <v>29.90679988861084</v>
+        <v>29.90459991455078</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.418176718503307</v>
+        <v>2.057879205778812</v>
       </c>
       <c r="V31" t="n">
-        <v>32.40166669209798</v>
+        <v>32.4009333674113</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-5.467828393418571</v>
+        <v>-5.805181253017419</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.16226431846619</v>
+        <v>32.16171432495117</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-4.764170652063894</v>
+        <v>-5.104559572291987</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2151945571366529</v>
+        <v>0.2147324212766795</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9445,13 +9449,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.61</v>
+        <v>13.56</v>
       </c>
       <c r="CA31" t="n">
         <v>0.71</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CC31" t="n">
         <v>2</v>
@@ -9501,10 +9505,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>96.19999694824219</v>
+        <v>96.22000122070312</v>
       </c>
       <c r="D32" t="n">
-        <v>96.19999694824219</v>
+        <v>96.22000122070312</v>
       </c>
       <c r="E32" t="n">
         <v>97.52999877929688</v>
@@ -9516,67 +9520,67 @@
         <v>96.68000030517578</v>
       </c>
       <c r="H32" t="n">
-        <v>5606300</v>
+        <v>6223800</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.003315372005322281</v>
+        <v>-0.003108116792343796</v>
       </c>
       <c r="J32" t="n">
-        <v>95.15444437662761</v>
+        <v>95.1566670735677</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.0987953095246</v>
+        <v>1.117456274832886</v>
       </c>
       <c r="M32" t="n">
-        <v>94.85699996948242</v>
+        <v>94.85900039672852</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.415812200672426</v>
+        <v>1.434761929055226</v>
       </c>
       <c r="P32" t="n">
-        <v>96.22615344707782</v>
+        <v>96.30923080444336</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.02718231779889042</v>
+        <v>-0.09264904619725989</v>
       </c>
       <c r="S32" t="n">
-        <v>91.00199981689452</v>
+        <v>91.16979995727539</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>5.711959233650439</v>
+        <v>5.539335685494975</v>
       </c>
       <c r="V32" t="n">
-        <v>83.88839986165364</v>
+        <v>83.90793324788412</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>14.67616155140935</v>
+        <v>14.67330620150804</v>
       </c>
       <c r="Y32" t="n">
-        <v>85.86974983215332</v>
+        <v>85.93054988861084</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.03013533436519</v>
+        <v>11.97414812942567</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2568304827548327</v>
+        <v>0.2614389009956699</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9726,13 +9730,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>42.01</v>
+        <v>42.02</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CC32" t="n">
         <v>8</v>
@@ -9786,10 +9790,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.09000015258789</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="D33" t="n">
-        <v>27.09000015258789</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="E33" t="n">
         <v>27.26000022888184</v>
@@ -9801,67 +9805,67 @@
         <v>27.06999969482422</v>
       </c>
       <c r="H33" t="n">
-        <v>4808700</v>
+        <v>7079500</v>
       </c>
       <c r="I33" t="n">
-        <v>0.005567914460159029</v>
+        <v>0.00148474414943478</v>
       </c>
       <c r="J33" t="n">
-        <v>27.41666687859429</v>
+        <v>27.40444458855523</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.191489568928774</v>
+        <v>-1.548818276346895</v>
       </c>
       <c r="M33" t="n">
-        <v>27.32700023651123</v>
+        <v>27.31600017547607</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.8672744240938992</v>
+        <v>-1.230050633626083</v>
       </c>
       <c r="P33" t="n">
-        <v>26.09346162355863</v>
+        <v>26.0892308308528</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>3.81911201896466</v>
+        <v>3.414315727277455</v>
       </c>
       <c r="S33" t="n">
-        <v>26.13880004882812</v>
+        <v>26.13660003662109</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>3.639035081881703</v>
+        <v>3.226890660734419</v>
       </c>
       <c r="V33" t="n">
-        <v>25.0535999806722</v>
+        <v>25.05286664326986</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>8.128173889128462</v>
+        <v>7.692265026621908</v>
       </c>
       <c r="Y33" t="n">
-        <v>23.94710000991821</v>
+        <v>23.94655000686646</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>13.12434550057409</v>
+        <v>12.66758482745973</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2574719733044071</v>
+        <v>0.2570518491549366</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10013,13 +10017,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>40.43</v>
+        <v>40.27</v>
       </c>
       <c r="CA33" t="n">
         <v>0.35</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CC33" t="n">
         <v>10</v>
@@ -10050,13 +10054,13 @@
         <v>5</v>
       </c>
       <c r="CM33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34">
@@ -10069,10 +10073,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>51.54000091552734</v>
+        <v>51.52999877929688</v>
       </c>
       <c r="D34" t="n">
-        <v>51.54000091552734</v>
+        <v>51.52999877929688</v>
       </c>
       <c r="E34" t="n">
         <v>51.84999847412109</v>
@@ -10084,67 +10088,67 @@
         <v>51.75</v>
       </c>
       <c r="H34" t="n">
-        <v>1906400</v>
+        <v>2327000</v>
       </c>
       <c r="I34" t="n">
-        <v>0.003700145025359758</v>
+        <v>0.003505361451305422</v>
       </c>
       <c r="J34" t="n">
-        <v>51.35666698879666</v>
+        <v>51.35555564032661</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3569817464413656</v>
+        <v>0.3396772497059461</v>
       </c>
       <c r="M34" t="n">
-        <v>51.09900016784668</v>
+        <v>51.09799995422363</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8630320480480843</v>
+        <v>0.8454319649697672</v>
       </c>
       <c r="P34" t="n">
-        <v>47.63115369356596</v>
+        <v>47.63076899601863</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>8.206492849425558</v>
+        <v>8.186367479400078</v>
       </c>
       <c r="S34" t="n">
-        <v>48.65659988403321</v>
+        <v>48.65639984130859</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>5.926022447861865</v>
+        <v>5.905901273749069</v>
       </c>
       <c r="V34" t="n">
-        <v>50.2874666595459</v>
+        <v>50.28739997863769</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>2.490748369690801</v>
+        <v>2.470994326982589</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.90280904769897</v>
+        <v>49.90275903701782</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.280760941259802</v>
+        <v>3.260821192415367</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3080683426964306</v>
+        <v>0.3080543923672593</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10326,7 +10330,7 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM34" t="n">
         <v>7</v>
@@ -10335,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
@@ -10348,10 +10352,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.72999954223633</v>
+        <v>39.54000091552734</v>
       </c>
       <c r="D35" t="n">
-        <v>39.72999954223633</v>
+        <v>39.54000091552734</v>
       </c>
       <c r="E35" t="n">
         <v>40.09000015258789</v>
@@ -10363,67 +10367,67 @@
         <v>39.68999862670898</v>
       </c>
       <c r="H35" t="n">
-        <v>3532400</v>
+        <v>4765900</v>
       </c>
       <c r="I35" t="n">
-        <v>0.006332320235529432</v>
+        <v>0.001519791641001023</v>
       </c>
       <c r="J35" t="n">
-        <v>39.27555550469292</v>
+        <v>39.25444454616971</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.15706584338216</v>
+        <v>0.7274497771119249</v>
       </c>
       <c r="M35" t="n">
-        <v>39.05699996948242</v>
+        <v>39.03800010681152</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.723121523106649</v>
+        <v>1.285928601214971</v>
       </c>
       <c r="P35" t="n">
-        <v>37.04269262460562</v>
+        <v>37.03538498511681</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>7.25462089072235</v>
+        <v>6.762764667944035</v>
       </c>
       <c r="S35" t="n">
-        <v>38.05500015258789</v>
+        <v>38.05120018005371</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>4.401522488325433</v>
+        <v>3.912624906517549</v>
       </c>
       <c r="V35" t="n">
-        <v>39.77886675516764</v>
+        <v>39.77760009765625</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.1228471721733116</v>
+        <v>-0.5973190477695589</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.65635005950928</v>
+        <v>39.65540006637573</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.1857192671956165</v>
+        <v>-0.2910048837112554</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.255784188105852</v>
+        <v>0.2552656279087309</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10571,13 +10575,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.3</v>
+        <v>32.15</v>
       </c>
       <c r="CA35" t="n">
         <v>0.92</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC35" t="n">
         <v>8</v>
@@ -10627,10 +10631,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.3799991607666</v>
+        <v>21.28000068664551</v>
       </c>
       <c r="D36" t="n">
-        <v>21.3799991607666</v>
+        <v>21.28000068664551</v>
       </c>
       <c r="E36" t="n">
         <v>21.52000045776367</v>
@@ -10642,67 +10646,67 @@
         <v>21.40999984741211</v>
       </c>
       <c r="H36" t="n">
-        <v>2769700</v>
+        <v>3334900</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0009346008467380207</v>
+        <v>-0.005607426823543427</v>
       </c>
       <c r="J36" t="n">
-        <v>20.65222210354275</v>
+        <v>20.64111116197374</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>3.523964896247193</v>
+        <v>3.095228351120785</v>
       </c>
       <c r="M36" t="n">
-        <v>20.50799980163574</v>
+        <v>20.49799995422363</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>4.251996135972798</v>
+        <v>3.815009923740107</v>
       </c>
       <c r="P36" t="n">
-        <v>19.29730752798227</v>
+        <v>19.29346143282377</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>10.79265399986137</v>
+        <v>10.29643778924014</v>
       </c>
       <c r="S36" t="n">
-        <v>18.0485998916626</v>
+        <v>18.04659992218017</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>18.45793739736519</v>
+        <v>17.91695265816428</v>
       </c>
       <c r="V36" t="n">
-        <v>16.69086661020915</v>
+        <v>16.69019995371501</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>28.09400290629184</v>
+        <v>27.49997450994514</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.41144998550415</v>
+        <v>16.41094999313355</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>30.27489453796622</v>
+        <v>29.6695236750414</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3723234044701671</v>
+        <v>0.3734766917361963</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10854,13 +10858,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.43</v>
+        <v>18.34</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="CB36" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CC36" t="n">
         <v>9</v>
@@ -10910,13 +10914,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.8700008392334</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="D37" t="n">
-        <v>25.8700008392334</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="E37" t="n">
-        <v>25.93000030517578</v>
+        <v>25.96999931335449</v>
       </c>
       <c r="F37" t="n">
         <v>24.77000045776367</v>
@@ -10925,67 +10929,67 @@
         <v>24.89999961853027</v>
       </c>
       <c r="H37" t="n">
-        <v>8072100</v>
+        <v>9801600</v>
       </c>
       <c r="I37" t="n">
-        <v>0.03232248166612472</v>
+        <v>0.03152437878544201</v>
       </c>
       <c r="J37" t="n">
-        <v>25.56111123826769</v>
+        <v>25.55888896518283</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.208435729129307</v>
+        <v>1.138983062540213</v>
       </c>
       <c r="M37" t="n">
-        <v>25.42000007629395</v>
+        <v>25.41800003051758</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.770262634102478</v>
+        <v>1.699584351378849</v>
       </c>
       <c r="P37" t="n">
-        <v>24.35115381387564</v>
+        <v>24.35038456550011</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>6.23726923564624</v>
+        <v>6.158489250696615</v>
       </c>
       <c r="S37" t="n">
-        <v>24.26539993286133</v>
+        <v>24.26499992370605</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>6.612711559717775</v>
+        <v>6.532043942910478</v>
       </c>
       <c r="V37" t="n">
-        <v>22.40339998881022</v>
+        <v>22.40326665242513</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>15.47354799786922</v>
+        <v>15.38496051722658</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.05614999771118</v>
+        <v>22.05604999542236</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>17.29155288623803</v>
+        <v>17.20140454358229</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.4014196889373084</v>
+        <v>0.4008782786155171</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11137,7 +11141,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>31.17</v>
+        <v>31.14</v>
       </c>
       <c r="CA37" t="n">
         <v>0.16</v>
@@ -11208,7 +11212,7 @@
         <v>11.25</v>
       </c>
       <c r="H38" t="n">
-        <v>6940800</v>
+        <v>8181800</v>
       </c>
       <c r="I38" t="n">
         <v>0.03568239225415692</v>
@@ -11480,10 +11484,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.610000133514404</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="D39" t="n">
-        <v>6.610000133514404</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="E39" t="n">
         <v>6.75</v>
@@ -11495,67 +11499,67 @@
         <v>6.75</v>
       </c>
       <c r="H39" t="n">
-        <v>7385000</v>
+        <v>8387000</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.01636899704041639</v>
+        <v>-0.01339280930962139</v>
       </c>
       <c r="J39" t="n">
-        <v>7.003333356645372</v>
+        <v>7.005555576748318</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-5.616371563374736</v>
+        <v>-5.360823394990704</v>
       </c>
       <c r="M39" t="n">
-        <v>6.963000011444092</v>
+        <v>6.965000009536743</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-5.069652123359357</v>
+        <v>-4.809761588472796</v>
       </c>
       <c r="P39" t="n">
-        <v>7.069230794906616</v>
+        <v>7.070000024942251</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-6.496189963455258</v>
+        <v>-6.223478202956969</v>
       </c>
       <c r="S39" t="n">
-        <v>8.889800004959106</v>
+        <v>8.890200004577636</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-25.64511991465425</v>
+        <v>-25.42349878487461</v>
       </c>
       <c r="V39" t="n">
-        <v>10.35173331896464</v>
+        <v>10.35186665217082</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-36.1459580744346</v>
+        <v>-35.95357883545971</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.31124999284744</v>
+        <v>11.31134999275208</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-41.56260238528746</v>
+        <v>-41.38630562497674</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.118537061685585</v>
+        <v>1.118574399348607</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11707,10 +11711,10 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>-7.78</v>
+        <v>-7.8</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CB39" t="n">
         <v>0.07000000000000001</v>
@@ -11767,10 +11771,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.53000068664551</v>
+        <v>23.3799991607666</v>
       </c>
       <c r="D40" t="n">
-        <v>23.53000068664551</v>
+        <v>23.3799991607666</v>
       </c>
       <c r="E40" t="n">
         <v>23.70000076293945</v>
@@ -11782,88 +11786,88 @@
         <v>23.6299991607666</v>
       </c>
       <c r="H40" t="n">
-        <v>2761500</v>
+        <v>3133900</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-0.006374905291186006</v>
       </c>
       <c r="J40" t="n">
-        <v>22.96444447835286</v>
+        <v>22.9477776421441</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>2.462747177819863</v>
+        <v>1.883500552265771</v>
       </c>
       <c r="M40" t="n">
-        <v>22.84300003051758</v>
+        <v>22.82799987792969</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.007488750208447</v>
+        <v>2.418079927232657</v>
       </c>
       <c r="P40" t="n">
-        <v>21.92653846740723</v>
+        <v>21.92076917795034</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>7.312883525239303</v>
+        <v>6.656837499498271</v>
       </c>
       <c r="S40" t="n">
-        <v>21.47100009918213</v>
+        <v>21.46800006866455</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.589681793824834</v>
+        <v>8.906274855536596</v>
       </c>
       <c r="V40" t="n">
-        <v>22.07346669514974</v>
+        <v>22.07246668497721</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6.598573806332901</v>
+        <v>5.923816737162906</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.63745002746582</v>
+        <v>22.63670001983643</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.942805652124081</v>
+        <v>3.28360202802894</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2597608384258145</v>
+        <v>0.2610778955364331</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE40" t="n">
         <v>23.2</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AF40" t="n">
         <v>23.3</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AG40" t="n">
         <v>23.4</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>23.6</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>23.7</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>23.8</v>
       </c>
       <c r="AJ40" t="n">
         <v>2</v>
@@ -11990,7 +11994,7 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>9.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="CA40" t="n">
         <v>0.38</v>
@@ -12024,7 +12028,7 @@
         <v>0</v>
       </c>
       <c r="CL40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM40" t="n">
         <v>9</v>
@@ -12033,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="CO40" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41">
@@ -12046,10 +12050,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.94000053405762</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="D41" t="n">
-        <v>25.94000053405762</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="E41" t="n">
         <v>26.07999992370605</v>
@@ -12061,67 +12065,67 @@
         <v>25.80999946594238</v>
       </c>
       <c r="H41" t="n">
-        <v>914200</v>
+        <v>1205700</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006987589424551688</v>
+        <v>0.003493794712275733</v>
       </c>
       <c r="J41" t="n">
-        <v>26.19222238328722</v>
+        <v>26.18222236633301</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.9629646753096345</v>
+        <v>-1.268883825883613</v>
       </c>
       <c r="M41" t="n">
-        <v>26.08000011444092</v>
+        <v>26.07100009918213</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.5368082046356282</v>
+        <v>-0.8476840814378093</v>
       </c>
       <c r="P41" t="n">
-        <v>24.69538461245023</v>
+        <v>24.69192306811993</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>5.039872596193169</v>
+        <v>4.690105789471721</v>
       </c>
       <c r="S41" t="n">
-        <v>24.92520004272461</v>
+        <v>24.92340003967285</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>4.071383537919561</v>
+        <v>3.717792678053233</v>
       </c>
       <c r="V41" t="n">
-        <v>26.38693331400554</v>
+        <v>26.38633331298828</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.693765526404303</v>
+        <v>-2.032616374381023</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.42574995994568</v>
+        <v>26.42529995918274</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.838167040194992</v>
+        <v>-2.177078703370009</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3215098518237812</v>
+        <v>0.3211065596122808</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12269,7 +12273,7 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>10.81</v>
+        <v>10.77</v>
       </c>
       <c r="CA41" t="n">
         <v>0.04</v>
@@ -12325,10 +12329,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.47999954223633</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="D42" t="n">
-        <v>27.47999954223633</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="E42" t="n">
         <v>27.54000091552734</v>
@@ -12340,67 +12344,67 @@
         <v>27.29999923706055</v>
       </c>
       <c r="H42" t="n">
-        <v>1572100</v>
+        <v>2576000</v>
       </c>
       <c r="I42" t="n">
-        <v>0.007331336164105196</v>
+        <v>0.004032210419143256</v>
       </c>
       <c r="J42" t="n">
-        <v>27.68111101786296</v>
+        <v>27.67111100090874</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.7265296378344392</v>
+        <v>-1.015902871594405</v>
       </c>
       <c r="M42" t="n">
-        <v>27.60899982452393</v>
+        <v>27.59999980926514</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.467239969240079</v>
+        <v>-0.760871090825885</v>
       </c>
       <c r="P42" t="n">
-        <v>26.59692302116981</v>
+        <v>26.5934614768395</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>3.320220614856975</v>
+        <v>2.995239688908665</v>
       </c>
       <c r="S42" t="n">
-        <v>27.1342000579834</v>
+        <v>27.13240005493164</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.274404565139144</v>
+        <v>0.9494159536025842</v>
       </c>
       <c r="V42" t="n">
-        <v>28.18013334910075</v>
+        <v>28.1795333480835</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.484494300261228</v>
+        <v>-2.801799265738212</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98100001335144</v>
+        <v>27.9805500125885</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-1.790502379743593</v>
+        <v>-2.110575462863934</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1791482873269455</v>
+        <v>0.1783641308868313</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12548,13 +12552,13 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="CA42" t="n">
         <v>0.83</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="CC42" t="n">
         <v>7</v>
@@ -12604,10 +12608,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.17000007629395</v>
+        <v>14.15999984741211</v>
       </c>
       <c r="D43" t="n">
-        <v>14.17000007629395</v>
+        <v>14.15999984741211</v>
       </c>
       <c r="E43" t="n">
         <v>14.18000030517578</v>
@@ -12619,67 +12623,67 @@
         <v>14.11999988555908</v>
       </c>
       <c r="H43" t="n">
-        <v>13562000</v>
+        <v>16749100</v>
       </c>
       <c r="I43" t="n">
-        <v>0.008540917005696258</v>
+        <v>0.007829156952594563</v>
       </c>
       <c r="J43" t="n">
-        <v>14.00222206115723</v>
+        <v>14.0011109246148</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.198224213299275</v>
+        <v>1.134830826302315</v>
       </c>
       <c r="M43" t="n">
-        <v>13.92099981307983</v>
+        <v>13.91999979019165</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.788666522214561</v>
+        <v>1.724138368087974</v>
       </c>
       <c r="P43" t="n">
-        <v>13.13076910605797</v>
+        <v>13.13038448187021</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>7.9144714360754</v>
+        <v>7.841471565158971</v>
       </c>
       <c r="S43" t="n">
-        <v>13.39699989318848</v>
+        <v>13.39679988861084</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>5.769949908699259</v>
+        <v>5.696882577533287</v>
       </c>
       <c r="V43" t="n">
-        <v>13.55199996948242</v>
+        <v>13.55193330128988</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>4.560213313187649</v>
+        <v>4.486935794351621</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.24407739162445</v>
+        <v>13.24402739048004</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.991220734296279</v>
+        <v>6.916117204578411</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2482114870251337</v>
+        <v>0.2480272980481343</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12872,13 +12876,13 @@
         <v>6</v>
       </c>
       <c r="CM43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN43" t="n">
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -12891,13 +12895,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.79000091552734</v>
+        <v>42.66999816894531</v>
       </c>
       <c r="D44" t="n">
-        <v>42.79000091552734</v>
+        <v>42.66999816894531</v>
       </c>
       <c r="E44" t="n">
-        <v>42.79999923706055</v>
+        <v>42.84000015258789</v>
       </c>
       <c r="F44" t="n">
         <v>42.09999847412109</v>
@@ -12906,67 +12910,67 @@
         <v>42.65000152587891</v>
       </c>
       <c r="H44" t="n">
-        <v>13953700</v>
+        <v>16883900</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01038966841226974</v>
+        <v>0.0075560733495601</v>
       </c>
       <c r="J44" t="n">
-        <v>42.16555489434136</v>
+        <v>42.15222125583225</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.480938701626769</v>
+        <v>1.228350245104644</v>
       </c>
       <c r="M44" t="n">
-        <v>41.93699951171875</v>
+        <v>41.92499923706055</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>2.034006757136334</v>
+        <v>1.776980191871315</v>
       </c>
       <c r="P44" t="n">
-        <v>40.03884564913236</v>
+        <v>40.0342301588792</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>6.87121524557389</v>
+        <v>6.583785924209962</v>
       </c>
       <c r="S44" t="n">
-        <v>41.25279968261719</v>
+        <v>41.25039962768555</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>3.72629553566492</v>
+        <v>3.441417668853301</v>
       </c>
       <c r="V44" t="n">
-        <v>42.39066652933757</v>
+        <v>42.38986651102702</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.94203375149435</v>
+        <v>0.6608458128676227</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.01511777877808</v>
+        <v>42.01451776504516</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.844296000380754</v>
+        <v>1.560128352694054</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2691568555097344</v>
+        <v>0.2683161236773978</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13134,13 +13138,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.16</v>
+        <v>10.14</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CC44" t="n">
         <v>10</v>
@@ -13194,10 +13198,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.45000076293945</v>
+        <v>19.42000007629395</v>
       </c>
       <c r="D45" t="n">
-        <v>19.45000076293945</v>
+        <v>19.42000007629395</v>
       </c>
       <c r="E45" t="n">
         <v>19.48999977111816</v>
@@ -13209,67 +13213,67 @@
         <v>19.35000038146973</v>
       </c>
       <c r="H45" t="n">
-        <v>1933900</v>
+        <v>2679000</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01196677720093109</v>
+        <v>0.01040586733010374</v>
       </c>
       <c r="J45" t="n">
-        <v>19.4944445292155</v>
+        <v>19.49111111958821</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.2279817011940857</v>
+        <v>-0.3648383248033732</v>
       </c>
       <c r="M45" t="n">
-        <v>19.45</v>
+        <v>19.44699993133545</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>3.922567886043921e-06</v>
+        <v>-0.1388381505467943</v>
       </c>
       <c r="P45" t="n">
-        <v>18.64307689666748</v>
+        <v>18.64192302410419</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.328276232214723</v>
+        <v>4.17380251588687</v>
       </c>
       <c r="S45" t="n">
-        <v>18.21</v>
+        <v>18.20939998626709</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.80944954936547</v>
+        <v>6.64821515777482</v>
       </c>
       <c r="V45" t="n">
-        <v>18.22346666971842</v>
+        <v>18.22326666514079</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>6.730520133466909</v>
+        <v>6.567063047166973</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.32627569198608</v>
+        <v>18.32612568855286</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>6.131769977927182</v>
+        <v>5.968934221728933</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2005432296444223</v>
+        <v>0.1999341361790651</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13421,7 +13425,7 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.42</v>
+        <v>32.37</v>
       </c>
       <c r="CA45" t="n">
         <v>0.2</v>
@@ -13481,10 +13485,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.22000026702881</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="D46" t="n">
-        <v>11.22000026702881</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="E46" t="n">
         <v>11.35999965667725</v>
@@ -13496,67 +13500,67 @@
         <v>11.31999969482422</v>
       </c>
       <c r="H46" t="n">
-        <v>6490100</v>
+        <v>8446600</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0008920810747372609</v>
+        <v>-0.005352401374890348</v>
       </c>
       <c r="J46" t="n">
-        <v>11.36222224765354</v>
+        <v>11.35444439782037</v>
       </c>
       <c r="K46" t="n">
         <v>-1</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.251709194951718</v>
+        <v>-1.800570526633063</v>
       </c>
       <c r="M46" t="n">
-        <v>11.33200006484985</v>
+        <v>11.325</v>
       </c>
       <c r="N46" t="n">
         <v>-1</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.9883497809751346</v>
+        <v>-1.545257231520758</v>
       </c>
       <c r="P46" t="n">
-        <v>11.1757692190317</v>
+        <v>11.17307688639714</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3957763186607814</v>
+        <v>-0.2065435340820463</v>
       </c>
       <c r="S46" t="n">
-        <v>12.36479999542236</v>
+        <v>12.36339998245239</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-9.258538179488358</v>
+        <v>-9.814455292592015</v>
       </c>
       <c r="V46" t="n">
-        <v>14.03853338241577</v>
+        <v>14.03806671142578</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-20.07711944409641</v>
+        <v>-20.5731113283916</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.10400003910065</v>
+        <v>14.10365003585815</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-20.44809815709373</v>
+        <v>-20.94245397339202</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.3971500568518591</v>
+        <v>0.3965261816948947</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13708,13 +13712,13 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>7.58</v>
+        <v>7.53</v>
       </c>
       <c r="CA46" t="n">
         <v>-0.13</v>
       </c>
       <c r="CB46" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CC46" t="n">
         <v>5</v>
@@ -13749,13 +13753,13 @@
         <v>1</v>
       </c>
       <c r="CM46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN46" t="n">
         <v>0</v>
       </c>
       <c r="CO46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -13768,10 +13772,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.34000015258789</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="D47" t="n">
-        <v>17.34000015258789</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="E47" t="n">
         <v>17.40999984741211</v>
@@ -13783,67 +13787,67 @@
         <v>17.29000091552734</v>
       </c>
       <c r="H47" t="n">
-        <v>2934300</v>
+        <v>3641400</v>
       </c>
       <c r="I47" t="n">
-        <v>0.007553810286516915</v>
+        <v>0.008134881141474537</v>
       </c>
       <c r="J47" t="n">
-        <v>17.54111120435927</v>
+        <v>17.54222234090169</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.146512609311763</v>
+        <v>-1.095767432976708</v>
       </c>
       <c r="M47" t="n">
-        <v>17.61700000762939</v>
+        <v>17.61800003051758</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.572344070622366</v>
+        <v>-1.521169534473989</v>
       </c>
       <c r="P47" t="n">
-        <v>17.51730768497174</v>
+        <v>17.5176923091595</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.012184837833042</v>
+        <v>-0.957271795452716</v>
       </c>
       <c r="S47" t="n">
-        <v>16.78840000152588</v>
+        <v>16.78860000610351</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>3.285602862761652</v>
+        <v>3.343938000560583</v>
       </c>
       <c r="V47" t="n">
-        <v>17.56593337376912</v>
+        <v>17.56600004196167</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-1.286201059595356</v>
+        <v>-1.229646248297632</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.03000006198883</v>
+        <v>18.03005006313324</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-3.826954559227146</v>
+        <v>-3.771757034962628</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4632525127982288</v>
+        <v>0.4633409456891882</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -13991,7 +13995,7 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>64.22</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="CA47" t="n">
         <v>2.04</v>
@@ -14051,10 +14055,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.610000133514404</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="D48" t="n">
-        <v>5.610000133514404</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="E48" t="n">
         <v>5.690000057220459</v>
@@ -14066,67 +14070,67 @@
         <v>5.630000114440918</v>
       </c>
       <c r="H48" t="n">
-        <v>15268600</v>
+        <v>19159000</v>
       </c>
       <c r="I48" t="n">
-        <v>0.007181321475811853</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>5.670000076293945</v>
+        <v>5.665555636088054</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.058200034783042</v>
+        <v>-1.686603584263021</v>
       </c>
       <c r="M48" t="n">
-        <v>5.565000057220459</v>
+        <v>5.561000061035156</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8086266995731429</v>
+        <v>0.1618433829785859</v>
       </c>
       <c r="P48" t="n">
-        <v>4.793846194560711</v>
+        <v>4.792307734489441</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>17.02503388364304</v>
+        <v>16.22793193298112</v>
       </c>
       <c r="S48" t="n">
-        <v>4.817800049781799</v>
+        <v>4.817000050544738</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>16.44319140576381</v>
+        <v>15.6321385346775</v>
       </c>
       <c r="V48" t="n">
-        <v>6.754533327420552</v>
+        <v>6.754266661008199</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-16.94466720979563</v>
+        <v>-17.53360577519823</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.395797542333603</v>
+        <v>7.395597542524338</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-24.14610998472146</v>
+        <v>-24.68492045931194</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.847126113020642</v>
+        <v>0.8471557907548811</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14278,13 +14282,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>31.17</v>
+        <v>30.94</v>
       </c>
       <c r="CA48" t="n">
         <v>0.79</v>
       </c>
       <c r="CB48" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="CC48" t="n">
         <v>2</v>
@@ -14338,10 +14342,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.40999984741211</v>
+        <v>16.36000061035156</v>
       </c>
       <c r="D49" t="n">
-        <v>16.40999984741211</v>
+        <v>16.36000061035156</v>
       </c>
       <c r="E49" t="n">
         <v>16.52000045776367</v>
@@ -14353,67 +14357,67 @@
         <v>16.52000045776367</v>
       </c>
       <c r="H49" t="n">
-        <v>5770800</v>
+        <v>7925600</v>
       </c>
       <c r="I49" t="n">
-        <v>0.001831543845091543</v>
+        <v>-0.001220912786304651</v>
       </c>
       <c r="J49" t="n">
-        <v>16.4522221883138</v>
+        <v>16.4466667175293</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.2566360970476227</v>
+        <v>-0.5269524133140201</v>
       </c>
       <c r="M49" t="n">
-        <v>16.37599992752075</v>
+        <v>16.3710000038147</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2076204203825057</v>
+        <v>-0.0671882808659888</v>
       </c>
       <c r="P49" t="n">
-        <v>15.15269228128287</v>
+        <v>15.15076923370361</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>8.297585292366255</v>
+        <v>7.98132001085434</v>
       </c>
       <c r="S49" t="n">
-        <v>14.94099998474121</v>
+        <v>14.94</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>9.832004980731835</v>
+        <v>9.504689493651695</v>
       </c>
       <c r="V49" t="n">
-        <v>15.27546669006348</v>
+        <v>15.27513336181641</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>7.427158726918861</v>
+        <v>7.102178572443911</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.41505001068115</v>
+        <v>15.41480001449585</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>6.454405506576701</v>
+        <v>6.131773328015027</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3023426117704264</v>
+        <v>0.3026249779306345</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14565,13 +14569,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>9.890000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="CA49" t="n">
         <v>0.93</v>
       </c>
       <c r="CB49" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CC49" t="n">
         <v>5</v>
@@ -14625,10 +14629,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.670000076293945</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="D50" t="n">
-        <v>5.670000076293945</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="E50" t="n">
         <v>5.730000019073486</v>
@@ -14640,67 +14644,67 @@
         <v>5.570000171661377</v>
       </c>
       <c r="H50" t="n">
-        <v>6814100</v>
+        <v>7716800</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02162160025857451</v>
+        <v>0.02522520030167041</v>
       </c>
       <c r="J50" t="n">
-        <v>5.663333310021295</v>
+        <v>5.665555530124241</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.1177180629798683</v>
+        <v>0.4314586092439568</v>
       </c>
       <c r="M50" t="n">
-        <v>5.650999975204468</v>
+        <v>5.652999973297119</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.3362254675782385</v>
+        <v>0.654521211712652</v>
       </c>
       <c r="P50" t="n">
-        <v>5.223461572940533</v>
+        <v>5.221153882833628</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>8.548708497572713</v>
+        <v>8.979742503440233</v>
       </c>
       <c r="S50" t="n">
-        <v>4.991000022888183</v>
+        <v>4.972800025939941</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>13.60448908619398</v>
+        <v>14.42245872625765</v>
       </c>
       <c r="V50" t="n">
-        <v>6.496266670227051</v>
+        <v>6.466000006993611</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-12.71909907454933</v>
+        <v>-12.00123645118825</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.92520001411438</v>
+        <v>6.903650014400482</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-18.12510736530625</v>
+        <v>-17.57983030206402</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.6045750466241533</v>
+        <v>0.5973681690016989</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14848,10 +14852,10 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.2</v>
+        <v>-4.21</v>
       </c>
       <c r="CA50" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CB50" t="n">
         <v>0.61</v>
@@ -14889,13 +14893,13 @@
         <v>9</v>
       </c>
       <c r="CM50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN50" t="n">
         <v>-1</v>
       </c>
       <c r="CO50" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51">
@@ -14908,10 +14912,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30.25</v>
+        <v>30.19000053405762</v>
       </c>
       <c r="D51" t="n">
-        <v>30.25</v>
+        <v>30.19000053405762</v>
       </c>
       <c r="E51" t="n">
         <v>30.34000015258789</v>
@@ -14923,67 +14927,67 @@
         <v>30.02000045776367</v>
       </c>
       <c r="H51" t="n">
-        <v>3972800</v>
+        <v>4824100</v>
       </c>
       <c r="I51" t="n">
-        <v>0.01407978804452381</v>
+        <v>0.01206840802119702</v>
       </c>
       <c r="J51" t="n">
-        <v>30.07888899909126</v>
+        <v>30.07222239176432</v>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5688740728220197</v>
+        <v>0.3916509420519189</v>
       </c>
       <c r="M51" t="n">
-        <v>29.9060001373291</v>
+        <v>29.90000019073486</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>1.150270384174555</v>
+        <v>0.9699008076013829</v>
       </c>
       <c r="P51" t="n">
-        <v>28.19192314147949</v>
+        <v>28.18961546971248</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>7.300235773885206</v>
+        <v>7.096177195089429</v>
       </c>
       <c r="S51" t="n">
-        <v>28.43540008544922</v>
+        <v>28.43420009613037</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>6.381481917250528</v>
+        <v>6.174959844100533</v>
       </c>
       <c r="V51" t="n">
-        <v>30.31160002390544</v>
+        <v>30.31120002746582</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.2032226073742616</v>
+        <v>-0.3998505281822557</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.10845004081726</v>
+        <v>30.10815004348755</v>
       </c>
       <c r="Z51" t="n">
         <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.4701336634428014</v>
+        <v>0.2718549311460391</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2609097304165432</v>
+        <v>0.2601552962619544</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15135,13 +15139,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.71</v>
+        <v>12.68</v>
       </c>
       <c r="CA51" t="n">
         <v>0.29</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CC51" t="n">
         <v>8</v>
@@ -15195,10 +15199,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.889999866485596</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="D52" t="n">
-        <v>7.889999866485596</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="E52" t="n">
         <v>8.130000114440918</v>
@@ -15210,67 +15214,67 @@
         <v>8.060000419616699</v>
       </c>
       <c r="H52" t="n">
-        <v>6241200</v>
+        <v>8054600</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01743460412716524</v>
+        <v>-0.01245328866226092</v>
       </c>
       <c r="J52" t="n">
-        <v>8.643333276112875</v>
+        <v>8.647777716318766</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-8.715774176025667</v>
+        <v>-8.300142667007522</v>
       </c>
       <c r="M52" t="n">
-        <v>8.657999944686889</v>
+        <v>8.661999940872192</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-8.870409830304839</v>
+        <v>-8.450705582201412</v>
       </c>
       <c r="P52" t="n">
-        <v>8.377692204255323</v>
+        <v>8.371538363970243</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-5.821320787149613</v>
+        <v>-5.274281935228671</v>
       </c>
       <c r="S52" t="n">
-        <v>8.418400030136109</v>
+        <v>8.414600019454957</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.27672909055107</v>
+        <v>-5.759040120693973</v>
       </c>
       <c r="V52" t="n">
-        <v>9.114399973551432</v>
+        <v>9.107799975077311</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-13.43368856555401</v>
+        <v>-12.93177441271914</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.809899971485137</v>
+        <v>8.813149971961975</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-10.44166344654273</v>
+        <v>-10.02082282081881</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4411576138944477</v>
+        <v>0.444342617301848</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15422,7 +15426,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>-4.67</v>
+        <v>-4.69</v>
       </c>
       <c r="CA52" t="n">
         <v>0.37</v>
@@ -15482,10 +15486,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>56.16999816894531</v>
+        <v>56.22999954223633</v>
       </c>
       <c r="D53" t="n">
-        <v>56.16999816894531</v>
+        <v>56.22999954223633</v>
       </c>
       <c r="E53" t="n">
         <v>56.65000152587891</v>
@@ -15497,67 +15501,67 @@
         <v>54.63999938964844</v>
       </c>
       <c r="H53" t="n">
-        <v>7717800</v>
+        <v>9475000</v>
       </c>
       <c r="I53" t="n">
-        <v>0.03520088290629597</v>
+        <v>0.03630669520167173</v>
       </c>
       <c r="J53" t="n">
-        <v>53.84999974568685</v>
+        <v>53.85666656494141</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>4.308260787771466</v>
+        <v>4.406758027686529</v>
       </c>
       <c r="M53" t="n">
-        <v>53.70199966430664</v>
+        <v>53.70799980163574</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>4.595729246706323</v>
+        <v>4.695761804415167</v>
       </c>
       <c r="P53" t="n">
-        <v>49.89307667658879</v>
+        <v>49.89538442171537</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>12.58074648922548</v>
+        <v>12.69579379723953</v>
       </c>
       <c r="S53" t="n">
-        <v>48.21539970397949</v>
+        <v>48.21659973144531</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>16.49804525899073</v>
+        <v>16.61958714514025</v>
       </c>
       <c r="V53" t="n">
-        <v>47.98613327026367</v>
+        <v>47.98653327941894</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>17.05464545890608</v>
+        <v>17.17870764869973</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.62504998207092</v>
+        <v>44.62534998893738</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>25.87100337481488</v>
+        <v>26.00461297485788</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3504609276345493</v>
+        <v>0.3513010313368316</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15765,10 +15769,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50.4900016784668</v>
+        <v>50.43000030517578</v>
       </c>
       <c r="D54" t="n">
-        <v>50.4900016784668</v>
+        <v>50.43000030517578</v>
       </c>
       <c r="E54" t="n">
         <v>50.70000076293945</v>
@@ -15780,67 +15784,67 @@
         <v>49.06000137329102</v>
       </c>
       <c r="H54" t="n">
-        <v>40518500</v>
+        <v>46405700</v>
       </c>
       <c r="I54" t="n">
-        <v>0.03209328635090047</v>
+        <v>0.03086676600059701</v>
       </c>
       <c r="J54" t="n">
-        <v>48.54555553860135</v>
+        <v>48.53888871934679</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>4.005405063949279</v>
+        <v>3.896075158958531</v>
       </c>
       <c r="M54" t="n">
-        <v>48.37799987792969</v>
+        <v>48.37199974060059</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>4.365624469523832</v>
+        <v>4.254528602520916</v>
       </c>
       <c r="P54" t="n">
-        <v>44.84961539048415</v>
+        <v>44.79499992957482</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>12.5762199717311</v>
+        <v>12.579529823552</v>
       </c>
       <c r="S54" t="n">
-        <v>43.145</v>
+        <v>43.05459999084473</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>17.02399276501749</v>
+        <v>17.13034220710303</v>
       </c>
       <c r="V54" t="n">
-        <v>43.32846661885579</v>
+        <v>43.2908666229248</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>16.52847566152833</v>
+        <v>16.49108516222318</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.65170002937317</v>
+        <v>40.60295002937317</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>24.20145194908183</v>
+        <v>24.20279873431237</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3298900882277963</v>
+        <v>0.3190298227506866</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -15992,7 +15996,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="CA54" t="n">
         <v>0.5</v>
@@ -16048,10 +16052,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.46999979019165</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="D55" t="n">
-        <v>4.46999979019165</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="E55" t="n">
         <v>4.480000019073486</v>
@@ -16063,67 +16067,67 @@
         <v>4.449999809265137</v>
       </c>
       <c r="H55" t="n">
-        <v>8109700</v>
+        <v>9910500</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00902933711129017</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>4.529999944898817</v>
+        <v>4.525555504692925</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.324506742538313</v>
+        <v>-2.111468443049981</v>
       </c>
       <c r="M55" t="n">
-        <v>4.523999929428101</v>
+        <v>4.519999933242798</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.193637048603504</v>
+        <v>-1.991152792774621</v>
       </c>
       <c r="P55" t="n">
-        <v>4.406923055648804</v>
+        <v>4.405384595577534</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>1.431310094284374</v>
+        <v>0.5587533216918229</v>
       </c>
       <c r="S55" t="n">
-        <v>4.820399980545044</v>
+        <v>4.819599981307984</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-7.269110276483199</v>
+        <v>-8.083661600140257</v>
       </c>
       <c r="V55" t="n">
-        <v>5.762199986775716</v>
+        <v>5.761933320363362</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-22.42546596004431</v>
+        <v>-23.11608652806736</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.818468115329742</v>
+        <v>5.818268115520477</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-23.17565892619267</v>
+        <v>-23.86050727842173</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4603625756069936</v>
+        <v>0.4585959792486243</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16275,13 +16279,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="CA55" t="n">
         <v>0.28</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CC55" t="n">
         <v>9</v>
@@ -16335,10 +16339,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>65.51000213623047</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="D56" t="n">
-        <v>65.51000213623047</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="E56" t="n">
         <v>66.08000183105469</v>
@@ -16350,67 +16354,67 @@
         <v>63.90000152587891</v>
       </c>
       <c r="H56" t="n">
-        <v>7064700</v>
+        <v>8324300</v>
       </c>
       <c r="I56" t="n">
-        <v>0.02503524163101911</v>
+        <v>0.02769520359864841</v>
       </c>
       <c r="J56" t="n">
-        <v>63.15777884589301</v>
+        <v>63.17666753133138</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>3.724360377012237</v>
+        <v>3.962432448028244</v>
       </c>
       <c r="M56" t="n">
-        <v>63.24100112915039</v>
+        <v>63.25800094604492</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3.587863832905394</v>
+        <v>3.828763670854332</v>
       </c>
       <c r="P56" t="n">
-        <v>61.80038510836088</v>
+        <v>61.80692349947416</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>6.002579144717534</v>
+        <v>6.266412541524693</v>
       </c>
       <c r="S56" t="n">
-        <v>59.92680023193359</v>
+        <v>59.9302001953125</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>9.31670284862251</v>
+        <v>9.59416135958946</v>
       </c>
       <c r="V56" t="n">
-        <v>60.83660003662109</v>
+        <v>60.8377333577474</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>7.681892309557377</v>
+        <v>7.959315181836479</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.32489999771119</v>
+        <v>56.32574998855591</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.30735631824029</v>
+        <v>16.60741369359564</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.368283430789936</v>
+        <v>0.3696793709745642</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16562,7 +16566,7 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>22.06</v>
+        <v>22.11</v>
       </c>
       <c r="CA56" t="n">
         <v>0.42</v>
@@ -16596,16 +16600,16 @@
         <v>0</v>
       </c>
       <c r="CL56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57">
@@ -16618,10 +16622,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50.54999923706055</v>
+        <v>50.45000076293945</v>
       </c>
       <c r="D57" t="n">
-        <v>50.54999923706055</v>
+        <v>50.45000076293945</v>
       </c>
       <c r="E57" t="n">
         <v>50.61999893188477</v>
@@ -16633,67 +16637,67 @@
         <v>50.47000122070312</v>
       </c>
       <c r="H57" t="n">
-        <v>618900</v>
+        <v>803300</v>
       </c>
       <c r="I57" t="n">
-        <v>0.01019181279381143</v>
+        <v>0.008193442044580168</v>
       </c>
       <c r="J57" t="n">
-        <v>50.93333350287543</v>
+        <v>50.92222256130643</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.7526196293302634</v>
+        <v>-0.9273393316610543</v>
       </c>
       <c r="M57" t="n">
-        <v>50.78199996948242</v>
+        <v>50.77200012207031</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.4568562336286381</v>
+        <v>-0.6342065673140287</v>
       </c>
       <c r="P57" t="n">
-        <v>48.95653856717623</v>
+        <v>48.95269247201773</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>3.254847496413235</v>
+        <v>3.058684242501292</v>
       </c>
       <c r="S57" t="n">
-        <v>51.3810001373291</v>
+        <v>51.37900016784668</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-1.617331110814289</v>
+        <v>-1.808130562822041</v>
       </c>
       <c r="V57" t="n">
-        <v>50.9008667755127</v>
+        <v>50.90020011901856</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-0.6893154491839505</v>
+        <v>-0.8844746288352788</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.25510007858276</v>
+        <v>50.25460008621216</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.5868044397815462</v>
+        <v>0.3888214738393787</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.2580769263819558</v>
+        <v>0.2573157541806157</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16841,7 +16845,7 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.869999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="CA57" t="n">
         <v>-0.4</v>
@@ -16916,7 +16920,7 @@
         <v>19.70999908447266</v>
       </c>
       <c r="H58" t="n">
-        <v>6698000</v>
+        <v>8515900</v>
       </c>
       <c r="I58" t="n">
         <v>-0.004605944133624473</v>
@@ -16940,43 +16944,43 @@
         <v>-2.000299071341201</v>
       </c>
       <c r="P58" t="n">
-        <v>19.01846159421481</v>
+        <v>18.98615389603835</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.269054027250641</v>
+        <v>2.443079675014592</v>
       </c>
       <c r="S58" t="n">
-        <v>18.74700008392334</v>
+        <v>18.78580005645752</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>3.749936927876682</v>
+        <v>3.535653017096921</v>
       </c>
       <c r="V58" t="n">
-        <v>20.59053340911865</v>
+        <v>20.54206673940023</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-5.539111704964899</v>
+        <v>-5.316241984386907</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.43685688972473</v>
+        <v>21.4200313949585</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-9.268411582005902</v>
+        <v>-9.197141664706976</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.5027982282791218</v>
+        <v>0.4615542916954481</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17165,13 +17169,13 @@
         <v>5</v>
       </c>
       <c r="CM58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
@@ -17184,10 +17188,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.71000003814697</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="D59" t="n">
-        <v>14.71000003814697</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="E59" t="n">
         <v>14.78999996185303</v>
@@ -17199,88 +17203,88 @@
         <v>14.61999988555908</v>
       </c>
       <c r="H59" t="n">
-        <v>4357900</v>
+        <v>6998800</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0116918897345224</v>
+        <v>0.01100411608197271</v>
       </c>
       <c r="J59" t="n">
-        <v>14.6777778201633</v>
+        <v>14.67666668362088</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.219530629080682</v>
+        <v>0.1589810966430142</v>
       </c>
       <c r="M59" t="n">
-        <v>14.74000005722046</v>
+        <v>14.73900003433227</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.2035279440775265</v>
+        <v>-0.2646056379421455</v>
       </c>
       <c r="P59" t="n">
-        <v>14.25653853783241</v>
+        <v>14.25615391364464</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>3.180726507428295</v>
+        <v>3.113363522230814</v>
       </c>
       <c r="S59" t="n">
-        <v>14.07139999389648</v>
+        <v>14.07119998931885</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>4.538283642903214</v>
+        <v>4.468700753479435</v>
       </c>
       <c r="V59" t="n">
-        <v>14.87646668752035</v>
+        <v>14.8764000193278</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-1.118993191528598</v>
+        <v>-1.18577216150063</v>
       </c>
       <c r="Y59" t="n">
-        <v>14.92965002536774</v>
+        <v>14.92960002422333</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-1.471233329967853</v>
+        <v>-1.537885908434681</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3156762492517876</v>
+        <v>0.3154888056591661</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
       </c>
       <c r="AD59" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AE59" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AF59" t="n">
         <v>14.6</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AG59" t="n">
         <v>14.7</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
         <v>14.8</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AI59" t="n">
         <v>15.1</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>15.2</v>
       </c>
       <c r="AJ59" t="n">
         <v>2</v>
@@ -17407,7 +17411,7 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>26.27</v>
+        <v>26.25</v>
       </c>
       <c r="CA59" t="n">
         <v>0.64</v>
@@ -17467,10 +17471,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37.13999938964844</v>
+        <v>36.93999862670898</v>
       </c>
       <c r="D60" t="n">
-        <v>37.13999938964844</v>
+        <v>36.93999862670898</v>
       </c>
       <c r="E60" t="n">
         <v>37.40000152587891</v>
@@ -17482,88 +17486,88 @@
         <v>37.38999938964844</v>
       </c>
       <c r="H60" t="n">
-        <v>2786200</v>
+        <v>3377300</v>
       </c>
       <c r="I60" t="n">
-        <v>0.002429153966023945</v>
+        <v>-0.002968977398561723</v>
       </c>
       <c r="J60" t="n">
-        <v>37.32222239176432</v>
+        <v>37.30000008477105</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.4882426351869473</v>
+        <v>-0.9651513599032071</v>
       </c>
       <c r="M60" t="n">
-        <v>37.15800018310547</v>
+        <v>37.13800010681152</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.04844392423793158</v>
+        <v>-0.5331506261324632</v>
       </c>
       <c r="P60" t="n">
-        <v>35.33576935988206</v>
+        <v>35.3300002171443</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>5.105959378982075</v>
+        <v>4.557029152757861</v>
       </c>
       <c r="S60" t="n">
-        <v>35.03580009460449</v>
+        <v>35.01120010375976</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>6.005854838086014</v>
+        <v>5.509089997580785</v>
       </c>
       <c r="V60" t="n">
-        <v>36.74206667582194</v>
+        <v>36.69033335367838</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1.083043905334694</v>
+        <v>0.6804660797816678</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.3418999671936</v>
+        <v>38.28334997177124</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-3.134692278091453</v>
+        <v>-3.508970207813035</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3393191908587323</v>
+        <v>0.3358218586297237</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AF60" t="n">
         <v>36.8</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>37</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AH60" t="n">
         <v>37.1</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AI60" t="n">
         <v>37.7</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>38.6</v>
       </c>
       <c r="AJ60" t="n">
         <v>2</v>
@@ -17690,13 +17694,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>18.39</v>
+        <v>18.29</v>
       </c>
       <c r="CA60" t="n">
         <v>0.09</v>
       </c>
       <c r="CB60" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CC60" t="n">
         <v>9</v>
@@ -17728,7 +17732,7 @@
         <v>0</v>
       </c>
       <c r="CL60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM60" t="n">
         <v>5</v>
@@ -17737,7 +17741,7 @@
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -17750,10 +17754,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.40999984741211</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="D61" t="n">
-        <v>11.40999984741211</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="E61" t="n">
         <v>11.52999973297119</v>
@@ -17765,67 +17769,67 @@
         <v>11.35000038146973</v>
       </c>
       <c r="H61" t="n">
-        <v>1482300</v>
+        <v>1799200</v>
       </c>
       <c r="I61" t="n">
-        <v>0.003518026583609002</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>11.40666654374864</v>
+        <v>11.40222210354275</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.02922241700220746</v>
+        <v>-0.2825959509564161</v>
       </c>
       <c r="M61" t="n">
-        <v>11.3979998588562</v>
+        <v>11.3939998626709</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.1052815292551931</v>
+        <v>-0.2106369791213181</v>
       </c>
       <c r="P61" t="n">
-        <v>10.88269222699679</v>
+        <v>10.88115376692552</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>4.845378417550253</v>
+        <v>4.49259452724091</v>
       </c>
       <c r="S61" t="n">
-        <v>10.60619997024536</v>
+        <v>10.6053999710083</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>7.578584973145221</v>
+        <v>7.209533979302495</v>
       </c>
       <c r="V61" t="n">
-        <v>11.59346668243408</v>
+        <v>11.59320001602173</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-1.582501938785519</v>
+        <v>-1.925267658232292</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.40294999599457</v>
+        <v>11.4027499961853</v>
       </c>
       <c r="Z61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.06182480340629022</v>
+        <v>-0.287212388565718</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3560479697692505</v>
+        <v>0.3561978460319686</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17973,7 +17977,7 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="CA61" t="n">
         <v>0.45</v>
@@ -18014,13 +18018,13 @@
         <v>8</v>
       </c>
       <c r="CM61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN61" t="n">
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -18033,10 +18037,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>35.95999908447266</v>
+        <v>35.68000030517578</v>
       </c>
       <c r="D62" t="n">
-        <v>35.95999908447266</v>
+        <v>35.68000030517578</v>
       </c>
       <c r="E62" t="n">
         <v>36.27999877929688</v>
@@ -18048,88 +18052,90 @@
         <v>35.97000122070312</v>
       </c>
       <c r="H62" t="n">
-        <v>4642900</v>
+        <v>5723200</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0103961486456432</v>
+        <v>0.002528804501321424</v>
       </c>
       <c r="J62" t="n">
-        <v>36.27555550469292</v>
+        <v>36.24444452921549</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.8698872169702409</v>
+        <v>-1.557326181629658</v>
       </c>
       <c r="M62" t="n">
-        <v>36.11199989318848</v>
+        <v>36.08400001525879</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.420914956705263</v>
+        <v>-1.119608995433343</v>
       </c>
       <c r="P62" t="n">
-        <v>34.97576918968787</v>
+        <v>34.90653844980093</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>2.814033594077379</v>
+        <v>2.215807953822641</v>
       </c>
       <c r="S62" t="n">
-        <v>36.70859992980957</v>
+        <v>36.62259994506836</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.03930644799397</v>
+        <v>-2.57381955761311</v>
       </c>
       <c r="V62" t="n">
-        <v>42.85233334859213</v>
+        <v>42.75246668497721</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-16.08391825026702</v>
+        <v>-16.5428264804347</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.42585000991821</v>
+        <v>43.39110000610351</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-17.19218143971943</v>
+        <v>-17.77115514435695</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4435598109068563</v>
+        <v>0.4071202080782061</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
       </c>
-      <c r="AD62" t="n">
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE62" t="n">
         <v>26.7</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AF62" t="n">
         <v>35.3</v>
       </c>
-      <c r="AF62" t="n">
+      <c r="AG62" t="n">
         <v>35.7</v>
       </c>
-      <c r="AG62" t="n">
+      <c r="AH62" t="n">
         <v>36.5</v>
       </c>
-      <c r="AH62" t="n">
+      <c r="AI62" t="n">
         <v>37.2</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>37.6</v>
       </c>
       <c r="AJ62" t="n">
         <v>1</v>
@@ -18256,13 +18262,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>17.98</v>
+        <v>17.84</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CB62" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CC62" t="n">
         <v>10</v>
@@ -18293,13 +18299,13 @@
         <v>2</v>
       </c>
       <c r="CM62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN62" t="n">
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -18312,10 +18318,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30.07999992370605</v>
+        <v>30.06999969482422</v>
       </c>
       <c r="D63" t="n">
-        <v>30.07999992370605</v>
+        <v>30.06999969482422</v>
       </c>
       <c r="E63" t="n">
         <v>30.5</v>
@@ -18327,67 +18333,67 @@
         <v>30.48999977111816</v>
       </c>
       <c r="H63" t="n">
-        <v>2196900</v>
+        <v>2723600</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.009548926819676229</v>
+        <v>-0.009878206655220878</v>
       </c>
       <c r="J63" t="n">
-        <v>30.23666678534614</v>
+        <v>30.23555564880371</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.5181353578166562</v>
+        <v>-0.5475538663898922</v>
       </c>
       <c r="M63" t="n">
-        <v>30.14700012207031</v>
+        <v>30.14600009918213</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.2222449931766456</v>
+        <v>-0.2521077559472686</v>
       </c>
       <c r="P63" t="n">
-        <v>29.7615385055542</v>
+        <v>29.76115388136644</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.070043533174278</v>
+        <v>1.037748115173559</v>
       </c>
       <c r="S63" t="n">
-        <v>28.5838000869751</v>
+        <v>28.58360008239746</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>5.234432903176982</v>
+        <v>5.200183350389523</v>
       </c>
       <c r="V63" t="n">
-        <v>29.38800000508626</v>
+        <v>29.38793333689372</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>2.35470232237657</v>
+        <v>2.320906169588433</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.53714998245239</v>
+        <v>30.53709998130798</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-1.497029221813526</v>
+        <v>-1.52961573551411</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.181055760963719</v>
+        <v>0.1812306376215479</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18615,10 +18621,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.02000045776367</v>
+        <v>26.93000030517578</v>
       </c>
       <c r="D64" t="n">
-        <v>27.02000045776367</v>
+        <v>26.93000030517578</v>
       </c>
       <c r="E64" t="n">
         <v>27.35000038146973</v>
@@ -18630,88 +18636,88 @@
         <v>27.13999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>9722900</v>
+        <v>13559500</v>
       </c>
       <c r="I64" t="n">
-        <v>0.006706419677811493</v>
+        <v>0.003353209838905746</v>
       </c>
       <c r="J64" t="n">
-        <v>26.73888927035862</v>
+        <v>26.7288892534044</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1.051319613775736</v>
+        <v>0.752410808637558</v>
       </c>
       <c r="M64" t="n">
-        <v>26.57500038146973</v>
+        <v>26.56600036621094</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.674506377822047</v>
+        <v>1.370172152176184</v>
       </c>
       <c r="P64" t="n">
-        <v>25.38769245147705</v>
+        <v>25.38423090714675</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>6.42952489442046</v>
+        <v>6.089486830163657</v>
       </c>
       <c r="S64" t="n">
-        <v>26.99100006103516</v>
+        <v>26.9892000579834</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>0.1074446914265406</v>
+        <v>-0.2193460816935446</v>
       </c>
       <c r="V64" t="n">
-        <v>29.15763614654541</v>
+        <v>29.15703614552816</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-7.331306550496911</v>
+        <v>-7.638073462737529</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.5727983379364</v>
+        <v>28.57234833717346</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-5.434532039205497</v>
+        <v>-5.748033072454665</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3248190307500361</v>
+        <v>0.3243206096615594</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
       </c>
       <c r="AD64" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE64" t="n">
         <v>26.4</v>
       </c>
-      <c r="AE64" t="n">
+      <c r="AF64" t="n">
         <v>26.6</v>
       </c>
-      <c r="AF64" t="n">
+      <c r="AG64" t="n">
         <v>27</v>
       </c>
-      <c r="AG64" t="n">
+      <c r="AH64" t="n">
         <v>27.1</v>
       </c>
-      <c r="AH64" t="n">
+      <c r="AI64" t="n">
         <v>27.4</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>28.4</v>
       </c>
       <c r="AJ64" t="n">
         <v>1</v>
@@ -18838,13 +18844,13 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
       </c>
       <c r="CB64" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CC64" t="n">
         <v>9</v>
@@ -18913,7 +18919,7 @@
         <v>17.30999946594238</v>
       </c>
       <c r="H65" t="n">
-        <v>2994300</v>
+        <v>3613000</v>
       </c>
       <c r="I65" t="n">
         <v>0.03573480796847361</v>
@@ -19185,10 +19191,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.06999969482422</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="D66" t="n">
-        <v>17.06999969482422</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="E66" t="n">
         <v>17.25</v>
@@ -19200,67 +19206,67 @@
         <v>17.23999977111816</v>
       </c>
       <c r="H66" t="n">
-        <v>2849700</v>
+        <v>3664700</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.001170301789648831</v>
+        <v>0.000585150894824471</v>
       </c>
       <c r="J66" t="n">
-        <v>17.59222221374512</v>
+        <v>17.59555562337239</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.968485234985701</v>
+        <v>-2.81636597621513</v>
       </c>
       <c r="M66" t="n">
-        <v>17.55499992370606</v>
+        <v>17.5579999923706</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-2.762746972313563</v>
+        <v>-2.608495336028534</v>
       </c>
       <c r="P66" t="n">
-        <v>17.30923087780292</v>
+        <v>17.31038475036621</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-1.38210175060689</v>
+        <v>-1.215365065135445</v>
       </c>
       <c r="S66" t="n">
-        <v>18.60440010070801</v>
+        <v>18.60500011444092</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-8.247513478413083</v>
+        <v>-8.089221842052206</v>
       </c>
       <c r="V66" t="n">
-        <v>18.94760003407796</v>
+        <v>18.9478000386556</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-9.909436212907222</v>
+        <v>-9.752053818470529</v>
       </c>
       <c r="Y66" t="n">
-        <v>20.04694096565247</v>
+        <v>20.04709096908569</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-14.84985303208508</v>
+        <v>-14.70083910010001</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3383835449780145</v>
+        <v>0.3385676150678854</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19412,13 +19418,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.24</v>
+        <v>15.27</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CC66" t="n">
         <v>10</v>
@@ -19472,10 +19478,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>47.54000091552734</v>
+        <v>47.56000137329102</v>
       </c>
       <c r="D67" t="n">
-        <v>47.54000091552734</v>
+        <v>47.56000137329102</v>
       </c>
       <c r="E67" t="n">
         <v>47.77000045776367</v>
@@ -19487,67 +19493,67 @@
         <v>47.72999954223633</v>
       </c>
       <c r="H67" t="n">
-        <v>1623500</v>
+        <v>2648000</v>
       </c>
       <c r="I67" t="n">
-        <v>0.005074031339069141</v>
+        <v>0.00549687400474097</v>
       </c>
       <c r="J67" t="n">
-        <v>47.27111095852322</v>
+        <v>47.27333323160807</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5688251271269051</v>
+        <v>0.6064056035110974</v>
       </c>
       <c r="M67" t="n">
-        <v>47.11999969482422</v>
+        <v>47.12199974060059</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.8913438527659029</v>
+        <v>0.929505613304957</v>
       </c>
       <c r="P67" t="n">
-        <v>44.93423095116248</v>
+        <v>44.93500019953801</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>5.79907546920517</v>
+        <v>5.84177403381873</v>
       </c>
       <c r="S67" t="n">
-        <v>43.53460006713867</v>
+        <v>43.53500007629395</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>9.200499929278278</v>
+        <v>9.24543767070945</v>
       </c>
       <c r="V67" t="n">
-        <v>46.13486676534017</v>
+        <v>46.13500010172526</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>3.045709782439019</v>
+        <v>3.088763993548719</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.20100004196167</v>
+        <v>47.20110004425049</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.7182069728698585</v>
+        <v>0.7603664505786132</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.271269369018211</v>
+        <v>0.271294622020356</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19755,10 +19761,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40.81999969482422</v>
+        <v>40.79999923706055</v>
       </c>
       <c r="D68" t="n">
-        <v>40.81999969482422</v>
+        <v>40.79999923706055</v>
       </c>
       <c r="E68" t="n">
         <v>40.97999954223633</v>
@@ -19770,67 +19776,67 @@
         <v>40.59999847412109</v>
       </c>
       <c r="H68" t="n">
-        <v>647800</v>
+        <v>1316300</v>
       </c>
       <c r="I68" t="n">
-        <v>0.007652465715512813</v>
+        <v>0.007158749137078813</v>
       </c>
       <c r="J68" t="n">
-        <v>41.11333296034071</v>
+        <v>41.11111068725586</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.7134747888220437</v>
+        <v>-0.7567575893583307</v>
       </c>
       <c r="M68" t="n">
-        <v>40.97499961853028</v>
+        <v>40.97299957275391</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.3782792560075128</v>
+        <v>-0.4222300966424742</v>
       </c>
       <c r="P68" t="n">
-        <v>39.18499961266151</v>
+        <v>39.18423036428598</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>4.172515243905754</v>
+        <v>4.123518205546384</v>
       </c>
       <c r="S68" t="n">
-        <v>39.78379974365235</v>
+        <v>39.78339973449707</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>2.604577636748242</v>
+        <v>2.555335917362447</v>
       </c>
       <c r="V68" t="n">
-        <v>41.05293329874674</v>
+        <v>41.05279996236165</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-0.567398198388022</v>
+        <v>-0.6157941127837361</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.19400005340576</v>
+        <v>41.19390005111694</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-0.9079000779158839</v>
+        <v>-0.9562115108489561</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2078105486096099</v>
+        <v>0.2076731199625885</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20036,10 +20042,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.65999984741211</v>
+        <v>19.63999938964844</v>
       </c>
       <c r="D69" t="n">
-        <v>19.65999984741211</v>
+        <v>19.63999938964844</v>
       </c>
       <c r="E69" t="n">
         <v>19.77000045776367</v>
@@ -20051,67 +20057,67 @@
         <v>19.76000022888184</v>
       </c>
       <c r="H69" t="n">
-        <v>3845200</v>
+        <v>5017600</v>
       </c>
       <c r="I69" t="n">
-        <v>0.003061197182379072</v>
+        <v>0.00204076568368472</v>
       </c>
       <c r="J69" t="n">
-        <v>19.27000003390842</v>
+        <v>19.26777776082357</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>2.02387033117502</v>
+        <v>1.931834762915394</v>
       </c>
       <c r="M69" t="n">
-        <v>19.21800003051758</v>
+        <v>19.21599998474121</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>2.29992619519538</v>
+        <v>2.206491492734762</v>
       </c>
       <c r="P69" t="n">
-        <v>18.72961535820594</v>
+        <v>18.72884610983042</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>4.967451127065154</v>
+        <v>4.864972857776715</v>
       </c>
       <c r="S69" t="n">
-        <v>19.89340003967285</v>
+        <v>19.89300003051758</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-1.173254404954802</v>
+        <v>-1.27180737184444</v>
       </c>
       <c r="V69" t="n">
-        <v>23.25373334248861</v>
+        <v>23.25360000610351</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-15.45443667967982</v>
+        <v>-15.53996205106561</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.30630001068115</v>
+        <v>23.30620000839233</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-15.64512668934135</v>
+        <v>-15.73058077860713</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2147224399632758</v>
+        <v>0.2146469429276038</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20259,13 +20265,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="CA69" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CC69" t="n">
         <v>1</v>
@@ -20319,10 +20325,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>33.90999984741211</v>
+        <v>33.83000183105469</v>
       </c>
       <c r="D70" t="n">
-        <v>33.90999984741211</v>
+        <v>33.83000183105469</v>
       </c>
       <c r="E70" t="n">
         <v>34.54000091552734</v>
@@ -20334,67 +20340,67 @@
         <v>34.36999893188477</v>
       </c>
       <c r="H70" t="n">
-        <v>3017700</v>
+        <v>3591300</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.01338373868978848</v>
+        <v>-0.0157112923366759</v>
       </c>
       <c r="J70" t="n">
-        <v>33.97111087375217</v>
+        <v>33.96222220526801</v>
       </c>
       <c r="K70" t="n">
         <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.1798911627210729</v>
+        <v>-0.3893160271262115</v>
       </c>
       <c r="M70" t="n">
-        <v>34.07299995422363</v>
+        <v>34.06500015258789</v>
       </c>
       <c r="N70" t="n">
         <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.4783849588545496</v>
+        <v>-0.6898526947910549</v>
       </c>
       <c r="P70" t="n">
-        <v>32.75653839111328</v>
+        <v>32.73923081618089</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>3.52131669875031</v>
+        <v>3.331694079797064</v>
       </c>
       <c r="S70" t="n">
-        <v>31.27999984741211</v>
+        <v>31.34499988555908</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>8.407928429761762</v>
+        <v>7.927905422135498</v>
       </c>
       <c r="V70" t="n">
-        <v>32.79613328297933</v>
+        <v>32.7553999710083</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>3.396335033834193</v>
+        <v>3.280686118922413</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.5870999622345</v>
+        <v>35.53229996681213</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-4.712663062183061</v>
+        <v>-4.790847024671708</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3915529069171073</v>
+        <v>0.3788156888899826</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20542,13 +20548,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>22.02</v>
+        <v>21.97</v>
       </c>
       <c r="CA70" t="n">
         <v>0.17</v>
       </c>
       <c r="CB70" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CC70" t="n">
         <v>7</v>
@@ -20602,10 +20608,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.40999984741211</v>
+        <v>38.43000030517578</v>
       </c>
       <c r="D71" t="n">
-        <v>38.40999984741211</v>
+        <v>38.43000030517578</v>
       </c>
       <c r="E71" t="n">
         <v>38.7599983215332</v>
@@ -20617,67 +20623,67 @@
         <v>38.5</v>
       </c>
       <c r="H71" t="n">
-        <v>5293000</v>
+        <v>6385500</v>
       </c>
       <c r="I71" t="n">
-        <v>0.001042504994549276</v>
+        <v>0.001563757491824136</v>
       </c>
       <c r="J71" t="n">
-        <v>37.81888877020942</v>
+        <v>37.82111104329427</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1.563004880429798</v>
+        <v>1.609919024283833</v>
       </c>
       <c r="M71" t="n">
-        <v>37.56599998474121</v>
+        <v>37.56800003051758</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2.246712088094872</v>
+        <v>2.294506691753547</v>
       </c>
       <c r="P71" t="n">
-        <v>34.84923076629639</v>
+        <v>34.83923075749324</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>10.21764039784613</v>
+        <v>10.30668436015981</v>
       </c>
       <c r="S71" t="n">
-        <v>33.28819995880127</v>
+        <v>33.34979995727539</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>15.38623264384908</v>
+        <v>15.23307592371966</v>
       </c>
       <c r="V71" t="n">
-        <v>29.41873336791992</v>
+        <v>29.44773337046305</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>30.56306458556384</v>
+        <v>30.50240513153453</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.64770000457764</v>
+        <v>27.69275000572205</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>38.92656474517792</v>
+        <v>38.77278456359566</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3427333549245754</v>
+        <v>0.3427808864848846</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20829,7 +20835,7 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>14.28</v>
+        <v>14.29</v>
       </c>
       <c r="CA71" t="n">
         <v>0.33</v>
@@ -20885,13 +20891,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7.230000019073486</v>
+        <v>7.260000228881836</v>
       </c>
       <c r="D72" t="n">
-        <v>7.230000019073486</v>
+        <v>7.260000228881836</v>
       </c>
       <c r="E72" t="n">
-        <v>7.25</v>
+        <v>7.269999980926514</v>
       </c>
       <c r="F72" t="n">
         <v>6.929999828338623</v>
@@ -20900,67 +20906,67 @@
         <v>7.050000190734863</v>
       </c>
       <c r="H72" t="n">
-        <v>9435600</v>
+        <v>10709200</v>
       </c>
       <c r="I72" t="n">
-        <v>0.02844947415308674</v>
+        <v>0.03271692919049807</v>
       </c>
       <c r="J72" t="n">
-        <v>7.523333390553792</v>
+        <v>7.526666747199164</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.89898142555548</v>
+        <v>-3.542956361347616</v>
       </c>
       <c r="M72" t="n">
-        <v>7.530000066757202</v>
+        <v>7.533000087738037</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-3.984064342949079</v>
+        <v>-3.624052245805503</v>
       </c>
       <c r="P72" t="n">
-        <v>7.033461534059965</v>
+        <v>7.034615388283362</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>2.794335108847495</v>
+        <v>3.203939777203279</v>
       </c>
       <c r="S72" t="n">
-        <v>7.540799961090088</v>
+        <v>7.541399965286255</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-4.121577864686826</v>
+        <v>-3.731399179193878</v>
       </c>
       <c r="V72" t="n">
-        <v>7.906600001653035</v>
+        <v>7.906800003051758</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-8.557407513192672</v>
+        <v>-8.180297641527277</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.46420000076294</v>
+        <v>7.464350001811981</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-3.137643440228226</v>
+        <v>-2.737676728456452</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.5183534011022374</v>
+        <v>0.5206012581756374</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21112,7 +21118,7 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>-3.48</v>
+        <v>-3.49</v>
       </c>
       <c r="CA72" t="n">
         <v>-0.05</v>
@@ -21172,10 +21178,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74.83999633789062</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="D73" t="n">
-        <v>74.83999633789062</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="E73" t="n">
         <v>75.94000244140625</v>
@@ -21187,67 +21193,67 @@
         <v>75.83999633789062</v>
       </c>
       <c r="H73" t="n">
-        <v>13231400</v>
+        <v>18005300</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.008479159917580747</v>
+        <v>-0.01165878171270196</v>
       </c>
       <c r="J73" t="n">
-        <v>78.08222198486328</v>
+        <v>78.05555555555556</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-4.152322467976362</v>
+        <v>-4.427048218207854</v>
       </c>
       <c r="M73" t="n">
-        <v>78.10400009155273</v>
+        <v>78.08000030517579</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-4.179048127926965</v>
+        <v>-4.456969540795468</v>
       </c>
       <c r="P73" t="n">
-        <v>76.2196153494028</v>
+        <v>76.21038466233473</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-1.810057693400555</v>
+        <v>-2.113079727059212</v>
       </c>
       <c r="S73" t="n">
-        <v>75.44640014648438</v>
+        <v>75.44160018920898</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-0.8037544633228083</v>
+        <v>-1.115567157877268</v>
       </c>
       <c r="V73" t="n">
-        <v>80.03453348795573</v>
+        <v>80.03293350219727</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-6.490369748762038</v>
+        <v>-6.788374223377698</v>
       </c>
       <c r="Y73" t="n">
-        <v>78.95045009613037</v>
+        <v>78.94925010681152</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-5.206371532061994</v>
+        <v>-5.508920764676375</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2591369895131538</v>
+        <v>0.2602258735763535</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21395,13 +21401,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>21.32</v>
+        <v>21.25</v>
       </c>
       <c r="CA73" t="n">
         <v>0.21</v>
       </c>
       <c r="CB73" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21466,7 +21472,7 @@
         <v>3.25</v>
       </c>
       <c r="H74" t="n">
-        <v>7365400</v>
+        <v>8100300</v>
       </c>
       <c r="I74" t="n">
         <v>0.02160491760393746</v>
@@ -21713,13 +21719,13 @@
         <v>7</v>
       </c>
       <c r="CM74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN74" t="n">
         <v>-1</v>
       </c>
       <c r="CO74" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
@@ -21732,10 +21738,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.77999877929688</v>
+        <v>38.7599983215332</v>
       </c>
       <c r="D75" t="n">
-        <v>38.77999877929688</v>
+        <v>38.7599983215332</v>
       </c>
       <c r="E75" t="n">
         <v>38.91999816894531</v>
@@ -21747,67 +21753,67 @@
         <v>37.97999954223633</v>
       </c>
       <c r="H75" t="n">
-        <v>6618200</v>
+        <v>9707800</v>
       </c>
       <c r="I75" t="n">
-        <v>0.02864716165786141</v>
+        <v>0.02811664554754523</v>
       </c>
       <c r="J75" t="n">
-        <v>37.5477778116862</v>
+        <v>37.54555553860135</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>3.28174139569764</v>
+        <v>3.234584667906328</v>
       </c>
       <c r="M75" t="n">
-        <v>37.27600021362305</v>
+        <v>37.27400016784668</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>4.034763807958579</v>
+        <v>3.986688166000429</v>
       </c>
       <c r="P75" t="n">
-        <v>35.18576930119441</v>
+        <v>35.18500005281889</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>10.21500893538927</v>
+        <v>10.16057485675036</v>
       </c>
       <c r="S75" t="n">
-        <v>34.74259983062744</v>
+        <v>34.74219982147217</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>11.6208889615401</v>
+        <v>11.56460592796966</v>
       </c>
       <c r="V75" t="n">
-        <v>32.37959986368815</v>
+        <v>32.37946652730306</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>19.76676346388827</v>
+        <v>19.70548770113289</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.84949115753174</v>
+        <v>30.84939115524292</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>25.70709377755473</v>
+        <v>25.64266868827931</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2897762823337975</v>
+        <v>0.2893644514791855</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21959,7 +21965,7 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.45</v>
+        <v>15.44</v>
       </c>
       <c r="CA75" t="n">
         <v>0.39</v>
@@ -22015,10 +22021,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.5</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="D76" t="n">
-        <v>22.5</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="E76" t="n">
         <v>22.69000053405762</v>
@@ -22030,67 +22036,67 @@
         <v>22.45999908447266</v>
       </c>
       <c r="H76" t="n">
-        <v>1109200</v>
+        <v>1344600</v>
       </c>
       <c r="I76" t="n">
-        <v>0.00446430282021093</v>
+        <v>0.001785755187881932</v>
       </c>
       <c r="J76" t="n">
-        <v>22.81333308749729</v>
+        <v>22.80666648017036</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.373464746670481</v>
+        <v>-1.607713895546916</v>
       </c>
       <c r="M76" t="n">
-        <v>22.78199977874756</v>
+        <v>22.77599983215332</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-1.237818371900014</v>
+        <v>-1.475234020775532</v>
       </c>
       <c r="P76" t="n">
-        <v>21.97923080737774</v>
+        <v>21.97692313561073</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>2.369369506995902</v>
+        <v>2.107107512682407</v>
       </c>
       <c r="S76" t="n">
-        <v>22.17060009002686</v>
+        <v>22.16940010070801</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>1.48575098840613</v>
+        <v>1.220603318630026</v>
       </c>
       <c r="V76" t="n">
-        <v>24.36373335520426</v>
+        <v>24.36333335876465</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-7.649621377941068</v>
+        <v>-7.894374699819627</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.12460001945496</v>
+        <v>26.12430002212524</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-13.87427947894215</v>
+        <v>-14.10295963890827</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3032451029995589</v>
+        <v>0.3029767619231912</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22238,7 +22244,7 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.07</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
@@ -22298,13 +22304,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30.79999923706055</v>
+        <v>30.77000045776367</v>
       </c>
       <c r="D77" t="n">
-        <v>30.79999923706055</v>
+        <v>30.77000045776367</v>
       </c>
       <c r="E77" t="n">
-        <v>30.81999969482422</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="F77" t="n">
         <v>30.40999984741211</v>
@@ -22313,67 +22319,67 @@
         <v>30.64999961853027</v>
       </c>
       <c r="H77" t="n">
-        <v>2868400</v>
+        <v>3885400</v>
       </c>
       <c r="I77" t="n">
-        <v>0.009505047722162541</v>
+        <v>0.008521803570349151</v>
       </c>
       <c r="J77" t="n">
-        <v>30.31555557250977</v>
+        <v>30.31222237481011</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1.59800358397547</v>
+        <v>1.510209569239568</v>
       </c>
       <c r="M77" t="n">
-        <v>30.28299999237061</v>
+        <v>30.28000011444092</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1.707225984282245</v>
+        <v>1.618230982400386</v>
       </c>
       <c r="P77" t="n">
-        <v>29.94269231649546</v>
+        <v>29.94153851729173</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>2.863159102405762</v>
+        <v>2.766931766026294</v>
       </c>
       <c r="S77" t="n">
-        <v>31.90960018157959</v>
+        <v>31.90900020599365</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-3.477326378910829</v>
+        <v>-3.569525027036216</v>
       </c>
       <c r="V77" t="n">
-        <v>36.08820011138916</v>
+        <v>36.08800011952718</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-14.65354564097449</v>
+        <v>-14.73619941296205</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.69810011863709</v>
+        <v>35.6979501247406</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-13.72090073504882</v>
+        <v>-13.80457323111557</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1720794255311011</v>
+        <v>0.1715544678397566</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22521,7 +22527,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.63</v>
+        <v>15.62</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
@@ -22581,10 +22587,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.75</v>
+        <v>50.88000106811523</v>
       </c>
       <c r="D78" t="n">
-        <v>50.75</v>
+        <v>50.88000106811523</v>
       </c>
       <c r="E78" t="n">
         <v>51.29000091552734</v>
@@ -22596,76 +22602,76 @@
         <v>51.13999938964844</v>
       </c>
       <c r="H78" t="n">
-        <v>5825400</v>
+        <v>7047000</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0001970500828234467</v>
+        <v>0.002759152247088892</v>
       </c>
       <c r="J78" t="n">
-        <v>51.57000054253472</v>
+        <v>51.58444510565864</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.590072782447207</v>
+        <v>-1.365613289239644</v>
       </c>
       <c r="M78" t="n">
-        <v>51.3830005645752</v>
+        <v>51.39600067138672</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-1.231926040947491</v>
+        <v>-1.00396839546068</v>
       </c>
       <c r="P78" t="n">
-        <v>49.77076955942007</v>
+        <v>49.75692352881799</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>1.967481011943862</v>
+        <v>2.257128173623496</v>
       </c>
       <c r="S78" t="n">
-        <v>47.90140022277832</v>
+        <v>47.93140029907227</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>5.946798556980592</v>
+        <v>6.15171004945591</v>
       </c>
       <c r="V78" t="n">
-        <v>47.2557334391276</v>
+        <v>47.228466796875</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>7.394375891707471</v>
+        <v>7.731638392889457</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.46885005950928</v>
+        <v>47.49170007705688</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>6.91221703575568</v>
+        <v>7.134511894837874</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.1965717927319637</v>
+        <v>0.1858147832677375</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="AE78" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="AF78" t="n">
         <v>50</v>
@@ -22804,13 +22810,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>33.83</v>
+        <v>33.92</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12</v>
+        <v>12.03</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22845,13 +22851,13 @@
         <v>7</v>
       </c>
       <c r="CM78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO78" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79">
@@ -22864,13 +22870,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10.21000003814697</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="D79" t="n">
-        <v>10.21000003814697</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="E79" t="n">
-        <v>10.22000026702881</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="F79" t="n">
         <v>9.800000190734863</v>
@@ -22879,67 +22885,67 @@
         <v>9.979999542236328</v>
       </c>
       <c r="H79" t="n">
-        <v>3724200</v>
+        <v>5987500</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02923386689744567</v>
+        <v>0.02318543754711899</v>
       </c>
       <c r="J79" t="n">
-        <v>9.857777807447645</v>
+        <v>9.8511110941569</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>3.573038848909946</v>
+        <v>3.034059016456083</v>
       </c>
       <c r="M79" t="n">
-        <v>9.753999996185303</v>
+        <v>9.747999954223634</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>4.675005558130064</v>
+        <v>4.123919431621054</v>
       </c>
       <c r="P79" t="n">
-        <v>8.658461497380184</v>
+        <v>8.656153788933388</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>17.91933291192947</v>
+        <v>17.25761655836937</v>
       </c>
       <c r="S79" t="n">
-        <v>8.490600004196168</v>
+        <v>8.489399995803833</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>20.25063049844599</v>
+        <v>19.56085970206666</v>
       </c>
       <c r="V79" t="n">
-        <v>9.927866636912029</v>
+        <v>9.927466634114584</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>2.841833110307562</v>
+        <v>2.241588842524848</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.69909998416901</v>
+        <v>10.69879998207092</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-4.57141205097376</v>
+        <v>-5.129550645496047</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5504005319419378</v>
+        <v>0.5485694979112793</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23087,10 +23093,10 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>23.74</v>
+        <v>23.6</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CB79" t="n">
         <v>0.93</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.61999988555908</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="D2" t="n">
-        <v>15.61999988555908</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="E2" t="n">
         <v>15.77000045776367</v>
@@ -912,67 +912,67 @@
         <v>15.69999980926514</v>
       </c>
       <c r="H2" t="n">
-        <v>16175800</v>
+        <v>25452400</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.006992985370526394</v>
+        <v>-0.008264409698013231</v>
       </c>
       <c r="J2" t="n">
-        <v>15.71999984317356</v>
+        <v>15.71777767605252</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6361320522398123</v>
+        <v>-0.7493253627211878</v>
       </c>
       <c r="M2" t="n">
-        <v>15.70799989700317</v>
+        <v>15.70599994659424</v>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5602241661644015</v>
+        <v>-0.6748985450461358</v>
       </c>
       <c r="P2" t="n">
-        <v>15.26923069587121</v>
+        <v>15.26846148417546</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.297228961133737</v>
+        <v>2.171396886568286</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51159996032715</v>
+        <v>15.51119997024536</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.69883136174979</v>
+        <v>0.5724922081767281</v>
       </c>
       <c r="V2" t="n">
-        <v>15.69493333180746</v>
+        <v>15.69480000178019</v>
       </c>
       <c r="W2" t="n">
         <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.477437174559464</v>
+        <v>-0.6040192949238823</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.31254999637604</v>
+        <v>15.31244999885559</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.00782945528868</v>
+        <v>1.87788618173856</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1737575096995765</v>
+        <v>0.17421066095594</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>15.78</v>
+        <v>15.76</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
@@ -1165,13 +1165,13 @@
         <v>3</v>
       </c>
       <c r="CM2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN2" t="n">
         <v>1</v>
       </c>
       <c r="CO2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.59000015258789</v>
+        <v>28.48999977111816</v>
       </c>
       <c r="D3" t="n">
-        <v>28.59000015258789</v>
+        <v>28.48999977111816</v>
       </c>
       <c r="E3" t="n">
         <v>28.81999969482422</v>
@@ -1199,67 +1199,67 @@
         <v>28.53000068664551</v>
       </c>
       <c r="H3" t="n">
-        <v>4056600</v>
+        <v>7418100</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002103030651887439</v>
+        <v>-0.001402065004017627</v>
       </c>
       <c r="J3" t="n">
-        <v>28.75888888041179</v>
+        <v>28.74777772691515</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5872574859417732</v>
+        <v>-0.8966882875111316</v>
       </c>
       <c r="M3" t="n">
-        <v>28.73600006103516</v>
+        <v>28.72600002288818</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5080731769806597</v>
+        <v>-0.8215562611640309</v>
       </c>
       <c r="P3" t="n">
-        <v>27.11615386376014</v>
+        <v>27.11230769524207</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>5.435307294068348</v>
+        <v>5.081426824164663</v>
       </c>
       <c r="S3" t="n">
-        <v>27.22639999389649</v>
+        <v>27.22439998626709</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>5.008374808998221</v>
+        <v>4.648770167531642</v>
       </c>
       <c r="V3" t="n">
-        <v>28.9113333384196</v>
+        <v>28.9106666692098</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.111443675289415</v>
+        <v>-1.455057757418132</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.96549999237061</v>
+        <v>28.96499999046326</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.296369266477779</v>
+        <v>-1.639910994308597</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2628876563275886</v>
+        <v>0.2629959484657652</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.43</v>
+        <v>17.37</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.02000045776367</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="D4" t="n">
-        <v>10.02000045776367</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="E4" t="n">
-        <v>10.06999969482422</v>
+        <v>10.1899995803833</v>
       </c>
       <c r="F4" t="n">
         <v>9.619999885559082</v>
@@ -1482,67 +1482,67 @@
         <v>9.619999885559082</v>
       </c>
       <c r="H4" t="n">
-        <v>10089700</v>
+        <v>14110100</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03834205739479102</v>
+        <v>0.0476683996197953</v>
       </c>
       <c r="J4" t="n">
-        <v>9.499999894036186</v>
+        <v>9.509999805026585</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>5.473690205553858</v>
+        <v>6.309146834404002</v>
       </c>
       <c r="M4" t="n">
-        <v>9.46299991607666</v>
+        <v>9.471999835968017</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>5.886088414105612</v>
+        <v>6.735640115686585</v>
       </c>
       <c r="P4" t="n">
-        <v>8.699615350136391</v>
+        <v>8.703076857786913</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>15.17751135521849</v>
+        <v>16.16580919461277</v>
       </c>
       <c r="S4" t="n">
-        <v>8.572399959564208</v>
+        <v>8.57419994354248</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>16.88675872600156</v>
+        <v>17.91187193262771</v>
       </c>
       <c r="V4" t="n">
-        <v>8.70833327293396</v>
+        <v>8.708933267593384</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>15.06220701160411</v>
+        <v>16.08769232734092</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.556999940872192</v>
+        <v>8.55744993686676</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.09711963305635</v>
+        <v>18.14266786559711</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5291491121664802</v>
+        <v>0.534788737308172</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1692,13 +1692,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>19.27</v>
+        <v>19.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1758,7 +1758,7 @@
         <v>11.61999988555908</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67000007629395</v>
+        <v>11.68000030517578</v>
       </c>
       <c r="F5" t="n">
         <v>11.47000026702881</v>
@@ -1767,7 +1767,7 @@
         <v>11.52000045776367</v>
       </c>
       <c r="H5" t="n">
-        <v>886600</v>
+        <v>1829700</v>
       </c>
       <c r="I5" t="n">
         <v>0.003454228162052209</v>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.22000122070312</v>
+        <v>55.20999908447266</v>
       </c>
       <c r="D6" t="n">
-        <v>55.22000122070312</v>
+        <v>55.20999908447266</v>
       </c>
       <c r="E6" t="n">
-        <v>55.47999954223633</v>
+        <v>55.56999969482422</v>
       </c>
       <c r="F6" t="n">
         <v>54.45000076293945</v>
@@ -2046,67 +2046,67 @@
         <v>54.56000137329102</v>
       </c>
       <c r="H6" t="n">
-        <v>2930700</v>
+        <v>5000100</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005096516217567126</v>
+        <v>0.004914460584504177</v>
       </c>
       <c r="J6" t="n">
-        <v>55.33000013563368</v>
+        <v>55.32888878716363</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1988051954833008</v>
+        <v>-0.2148781681633086</v>
       </c>
       <c r="M6" t="n">
-        <v>55.35300025939942</v>
+        <v>55.35200004577636</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2402743086608139</v>
+        <v>-0.2565416989201341</v>
       </c>
       <c r="P6" t="n">
-        <v>53.01999987088717</v>
+        <v>53.01961517333984</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.149380149327307</v>
+        <v>4.131270858854169</v>
       </c>
       <c r="S6" t="n">
-        <v>52.55519981384278</v>
+        <v>52.55499977111816</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>5.070480972956845</v>
+        <v>5.05184915786749</v>
       </c>
       <c r="V6" t="n">
-        <v>55.97426663716634</v>
+        <v>55.97419995625814</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.347521748435727</v>
+        <v>-1.365273415935698</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.14095001220703</v>
+        <v>56.14090000152588</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.640422528125471</v>
+        <v>-1.658151039666127</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2786370383582554</v>
+        <v>0.2786152447211049</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2124,10 +2124,10 @@
         <v>55.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>55.5</v>
+        <v>55.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>55.9</v>
+        <v>57.4</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
@@ -2254,7 +2254,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.89</v>
+        <v>16.88</v>
       </c>
       <c r="CA6" t="n">
         <v>0.28</v>
@@ -2310,82 +2310,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.21000003814697</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="D7" t="n">
-        <v>15.21000003814697</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="E7" t="n">
-        <v>15.35999965667725</v>
+        <v>15.38000011444092</v>
       </c>
       <c r="F7" t="n">
-        <v>15.01000022888184</v>
+        <v>14.96000003814697</v>
       </c>
       <c r="G7" t="n">
         <v>15.34000015258789</v>
       </c>
       <c r="H7" t="n">
-        <v>1797700</v>
+        <v>3164000</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.005882362840909705</v>
+        <v>-0.01176472568181952</v>
       </c>
       <c r="J7" t="n">
-        <v>16.46333334181044</v>
+        <v>16.45333332485623</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.612876916489871</v>
+        <v>-8.10372836295041</v>
       </c>
       <c r="M7" t="n">
-        <v>16.49400005340576</v>
+        <v>16.48500003814697</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.784649030564686</v>
+        <v>-8.280255683525766</v>
       </c>
       <c r="P7" t="n">
-        <v>15.63692312974196</v>
+        <v>15.63346158541166</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.730224405739819</v>
+        <v>-3.284376253124345</v>
       </c>
       <c r="S7" t="n">
-        <v>16.50459999084473</v>
+        <v>16.50279998779297</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-7.843873546865014</v>
+        <v>-8.379184764141458</v>
       </c>
       <c r="V7" t="n">
-        <v>20.27700003306071</v>
+        <v>20.27640003204346</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.98890361814976</v>
+        <v>-25.43055048398901</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.59255000114441</v>
+        <v>21.59210000038147</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-29.55903755072541</v>
+        <v>-29.97438931233203</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5231532740117848</v>
+        <v>0.5238441941074459</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="CB7" t="n">
         <v>0.39</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.60000038146973</v>
+        <v>17.57999992370605</v>
       </c>
       <c r="D8" t="n">
-        <v>17.60000038146973</v>
+        <v>17.57999992370605</v>
       </c>
       <c r="E8" t="n">
         <v>17.76000022888184</v>
@@ -2608,67 +2608,67 @@
         <v>17.3700008392334</v>
       </c>
       <c r="H8" t="n">
-        <v>10970300</v>
+        <v>20184600</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01033296810490469</v>
+        <v>0.009184836206163061</v>
       </c>
       <c r="J8" t="n">
-        <v>17.44222259521484</v>
+        <v>17.44000032212999</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9045738603185128</v>
+        <v>0.8027499942096702</v>
       </c>
       <c r="M8" t="n">
-        <v>17.42400035858154</v>
+        <v>17.42200031280517</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.010101120673473</v>
+        <v>0.9068970730344356</v>
       </c>
       <c r="P8" t="n">
-        <v>16.01384632404034</v>
+        <v>16.01307707566481</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>9.904891213101106</v>
+        <v>9.78527013038927</v>
       </c>
       <c r="S8" t="n">
-        <v>15.70140003204346</v>
+        <v>15.70100002288818</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>12.09191757137326</v>
+        <v>11.96738996292435</v>
       </c>
       <c r="V8" t="n">
-        <v>16.63806671778361</v>
+        <v>16.63793338139852</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.781523057952126</v>
+        <v>5.662160802739973</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.1714500617981</v>
+        <v>16.17135005950928</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.833779990121611</v>
+        <v>8.710774666388765</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3299142372666306</v>
+        <v>0.3297453230436417</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>17.96</v>
+        <v>17.94</v>
       </c>
       <c r="CA8" t="n">
         <v>-0.01</v>
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.23999977111816</v>
+        <v>22.5</v>
       </c>
       <c r="D9" t="n">
-        <v>22.23999977111816</v>
+        <v>22.5</v>
       </c>
       <c r="E9" t="n">
-        <v>22.32999992370605</v>
+        <v>22.67000007629395</v>
       </c>
       <c r="F9" t="n">
         <v>21.51000022888184</v>
@@ -2895,88 +2895,88 @@
         <v>21.95000076293945</v>
       </c>
       <c r="H9" t="n">
-        <v>15058200</v>
+        <v>26163100</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009074357862205007</v>
+        <v>0.02087110096935541</v>
       </c>
       <c r="J9" t="n">
-        <v>22.38222249348958</v>
+        <v>22.41111140780979</v>
       </c>
       <c r="K9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6354271673100697</v>
+        <v>0.3966273272785415</v>
       </c>
       <c r="M9" t="n">
-        <v>22.37000026702881</v>
+        <v>22.39600028991699</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5811376591812166</v>
+        <v>0.4643673367419603</v>
       </c>
       <c r="P9" t="n">
-        <v>20.33269236637996</v>
+        <v>20.34269237518311</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>9.380496052219486</v>
+        <v>10.60482843189766</v>
       </c>
       <c r="S9" t="n">
-        <v>20.45680004119873</v>
+        <v>20.46200004577637</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>8.716904532127122</v>
+        <v>9.9599254699655</v>
       </c>
       <c r="V9" t="n">
-        <v>21.88400000254313</v>
+        <v>21.88573333740234</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.626758218486845</v>
+        <v>2.806699017701574</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.04430000305176</v>
+        <v>22.04560000419617</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8877567808427227</v>
+        <v>2.061182257309132</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.365821064850227</v>
+        <v>0.3694550271463342</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -3123,13 +3123,13 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.859999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CC9" t="n">
         <v>1</v>
@@ -3157,16 +3157,16 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.02000045776367</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="D10" t="n">
-        <v>16.02000045776367</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="E10" t="n">
         <v>16.13999938964844</v>
@@ -3194,88 +3194,88 @@
         <v>16.06999969482422</v>
       </c>
       <c r="H10" t="n">
-        <v>2531800</v>
+        <v>3856000</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.004350509270378056</v>
+        <v>-0.008079559553018978</v>
       </c>
       <c r="J10" t="n">
-        <v>16.02111127641466</v>
+        <v>16.01444456312392</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.006933468170969615</v>
+        <v>-0.3399713599952881</v>
       </c>
       <c r="M10" t="n">
-        <v>15.97800016403198</v>
+        <v>15.97200012207031</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2628632701246065</v>
+        <v>-0.0751320049563359</v>
       </c>
       <c r="P10" t="n">
-        <v>15.14000008656428</v>
+        <v>15.13769237811749</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>5.812419855798606</v>
+        <v>5.432186356344396</v>
       </c>
       <c r="S10" t="n">
-        <v>15.5568177986145</v>
+        <v>15.55561779022217</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2.977361213232322</v>
+        <v>2.599589764792163</v>
       </c>
       <c r="V10" t="n">
-        <v>16.2053392791748</v>
+        <v>16.20493927637736</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.143689855659538</v>
+        <v>-1.511509756703905</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29570446491241</v>
+        <v>16.29540446281433</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.691881487801791</v>
+        <v>-2.05827615652464</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2313752266575348</v>
+        <v>0.232211623898299</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AE10" t="n">
         <v>15.8</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>15.9</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>16</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>16.1</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>16.2</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>16.3</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -3422,13 +3422,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.15</v>
+        <v>7.13</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="CC10" t="n">
         <v>2</v>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.1200008392334</v>
+        <v>18.05999946594238</v>
       </c>
       <c r="D11" t="n">
-        <v>18.1200008392334</v>
+        <v>18.05999946594238</v>
       </c>
       <c r="E11" t="n">
         <v>18.25</v>
@@ -3493,88 +3493,88 @@
         <v>18.20999908447266</v>
       </c>
       <c r="H11" t="n">
-        <v>13657600</v>
+        <v>23585900</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.004395600019366896</v>
+        <v>-0.007692378633420427</v>
       </c>
       <c r="J11" t="n">
-        <v>18.15777799818251</v>
+        <v>18.15111117892795</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2080494593165149</v>
+        <v>-0.5019621778932338</v>
       </c>
       <c r="M11" t="n">
-        <v>18.11700019836426</v>
+        <v>18.11100006103516</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01656257016219564</v>
+        <v>-0.281600104471859</v>
       </c>
       <c r="P11" t="n">
-        <v>17.18807711968055</v>
+        <v>17.18576937455397</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>5.421919584511202</v>
+        <v>5.08694183155299</v>
       </c>
       <c r="S11" t="n">
-        <v>17.74694046020508</v>
+        <v>17.74574043273926</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2.102110951827747</v>
+        <v>1.770898398938296</v>
       </c>
       <c r="V11" t="n">
-        <v>18.62251349131266</v>
+        <v>18.62211348215739</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.69841475649184</v>
+        <v>-3.018529646238007</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.79483512878418</v>
+        <v>18.79453512191773</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.59053050972113</v>
+        <v>-3.908240620002062</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2712696497593736</v>
+        <v>0.2718399029445683</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AE11" t="n">
         <v>17.9</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>18</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>18.1</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>18.2</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>18.3</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>18.4</v>
       </c>
       <c r="AJ11" t="n">
         <v>2</v>
@@ -3721,13 +3721,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.09</v>
+        <v>8.06</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.7599983215332</v>
+        <v>40.72000122070312</v>
       </c>
       <c r="D12" t="n">
-        <v>40.7599983215332</v>
+        <v>40.72000122070312</v>
       </c>
       <c r="E12" t="n">
-        <v>40.88000106811523</v>
+        <v>40.95000076293945</v>
       </c>
       <c r="F12" t="n">
         <v>40.0099983215332</v>
@@ -3792,67 +3792,67 @@
         <v>40.15999984741211</v>
       </c>
       <c r="H12" t="n">
-        <v>3706700</v>
+        <v>5469500</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01494020110559724</v>
+        <v>0.01394425735604443</v>
       </c>
       <c r="J12" t="n">
-        <v>40.9444440205892</v>
+        <v>40.93999989827474</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4504779670795924</v>
+        <v>-0.537368534729498</v>
       </c>
       <c r="M12" t="n">
-        <v>41.02899971008301</v>
+        <v>41.025</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6556372089268735</v>
+        <v>-0.7434461408820807</v>
       </c>
       <c r="P12" t="n">
-        <v>39.26769212576059</v>
+        <v>39.26615377572867</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.800340980043548</v>
+        <v>3.702546099315473</v>
       </c>
       <c r="S12" t="n">
-        <v>39.99739974975586</v>
+        <v>39.99659980773926</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.90662037169554</v>
+        <v>1.808657276971554</v>
       </c>
       <c r="V12" t="n">
-        <v>37.03186655680339</v>
+        <v>37.03159990946452</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>10.06736119825668</v>
+        <v>9.960145714082225</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.70549993515014</v>
+        <v>36.705299949646</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.04602414773369</v>
+        <v>10.93766098237769</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3243307709060902</v>
+        <v>0.3239372011863906</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4024,13 +4024,13 @@
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>6.26</v>
+        <v>6.25</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.03000020980835</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="D13" t="n">
-        <v>4.03000020980835</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="E13" t="n">
         <v>4.039999961853027</v>
@@ -4095,67 +4095,67 @@
         <v>4.03000020980835</v>
       </c>
       <c r="H13" t="n">
-        <v>6406100</v>
+        <v>10088800</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.002475186173044208</v>
+        <v>-0.0123762259377227</v>
       </c>
       <c r="J13" t="n">
-        <v>3.990000036027697</v>
+        <v>3.985555569330851</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.002510612016831</v>
+        <v>0.1115136930994609</v>
       </c>
       <c r="M13" t="n">
-        <v>3.977000021934509</v>
+        <v>3.973000001907349</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.332667527823141</v>
+        <v>0.4278884374838416</v>
       </c>
       <c r="P13" t="n">
-        <v>3.779615393051734</v>
+        <v>3.778076923810519</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>6.624610991290562</v>
+        <v>5.609284564605465</v>
       </c>
       <c r="S13" t="n">
-        <v>3.678800005912781</v>
+        <v>3.678000001907348</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>9.546596806869074</v>
+        <v>8.482871328645917</v>
       </c>
       <c r="V13" t="n">
-        <v>4.041800006230672</v>
+        <v>4.041533338228861</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2919440943176944</v>
+        <v>-1.275093494953123</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.495700006484985</v>
+        <v>4.495500005483628</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-10.35878274806749</v>
+        <v>-11.24457780736901</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5408636902063708</v>
+        <v>0.5426450574873564</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4307,13 +4307,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.68</v>
+        <v>5.62</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CC13" t="n">
         <v>8</v>
@@ -4348,13 +4348,13 @@
         <v>8</v>
       </c>
       <c r="CM13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CN13" t="n">
         <v>0</v>
       </c>
       <c r="CO13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -4367,13 +4367,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.88999938964844</v>
+        <v>60.68000030517578</v>
       </c>
       <c r="D14" t="n">
-        <v>60.88999938964844</v>
+        <v>60.68000030517578</v>
       </c>
       <c r="E14" t="n">
-        <v>61.15999984741211</v>
+        <v>61.20000076293945</v>
       </c>
       <c r="F14" t="n">
         <v>59.81000137329102</v>
@@ -4382,67 +4382,67 @@
         <v>60.16999816894531</v>
       </c>
       <c r="H14" t="n">
-        <v>5826000</v>
+        <v>8466300</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01146177106253066</v>
+        <v>0.007973414221812192</v>
       </c>
       <c r="J14" t="n">
-        <v>60.05333370632596</v>
+        <v>60.03000047471788</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.393204392971686</v>
+        <v>1.082791646372973</v>
       </c>
       <c r="M14" t="n">
-        <v>59.81600036621094</v>
+        <v>59.79500045776367</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.795504575468382</v>
+        <v>1.480056594425871</v>
       </c>
       <c r="P14" t="n">
-        <v>55.01692331754244</v>
+        <v>55.00884642967811</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>10.67503545810482</v>
+        <v>10.30953063658139</v>
       </c>
       <c r="S14" t="n">
-        <v>55.54800010681152</v>
+        <v>55.54380012512207</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.616906589913143</v>
+        <v>9.247116993226118</v>
       </c>
       <c r="V14" t="n">
-        <v>56.28733324686687</v>
+        <v>56.28593325297038</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>8.177090434529996</v>
+        <v>7.806687742844723</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.08994993209839</v>
+        <v>56.08889993667603</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.557770979223388</v>
+        <v>8.185399203198978</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3543064702377521</v>
+        <v>0.3536915239873394</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4612,13 +4612,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.68</v>
+        <v>13.64</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC14" t="n">
         <v>6</v>
@@ -4672,82 +4672,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.27000045776367</v>
+        <v>20.8700008392334</v>
       </c>
       <c r="D15" t="n">
-        <v>21.27000045776367</v>
+        <v>20.8700008392334</v>
       </c>
       <c r="E15" t="n">
         <v>21.61000061035156</v>
       </c>
       <c r="F15" t="n">
-        <v>21.20999908447266</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="G15" t="n">
         <v>21.47999954223633</v>
       </c>
       <c r="H15" t="n">
-        <v>1176900</v>
+        <v>2795400</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0097764938988818</v>
+        <v>-0.02839845046567546</v>
       </c>
       <c r="J15" t="n">
-        <v>22.19999991522895</v>
+        <v>22.15555551317003</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.189186761335568</v>
+        <v>-5.802403253542671</v>
       </c>
       <c r="M15" t="n">
-        <v>22.27799987792969</v>
+        <v>22.23799991607666</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.524640567776545</v>
+        <v>-6.151628212995385</v>
       </c>
       <c r="P15" t="n">
-        <v>21.61230762188251</v>
+        <v>21.59692302116981</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.58385291431005</v>
+        <v>-3.365859947844714</v>
       </c>
       <c r="S15" t="n">
-        <v>21.57319999694824</v>
+        <v>21.56520000457764</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.405445363819288</v>
+        <v>-3.223708406120364</v>
       </c>
       <c r="V15" t="n">
-        <v>22.63886669158936</v>
+        <v>22.63620002746582</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.046531624015601</v>
+        <v>-7.802542768173934</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.3759499835968</v>
+        <v>22.37394998550415</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-4.942581327916225</v>
+        <v>-6.721875874600351</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2684885046674803</v>
+        <v>0.2794492467329537</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,13 +4903,13 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.69</v>
+        <v>10.49</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="CC15" t="n">
         <v>2</v>
@@ -4941,7 +4941,7 @@
         <v>-1</v>
       </c>
       <c r="CL15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM15" t="n">
         <v>2</v>
@@ -4950,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.67000007629395</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="D16" t="n">
-        <v>17.67000007629395</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="E16" t="n">
         <v>17.79999923706055</v>
@@ -4978,67 +4978,67 @@
         <v>17.79999923706055</v>
       </c>
       <c r="H16" t="n">
-        <v>1735200</v>
+        <v>2508400</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0134003223429866</v>
+        <v>-0.01172524211400261</v>
       </c>
       <c r="J16" t="n">
-        <v>18.18222215440538</v>
+        <v>18.18555556403266</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.817158836590985</v>
+        <v>-2.670002570905984</v>
       </c>
       <c r="M16" t="n">
-        <v>18.25599994659424</v>
+        <v>18.25900001525879</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.209902892279605</v>
+        <v>-3.061499818457678</v>
       </c>
       <c r="P16" t="n">
-        <v>18.22807678809533</v>
+        <v>18.22923066065862</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.06163243818383</v>
+        <v>-2.90319381860321</v>
       </c>
       <c r="S16" t="n">
-        <v>18.94419990539551</v>
+        <v>18.94479991912842</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.726068324155809</v>
+        <v>-6.570664042390336</v>
       </c>
       <c r="V16" t="n">
-        <v>19.18306657155355</v>
+        <v>19.18326657613119</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.887511048433316</v>
+        <v>-7.732081537339883</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.39779991149902</v>
+        <v>18.39794991493225</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.955906894879255</v>
+        <v>-3.793624589804566</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4063351682705294</v>
+        <v>0.4060119021010896</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>35.34</v>
+        <v>35.4</v>
       </c>
       <c r="CA16" t="n">
         <v>1.29</v>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM16" t="n">
         <v>2</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -5242,82 +5242,82 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.639999866485596</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="D17" t="n">
-        <v>4.639999866485596</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="E17" t="n">
         <v>5.21999979019165</v>
       </c>
       <c r="F17" t="n">
-        <v>4.550000190734863</v>
+        <v>4.5</v>
       </c>
       <c r="G17" t="n">
         <v>5.199999809265137</v>
       </c>
       <c r="H17" t="n">
-        <v>8474600</v>
+        <v>10899000</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1310861921535823</v>
+        <v>-0.153558080192935</v>
       </c>
       <c r="J17" t="n">
-        <v>5.038888931274414</v>
+        <v>5.025555610656738</v>
       </c>
       <c r="K17" t="n">
         <v>-1</v>
       </c>
       <c r="L17" t="n">
-        <v>-7.916210700995409</v>
+        <v>-10.05969625842343</v>
       </c>
       <c r="M17" t="n">
-        <v>5.023000049591064</v>
+        <v>5.011000061035157</v>
       </c>
       <c r="N17" t="n">
         <v>-1</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.624928913481687</v>
+        <v>-9.79844490377463</v>
       </c>
       <c r="P17" t="n">
-        <v>4.859999986795279</v>
+        <v>4.855384606581468</v>
       </c>
       <c r="Q17" t="n">
         <v>-1</v>
       </c>
       <c r="R17" t="n">
-        <v>-4.526751459000571</v>
+        <v>-6.9074780440738</v>
       </c>
       <c r="S17" t="n">
-        <v>5.460199985504151</v>
+        <v>5.457799987792969</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-15.02143000615433</v>
+        <v>-17.18274779149031</v>
       </c>
       <c r="V17" t="n">
-        <v>8.267333300908406</v>
+        <v>8.266533301671346</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-43.87549530662134</v>
+        <v>-45.32169875838219</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.272149977684021</v>
+        <v>8.271549978256225</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-43.90817527483139</v>
+        <v>-45.3548610259452</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.146687172834166</v>
+        <v>1.169761991573947</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5469,13 +5469,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="CA17" t="n">
-        <v>11.63</v>
+        <v>11.94</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="CC17" t="n">
         <v>1</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.319999694824219</v>
+        <v>9.289999961853027</v>
       </c>
       <c r="D18" t="n">
-        <v>9.319999694824219</v>
+        <v>9.289999961853027</v>
       </c>
       <c r="E18" t="n">
-        <v>9.390000343322754</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="F18" t="n">
         <v>9.100000381469727</v>
@@ -5544,88 +5544,90 @@
         <v>9.270000457763672</v>
       </c>
       <c r="H18" t="n">
-        <v>4514900</v>
+        <v>6312900</v>
       </c>
       <c r="I18" t="n">
-        <v>0.006479423807706386</v>
+        <v>0.003239711903853193</v>
       </c>
       <c r="J18" t="n">
-        <v>9.289999961853027</v>
+        <v>9.286666658189562</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3229250063980357</v>
+        <v>0.0358934350305984</v>
       </c>
       <c r="M18" t="n">
+        <v>9.297000026702881</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.0752938026217871</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8.484615435967079</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>9.492292632048446</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9.092200031280518</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.17549030918815</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10.83206666946411</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-14.23612644444123</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.34225001335144</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-18.09385306339239</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.5239521098969746</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG18" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.2150504819808391</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8.485769271850586</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>9.830934547572291</v>
-      </c>
-      <c r="S18" t="n">
-        <v>9.092800025939942</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.498676625859155</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10.83226666768392</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-13.96076203857935</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>11.3424000120163</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-17.83044430675623</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.5242741683407404</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
         <v>9.5</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9.699999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
@@ -5752,13 +5754,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
       <c r="CA18" t="n">
         <v>0.05</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="CC18" t="n">
         <v>6</v>
@@ -5793,13 +5795,13 @@
         <v>4</v>
       </c>
       <c r="CM18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN18" t="n">
         <v>0</v>
       </c>
       <c r="CO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -5812,13 +5814,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.28999996185303</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="D19" t="n">
-        <v>11.28999996185303</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="E19" t="n">
-        <v>11.30000019073486</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="F19" t="n">
         <v>11.0600004196167</v>
@@ -5827,67 +5829,67 @@
         <v>11.10000038146973</v>
       </c>
       <c r="H19" t="n">
-        <v>6074300</v>
+        <v>12152900</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01711707872555435</v>
+        <v>0.01801800021547884</v>
       </c>
       <c r="J19" t="n">
-        <v>11.33222230275472</v>
+        <v>11.33333343929715</v>
       </c>
       <c r="K19" t="n">
         <v>-1</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3725865922293952</v>
+        <v>-0.2941168963290451</v>
       </c>
       <c r="M19" t="n">
-        <v>11.29600009918213</v>
+        <v>11.29700012207031</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0531173625745244</v>
+        <v>0.02655633028356286</v>
       </c>
       <c r="P19" t="n">
-        <v>10.70692308132465</v>
+        <v>10.70730770551241</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>5.445793120017817</v>
+        <v>5.535401629648843</v>
       </c>
       <c r="S19" t="n">
-        <v>10.90779996871948</v>
+        <v>10.90799997329712</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.503914576996166</v>
+        <v>3.593694704779645</v>
       </c>
       <c r="V19" t="n">
-        <v>11.52040005366007</v>
+        <v>11.52046672185262</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.999931345559895</v>
+        <v>-1.913694439996649</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.4406000328064</v>
+        <v>11.44065003395081</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.316365142750524</v>
+        <v>-1.229386816295895</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2843878105649324</v>
+        <v>0.2848654978492932</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6039,7 +6041,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.68</v>
+        <v>6.69</v>
       </c>
       <c r="CA19" t="n">
         <v>0.55</v>
@@ -6054,7 +6056,7 @@
         <v>5</v>
       </c>
       <c r="CE19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF19" t="n">
         <v>9</v>
@@ -6076,13 +6078,13 @@
         <v>5</v>
       </c>
       <c r="CM19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN19" t="n">
         <v>0</v>
       </c>
       <c r="CO19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6095,10 +6097,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.070000171661377</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="D20" t="n">
-        <v>6.070000171661377</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="E20" t="n">
         <v>6.199999809265137</v>
@@ -6110,67 +6112,67 @@
         <v>6.199999809265137</v>
       </c>
       <c r="H20" t="n">
-        <v>10995300</v>
+        <v>13080400</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02096768412952066</v>
+        <v>-0.02258062432137231</v>
       </c>
       <c r="J20" t="n">
-        <v>6.574444399939643</v>
+        <v>6.573333263397217</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.672803929757121</v>
+        <v>-7.809330518446525</v>
       </c>
       <c r="M20" t="n">
-        <v>6.556999969482422</v>
+        <v>6.555999946594238</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.427174013842282</v>
+        <v>-7.565588893458782</v>
       </c>
       <c r="P20" t="n">
-        <v>6.108076920876136</v>
+        <v>6.107692296688374</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.6233835904164942</v>
+        <v>-0.7808571812743679</v>
       </c>
       <c r="S20" t="n">
-        <v>5.817799978256225</v>
+        <v>5.817599973678589</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>4.334975323107342</v>
+        <v>4.166666154388022</v>
       </c>
       <c r="V20" t="n">
-        <v>5.145333321889241</v>
+        <v>5.145266653696696</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>17.9709805356715</v>
+        <v>17.7781512727944</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.267899992465973</v>
+        <v>5.267849991321564</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.22618463415305</v>
+        <v>15.03744322186457</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5146746289758031</v>
+        <v>0.515332759671732</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6322,13 +6324,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>14.8</v>
+        <v>14.78</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6360,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM20" t="n">
         <v>1</v>
@@ -6369,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -6382,82 +6384,82 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.390000104904175</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="D21" t="n">
-        <v>2.390000104904175</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="E21" t="n">
         <v>2.470000028610229</v>
       </c>
       <c r="F21" t="n">
-        <v>2.359999895095825</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="G21" t="n">
         <v>2.400000095367432</v>
       </c>
       <c r="H21" t="n">
-        <v>21016700</v>
+        <v>36070800</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.01673648473467759</v>
       </c>
       <c r="J21" t="n">
-        <v>2.387777805328369</v>
+        <v>2.383333338631524</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09306978106784319</v>
+        <v>-1.398605619224682</v>
       </c>
       <c r="M21" t="n">
-        <v>2.390000033378601</v>
+        <v>2.386000013351441</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.992701795363282e-06</v>
+        <v>-1.50880588924664</v>
       </c>
       <c r="P21" t="n">
-        <v>2.243461544697101</v>
+        <v>2.241923075455886</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>6.531806197144263</v>
+        <v>4.820719781150632</v>
       </c>
       <c r="S21" t="n">
-        <v>2.236000008583069</v>
+        <v>2.235200004577637</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>6.887303029068165</v>
+        <v>5.136001244623483</v>
       </c>
       <c r="V21" t="n">
-        <v>2.658466668128967</v>
+        <v>2.658200000127156</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-10.09854915404073</v>
+        <v>-11.59431553230927</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.909499957561493</v>
+        <v>2.909299956560135</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-17.85529679446089</v>
+        <v>-19.22455780698754</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4530454495447436</v>
+        <v>0.4560318603925175</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6609,10 +6611,10 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>7.24</v>
+        <v>7.12</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="CB21" t="n">
         <v>0.36</v>
@@ -6647,16 +6649,16 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CN21" t="n">
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -6669,10 +6671,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.34999847412109</v>
+        <v>45.13000106811523</v>
       </c>
       <c r="D22" t="n">
-        <v>45.34999847412109</v>
+        <v>45.13000106811523</v>
       </c>
       <c r="E22" t="n">
         <v>45.58000183105469</v>
@@ -6684,88 +6686,88 @@
         <v>44.7400016784668</v>
       </c>
       <c r="H22" t="n">
-        <v>593200</v>
+        <v>995300</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01408759472766552</v>
+        <v>0.009168153761639486</v>
       </c>
       <c r="J22" t="n">
-        <v>45.96222220526801</v>
+        <v>45.93777804904514</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.332015080586657</v>
+        <v>-1.758415437654568</v>
       </c>
       <c r="M22" t="n">
-        <v>45.97400016784668</v>
+        <v>45.95200042724609</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.357292581562227</v>
+        <v>-1.788821708496226</v>
       </c>
       <c r="P22" t="n">
-        <v>44.23461561936598</v>
+        <v>44.22615418067345</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.521515874248482</v>
+        <v>2.043693158915354</v>
       </c>
       <c r="S22" t="n">
-        <v>45.15520004272461</v>
+        <v>45.15080009460449</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4313975604408181</v>
+        <v>-0.0460656875308456</v>
       </c>
       <c r="V22" t="n">
-        <v>46.87706649780274</v>
+        <v>46.87559984842936</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.257601504891995</v>
+        <v>-3.72389641083732</v>
       </c>
       <c r="Y22" t="n">
-        <v>48.00429992675781</v>
+        <v>48.00319993972779</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.529299368361784</v>
+        <v>-5.985431961244466</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.274760893499966</v>
+        <v>0.272869007649624</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="AE22" t="n">
         <v>45</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>45.1</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
         <v>45.2</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>46.7</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>47.2</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>48.3</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
@@ -6892,13 +6894,13 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>9.07</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="CA22" t="n">
         <v>0.5</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CC22" t="n">
         <v>3</v>
@@ -6952,10 +6954,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.07999992370605</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="D23" t="n">
-        <v>16.07999992370605</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="E23" t="n">
         <v>16.20000076293945</v>
@@ -6967,67 +6969,67 @@
         <v>15.86999988555908</v>
       </c>
       <c r="H23" t="n">
-        <v>6329700</v>
+        <v>14232900</v>
       </c>
       <c r="I23" t="n">
-        <v>0.008782957779688294</v>
+        <v>0.005018875751968244</v>
       </c>
       <c r="J23" t="n">
-        <v>15.96111096276177</v>
+        <v>15.95444435543484</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7448664521013452</v>
+        <v>0.4108955527899608</v>
       </c>
       <c r="M23" t="n">
-        <v>15.92499990463257</v>
+        <v>15.91899995803833</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9733125274832666</v>
+        <v>0.6344651045390617</v>
       </c>
       <c r="P23" t="n">
-        <v>14.88615373464731</v>
+        <v>14.8838460628803</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>8.019843206913043</v>
+        <v>7.633473163343833</v>
       </c>
       <c r="S23" t="n">
-        <v>14.88239995956421</v>
+        <v>14.88119997024536</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>8.047088960085402</v>
+        <v>7.652611951961649</v>
       </c>
       <c r="V23" t="n">
-        <v>15.02453326543172</v>
+        <v>15.02413326899211</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>7.024954716581698</v>
+        <v>6.628450180396821</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.5419499540329</v>
+        <v>14.54164995670319</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.57664188458173</v>
+        <v>10.16631885282742</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2231091943824397</v>
+        <v>0.2224843925069958</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7179,7 +7181,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
@@ -7235,13 +7237,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.640000104904175</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="D24" t="n">
-        <v>3.640000104904175</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="E24" t="n">
-        <v>3.660000085830688</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="F24" t="n">
         <v>3.5</v>
@@ -7250,67 +7252,67 @@
         <v>3.519999980926514</v>
       </c>
       <c r="H24" t="n">
-        <v>19036900</v>
+        <v>35655400</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02824862828495678</v>
+        <v>0.02542377219144942</v>
       </c>
       <c r="J24" t="n">
-        <v>3.73999998304579</v>
+        <v>3.738888872994317</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.673793545319131</v>
+        <v>-2.912329364477599</v>
       </c>
       <c r="M24" t="n">
-        <v>3.744999980926514</v>
+        <v>3.743999981880188</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.803735021551641</v>
+        <v>-3.044868268990233</v>
       </c>
       <c r="P24" t="n">
-        <v>3.60115385055542</v>
+        <v>3.600769235537602</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.078716876891096</v>
+        <v>0.8117953967952994</v>
       </c>
       <c r="S24" t="n">
-        <v>3.744600019454956</v>
+        <v>3.744400019645691</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.79335346919125</v>
+        <v>-3.055226594502529</v>
       </c>
       <c r="V24" t="n">
-        <v>4.52253333568573</v>
+        <v>4.522466669082641</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-19.51413434186972</v>
+        <v>-19.73406594111518</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.797200011014938</v>
+        <v>4.797150011062622</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-24.12240272354073</v>
+        <v>-24.330068768543</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6371548925724726</v>
+        <v>0.6359955969052015</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7462,13 +7464,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>-1.52</v>
+        <v>-1.51</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7522,10 +7524,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.90000152587891</v>
+        <v>56.41999816894531</v>
       </c>
       <c r="D25" t="n">
-        <v>56.90000152587891</v>
+        <v>56.41999816894531</v>
       </c>
       <c r="E25" t="n">
         <v>57.63000106811523</v>
@@ -7537,67 +7539,67 @@
         <v>57</v>
       </c>
       <c r="H25" t="n">
-        <v>2119800</v>
+        <v>3440000</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.006113510464997307</v>
+        <v>-0.01449784857737446</v>
       </c>
       <c r="J25" t="n">
-        <v>56.52222230699327</v>
+        <v>56.46888860066732</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6683729044370822</v>
+        <v>-0.0865794120152558</v>
       </c>
       <c r="M25" t="n">
-        <v>56.58400001525879</v>
+        <v>56.53599967956543</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5584644255176441</v>
+        <v>-0.2051816741148804</v>
       </c>
       <c r="P25" t="n">
-        <v>55.80730790358324</v>
+        <v>55.78884623600887</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.957975869725676</v>
+        <v>1.131322792133799</v>
       </c>
       <c r="S25" t="n">
-        <v>59.70919982910156</v>
+        <v>59.69959976196289</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.704799781713851</v>
+        <v>-5.493506834374378</v>
       </c>
       <c r="V25" t="n">
-        <v>57.19426651000977</v>
+        <v>57.19106648763021</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5145008443798503</v>
+        <v>-1.348232103438166</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.21559991836548</v>
+        <v>54.21319990158081</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.95134539054338</v>
+        <v>4.070592164584914</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.3167676188419489</v>
+        <v>0.3182178978401977</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7745,13 +7747,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>15.98</v>
+        <v>15.85</v>
       </c>
       <c r="CA25" t="n">
         <v>0.32</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CC25" t="n">
         <v>6</v>
@@ -7786,13 +7788,13 @@
         <v>2</v>
       </c>
       <c r="CM25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CN25" t="n">
         <v>0</v>
       </c>
       <c r="CO25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -7805,13 +7807,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.46999979019165</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="D26" t="n">
-        <v>6.46999979019165</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="E26" t="n">
-        <v>6.53000020980835</v>
+        <v>6.539999961853027</v>
       </c>
       <c r="F26" t="n">
         <v>6.170000076293945</v>
@@ -7820,67 +7822,67 @@
         <v>6.190000057220459</v>
       </c>
       <c r="H26" t="n">
-        <v>15124200</v>
+        <v>22955400</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0418679147258525</v>
+        <v>0.02254426177545898</v>
       </c>
       <c r="J26" t="n">
-        <v>6.594444433848063</v>
+        <v>6.581111113230388</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.88711338619614</v>
+        <v>-3.511735398802234</v>
       </c>
       <c r="M26" t="n">
-        <v>6.532999992370605</v>
+        <v>6.521000003814697</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9643380109066008</v>
+        <v>-2.622298713112955</v>
       </c>
       <c r="P26" t="n">
-        <v>5.496538437329805</v>
+        <v>5.491923057115995</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>17.71044383589808</v>
+        <v>15.62434212192295</v>
       </c>
       <c r="S26" t="n">
-        <v>5.282799978256225</v>
+        <v>5.280399980545044</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>22.4729275539844</v>
+        <v>20.25603984600272</v>
       </c>
       <c r="V26" t="n">
-        <v>6.165333325068156</v>
+        <v>6.164533325831095</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>4.941605734189991</v>
+        <v>3.008606961768172</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.993150002956391</v>
+        <v>6.992550003528595</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-7.480895055069257</v>
+        <v>-9.189066915099376</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6885962105493034</v>
+        <v>0.6838186061687926</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8032,13 +8034,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>-4.28</v>
+        <v>-4.21</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.31</v>
+        <v>4.39</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="CC26" t="n">
         <v>2</v>
@@ -8069,13 +8071,13 @@
         <v>10</v>
       </c>
       <c r="CM26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN26" t="n">
         <v>-1</v>
       </c>
       <c r="CO26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
@@ -8088,103 +8090,103 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31.52000045776367</v>
+        <v>30.98999977111816</v>
       </c>
       <c r="D27" t="n">
-        <v>31.52000045776367</v>
+        <v>30.98999977111816</v>
       </c>
       <c r="E27" t="n">
         <v>31.95000076293945</v>
       </c>
       <c r="F27" t="n">
-        <v>30.95999908447266</v>
+        <v>30.86000061035156</v>
       </c>
       <c r="G27" t="n">
         <v>31.05999946594238</v>
       </c>
       <c r="H27" t="n">
-        <v>1318300</v>
+        <v>2938400</v>
       </c>
       <c r="I27" t="n">
-        <v>0.008640014648437555</v>
+        <v>-0.008320007324218781</v>
       </c>
       <c r="J27" t="n">
-        <v>32.17111121283637</v>
+        <v>32.11222224765353</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.023898866175643</v>
+        <v>-3.494689554278268</v>
       </c>
       <c r="M27" t="n">
-        <v>32.32000007629394</v>
+        <v>32.26700000762939</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.475246338619459</v>
+        <v>-3.957604475808989</v>
       </c>
       <c r="P27" t="n">
-        <v>31.91307698763334</v>
+        <v>31.89269234583928</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.231709903817762</v>
+        <v>-2.830405677051221</v>
       </c>
       <c r="S27" t="n">
-        <v>31.61280010223389</v>
+        <v>31.60220008850098</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.293550853357206</v>
+        <v>-1.937207902197832</v>
       </c>
       <c r="V27" t="n">
-        <v>33.35706673940023</v>
+        <v>33.35353340148926</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.507277651205102</v>
+        <v>-7.086306574839717</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.64515000343323</v>
+        <v>33.6425</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-6.316362225915779</v>
+        <v>-7.884373125902755</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4230200243900764</v>
+        <v>0.4230099972431012</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AG27" t="n">
         <v>31</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="n">
         <v>31.3</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AI27" t="n">
         <v>31.4</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>32.2</v>
       </c>
       <c r="AJ27" t="n">
         <v>2</v>
@@ -8311,13 +8313,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>9.109999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB27" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8371,13 +8373,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20.36000061035156</v>
+        <v>20.42000007629395</v>
       </c>
       <c r="D28" t="n">
-        <v>20.36000061035156</v>
+        <v>20.42000007629395</v>
       </c>
       <c r="E28" t="n">
-        <v>20.39999961853027</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="F28" t="n">
         <v>20.01000022888184</v>
@@ -8386,67 +8388,67 @@
         <v>20.17000007629395</v>
       </c>
       <c r="H28" t="n">
-        <v>2181600</v>
+        <v>3034600</v>
       </c>
       <c r="I28" t="n">
-        <v>0.009419957032173132</v>
+        <v>0.01239464546625491</v>
       </c>
       <c r="J28" t="n">
-        <v>20.0477778116862</v>
+        <v>20.05444441901313</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.557393550537872</v>
+        <v>1.822816178015088</v>
       </c>
       <c r="M28" t="n">
-        <v>20.02200012207031</v>
+        <v>20.02800006866455</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.688145471084431</v>
+        <v>1.9572598676126</v>
       </c>
       <c r="P28" t="n">
-        <v>19.14730768937331</v>
+        <v>19.14961536114032</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>6.333490538992555</v>
+        <v>6.633995989974665</v>
       </c>
       <c r="S28" t="n">
-        <v>20.09020004272461</v>
+        <v>20.09140003204346</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.342946148137814</v>
+        <v>1.63552586542705</v>
       </c>
       <c r="V28" t="n">
-        <v>18.89320008595784</v>
+        <v>18.89360008239746</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>7.763642568332835</v>
+        <v>8.078926129692874</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.30785008907318</v>
+        <v>18.30815008640289</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>11.20912893263848</v>
+        <v>11.53502664072807</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.25993432165265</v>
+        <v>0.2609151062985172</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8606,13 +8608,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>13.95</v>
+        <v>13.99</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8666,13 +8668,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.79000091552734</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="D29" t="n">
-        <v>26.79000091552734</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="E29" t="n">
-        <v>26.89999961853027</v>
+        <v>26.98999977111816</v>
       </c>
       <c r="F29" t="n">
         <v>25.78000068664551</v>
@@ -8681,67 +8683,67 @@
         <v>25.79999923706055</v>
       </c>
       <c r="H29" t="n">
-        <v>4626600</v>
+        <v>7199700</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03436298494615864</v>
+        <v>0.02972974784187921</v>
       </c>
       <c r="J29" t="n">
-        <v>25.75000021192763</v>
+        <v>25.73666678534614</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>4.038837650641955</v>
+        <v>3.626473073347734</v>
       </c>
       <c r="M29" t="n">
-        <v>25.7230001449585</v>
+        <v>25.71100006103516</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>4.148041692477189</v>
+        <v>3.729921095959801</v>
       </c>
       <c r="P29" t="n">
-        <v>23.80884625361516</v>
+        <v>23.80423083672157</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>12.52120590034691</v>
+        <v>12.03890711373671</v>
       </c>
       <c r="S29" t="n">
-        <v>22.7642000579834</v>
+        <v>22.76180004119873</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>17.68478948212414</v>
+        <v>17.16999546618192</v>
       </c>
       <c r="V29" t="n">
-        <v>24.53093335469564</v>
+        <v>24.53013334910075</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>9.209056696569935</v>
+        <v>8.72342068728152</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.90145000457764</v>
+        <v>25.90085000038147</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.430506441889049</v>
+        <v>2.969593955029067</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.4054965600862895</v>
+        <v>0.403061683027433</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8893,7 +8895,7 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>6.19</v>
+        <v>6.16</v>
       </c>
       <c r="CA29" t="n">
         <v>0.4</v>
@@ -8914,7 +8916,7 @@
         <v>10</v>
       </c>
       <c r="CG29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CH29" t="n">
         <v>5</v>
@@ -8949,103 +8951,103 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.27999973297119</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="D30" t="n">
-        <v>10.27999973297119</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="E30" t="n">
         <v>10.4399995803833</v>
       </c>
       <c r="F30" t="n">
-        <v>10.06999969482422</v>
+        <v>10.02999973297119</v>
       </c>
       <c r="G30" t="n">
         <v>10.26000022888184</v>
       </c>
       <c r="H30" t="n">
-        <v>7963600</v>
+        <v>12001800</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0009736392173147479</v>
+        <v>-0.01265823842711167</v>
       </c>
       <c r="J30" t="n">
-        <v>10.82000011867947</v>
+        <v>10.80444463094076</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-4.990761365852769</v>
+        <v>-6.149731062670529</v>
       </c>
       <c r="M30" t="n">
-        <v>10.88400011062622</v>
+        <v>10.87000017166138</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.549433769899863</v>
+        <v>-6.715729685467429</v>
       </c>
       <c r="P30" t="n">
-        <v>10.79846162062425</v>
+        <v>10.79307702871469</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.801256937032901</v>
+        <v>-6.050885059510334</v>
       </c>
       <c r="S30" t="n">
-        <v>11.39440002441406</v>
+        <v>11.39160003662109</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-9.780245463167137</v>
+        <v>-10.98704035670815</v>
       </c>
       <c r="V30" t="n">
-        <v>13.13513336181641</v>
+        <v>13.13420003255208</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.73661698133219</v>
+        <v>-22.79697036597921</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.64220002174377</v>
+        <v>13.64150002479553</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-24.6455871004215</v>
+        <v>-25.6679960056318</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3993111990325136</v>
+        <v>0.3997490480209286</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE30" t="n">
         <v>9.6</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AF30" t="n">
         <v>9.9</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AG30" t="n">
         <v>10.2</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>10.4</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>13.1</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
@@ -9172,13 +9174,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.39</v>
+        <v>6.3</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CC30" t="n">
         <v>9</v>
@@ -9228,10 +9230,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.70000076293945</v>
+        <v>30.72999954223633</v>
       </c>
       <c r="D31" t="n">
-        <v>30.70000076293945</v>
+        <v>30.72999954223633</v>
       </c>
       <c r="E31" t="n">
         <v>30.85000038146973</v>
@@ -9243,67 +9245,67 @@
         <v>30.52000045776367</v>
       </c>
       <c r="H31" t="n">
-        <v>786100</v>
+        <v>1378700</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0058977818635646</v>
+        <v>0.006880703844132308</v>
       </c>
       <c r="J31" t="n">
-        <v>30.61666658189561</v>
+        <v>30.61999977959527</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.272185676454784</v>
+        <v>0.3592415526872802</v>
       </c>
       <c r="M31" t="n">
-        <v>30.56999988555908</v>
+        <v>30.57299976348877</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4252563881813514</v>
+        <v>0.5135242860108609</v>
       </c>
       <c r="P31" t="n">
-        <v>29.24346153552716</v>
+        <v>29.24461533473088</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>4.980734670014296</v>
+        <v>5.079171637253188</v>
       </c>
       <c r="S31" t="n">
-        <v>29.93359992980957</v>
+        <v>29.93419990539551</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.560336327494833</v>
+        <v>2.65849643336343</v>
       </c>
       <c r="V31" t="n">
-        <v>32.41060003916422</v>
+        <v>32.41080003102621</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-5.27790066878651</v>
+        <v>-5.185927182238269</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.16896432876587</v>
+        <v>32.16911432266235</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-4.566399933841977</v>
+        <v>-4.473591551173677</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2187383918694568</v>
+        <v>0.2189578778601677</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9451,7 +9453,7 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.64</v>
+        <v>13.66</v>
       </c>
       <c r="CA31" t="n">
         <v>0.7</v>
@@ -9507,82 +9509,82 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>96.48999786376953</v>
+        <v>94.98000335693359</v>
       </c>
       <c r="D32" t="n">
-        <v>96.48999786376953</v>
+        <v>94.98000335693359</v>
       </c>
       <c r="E32" t="n">
         <v>97.5</v>
       </c>
       <c r="F32" t="n">
-        <v>95.97000122070312</v>
+        <v>94.58000183105469</v>
       </c>
       <c r="G32" t="n">
         <v>96</v>
       </c>
       <c r="H32" t="n">
-        <v>2504400</v>
+        <v>3944300</v>
       </c>
       <c r="I32" t="n">
-        <v>0.002806034500530741</v>
+        <v>-0.01288711128703179</v>
       </c>
       <c r="J32" t="n">
-        <v>95.6000001695421</v>
+        <v>95.43222300211589</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9309599295492292</v>
+        <v>-0.4738647292877898</v>
       </c>
       <c r="M32" t="n">
-        <v>95.29000015258789</v>
+        <v>95.13900070190429</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.259311270080891</v>
+        <v>-0.1671211004926162</v>
       </c>
       <c r="P32" t="n">
-        <v>96.37961519681491</v>
+        <v>96.32153848501352</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1145290596244969</v>
+        <v>-1.39276754626241</v>
       </c>
       <c r="S32" t="n">
-        <v>91.2063998413086</v>
+        <v>91.17619995117188</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>5.793012367173738</v>
+        <v>4.171925796204256</v>
       </c>
       <c r="V32" t="n">
-        <v>83.92013320922851</v>
+        <v>83.91006657918294</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>14.97836594610975</v>
+        <v>13.19262065809989</v>
       </c>
       <c r="Y32" t="n">
-        <v>85.93969985961914</v>
+        <v>85.93214988708496</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>12.2763961491419</v>
+        <v>10.52906680647177</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2430265874722687</v>
+        <v>0.2471244203369331</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9732,13 +9734,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>42.14</v>
+        <v>41.48</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="CC32" t="n">
         <v>8</v>
@@ -9770,16 +9772,16 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
@@ -9792,13 +9794,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.01000022888184</v>
+        <v>27</v>
       </c>
       <c r="D33" t="n">
-        <v>27.01000022888184</v>
+        <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>27.14999961853027</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="F33" t="n">
         <v>26.6200008392334</v>
@@ -9807,67 +9809,67 @@
         <v>26.84000015258789</v>
       </c>
       <c r="H33" t="n">
-        <v>3760200</v>
+        <v>7661500</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001111960235527176</v>
+        <v>0.0007413068236847842</v>
       </c>
       <c r="J33" t="n">
-        <v>27.35777791341146</v>
+        <v>27.35666677686903</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.271220512244644</v>
+        <v>-1.303765476174924</v>
       </c>
       <c r="M33" t="n">
-        <v>27.36500015258789</v>
+        <v>27.36400012969971</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.297277258273581</v>
+        <v>-1.330215348539769</v>
       </c>
       <c r="P33" t="n">
-        <v>26.15423085139348</v>
+        <v>26.15384622720572</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>3.27201125642264</v>
+        <v>3.235293828079863</v>
       </c>
       <c r="S33" t="n">
-        <v>26.17040004730224</v>
+        <v>26.17020004272461</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>3.208205377304275</v>
+        <v>3.170781866094591</v>
       </c>
       <c r="V33" t="n">
-        <v>25.06413331349691</v>
+        <v>25.06406664530436</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>7.763551570072004</v>
+        <v>7.723939542980456</v>
       </c>
       <c r="Y33" t="n">
-        <v>23.95500000953674</v>
+        <v>23.95495000839233</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.75307959978653</v>
+        <v>12.71156896817095</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2869528351101938</v>
+        <v>0.286947780387446</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10019,7 +10021,7 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>40.31</v>
+        <v>40.3</v>
       </c>
       <c r="CA33" t="n">
         <v>0.35</v>
@@ -10075,13 +10077,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>51.72000122070312</v>
+        <v>51.84000015258789</v>
       </c>
       <c r="D34" t="n">
-        <v>51.72000122070312</v>
+        <v>51.84000015258789</v>
       </c>
       <c r="E34" t="n">
-        <v>51.97999954223633</v>
+        <v>52.06000137329102</v>
       </c>
       <c r="F34" t="n">
         <v>51.11999893188477</v>
@@ -10090,86 +10092,88 @@
         <v>51.61999893188477</v>
       </c>
       <c r="H34" t="n">
-        <v>1378100</v>
+        <v>3033500</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0036872199865563</v>
+        <v>0.00601593985318627</v>
       </c>
       <c r="J34" t="n">
-        <v>51.41888893975152</v>
+        <v>51.43222215440538</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.585606354319374</v>
+        <v>0.7928453819442495</v>
       </c>
       <c r="M34" t="n">
-        <v>51.39200019836426</v>
+        <v>51.40400009155273</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6382336182145856</v>
+        <v>0.8481831380021482</v>
       </c>
       <c r="P34" t="n">
-        <v>47.83846136239859</v>
+        <v>47.84307670593262</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>8.113847619178355</v>
+        <v>8.354235809754368</v>
       </c>
       <c r="S34" t="n">
-        <v>48.71959983825683</v>
+        <v>48.72199981689453</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>6.158509906500178</v>
+        <v>6.399573801180841</v>
       </c>
       <c r="V34" t="n">
-        <v>50.29039998372396</v>
+        <v>50.29119997660319</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>2.842692119056211</v>
+        <v>3.079664388014693</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.91690450668335</v>
+        <v>49.91750450134278</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.612196573163621</v>
+        <v>3.851345676131305</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3081091608275778</v>
+        <v>0.3083535384035126</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="AH34" t="n">
         <v>59.2</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
       <c r="AI34" t="inlineStr">
         <is>
           <t>Foguete</t>
@@ -10179,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
@@ -10300,7 +10304,7 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>13.68</v>
+        <v>13.71</v>
       </c>
       <c r="CA34" t="n">
         <v>0.26</v>
@@ -10337,13 +10341,13 @@
         <v>7</v>
       </c>
       <c r="CM34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -10356,10 +10360,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.83000183105469</v>
+        <v>39.61000061035156</v>
       </c>
       <c r="D35" t="n">
-        <v>39.83000183105469</v>
+        <v>39.61000061035156</v>
       </c>
       <c r="E35" t="n">
         <v>40.02999877929688</v>
@@ -10371,90 +10375,88 @@
         <v>39.54000091552734</v>
       </c>
       <c r="H35" t="n">
-        <v>3245900</v>
+        <v>5515300</v>
       </c>
       <c r="I35" t="n">
-        <v>0.007334367951758347</v>
+        <v>0.001770351370850021</v>
       </c>
       <c r="J35" t="n">
-        <v>39.41555574205186</v>
+        <v>39.39111116197374</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.05147848660334</v>
+        <v>0.5556823403070893</v>
       </c>
       <c r="M35" t="n">
-        <v>39.3120002746582</v>
+        <v>39.29000015258789</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.317667767545283</v>
+        <v>0.8144577666604863</v>
       </c>
       <c r="P35" t="n">
-        <v>37.15307734562801</v>
+        <v>37.14461576021635</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>7.205121827523903</v>
+        <v>6.63726033956114</v>
       </c>
       <c r="S35" t="n">
-        <v>38.11240020751953</v>
+        <v>38.10800018310547</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>4.506673980601933</v>
+        <v>3.94143072328414</v>
       </c>
       <c r="V35" t="n">
-        <v>39.79800010681152</v>
+        <v>39.79653343200684</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>0.08041038282646991</v>
+        <v>-0.4687162563391906</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.67070007324219</v>
+        <v>39.66960006713867</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.4015602384590857</v>
+        <v>-0.1502396209849425</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2673606817306037</v>
+        <v>0.2666886724582369</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AE35" t="n">
         <v>39.3</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AF35" t="n">
         <v>39.5</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
         <v>39.8</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>41.2</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>46.3</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
@@ -10581,13 +10583,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.38</v>
+        <v>32.2</v>
       </c>
       <c r="CA35" t="n">
         <v>0.92</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC35" t="n">
         <v>8</v>
@@ -10615,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM35" t="n">
         <v>8</v>
@@ -10624,7 +10626,7 @@
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
@@ -10637,10 +10639,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.35000038146973</v>
+        <v>21.32999992370605</v>
       </c>
       <c r="D36" t="n">
-        <v>21.35000038146973</v>
+        <v>21.32999992370605</v>
       </c>
       <c r="E36" t="n">
         <v>21.44000053405762</v>
@@ -10652,67 +10654,67 @@
         <v>21.22999954223633</v>
       </c>
       <c r="H36" t="n">
-        <v>1760900</v>
+        <v>2610200</v>
       </c>
       <c r="I36" t="n">
-        <v>0.003289459237101777</v>
+        <v>0.00234958813191799</v>
       </c>
       <c r="J36" t="n">
-        <v>20.82777786254883</v>
+        <v>20.82555558946397</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>2.50733670373893</v>
+        <v>2.422237102271058</v>
       </c>
       <c r="M36" t="n">
-        <v>20.71200008392334</v>
+        <v>20.71000003814697</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>3.080341323683189</v>
+        <v>2.993722281106073</v>
       </c>
       <c r="P36" t="n">
-        <v>19.3907691515409</v>
+        <v>19.38999990316538</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>10.10393767579422</v>
+        <v>10.0051574534767</v>
       </c>
       <c r="S36" t="n">
-        <v>18.09719993591309</v>
+        <v>18.09679992675781</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>17.97405376011569</v>
+        <v>17.86614213581295</v>
       </c>
       <c r="V36" t="n">
-        <v>16.70706662495931</v>
+        <v>16.70693328857422</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>27.79023906910244</v>
+        <v>27.67154543134211</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.42359999656677</v>
+        <v>16.42349999427795</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>29.99586196651636</v>
+        <v>29.8748739984629</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3749403964461156</v>
+        <v>0.3750388324479786</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10864,7 +10866,7 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.41</v>
+        <v>18.39</v>
       </c>
       <c r="CA36" t="n">
         <v>0.27</v>
@@ -10920,82 +10922,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.6299991607666</v>
+        <v>25.34000015258789</v>
       </c>
       <c r="D37" t="n">
-        <v>25.6299991607666</v>
+        <v>25.34000015258789</v>
       </c>
       <c r="E37" t="n">
         <v>26.04000091552734</v>
       </c>
       <c r="F37" t="n">
-        <v>25.61000061035156</v>
+        <v>25.32999992370605</v>
       </c>
       <c r="G37" t="n">
         <v>25.73999977111816</v>
       </c>
       <c r="H37" t="n">
-        <v>3553300</v>
+        <v>5283700</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.008510685394837791</v>
+        <v>-0.01972921552633411</v>
       </c>
       <c r="J37" t="n">
-        <v>25.58222219679091</v>
+        <v>25.55000008477105</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1867584590899461</v>
+        <v>-0.8219175400642301</v>
       </c>
       <c r="M37" t="n">
-        <v>25.56599998474121</v>
+        <v>25.53700008392334</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2503292500335909</v>
+        <v>-0.7714294188355659</v>
       </c>
       <c r="P37" t="n">
-        <v>24.36499991783729</v>
+        <v>24.35384610983042</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>5.191870499466838</v>
+        <v>4.049274345867746</v>
       </c>
       <c r="S37" t="n">
-        <v>24.27259990692139</v>
+        <v>24.26679992675781</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>5.59231091457224</v>
+        <v>4.422504117020855</v>
       </c>
       <c r="V37" t="n">
-        <v>22.40579998016358</v>
+        <v>22.40386665344238</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>14.39002036730441</v>
+        <v>13.10547658832083</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.0579499912262</v>
+        <v>22.0564999961853</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>16.19393085468609</v>
+        <v>14.88676878457813</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.3944912270985305</v>
+        <v>0.3979925472615247</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11147,13 +11149,13 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>30.88</v>
+        <v>30.53</v>
       </c>
       <c r="CA37" t="n">
         <v>0.16</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CC37" t="n">
         <v>1</v>
@@ -11184,13 +11186,13 @@
         <v>6</v>
       </c>
       <c r="CM37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -11203,82 +11205,82 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.47000026702881</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="D38" t="n">
-        <v>11.47000026702881</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="E38" t="n">
         <v>11.63000011444092</v>
       </c>
       <c r="F38" t="n">
-        <v>11.47000026702881</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="G38" t="n">
         <v>11.60999965667725</v>
       </c>
       <c r="H38" t="n">
-        <v>2648600</v>
+        <v>4459700</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.01205851798349711</v>
+        <v>-0.02239442574470585</v>
       </c>
       <c r="J38" t="n">
-        <v>11.34777789645725</v>
+        <v>11.33444457583957</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.077059946773522</v>
+        <v>0.1372436516502303</v>
       </c>
       <c r="M38" t="n">
-        <v>11.32500009536743</v>
+        <v>11.31300010681152</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.280354705874921</v>
+        <v>0.3270597923527377</v>
       </c>
       <c r="P38" t="n">
-        <v>10.78153848648071</v>
+        <v>10.7769231062669</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>6.385561591338547</v>
+        <v>5.317633517024658</v>
       </c>
       <c r="S38" t="n">
-        <v>10.68400001525879</v>
+        <v>10.68160001754761</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>7.356797553795033</v>
+        <v>6.25749291139978</v>
       </c>
       <c r="V38" t="n">
-        <v>9.889533338546753</v>
+        <v>9.888733339309692</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>15.98120835815193</v>
+        <v>14.77709016938708</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.720794088840485</v>
+        <v>9.72019408941269</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>17.99447825148791</v>
+        <v>16.76721963640864</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3861480141776658</v>
+        <v>0.390343064776462</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11430,13 +11432,13 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>26.67</v>
+        <v>26.4</v>
       </c>
       <c r="CA38" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="CB38" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="CC38" t="n">
         <v>1</v>
@@ -11468,16 +11470,16 @@
         <v>0</v>
       </c>
       <c r="CL38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN38" t="n">
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -11490,82 +11492,82 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.619999885559082</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="D39" t="n">
-        <v>6.619999885559082</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="E39" t="n">
         <v>6.739999771118164</v>
       </c>
       <c r="F39" t="n">
-        <v>6.489999771118164</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="G39" t="n">
         <v>6.630000114440918</v>
       </c>
       <c r="H39" t="n">
-        <v>6052200</v>
+        <v>7994200</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.001508330122054535</v>
+        <v>-0.02111619018193023</v>
       </c>
       <c r="J39" t="n">
-        <v>6.97777779897054</v>
+        <v>6.963333341810438</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-5.127390463253824</v>
+        <v>-6.797514171125539</v>
       </c>
       <c r="M39" t="n">
-        <v>6.967000007629395</v>
+        <v>6.953999996185303</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-4.98062468336904</v>
+        <v>-6.672421991971116</v>
       </c>
       <c r="P39" t="n">
-        <v>6.92846155166626</v>
+        <v>6.923461547264686</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-4.452094650550443</v>
+        <v>-6.260766716004558</v>
       </c>
       <c r="S39" t="n">
-        <v>8.816599998474121</v>
+        <v>8.813999996185302</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-24.91436736718465</v>
+        <v>-26.36714574623287</v>
       </c>
       <c r="V39" t="n">
-        <v>10.32733331680298</v>
+        <v>10.32646664937337</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-35.89826451337557</v>
+        <v>-37.15178684558103</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.2929499912262</v>
+        <v>11.29229999065399</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-41.37935711481639</v>
+        <v>-42.52721078531765</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.133803528560473</v>
+        <v>1.132985876405218</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11717,10 +11719,10 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>-7.79</v>
+        <v>-7.64</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CB39" t="n">
         <v>0.07000000000000001</v>
@@ -11777,10 +11779,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.57999992370605</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="D40" t="n">
-        <v>23.57999992370605</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="E40" t="n">
         <v>23.77000045776367</v>
@@ -11792,67 +11794,67 @@
         <v>23.34000015258789</v>
       </c>
       <c r="H40" t="n">
-        <v>629900</v>
+        <v>1892600</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00855435287076789</v>
+        <v>0.007271175466046165</v>
       </c>
       <c r="J40" t="n">
-        <v>23.0722221798367</v>
+        <v>23.06888877020942</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>2.200818542364401</v>
+        <v>2.085538109977892</v>
       </c>
       <c r="M40" t="n">
-        <v>23.01099987030029</v>
+        <v>23.00799980163574</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>2.472730679296367</v>
+        <v>2.355699930883488</v>
       </c>
       <c r="P40" t="n">
-        <v>21.99499995891864</v>
+        <v>21.99384608635535</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>7.20618307682568</v>
+        <v>7.075402567587331</v>
       </c>
       <c r="S40" t="n">
-        <v>21.50660007476807</v>
+        <v>21.50600006103516</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.640760704759369</v>
+        <v>9.504320516248555</v>
       </c>
       <c r="V40" t="n">
-        <v>22.08533335367839</v>
+        <v>22.08513334910075</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6.767688520213015</v>
+        <v>6.63281432266944</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.64635002136231</v>
+        <v>22.64620001792908</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.122738990888319</v>
+        <v>3.990953088888778</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2597237955945409</v>
+        <v>0.259519666814724</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12000,13 +12002,13 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>9.869999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="CA40" t="n">
         <v>0.38</v>
       </c>
       <c r="CB40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CC40" t="n">
         <v>4</v>
@@ -12037,13 +12039,13 @@
         <v>9</v>
       </c>
       <c r="CM40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
       </c>
       <c r="CO40" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
@@ -12062,7 +12064,7 @@
         <v>25.94000053405762</v>
       </c>
       <c r="E41" t="n">
-        <v>26.03000068664551</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="F41" t="n">
         <v>25.68000030517578</v>
@@ -12071,7 +12073,7 @@
         <v>25.68000030517578</v>
       </c>
       <c r="H41" t="n">
-        <v>723900</v>
+        <v>1652800</v>
       </c>
       <c r="I41" t="n">
         <v>0.003481630609661668</v>
@@ -12313,16 +12315,16 @@
         <v>0</v>
       </c>
       <c r="CL41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN41" t="n">
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -12335,13 +12337,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.52000045776367</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="D42" t="n">
-        <v>27.52000045776367</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="E42" t="n">
-        <v>27.55999946594238</v>
+        <v>27.56999969482422</v>
       </c>
       <c r="F42" t="n">
         <v>27.05999946594238</v>
@@ -12350,67 +12352,67 @@
         <v>27.35000038146973</v>
       </c>
       <c r="H42" t="n">
-        <v>1050600</v>
+        <v>2552900</v>
       </c>
       <c r="I42" t="n">
-        <v>0.004746296860611343</v>
+        <v>-0.007666998508660816</v>
       </c>
       <c r="J42" t="n">
-        <v>27.65777778625488</v>
+        <v>27.6199999915229</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4981503921102522</v>
+        <v>-1.593047380456766</v>
       </c>
       <c r="M42" t="n">
-        <v>27.65599994659424</v>
+        <v>27.62199993133545</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.49175401031672</v>
+        <v>-1.600172425090212</v>
       </c>
       <c r="P42" t="n">
-        <v>26.65692300062913</v>
+        <v>26.64384607168344</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>3.237723487869065</v>
+        <v>2.012300446601628</v>
       </c>
       <c r="S42" t="n">
-        <v>27.16540004730225</v>
+        <v>27.15860004425049</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.305338444653757</v>
+        <v>0.07879736396730855</v>
       </c>
       <c r="V42" t="n">
-        <v>28.19053334554036</v>
+        <v>28.18826667785645</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.37857467809408</v>
+        <v>-3.576900929040517</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98880001068115</v>
+        <v>27.98710000991821</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-1.674954098562914</v>
+        <v>-2.883827565043918</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1920315674893897</v>
+        <v>0.1932403916913842</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12558,13 +12560,13 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.73</v>
+        <v>7.63</v>
       </c>
       <c r="CA42" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="CC42" t="n">
         <v>7</v>
@@ -12595,13 +12597,13 @@
         <v>3</v>
       </c>
       <c r="CM42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN42" t="n">
         <v>1</v>
       </c>
       <c r="CO42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
@@ -12629,7 +12631,7 @@
         <v>14.10999965667725</v>
       </c>
       <c r="H43" t="n">
-        <v>8390900</v>
+        <v>12269400</v>
       </c>
       <c r="I43" t="n">
         <v>-0.002118625232660154</v>
@@ -12879,16 +12881,16 @@
         <v>0</v>
       </c>
       <c r="CL43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN43" t="n">
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
@@ -12901,10 +12903,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.34000015258789</v>
+        <v>42.31999969482422</v>
       </c>
       <c r="D44" t="n">
-        <v>42.34000015258789</v>
+        <v>42.31999969482422</v>
       </c>
       <c r="E44" t="n">
         <v>42.66999816894531</v>
@@ -12916,67 +12918,67 @@
         <v>42.52000045776367</v>
       </c>
       <c r="H44" t="n">
-        <v>9906800</v>
+        <v>15804300</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.007733724643034789</v>
+        <v>-0.008202448772913651</v>
       </c>
       <c r="J44" t="n">
-        <v>42.255554623074</v>
+        <v>42.25333234998915</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1998448021027123</v>
+        <v>0.1577800876930952</v>
       </c>
       <c r="M44" t="n">
-        <v>42.17099914550781</v>
+        <v>42.16899909973144</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4007517263154037</v>
+        <v>0.3580843707854013</v>
       </c>
       <c r="P44" t="n">
-        <v>40.1080763890193</v>
+        <v>40.10730714064378</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>5.564773892221965</v>
+        <v>5.516931232558732</v>
       </c>
       <c r="S44" t="n">
-        <v>41.2887996673584</v>
+        <v>41.28839965820313</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>2.54597007832257</v>
+        <v>2.498522696837285</v>
       </c>
       <c r="V44" t="n">
-        <v>42.4026665242513</v>
+        <v>42.40253318786621</v>
       </c>
       <c r="W44" t="n">
         <v>-1</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.1477887519823089</v>
+        <v>-0.1946428357860712</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.02411777496338</v>
+        <v>42.02401777267456</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.7516692660058744</v>
+        <v>0.7043160978818042</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2778419832157527</v>
+        <v>0.277951348870025</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13144,7 +13146,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
@@ -13181,13 +13183,13 @@
         <v>4</v>
       </c>
       <c r="CM44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
@@ -13200,82 +13202,82 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.43000030517578</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="D45" t="n">
-        <v>19.43000030517578</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="E45" t="n">
         <v>19.53000068664551</v>
       </c>
       <c r="F45" t="n">
-        <v>19.30999946594238</v>
+        <v>19.27000045776367</v>
       </c>
       <c r="G45" t="n">
         <v>19.35000038146973</v>
       </c>
       <c r="H45" t="n">
-        <v>798600</v>
+        <v>1580900</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0005149448425616487</v>
+        <v>-0.006179239895054534</v>
       </c>
       <c r="J45" t="n">
-        <v>19.48333337571886</v>
+        <v>19.46888881259494</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.2737368884194227</v>
+        <v>-0.8674844114633697</v>
       </c>
       <c r="M45" t="n">
-        <v>19.48500003814697</v>
+        <v>19.47199993133545</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.2822670406133624</v>
+        <v>-0.8833232070739163</v>
       </c>
       <c r="P45" t="n">
-        <v>18.70230762775128</v>
+        <v>18.69730758666992</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>3.890924542085503</v>
+        <v>3.223414107068061</v>
       </c>
       <c r="S45" t="n">
-        <v>18.25459999084473</v>
+        <v>18.25199996948242</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.438926708449129</v>
+        <v>5.741832507836906</v>
       </c>
       <c r="V45" t="n">
-        <v>18.2206666692098</v>
+        <v>18.21979999542236</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>6.637153612000246</v>
+        <v>5.928710753738122</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.33629549980164</v>
+        <v>18.33564549446106</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>5.96469884217331</v>
+        <v>5.259448012838197</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.199936505262366</v>
+        <v>0.2013535765422408</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13427,13 +13429,13 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.38</v>
+        <v>32.17</v>
       </c>
       <c r="CA45" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CC45" t="n">
         <v>4</v>
@@ -13487,13 +13489,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.5</v>
+        <v>11.48999977111816</v>
       </c>
       <c r="D46" t="n">
-        <v>11.5</v>
+        <v>11.48999977111816</v>
       </c>
       <c r="E46" t="n">
-        <v>11.5600004196167</v>
+        <v>11.59000015258789</v>
       </c>
       <c r="F46" t="n">
         <v>11.10000038146973</v>
@@ -13502,67 +13504,67 @@
         <v>11.13000011444092</v>
       </c>
       <c r="H46" t="n">
-        <v>6907400</v>
+        <v>12456300</v>
       </c>
       <c r="I46" t="n">
-        <v>0.03139016981561671</v>
+        <v>0.03049328827086617</v>
       </c>
       <c r="J46" t="n">
-        <v>11.37222215864393</v>
+        <v>11.37111102210151</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.123596070966155</v>
+        <v>1.045533270984483</v>
       </c>
       <c r="M46" t="n">
-        <v>11.36899995803833</v>
+        <v>11.36799993515015</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.152256508445562</v>
+        <v>1.073186459042726</v>
       </c>
       <c r="P46" t="n">
-        <v>11.14923073695256</v>
+        <v>11.1488461127648</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>3.146129731487771</v>
+        <v>3.059990737182777</v>
       </c>
       <c r="S46" t="n">
-        <v>12.35099998474121</v>
+        <v>12.35079998016357</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.89013023878683</v>
+        <v>-6.969590718236288</v>
       </c>
       <c r="V46" t="n">
-        <v>14.03393337885539</v>
+        <v>14.03386671066284</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-18.0557603520707</v>
+        <v>-18.12662890414845</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.10055003643036</v>
+        <v>14.10050003528595</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-18.44289782818078</v>
+        <v>-18.51352971621653</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.4147519988310693</v>
+        <v>0.4140598803721344</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13714,7 +13716,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="CA46" t="n">
         <v>-0.13</v>
@@ -13774,91 +13776,91 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.10000038146973</v>
+        <v>17.11000061035156</v>
       </c>
       <c r="D47" t="n">
-        <v>17.10000038146973</v>
+        <v>17.11000061035156</v>
       </c>
       <c r="E47" t="n">
         <v>17.29000091552734</v>
       </c>
       <c r="F47" t="n">
-        <v>16.97999954223633</v>
+        <v>16.90999984741211</v>
       </c>
       <c r="G47" t="n">
         <v>17.25</v>
       </c>
       <c r="H47" t="n">
-        <v>1155300</v>
+        <v>2198100</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.01440922158520563</v>
+        <v>-0.01383283952976111</v>
       </c>
       <c r="J47" t="n">
-        <v>17.38666682773166</v>
+        <v>17.38777796427409</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.648771723195986</v>
+        <v>-1.597543714287497</v>
       </c>
       <c r="M47" t="n">
-        <v>17.4980001449585</v>
+        <v>17.49900016784668</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.27454429187121</v>
+        <v>-2.222981620457842</v>
       </c>
       <c r="P47" t="n">
-        <v>17.5623077245859</v>
+        <v>17.56269234877366</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.63238379810973</v>
+        <v>-2.57757597429935</v>
       </c>
       <c r="S47" t="n">
-        <v>16.81180002212524</v>
+        <v>16.81200002670288</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1.714274253590903</v>
+        <v>1.772546890169892</v>
       </c>
       <c r="V47" t="n">
-        <v>17.57373338063558</v>
+        <v>17.57380004882813</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.695687870671</v>
+        <v>-2.639152813779117</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.03585006713867</v>
+        <v>18.03590006828308</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-5.18883048032243</v>
+        <v>-5.133647084016353</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4630452691603089</v>
+        <v>0.4629004503107597</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AE47" t="n">
         <v>16.8</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>16.9</v>
       </c>
       <c r="AF47" t="n">
         <v>17.1</v>
@@ -13997,7 +13999,7 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>63.33</v>
+        <v>63.37</v>
       </c>
       <c r="CA47" t="n">
         <v>2.07</v>
@@ -14057,13 +14059,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.909999847412109</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="D48" t="n">
-        <v>5.909999847412109</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="E48" t="n">
-        <v>5.949999809265137</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="F48" t="n">
         <v>5.53000020980835</v>
@@ -14072,67 +14074,67 @@
         <v>5.570000171661377</v>
       </c>
       <c r="H48" t="n">
-        <v>19290000</v>
+        <v>25113400</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06104123254440053</v>
+        <v>0.05924594497949975</v>
       </c>
       <c r="J48" t="n">
-        <v>5.722222275204128</v>
+        <v>5.721111191643609</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>3.281549775192585</v>
+        <v>3.126820957178948</v>
       </c>
       <c r="M48" t="n">
-        <v>5.690000057220459</v>
+        <v>5.689000082015991</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>3.866428611234836</v>
+        <v>3.708912116532593</v>
       </c>
       <c r="P48" t="n">
-        <v>4.853461568172161</v>
+        <v>4.853076962324289</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>21.7687575022428</v>
+        <v>21.57235793231143</v>
       </c>
       <c r="S48" t="n">
-        <v>4.848800044059754</v>
+        <v>4.848600049018859</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>21.88582316675292</v>
+        <v>21.68461072720008</v>
       </c>
       <c r="V48" t="n">
-        <v>6.764866658846537</v>
+        <v>6.764799993832906</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-12.63686122056084</v>
+        <v>-12.78382064885679</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.403547540903092</v>
+        <v>7.403497542142868</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-20.17340586035864</v>
+        <v>-20.30793470541579</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.8654967175143466</v>
+        <v>0.8645181997295395</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14284,7 +14286,7 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>32.83</v>
+        <v>32.78</v>
       </c>
       <c r="CA48" t="n">
         <v>0.75</v>
@@ -14344,113 +14346,111 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.31999969482422</v>
+        <v>16.23999977111816</v>
       </c>
       <c r="D49" t="n">
-        <v>16.31999969482422</v>
+        <v>16.23999977111816</v>
       </c>
       <c r="E49" t="n">
         <v>16.47999954223633</v>
       </c>
       <c r="F49" t="n">
-        <v>16.26000022888184</v>
+        <v>16.15999984741211</v>
       </c>
       <c r="G49" t="n">
         <v>16.3799991607666</v>
       </c>
       <c r="H49" t="n">
-        <v>3328200</v>
+        <v>7862800</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.002445043645171618</v>
+        <v>-0.007335014349416968</v>
       </c>
       <c r="J49" t="n">
-        <v>16.46333334181044</v>
+        <v>16.45444446139865</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.8706234880284522</v>
+        <v>-1.30326302284813</v>
       </c>
       <c r="M49" t="n">
-        <v>16.43400001525879</v>
+        <v>16.42600002288818</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.6936857753968739</v>
+        <v>-1.132352681790108</v>
       </c>
       <c r="P49" t="n">
-        <v>15.22576922636766</v>
+        <v>15.22269230622512</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>7.186700732082538</v>
+        <v>6.682835364655128</v>
       </c>
       <c r="S49" t="n">
-        <v>14.9789999961853</v>
+        <v>14.97739999771118</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>8.952531537355148</v>
+        <v>8.430033073830776</v>
       </c>
       <c r="V49" t="n">
-        <v>15.28813336054484</v>
+        <v>15.28760002772013</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>6.749459269778405</v>
+        <v>6.229883969171739</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.42455001354218</v>
+        <v>15.42415001392365</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.805353676417608</v>
+        <v>5.289430901917039</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3083263262632618</v>
+        <v>0.3094554558132984</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AE49" t="n">
         <v>15.7</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AF49" t="n">
         <v>15.8</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AG49" t="n">
         <v>16.3</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AH49" t="n">
         <v>17.8</v>
       </c>
-      <c r="AH49" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>Foguete</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ49" t="n">
         <v>1</v>
       </c>
       <c r="AK49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
@@ -14571,13 +14571,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB49" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CC49" t="n">
         <v>5</v>
@@ -14612,13 +14612,13 @@
         <v>8</v>
       </c>
       <c r="CM49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50">
@@ -14631,13 +14631,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.860000133514404</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="D50" t="n">
-        <v>5.860000133514404</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="E50" t="n">
-        <v>5.949999809265137</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="F50" t="n">
         <v>5.619999885559082</v>
@@ -14646,67 +14646,67 @@
         <v>5.679999828338623</v>
       </c>
       <c r="H50" t="n">
-        <v>7606100</v>
+        <v>13913100</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02987699026087354</v>
+        <v>0.02108961060673553</v>
       </c>
       <c r="J50" t="n">
-        <v>5.68555556403266</v>
+        <v>5.679999987284343</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>3.068206220431579</v>
+        <v>2.288731615954675</v>
       </c>
       <c r="M50" t="n">
-        <v>5.684999990463257</v>
+        <v>5.679999971389771</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>3.078278686802378</v>
+        <v>2.288731902193338</v>
       </c>
       <c r="P50" t="n">
-        <v>5.2780769604903</v>
+        <v>5.276153876231267</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>11.0252877587834</v>
+        <v>10.11809130422098</v>
       </c>
       <c r="S50" t="n">
-        <v>5.002400026321411</v>
+        <v>5.001400022506714</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>17.14377304254977</v>
+        <v>16.16747144067782</v>
       </c>
       <c r="V50" t="n">
-        <v>6.475866673787435</v>
+        <v>6.475533339182536</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.510179429201226</v>
+        <v>-10.27766149200324</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.911050014495849</v>
+        <v>6.910800013542175</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-15.20825169513865</v>
+        <v>-15.92869231645458</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.6061215150351932</v>
+        <v>0.6039217752857634</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14854,10 +14854,10 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.34</v>
+        <v>-4.3</v>
       </c>
       <c r="CA50" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CB50" t="n">
         <v>0.63</v>
@@ -14895,13 +14895,13 @@
         <v>10</v>
       </c>
       <c r="CM50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN50" t="n">
         <v>-1</v>
       </c>
       <c r="CO50" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51">
@@ -14914,82 +14914,82 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30.20000076293945</v>
+        <v>30.02000045776367</v>
       </c>
       <c r="D51" t="n">
-        <v>30.20000076293945</v>
+        <v>30.02000045776367</v>
       </c>
       <c r="E51" t="n">
         <v>30.47999954223633</v>
       </c>
       <c r="F51" t="n">
-        <v>29.96999931335449</v>
+        <v>29.95000076293945</v>
       </c>
       <c r="G51" t="n">
         <v>30.20000076293945</v>
       </c>
       <c r="H51" t="n">
-        <v>1787800</v>
+        <v>2741300</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0003312430839659264</v>
+        <v>-0.005631006071105116</v>
       </c>
       <c r="J51" t="n">
-        <v>30.15777799818251</v>
+        <v>30.13777796427409</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1400062191567544</v>
+        <v>-0.3907969149219747</v>
       </c>
       <c r="M51" t="n">
-        <v>30.08500022888184</v>
+        <v>30.06700019836426</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.3822520630969332</v>
+        <v>-0.1563166936858024</v>
       </c>
       <c r="P51" t="n">
-        <v>28.2730770111084</v>
+        <v>28.26615392244779</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>6.815401631290335</v>
+        <v>6.20475831316778</v>
       </c>
       <c r="S51" t="n">
-        <v>28.46580009460449</v>
+        <v>28.46220008850098</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>6.092225275844843</v>
+        <v>5.473225416232181</v>
       </c>
       <c r="V51" t="n">
-        <v>30.2877333577474</v>
+        <v>30.28653335571289</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.2896637849114614</v>
+        <v>-0.8800376550819184</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.11155004501343</v>
+        <v>30.11065004348755</v>
       </c>
       <c r="Z51" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.2937434897698793</v>
+        <v>-0.3010548945072789</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2583027211942314</v>
+        <v>0.2590938342454435</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15141,13 +15141,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.69</v>
+        <v>12.61</v>
       </c>
       <c r="CA51" t="n">
         <v>0.29</v>
       </c>
       <c r="CB51" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CC51" t="n">
         <v>8</v>
@@ -15182,13 +15182,13 @@
         <v>7</v>
       </c>
       <c r="CM51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -15201,10 +15201,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.880000114440918</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="D52" t="n">
-        <v>7.880000114440918</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="E52" t="n">
         <v>7.980000019073486</v>
@@ -15216,67 +15216,67 @@
         <v>7.949999809265137</v>
       </c>
       <c r="H52" t="n">
-        <v>2402600</v>
+        <v>4056800</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.006305134297610704</v>
+        <v>-0.01008826298080956</v>
       </c>
       <c r="J52" t="n">
-        <v>8.492222203148735</v>
+        <v>8.488888846503365</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.209209486779776</v>
+        <v>-7.526178672182275</v>
       </c>
       <c r="M52" t="n">
-        <v>8.570999956130981</v>
+        <v>8.567999935150146</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-8.062067964377706</v>
+        <v>-8.380019093744256</v>
       </c>
       <c r="P52" t="n">
-        <v>8.363846063613892</v>
+        <v>8.362692209390493</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-5.784969564156602</v>
+        <v>-6.130708770821689</v>
       </c>
       <c r="S52" t="n">
-        <v>8.410600023269653</v>
+        <v>8.410000019073486</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.308704579467834</v>
+        <v>-6.65874094138958</v>
       </c>
       <c r="V52" t="n">
-        <v>9.106466643015544</v>
+        <v>9.106266641616822</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-13.46808346918284</v>
+        <v>-13.79562872937358</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.81214997291565</v>
+        <v>8.811999971866607</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-10.57800719846708</v>
+        <v>-10.91693225494033</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.437461835070899</v>
+        <v>0.4379103214762182</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15428,7 +15428,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>-4.66</v>
+        <v>-4.64</v>
       </c>
       <c r="CA52" t="n">
         <v>0.37</v>
@@ -15488,10 +15488,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.31000137329102</v>
+        <v>53.95999908447266</v>
       </c>
       <c r="D53" t="n">
-        <v>54.31000137329102</v>
+        <v>53.95999908447266</v>
       </c>
       <c r="E53" t="n">
         <v>55.66999816894531</v>
@@ -15503,67 +15503,67 @@
         <v>55.52000045776367</v>
       </c>
       <c r="H53" t="n">
-        <v>7044600</v>
+        <v>9673500</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.03414544166060562</v>
+        <v>-0.04036991777064824</v>
       </c>
       <c r="J53" t="n">
-        <v>53.94222217135959</v>
+        <v>53.90333302815755</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.6818020969975866</v>
+        <v>0.1051253292361366</v>
       </c>
       <c r="M53" t="n">
-        <v>53.90200004577637</v>
+        <v>53.86699981689453</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.756931704144839</v>
+        <v>0.1726460873897685</v>
       </c>
       <c r="P53" t="n">
-        <v>50.16846143282377</v>
+        <v>50.15499980633076</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>8.255266002153212</v>
+        <v>7.586480496131151</v>
       </c>
       <c r="S53" t="n">
-        <v>48.35859977722168</v>
+        <v>48.35159973144531</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>12.30681124657506</v>
+        <v>11.59920123465934</v>
       </c>
       <c r="V53" t="n">
-        <v>48.03386662801107</v>
+        <v>48.03153327941894</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>13.06606189729478</v>
+        <v>12.34286186652718</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.66085000038147</v>
+        <v>44.65909998893738</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>21.6053912382481</v>
+        <v>20.82643648850789</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.357463086621889</v>
+        <v>0.3636281454653307</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15715,13 +15715,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CC53" t="n">
         <v>1</v>
@@ -15752,13 +15752,13 @@
         <v>9</v>
       </c>
       <c r="CM53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>49.02999877929688</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="D54" t="n">
-        <v>49.02999877929688</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="E54" t="n">
         <v>49.97999954223633</v>
@@ -15786,67 +15786,67 @@
         <v>49.93999862670898</v>
       </c>
       <c r="H54" t="n">
-        <v>26709900</v>
+        <v>34042600</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0277612833116565</v>
+        <v>-0.03291691131006669</v>
       </c>
       <c r="J54" t="n">
-        <v>48.63111072116428</v>
+        <v>48.6022220187717</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8202322591801351</v>
+        <v>0.3452073424280321</v>
       </c>
       <c r="M54" t="n">
-        <v>48.5879997253418</v>
+        <v>48.56199989318848</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9096876933679334</v>
+        <v>0.4283196018135345</v>
       </c>
       <c r="P54" t="n">
-        <v>45.10884607755221</v>
+        <v>45.09884614210863</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>8.692646881286494</v>
+        <v>8.140240005447282</v>
       </c>
       <c r="S54" t="n">
-        <v>43.27979995727539</v>
+        <v>43.27459999084473</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>13.2861030496858</v>
+        <v>12.69890528874112</v>
       </c>
       <c r="V54" t="n">
-        <v>43.37339993794759</v>
+        <v>43.37166661580404</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>13.04163115974752</v>
+        <v>12.446682968813</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.68540001869201</v>
+        <v>40.68410002708435</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>20.51005706413386</v>
+        <v>19.87484158503286</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3308723755657464</v>
+        <v>0.3355524246176746</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -15998,13 +15998,13 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.87</v>
+        <v>5.84</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="CB54" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CC54" t="n">
         <v>1</v>
@@ -16054,13 +16054,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.539999961853027</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="D55" t="n">
-        <v>4.539999961853027</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="E55" t="n">
-        <v>4.570000171661377</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="F55" t="n">
         <v>4.409999847412109</v>
@@ -16069,67 +16069,67 @@
         <v>4.440000057220459</v>
       </c>
       <c r="H55" t="n">
-        <v>5977900</v>
+        <v>11807400</v>
       </c>
       <c r="I55" t="n">
-        <v>0.02483073087514254</v>
+        <v>0.02257345041641456</v>
       </c>
       <c r="J55" t="n">
-        <v>4.518888844384088</v>
+        <v>4.517777760823567</v>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4671749670314623</v>
+        <v>0.2705411738215761</v>
       </c>
       <c r="M55" t="n">
-        <v>4.526999950408936</v>
+        <v>4.525999975204468</v>
       </c>
       <c r="N55" t="n">
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.2871661494698596</v>
+        <v>0.08838344290315517</v>
       </c>
       <c r="P55" t="n">
-        <v>4.410384599979107</v>
+        <v>4.409999994131235</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.938867550792156</v>
+        <v>2.721093329632859</v>
       </c>
       <c r="S55" t="n">
-        <v>4.822199983596802</v>
+        <v>4.821999988555908</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-5.85210117174124</v>
+        <v>-6.055574024068105</v>
       </c>
       <c r="V55" t="n">
-        <v>5.762799987792969</v>
+        <v>5.762733322779337</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-21.21885244204438</v>
+        <v>-21.39146554115482</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.818918116092682</v>
+        <v>5.818868117332459</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-21.97862435463226</v>
+        <v>-22.14980442132729</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4757756241260908</v>
+        <v>0.4745836228114181</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16281,13 +16281,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="CA55" t="n">
         <v>0.27</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CC55" t="n">
         <v>9</v>
@@ -16341,10 +16341,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>63.36999893188477</v>
+        <v>63.18999862670898</v>
       </c>
       <c r="D56" t="n">
-        <v>63.36999893188477</v>
+        <v>63.18999862670898</v>
       </c>
       <c r="E56" t="n">
         <v>64.87999725341797</v>
@@ -16356,67 +16356,67 @@
         <v>64.87999725341797</v>
       </c>
       <c r="H56" t="n">
-        <v>4915900</v>
+        <v>7329500</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0351705444969217</v>
+        <v>-0.03791110942291787</v>
       </c>
       <c r="J56" t="n">
-        <v>63.06111145019531</v>
+        <v>63.0411114162869</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.4898224509306463</v>
+        <v>0.2361747867021635</v>
       </c>
       <c r="M56" t="n">
-        <v>63.19600067138672</v>
+        <v>63.17800064086914</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.2753311264154517</v>
+        <v>0.01899076532675133</v>
       </c>
       <c r="P56" t="n">
-        <v>61.88884647075947</v>
+        <v>61.88192338209886</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.393246191500912</v>
+        <v>2.113824479134599</v>
       </c>
       <c r="S56" t="n">
-        <v>59.97280014038086</v>
+        <v>59.96920013427734</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>5.664565909132035</v>
+        <v>5.370754462657388</v>
       </c>
       <c r="V56" t="n">
-        <v>60.85193333943685</v>
+        <v>60.85073333740235</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>4.138020690981092</v>
+        <v>3.844268032623351</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.336399974823</v>
+        <v>56.33549997329712</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>12.48499897083434</v>
+        <v>12.16728112231343</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3334969144374711</v>
+        <v>0.3362970098590917</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16568,13 +16568,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>21.34</v>
+        <v>21.28</v>
       </c>
       <c r="CA56" t="n">
         <v>0.44</v>
       </c>
       <c r="CB56" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CC56" t="n">
         <v>10</v>
@@ -16624,13 +16624,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50.27999877929688</v>
+        <v>49.95999908447266</v>
       </c>
       <c r="D57" t="n">
-        <v>50.27999877929688</v>
+        <v>49.95999908447266</v>
       </c>
       <c r="E57" t="n">
-        <v>50.45000076293945</v>
+        <v>50.54000091552734</v>
       </c>
       <c r="F57" t="n">
         <v>49.88000106811523</v>
@@ -16639,91 +16639,91 @@
         <v>50.08000183105469</v>
       </c>
       <c r="H57" t="n">
-        <v>453800</v>
+        <v>879500</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.00336971221153004</v>
+        <v>-0.009712619842550119</v>
       </c>
       <c r="J57" t="n">
-        <v>50.84333335028754</v>
+        <v>50.80777782864041</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.107981192164466</v>
+        <v>-1.668600321444999</v>
       </c>
       <c r="M57" t="n">
-        <v>50.85800018310547</v>
+        <v>50.82600021362305</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.136500455636474</v>
+        <v>-1.703854573467447</v>
       </c>
       <c r="P57" t="n">
-        <v>48.97500008803148</v>
+        <v>48.96269240746131</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.664622131535865</v>
+        <v>2.036870580383704</v>
       </c>
       <c r="S57" t="n">
-        <v>51.35460014343262</v>
+        <v>51.34820014953613</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.092512376952405</v>
+        <v>-2.703504818125583</v>
       </c>
       <c r="V57" t="n">
-        <v>50.88306678771973</v>
+        <v>50.8809334564209</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-1.185203735731586</v>
+        <v>-1.809979317177847</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.2730500793457</v>
+        <v>50.27145008087158</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01382191838411787</v>
+        <v>-0.619538517185986</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.2565312455294235</v>
+        <v>0.2573961882060521</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
       <c r="AD57" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AF57" t="n">
         <v>49.7</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>50.1</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AH57" t="n">
         <v>50.2</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>50.4</v>
       </c>
-      <c r="AH57" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>50.7</v>
-      </c>
       <c r="AJ57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK57" t="n">
         <v>0</v>
@@ -16847,13 +16847,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.82</v>
+        <v>8.76</v>
       </c>
       <c r="CA57" t="n">
         <v>-0.4</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CC57" t="n">
         <v>7</v>
@@ -16885,7 +16885,7 @@
         <v>0</v>
       </c>
       <c r="CL57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM57" t="n">
         <v>3</v>
@@ -16894,7 +16894,7 @@
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -16907,13 +16907,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>19.79000091552734</v>
+        <v>20.13999938964844</v>
       </c>
       <c r="D58" t="n">
-        <v>19.79000091552734</v>
+        <v>20.13999938964844</v>
       </c>
       <c r="E58" t="n">
-        <v>19.79999923706055</v>
+        <v>20.23999977111816</v>
       </c>
       <c r="F58" t="n">
         <v>19.27000045776367</v>
@@ -16922,91 +16922,91 @@
         <v>19.43000030517578</v>
       </c>
       <c r="H58" t="n">
-        <v>5537500</v>
+        <v>10002000</v>
       </c>
       <c r="I58" t="n">
-        <v>0.01748072695378688</v>
+        <v>0.03547550640839692</v>
       </c>
       <c r="J58" t="n">
-        <v>19.8200003306071</v>
+        <v>19.85888904995388</v>
       </c>
       <c r="K58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.1513593066566558</v>
+        <v>1.415539101847221</v>
       </c>
       <c r="M58" t="n">
-        <v>19.86000022888184</v>
+        <v>19.89500007629395</v>
       </c>
       <c r="N58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.3524638094046725</v>
+        <v>1.231461736189796</v>
       </c>
       <c r="P58" t="n">
-        <v>19.00192319429838</v>
+        <v>19.01538467407227</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>4.147357681486853</v>
+        <v>5.914235945537296</v>
       </c>
       <c r="S58" t="n">
-        <v>18.79400009155274</v>
+        <v>18.80100006103516</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>5.299568048966205</v>
+        <v>7.121958003650771</v>
       </c>
       <c r="V58" t="n">
-        <v>20.54480008443197</v>
+        <v>20.54713340759277</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-3.673918294666585</v>
+        <v>-1.981463836672656</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.4220814037323</v>
+        <v>21.4238313961029</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-7.618683065598862</v>
+        <v>-5.992541589400309</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.5020688607955439</v>
+        <v>0.5095090839551721</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="AE58" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="AF58" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="AG58" t="n">
-        <v>19.9</v>
+        <v>20.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="AI58" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK58" t="n">
         <v>0</v>
@@ -17130,13 +17130,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>26.74</v>
+        <v>27.22</v>
       </c>
       <c r="CA58" t="n">
         <v>0.09</v>
       </c>
       <c r="CB58" t="n">
-        <v>4.72</v>
+        <v>4.81</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17168,16 +17168,16 @@
         <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CM58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59">
@@ -17190,13 +17190,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.97999954223633</v>
+        <v>14.93000030517578</v>
       </c>
       <c r="D59" t="n">
-        <v>14.97999954223633</v>
+        <v>14.93000030517578</v>
       </c>
       <c r="E59" t="n">
-        <v>14.98999977111816</v>
+        <v>15.03999996185303</v>
       </c>
       <c r="F59" t="n">
         <v>14.59000015258789</v>
@@ -17205,67 +17205,67 @@
         <v>14.69999980926514</v>
       </c>
       <c r="H59" t="n">
-        <v>3533700</v>
+        <v>6690600</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01904760112953974</v>
+        <v>0.01564629244183258</v>
       </c>
       <c r="J59" t="n">
-        <v>14.71222220526801</v>
+        <v>14.70666673448351</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1.820101227620339</v>
+        <v>1.518587282382703</v>
       </c>
       <c r="M59" t="n">
-        <v>14.70699996948242</v>
+        <v>14.70200004577637</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.856256023120904</v>
+        <v>1.550811173238394</v>
       </c>
       <c r="P59" t="n">
-        <v>14.32384619346032</v>
+        <v>14.32192314588107</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>4.580846093387845</v>
+        <v>4.245778678609909</v>
       </c>
       <c r="S59" t="n">
-        <v>14.10079998016357</v>
+        <v>14.09979999542236</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>6.235104131039205</v>
+        <v>5.888028979297221</v>
       </c>
       <c r="V59" t="n">
-        <v>14.87313334782918</v>
+        <v>14.87280001958211</v>
       </c>
       <c r="W59" t="n">
         <v>1</v>
       </c>
       <c r="X59" t="n">
-        <v>0.7185183640052716</v>
+        <v>0.3845966160935103</v>
       </c>
       <c r="Y59" t="n">
-        <v>14.92735002040863</v>
+        <v>14.92710002422333</v>
       </c>
       <c r="Z59" t="n">
         <v>1</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.3527050799754533</v>
+        <v>0.01942963434120664</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3192664128626074</v>
+        <v>0.317852829489534</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17413,7 +17413,7 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>26.75</v>
+        <v>26.66</v>
       </c>
       <c r="CA59" t="n">
         <v>0.63</v>
@@ -17488,7 +17488,7 @@
         <v>36.86999893188477</v>
       </c>
       <c r="H60" t="n">
-        <v>1976900</v>
+        <v>3082800</v>
       </c>
       <c r="I60" t="n">
         <v>0.007038498806074101</v>
@@ -17756,10 +17756,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.07999992370605</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="D61" t="n">
-        <v>11.07999992370605</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="E61" t="n">
         <v>11.42000007629395</v>
@@ -17771,67 +17771,67 @@
         <v>11.38000011444092</v>
       </c>
       <c r="H61" t="n">
-        <v>937800</v>
+        <v>1448400</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.02550571370025723</v>
+        <v>-0.02814421266887146</v>
       </c>
       <c r="J61" t="n">
-        <v>11.35111098819309</v>
+        <v>11.34777768452962</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.388409951845518</v>
+        <v>-2.624104049912068</v>
       </c>
       <c r="M61" t="n">
-        <v>11.36999988555908</v>
+        <v>11.36699991226196</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.550571370025722</v>
+        <v>-2.788772094430493</v>
       </c>
       <c r="P61" t="n">
-        <v>10.89423069587121</v>
+        <v>10.8930768599877</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.705207398492607</v>
+        <v>1.440578568976892</v>
       </c>
       <c r="S61" t="n">
-        <v>10.63499996185303</v>
+        <v>10.6343999671936</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>4.184296788426979</v>
+        <v>3.908074031664767</v>
       </c>
       <c r="V61" t="n">
-        <v>11.59413335164388</v>
+        <v>11.59393335342407</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-4.43442741552501</v>
+        <v>-4.691532598197723</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.40574999809265</v>
+        <v>11.4055999994278</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-2.856016258826221</v>
+        <v>-3.117765033937477</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3646658019345434</v>
+        <v>0.366524325474335</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17979,7 +17979,7 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="CA61" t="n">
         <v>0.47</v>
@@ -18039,13 +18039,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36.72000122070312</v>
+        <v>36.43000030517578</v>
       </c>
       <c r="D62" t="n">
-        <v>36.72000122070312</v>
+        <v>36.43000030517578</v>
       </c>
       <c r="E62" t="n">
-        <v>36.90999984741211</v>
+        <v>36.93999862670898</v>
       </c>
       <c r="F62" t="n">
         <v>35.41999816894531</v>
@@ -18054,91 +18054,91 @@
         <v>35.4900016784668</v>
       </c>
       <c r="H62" t="n">
-        <v>3551100</v>
+        <v>5855100</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02914800747287205</v>
+        <v>0.02102017919240895</v>
       </c>
       <c r="J62" t="n">
-        <v>36.28444459703233</v>
+        <v>36.25222227308485</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1.200394903402808</v>
+        <v>0.4903920944535226</v>
       </c>
       <c r="M62" t="n">
-        <v>36.29200019836426</v>
+        <v>36.26300010681152</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>1.179326077371066</v>
+        <v>0.4605250472171705</v>
       </c>
       <c r="P62" t="n">
-        <v>34.92269237224873</v>
+        <v>34.91153849088229</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>5.146535751872981</v>
+        <v>4.349455452070856</v>
       </c>
       <c r="S62" t="n">
-        <v>36.63099998474121</v>
+        <v>36.62519996643066</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>0.2429669842455575</v>
+        <v>-0.5329654484720779</v>
       </c>
       <c r="V62" t="n">
-        <v>42.7552666982015</v>
+        <v>42.75333335876465</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-14.1158410263226</v>
+        <v>-14.79026910142096</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.39320001602173</v>
+        <v>43.39175001144409</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-15.37844361064571</v>
+        <v>-16.04394776526004</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4493437471291947</v>
+        <v>0.4452287490279138</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
       </c>
       <c r="AD62" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AE62" t="n">
         <v>35.3</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AF62" t="n">
         <v>35.7</v>
       </c>
-      <c r="AF62" t="n">
+      <c r="AG62" t="n">
         <v>36.5</v>
       </c>
-      <c r="AG62" t="n">
+      <c r="AH62" t="n">
         <v>37.2</v>
       </c>
-      <c r="AH62" t="n">
+      <c r="AI62" t="n">
         <v>37.6</v>
       </c>
-      <c r="AI62" t="n">
-        <v>38.1</v>
-      </c>
       <c r="AJ62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK62" t="n">
         <v>0</v>
@@ -18262,13 +18262,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>18.36</v>
+        <v>18.22</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="CB62" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CC62" t="n">
         <v>10</v>
@@ -18299,13 +18299,13 @@
         <v>3</v>
       </c>
       <c r="CM62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN62" t="n">
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63">
@@ -18318,103 +18318,103 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>29.93000030517578</v>
+        <v>29.65999984741211</v>
       </c>
       <c r="D63" t="n">
-        <v>29.93000030517578</v>
+        <v>29.65999984741211</v>
       </c>
       <c r="E63" t="n">
         <v>30.29999923706055</v>
       </c>
       <c r="F63" t="n">
-        <v>29.90999984741211</v>
+        <v>29.6299991607666</v>
       </c>
       <c r="G63" t="n">
         <v>30</v>
       </c>
       <c r="H63" t="n">
-        <v>1146000</v>
+        <v>1823700</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.004655782875599312</v>
+        <v>-0.01363484707592733</v>
       </c>
       <c r="J63" t="n">
-        <v>30.23666678534614</v>
+        <v>30.20666673448351</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-1.014220523536606</v>
+        <v>-1.809755746559513</v>
       </c>
       <c r="M63" t="n">
-        <v>30.20500011444092</v>
+        <v>30.17800006866455</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.9104446555974666</v>
+        <v>-1.716482934832751</v>
       </c>
       <c r="P63" t="n">
-        <v>29.78730773925781</v>
+        <v>29.7769231062669</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>0.4790381432488739</v>
+        <v>-0.3926640050670165</v>
       </c>
       <c r="S63" t="n">
-        <v>28.66200008392334</v>
+        <v>28.65660007476806</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>4.42397675507534</v>
+        <v>3.501461338840162</v>
       </c>
       <c r="V63" t="n">
-        <v>29.34760000864665</v>
+        <v>29.34580000559489</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>1.984490371810784</v>
+        <v>1.070680784839116</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.51879998207092</v>
+        <v>30.5174499797821</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-1.929301536236839</v>
+        <v>-2.809704391874345</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.1815163171349454</v>
+        <v>0.185763641454478</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AE63" t="n">
         <v>29.1</v>
       </c>
-      <c r="AE63" t="n">
+      <c r="AF63" t="n">
         <v>29.6</v>
       </c>
-      <c r="AF63" t="n">
+      <c r="AG63" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>30</v>
       </c>
-      <c r="AH63" t="n">
+      <c r="AI63" t="n">
         <v>30.1</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>30.2</v>
       </c>
       <c r="AJ63" t="n">
         <v>2</v>
@@ -18561,13 +18561,13 @@
         <v>18881600000</v>
       </c>
       <c r="BZ63" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
       <c r="CA63" t="n">
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CC63" t="n">
         <v>4</v>
@@ -18599,7 +18599,7 @@
         <v>0</v>
       </c>
       <c r="CL63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM63" t="n">
         <v>3</v>
@@ -18608,7 +18608,7 @@
         <v>1</v>
       </c>
       <c r="CO63" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -18621,13 +18621,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.09000015258789</v>
+        <v>27.11000061035156</v>
       </c>
       <c r="D64" t="n">
-        <v>27.09000015258789</v>
+        <v>27.11000061035156</v>
       </c>
       <c r="E64" t="n">
-        <v>27.26000022888184</v>
+        <v>27.30999946594238</v>
       </c>
       <c r="F64" t="n">
         <v>26.70000076293945</v>
@@ -18636,88 +18636,88 @@
         <v>26.88999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>6555500</v>
+        <v>12915800</v>
       </c>
       <c r="I64" t="n">
-        <v>0.005941323639025775</v>
+        <v>0.006684006800445008</v>
       </c>
       <c r="J64" t="n">
-        <v>26.83333375718858</v>
+        <v>26.83555603027344</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.9565207130871201</v>
+        <v>1.022690119662591</v>
       </c>
       <c r="M64" t="n">
-        <v>26.76500034332275</v>
+        <v>26.76700038909912</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.214271642429538</v>
+        <v>1.28142943275829</v>
       </c>
       <c r="P64" t="n">
-        <v>25.40500017312857</v>
+        <v>25.40576942150409</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>6.632552521064675</v>
+        <v>6.708047926330325</v>
       </c>
       <c r="S64" t="n">
-        <v>26.94160007476806</v>
+        <v>26.94200008392334</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0.5508213224455389</v>
+        <v>0.6235636771765551</v>
       </c>
       <c r="V64" t="n">
-        <v>29.14031379699707</v>
+        <v>29.14044713338216</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-7.036004000136971</v>
+        <v>-6.967794672939654</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.57142736434936</v>
+        <v>28.57152736663818</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-5.184995460219668</v>
+        <v>-5.115325959063658</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3211660364924162</v>
+        <v>0.3213109289343652</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="AE64" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="AF64" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="AG64" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="AH64" t="n">
-        <v>27.4</v>
+        <v>28.4</v>
       </c>
       <c r="AI64" t="n">
-        <v>28.4</v>
+        <v>29.1</v>
       </c>
       <c r="AJ64" t="n">
         <v>1</v>
@@ -18844,13 +18844,13 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.92</v>
+        <v>10.93</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
       </c>
       <c r="CB64" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CC64" t="n">
         <v>9</v>
@@ -18885,13 +18885,13 @@
         <v>3</v>
       </c>
       <c r="CM64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -18904,10 +18904,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.89999961853027</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="D65" t="n">
-        <v>17.89999961853027</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="E65" t="n">
         <v>18.09000015258789</v>
@@ -18919,67 +18919,67 @@
         <v>17.89999961853027</v>
       </c>
       <c r="H65" t="n">
-        <v>695200</v>
+        <v>1175100</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.003895364357203834</v>
+        <v>-0.009460216070659944</v>
       </c>
       <c r="J65" t="n">
-        <v>17.46888881259494</v>
+        <v>17.45777765909831</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>2.467877668466821</v>
+        <v>1.960281455319635</v>
       </c>
       <c r="M65" t="n">
-        <v>17.35999984741211</v>
+        <v>17.34999980926514</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>3.110597787238251</v>
+        <v>2.593656672866969</v>
       </c>
       <c r="P65" t="n">
-        <v>15.83730759987464</v>
+        <v>15.83346143135658</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>13.02425936762103</v>
+        <v>12.42013828896213</v>
       </c>
       <c r="S65" t="n">
-        <v>14.72179998397827</v>
+        <v>14.71979997634888</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>21.588390264851</v>
+        <v>20.92555106496554</v>
       </c>
       <c r="V65" t="n">
-        <v>15.84026663462321</v>
+        <v>15.83959996541341</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>13.00314591551734</v>
+        <v>12.37657059476104</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.63433881282806</v>
+        <v>15.63383881092071</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>14.49156777799405</v>
+        <v>13.85558884377587</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.379992517657591</v>
+        <v>0.3821094968405785</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19131,13 +19131,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>27.54</v>
+        <v>27.38</v>
       </c>
       <c r="CA65" t="n">
         <v>0.71</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CC65" t="n">
         <v>3</v>
@@ -19191,13 +19191,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.22999954223633</v>
+        <v>17.20999908447266</v>
       </c>
       <c r="D66" t="n">
-        <v>17.22999954223633</v>
+        <v>17.20999908447266</v>
       </c>
       <c r="E66" t="n">
-        <v>17.35000038146973</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="F66" t="n">
         <v>16.95999908447266</v>
@@ -19206,67 +19206,67 @@
         <v>17.10000038146973</v>
       </c>
       <c r="H66" t="n">
-        <v>1169500</v>
+        <v>2393400</v>
       </c>
       <c r="I66" t="n">
-        <v>0.007602289933716921</v>
+        <v>0.006432672546728746</v>
       </c>
       <c r="J66" t="n">
-        <v>17.54111120435927</v>
+        <v>17.53888893127441</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-1.773614330918918</v>
+        <v>-1.87520342987804</v>
       </c>
       <c r="M66" t="n">
-        <v>17.55900001525879</v>
+        <v>17.55699996948242</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-1.873685703835977</v>
+        <v>-1.976424705888952</v>
       </c>
       <c r="P66" t="n">
-        <v>17.28384626828707</v>
+        <v>17.28307701991154</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.3115436530440725</v>
+        <v>-0.4228294264655348</v>
       </c>
       <c r="S66" t="n">
-        <v>18.59120010375976</v>
+        <v>18.59080009460449</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-7.321746600146353</v>
+        <v>-7.427335042629925</v>
       </c>
       <c r="V66" t="n">
-        <v>18.94320003509522</v>
+        <v>18.94306669871012</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-9.043881127185053</v>
+        <v>-9.148822847968303</v>
       </c>
       <c r="Y66" t="n">
-        <v>20.04364096641541</v>
+        <v>20.04354096412659</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-14.0375764507733</v>
+        <v>-14.13693261447831</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3467269187277984</v>
+        <v>0.3464007402527914</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19418,7 +19418,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.38</v>
+        <v>15.37</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
@@ -19459,13 +19459,13 @@
         <v>1</v>
       </c>
       <c r="CM66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN66" t="n">
         <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -19478,103 +19478,103 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>47.38000106811523</v>
+        <v>46.81000137329102</v>
       </c>
       <c r="D67" t="n">
-        <v>47.38000106811523</v>
+        <v>46.81000137329102</v>
       </c>
       <c r="E67" t="n">
         <v>47.66999816894531</v>
       </c>
       <c r="F67" t="n">
-        <v>47.27000045776367</v>
+        <v>46.7599983215332</v>
       </c>
       <c r="G67" t="n">
         <v>47.41999816894531</v>
       </c>
       <c r="H67" t="n">
-        <v>1200600</v>
+        <v>3509200</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.003784699326709107</v>
+        <v>-0.01576955379192202</v>
       </c>
       <c r="J67" t="n">
-        <v>47.34333335028754</v>
+        <v>47.28000005086263</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.07745064665470472</v>
+        <v>-0.9940750360956097</v>
       </c>
       <c r="M67" t="n">
-        <v>47.28400001525879</v>
+        <v>47.22700004577636</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.2030307351862445</v>
+        <v>-0.882966676014057</v>
       </c>
       <c r="P67" t="n">
-        <v>45.16923097463754</v>
+        <v>45.147307909452</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>4.894416056627211</v>
+        <v>3.682818623811941</v>
       </c>
       <c r="S67" t="n">
-        <v>43.6568000793457</v>
+        <v>43.64540008544922</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>8.528341477164295</v>
+        <v>7.250709769290975</v>
       </c>
       <c r="V67" t="n">
-        <v>46.17560010274251</v>
+        <v>46.17180010477702</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>2.608306037588858</v>
+        <v>1.382231723835186</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.23155004501343</v>
+        <v>47.22870004653931</v>
       </c>
       <c r="Z67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.3143047877114492</v>
+        <v>-0.8865344014036096</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2785327180624686</v>
+        <v>0.2833100460826787</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
       </c>
       <c r="AD67" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AF67" t="n">
         <v>42.7</v>
       </c>
-      <c r="AE67" t="n">
+      <c r="AG67" t="n">
         <v>47.1</v>
       </c>
-      <c r="AF67" t="n">
+      <c r="AH67" t="n">
         <v>47.3</v>
       </c>
-      <c r="AG67" t="n">
+      <c r="AI67" t="n">
         <v>48.8</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>49.4</v>
       </c>
       <c r="AJ67" t="n">
         <v>1</v>
@@ -19701,13 +19701,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="CA67" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="CC67" t="n">
         <v>3</v>
@@ -19742,13 +19742,13 @@
         <v>8</v>
       </c>
       <c r="CM67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN67" t="n">
         <v>0</v>
       </c>
       <c r="CO67" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68">
@@ -19761,13 +19761,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.2400016784668</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="D68" t="n">
-        <v>41.2400016784668</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="E68" t="n">
-        <v>41.38999938964844</v>
+        <v>41.41999816894531</v>
       </c>
       <c r="F68" t="n">
         <v>40.66999816894531</v>
@@ -19776,67 +19776,67 @@
         <v>40.79999923706055</v>
       </c>
       <c r="H68" t="n">
-        <v>485700</v>
+        <v>840700</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01078437376554109</v>
+        <v>0.009068601441263757</v>
       </c>
       <c r="J68" t="n">
-        <v>41.1499998304579</v>
+        <v>41.14222166273329</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.218716520971355</v>
+        <v>0.06751338427885874</v>
       </c>
       <c r="M68" t="n">
-        <v>41.12399978637696</v>
+        <v>41.1169994354248</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.2820783306400769</v>
+        <v>0.1288973763850312</v>
       </c>
       <c r="P68" t="n">
-        <v>39.28961504422701</v>
+        <v>39.28692260155311</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>4.964127625186195</v>
+        <v>4.793135839348643</v>
       </c>
       <c r="S68" t="n">
-        <v>39.80019973754883</v>
+        <v>39.7987996673584</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>3.617574661464852</v>
+        <v>3.445326273775858</v>
       </c>
       <c r="V68" t="n">
-        <v>41.0447333017985</v>
+        <v>41.04426661173503</v>
       </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
       <c r="X68" t="n">
-        <v>0.4757452685403097</v>
+        <v>0.3063315965653989</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.18565006256104</v>
+        <v>41.18530004501343</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.1319673619894277</v>
+        <v>-0.03715373216023869</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2093926009951216</v>
+        <v>0.2087678455481168</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -19986,13 +19986,13 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CA68" t="n">
         <v>0.24</v>
       </c>
       <c r="CB68" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CC68" t="n">
         <v>6</v>
@@ -20007,7 +20007,7 @@
         <v>8</v>
       </c>
       <c r="CG68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CH68" t="n">
         <v>5</v>
@@ -20042,10 +20042,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.60000038146973</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="D69" t="n">
-        <v>19.60000038146973</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="E69" t="n">
         <v>19.70999908447266</v>
@@ -20057,88 +20057,88 @@
         <v>19.63999938964844</v>
       </c>
       <c r="H69" t="n">
-        <v>1637200</v>
+        <v>2735700</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.00203660944102646</v>
+        <v>-0.003564139358431584</v>
       </c>
       <c r="J69" t="n">
-        <v>19.35666677686903</v>
+        <v>19.35333336724175</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.257104890039608</v>
+        <v>1.119529765085349</v>
       </c>
       <c r="M69" t="n">
-        <v>19.30100002288818</v>
+        <v>19.29799995422363</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1.549144387477195</v>
+        <v>1.409471143360914</v>
       </c>
       <c r="P69" t="n">
-        <v>18.75961538461538</v>
+        <v>18.7584615120521</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>4.479756005784301</v>
+        <v>4.326251287989249</v>
       </c>
       <c r="S69" t="n">
-        <v>19.90900005340576</v>
+        <v>19.90840003967285</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-1.552060229580321</v>
+        <v>-1.699786744159648</v>
       </c>
       <c r="V69" t="n">
-        <v>23.25893334706624</v>
+        <v>23.25873334248861</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-15.73130165084735</v>
+        <v>-15.85956377480747</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.31020001411438</v>
+        <v>23.31005001068115</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-15.91663576630882</v>
+        <v>-16.04479747638106</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2144655714354614</v>
+        <v>0.2146766970258696</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
       </c>
       <c r="AD69" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AE69" t="n">
         <v>19</v>
       </c>
-      <c r="AE69" t="n">
+      <c r="AF69" t="n">
         <v>19.5</v>
       </c>
-      <c r="AF69" t="n">
+      <c r="AG69" t="n">
         <v>19.6</v>
       </c>
-      <c r="AG69" t="n">
+      <c r="AH69" t="n">
         <v>21.9</v>
       </c>
-      <c r="AH69" t="n">
+      <c r="AI69" t="n">
         <v>22.2</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>22.3</v>
       </c>
       <c r="AJ69" t="n">
         <v>1</v>
@@ -20265,7 +20265,7 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="CA69" t="n">
         <v>-0.06</v>
@@ -20325,10 +20325,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>34.47000122070312</v>
+        <v>34.45999908447266</v>
       </c>
       <c r="D70" t="n">
-        <v>34.47000122070312</v>
+        <v>34.45999908447266</v>
       </c>
       <c r="E70" t="n">
         <v>34.77999877929688</v>
@@ -20340,67 +20340,67 @@
         <v>33.86999893188477</v>
       </c>
       <c r="H70" t="n">
-        <v>3578300</v>
+        <v>5383600</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0189181009461532</v>
+        <v>0.0186224421909329</v>
       </c>
       <c r="J70" t="n">
-        <v>33.93222215440538</v>
+        <v>33.93111080593533</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>1.584862505764083</v>
+        <v>1.558711948931564</v>
       </c>
       <c r="M70" t="n">
-        <v>34.01300010681152</v>
+        <v>34.01199989318847</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>1.343607186829956</v>
+        <v>1.317179797398219</v>
       </c>
       <c r="P70" t="n">
-        <v>32.84038470341609</v>
+        <v>32.84000000586877</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>4.962233335584278</v>
+        <v>4.933005719593128</v>
       </c>
       <c r="S70" t="n">
-        <v>31.39759990692139</v>
+        <v>31.39739986419678</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>9.785465522491894</v>
+        <v>9.754308425291722</v>
       </c>
       <c r="V70" t="n">
-        <v>32.7729333114624</v>
+        <v>32.7728666305542</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>5.178260649153335</v>
+        <v>5.147955084116878</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.54544997215271</v>
+        <v>35.54539996147156</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-3.025559536571126</v>
+        <v>-3.053562143555547</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3913259520267601</v>
+        <v>0.3912226753837268</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20608,10 +20608,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.63000106811523</v>
+        <v>38.75</v>
       </c>
       <c r="D71" t="n">
-        <v>38.63000106811523</v>
+        <v>38.75</v>
       </c>
       <c r="E71" t="n">
         <v>38.95999908447266</v>
@@ -20623,67 +20623,67 @@
         <v>38.43000030517578</v>
       </c>
       <c r="H71" t="n">
-        <v>2509900</v>
+        <v>4595300</v>
       </c>
       <c r="I71" t="n">
-        <v>0.005204287310726752</v>
+        <v>0.00832681999175322</v>
       </c>
       <c r="J71" t="n">
-        <v>38.03222232394748</v>
+        <v>38.04555553860135</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1.571769167407701</v>
+        <v>1.851581482846047</v>
       </c>
       <c r="M71" t="n">
-        <v>37.90200004577637</v>
+        <v>37.91399993896484</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>1.92074566371067</v>
+        <v>2.204990405604729</v>
       </c>
       <c r="P71" t="n">
-        <v>35.13269233703613</v>
+        <v>35.13730768057016</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>9.954570795567278</v>
+        <v>10.28164238498998</v>
       </c>
       <c r="S71" t="n">
-        <v>33.5023999786377</v>
+        <v>33.50479995727539</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>15.30517542846803</v>
+        <v>15.65507046576365</v>
       </c>
       <c r="V71" t="n">
-        <v>29.49860004425049</v>
+        <v>29.49940003712972</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>30.95537079782378</v>
+        <v>31.35860373847236</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.73090001106262</v>
+        <v>27.73150000572205</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>39.30309168726821</v>
+        <v>39.732794807365</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3424969872272435</v>
+        <v>0.3426020867940484</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>21.6</v>
       </c>
       <c r="AG71" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -20835,13 +20835,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>14.36</v>
+        <v>14.41</v>
       </c>
       <c r="CA71" t="n">
         <v>0.32</v>
       </c>
       <c r="CB71" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CC71" t="n">
         <v>4</v>
@@ -20891,82 +20891,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7.099999904632568</v>
+        <v>6.989999771118164</v>
       </c>
       <c r="D72" t="n">
-        <v>7.099999904632568</v>
+        <v>6.989999771118164</v>
       </c>
       <c r="E72" t="n">
         <v>7.269999980926514</v>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="G72" t="n">
         <v>7.260000228881836</v>
       </c>
       <c r="H72" t="n">
-        <v>8633200</v>
+        <v>12480000</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.02203861146074793</v>
+        <v>-0.03719014452500324</v>
       </c>
       <c r="J72" t="n">
-        <v>7.450000074174669</v>
+        <v>7.437777837117513</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-4.697988806139372</v>
+        <v>-6.020320528595994</v>
       </c>
       <c r="M72" t="n">
-        <v>7.484000062942505</v>
+        <v>7.473000049591064</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-5.130948090331225</v>
+        <v>-6.463271447446746</v>
       </c>
       <c r="P72" t="n">
-        <v>7.032307698176457</v>
+        <v>7.028076923810518</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>0.9625888024448103</v>
+        <v>-0.5417862255228328</v>
       </c>
       <c r="S72" t="n">
-        <v>7.540199966430664</v>
+        <v>7.537999963760376</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-5.838042276834666</v>
+        <v>-7.269835437473768</v>
       </c>
       <c r="V72" t="n">
-        <v>7.906400003433228</v>
+        <v>7.905666669209798</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-10.19933343178302</v>
+        <v>-11.58241216591995</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.464050002098084</v>
+        <v>7.463500001430512</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-4.877380207302791</v>
+        <v>-6.344211565908658</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.5225758182244329</v>
+        <v>0.5295308216326897</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21118,7 +21118,7 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>-3.41</v>
+        <v>-3.36</v>
       </c>
       <c r="CA72" t="n">
         <v>-0.06</v>
@@ -21156,7 +21156,7 @@
         <v>-1</v>
       </c>
       <c r="CL72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM72" t="n">
         <v>1</v>
@@ -21165,7 +21165,7 @@
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
@@ -21178,82 +21178,82 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="D73" t="n">
-        <v>74</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="E73" t="n">
         <v>75.45999908447266</v>
       </c>
       <c r="F73" t="n">
-        <v>73.70999908447266</v>
+        <v>72.5</v>
       </c>
       <c r="G73" t="n">
         <v>75.05999755859375</v>
       </c>
       <c r="H73" t="n">
-        <v>36035300</v>
+        <v>44390900</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.008042875152728501</v>
+        <v>-0.02694372891881147</v>
       </c>
       <c r="J73" t="n">
-        <v>77.2999996609158</v>
+        <v>77.14333258734808</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-4.269081080713559</v>
+        <v>-5.902436538247546</v>
       </c>
       <c r="M73" t="n">
-        <v>77.65000000000001</v>
+        <v>77.50899963378906</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-4.700579523502904</v>
+        <v>-6.346364059837585</v>
       </c>
       <c r="P73" t="n">
-        <v>76.13615388136644</v>
+        <v>76.08192297128531</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-2.805702379837763</v>
+        <v>-4.589692921816132</v>
       </c>
       <c r="S73" t="n">
-        <v>75.40300018310546</v>
+        <v>75.37480010986329</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-1.860668911977608</v>
+        <v>-3.694608500339163</v>
       </c>
       <c r="V73" t="n">
-        <v>80.02006683349609</v>
+        <v>80.01066680908202</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-7.523196457736662</v>
+        <v>-9.274601458950819</v>
       </c>
       <c r="Y73" t="n">
-        <v>78.93960010528565</v>
+        <v>78.9325500869751</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-6.257442524027813</v>
+        <v>-8.03540965304639</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2526361983895519</v>
+        <v>0.2634648794291914</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21401,13 +21401,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>21.08</v>
+        <v>20.68</v>
       </c>
       <c r="CA73" t="n">
         <v>0.22</v>
       </c>
       <c r="CB73" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21457,10 +21457,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.410000085830688</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="D74" t="n">
-        <v>3.410000085830688</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="E74" t="n">
         <v>3.450000047683716</v>
@@ -21472,67 +21472,67 @@
         <v>3.309999942779541</v>
       </c>
       <c r="H74" t="n">
-        <v>7569700</v>
+        <v>11647900</v>
       </c>
       <c r="I74" t="n">
-        <v>0.03021152410267813</v>
+        <v>0.009063435621868399</v>
       </c>
       <c r="J74" t="n">
-        <v>3.383333338631524</v>
+        <v>3.37555554178026</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>0.7881797189380828</v>
+        <v>-1.05332669455045</v>
       </c>
       <c r="M74" t="n">
-        <v>3.391000008583069</v>
+        <v>3.383999991416931</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5603089707911482</v>
+        <v>-1.30023869264834</v>
       </c>
       <c r="P74" t="n">
-        <v>3.054999993397639</v>
+        <v>3.052307679102971</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>11.62029764976312</v>
+        <v>9.425400887203121</v>
       </c>
       <c r="S74" t="n">
-        <v>3.104199991226196</v>
+        <v>3.102799987792969</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>9.851172458888437</v>
+        <v>7.644705662934584</v>
       </c>
       <c r="V74" t="n">
-        <v>3.460461460749308</v>
+        <v>3.459994792938232</v>
       </c>
       <c r="W74" t="n">
         <v>-1</v>
       </c>
       <c r="X74" t="n">
-        <v>-1.458226756488511</v>
+        <v>-3.468065299226103</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.520196090936661</v>
+        <v>3.519846090078354</v>
       </c>
       <c r="Z74" t="n">
         <v>-1</v>
       </c>
       <c r="AA74" t="n">
-        <v>-3.13039393997654</v>
+        <v>-5.1094897704757</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.789175229188344</v>
+        <v>0.7851297279795113</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21680,13 +21680,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>13.64</v>
+        <v>13.36</v>
       </c>
       <c r="CA74" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="CC74" t="n">
         <v>6</v>
@@ -21714,16 +21714,16 @@
         <v>0</v>
       </c>
       <c r="CL74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM74" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CN74" t="n">
         <v>-1</v>
       </c>
       <c r="CO74" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75">
@@ -21736,10 +21736,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.70000076293945</v>
+        <v>38.88999938964844</v>
       </c>
       <c r="D75" t="n">
-        <v>38.70000076293945</v>
+        <v>38.88999938964844</v>
       </c>
       <c r="E75" t="n">
         <v>39.09999847412109</v>
@@ -21751,67 +21751,67 @@
         <v>38.59999847412109</v>
       </c>
       <c r="H75" t="n">
-        <v>3701300</v>
+        <v>8066600</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.001547924695353253</v>
+        <v>0.003354000870609219</v>
       </c>
       <c r="J75" t="n">
-        <v>37.8066669040256</v>
+        <v>37.82777786254883</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>2.362900334963746</v>
+        <v>2.808046327646583</v>
       </c>
       <c r="M75" t="n">
-        <v>37.66100006103515</v>
+        <v>37.67999992370606</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>2.758823982954375</v>
+        <v>3.211251243079542</v>
       </c>
       <c r="P75" t="n">
-        <v>35.38730782728929</v>
+        <v>35.39461546677809</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>9.361245991975531</v>
+        <v>9.875467996399523</v>
       </c>
       <c r="S75" t="n">
-        <v>34.84739986419677</v>
+        <v>34.85119983673096</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>11.05563374529114</v>
+        <v>11.58869586079743</v>
       </c>
       <c r="V75" t="n">
-        <v>32.41453320821126</v>
+        <v>32.41579986572265</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>19.3908933204565</v>
+        <v>19.97235777227197</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.87569116592407</v>
+        <v>30.87664115905762</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>25.34132614220042</v>
+        <v>25.9528171775903</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2936974593652392</v>
+        <v>0.2934600275010292</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21963,13 +21963,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.42</v>
+        <v>15.49</v>
       </c>
       <c r="CA75" t="n">
         <v>0.39</v>
       </c>
       <c r="CB75" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CC75" t="n">
         <v>5</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.8799991607666</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="D76" t="n">
-        <v>22.8799991607666</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="E76" t="n">
-        <v>22.95000076293945</v>
+        <v>23.06999969482422</v>
       </c>
       <c r="F76" t="n">
         <v>22.30999946594238</v>
@@ -22034,67 +22034,67 @@
         <v>22.38999938964844</v>
       </c>
       <c r="H76" t="n">
-        <v>1181400</v>
+        <v>2022700</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0196077814722504</v>
+        <v>0.01871658049457281</v>
       </c>
       <c r="J76" t="n">
-        <v>22.70888858371311</v>
+        <v>22.70666652255588</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0.7534960437307118</v>
+        <v>0.6752822464863575</v>
       </c>
       <c r="M76" t="n">
-        <v>22.81399974822998</v>
+        <v>22.81199989318848</v>
       </c>
       <c r="N76" t="n">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.2892934744673179</v>
+        <v>0.2104187155349639</v>
       </c>
       <c r="P76" t="n">
-        <v>22.02461543449989</v>
+        <v>22.02384625948392</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>3.88376236947512</v>
+        <v>3.796586395564636</v>
       </c>
       <c r="S76" t="n">
-        <v>22.17360008239746</v>
+        <v>22.17320011138916</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>3.185766297507627</v>
+        <v>3.097435171793854</v>
       </c>
       <c r="V76" t="n">
-        <v>24.32293334960938</v>
+        <v>24.32280002593994</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-5.932402017892086</v>
+        <v>-6.014107808427987</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.06975001335144</v>
+        <v>26.06965002059937</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-12.2354485599257</v>
+        <v>-12.31182393208825</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3068067187477094</v>
+        <v>0.3063371899319838</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22112,10 +22112,10 @@
         <v>22.9</v>
       </c>
       <c r="AH76" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AI76" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="AJ76" t="n">
         <v>3</v>
@@ -22242,7 +22242,7 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
@@ -22283,13 +22283,13 @@
         <v>5</v>
       </c>
       <c r="CM76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77">
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30.63999938964844</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="D77" t="n">
-        <v>30.63999938964844</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="E77" t="n">
         <v>30.80999946594238</v>
@@ -22317,67 +22317,67 @@
         <v>30.61000061035156</v>
       </c>
       <c r="H77" t="n">
-        <v>1621400</v>
+        <v>3167700</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.004224929027663804</v>
+        <v>-0.003899929718822026</v>
       </c>
       <c r="J77" t="n">
-        <v>30.36111111111111</v>
+        <v>30.36222224765354</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>0.9185707252830525</v>
+        <v>0.9478139265612411</v>
       </c>
       <c r="M77" t="n">
-        <v>30.34500007629395</v>
+        <v>30.34600009918213</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9721513020688709</v>
+        <v>1.001777889522709</v>
       </c>
       <c r="P77" t="n">
-        <v>29.94500006162203</v>
+        <v>29.9453846858098</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>2.320919440962456</v>
+        <v>2.353000103733426</v>
       </c>
       <c r="S77" t="n">
-        <v>31.91080020904541</v>
+        <v>31.91100021362305</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-3.982353344548066</v>
+        <v>-3.951617268813918</v>
       </c>
       <c r="V77" t="n">
-        <v>36.08860012054443</v>
+        <v>36.08866678873698</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-15.09784450684256</v>
+        <v>-15.07029118599659</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.69840012550354</v>
+        <v>35.69845012664795</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-14.16982474864832</v>
+        <v>-14.14193190518694</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1723144689719372</v>
+        <v>0.1722756571767558</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22525,7 +22525,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
@@ -22566,13 +22566,13 @@
         <v>2</v>
       </c>
       <c r="CM77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN77" t="n">
         <v>1</v>
       </c>
       <c r="CO77" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
@@ -22585,13 +22585,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.36000061035156</v>
+        <v>51.45999908447266</v>
       </c>
       <c r="D78" t="n">
-        <v>51.36000061035156</v>
+        <v>51.45999908447266</v>
       </c>
       <c r="E78" t="n">
-        <v>51.77000045776367</v>
+        <v>51.79000091552734</v>
       </c>
       <c r="F78" t="n">
         <v>50.20999908447266</v>
@@ -22600,67 +22600,67 @@
         <v>50.95000076293945</v>
       </c>
       <c r="H78" t="n">
-        <v>3039300</v>
+        <v>4883300</v>
       </c>
       <c r="I78" t="n">
-        <v>0.009433953069178047</v>
+        <v>0.0113993318431922</v>
       </c>
       <c r="J78" t="n">
-        <v>51.64222293429904</v>
+        <v>51.65333387586806</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.5464953054141998</v>
+        <v>-0.3742929582435434</v>
       </c>
       <c r="M78" t="n">
-        <v>51.56200065612793</v>
+        <v>51.57200050354004</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.3917614584498457</v>
+        <v>-0.2171748583995588</v>
       </c>
       <c r="P78" t="n">
-        <v>49.90038504967323</v>
+        <v>49.90423114483173</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2.925058712924491</v>
+        <v>3.117507080964304</v>
       </c>
       <c r="S78" t="n">
-        <v>48.00600028991699</v>
+        <v>48.00800025939942</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>6.986627296961115</v>
+        <v>7.190465769082681</v>
       </c>
       <c r="V78" t="n">
-        <v>47.25333346048991</v>
+        <v>47.25400011698405</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>8.690745920169588</v>
+        <v>8.900831584788696</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.51035007476807</v>
+        <v>47.51085006713867</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>8.102761881411553</v>
+        <v>8.312099261017966</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.1896129104377755</v>
+        <v>0.1903497167132751</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22808,13 +22808,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>34.24</v>
+        <v>34.31</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12.14</v>
+        <v>12.17</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22849,13 +22849,13 @@
         <v>8</v>
       </c>
       <c r="CM78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN78" t="n">
         <v>1</v>
       </c>
       <c r="CO78" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79">
@@ -22868,82 +22868,82 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10.15999984741211</v>
+        <v>10.11999988555908</v>
       </c>
       <c r="D79" t="n">
-        <v>10.15999984741211</v>
+        <v>10.11999988555908</v>
       </c>
       <c r="E79" t="n">
         <v>10.48999977111816</v>
       </c>
       <c r="F79" t="n">
-        <v>10.09000015258789</v>
+        <v>10.07999992370605</v>
       </c>
       <c r="G79" t="n">
         <v>10.14000034332275</v>
       </c>
       <c r="H79" t="n">
-        <v>2839000</v>
+        <v>4236600</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0009852442618401014</v>
+        <v>-0.002955638827455975</v>
       </c>
       <c r="J79" t="n">
-        <v>9.945555475023058</v>
+        <v>9.941111034817165</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.156182959590342</v>
+        <v>1.799485491263369</v>
       </c>
       <c r="M79" t="n">
-        <v>9.881999969482422</v>
+        <v>9.877999973297118</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.813194482778854</v>
+        <v>2.449887759831487</v>
       </c>
       <c r="P79" t="n">
-        <v>8.756923015301044</v>
+        <v>8.755384555229774</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>16.02248677599948</v>
+        <v>15.58601249004185</v>
       </c>
       <c r="S79" t="n">
-        <v>8.541799993515015</v>
+        <v>8.540999994277954</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>18.94448307295466</v>
+        <v>18.48729530896827</v>
       </c>
       <c r="V79" t="n">
-        <v>9.944933300018311</v>
+        <v>9.944666633605957</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>2.16257405560882</v>
+        <v>1.763088280512315</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.71189998149872</v>
+        <v>10.71169998168945</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-5.152215153612657</v>
+        <v>-5.523867333306767</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5505434359653308</v>
+        <v>0.5510360418853029</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23091,10 +23091,10 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>23.63</v>
+        <v>23.53</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CB79" t="n">
         <v>0.93</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.60000038146973</v>
+        <v>15.63000011444092</v>
       </c>
       <c r="D2" t="n">
-        <v>15.60000038146973</v>
+        <v>15.63000011444092</v>
       </c>
       <c r="E2" t="n">
         <v>15.77000045776367</v>
@@ -912,67 +912,67 @@
         <v>15.69999980926514</v>
       </c>
       <c r="H2" t="n">
-        <v>25452400</v>
+        <v>32090400</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.008264409698013231</v>
+        <v>-0.006357242892913173</v>
       </c>
       <c r="J2" t="n">
-        <v>15.71777767605252</v>
+        <v>15.72111097971598</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7493253627211878</v>
+        <v>-0.5795446987978106</v>
       </c>
       <c r="M2" t="n">
-        <v>15.70599994659424</v>
+        <v>15.70899991989136</v>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6748985450461358</v>
+        <v>-0.5028951929040847</v>
       </c>
       <c r="P2" t="n">
-        <v>15.26846148417546</v>
+        <v>15.26961532005897</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.171396886568286</v>
+        <v>2.360143244136138</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51119997024536</v>
+        <v>15.51179996490479</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5724922081767281</v>
+        <v>0.7620015072625919</v>
       </c>
       <c r="V2" t="n">
-        <v>15.69480000178019</v>
+        <v>15.695</v>
       </c>
       <c r="W2" t="n">
         <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6040192949238823</v>
+        <v>-0.4141439028931654</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.31244999885559</v>
+        <v>15.31259999752045</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.87788618173856</v>
+        <v>2.07280355375225</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.17421066095594</v>
+        <v>0.1735598226347154</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>15.76</v>
+        <v>15.79</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
@@ -1184,82 +1184,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.48999977111816</v>
+        <v>28.45999908447266</v>
       </c>
       <c r="D3" t="n">
-        <v>28.48999977111816</v>
+        <v>28.45999908447266</v>
       </c>
       <c r="E3" t="n">
         <v>28.81999969482422</v>
       </c>
       <c r="F3" t="n">
-        <v>28.42000007629395</v>
+        <v>28.39999961853027</v>
       </c>
       <c r="G3" t="n">
         <v>28.53000068664551</v>
       </c>
       <c r="H3" t="n">
-        <v>7418100</v>
+        <v>9012600</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001402065004017627</v>
+        <v>-0.002453613757030793</v>
       </c>
       <c r="J3" t="n">
-        <v>28.74777772691515</v>
+        <v>28.74444431728787</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8966882875111316</v>
+        <v>-0.9895659476851929</v>
       </c>
       <c r="M3" t="n">
-        <v>28.72600002288818</v>
+        <v>28.72299995422363</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8215562611640309</v>
+        <v>-0.9156455459740432</v>
       </c>
       <c r="P3" t="n">
-        <v>27.11230769524207</v>
+        <v>27.11115382267879</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>5.081426824164663</v>
+        <v>4.975241078325278</v>
       </c>
       <c r="S3" t="n">
-        <v>27.22439998626709</v>
+        <v>27.22379997253418</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4.648770167531642</v>
+        <v>4.540876413967427</v>
       </c>
       <c r="V3" t="n">
-        <v>28.9106666692098</v>
+        <v>28.91046666463216</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.455057757418132</v>
+        <v>-1.558147038527701</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.96499999046326</v>
+        <v>28.96484998703003</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.639910994308597</v>
+        <v>-1.742977791300269</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2629959484657652</v>
+        <v>0.2631049274277038</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.10999965667725</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="D4" t="n">
-        <v>10.10999965667725</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="E4" t="n">
         <v>10.1899995803833</v>
@@ -1482,67 +1482,67 @@
         <v>9.619999885559082</v>
       </c>
       <c r="H4" t="n">
-        <v>14110100</v>
+        <v>16499800</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0476683996197953</v>
+        <v>0.04663220525681111</v>
       </c>
       <c r="J4" t="n">
-        <v>9.509999805026585</v>
+        <v>9.508888774447971</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>6.309146834404002</v>
+        <v>6.216410992314627</v>
       </c>
       <c r="M4" t="n">
-        <v>9.471999835968017</v>
+        <v>9.470999908447265</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>6.735640115686585</v>
+        <v>6.641331212150586</v>
       </c>
       <c r="P4" t="n">
-        <v>8.703076857786913</v>
+        <v>8.702692270278931</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>16.16580919461277</v>
+        <v>16.05604412743426</v>
       </c>
       <c r="S4" t="n">
-        <v>8.57419994354248</v>
+        <v>8.57399995803833</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>17.91187193262771</v>
+        <v>17.79799896080865</v>
       </c>
       <c r="V4" t="n">
-        <v>8.708933267593384</v>
+        <v>8.708866605758667</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>16.08769232734092</v>
+        <v>15.97376373627291</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.55744993686676</v>
+        <v>8.557399940490722</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.14266786559711</v>
+        <v>18.02650865574181</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.534788737308172</v>
+        <v>0.5340975455380089</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1692,7 +1692,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>19.44</v>
+        <v>19.42</v>
       </c>
       <c r="CA4" t="n">
         <v>0.88</v>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.61999988555908</v>
+        <v>11.67000007629395</v>
       </c>
       <c r="D5" t="n">
-        <v>11.61999988555908</v>
+        <v>11.67000007629395</v>
       </c>
       <c r="E5" t="n">
         <v>11.68000030517578</v>
@@ -1767,73 +1767,73 @@
         <v>11.52000045776367</v>
       </c>
       <c r="H5" t="n">
-        <v>1829700</v>
+        <v>2320200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003454228162052209</v>
+        <v>0.007772033953441282</v>
       </c>
       <c r="J5" t="n">
-        <v>11.82000001271566</v>
+        <v>11.82555558946398</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.692048451281058</v>
+        <v>-1.315418222790508</v>
       </c>
       <c r="M5" t="n">
-        <v>11.8039999961853</v>
+        <v>11.80900001525879</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.558794566974616</v>
+        <v>-1.177067819334723</v>
       </c>
       <c r="P5" t="n">
-        <v>10.99192311213567</v>
+        <v>10.9938461963947</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.713984413973785</v>
+        <v>6.150294153842</v>
       </c>
       <c r="S5" t="n">
-        <v>11.25459997177124</v>
+        <v>11.22819997787476</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3.246671713826676</v>
+        <v>3.934736638907038</v>
       </c>
       <c r="V5" t="n">
-        <v>11.97633331934611</v>
+        <v>11.97159998575846</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.975313263963866</v>
+        <v>-2.519294913155332</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.94504998207092</v>
+        <v>11.93934998035431</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2.721211690195766</v>
+        <v>-2.255984659998812</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2945445748853566</v>
+        <v>0.290216574234037</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="AE5" t="n">
         <v>11.4</v>
@@ -1975,13 +1975,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.49</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.20999908447266</v>
+        <v>55.22999954223633</v>
       </c>
       <c r="D6" t="n">
-        <v>55.20999908447266</v>
+        <v>55.22999954223633</v>
       </c>
       <c r="E6" t="n">
         <v>55.56999969482422</v>
@@ -2046,67 +2046,67 @@
         <v>54.56000137329102</v>
       </c>
       <c r="H6" t="n">
-        <v>5000100</v>
+        <v>7080300</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004914460584504177</v>
+        <v>0.005278502416750319</v>
       </c>
       <c r="J6" t="n">
-        <v>55.32888878716363</v>
+        <v>55.33111106024848</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2148781681633086</v>
+        <v>-0.1827389981416713</v>
       </c>
       <c r="M6" t="n">
-        <v>55.35200004577636</v>
+        <v>55.35400009155273</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2565416989201341</v>
+        <v>-0.2240137101407587</v>
       </c>
       <c r="P6" t="n">
-        <v>53.01961517333984</v>
+        <v>53.02038442171537</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>4.131270858854169</v>
+        <v>4.167482270490619</v>
       </c>
       <c r="S6" t="n">
-        <v>52.55499977111816</v>
+        <v>52.52459976196289</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>5.05184915786749</v>
+        <v>5.150728977534498</v>
       </c>
       <c r="V6" t="n">
-        <v>55.97419995625814</v>
+        <v>55.92913327534993</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.365273415935698</v>
+        <v>-1.250034985651636</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.14090000152588</v>
+        <v>56.08744998931885</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.658151039666127</v>
+        <v>-1.52877416827795</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2786152447211049</v>
+        <v>0.246112021462997</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.88</v>
+        <v>16.89</v>
       </c>
       <c r="CA6" t="n">
         <v>0.28</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.11999988555908</v>
+        <v>15.02999973297119</v>
       </c>
       <c r="D7" t="n">
-        <v>15.11999988555908</v>
+        <v>15.02999973297119</v>
       </c>
       <c r="E7" t="n">
         <v>15.38000011444092</v>
@@ -2325,67 +2325,67 @@
         <v>15.34000015258789</v>
       </c>
       <c r="H7" t="n">
-        <v>3164000</v>
+        <v>3672800</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01176472568181952</v>
+        <v>-0.01764708852272923</v>
       </c>
       <c r="J7" t="n">
-        <v>16.45333332485623</v>
+        <v>16.44333330790202</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.10372836295041</v>
+        <v>-8.595176832252347</v>
       </c>
       <c r="M7" t="n">
-        <v>16.48500003814697</v>
+        <v>16.47600002288818</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.280255683525766</v>
+        <v>-8.776403786770041</v>
       </c>
       <c r="P7" t="n">
-        <v>15.63346158541166</v>
+        <v>15.63000004108136</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-3.284376253124345</v>
+        <v>-3.838773554274756</v>
       </c>
       <c r="S7" t="n">
-        <v>16.50279998779297</v>
+        <v>16.47439998626709</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.379184764141458</v>
+        <v>-8.767543913586769</v>
       </c>
       <c r="V7" t="n">
-        <v>20.27640003204346</v>
+        <v>20.21626669565837</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-25.43055048398901</v>
+        <v>-25.6539302768546</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.59210000038147</v>
+        <v>21.53295000076294</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-29.97438931233203</v>
+        <v>-30.19999706292607</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5238441941074459</v>
+        <v>0.5180244826537254</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CA7" t="n">
         <v>0.7</v>
@@ -2608,7 +2608,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="H8" t="n">
-        <v>20184600</v>
+        <v>30852600</v>
       </c>
       <c r="I8" t="n">
         <v>0.009184836206163061</v>
@@ -2641,34 +2641,34 @@
         <v>9.78527013038927</v>
       </c>
       <c r="S8" t="n">
-        <v>15.70100002288818</v>
+        <v>15.70380002975464</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>11.96738996292435</v>
+        <v>11.94742603953503</v>
       </c>
       <c r="V8" t="n">
-        <v>16.63793338139852</v>
+        <v>16.61826670964559</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.662160802739973</v>
+        <v>5.787205313670023</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.17135005950928</v>
+        <v>16.17385005950928</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.710774666388765</v>
+        <v>8.693971188202301</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3297453230436417</v>
+        <v>0.3175573527726396</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.5</v>
+        <v>22.70999908447266</v>
       </c>
       <c r="D9" t="n">
-        <v>22.5</v>
+        <v>22.70999908447266</v>
       </c>
       <c r="E9" t="n">
-        <v>22.67000007629395</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="F9" t="n">
         <v>21.51000022888184</v>
@@ -2895,88 +2895,88 @@
         <v>21.95000076293945</v>
       </c>
       <c r="H9" t="n">
-        <v>26163100</v>
+        <v>31940600</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02087110096935541</v>
+        <v>0.03039918970571787</v>
       </c>
       <c r="J9" t="n">
-        <v>22.41111140780979</v>
+        <v>22.43444463941786</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3966273272785415</v>
+        <v>1.228265060640898</v>
       </c>
       <c r="M9" t="n">
-        <v>22.39600028991699</v>
+        <v>22.41700019836426</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4643673367419603</v>
+        <v>1.307038780906018</v>
       </c>
       <c r="P9" t="n">
-        <v>20.34269237518311</v>
+        <v>20.35076926304744</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>10.60482843189766</v>
+        <v>11.59282870799908</v>
       </c>
       <c r="S9" t="n">
-        <v>20.46200004577637</v>
+        <v>20.472200050354</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>9.9599254699655</v>
+        <v>10.93091621132315</v>
       </c>
       <c r="V9" t="n">
-        <v>21.88573333740234</v>
+        <v>21.85520000457764</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>2.806699017701574</v>
+        <v>3.911193124363904</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.04560000419617</v>
+        <v>22.03695000648499</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.061182257309132</v>
+        <v>3.05418434851287</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3694550271463342</v>
+        <v>0.370556158428223</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="AH9" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>22.9</v>
+        <v>30</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -3123,13 +3123,13 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.960000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="CC9" t="n">
         <v>1</v>
@@ -3160,13 +3160,13 @@
         <v>9</v>
       </c>
       <c r="CM9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.96000003814697</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="D10" t="n">
-        <v>15.96000003814697</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="E10" t="n">
         <v>16.13999938964844</v>
@@ -3194,67 +3194,67 @@
         <v>16.06999969482422</v>
       </c>
       <c r="H10" t="n">
-        <v>3856000</v>
+        <v>5038700</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008079559553018978</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>16.01444456312392</v>
+        <v>16.02888902028402</v>
       </c>
       <c r="K10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3399713599952881</v>
+        <v>0.3812561945281474</v>
       </c>
       <c r="M10" t="n">
-        <v>15.97200012207031</v>
+        <v>15.9850001335144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0751320049563359</v>
+        <v>0.6568659255331605</v>
       </c>
       <c r="P10" t="n">
-        <v>15.13769237811749</v>
+        <v>15.14269238251906</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>5.432186356344396</v>
+        <v>6.255874095166947</v>
       </c>
       <c r="S10" t="n">
-        <v>15.55561779022217</v>
+        <v>15.54841777801514</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2.599589764792163</v>
+        <v>3.483199270208252</v>
       </c>
       <c r="V10" t="n">
-        <v>16.20493927637736</v>
+        <v>16.18587261199951</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.511509756703905</v>
+        <v>-0.5923218457838603</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29540446281433</v>
+        <v>16.29030446529389</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.05827615652464</v>
+        <v>-1.229592197817659</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.232211623898299</v>
+        <v>0.222484431726852</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         <v>15.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -3422,13 +3422,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.13</v>
+        <v>7.18</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="CC10" t="n">
         <v>2</v>
@@ -3456,16 +3456,16 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.05999946594238</v>
+        <v>18.20999908447266</v>
       </c>
       <c r="D11" t="n">
-        <v>18.05999946594238</v>
+        <v>18.20999908447266</v>
       </c>
       <c r="E11" t="n">
         <v>18.25</v>
@@ -3493,88 +3493,88 @@
         <v>18.20999908447266</v>
       </c>
       <c r="H11" t="n">
-        <v>23585900</v>
+        <v>34348900</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.007692378633420427</v>
+        <v>0.0005493583029712035</v>
       </c>
       <c r="J11" t="n">
-        <v>18.15111117892795</v>
+        <v>18.16777780320909</v>
       </c>
       <c r="K11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5019621778932338</v>
+        <v>0.2323965083726813</v>
       </c>
       <c r="M11" t="n">
-        <v>18.11100006103516</v>
+        <v>18.12600002288819</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.281600104471859</v>
+        <v>0.4634175299481594</v>
       </c>
       <c r="P11" t="n">
-        <v>17.18576937455397</v>
+        <v>17.19153859065129</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>5.08694183155299</v>
+        <v>5.924196304193512</v>
       </c>
       <c r="S11" t="n">
-        <v>17.74574043273926</v>
+        <v>17.73594043731689</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.770898398938296</v>
+        <v>2.67287009014943</v>
       </c>
       <c r="V11" t="n">
-        <v>18.62211348215739</v>
+        <v>18.59824681599935</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.018529646238007</v>
+        <v>-2.087550161946979</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.79453512191773</v>
+        <v>18.78643511772156</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.908240620002062</v>
+        <v>-3.068363048320637</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2718399029445683</v>
+        <v>0.2605371784137899</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AJ11" t="n">
         <v>2</v>
@@ -3721,13 +3721,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3758,13 +3758,13 @@
         <v>4</v>
       </c>
       <c r="CM11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CN11" t="n">
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.72000122070312</v>
+        <v>40.59000015258789</v>
       </c>
       <c r="D12" t="n">
-        <v>40.72000122070312</v>
+        <v>40.59000015258789</v>
       </c>
       <c r="E12" t="n">
         <v>40.95000076293945</v>
@@ -3792,98 +3792,94 @@
         <v>40.15999984741211</v>
       </c>
       <c r="H12" t="n">
-        <v>5469500</v>
+        <v>6865700</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01394425735604443</v>
+        <v>0.01070717895442153</v>
       </c>
       <c r="J12" t="n">
-        <v>40.93999989827474</v>
+        <v>40.92555533515083</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.537368534729498</v>
+        <v>-0.8199160153478176</v>
       </c>
       <c r="M12" t="n">
-        <v>41.025</v>
+        <v>41.01199989318847</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7434461408820807</v>
+        <v>-1.028966501754701</v>
       </c>
       <c r="P12" t="n">
-        <v>39.26615377572867</v>
+        <v>39.26115373464731</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.702546099315473</v>
+        <v>3.384634152429141</v>
       </c>
       <c r="S12" t="n">
-        <v>39.99659980773926</v>
+        <v>39.98759979248047</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.808657276971554</v>
+        <v>1.506467913137171</v>
       </c>
       <c r="V12" t="n">
-        <v>37.03159990946452</v>
+        <v>37.03653322855632</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>9.960145714082225</v>
+        <v>9.594491207108288</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.705299949646</v>
+        <v>36.72509994506836</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.93766098237769</v>
+        <v>10.52386573025115</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3239372011863906</v>
+        <v>0.3158706109274457</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AE12" t="n">
         <v>39.6</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>40.2</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>40.6</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AI12" t="n">
         <v>43</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ12" t="n">
         <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -4024,13 +4020,13 @@
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="n">
-        <v>8.609999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4080,10 +4076,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.990000009536743</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3.990000009536743</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>4.039999961853027</v>
@@ -4095,67 +4091,67 @@
         <v>4.03000020980835</v>
       </c>
       <c r="H13" t="n">
-        <v>10088800</v>
+        <v>13530500</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0123762259377227</v>
+        <v>-0.009900980750178201</v>
       </c>
       <c r="J13" t="n">
-        <v>3.985555569330851</v>
+        <v>3.986666679382324</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1115136930994609</v>
+        <v>0.3344478405137593</v>
       </c>
       <c r="M13" t="n">
-        <v>3.973000001907349</v>
+        <v>3.974000000953674</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4278884374838416</v>
+        <v>0.6542526180192837</v>
       </c>
       <c r="P13" t="n">
-        <v>3.778076923810519</v>
+        <v>3.778461538828336</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>5.609284564605465</v>
+        <v>5.863192172133652</v>
       </c>
       <c r="S13" t="n">
-        <v>3.678000001907348</v>
+        <v>3.674800000190735</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>8.482871328645917</v>
+        <v>8.84946118951742</v>
       </c>
       <c r="V13" t="n">
-        <v>4.041533338228861</v>
+        <v>4.022800005276998</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.275093494953123</v>
+        <v>-0.5667695447720305</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.495500005483628</v>
+        <v>4.480450004339218</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-11.24457780736901</v>
+        <v>-10.72325333111435</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5426450574873564</v>
+        <v>0.535831554632093</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4307,10 +4303,10 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB13" t="n">
         <v>3.17</v>
@@ -4367,10 +4363,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60.68000030517578</v>
+        <v>60.83000183105469</v>
       </c>
       <c r="D14" t="n">
-        <v>60.68000030517578</v>
+        <v>60.83000183105469</v>
       </c>
       <c r="E14" t="n">
         <v>61.20000076293945</v>
@@ -4382,67 +4378,67 @@
         <v>60.16999816894531</v>
       </c>
       <c r="H14" t="n">
-        <v>8466300</v>
+        <v>10438300</v>
       </c>
       <c r="I14" t="n">
-        <v>0.007973414221812192</v>
+        <v>0.01046513388921877</v>
       </c>
       <c r="J14" t="n">
-        <v>60.03000047471788</v>
+        <v>60.04666731092665</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.082791646372973</v>
+        <v>1.304542875080585</v>
       </c>
       <c r="M14" t="n">
-        <v>59.79500045776367</v>
+        <v>59.81000061035157</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.480056594425871</v>
+        <v>1.705402458274823</v>
       </c>
       <c r="P14" t="n">
-        <v>55.00884642967811</v>
+        <v>55.01461571913499</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>10.30953063658139</v>
+        <v>10.57062025409551</v>
       </c>
       <c r="S14" t="n">
-        <v>55.54380012512207</v>
+        <v>55.54680015563965</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.247116993226118</v>
+        <v>9.511261963986659</v>
       </c>
       <c r="V14" t="n">
-        <v>56.28593325297038</v>
+        <v>56.28693326314291</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>7.806687742844723</v>
+        <v>8.071266819019639</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.08889993667603</v>
+        <v>56.08964994430542</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.185399203198978</v>
+        <v>8.451384331077533</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3536915239873394</v>
+        <v>0.3541014329578696</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4612,13 +4608,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.64</v>
+        <v>13.67</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CC14" t="n">
         <v>6</v>
@@ -4650,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM14" t="n">
         <v>9</v>
@@ -4659,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -4672,82 +4668,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.8700008392334</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="D15" t="n">
-        <v>20.8700008392334</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="E15" t="n">
         <v>21.61000061035156</v>
       </c>
       <c r="F15" t="n">
-        <v>20.85000038146973</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="G15" t="n">
         <v>21.47999954223633</v>
       </c>
       <c r="H15" t="n">
-        <v>2795400</v>
+        <v>3719200</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02839845046567546</v>
+        <v>-0.02932957049313845</v>
       </c>
       <c r="J15" t="n">
-        <v>22.15555551317003</v>
+        <v>22.15333324008518</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.802403253542671</v>
+        <v>-5.883235919807978</v>
       </c>
       <c r="M15" t="n">
-        <v>22.23799991607666</v>
+        <v>22.23599987030029</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.151628212995385</v>
+        <v>-6.233133193537158</v>
       </c>
       <c r="P15" t="n">
-        <v>21.59692302116981</v>
+        <v>21.59615377279428</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.365859947844714</v>
+        <v>-3.455029072188417</v>
       </c>
       <c r="S15" t="n">
-        <v>21.56520000457764</v>
+        <v>21.56199996948242</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.223708406120364</v>
+        <v>-3.302103650034399</v>
       </c>
       <c r="V15" t="n">
-        <v>22.63620002746582</v>
+        <v>22.61653335571289</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.802542768173934</v>
+        <v>-7.810803479291577</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.37394998550415</v>
+        <v>22.38879998207092</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-6.721875874600351</v>
+        <v>-6.873077618422935</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2794492467329537</v>
+        <v>0.2868952110704882</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,7 +4899,7 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
@@ -4944,13 +4940,13 @@
         <v>2</v>
       </c>
       <c r="CM15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -4963,13 +4959,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.70000076293945</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="D16" t="n">
-        <v>17.70000076293945</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="E16" t="n">
-        <v>17.79999923706055</v>
+        <v>17.80999946594238</v>
       </c>
       <c r="F16" t="n">
         <v>17.54999923706055</v>
@@ -4978,67 +4974,67 @@
         <v>17.79999923706055</v>
       </c>
       <c r="H16" t="n">
-        <v>2508400</v>
+        <v>3266200</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01172524211400261</v>
+        <v>-0.01005026838131384</v>
       </c>
       <c r="J16" t="n">
-        <v>18.18555556403266</v>
+        <v>18.18888876173231</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.670002570905984</v>
+        <v>-2.522909593363647</v>
       </c>
       <c r="M16" t="n">
-        <v>18.25900001525879</v>
+        <v>18.26199989318848</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.061499818457678</v>
+        <v>-2.913154934091196</v>
       </c>
       <c r="P16" t="n">
-        <v>18.22923066065862</v>
+        <v>18.23038445986234</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-2.90319381860321</v>
+        <v>-2.744785326539367</v>
       </c>
       <c r="S16" t="n">
-        <v>18.94479991912842</v>
+        <v>18.93799987792969</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.570664042390336</v>
+        <v>-6.378711286724428</v>
       </c>
       <c r="V16" t="n">
-        <v>19.18326657613119</v>
+        <v>19.18726656595866</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.732081537339883</v>
+        <v>-7.594969396567201</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.39794991493225</v>
+        <v>18.42199990749359</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.793624589804566</v>
+        <v>-3.756380244990539</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4060119021010896</v>
+        <v>0.3830374733211145</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5186,7 +5182,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>35.4</v>
+        <v>35.46</v>
       </c>
       <c r="CA16" t="n">
         <v>1.29</v>
@@ -5242,10 +5238,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.519999980926514</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="D17" t="n">
-        <v>4.519999980926514</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="E17" t="n">
         <v>5.21999979019165</v>
@@ -5257,67 +5253,67 @@
         <v>5.199999809265137</v>
       </c>
       <c r="H17" t="n">
-        <v>10899000</v>
+        <v>12487700</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.153558080192935</v>
+        <v>-0.1516853782086497</v>
       </c>
       <c r="J17" t="n">
-        <v>5.025555610656738</v>
+        <v>5.026666747199164</v>
       </c>
       <c r="K17" t="n">
         <v>-1</v>
       </c>
       <c r="L17" t="n">
-        <v>-10.05969625842343</v>
+        <v>-9.880633874675601</v>
       </c>
       <c r="M17" t="n">
-        <v>5.011000061035157</v>
+        <v>5.01200008392334</v>
       </c>
       <c r="N17" t="n">
         <v>-1</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.79844490377463</v>
+        <v>-9.616916720753244</v>
       </c>
       <c r="P17" t="n">
-        <v>4.855384606581468</v>
+        <v>4.855769230769231</v>
       </c>
       <c r="Q17" t="n">
         <v>-1</v>
       </c>
       <c r="R17" t="n">
-        <v>-6.9074780440738</v>
+        <v>-6.708906570283495</v>
       </c>
       <c r="S17" t="n">
-        <v>5.457799987792969</v>
+        <v>5.457999992370605</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-17.18274779149031</v>
+        <v>-17.00256108207124</v>
       </c>
       <c r="V17" t="n">
-        <v>8.266533301671346</v>
+        <v>8.266599969863892</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-45.32169875838219</v>
+        <v>-45.20116823939001</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.271549978256225</v>
+        <v>8.271599979400635</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-45.3548610259452</v>
+        <v>-45.23429298938854</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.169761991573947</v>
+        <v>1.1677177173739</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5469,10 +5465,10 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="CA17" t="n">
-        <v>11.94</v>
+        <v>11.91</v>
       </c>
       <c r="CB17" t="n">
         <v>-0.23</v>
@@ -5529,10 +5525,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.289999961853027</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="D18" t="n">
-        <v>9.289999961853027</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="E18" t="n">
         <v>9.399999618530273</v>
@@ -5544,67 +5540,67 @@
         <v>9.270000457763672</v>
       </c>
       <c r="H18" t="n">
-        <v>6312900</v>
+        <v>7529600</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003239711903853193</v>
+        <v>-0.004319650201332403</v>
       </c>
       <c r="J18" t="n">
-        <v>9.286666658189562</v>
+        <v>9.278888914320204</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0358934350305984</v>
+        <v>-0.6346519269188766</v>
       </c>
       <c r="M18" t="n">
-        <v>9.297000026702881</v>
+        <v>9.290000057220459</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0752938026217871</v>
+        <v>-0.7534961222873638</v>
       </c>
       <c r="P18" t="n">
-        <v>8.484615435967079</v>
+        <v>8.481923140012301</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>9.492292632048446</v>
+        <v>8.701766272023042</v>
       </c>
       <c r="S18" t="n">
-        <v>9.092200031280518</v>
+        <v>9.064600028991698</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.17549030918815</v>
+        <v>1.71436398230575</v>
       </c>
       <c r="V18" t="n">
-        <v>10.83206666946411</v>
+        <v>10.80420000076294</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.23612644444123</v>
+        <v>-14.66281384667317</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.34225001335144</v>
+        <v>11.29525001525879</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-18.09385306339239</v>
+        <v>-18.37276505988375</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5239521098969746</v>
+        <v>0.511101033236728</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5754,7 +5750,7 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>4.89</v>
+        <v>4.85</v>
       </c>
       <c r="CA18" t="n">
         <v>0.05</v>
@@ -5795,13 +5791,13 @@
         <v>4</v>
       </c>
       <c r="CM18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN18" t="n">
         <v>0</v>
       </c>
       <c r="CO18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -5814,10 +5810,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.30000019073486</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="D19" t="n">
-        <v>11.30000019073486</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="E19" t="n">
         <v>11.35000038146973</v>
@@ -5829,67 +5825,67 @@
         <v>11.10000038146973</v>
       </c>
       <c r="H19" t="n">
-        <v>12152900</v>
+        <v>18386500</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01801800021547884</v>
+        <v>0.02162160025857451</v>
       </c>
       <c r="J19" t="n">
-        <v>11.33333343929715</v>
+        <v>11.33777787950304</v>
       </c>
       <c r="K19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2941168963290451</v>
+        <v>0.01960060523737867</v>
       </c>
       <c r="M19" t="n">
-        <v>11.29700012207031</v>
+        <v>11.30100011825562</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02655633028356286</v>
+        <v>0.3451025035321856</v>
       </c>
       <c r="P19" t="n">
-        <v>10.70730770551241</v>
+        <v>10.70884616558368</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>5.535401629648843</v>
+        <v>5.893762756931028</v>
       </c>
       <c r="S19" t="n">
-        <v>10.90799997329712</v>
+        <v>10.90879997253418</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.593694704779645</v>
+        <v>3.952773734410501</v>
       </c>
       <c r="V19" t="n">
-        <v>11.52046672185262</v>
+        <v>11.52073338826497</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.913694439996649</v>
+        <v>-1.568765022035647</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.44065003395081</v>
+        <v>11.44085003376007</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.229386816295895</v>
+        <v>-0.8814894074705051</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2848654978492932</v>
+        <v>0.2870058869610226</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6041,7 +6037,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
       <c r="CA19" t="n">
         <v>0.55</v>
@@ -6056,7 +6052,7 @@
         <v>5</v>
       </c>
       <c r="CE19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CF19" t="n">
         <v>9</v>
@@ -6075,16 +6071,16 @@
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN19" t="n">
         <v>0</v>
       </c>
       <c r="CO19" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -6097,10 +6093,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.059999942779541</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="D20" t="n">
-        <v>6.059999942779541</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="E20" t="n">
         <v>6.199999809265137</v>
@@ -6112,67 +6108,67 @@
         <v>6.199999809265137</v>
       </c>
       <c r="H20" t="n">
-        <v>13080400</v>
+        <v>14332600</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02258062432137231</v>
+        <v>-0.01935482084689055</v>
       </c>
       <c r="J20" t="n">
-        <v>6.573333263397217</v>
+        <v>6.575555483500163</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.809330518446525</v>
+        <v>-7.536329988205415</v>
       </c>
       <c r="M20" t="n">
-        <v>6.555999946594238</v>
+        <v>6.557999944686889</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.565588893458782</v>
+        <v>-7.288807944685895</v>
       </c>
       <c r="P20" t="n">
-        <v>6.107692296688374</v>
+        <v>6.108461526724009</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.7808571812743679</v>
+        <v>-0.4659373377967059</v>
       </c>
       <c r="S20" t="n">
-        <v>5.817599973678589</v>
+        <v>5.836199970245361</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>4.166666154388022</v>
+        <v>4.177374913533745</v>
       </c>
       <c r="V20" t="n">
-        <v>5.145266653696696</v>
+        <v>5.141866655349731</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>17.7781512727944</v>
+        <v>18.24499410890528</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.267849991321564</v>
+        <v>5.268449990749359</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.03744322186457</v>
+        <v>15.40396007139975</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.515332759671732</v>
+        <v>0.5060613890852647</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6324,13 +6320,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>14.78</v>
+        <v>14.83</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6399,7 +6395,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="H21" t="n">
-        <v>36070800</v>
+        <v>40962000</v>
       </c>
       <c r="I21" t="n">
         <v>-0.01673648473467759</v>
@@ -6432,34 +6428,34 @@
         <v>4.820719781150632</v>
       </c>
       <c r="S21" t="n">
-        <v>2.235200004577637</v>
+        <v>2.233600006103516</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>5.136001244623483</v>
+        <v>5.211313494402737</v>
       </c>
       <c r="V21" t="n">
-        <v>2.658200000127156</v>
+        <v>2.647133334477743</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-11.59431553230927</v>
+        <v>-11.22472472297268</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.909299956560135</v>
+        <v>2.902540867328644</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-19.22455780698754</v>
+        <v>-19.03645764011609</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4560318603925175</v>
+        <v>0.4115107986407652</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6649,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM21" t="n">
         <v>3</v>
@@ -6658,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -6671,10 +6667,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.13000106811523</v>
+        <v>45.13999938964844</v>
       </c>
       <c r="D22" t="n">
-        <v>45.13000106811523</v>
+        <v>45.13999938964844</v>
       </c>
       <c r="E22" t="n">
         <v>45.58000183105469</v>
@@ -6686,67 +6682,67 @@
         <v>44.7400016784668</v>
       </c>
       <c r="H22" t="n">
-        <v>995300</v>
+        <v>1771400</v>
       </c>
       <c r="I22" t="n">
-        <v>0.009168153761639486</v>
+        <v>0.009391729818443606</v>
       </c>
       <c r="J22" t="n">
-        <v>45.93777804904514</v>
+        <v>45.93888897365994</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.758415437654568</v>
+        <v>-1.73902678506127</v>
       </c>
       <c r="M22" t="n">
-        <v>45.95200042724609</v>
+        <v>45.95300025939942</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.788821708496226</v>
+        <v>-1.769200846868937</v>
       </c>
       <c r="P22" t="n">
-        <v>44.22615418067345</v>
+        <v>44.22653873150166</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.043693158915354</v>
+        <v>2.06541294965989</v>
       </c>
       <c r="S22" t="n">
-        <v>45.15080009460449</v>
+        <v>45.13020011901855</v>
       </c>
       <c r="T22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0460656875308456</v>
+        <v>0.02171333298775776</v>
       </c>
       <c r="V22" t="n">
-        <v>46.87559984842936</v>
+        <v>46.83699984232585</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.72389641083732</v>
+        <v>-3.623204855969138</v>
       </c>
       <c r="Y22" t="n">
-        <v>48.00319993972779</v>
+        <v>47.98424993515015</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.985431961244466</v>
+        <v>-5.927466927889177</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.272869007649624</v>
+        <v>0.2676673642401385</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6954,10 +6950,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.02000045776367</v>
+        <v>16.07999992370605</v>
       </c>
       <c r="D23" t="n">
-        <v>16.02000045776367</v>
+        <v>16.07999992370605</v>
       </c>
       <c r="E23" t="n">
         <v>16.20000076293945</v>
@@ -6969,67 +6965,67 @@
         <v>15.86999988555908</v>
       </c>
       <c r="H23" t="n">
-        <v>14232900</v>
+        <v>18357800</v>
       </c>
       <c r="I23" t="n">
-        <v>0.005018875751968244</v>
+        <v>0.008782957779688294</v>
       </c>
       <c r="J23" t="n">
-        <v>15.95444435543484</v>
+        <v>15.96111096276177</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4108955527899608</v>
+        <v>0.7448664521013452</v>
       </c>
       <c r="M23" t="n">
-        <v>15.91899995803833</v>
+        <v>15.92499990463257</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6344651045390617</v>
+        <v>0.9733125274832666</v>
       </c>
       <c r="P23" t="n">
-        <v>14.8838460628803</v>
+        <v>14.88615373464731</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7.633473163343833</v>
+        <v>8.019843206913043</v>
       </c>
       <c r="S23" t="n">
-        <v>14.88119997024536</v>
+        <v>14.87019996643066</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.652611951961649</v>
+        <v>8.135734287410404</v>
       </c>
       <c r="V23" t="n">
-        <v>15.02413326899211</v>
+        <v>15.02839993158976</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>6.628450180396821</v>
+        <v>6.997418200894594</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.54164995670319</v>
+        <v>14.54659995555878</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.16631885282742</v>
+        <v>10.54129468626316</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2224843925069958</v>
+        <v>0.1984120198413729</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7181,7 +7177,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.6</v>
+        <v>17.67</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
@@ -7237,10 +7233,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="D24" t="n">
-        <v>3.630000114440918</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="E24" t="n">
         <v>3.700000047683716</v>
@@ -7252,67 +7248,67 @@
         <v>3.519999980926514</v>
       </c>
       <c r="H24" t="n">
-        <v>35655400</v>
+        <v>42418100</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02542377219144942</v>
+        <v>0.03107348437846436</v>
       </c>
       <c r="J24" t="n">
-        <v>3.738888872994317</v>
+        <v>3.741111093097263</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.912329364477599</v>
+        <v>-2.435399416444501</v>
       </c>
       <c r="M24" t="n">
-        <v>3.743999981880188</v>
+        <v>3.745999979972839</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.044868268990233</v>
+        <v>-2.562730515714087</v>
       </c>
       <c r="P24" t="n">
-        <v>3.600769235537602</v>
+        <v>3.601538465573237</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8117953967952994</v>
+        <v>1.34558134690034</v>
       </c>
       <c r="S24" t="n">
-        <v>3.744400019645691</v>
+        <v>3.737000021934509</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.055226594502529</v>
+        <v>-2.328068666214272</v>
       </c>
       <c r="V24" t="n">
-        <v>4.522466669082641</v>
+        <v>4.505333336194356</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-19.73406594111518</v>
+        <v>-18.98490471183254</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.797150011062622</v>
+        <v>4.785150011777878</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-24.330068768543</v>
+        <v>-23.72234754639786</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6359955969052015</v>
+        <v>0.6007915291017736</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7464,13 +7460,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>-1.51</v>
+        <v>-1.52</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7502,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="CL24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM24" t="n">
         <v>2</v>
@@ -7511,7 +7507,7 @@
         <v>-1</v>
       </c>
       <c r="CO24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -7524,10 +7520,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.41999816894531</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="D25" t="n">
-        <v>56.41999816894531</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="E25" t="n">
         <v>57.63000106811523</v>
@@ -7539,67 +7535,67 @@
         <v>57</v>
       </c>
       <c r="H25" t="n">
-        <v>3440000</v>
+        <v>4120100</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01449784857737446</v>
+        <v>-0.009606973573110023</v>
       </c>
       <c r="J25" t="n">
-        <v>56.46888860066732</v>
+        <v>56.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0865794120152558</v>
+        <v>0.353983651220271</v>
       </c>
       <c r="M25" t="n">
-        <v>56.53599967956543</v>
+        <v>56.56399993896484</v>
       </c>
       <c r="N25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2051816741148804</v>
+        <v>0.240437069728738</v>
       </c>
       <c r="P25" t="n">
-        <v>55.78884623600887</v>
+        <v>55.7996155665471</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.131322792133799</v>
+        <v>1.613604658832358</v>
       </c>
       <c r="S25" t="n">
-        <v>59.69959976196289</v>
+        <v>59.65659980773925</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.493506834374378</v>
+        <v>-4.956030102835734</v>
       </c>
       <c r="V25" t="n">
-        <v>57.19106648763021</v>
+        <v>57.2275331624349</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.348232103438166</v>
+        <v>-0.9218157246060066</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.21319990158081</v>
+        <v>54.32124990463257</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.070592164584914</v>
+        <v>4.379042938965999</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.3182178978401977</v>
+        <v>0.2912029824785767</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7747,13 +7743,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>15.85</v>
+        <v>15.93</v>
       </c>
       <c r="CA25" t="n">
         <v>0.32</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CC25" t="n">
         <v>6</v>
@@ -7788,13 +7784,13 @@
         <v>2</v>
       </c>
       <c r="CM25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN25" t="n">
         <v>0</v>
       </c>
       <c r="CO25" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -7807,10 +7803,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="D26" t="n">
-        <v>6.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E26" t="n">
         <v>6.539999961853027</v>
@@ -7822,67 +7818,67 @@
         <v>6.190000057220459</v>
       </c>
       <c r="H26" t="n">
-        <v>22955400</v>
+        <v>25266300</v>
       </c>
       <c r="I26" t="n">
-        <v>0.02254426177545898</v>
+        <v>0.04025764870600534</v>
       </c>
       <c r="J26" t="n">
-        <v>6.581111113230388</v>
+        <v>6.593333350287543</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.511735398802234</v>
+        <v>-2.022244364980512</v>
       </c>
       <c r="M26" t="n">
-        <v>6.521000003814697</v>
+        <v>6.532000017166138</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.622298713112955</v>
+        <v>-1.102265444426651</v>
       </c>
       <c r="P26" t="n">
-        <v>5.491923057115995</v>
+        <v>5.496153831481934</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>15.62434212192295</v>
+        <v>17.53673998613602</v>
       </c>
       <c r="S26" t="n">
-        <v>5.280399980545044</v>
+        <v>5.276999988555908</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>20.25603984600272</v>
+        <v>22.41804154172078</v>
       </c>
       <c r="V26" t="n">
-        <v>6.164533325831095</v>
+        <v>6.129333324432373</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.008606961768172</v>
+        <v>5.394823485884116</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.992550003528595</v>
+        <v>6.973850002288819</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-9.189066915099376</v>
+        <v>-7.368239408263733</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6838186061687926</v>
+        <v>0.6611517382862805</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8034,13 +8030,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>-4.21</v>
+        <v>-4.28</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="CC26" t="n">
         <v>2</v>
@@ -8071,13 +8067,13 @@
         <v>10</v>
       </c>
       <c r="CM26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CN26" t="n">
         <v>-1</v>
       </c>
       <c r="CO26" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -8090,106 +8086,106 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30.98999977111816</v>
+        <v>30.46999931335449</v>
       </c>
       <c r="D27" t="n">
-        <v>30.98999977111816</v>
+        <v>30.46999931335449</v>
       </c>
       <c r="E27" t="n">
         <v>31.95000076293945</v>
       </c>
       <c r="F27" t="n">
-        <v>30.86000061035156</v>
+        <v>30.46999931335449</v>
       </c>
       <c r="G27" t="n">
         <v>31.05999946594238</v>
       </c>
       <c r="H27" t="n">
-        <v>2938400</v>
+        <v>3679400</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.008320007324218781</v>
+        <v>-0.02496002197265623</v>
       </c>
       <c r="J27" t="n">
-        <v>32.11222224765353</v>
+        <v>32.05444441901313</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.494689554278268</v>
+        <v>-4.942981026115749</v>
       </c>
       <c r="M27" t="n">
-        <v>32.26700000762939</v>
+        <v>32.21499996185302</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.957604475808989</v>
+        <v>-5.41673335578101</v>
       </c>
       <c r="P27" t="n">
-        <v>31.89269234583928</v>
+        <v>31.87269232823299</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.830405677051221</v>
+        <v>-4.400924152980894</v>
       </c>
       <c r="S27" t="n">
-        <v>31.60220008850098</v>
+        <v>31.54560009002686</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.937207902197832</v>
+        <v>-3.409669727641081</v>
       </c>
       <c r="V27" t="n">
-        <v>33.35353340148926</v>
+        <v>33.30706673940023</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.086306574839717</v>
+        <v>-8.517914376079409</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.6425</v>
+        <v>33.60525000572205</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-7.884373125902755</v>
+        <v>-9.329645492396899</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4230099972431012</v>
+        <v>0.4287120918145144</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AE27" t="n">
         <v>29.4</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
         <v>29.5</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AG27" t="n">
         <v>30.9</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>31</v>
       </c>
-      <c r="AH27" t="n">
-        <v>31.3</v>
-      </c>
       <c r="AI27" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -8313,13 +8309,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>8.960000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB27" t="n">
-        <v>6.19</v>
+        <v>6.08</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8351,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="CL27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM27" t="n">
         <v>2</v>
@@ -8360,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="CO27" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -8373,13 +8369,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20.42000007629395</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="D28" t="n">
-        <v>20.42000007629395</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="E28" t="n">
-        <v>20.48999977111816</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="F28" t="n">
         <v>20.01000022888184</v>
@@ -8388,67 +8384,67 @@
         <v>20.17000007629395</v>
       </c>
       <c r="H28" t="n">
-        <v>3034600</v>
+        <v>4180800</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01239464546625491</v>
+        <v>0.01933561666699291</v>
       </c>
       <c r="J28" t="n">
-        <v>20.05444441901313</v>
+        <v>20.06999990675185</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.822816178015088</v>
+        <v>2.441452722805911</v>
       </c>
       <c r="M28" t="n">
-        <v>20.02800006866455</v>
+        <v>20.04200000762939</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.9572598676126</v>
+        <v>2.584569694221146</v>
       </c>
       <c r="P28" t="n">
-        <v>19.14961536114032</v>
+        <v>19.15499995304988</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>6.633995989974665</v>
+        <v>7.334896979045914</v>
       </c>
       <c r="S28" t="n">
-        <v>20.09140003204346</v>
+        <v>20.05500003814697</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.63552586542705</v>
+        <v>2.518072434978025</v>
       </c>
       <c r="V28" t="n">
-        <v>18.89360008239746</v>
+        <v>18.89880007425944</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>8.078926129692874</v>
+        <v>8.789972829785791</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.30815008640289</v>
+        <v>18.32350008487701</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>11.53502664072807</v>
+        <v>12.20563413488466</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2609151062985172</v>
+        <v>0.2470317338159689</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8608,13 +8604,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>13.99</v>
+        <v>14.08</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8649,13 +8645,13 @@
         <v>4</v>
       </c>
       <c r="CM28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN28" t="n">
         <v>0</v>
       </c>
       <c r="CO28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
@@ -8668,10 +8664,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.67000007629395</v>
+        <v>26.6200008392334</v>
       </c>
       <c r="D29" t="n">
-        <v>26.67000007629395</v>
+        <v>26.6200008392334</v>
       </c>
       <c r="E29" t="n">
         <v>26.98999977111816</v>
@@ -8683,67 +8679,67 @@
         <v>25.79999923706055</v>
       </c>
       <c r="H29" t="n">
-        <v>7199700</v>
+        <v>8531700</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02972974784187921</v>
+        <v>0.02779927534006599</v>
       </c>
       <c r="J29" t="n">
-        <v>25.73666678534614</v>
+        <v>25.73111131456163</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>3.626473073347734</v>
+        <v>3.454532195695457</v>
       </c>
       <c r="M29" t="n">
-        <v>25.71100006103516</v>
+        <v>25.7060001373291</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>3.729921095959801</v>
+        <v>3.55559284611154</v>
       </c>
       <c r="P29" t="n">
-        <v>23.80423083672157</v>
+        <v>23.80230778914231</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>12.03890711373671</v>
+        <v>11.83789855610726</v>
       </c>
       <c r="S29" t="n">
-        <v>22.76180004119873</v>
+        <v>22.74580005645752</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>17.16999546618192</v>
+        <v>17.03259842766444</v>
       </c>
       <c r="V29" t="n">
-        <v>24.53013334910075</v>
+        <v>24.46760000864665</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>8.72342068728152</v>
+        <v>8.796943017811754</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.90085000038147</v>
+        <v>25.83460000038147</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.969593955029067</v>
+        <v>3.040112248071696</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.403061683027433</v>
+        <v>0.3919401280328311</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8895,13 +8891,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>6.16</v>
+        <v>6.15</v>
       </c>
       <c r="CA29" t="n">
         <v>0.4</v>
       </c>
       <c r="CB29" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CC29" t="n">
         <v>8</v>
@@ -8916,7 +8912,7 @@
         <v>10</v>
       </c>
       <c r="CG29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CH29" t="n">
         <v>5</v>
@@ -8951,10 +8947,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.14000034332275</v>
+        <v>10.07999992370605</v>
       </c>
       <c r="D30" t="n">
-        <v>10.14000034332275</v>
+        <v>10.07999992370605</v>
       </c>
       <c r="E30" t="n">
         <v>10.4399995803833</v>
@@ -8966,67 +8962,67 @@
         <v>10.26000022888184</v>
       </c>
       <c r="H30" t="n">
-        <v>12001800</v>
+        <v>14393200</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.01265823842711167</v>
+        <v>-0.01850053803201002</v>
       </c>
       <c r="J30" t="n">
-        <v>10.80444463094076</v>
+        <v>10.79777791765001</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.149731062670529</v>
+        <v>-6.647460240598938</v>
       </c>
       <c r="M30" t="n">
-        <v>10.87000017166138</v>
+        <v>10.86400012969971</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.715729685467429</v>
+        <v>-7.2164966553192</v>
       </c>
       <c r="P30" t="n">
-        <v>10.79307702871469</v>
+        <v>10.7907693202679</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.050885059510334</v>
+        <v>-6.586827829104182</v>
       </c>
       <c r="S30" t="n">
-        <v>11.39160003662109</v>
+        <v>11.39040002822876</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-10.98704035670815</v>
+        <v>-11.50442566788829</v>
       </c>
       <c r="V30" t="n">
-        <v>13.13420003255208</v>
+        <v>13.13380002975464</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-22.79697036597921</v>
+        <v>-23.25145882478945</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.64150002479553</v>
+        <v>13.64120002269745</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-25.6679960056318</v>
+        <v>-26.10620834725648</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3997490480209286</v>
+        <v>0.4011295898092605</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9174,13 +9170,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CC30" t="n">
         <v>9</v>
@@ -9230,10 +9226,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.72999954223633</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="D31" t="n">
-        <v>30.72999954223633</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="E31" t="n">
         <v>30.85000038146973</v>
@@ -9245,67 +9241,67 @@
         <v>30.52000045776367</v>
       </c>
       <c r="H31" t="n">
-        <v>1378700</v>
+        <v>2239000</v>
       </c>
       <c r="I31" t="n">
-        <v>0.006880703844132308</v>
+        <v>0.004259474404219254</v>
       </c>
       <c r="J31" t="n">
-        <v>30.61999977959527</v>
+        <v>30.61111089918349</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3592415526872802</v>
+        <v>0.1270411893082388</v>
       </c>
       <c r="M31" t="n">
-        <v>30.57299976348877</v>
+        <v>30.56499977111816</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5135242860108609</v>
+        <v>0.278095364137477</v>
       </c>
       <c r="P31" t="n">
-        <v>29.24461533473088</v>
+        <v>29.24153841458834</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>5.079171637253188</v>
+        <v>4.81664536240427</v>
       </c>
       <c r="S31" t="n">
-        <v>29.93419990539551</v>
+        <v>29.86259990692139</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.65849643336343</v>
+        <v>2.636741991866518</v>
       </c>
       <c r="V31" t="n">
-        <v>32.41080003102621</v>
+        <v>32.38226669311523</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-5.185927182238269</v>
+        <v>-5.34943119022998</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.16911432266235</v>
+        <v>32.16021431922913</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-4.473591551173677</v>
+        <v>-4.695909939244001</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2189578778601677</v>
+        <v>0.2149995177802381</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9453,13 +9449,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="CA31" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CC31" t="n">
         <v>2</v>
@@ -9490,13 +9486,13 @@
         <v>4</v>
       </c>
       <c r="CM31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN31" t="n">
         <v>0</v>
       </c>
       <c r="CO31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
@@ -9509,10 +9505,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>94.98000335693359</v>
+        <v>95.29000091552734</v>
       </c>
       <c r="D32" t="n">
-        <v>94.98000335693359</v>
+        <v>95.29000091552734</v>
       </c>
       <c r="E32" t="n">
         <v>97.5</v>
@@ -9524,67 +9520,67 @@
         <v>96</v>
       </c>
       <c r="H32" t="n">
-        <v>3944300</v>
+        <v>4888700</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.01288711128703179</v>
+        <v>-0.009665353288061285</v>
       </c>
       <c r="J32" t="n">
-        <v>95.43222300211589</v>
+        <v>95.46666717529297</v>
       </c>
       <c r="K32" t="n">
         <v>-1</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4738647292877898</v>
+        <v>-0.1850554387126931</v>
       </c>
       <c r="M32" t="n">
-        <v>95.13900070190429</v>
+        <v>95.17000045776368</v>
       </c>
       <c r="N32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.1671211004926162</v>
+        <v>0.1260906348497101</v>
       </c>
       <c r="P32" t="n">
-        <v>96.32153848501352</v>
+        <v>96.33346146803636</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.39276754626241</v>
+        <v>-1.083175603375614</v>
       </c>
       <c r="S32" t="n">
-        <v>91.17619995117188</v>
+        <v>91.18239990234375</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4.171925796204256</v>
+        <v>4.504817835001966</v>
       </c>
       <c r="V32" t="n">
-        <v>83.91006657918294</v>
+        <v>83.91213322957357</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>13.19262065809989</v>
+        <v>13.55926401587871</v>
       </c>
       <c r="Y32" t="n">
-        <v>85.93214988708496</v>
+        <v>85.93369987487793</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>10.52906680647177</v>
+        <v>10.88781357520096</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2471244203369331</v>
+        <v>0.2456025607912243</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9734,13 +9730,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>41.48</v>
+        <v>41.61</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="CC32" t="n">
         <v>8</v>
@@ -9775,13 +9771,13 @@
         <v>6</v>
       </c>
       <c r="CM32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33">
@@ -9809,7 +9805,7 @@
         <v>26.84000015258789</v>
       </c>
       <c r="H33" t="n">
-        <v>7661500</v>
+        <v>10329800</v>
       </c>
       <c r="I33" t="n">
         <v>0.0007413068236847842</v>
@@ -9842,34 +9838,34 @@
         <v>3.235293828079863</v>
       </c>
       <c r="S33" t="n">
-        <v>26.17020004272461</v>
+        <v>26.16320003509522</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>3.170781866094591</v>
+        <v>3.198385380161083</v>
       </c>
       <c r="V33" t="n">
-        <v>25.06406664530436</v>
+        <v>25.08659997304281</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>7.723939542980456</v>
+        <v>7.627179566036324</v>
       </c>
       <c r="Y33" t="n">
-        <v>23.95495000839233</v>
+        <v>23.98450000762939</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>12.71156896817095</v>
+        <v>12.57270316834366</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.286947780387446</v>
+        <v>0.2531440297571493</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10077,13 +10073,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>51.84000015258789</v>
+        <v>52.20999908447266</v>
       </c>
       <c r="D34" t="n">
-        <v>51.84000015258789</v>
+        <v>52.20999908447266</v>
       </c>
       <c r="E34" t="n">
-        <v>52.06000137329102</v>
+        <v>52.20999908447266</v>
       </c>
       <c r="F34" t="n">
         <v>51.11999893188477</v>
@@ -10092,67 +10088,67 @@
         <v>51.61999893188477</v>
       </c>
       <c r="H34" t="n">
-        <v>3033500</v>
+        <v>3647000</v>
       </c>
       <c r="I34" t="n">
-        <v>0.00601593985318627</v>
+        <v>0.0131962026253527</v>
       </c>
       <c r="J34" t="n">
-        <v>51.43222215440538</v>
+        <v>51.47333314683702</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7928453819442495</v>
+        <v>1.431160355468262</v>
       </c>
       <c r="M34" t="n">
-        <v>51.40400009155273</v>
+        <v>51.44099998474121</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8481831380021482</v>
+        <v>1.494914756632941</v>
       </c>
       <c r="P34" t="n">
-        <v>47.84307670593262</v>
+        <v>47.85730743408203</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>8.354235809754368</v>
+        <v>9.09514530541853</v>
       </c>
       <c r="S34" t="n">
-        <v>48.72199981689453</v>
+        <v>48.72939979553222</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>6.399573801180841</v>
+        <v>7.142709131540653</v>
       </c>
       <c r="V34" t="n">
-        <v>50.29119997660319</v>
+        <v>50.29366663614909</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>3.079664388014693</v>
+        <v>3.810285820255113</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.91750450134278</v>
+        <v>49.9193544960022</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.851345676131305</v>
+        <v>4.588690321814766</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3083535384035126</v>
+        <v>0.3100321552809702</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10304,13 +10300,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>13.71</v>
+        <v>13.81</v>
       </c>
       <c r="CA34" t="n">
         <v>0.26</v>
       </c>
       <c r="CB34" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CC34" t="n">
         <v>5</v>
@@ -10338,16 +10334,16 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
@@ -10360,10 +10356,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.61000061035156</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="D35" t="n">
-        <v>39.61000061035156</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="E35" t="n">
         <v>40.02999877929688</v>
@@ -10375,67 +10371,67 @@
         <v>39.54000091552734</v>
       </c>
       <c r="H35" t="n">
-        <v>5515300</v>
+        <v>7184900</v>
       </c>
       <c r="I35" t="n">
-        <v>0.001770351370850021</v>
+        <v>0.0005058284598020713</v>
       </c>
       <c r="J35" t="n">
-        <v>39.39111116197374</v>
+        <v>39.38555569118924</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5556823403070893</v>
+        <v>0.4429179150588975</v>
       </c>
       <c r="M35" t="n">
-        <v>39.29000015258789</v>
+        <v>39.28500022888183</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8144577666604863</v>
+        <v>0.7000156365202302</v>
       </c>
       <c r="P35" t="n">
-        <v>37.14461576021635</v>
+        <v>37.14269271263709</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>6.63726033956114</v>
+        <v>6.508167513206385</v>
       </c>
       <c r="S35" t="n">
-        <v>38.10800018310547</v>
+        <v>38.05960021972656</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>3.94143072328414</v>
+        <v>3.942240971797663</v>
       </c>
       <c r="V35" t="n">
-        <v>39.79653343200684</v>
+        <v>39.76526677449544</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.4687162563391906</v>
+        <v>-0.5161926924028113</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.66960006713867</v>
+        <v>39.65745006561279</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.1502396209849425</v>
+        <v>-0.2457260670077099</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2666886724582369</v>
+        <v>0.254259825015129</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10583,7 +10579,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.2</v>
+        <v>32.16</v>
       </c>
       <c r="CA35" t="n">
         <v>0.92</v>
@@ -10620,13 +10616,13 @@
         <v>5</v>
       </c>
       <c r="CM35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -10639,10 +10635,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.32999992370605</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="D36" t="n">
-        <v>21.32999992370605</v>
+        <v>21.35000038146973</v>
       </c>
       <c r="E36" t="n">
         <v>21.44000053405762</v>
@@ -10654,67 +10650,67 @@
         <v>21.22999954223633</v>
       </c>
       <c r="H36" t="n">
-        <v>2610200</v>
+        <v>3454000</v>
       </c>
       <c r="I36" t="n">
-        <v>0.00234958813191799</v>
+        <v>0.003289459237101777</v>
       </c>
       <c r="J36" t="n">
-        <v>20.82555558946397</v>
+        <v>20.82777786254883</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>2.422237102271058</v>
+        <v>2.50733670373893</v>
       </c>
       <c r="M36" t="n">
-        <v>20.71000003814697</v>
+        <v>20.71200008392334</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>2.993722281106073</v>
+        <v>3.080341323683189</v>
       </c>
       <c r="P36" t="n">
-        <v>19.38999990316538</v>
+        <v>19.3907691515409</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>10.0051574534767</v>
+        <v>10.10393767579422</v>
       </c>
       <c r="S36" t="n">
-        <v>18.09679992675781</v>
+        <v>18.16219993591309</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>17.86614213581295</v>
+        <v>17.55184094881167</v>
       </c>
       <c r="V36" t="n">
-        <v>16.70693328857422</v>
+        <v>16.71959995269775</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>27.67154543134211</v>
+        <v>27.69444509361509</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.42349999427795</v>
+        <v>16.44254999637604</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>29.8748739984629</v>
+        <v>29.84604204442315</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3750388324479786</v>
+        <v>0.3732723319769403</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10866,7 +10862,7 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.39</v>
+        <v>18.41</v>
       </c>
       <c r="CA36" t="n">
         <v>0.27</v>
@@ -10922,82 +10918,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25.34000015258789</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="D37" t="n">
-        <v>25.34000015258789</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="E37" t="n">
         <v>26.04000091552734</v>
       </c>
       <c r="F37" t="n">
-        <v>25.32999992370605</v>
+        <v>25.22999954223633</v>
       </c>
       <c r="G37" t="n">
         <v>25.73999977111816</v>
       </c>
       <c r="H37" t="n">
-        <v>5283700</v>
+        <v>7980700</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01972921552633411</v>
+        <v>-0.009671179741227776</v>
       </c>
       <c r="J37" t="n">
-        <v>25.55000008477105</v>
+        <v>25.57888899909126</v>
       </c>
       <c r="K37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.8219175400642301</v>
+        <v>0.08253439928224193</v>
       </c>
       <c r="M37" t="n">
-        <v>25.53700008392334</v>
+        <v>25.56300010681152</v>
       </c>
       <c r="N37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.7714294188355659</v>
+        <v>0.1447415190063918</v>
       </c>
       <c r="P37" t="n">
-        <v>24.35384610983042</v>
+        <v>24.36384611863356</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>4.049274345867746</v>
+        <v>5.073723815267192</v>
       </c>
       <c r="S37" t="n">
-        <v>24.26679992675781</v>
+        <v>24.33999992370606</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>4.422504117020855</v>
+        <v>5.176665824622649</v>
       </c>
       <c r="V37" t="n">
-        <v>22.40386665344238</v>
+        <v>22.4255999883016</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>13.10547658832083</v>
+        <v>14.15525290214786</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.0564999961853</v>
+        <v>22.0902499961853</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>14.88676878457813</v>
+        <v>15.88823298011798</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.3979925472615247</v>
+        <v>0.401055703278666</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11149,13 +11145,13 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>30.53</v>
+        <v>30.84</v>
       </c>
       <c r="CA37" t="n">
         <v>0.16</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CC37" t="n">
         <v>1</v>
@@ -11186,13 +11182,13 @@
         <v>6</v>
       </c>
       <c r="CM37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38">
@@ -11205,82 +11201,82 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.35000038146973</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="D38" t="n">
-        <v>11.35000038146973</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="E38" t="n">
         <v>11.63000011444092</v>
       </c>
       <c r="F38" t="n">
-        <v>11.35000038146973</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="G38" t="n">
         <v>11.60999965667725</v>
       </c>
       <c r="H38" t="n">
-        <v>4459700</v>
+        <v>5667000</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.02239442574470585</v>
+        <v>-0.01378121034827839</v>
       </c>
       <c r="J38" t="n">
-        <v>11.33444457583957</v>
+        <v>11.3455556233724</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1372436516502303</v>
+        <v>0.9205735651904098</v>
       </c>
       <c r="M38" t="n">
-        <v>11.31300010681152</v>
+        <v>11.32300004959106</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3270597923527377</v>
+        <v>1.121608753138346</v>
       </c>
       <c r="P38" t="n">
-        <v>10.7769231062669</v>
+        <v>10.78076923810519</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>5.317633517024658</v>
+        <v>6.207632835647016</v>
       </c>
       <c r="S38" t="n">
-        <v>10.68160001754761</v>
+        <v>10.71459999084473</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>6.25749291139978</v>
+        <v>6.863530314232773</v>
       </c>
       <c r="V38" t="n">
-        <v>9.888733339309692</v>
+        <v>9.897333332697551</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>14.77709016938708</v>
+        <v>15.68772541425965</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.72019408941269</v>
+        <v>9.735868074893951</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.76721963640864</v>
+        <v>17.60635745251568</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.390343064776462</v>
+        <v>0.3946386387681166</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11432,13 +11428,13 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>26.4</v>
+        <v>26.63</v>
       </c>
       <c r="CA38" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="CB38" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="CC38" t="n">
         <v>1</v>
@@ -11473,13 +11469,13 @@
         <v>7</v>
       </c>
       <c r="CM38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN38" t="n">
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
@@ -11501,13 +11497,13 @@
         <v>6.739999771118164</v>
       </c>
       <c r="F39" t="n">
-        <v>6.480000019073486</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="G39" t="n">
         <v>6.630000114440918</v>
       </c>
       <c r="H39" t="n">
-        <v>7994200</v>
+        <v>9128100</v>
       </c>
       <c r="I39" t="n">
         <v>-0.02111619018193023</v>
@@ -11540,34 +11536,34 @@
         <v>-6.260766716004558</v>
       </c>
       <c r="S39" t="n">
-        <v>8.813999996185302</v>
+        <v>8.816200008392334</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-26.36714574623287</v>
+        <v>-26.385520236154</v>
       </c>
       <c r="V39" t="n">
-        <v>10.32646664937337</v>
+        <v>10.31879998524984</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-37.15178684558103</v>
+        <v>-37.10509186731728</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.29229999065399</v>
+        <v>11.25849999427795</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-42.52721078531765</v>
+        <v>-42.35466736761863</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.132985876405218</v>
+        <v>1.118526810547081</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11794,7 +11790,7 @@
         <v>23.34000015258789</v>
       </c>
       <c r="H40" t="n">
-        <v>1892600</v>
+        <v>2317400</v>
       </c>
       <c r="I40" t="n">
         <v>0.007271175466046165</v>
@@ -11827,34 +11823,34 @@
         <v>7.075402567587331</v>
       </c>
       <c r="S40" t="n">
-        <v>21.50600006103516</v>
+        <v>21.52540004730225</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.504320516248555</v>
+        <v>9.405628630869709</v>
       </c>
       <c r="V40" t="n">
-        <v>22.08513334910075</v>
+        <v>22.07133335113526</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6.63281432266944</v>
+        <v>6.699485991177037</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.64620001792908</v>
+        <v>22.62745001792908</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.990953088888778</v>
+        <v>4.077124105458096</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.259519666814724</v>
+        <v>0.2613092839334568</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12058,10 +12054,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.94000053405762</v>
+        <v>25.86000061035156</v>
       </c>
       <c r="D41" t="n">
-        <v>25.94000053405762</v>
+        <v>25.86000061035156</v>
       </c>
       <c r="E41" t="n">
         <v>26.13999938964844</v>
@@ -12073,67 +12069,67 @@
         <v>25.68000030517578</v>
       </c>
       <c r="H41" t="n">
-        <v>1652800</v>
+        <v>2035400</v>
       </c>
       <c r="I41" t="n">
-        <v>0.003481630609661668</v>
+        <v>0.0003868560438786695</v>
       </c>
       <c r="J41" t="n">
-        <v>26.17444462246365</v>
+        <v>26.16555574205186</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.8956984256499793</v>
+        <v>-1.167776196739558</v>
       </c>
       <c r="M41" t="n">
-        <v>26.15800018310547</v>
+        <v>26.15000019073486</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.8333957012074997</v>
+        <v>-1.108985002937213</v>
       </c>
       <c r="P41" t="n">
-        <v>24.7415384879479</v>
+        <v>24.73846156780536</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>4.843926931599299</v>
+        <v>4.533584432775604</v>
       </c>
       <c r="S41" t="n">
-        <v>24.94360004425049</v>
+        <v>24.94200004577637</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>3.994613800892788</v>
+        <v>3.680541106929584</v>
       </c>
       <c r="V41" t="n">
-        <v>26.36566664377848</v>
+        <v>26.36513331095378</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.614471257154082</v>
+        <v>-1.915911801562367</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.42444995880127</v>
+        <v>26.42404995918274</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.833337781860979</v>
+        <v>-2.134605973355575</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3198817959153408</v>
+        <v>0.3197715433742791</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12281,7 +12277,7 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>10.81</v>
+        <v>10.78</v>
       </c>
       <c r="CA41" t="n">
         <v>0.04</v>
@@ -12315,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="CL41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM41" t="n">
         <v>4</v>
@@ -12324,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
@@ -12337,10 +12333,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.18000030517578</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="D42" t="n">
-        <v>27.18000030517578</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="E42" t="n">
         <v>27.56999969482422</v>
@@ -12352,67 +12348,67 @@
         <v>27.35000038146973</v>
       </c>
       <c r="H42" t="n">
-        <v>2552900</v>
+        <v>4062500</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.007666998508660816</v>
+        <v>-0.001460350824024736</v>
       </c>
       <c r="J42" t="n">
-        <v>27.6199999915229</v>
+        <v>27.63888888888889</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.593047380456766</v>
+        <v>-1.045224750461292</v>
       </c>
       <c r="M42" t="n">
-        <v>27.62199993133545</v>
+        <v>27.63899993896484</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.600172425090212</v>
+        <v>-1.045622338482993</v>
       </c>
       <c r="P42" t="n">
-        <v>26.64384607168344</v>
+        <v>26.65038453615629</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.012300446601628</v>
+        <v>2.625162291239278</v>
       </c>
       <c r="S42" t="n">
-        <v>27.15860004425049</v>
+        <v>27.16200004577637</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0.07879736396730855</v>
+        <v>0.6921446704091055</v>
       </c>
       <c r="V42" t="n">
-        <v>28.18826667785645</v>
+        <v>28.18940001169841</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-3.576900929040517</v>
+        <v>-2.97771371465989</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98710000991821</v>
+        <v>27.98795001029968</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-2.883827565043918</v>
+        <v>-2.279372474922921</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1932403916913842</v>
+        <v>0.191795195854051</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12560,10 +12556,10 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.63</v>
+        <v>7.68</v>
       </c>
       <c r="CA42" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="CB42" t="n">
         <v>0.84</v>
@@ -12597,13 +12593,13 @@
         <v>3</v>
       </c>
       <c r="CM42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -12616,10 +12612,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.13000011444092</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="D43" t="n">
-        <v>14.13000011444092</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="E43" t="n">
         <v>14.23999977111816</v>
@@ -12631,67 +12627,67 @@
         <v>14.10999965667725</v>
       </c>
       <c r="H43" t="n">
-        <v>12269400</v>
+        <v>18152700</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.002118625232660154</v>
+        <v>0.002824856093507577</v>
       </c>
       <c r="J43" t="n">
-        <v>14.05444431304932</v>
+        <v>14.06222205691867</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5375936586937788</v>
+        <v>0.9797722706183197</v>
       </c>
       <c r="M43" t="n">
-        <v>14.01399984359741</v>
+        <v>14.02099981307983</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8277456267883623</v>
+        <v>1.276656433718213</v>
       </c>
       <c r="P43" t="n">
-        <v>13.16923064451951</v>
+        <v>13.17192294047429</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>7.29556263274376</v>
+        <v>7.80506288593446</v>
       </c>
       <c r="S43" t="n">
-        <v>13.41699989318848</v>
+        <v>13.41099988937378</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>5.314155376973777</v>
+        <v>5.883229635372103</v>
       </c>
       <c r="V43" t="n">
-        <v>13.55866663614909</v>
+        <v>13.54933329900106</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>4.213788078309885</v>
+        <v>4.802203148342734</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.24907739162445</v>
+        <v>13.25713523387909</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.648936350642446</v>
+        <v>7.112129119544032</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2565314511032892</v>
+        <v>0.2425439017245171</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12843,13 +12839,13 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA43" t="n">
         <v>0.03</v>
       </c>
       <c r="CB43" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CC43" t="n">
         <v>2</v>
@@ -12884,13 +12880,13 @@
         <v>7</v>
       </c>
       <c r="CM43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN43" t="n">
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44">
@@ -12903,13 +12899,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.31999969482422</v>
+        <v>42.61999893188477</v>
       </c>
       <c r="D44" t="n">
-        <v>42.31999969482422</v>
+        <v>42.61999893188477</v>
       </c>
       <c r="E44" t="n">
-        <v>42.66999816894531</v>
+        <v>42.68999862670898</v>
       </c>
       <c r="F44" t="n">
         <v>42.0099983215332</v>
@@ -12918,67 +12914,67 @@
         <v>42.52000045776367</v>
       </c>
       <c r="H44" t="n">
-        <v>15804300</v>
+        <v>24584600</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.008202448772913651</v>
+        <v>-0.001171765624703891</v>
       </c>
       <c r="J44" t="n">
-        <v>42.25333234998915</v>
+        <v>42.28666559855143</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1577800876930952</v>
+        <v>0.7882705543582854</v>
       </c>
       <c r="M44" t="n">
-        <v>42.16899909973144</v>
+        <v>42.1989990234375</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.3580843707854013</v>
+        <v>0.9976537789757502</v>
       </c>
       <c r="P44" t="n">
-        <v>40.10730714064378</v>
+        <v>40.11884557283842</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>5.516931232558732</v>
+        <v>6.234360244751658</v>
       </c>
       <c r="S44" t="n">
-        <v>41.28839965820313</v>
+        <v>41.25419960021973</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>2.498522696837285</v>
+        <v>3.310691626308424</v>
       </c>
       <c r="V44" t="n">
-        <v>42.40253318786621</v>
+        <v>42.35193316141764</v>
       </c>
       <c r="W44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.1946428357860712</v>
+        <v>0.6329481335490279</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.02401777267456</v>
+        <v>42.0338798904419</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.7043160978818042</v>
+        <v>1.39439671753011</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.277951348870025</v>
+        <v>0.2580858052616654</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13146,13 +13142,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.05</v>
+        <v>10.12</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CC44" t="n">
         <v>10</v>
@@ -13175,21 +13171,25 @@
       <c r="CI44" t="n">
         <v>29</v>
       </c>
-      <c r="CJ44" t="inlineStr"/>
+      <c r="CJ44" t="inlineStr">
+        <is>
+          <t>melhor</t>
+        </is>
+      </c>
       <c r="CK44" t="n">
         <v>0</v>
       </c>
       <c r="CL44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.29999923706055</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="D45" t="n">
-        <v>19.29999923706055</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="E45" t="n">
         <v>19.53000068664551</v>
@@ -13217,67 +13217,67 @@
         <v>19.35000038146973</v>
       </c>
       <c r="H45" t="n">
-        <v>1580900</v>
+        <v>2153800</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.006179239895054534</v>
+        <v>-0.001029889685123409</v>
       </c>
       <c r="J45" t="n">
-        <v>19.46888881259494</v>
+        <v>19.47999996609158</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.8674844114633697</v>
+        <v>-0.4106794029802923</v>
       </c>
       <c r="M45" t="n">
-        <v>19.47199993133545</v>
+        <v>19.48199996948242</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.8833232070739163</v>
+        <v>-0.4209031469079114</v>
       </c>
       <c r="P45" t="n">
-        <v>18.69730758666992</v>
+        <v>18.70115375518799</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>3.223414107068061</v>
+        <v>3.736913093655597</v>
       </c>
       <c r="S45" t="n">
-        <v>18.25199996948242</v>
+        <v>18.25399997711182</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>5.741832507836906</v>
+        <v>6.278074081600707</v>
       </c>
       <c r="V45" t="n">
-        <v>18.21979999542236</v>
+        <v>18.22046666463216</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>5.928710753738122</v>
+        <v>6.47367038182237</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.33564549446106</v>
+        <v>18.33614549636841</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>5.259448012838197</v>
+        <v>5.801950700994203</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2013535765422408</v>
+        <v>0.2000975147520356</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13429,13 +13429,13 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.17</v>
+        <v>32.33</v>
       </c>
       <c r="CA45" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CC45" t="n">
         <v>4</v>
@@ -13470,13 +13470,13 @@
         <v>7</v>
       </c>
       <c r="CM45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN45" t="n">
         <v>0</v>
       </c>
       <c r="CO45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -13489,10 +13489,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.48999977111816</v>
+        <v>11.5</v>
       </c>
       <c r="D46" t="n">
-        <v>11.48999977111816</v>
+        <v>11.5</v>
       </c>
       <c r="E46" t="n">
         <v>11.59000015258789</v>
@@ -13504,67 +13504,67 @@
         <v>11.13000011444092</v>
       </c>
       <c r="H46" t="n">
-        <v>12456300</v>
+        <v>16103400</v>
       </c>
       <c r="I46" t="n">
-        <v>0.03049328827086617</v>
+        <v>0.03139016981561671</v>
       </c>
       <c r="J46" t="n">
-        <v>11.37111102210151</v>
+        <v>11.37222215864393</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.045533270984483</v>
+        <v>1.123596070966155</v>
       </c>
       <c r="M46" t="n">
-        <v>11.36799993515015</v>
+        <v>11.36899995803833</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.073186459042726</v>
+        <v>1.152256508445562</v>
       </c>
       <c r="P46" t="n">
-        <v>11.1488461127648</v>
+        <v>11.14923073695256</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>3.059990737182777</v>
+        <v>3.146129731487771</v>
       </c>
       <c r="S46" t="n">
-        <v>12.35079998016357</v>
+        <v>12.32039999008179</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.969590718236288</v>
+        <v>-6.658874636718197</v>
       </c>
       <c r="V46" t="n">
-        <v>14.03386671066284</v>
+        <v>14.01193337758382</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-18.12662890414845</v>
+        <v>-17.92710049280132</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.10050003528595</v>
+        <v>14.08500003814697</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-18.51352971621653</v>
+        <v>-18.35285787111049</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.4140598803721344</v>
+        <v>0.4111899356752801</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>7.76</v>
+        <v>7.77</v>
       </c>
       <c r="CA46" t="n">
         <v>-0.13</v>
@@ -13776,10 +13776,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.11000061035156</v>
+        <v>17.01000022888184</v>
       </c>
       <c r="D47" t="n">
-        <v>17.11000061035156</v>
+        <v>17.01000022888184</v>
       </c>
       <c r="E47" t="n">
         <v>17.29000091552734</v>
@@ -13791,88 +13791,88 @@
         <v>17.25</v>
       </c>
       <c r="H47" t="n">
-        <v>2198100</v>
+        <v>3320100</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.01383283952976111</v>
+        <v>-0.0195965501505706</v>
       </c>
       <c r="J47" t="n">
-        <v>17.38777796427409</v>
+        <v>17.37666681077745</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.597543714287497</v>
+        <v>-2.110108836685519</v>
       </c>
       <c r="M47" t="n">
-        <v>17.49900016784668</v>
+        <v>17.48900012969971</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.222981620457842</v>
+        <v>-2.738863841646597</v>
       </c>
       <c r="P47" t="n">
-        <v>17.56269234877366</v>
+        <v>17.5588461802556</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.57757597429935</v>
+        <v>-3.125751804756518</v>
       </c>
       <c r="S47" t="n">
-        <v>16.81200002670288</v>
+        <v>16.81000001907348</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1.772546890169892</v>
+        <v>1.189769242007263</v>
       </c>
       <c r="V47" t="n">
-        <v>17.57380004882813</v>
+        <v>17.57313337961833</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.639152813779117</v>
+        <v>-3.204511902183726</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.03590006828308</v>
+        <v>18.03540006637573</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-5.133647084016353</v>
+        <v>-5.685484290451639</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4629004503107597</v>
+        <v>0.464616928932498</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AE47" t="n">
         <v>16.7</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AF47" t="n">
         <v>16.8</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
         <v>17.1</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>17.3</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>17.4</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>18.1</v>
       </c>
       <c r="AJ47" t="n">
         <v>2</v>
@@ -13999,13 +13999,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>63.37</v>
+        <v>63</v>
       </c>
       <c r="CA47" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CC47" t="n">
         <v>7</v>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.900000095367432</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="D48" t="n">
-        <v>5.900000095367432</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="E48" t="n">
         <v>5.980000019073486</v>
@@ -14074,67 +14074,67 @@
         <v>5.570000171661377</v>
       </c>
       <c r="H48" t="n">
-        <v>25113400</v>
+        <v>29819000</v>
       </c>
       <c r="I48" t="n">
-        <v>0.05924594497949975</v>
+        <v>0.06642726645531161</v>
       </c>
       <c r="J48" t="n">
-        <v>5.721111191643609</v>
+        <v>5.725555631849501</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>3.126820957178948</v>
+        <v>3.74539065131199</v>
       </c>
       <c r="M48" t="n">
-        <v>5.689000082015991</v>
+        <v>5.693000078201294</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>3.708912116532593</v>
+        <v>4.338661086005198</v>
       </c>
       <c r="P48" t="n">
-        <v>4.853076962324289</v>
+        <v>4.854615422395559</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>21.57235793231143</v>
+        <v>22.35778821567921</v>
       </c>
       <c r="S48" t="n">
-        <v>4.848600049018859</v>
+        <v>4.84940004825592</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>21.68461072720008</v>
+        <v>22.48938009056958</v>
       </c>
       <c r="V48" t="n">
-        <v>6.764799993832906</v>
+        <v>6.765066660245259</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-12.78382064885679</v>
+        <v>-12.19598629934104</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.403497542142868</v>
+        <v>7.403697541952133</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-20.30793470541579</v>
+        <v>-19.76981739783148</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.8645181997295395</v>
+        <v>0.8686127922341264</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14286,7 +14286,7 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>32.78</v>
+        <v>33</v>
       </c>
       <c r="CA48" t="n">
         <v>0.75</v>
@@ -14346,10 +14346,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.23999977111816</v>
+        <v>16.22999954223633</v>
       </c>
       <c r="D49" t="n">
-        <v>16.23999977111816</v>
+        <v>16.22999954223633</v>
       </c>
       <c r="E49" t="n">
         <v>16.47999954223633</v>
@@ -14361,67 +14361,67 @@
         <v>16.3799991607666</v>
       </c>
       <c r="H49" t="n">
-        <v>7862800</v>
+        <v>9726600</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.007335014349416968</v>
+        <v>-0.00794627526070979</v>
       </c>
       <c r="J49" t="n">
-        <v>16.45444446139865</v>
+        <v>16.45333332485623</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.30326302284813</v>
+        <v>-1.357377123591771</v>
       </c>
       <c r="M49" t="n">
-        <v>16.42600002288818</v>
+        <v>16.425</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.132352681790108</v>
+        <v>-1.187217398865587</v>
       </c>
       <c r="P49" t="n">
-        <v>15.22269230622512</v>
+        <v>15.22230768203735</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>6.682835364655128</v>
+        <v>6.619836369409827</v>
       </c>
       <c r="S49" t="n">
-        <v>14.97739999771118</v>
+        <v>14.97179998397827</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>8.430033073830776</v>
+        <v>8.403796200887598</v>
       </c>
       <c r="V49" t="n">
-        <v>15.28760002772013</v>
+        <v>15.26880002339681</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>6.229883969171739</v>
+        <v>6.29518703085144</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.42415001392365</v>
+        <v>15.41600001335144</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.289430901917039</v>
+        <v>5.280225273611188</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3094554558132984</v>
+        <v>0.3038383446670216</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14612,13 +14612,13 @@
         <v>8</v>
       </c>
       <c r="CM49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -14631,10 +14631,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.809999942779541</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="D50" t="n">
-        <v>5.809999942779541</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="E50" t="n">
         <v>5.96999979019165</v>
@@ -14646,67 +14646,67 @@
         <v>5.679999828338623</v>
       </c>
       <c r="H50" t="n">
-        <v>13913100</v>
+        <v>18069100</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02108961060673553</v>
+        <v>0.003514935101122552</v>
       </c>
       <c r="J50" t="n">
-        <v>5.679999987284343</v>
+        <v>5.668888886769612</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>2.288731615954675</v>
+        <v>0.7252065122198453</v>
       </c>
       <c r="M50" t="n">
-        <v>5.679999971389771</v>
+        <v>5.669999980926514</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>2.288731902193338</v>
+        <v>0.7054683836863499</v>
       </c>
       <c r="P50" t="n">
-        <v>5.276153876231267</v>
+        <v>5.272307726053091</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>10.11809130422098</v>
+        <v>8.301721652759882</v>
       </c>
       <c r="S50" t="n">
-        <v>5.001400022506714</v>
+        <v>4.984200029373169</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>16.16747144067782</v>
+        <v>14.56201606068131</v>
       </c>
       <c r="V50" t="n">
-        <v>6.475533339182536</v>
+        <v>6.443400004704793</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-10.27766149200324</v>
+        <v>-11.38218899994277</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.910800013542175</v>
+        <v>6.887700016498566</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-15.92869231645458</v>
+        <v>-17.09859569276493</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.6039217752857634</v>
+        <v>0.5944821551053536</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14854,13 +14854,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.3</v>
+        <v>-4.23</v>
       </c>
       <c r="CA50" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="CB50" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="CC50" t="n">
         <v>7</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="CL50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CM50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CN50" t="n">
         <v>-1</v>
       </c>
       <c r="CO50" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51">
@@ -14914,10 +14914,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30.02000045776367</v>
+        <v>30.05999946594238</v>
       </c>
       <c r="D51" t="n">
-        <v>30.02000045776367</v>
+        <v>30.05999946594238</v>
       </c>
       <c r="E51" t="n">
         <v>30.47999954223633</v>
@@ -14929,73 +14929,73 @@
         <v>30.20000076293945</v>
       </c>
       <c r="H51" t="n">
-        <v>2741300</v>
+        <v>3438500</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.005631006071105116</v>
+        <v>-0.004306096913399449</v>
       </c>
       <c r="J51" t="n">
-        <v>30.13777796427409</v>
+        <v>30.14222229851617</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.3907969149219747</v>
+        <v>-0.2727829148079489</v>
       </c>
       <c r="M51" t="n">
-        <v>30.06700019836426</v>
+        <v>30.07100009918213</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.1563166936858024</v>
+        <v>-0.03658219947279136</v>
       </c>
       <c r="P51" t="n">
-        <v>28.26615392244779</v>
+        <v>28.26769234583928</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>6.20475831316778</v>
+        <v>6.34047908182683</v>
       </c>
       <c r="S51" t="n">
-        <v>28.46220008850098</v>
+        <v>28.46300006866455</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>5.473225416232181</v>
+        <v>5.610790828181169</v>
       </c>
       <c r="V51" t="n">
-        <v>30.28653335571289</v>
+        <v>30.28680001576742</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.8800376550819184</v>
+        <v>-0.748842894287146</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.11065004348755</v>
+        <v>30.11085003852844</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.3010548945072789</v>
+        <v>-0.1688779045460185</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2590938342454435</v>
+        <v>0.2588185609322612</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="AE51" t="n">
         <v>29.6</v>
@@ -15141,7 +15141,7 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.61</v>
+        <v>12.63</v>
       </c>
       <c r="CA51" t="n">
         <v>0.29</v>
@@ -15182,13 +15182,13 @@
         <v>7</v>
       </c>
       <c r="CM51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
@@ -15201,10 +15201,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.849999904632568</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="D52" t="n">
-        <v>7.849999904632568</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="E52" t="n">
         <v>7.980000019073486</v>
@@ -15216,67 +15216,67 @@
         <v>7.949999809265137</v>
       </c>
       <c r="H52" t="n">
-        <v>4056800</v>
+        <v>5445800</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01008826298080956</v>
+        <v>-0.00126100280720598</v>
       </c>
       <c r="J52" t="n">
-        <v>8.488888846503365</v>
+        <v>8.496666643354628</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.526178672182275</v>
+        <v>-6.78697413075164</v>
       </c>
       <c r="M52" t="n">
-        <v>8.567999935150146</v>
+        <v>8.574999952316285</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-8.380019093744256</v>
+        <v>-7.638482561686898</v>
       </c>
       <c r="P52" t="n">
-        <v>8.362692209390493</v>
+        <v>8.365384523685162</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-6.130708770821689</v>
+        <v>-5.324135981199502</v>
       </c>
       <c r="S52" t="n">
-        <v>8.410000019073486</v>
+        <v>8.411400022506713</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.65874094138958</v>
+        <v>-5.842070819339348</v>
       </c>
       <c r="V52" t="n">
-        <v>9.106266641616822</v>
+        <v>9.106733309427897</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-13.79562872937358</v>
+        <v>-13.03138230594022</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.811999971866607</v>
+        <v>8.812349972724915</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-10.91693225494033</v>
+        <v>-10.12612866253474</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4379103214762182</v>
+        <v>0.4372910036277359</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15428,7 +15428,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>-4.64</v>
+        <v>-4.69</v>
       </c>
       <c r="CA52" t="n">
         <v>0.37</v>
@@ -15488,82 +15488,82 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.95999908447266</v>
+        <v>53.83000183105469</v>
       </c>
       <c r="D53" t="n">
-        <v>53.95999908447266</v>
+        <v>53.83000183105469</v>
       </c>
       <c r="E53" t="n">
         <v>55.66999816894531</v>
       </c>
       <c r="F53" t="n">
-        <v>53.88000106811523</v>
+        <v>53.83000183105469</v>
       </c>
       <c r="G53" t="n">
         <v>55.52000045776367</v>
       </c>
       <c r="H53" t="n">
-        <v>9673500</v>
+        <v>12416500</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.04036991777064824</v>
+        <v>-0.042681802075757</v>
       </c>
       <c r="J53" t="n">
-        <v>53.90333302815755</v>
+        <v>53.88888888888889</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1051253292361366</v>
+        <v>-0.1092749526820174</v>
       </c>
       <c r="M53" t="n">
-        <v>53.86699981689453</v>
+        <v>53.85400009155273</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.1726460873897685</v>
+        <v>-0.04456170471506186</v>
       </c>
       <c r="P53" t="n">
-        <v>50.15499980633076</v>
+        <v>50.14999991196852</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>7.586480496131151</v>
+        <v>7.337989881447473</v>
       </c>
       <c r="S53" t="n">
-        <v>48.35159973144531</v>
+        <v>48.43399978637695</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>11.59920123465934</v>
+        <v>11.14093832530319</v>
       </c>
       <c r="V53" t="n">
-        <v>48.03153327941894</v>
+        <v>48.0809999593099</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>12.34286186652718</v>
+        <v>11.95690995738455</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.65909998893738</v>
+        <v>44.72419999122619</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>20.82643648850789</v>
+        <v>20.359898760883</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3636281454653307</v>
+        <v>0.375551106636819</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15715,7 +15715,7 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="CA53" t="n">
         <v>0.47</v>
@@ -15752,13 +15752,13 @@
         <v>9</v>
       </c>
       <c r="CM53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>48.77000045776367</v>
+        <v>48.65000152587891</v>
       </c>
       <c r="D54" t="n">
-        <v>48.77000045776367</v>
+        <v>48.65000152587891</v>
       </c>
       <c r="E54" t="n">
         <v>49.97999954223633</v>
@@ -15786,67 +15786,67 @@
         <v>49.93999862670898</v>
       </c>
       <c r="H54" t="n">
-        <v>34042600</v>
+        <v>52393500</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.03291691131006669</v>
+        <v>-0.03529642610599371</v>
       </c>
       <c r="J54" t="n">
-        <v>48.6022220187717</v>
+        <v>48.58888880411784</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3452073424280321</v>
+        <v>0.1257750964576306</v>
       </c>
       <c r="M54" t="n">
-        <v>48.56199989318848</v>
+        <v>48.55</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.4283196018135345</v>
+        <v>0.2059763663829229</v>
       </c>
       <c r="P54" t="n">
-        <v>45.09884614210863</v>
+        <v>45.09423079857459</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>8.140240005447282</v>
+        <v>7.885200976566408</v>
       </c>
       <c r="S54" t="n">
-        <v>43.27459999084473</v>
+        <v>43.34800003051757</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>12.69890528874112</v>
+        <v>12.23124825050441</v>
       </c>
       <c r="V54" t="n">
-        <v>43.37166661580404</v>
+        <v>43.40359995524089</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>12.446682968813</v>
+        <v>12.08748024598943</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.68410002708435</v>
+        <v>40.73325003623962</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>19.87484158503286</v>
+        <v>19.43559986643809</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3355524246176746</v>
+        <v>0.3459562291845038</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -15998,7 +15998,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
       <c r="CA54" t="n">
         <v>0.52</v>
@@ -16035,13 +16035,13 @@
         <v>9</v>
       </c>
       <c r="CM54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
       </c>
       <c r="CO54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55">
@@ -16069,7 +16069,7 @@
         <v>4.440000057220459</v>
       </c>
       <c r="H55" t="n">
-        <v>11807400</v>
+        <v>15251300</v>
       </c>
       <c r="I55" t="n">
         <v>0.02257345041641456</v>
@@ -16102,34 +16102,34 @@
         <v>2.721093329632859</v>
       </c>
       <c r="S55" t="n">
-        <v>4.821999988555908</v>
+        <v>4.796799983978271</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-6.055574024068105</v>
+        <v>-5.562036671553039</v>
       </c>
       <c r="V55" t="n">
-        <v>5.762733322779337</v>
+        <v>5.749199988047282</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-21.39146554115482</v>
+        <v>-21.2064249073554</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.818868117332459</v>
+        <v>5.811827211380005</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-22.14980442132729</v>
+        <v>-22.0554905531558</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4745836228114181</v>
+        <v>0.3588367666121303</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16341,82 +16341,82 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>63.18999862670898</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="D56" t="n">
-        <v>63.18999862670898</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="E56" t="n">
         <v>64.87999725341797</v>
       </c>
       <c r="F56" t="n">
-        <v>62.68000030517578</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="G56" t="n">
         <v>64.87999725341797</v>
       </c>
       <c r="H56" t="n">
-        <v>7329500</v>
+        <v>9073800</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.03791110942291787</v>
+        <v>-0.04719851491652327</v>
       </c>
       <c r="J56" t="n">
-        <v>63.0411114162869</v>
+        <v>62.97333399454752</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2361747867021635</v>
+        <v>-0.6246011423293746</v>
       </c>
       <c r="M56" t="n">
-        <v>63.17800064086914</v>
+        <v>63.11700096130371</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01899076532675133</v>
+        <v>-0.8507995026225182</v>
       </c>
       <c r="P56" t="n">
-        <v>61.88192338209886</v>
+        <v>61.85846196688139</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.113824479134599</v>
+        <v>1.166436799802118</v>
       </c>
       <c r="S56" t="n">
-        <v>59.96920013427734</v>
+        <v>60.05720024108886</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>5.370754462657388</v>
+        <v>4.200664666082482</v>
       </c>
       <c r="V56" t="n">
-        <v>60.85073333740235</v>
+        <v>60.91460004170736</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>3.844268032623351</v>
+        <v>2.733994458154615</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.33549997329712</v>
+        <v>56.45104999542237</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>12.16728112231343</v>
+        <v>10.85710865631254</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3362970098590917</v>
+        <v>0.398390686674699</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16568,13 +16568,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>21.28</v>
+        <v>21.07</v>
       </c>
       <c r="CA56" t="n">
         <v>0.44</v>
       </c>
       <c r="CB56" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CC56" t="n">
         <v>10</v>
@@ -16602,16 +16602,16 @@
         <v>0</v>
       </c>
       <c r="CL56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
@@ -16624,82 +16624,82 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>49.95999908447266</v>
+        <v>49.86999893188477</v>
       </c>
       <c r="D57" t="n">
-        <v>49.95999908447266</v>
+        <v>49.86999893188477</v>
       </c>
       <c r="E57" t="n">
         <v>50.54000091552734</v>
       </c>
       <c r="F57" t="n">
-        <v>49.88000106811523</v>
+        <v>49.75</v>
       </c>
       <c r="G57" t="n">
         <v>50.08000183105469</v>
       </c>
       <c r="H57" t="n">
-        <v>879500</v>
+        <v>1201000</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.009712619842550119</v>
+        <v>-0.01149656733961357</v>
       </c>
       <c r="J57" t="n">
-        <v>50.80777782864041</v>
+        <v>50.7977778116862</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.668600321444999</v>
+        <v>-1.826416272067695</v>
       </c>
       <c r="M57" t="n">
-        <v>50.82600021362305</v>
+        <v>50.81700019836425</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.703854573467447</v>
+        <v>-1.863552084504926</v>
       </c>
       <c r="P57" t="n">
-        <v>48.96269240746131</v>
+        <v>48.95923086313101</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.036870580383704</v>
+        <v>1.860258122313789</v>
       </c>
       <c r="S57" t="n">
-        <v>51.34820014953613</v>
+        <v>51.34640014648438</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.703504818125583</v>
+        <v>-2.875374340533392</v>
       </c>
       <c r="V57" t="n">
-        <v>50.8809334564209</v>
+        <v>50.88033345540364</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-1.809979317177847</v>
+        <v>-1.98570735469812</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.27145008087158</v>
+        <v>50.27100008010864</v>
       </c>
       <c r="Z57" t="n">
         <v>-1</v>
       </c>
       <c r="AA57" t="n">
-        <v>-0.619538517185986</v>
+        <v>-0.797678875663637</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.2573961882060521</v>
+        <v>0.2578751652895441</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16847,7 +16847,7 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.76</v>
+        <v>8.75</v>
       </c>
       <c r="CA57" t="n">
         <v>-0.4</v>
@@ -16907,10 +16907,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20.13999938964844</v>
+        <v>20.22999954223633</v>
       </c>
       <c r="D58" t="n">
-        <v>20.13999938964844</v>
+        <v>20.22999954223633</v>
       </c>
       <c r="E58" t="n">
         <v>20.23999977111816</v>
@@ -16922,67 +16922,67 @@
         <v>19.43000030517578</v>
       </c>
       <c r="H58" t="n">
-        <v>10002000</v>
+        <v>11991700</v>
       </c>
       <c r="I58" t="n">
-        <v>0.03547550640839692</v>
+        <v>0.04010276342935182</v>
       </c>
       <c r="J58" t="n">
-        <v>19.85888904995388</v>
+        <v>19.8688890669081</v>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1.415539101847221</v>
+        <v>1.817466865470935</v>
       </c>
       <c r="M58" t="n">
-        <v>19.89500007629395</v>
+        <v>19.90400009155274</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>1.231461736189796</v>
+        <v>1.637858968971505</v>
       </c>
       <c r="P58" t="n">
-        <v>19.01538467407227</v>
+        <v>19.01884621840257</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>5.914235945537296</v>
+        <v>6.368174546055541</v>
       </c>
       <c r="S58" t="n">
-        <v>18.80100006103516</v>
+        <v>18.83840003967285</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>7.121958003650771</v>
+        <v>7.387036582898911</v>
       </c>
       <c r="V58" t="n">
-        <v>20.54713340759277</v>
+        <v>20.49933340708415</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.981463836672656</v>
+        <v>-1.313866453602552</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.4238313961029</v>
+        <v>21.40877943038941</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-5.992541589400309</v>
+        <v>-5.50605835323717</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.5095090839551721</v>
+        <v>0.4680220863414589</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17003,7 +17003,7 @@
         <v>20.7</v>
       </c>
       <c r="AI58" t="n">
-        <v>21.3</v>
+        <v>24</v>
       </c>
       <c r="AJ58" t="n">
         <v>1</v>
@@ -17130,13 +17130,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>27.22</v>
+        <v>27.34</v>
       </c>
       <c r="CA58" t="n">
         <v>0.09</v>
       </c>
       <c r="CB58" t="n">
-        <v>4.81</v>
+        <v>4.83</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17171,13 +17171,13 @@
         <v>8</v>
       </c>
       <c r="CM58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59">
@@ -17190,10 +17190,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.93000030517578</v>
+        <v>14.85000038146973</v>
       </c>
       <c r="D59" t="n">
-        <v>14.93000030517578</v>
+        <v>14.85000038146973</v>
       </c>
       <c r="E59" t="n">
         <v>15.03999996185303</v>
@@ -17205,67 +17205,67 @@
         <v>14.69999980926514</v>
       </c>
       <c r="H59" t="n">
-        <v>6690600</v>
+        <v>10704600</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01564629244183258</v>
+        <v>0.01020412069053545</v>
       </c>
       <c r="J59" t="n">
-        <v>14.70666673448351</v>
+        <v>14.69777785407172</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1.518587282382703</v>
+        <v>1.035683957870084</v>
       </c>
       <c r="M59" t="n">
-        <v>14.70200004577637</v>
+        <v>14.69400005340576</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.550811173238394</v>
+        <v>1.061660048298465</v>
       </c>
       <c r="P59" t="n">
-        <v>14.32192314588107</v>
+        <v>14.31884622573853</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>4.245778678609909</v>
+        <v>3.709475940711178</v>
       </c>
       <c r="S59" t="n">
-        <v>14.09979999542236</v>
+        <v>14.09819999694824</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>5.888028979297221</v>
+        <v>5.332598379113803</v>
       </c>
       <c r="V59" t="n">
-        <v>14.87280001958211</v>
+        <v>14.87226668675741</v>
       </c>
       <c r="W59" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>0.3845966160935103</v>
+        <v>-0.1497169581251936</v>
       </c>
       <c r="Y59" t="n">
-        <v>14.92710002422333</v>
+        <v>14.9267000246048</v>
       </c>
       <c r="Z59" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.01942963434120664</v>
+        <v>-0.5138419276105261</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.317852829489534</v>
+        <v>0.316217772656056</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17413,13 +17413,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>26.66</v>
+        <v>26.52</v>
       </c>
       <c r="CA59" t="n">
         <v>0.63</v>
       </c>
       <c r="CB59" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CC59" t="n">
         <v>8</v>
@@ -17454,13 +17454,13 @@
         <v>7</v>
       </c>
       <c r="CM59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60">
@@ -17473,10 +17473,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37.20000076293945</v>
+        <v>37.27999877929688</v>
       </c>
       <c r="D60" t="n">
-        <v>37.20000076293945</v>
+        <v>37.27999877929688</v>
       </c>
       <c r="E60" t="n">
         <v>37.43000030517578</v>
@@ -17488,67 +17488,67 @@
         <v>36.86999893188477</v>
       </c>
       <c r="H60" t="n">
-        <v>3082800</v>
+        <v>3882900</v>
       </c>
       <c r="I60" t="n">
-        <v>0.007038498806074101</v>
+        <v>0.009204119253595655</v>
       </c>
       <c r="J60" t="n">
-        <v>37.30777782864041</v>
+        <v>37.31666649712457</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.2888863180111997</v>
+        <v>-0.09826096827409707</v>
       </c>
       <c r="M60" t="n">
-        <v>37.29000015258789</v>
+        <v>37.29799995422363</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.2413499310275397</v>
+        <v>-0.04826311048542102</v>
       </c>
       <c r="P60" t="n">
-        <v>35.45423096876878</v>
+        <v>35.45730781555176</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>4.924009762638761</v>
+        <v>5.140522718833367</v>
       </c>
       <c r="S60" t="n">
-        <v>35.07580009460449</v>
+        <v>35.06020004272461</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>6.056029121518793</v>
+        <v>6.331392102347399</v>
       </c>
       <c r="V60" t="n">
-        <v>36.71186668395996</v>
+        <v>36.65780001322428</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1.329635682057992</v>
+        <v>1.697316166949831</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.29949996948242</v>
+        <v>38.24219997406006</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-2.870792588464763</v>
+        <v>-2.516071762126262</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3350326970300297</v>
+        <v>0.3356872234786658</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17696,10 +17696,10 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>18.42</v>
+        <v>18.46</v>
       </c>
       <c r="CA60" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="CB60" t="n">
         <v>4.31</v>
@@ -17756,10 +17756,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.05000019073486</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="D61" t="n">
-        <v>11.05000019073486</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="E61" t="n">
         <v>11.42000007629395</v>
@@ -17771,67 +17771,67 @@
         <v>11.38000011444092</v>
       </c>
       <c r="H61" t="n">
-        <v>1448400</v>
+        <v>1802500</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.02814421266887146</v>
+        <v>-0.02902374028386612</v>
       </c>
       <c r="J61" t="n">
-        <v>11.34777768452962</v>
+        <v>11.3466665479872</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.624104049912068</v>
+        <v>-2.702702021225509</v>
       </c>
       <c r="M61" t="n">
-        <v>11.36699991226196</v>
+        <v>11.36599988937378</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.788772094430493</v>
+        <v>-2.868202803921658</v>
       </c>
       <c r="P61" t="n">
-        <v>10.8930768599877</v>
+        <v>10.89269223579994</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.440578568976892</v>
+        <v>1.352353696076616</v>
       </c>
       <c r="S61" t="n">
-        <v>10.6343999671936</v>
+        <v>10.63419996261597</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>3.908074031664767</v>
+        <v>3.815989925557466</v>
       </c>
       <c r="V61" t="n">
-        <v>11.59393335342407</v>
+        <v>11.59386668523153</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-4.691532598197723</v>
+        <v>-4.777239021421773</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.4055999994278</v>
+        <v>11.40554999828339</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-3.117765033937477</v>
+        <v>-3.205018929252653</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.366524325474335</v>
+        <v>0.3671771573484233</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -18039,10 +18039,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36.43000030517578</v>
+        <v>36.43999862670898</v>
       </c>
       <c r="D62" t="n">
-        <v>36.43000030517578</v>
+        <v>36.43999862670898</v>
       </c>
       <c r="E62" t="n">
         <v>36.93999862670898</v>
@@ -18054,67 +18054,67 @@
         <v>35.4900016784668</v>
       </c>
       <c r="H62" t="n">
-        <v>5855100</v>
+        <v>8649500</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02102017919240895</v>
+        <v>0.02130040120607735</v>
       </c>
       <c r="J62" t="n">
-        <v>36.25222227308485</v>
+        <v>36.25333319769965</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4903920944535226</v>
+        <v>0.5148917700653663</v>
       </c>
       <c r="M62" t="n">
-        <v>36.26300010681152</v>
+        <v>36.26399993896484</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4605250472171705</v>
+        <v>0.4853261858602477</v>
       </c>
       <c r="P62" t="n">
-        <v>34.91153849088229</v>
+        <v>34.91192304171049</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>4.349455452070856</v>
+        <v>4.376944756588894</v>
       </c>
       <c r="S62" t="n">
-        <v>36.62519996643066</v>
+        <v>36.56959991455078</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.5329654484720779</v>
+        <v>-0.3543962420825573</v>
       </c>
       <c r="V62" t="n">
-        <v>42.75333335876465</v>
+        <v>42.65819999694824</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-14.79026910142096</v>
+        <v>-14.57680204669701</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.39175001144409</v>
+        <v>43.3557500076294</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-16.04394776526004</v>
+        <v>-15.95117459553446</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4452287490279138</v>
+        <v>0.4045536471477569</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18318,82 +18318,82 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>29.65999984741211</v>
+        <v>29.78000068664551</v>
       </c>
       <c r="D63" t="n">
-        <v>29.65999984741211</v>
+        <v>29.78000068664551</v>
       </c>
       <c r="E63" t="n">
         <v>30.29999923706055</v>
       </c>
       <c r="F63" t="n">
-        <v>29.6299991607666</v>
+        <v>29.59000015258789</v>
       </c>
       <c r="G63" t="n">
         <v>30</v>
       </c>
       <c r="H63" t="n">
-        <v>1823700</v>
+        <v>2425600</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.01363484707592733</v>
+        <v>-0.009644130732353373</v>
       </c>
       <c r="J63" t="n">
-        <v>30.20666673448351</v>
+        <v>30.22000016106499</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-1.809755746559513</v>
+        <v>-1.455987664045005</v>
       </c>
       <c r="M63" t="n">
-        <v>30.17800006866455</v>
+        <v>30.19000015258789</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-1.716482934832751</v>
+        <v>-1.358063808778216</v>
       </c>
       <c r="P63" t="n">
-        <v>29.7769231062669</v>
+        <v>29.7815385231605</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-0.3926640050670165</v>
+        <v>-0.005163724210526937</v>
       </c>
       <c r="S63" t="n">
-        <v>28.65660007476806</v>
+        <v>28.65900009155273</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>3.501461338840162</v>
+        <v>3.911513282081288</v>
       </c>
       <c r="V63" t="n">
-        <v>29.34580000559489</v>
+        <v>29.34660001118978</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>1.070680784839116</v>
+        <v>1.47683437021827</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.5174499797821</v>
+        <v>30.51804998397827</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-2.809704391874345</v>
+        <v>-2.418402544462162</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.185763641454478</v>
+        <v>0.1834328025825461</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18561,13 +18561,13 @@
         <v>18881600000</v>
       </c>
       <c r="BZ63" t="n">
-        <v>7.18</v>
+        <v>7.21</v>
       </c>
       <c r="CA63" t="n">
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CC63" t="n">
         <v>4</v>
@@ -18582,13 +18582,13 @@
         <v>9</v>
       </c>
       <c r="CG63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CH63" t="n">
         <v>1</v>
       </c>
       <c r="CI63" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CJ63" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>1</v>
       </c>
       <c r="CO63" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64">
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.11000061035156</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="D64" t="n">
-        <v>27.11000061035156</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="E64" t="n">
         <v>27.30999946594238</v>
@@ -18636,88 +18636,88 @@
         <v>26.88999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>12915800</v>
+        <v>16287700</v>
       </c>
       <c r="I64" t="n">
-        <v>0.006684006800445008</v>
+        <v>0.005941323639025775</v>
       </c>
       <c r="J64" t="n">
-        <v>26.83555603027344</v>
+        <v>26.83333375718858</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1.022690119662591</v>
+        <v>0.9565207130871201</v>
       </c>
       <c r="M64" t="n">
-        <v>26.76700038909912</v>
+        <v>26.76500034332275</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.28142943275829</v>
+        <v>1.214271642429538</v>
       </c>
       <c r="P64" t="n">
-        <v>25.40576942150409</v>
+        <v>25.40500017312857</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>6.708047926330325</v>
+        <v>6.632552521064675</v>
       </c>
       <c r="S64" t="n">
-        <v>26.94200008392334</v>
+        <v>26.94160007476806</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0.6235636771765551</v>
+        <v>0.5508213224455389</v>
       </c>
       <c r="V64" t="n">
-        <v>29.14044713338216</v>
+        <v>29.14031379699707</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-6.967794672939654</v>
+        <v>-7.036004000136971</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.57152736663818</v>
+        <v>28.57142736434936</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-5.115325959063658</v>
+        <v>-5.184995460219668</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3213109289343652</v>
+        <v>0.3211660364924162</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
       </c>
       <c r="AD64" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AE64" t="n">
         <v>26.6</v>
       </c>
-      <c r="AE64" t="n">
+      <c r="AF64" t="n">
         <v>27</v>
       </c>
-      <c r="AF64" t="n">
+      <c r="AG64" t="n">
         <v>27.1</v>
       </c>
-      <c r="AG64" t="n">
+      <c r="AH64" t="n">
         <v>27.4</v>
       </c>
-      <c r="AH64" t="n">
+      <c r="AI64" t="n">
         <v>28.4</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>29.1</v>
       </c>
       <c r="AJ64" t="n">
         <v>1</v>
@@ -18844,13 +18844,13 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.93</v>
+        <v>10.92</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
       </c>
       <c r="CB64" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CC64" t="n">
         <v>9</v>
@@ -18885,13 +18885,13 @@
         <v>3</v>
       </c>
       <c r="CM64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65">
@@ -18904,82 +18904,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.79999923706055</v>
+        <v>17.75</v>
       </c>
       <c r="D65" t="n">
-        <v>17.79999923706055</v>
+        <v>17.75</v>
       </c>
       <c r="E65" t="n">
         <v>18.09000015258789</v>
       </c>
       <c r="F65" t="n">
-        <v>17.72999954223633</v>
+        <v>17.55999946594238</v>
       </c>
       <c r="G65" t="n">
         <v>17.89999961853027</v>
       </c>
       <c r="H65" t="n">
-        <v>1175100</v>
+        <v>2180900</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.009460216070659944</v>
+        <v>-0.012242588857029</v>
       </c>
       <c r="J65" t="n">
-        <v>17.45777765909831</v>
+        <v>17.4522221883138</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1.960281455319635</v>
+        <v>1.706245820578622</v>
       </c>
       <c r="M65" t="n">
-        <v>17.34999980926514</v>
+        <v>17.34499988555908</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>2.593656672866969</v>
+        <v>2.334967524433985</v>
       </c>
       <c r="P65" t="n">
-        <v>15.83346143135658</v>
+        <v>15.83153838377732</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>12.42013828896213</v>
+        <v>12.11797343831434</v>
       </c>
       <c r="S65" t="n">
-        <v>14.71979997634888</v>
+        <v>14.7229999923706</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>20.92555106496554</v>
+        <v>20.55966860828617</v>
       </c>
       <c r="V65" t="n">
-        <v>15.83959996541341</v>
+        <v>15.82293330510457</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>12.37657059476104</v>
+        <v>12.17894721374919</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.63383881092071</v>
+        <v>15.62923881530762</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>13.85558884377587</v>
+        <v>13.56919047532413</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.3821094968405785</v>
+        <v>0.385242874353028</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19131,10 +19131,10 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>27.38</v>
+        <v>27.31</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="CB65" t="n">
         <v>1.67</v>
@@ -19172,13 +19172,13 @@
         <v>10</v>
       </c>
       <c r="CM65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
@@ -19191,10 +19191,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.20999908447266</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="D66" t="n">
-        <v>17.20999908447266</v>
+        <v>17.1200008392334</v>
       </c>
       <c r="E66" t="n">
         <v>17.3799991607666</v>
@@ -19206,67 +19206,67 @@
         <v>17.10000038146973</v>
       </c>
       <c r="H66" t="n">
-        <v>2393400</v>
+        <v>3422900</v>
       </c>
       <c r="I66" t="n">
-        <v>0.006432672546728746</v>
+        <v>0.001169617386988175</v>
       </c>
       <c r="J66" t="n">
-        <v>17.53888893127441</v>
+        <v>17.52888912624783</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-1.87520342987804</v>
+        <v>-2.332653735610433</v>
       </c>
       <c r="M66" t="n">
-        <v>17.55699996948242</v>
+        <v>17.5480001449585</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-1.976424705888952</v>
+        <v>-2.439020413662703</v>
       </c>
       <c r="P66" t="n">
-        <v>17.28307701991154</v>
+        <v>17.2796155489408</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.4228294264655348</v>
+        <v>-0.9237167878841447</v>
       </c>
       <c r="S66" t="n">
-        <v>18.59080009460449</v>
+        <v>18.5530001449585</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-7.427335042629925</v>
+        <v>-7.723814447953281</v>
       </c>
       <c r="V66" t="n">
-        <v>18.94306669871012</v>
+        <v>18.91640004475911</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-9.148822847968303</v>
+        <v>-9.496517314473998</v>
       </c>
       <c r="Y66" t="n">
-        <v>20.04354096412659</v>
+        <v>20.00944097518921</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-14.13693261447831</v>
+        <v>-14.44038411437172</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3464007402527914</v>
+        <v>0.3301668995294</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19418,13 +19418,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.37</v>
+        <v>15.29</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CC66" t="n">
         <v>10</v>
@@ -19459,13 +19459,13 @@
         <v>1</v>
       </c>
       <c r="CM66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN66" t="n">
         <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -19478,91 +19478,91 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>46.81000137329102</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="D67" t="n">
-        <v>46.81000137329102</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="E67" t="n">
         <v>47.66999816894531</v>
       </c>
       <c r="F67" t="n">
-        <v>46.7599983215332</v>
+        <v>46.63000106811523</v>
       </c>
       <c r="G67" t="n">
         <v>47.41999816894531</v>
       </c>
       <c r="H67" t="n">
-        <v>3509200</v>
+        <v>4740900</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.01576955379192202</v>
+        <v>-0.01808243451469971</v>
       </c>
       <c r="J67" t="n">
-        <v>47.28000005086263</v>
+        <v>47.26777776082357</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.9940750360956097</v>
+        <v>-1.201192492604764</v>
       </c>
       <c r="M67" t="n">
-        <v>47.22700004577636</v>
+        <v>47.21599998474121</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.882966676014057</v>
+        <v>-1.092848233582921</v>
       </c>
       <c r="P67" t="n">
-        <v>45.147307909452</v>
+        <v>45.14307711674617</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>3.682818623811941</v>
+        <v>3.448864688968512</v>
       </c>
       <c r="S67" t="n">
-        <v>43.64540008544922</v>
+        <v>43.65060012817383</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>7.250709769290975</v>
+        <v>6.985930607623929</v>
       </c>
       <c r="V67" t="n">
-        <v>46.17180010477702</v>
+        <v>46.10406677246094</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>1.382231723835186</v>
+        <v>1.29258443386274</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.22870004653931</v>
+        <v>47.19560005187989</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-0.8865344014036096</v>
+        <v>-1.050096382704413</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2833100460826787</v>
+        <v>0.278033418846802</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>39.2</v>
+        <v>41.9</v>
       </c>
       <c r="AE67" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="AF67" t="n">
         <v>42.7</v>
@@ -19701,7 +19701,7 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="CA67" t="n">
         <v>1.16</v>
@@ -19761,10 +19761,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.16999816894531</v>
+        <v>41.04999923706055</v>
       </c>
       <c r="D68" t="n">
-        <v>41.16999816894531</v>
+        <v>41.04999923706055</v>
       </c>
       <c r="E68" t="n">
         <v>41.41999816894531</v>
@@ -19776,67 +19776,67 @@
         <v>40.79999923706055</v>
       </c>
       <c r="H68" t="n">
-        <v>840700</v>
+        <v>1186600</v>
       </c>
       <c r="I68" t="n">
-        <v>0.009068601441263757</v>
+        <v>0.00612745109497248</v>
       </c>
       <c r="J68" t="n">
-        <v>41.14222166273329</v>
+        <v>41.12888844807943</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.06751338427885874</v>
+        <v>-0.1918097327586941</v>
       </c>
       <c r="M68" t="n">
-        <v>41.1169994354248</v>
+        <v>41.10499954223633</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.1288973763850312</v>
+        <v>-0.1338044174389716</v>
       </c>
       <c r="P68" t="n">
-        <v>39.28692260155311</v>
+        <v>39.28230725801908</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>4.793135839348643</v>
+        <v>4.499969839935025</v>
       </c>
       <c r="S68" t="n">
-        <v>39.7987996673584</v>
+        <v>39.7963996887207</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>3.445326273775858</v>
+        <v>3.150032561099098</v>
       </c>
       <c r="V68" t="n">
-        <v>41.04426661173503</v>
+        <v>41.0434666188558</v>
       </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
       <c r="X68" t="n">
-        <v>0.3063315965653989</v>
+        <v>0.01591634124236041</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.18530004501343</v>
+        <v>41.184700050354</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-0.03715373216023869</v>
+        <v>-0.3270651798574853</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2087678455481168</v>
+        <v>0.2079693207956105</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -19986,7 +19986,7 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>9.050000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="CA68" t="n">
         <v>0.24</v>
@@ -20007,7 +20007,7 @@
         <v>8</v>
       </c>
       <c r="CG68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CH68" t="n">
         <v>5</v>
@@ -20020,16 +20020,16 @@
         <v>0</v>
       </c>
       <c r="CL68" t="n">
+        <v>4</v>
+      </c>
+      <c r="CM68" t="n">
         <v>5</v>
       </c>
-      <c r="CM68" t="n">
-        <v>6</v>
-      </c>
       <c r="CN68" t="n">
         <v>0</v>
       </c>
       <c r="CO68" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69">
@@ -20042,10 +20042,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.56999969482422</v>
+        <v>19.57999992370605</v>
       </c>
       <c r="D69" t="n">
-        <v>19.56999969482422</v>
+        <v>19.57999992370605</v>
       </c>
       <c r="E69" t="n">
         <v>19.70999908447266</v>
@@ -20057,67 +20057,67 @@
         <v>19.63999938964844</v>
       </c>
       <c r="H69" t="n">
-        <v>2735700</v>
+        <v>3334700</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.003564139358431584</v>
+        <v>-0.003054962719296506</v>
       </c>
       <c r="J69" t="n">
-        <v>19.35333336724175</v>
+        <v>19.35444450378418</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.119529765085349</v>
+        <v>1.165393405518688</v>
       </c>
       <c r="M69" t="n">
-        <v>19.29799995422363</v>
+        <v>19.29899997711182</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1.409471143360914</v>
+        <v>1.456033716397216</v>
       </c>
       <c r="P69" t="n">
-        <v>18.7584615120521</v>
+        <v>18.75884613623986</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>4.326251287989249</v>
+        <v>4.377421625522173</v>
       </c>
       <c r="S69" t="n">
-        <v>19.90840003967285</v>
+        <v>19.8346000289917</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-1.699786744159648</v>
+        <v>-1.283616029128398</v>
       </c>
       <c r="V69" t="n">
-        <v>23.25873334248861</v>
+        <v>23.20973333994548</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-15.85956377480747</v>
+        <v>-15.6388415285772</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.31005001068115</v>
+        <v>23.2795500087738</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-16.04479747638106</v>
+        <v>-15.89184534784147</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2146766970258696</v>
+        <v>0.2026139872390125</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
         <v>18.9</v>
       </c>
       <c r="AE69" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AF69" t="n">
         <v>19.5</v>
@@ -20265,7 +20265,7 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="CA69" t="n">
         <v>-0.06</v>
@@ -20325,10 +20325,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>34.45999908447266</v>
+        <v>34.2400016784668</v>
       </c>
       <c r="D70" t="n">
-        <v>34.45999908447266</v>
+        <v>34.2400016784668</v>
       </c>
       <c r="E70" t="n">
         <v>34.77999877929688</v>
@@ -20340,67 +20340,67 @@
         <v>33.86999893188477</v>
       </c>
       <c r="H70" t="n">
-        <v>5383600</v>
+        <v>6386500</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0186224421909329</v>
+        <v>0.0121194154661779</v>
       </c>
       <c r="J70" t="n">
-        <v>33.93111080593533</v>
+        <v>33.90666664971246</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>1.558711948931564</v>
+        <v>0.9830958383435426</v>
       </c>
       <c r="M70" t="n">
-        <v>34.01199989318847</v>
+        <v>33.99000015258789</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>1.317179797398219</v>
+        <v>0.7355149301459282</v>
       </c>
       <c r="P70" t="n">
-        <v>32.84000000586877</v>
+        <v>32.83153856717623</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>4.933005719593128</v>
+        <v>4.289969866653448</v>
       </c>
       <c r="S70" t="n">
-        <v>31.39739986419678</v>
+        <v>31.39299991607666</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>9.754308425291722</v>
+        <v>9.06890634855243</v>
       </c>
       <c r="V70" t="n">
-        <v>32.7728666305542</v>
+        <v>32.77139998118083</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>5.147955084116878</v>
+        <v>4.481351721712598</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.54539996147156</v>
+        <v>35.54429997444153</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-3.053562143555547</v>
+        <v>-3.669500586346054</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3912226753837268</v>
+        <v>0.3894212958013752</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20548,13 +20548,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>22.38</v>
+        <v>22.23</v>
       </c>
       <c r="CA70" t="n">
         <v>0.17</v>
       </c>
       <c r="CB70" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="CC70" t="n">
         <v>7</v>
@@ -20586,16 +20586,16 @@
         <v>0</v>
       </c>
       <c r="CL70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71">
@@ -20608,10 +20608,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.75</v>
+        <v>38.93000030517578</v>
       </c>
       <c r="D71" t="n">
-        <v>38.75</v>
+        <v>38.93000030517578</v>
       </c>
       <c r="E71" t="n">
         <v>38.95999908447266</v>
@@ -20623,67 +20623,67 @@
         <v>38.43000030517578</v>
       </c>
       <c r="H71" t="n">
-        <v>4595300</v>
+        <v>6354600</v>
       </c>
       <c r="I71" t="n">
-        <v>0.00832681999175322</v>
+        <v>0.01301066864505485</v>
       </c>
       <c r="J71" t="n">
-        <v>38.04555553860135</v>
+        <v>38.06555557250977</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1.851581482846047</v>
+        <v>2.270936860541453</v>
       </c>
       <c r="M71" t="n">
-        <v>37.91399993896484</v>
+        <v>37.93199996948242</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2.204990405604729</v>
+        <v>2.631024824676493</v>
       </c>
       <c r="P71" t="n">
-        <v>35.13730768057016</v>
+        <v>35.14423076923077</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>10.28164238498998</v>
+        <v>10.77209389160825</v>
       </c>
       <c r="S71" t="n">
-        <v>33.50479995727539</v>
+        <v>33.56439994812012</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>15.65507046576365</v>
+        <v>15.98598623943575</v>
       </c>
       <c r="V71" t="n">
-        <v>29.49940003712972</v>
+        <v>29.52766670227051</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>31.35860373847236</v>
+        <v>31.84245371539054</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.73150000572205</v>
+        <v>27.77670001029968</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>39.732794807365</v>
+        <v>40.15343900009873</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3426020867940484</v>
+        <v>0.3379504817640701</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20835,13 +20835,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>14.41</v>
+        <v>14.47</v>
       </c>
       <c r="CA71" t="n">
         <v>0.32</v>
       </c>
       <c r="CB71" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CC71" t="n">
         <v>4</v>
@@ -20869,16 +20869,16 @@
         <v>0</v>
       </c>
       <c r="CL71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CM71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN71" t="n">
         <v>0</v>
       </c>
       <c r="CO71" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
@@ -20891,82 +20891,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6.989999771118164</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="D72" t="n">
-        <v>6.989999771118164</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E72" t="n">
         <v>7.269999980926514</v>
       </c>
       <c r="F72" t="n">
-        <v>6.980000019073486</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="G72" t="n">
         <v>7.260000228881836</v>
       </c>
       <c r="H72" t="n">
-        <v>12480000</v>
+        <v>15032100</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.03719014452500324</v>
+        <v>-0.03168044239978074</v>
       </c>
       <c r="J72" t="n">
-        <v>7.437777837117513</v>
+        <v>7.442222330305311</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-6.020320528595994</v>
+        <v>-5.538965408468932</v>
       </c>
       <c r="M72" t="n">
-        <v>7.473000049591064</v>
+        <v>7.477000093460083</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-6.463271447446746</v>
+        <v>-5.978331925429706</v>
       </c>
       <c r="P72" t="n">
-        <v>7.028076923810518</v>
+        <v>7.02961540222168</v>
       </c>
       <c r="Q72" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>-0.5417862255228328</v>
+        <v>0.005474091606040141</v>
       </c>
       <c r="S72" t="n">
-        <v>7.537999963760376</v>
+        <v>7.513399963378906</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-7.269835437473768</v>
+        <v>-6.433834960559763</v>
       </c>
       <c r="V72" t="n">
-        <v>7.905666669209798</v>
+        <v>7.91200000445048</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-11.58241216591995</v>
+        <v>-11.14762126069271</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.463500001430512</v>
+        <v>7.472200002670288</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-6.344211565908658</v>
+        <v>-5.917933041191517</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.5295308216326897</v>
+        <v>0.5281279151000869</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21118,7 +21118,7 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>-3.36</v>
+        <v>-3.38</v>
       </c>
       <c r="CA72" t="n">
         <v>-0.06</v>
@@ -21159,13 +21159,13 @@
         <v>1</v>
       </c>
       <c r="CM72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN72" t="n">
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73">
@@ -21178,82 +21178,82 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72.58999633789062</v>
+        <v>73</v>
       </c>
       <c r="D73" t="n">
-        <v>72.58999633789062</v>
+        <v>73</v>
       </c>
       <c r="E73" t="n">
         <v>75.45999908447266</v>
       </c>
       <c r="F73" t="n">
-        <v>72.5</v>
+        <v>72.41000366210938</v>
       </c>
       <c r="G73" t="n">
         <v>75.05999755859375</v>
       </c>
       <c r="H73" t="n">
-        <v>44390900</v>
+        <v>51906100</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.02694372891881147</v>
+        <v>-0.02144770116417816</v>
       </c>
       <c r="J73" t="n">
-        <v>77.14333258734808</v>
+        <v>77.18888854980469</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-5.902436538247546</v>
+        <v>-5.426802521067375</v>
       </c>
       <c r="M73" t="n">
-        <v>77.50899963378906</v>
+        <v>77.55</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-6.346364059837585</v>
+        <v>-5.867182462927141</v>
       </c>
       <c r="P73" t="n">
-        <v>76.08192297128531</v>
+        <v>76.09769234290489</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-4.589692921816132</v>
+        <v>-4.070678423395991</v>
       </c>
       <c r="S73" t="n">
-        <v>75.37480010986329</v>
+        <v>75.38300018310547</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-3.694608500339163</v>
+        <v>-3.161190423991024</v>
       </c>
       <c r="V73" t="n">
-        <v>80.01066680908202</v>
+        <v>80.01340016682943</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-9.274601458950819</v>
+        <v>-8.765282005522023</v>
       </c>
       <c r="Y73" t="n">
-        <v>78.9325500869751</v>
+        <v>78.93460010528564</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-8.03540965304639</v>
+        <v>-7.518376095362324</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2634648794291914</v>
+        <v>0.2591713631793146</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21401,7 +21401,7 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>20.68</v>
+        <v>20.8</v>
       </c>
       <c r="CA73" t="n">
         <v>0.22</v>
@@ -21457,10 +21457,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.339999914169312</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="D74" t="n">
-        <v>3.339999914169312</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="E74" t="n">
         <v>3.450000047683716</v>
@@ -21472,67 +21472,67 @@
         <v>3.309999942779541</v>
       </c>
       <c r="H74" t="n">
-        <v>11647900</v>
+        <v>13485900</v>
       </c>
       <c r="I74" t="n">
-        <v>0.009063435621868399</v>
+        <v>0.006042290414578932</v>
       </c>
       <c r="J74" t="n">
-        <v>3.37555554178026</v>
+        <v>3.374444431728787</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.05332669455045</v>
+        <v>-1.317091121869876</v>
       </c>
       <c r="M74" t="n">
-        <v>3.383999991416931</v>
+        <v>3.382999992370606</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>-1.30023869264834</v>
+        <v>-1.566658846706398</v>
       </c>
       <c r="P74" t="n">
-        <v>3.052307679102971</v>
+        <v>3.051923064085154</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>9.425400887203121</v>
+        <v>9.111529150039619</v>
       </c>
       <c r="S74" t="n">
-        <v>3.102799987792969</v>
+        <v>3.102999987602234</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>7.644705662934584</v>
+        <v>7.315499097994822</v>
       </c>
       <c r="V74" t="n">
-        <v>3.459994792938232</v>
+        <v>3.449594793319702</v>
       </c>
       <c r="W74" t="n">
         <v>-1</v>
       </c>
       <c r="X74" t="n">
-        <v>-3.468065299226103</v>
+        <v>-3.466925154376057</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.519846090078354</v>
+        <v>3.516246091127396</v>
       </c>
       <c r="Z74" t="n">
         <v>-1</v>
       </c>
       <c r="AA74" t="n">
-        <v>-5.1094897704757</v>
+        <v>-5.296733009993217</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.7851297279795113</v>
+        <v>0.7614452342719977</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21680,13 +21680,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>13.36</v>
+        <v>13.32</v>
       </c>
       <c r="CA74" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CC74" t="n">
         <v>6</v>
@@ -21717,13 +21717,13 @@
         <v>8</v>
       </c>
       <c r="CM74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN74" t="n">
         <v>-1</v>
       </c>
       <c r="CO74" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
@@ -21736,10 +21736,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.88999938964844</v>
+        <v>39.06000137329102</v>
       </c>
       <c r="D75" t="n">
-        <v>38.88999938964844</v>
+        <v>39.06000137329102</v>
       </c>
       <c r="E75" t="n">
         <v>39.09999847412109</v>
@@ -21751,73 +21751,73 @@
         <v>38.59999847412109</v>
       </c>
       <c r="H75" t="n">
-        <v>8066600</v>
+        <v>11416300</v>
       </c>
       <c r="I75" t="n">
-        <v>0.003354000870609219</v>
+        <v>0.007740017150391409</v>
       </c>
       <c r="J75" t="n">
-        <v>37.82777786254883</v>
+        <v>37.84666697184245</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>2.808046327646583</v>
+        <v>3.20592141535549</v>
       </c>
       <c r="M75" t="n">
-        <v>37.67999992370606</v>
+        <v>37.69700012207031</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>3.211251243079542</v>
+        <v>3.615675642112198</v>
       </c>
       <c r="P75" t="n">
-        <v>35.39461546677809</v>
+        <v>35.4011540046105</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>9.875467996399523</v>
+        <v>10.33539010678578</v>
       </c>
       <c r="S75" t="n">
-        <v>34.85119983673096</v>
+        <v>34.90619983673096</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>11.58869586079743</v>
+        <v>11.89989616741125</v>
       </c>
       <c r="V75" t="n">
-        <v>32.41579986572265</v>
+        <v>32.42833320617676</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>19.97235777227197</v>
+        <v>20.45022827707684</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.87664115905762</v>
+        <v>30.92009989738465</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>25.9528171775903</v>
+        <v>26.3255988917257</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2934600275010292</v>
+        <v>0.2823229302523195</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>32.7</v>
+        <v>31</v>
       </c>
       <c r="AE75" t="n">
         <v>33</v>
@@ -21963,7 +21963,7 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.49</v>
+        <v>15.56</v>
       </c>
       <c r="CA75" t="n">
         <v>0.39</v>
@@ -22019,10 +22019,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.86000061035156</v>
+        <v>22.71999931335449</v>
       </c>
       <c r="D76" t="n">
-        <v>22.86000061035156</v>
+        <v>22.71999931335449</v>
       </c>
       <c r="E76" t="n">
         <v>23.06999969482422</v>
@@ -22034,88 +22034,88 @@
         <v>22.38999938964844</v>
       </c>
       <c r="H76" t="n">
-        <v>2022700</v>
+        <v>2362000</v>
       </c>
       <c r="I76" t="n">
-        <v>0.01871658049457281</v>
+        <v>0.01247766366457581</v>
       </c>
       <c r="J76" t="n">
-        <v>22.70666652255588</v>
+        <v>22.69111082288954</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0.6752822464863575</v>
+        <v>0.1273119270820782</v>
       </c>
       <c r="M76" t="n">
-        <v>22.81199989318848</v>
+        <v>22.79799976348877</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.2104187155349639</v>
+        <v>-0.3421372530198656</v>
       </c>
       <c r="P76" t="n">
-        <v>22.02384625948392</v>
+        <v>22.01846159421481</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>3.796586395564636</v>
+        <v>3.186134127209008</v>
       </c>
       <c r="S76" t="n">
-        <v>22.17320011138916</v>
+        <v>22.17040008544922</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>3.097435171793854</v>
+        <v>2.478977491551822</v>
       </c>
       <c r="V76" t="n">
-        <v>24.32280002593994</v>
+        <v>24.32186668395996</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-6.014107808427987</v>
+        <v>-6.586120183208983</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.06965002059937</v>
+        <v>26.06895001411438</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-12.31182393208825</v>
+        <v>-12.84651165062912</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3063371899319838</v>
+        <v>0.3036457729654149</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
       </c>
       <c r="AD76" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE76" t="n">
         <v>22.1</v>
       </c>
-      <c r="AE76" t="n">
+      <c r="AF76" t="n">
         <v>22.3</v>
       </c>
-      <c r="AF76" t="n">
+      <c r="AG76" t="n">
         <v>22.8</v>
       </c>
-      <c r="AG76" t="n">
+      <c r="AH76" t="n">
         <v>22.9</v>
       </c>
-      <c r="AH76" t="n">
+      <c r="AI76" t="n">
         <v>23.2</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>23.6</v>
       </c>
       <c r="AJ76" t="n">
         <v>3</v>
@@ -22242,13 +22242,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.220000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CC76" t="n">
         <v>8</v>
@@ -22280,16 +22280,16 @@
         <v>1</v>
       </c>
       <c r="CL76" t="n">
+        <v>4</v>
+      </c>
+      <c r="CM76" t="n">
         <v>5</v>
       </c>
-      <c r="CM76" t="n">
-        <v>7</v>
-      </c>
       <c r="CN76" t="n">
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30.64999961853027</v>
+        <v>30.70999908447266</v>
       </c>
       <c r="D77" t="n">
-        <v>30.64999961853027</v>
+        <v>30.70999908447266</v>
       </c>
       <c r="E77" t="n">
         <v>30.80999946594238</v>
@@ -22317,67 +22317,67 @@
         <v>30.61000061035156</v>
       </c>
       <c r="H77" t="n">
-        <v>3167700</v>
+        <v>4259400</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.003899929718822026</v>
+        <v>-0.001949995853051001</v>
       </c>
       <c r="J77" t="n">
-        <v>30.36222224765354</v>
+        <v>30.36888885498047</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>0.9478139265612411</v>
+        <v>1.1232226214172</v>
       </c>
       <c r="M77" t="n">
-        <v>30.34600009918213</v>
+        <v>30.35200004577637</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1.001777889522709</v>
+        <v>1.179490768833554</v>
       </c>
       <c r="P77" t="n">
-        <v>29.9453846858098</v>
+        <v>29.94769235757681</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>2.353000103733426</v>
+        <v>2.54546065784926</v>
       </c>
       <c r="S77" t="n">
-        <v>31.91100021362305</v>
+        <v>31.83700016021729</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-3.951617268813918</v>
+        <v>-3.539909759314894</v>
       </c>
       <c r="V77" t="n">
-        <v>36.08866678873698</v>
+        <v>36.02793343861898</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-15.07029118599659</v>
+        <v>-14.76058670755158</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.69845012664795</v>
+        <v>35.67755011558533</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-14.14193190518694</v>
+        <v>-13.92346451765659</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1722756571767558</v>
+        <v>0.1623018029318227</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22525,13 +22525,13 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.56</v>
+        <v>15.59</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
       </c>
       <c r="CB77" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CC77" t="n">
         <v>5</v>
@@ -22585,10 +22585,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.45999908447266</v>
+        <v>51.27999877929688</v>
       </c>
       <c r="D78" t="n">
-        <v>51.45999908447266</v>
+        <v>51.27999877929688</v>
       </c>
       <c r="E78" t="n">
         <v>51.79000091552734</v>
@@ -22600,76 +22600,76 @@
         <v>50.95000076293945</v>
       </c>
       <c r="H78" t="n">
-        <v>4883300</v>
+        <v>6858200</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0113993318431922</v>
+        <v>0.007861590070451285</v>
       </c>
       <c r="J78" t="n">
-        <v>51.65333387586806</v>
+        <v>51.63333384195963</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.3742929582435434</v>
+        <v>-0.6843158021603898</v>
       </c>
       <c r="M78" t="n">
-        <v>51.57200050354004</v>
+        <v>51.55400047302246</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.2171748583995588</v>
+        <v>-0.5314848337889295</v>
       </c>
       <c r="P78" t="n">
-        <v>49.90423114483173</v>
+        <v>49.89730805617113</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>3.117507080964304</v>
+        <v>2.771072783263588</v>
       </c>
       <c r="S78" t="n">
-        <v>48.00800025939942</v>
+        <v>48.03960029602051</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>7.190465769082681</v>
+        <v>6.745265288031117</v>
       </c>
       <c r="V78" t="n">
-        <v>47.25400011698405</v>
+        <v>47.21200012207031</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>8.900831584788696</v>
+        <v>8.616450577625248</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.51085006713867</v>
+        <v>47.533300075531</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>8.312099261017966</v>
+        <v>7.882260852523014</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.1903497167132751</v>
+        <v>0.1786062420733219</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="AE78" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="AF78" t="n">
         <v>50</v>
@@ -22808,13 +22808,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>34.31</v>
+        <v>34.19</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12.17</v>
+        <v>12.12</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22846,7 +22846,7 @@
         <v>0</v>
       </c>
       <c r="CL78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM78" t="n">
         <v>5</v>
@@ -22855,7 +22855,7 @@
         <v>1</v>
       </c>
       <c r="CO78" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79">
@@ -22868,10 +22868,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10.11999988555908</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="D79" t="n">
-        <v>10.11999988555908</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="E79" t="n">
         <v>10.48999977111816</v>
@@ -22883,67 +22883,67 @@
         <v>10.14000034332275</v>
       </c>
       <c r="H79" t="n">
-        <v>4236600</v>
+        <v>4918200</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.002955638827455975</v>
+        <v>-0.004926033393071849</v>
       </c>
       <c r="J79" t="n">
-        <v>9.941111034817165</v>
+        <v>9.938888867696127</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1.799485491263369</v>
+        <v>1.621021382956121</v>
       </c>
       <c r="M79" t="n">
-        <v>9.877999973297118</v>
+        <v>9.876000022888183</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.449887759831487</v>
+        <v>2.268128372442385</v>
       </c>
       <c r="P79" t="n">
-        <v>8.755384555229774</v>
+        <v>8.754615343534029</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>15.58601249004185</v>
+        <v>15.36772302542533</v>
       </c>
       <c r="S79" t="n">
-        <v>8.540999994277954</v>
+        <v>8.524200010299683</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>18.48729530896827</v>
+        <v>18.48619658461818</v>
       </c>
       <c r="V79" t="n">
-        <v>9.944666633605957</v>
+        <v>9.903399969736736</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>1.763088280512315</v>
+        <v>1.985180971522623</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.71169998168945</v>
+        <v>10.68489998340607</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-5.523867333306767</v>
+        <v>-5.474076527105591</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5510360418853029</v>
+        <v>0.5471959536937019</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23091,13 +23091,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>23.53</v>
+        <v>23.49</v>
       </c>
       <c r="CA79" t="n">
         <v>1.55</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="CC79" t="n">
         <v>5</v>
@@ -23132,13 +23132,13 @@
         <v>10</v>
       </c>
       <c r="CM79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.67000007629395</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="D2" t="n">
-        <v>15.67000007629395</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="E2" t="n">
         <v>15.72999954223633</v>
@@ -912,67 +912,67 @@
         <v>15.63000011444092</v>
       </c>
       <c r="H2" t="n">
-        <v>9892900</v>
+        <v>13693700</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002559178602696832</v>
+        <v>-0.001279619809163801</v>
       </c>
       <c r="J2" t="n">
-        <v>15.71111096276177</v>
+        <v>15.70444424947103</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2616675966789827</v>
+        <v>-0.6013876791403446</v>
       </c>
       <c r="M2" t="n">
-        <v>15.71599988937378</v>
+        <v>15.70999984741211</v>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2926941550243776</v>
+        <v>-0.6365384577093863</v>
       </c>
       <c r="P2" t="n">
-        <v>15.29499992957482</v>
+        <v>15.29269222112802</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.451782598534149</v>
+        <v>2.074895845421112</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51279996871948</v>
+        <v>15.51159996032715</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.013357407376142</v>
+        <v>0.6343620039310429</v>
       </c>
       <c r="V2" t="n">
-        <v>15.69506666819255</v>
+        <v>15.6946666653951</v>
       </c>
       <c r="W2" t="n">
         <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1597100058797447</v>
+        <v>-0.5394635676113805</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.32259999752045</v>
+        <v>15.32229999542236</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.26723975584898</v>
+        <v>1.877653233136251</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1737180313489918</v>
+        <v>0.1735248105929255</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>15.83</v>
+        <v>15.77</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1299991607666</v>
+        <v>28.26000022888184</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1299991607666</v>
+        <v>28.26000022888184</v>
       </c>
       <c r="E3" t="n">
         <v>28.76000022888184</v>
@@ -1199,88 +1199,88 @@
         <v>28.76000022888184</v>
       </c>
       <c r="H3" t="n">
-        <v>2732100</v>
+        <v>5239300</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01159521905557959</v>
+        <v>-0.007027366901776744</v>
       </c>
       <c r="J3" t="n">
-        <v>28.64555528428819</v>
+        <v>28.65999984741211</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.799777027902018</v>
+        <v>-1.395672088834264</v>
       </c>
       <c r="M3" t="n">
-        <v>28.68299980163574</v>
+        <v>28.69599990844727</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.92797351983248</v>
+        <v>-1.519374410916013</v>
       </c>
       <c r="P3" t="n">
-        <v>27.1911538197444</v>
+        <v>27.19615386082576</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>3.452760214759518</v>
+        <v>3.911753012945244</v>
       </c>
       <c r="S3" t="n">
-        <v>27.24759994506836</v>
+        <v>27.25019996643066</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>3.238447487034363</v>
+        <v>3.705661843564958</v>
       </c>
       <c r="V3" t="n">
-        <v>28.88939998626709</v>
+        <v>28.89026666005453</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.62864865958268</v>
+        <v>-2.181587448080342</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.9656999874115</v>
+        <v>28.96634999275208</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2.885139413195923</v>
+        <v>-2.438518363711622</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2654760656149308</v>
+        <v>0.2639331271636906</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.9</v>
+        <v>26.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
@@ -1407,13 +1407,13 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.15</v>
+        <v>17.23</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CC3" t="n">
         <v>9</v>
@@ -1448,13 +1448,13 @@
         <v>5</v>
       </c>
       <c r="CM3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.22000026702881</v>
+        <v>10.22999954223633</v>
       </c>
       <c r="D4" t="n">
-        <v>10.22000026702881</v>
+        <v>10.22999954223633</v>
       </c>
       <c r="E4" t="n">
         <v>10.27999973297119</v>
@@ -1482,67 +1482,67 @@
         <v>10.14000034332275</v>
       </c>
       <c r="H4" t="n">
-        <v>5468800</v>
+        <v>7766700</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01188117633928454</v>
+        <v>0.01287120355016103</v>
       </c>
       <c r="J4" t="n">
-        <v>9.632222175598145</v>
+        <v>9.633333206176758</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>6.10220653879554</v>
+        <v>6.193768276145542</v>
       </c>
       <c r="M4" t="n">
-        <v>9.579999923706055</v>
+        <v>9.580999851226807</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>6.680588188096433</v>
+        <v>6.773820071883415</v>
       </c>
       <c r="P4" t="n">
-        <v>8.784999975791344</v>
+        <v>8.785384563299326</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>16.33466471476229</v>
+        <v>16.44338922819426</v>
       </c>
       <c r="S4" t="n">
-        <v>8.599199981689454</v>
+        <v>8.607999954223633</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>18.84826831322188</v>
+        <v>18.84293211708068</v>
       </c>
       <c r="V4" t="n">
-        <v>8.712866614659628</v>
+        <v>8.718533271153769</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>17.29779324101425</v>
+        <v>17.33624480259097</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.551799945831299</v>
+        <v>8.561549940109252</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.50700825281465</v>
+        <v>19.48770507441303</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5335574347578955</v>
+        <v>0.534098177692138</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>19.65</v>
+        <v>19.67</v>
       </c>
       <c r="CA4" t="n">
         <v>0.87</v>
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.9399995803833</v>
+        <v>11.93000030517578</v>
       </c>
       <c r="D5" t="n">
-        <v>11.9399995803833</v>
+        <v>11.93000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>11.94999980926514</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="F5" t="n">
         <v>11.52999973297119</v>
@@ -1769,67 +1769,67 @@
         <v>11.72000026702881</v>
       </c>
       <c r="H5" t="n">
-        <v>1168800</v>
+        <v>1653300</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02313620414089135</v>
+        <v>0.02227936822468335</v>
       </c>
       <c r="J5" t="n">
-        <v>11.85999997456869</v>
+        <v>11.85888894399007</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6745329341160025</v>
+        <v>0.5996460673640707</v>
       </c>
       <c r="M5" t="n">
-        <v>11.83699998855591</v>
+        <v>11.83600006103516</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8701494629295737</v>
+        <v>0.7941892840139464</v>
       </c>
       <c r="P5" t="n">
-        <v>11.04769233556894</v>
+        <v>11.04730774806096</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>8.076865445840705</v>
+        <v>7.990114670877634</v>
       </c>
       <c r="S5" t="n">
-        <v>11.23319997787476</v>
+        <v>11.25279998779297</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>6.292059287653368</v>
+        <v>6.018060554861359</v>
       </c>
       <c r="V5" t="n">
-        <v>11.97419998168945</v>
+        <v>11.97979998906454</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856174221112984</v>
+        <v>-0.4156971229420541</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.93819997787476</v>
+        <v>11.94549998283386</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.015074320348794</v>
+        <v>-0.1297532768017625</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2946250220551365</v>
+        <v>0.3007774801235278</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>12.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>14.7</v>
+        <v>12.2</v>
       </c>
       <c r="AJ5" t="n">
         <v>2</v>
@@ -1977,7 +1977,7 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="CA5" t="n">
         <v>1.62</v>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.18000030517578</v>
+        <v>55.47999954223633</v>
       </c>
       <c r="D6" t="n">
-        <v>55.18000030517578</v>
+        <v>55.47999954223633</v>
       </c>
       <c r="E6" t="n">
         <v>55.68999862670898</v>
@@ -2048,88 +2048,88 @@
         <v>55.31000137329102</v>
       </c>
       <c r="H6" t="n">
-        <v>3674100</v>
+        <v>6280000</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0009052912814585534</v>
+        <v>0.004526525476590271</v>
       </c>
       <c r="J6" t="n">
-        <v>55.26777776082357</v>
+        <v>55.30111100938585</v>
       </c>
       <c r="K6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1588221187898198</v>
+        <v>0.3234809022555036</v>
       </c>
       <c r="M6" t="n">
-        <v>55.31599998474121</v>
+        <v>55.34599990844727</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2458595697500631</v>
+        <v>0.2421125899084312</v>
       </c>
       <c r="P6" t="n">
-        <v>53.24153826786922</v>
+        <v>53.25307670006385</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.640882852696254</v>
+        <v>4.181773110904233</v>
       </c>
       <c r="S6" t="n">
-        <v>52.56719978332519</v>
+        <v>52.59719978332519</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.970400806244567</v>
+        <v>5.480899688171351</v>
       </c>
       <c r="V6" t="n">
-        <v>55.9046666208903</v>
+        <v>55.9533332824707</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.296253711034069</v>
+        <v>-0.8459437757619019</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.04284999847412</v>
+        <v>56.10559999465942</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.539624935780085</v>
+        <v>-1.115041016373843</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2461594910718222</v>
+        <v>0.2787921131011762</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>54.6</v>
+        <v>55.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>54.8</v>
+        <v>55.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>55.1</v>
+        <v>55.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>55.2</v>
+        <v>55.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>55.4</v>
+        <v>57.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>55.9</v>
+        <v>58.2</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
@@ -2256,13 +2256,13 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.87</v>
+        <v>16.97</v>
       </c>
       <c r="CA6" t="n">
         <v>0.28</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -2293,13 +2293,13 @@
         <v>6</v>
       </c>
       <c r="CM6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN6" t="n">
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.96000003814697</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="D7" t="n">
-        <v>14.96000003814697</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="E7" t="n">
         <v>15.19999980926514</v>
@@ -2327,67 +2327,67 @@
         <v>15.19999980926514</v>
       </c>
       <c r="H7" t="n">
-        <v>1756700</v>
+        <v>2159600</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.004657331741041992</v>
+        <v>-0.002661341487936286</v>
       </c>
       <c r="J7" t="n">
-        <v>16.20777776506212</v>
+        <v>16.21111106872559</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.698635463801128</v>
+        <v>-7.532557715696521</v>
       </c>
       <c r="M7" t="n">
-        <v>16.29499998092651</v>
+        <v>16.29799995422363</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.192696804800077</v>
+        <v>-8.025525750271594</v>
       </c>
       <c r="P7" t="n">
-        <v>15.57769236197838</v>
+        <v>15.57884619786189</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-3.965236374413571</v>
+        <v>-3.779782015079799</v>
       </c>
       <c r="S7" t="n">
-        <v>16.41559999465942</v>
+        <v>16.43919998168945</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.86717486406838</v>
+        <v>-8.815515427669576</v>
       </c>
       <c r="V7" t="n">
-        <v>20.14366669336955</v>
+        <v>20.20453336079915</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-25.73348106940639</v>
+        <v>-25.80873062774234</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.46170000553131</v>
+        <v>21.52414999961853</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-30.29443131582615</v>
+        <v>-30.35729740136623</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5180069571626467</v>
+        <v>0.5242951153938711</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="CB7" t="n">
         <v>0.39</v>
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.72999954223633</v>
+        <v>17.67000007629395</v>
       </c>
       <c r="D8" t="n">
-        <v>17.72999954223633</v>
+        <v>17.67000007629395</v>
       </c>
       <c r="E8" t="n">
         <v>17.79000091552734</v>
@@ -2610,67 +2610,67 @@
         <v>17.72999954223633</v>
       </c>
       <c r="H8" t="n">
-        <v>17070800</v>
+        <v>25726100</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008532401546145874</v>
+        <v>0.005119462626761884</v>
       </c>
       <c r="J8" t="n">
-        <v>17.48222245110406</v>
+        <v>17.47555584377713</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41730887949331</v>
+        <v>1.112664079214732</v>
       </c>
       <c r="M8" t="n">
-        <v>17.46900024414062</v>
+        <v>17.46300029754639</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.494071180079397</v>
+        <v>1.185362052456947</v>
       </c>
       <c r="P8" t="n">
-        <v>16.1453847518334</v>
+        <v>16.14307708006639</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>9.814661061099738</v>
+        <v>9.4586861516818</v>
       </c>
       <c r="S8" t="n">
-        <v>15.773600025177</v>
+        <v>15.76380002975464</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>12.40299940366576</v>
+        <v>12.09226229044581</v>
       </c>
       <c r="V8" t="n">
-        <v>16.62013336817423</v>
+        <v>16.63826670964559</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>6.677841564059703</v>
+        <v>6.200966631038781</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.18895005702973</v>
+        <v>16.18885005950928</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.519144106182683</v>
+        <v>9.149198438061044</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3151822749858791</v>
+        <v>0.3297452678214151</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2822,13 +2822,13 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>18.09</v>
+        <v>18.03</v>
       </c>
       <c r="CA8" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="CC8" t="n">
         <v>4</v>
@@ -2863,13 +2863,13 @@
         <v>9</v>
       </c>
       <c r="CM8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.92000007629395</v>
+        <v>22.94000053405762</v>
       </c>
       <c r="D9" t="n">
-        <v>22.92000007629395</v>
+        <v>22.94000053405762</v>
       </c>
       <c r="E9" t="n">
-        <v>23.01000022888184</v>
+        <v>23.03000068664551</v>
       </c>
       <c r="F9" t="n">
         <v>22.29999923706055</v>
@@ -2897,67 +2897,67 @@
         <v>22.79000091552734</v>
       </c>
       <c r="H9" t="n">
-        <v>20438000</v>
+        <v>26816200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009247071787196637</v>
+        <v>0.01012776128829596</v>
       </c>
       <c r="J9" t="n">
-        <v>22.48666678534614</v>
+        <v>22.48888905843099</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.927067693421762</v>
+        <v>2.005930459501774</v>
       </c>
       <c r="M9" t="n">
-        <v>22.48300018310547</v>
+        <v>22.48500022888184</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.943690297689253</v>
+        <v>2.023572606378429</v>
       </c>
       <c r="P9" t="n">
-        <v>20.49076923957238</v>
+        <v>20.4915384879479</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>11.85524471199531</v>
+        <v>11.94864918292873</v>
       </c>
       <c r="S9" t="n">
-        <v>20.54000003814697</v>
+        <v>20.53040004730225</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>11.58714719438573</v>
+        <v>11.73674395629713</v>
       </c>
       <c r="V9" t="n">
-        <v>21.84266667683919</v>
+        <v>21.87460000356038</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>4.932243005828123</v>
+        <v>4.870491484753202</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.04045001029968</v>
+        <v>22.05150000572205</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.990617549021194</v>
+        <v>4.029206757386194</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3710135848605337</v>
+        <v>0.3722858348247507</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3125,7 +3125,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.130000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.97999954223633</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="D10" t="n">
-        <v>15.97999954223633</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="E10" t="n">
         <v>16.13999938964844</v>
@@ -3196,67 +3196,67 @@
         <v>16.09000015258789</v>
       </c>
       <c r="H10" t="n">
-        <v>3693500</v>
+        <v>4769100</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.00683658230630102</v>
+        <v>-0.002486073035922853</v>
       </c>
       <c r="J10" t="n">
-        <v>16.06333340538873</v>
+        <v>16.07111114925808</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5187831258264328</v>
+        <v>-0.1313656037934323</v>
       </c>
       <c r="M10" t="n">
-        <v>16.02400007247925</v>
+        <v>16.03100004196167</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2745914256359006</v>
+        <v>0.1185153455751192</v>
       </c>
       <c r="P10" t="n">
-        <v>15.19115389310397</v>
+        <v>15.19384618905874</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>5.192796114654985</v>
+        <v>5.634867151796809</v>
       </c>
       <c r="S10" t="n">
-        <v>15.55801776885986</v>
+        <v>15.56801776885986</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2.712310653231692</v>
+        <v>3.095971981511819</v>
       </c>
       <c r="V10" t="n">
-        <v>16.17153928120931</v>
+        <v>16.19240594228109</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.184424906264444</v>
+        <v>-0.8794660023233057</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.28700446605682</v>
+        <v>16.29520446300507</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.88496862305352</v>
+        <v>-1.504769249758165</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2210383681244772</v>
+        <v>0.2272453495071886</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3424,7 +3424,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.13</v>
+        <v>7.17</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3462,16 +3462,16 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.15999984741211</v>
+        <v>18.18000030517578</v>
       </c>
       <c r="D11" t="n">
-        <v>18.15999984741211</v>
+        <v>18.18000030517578</v>
       </c>
       <c r="E11" t="n">
         <v>18.26000022888184</v>
@@ -3499,67 +3499,67 @@
         <v>18.19000053405762</v>
       </c>
       <c r="H11" t="n">
-        <v>24567600</v>
+        <v>35858400</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.002745702337963341</v>
+        <v>-0.001647379506045876</v>
       </c>
       <c r="J11" t="n">
-        <v>18.20888879564073</v>
+        <v>18.21111106872559</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2684894656522189</v>
+        <v>-0.1708339674191105</v>
       </c>
       <c r="M11" t="n">
-        <v>18.16700000762939</v>
+        <v>18.16900005340576</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.03853228499116346</v>
+        <v>0.06054406812530647</v>
       </c>
       <c r="P11" t="n">
-        <v>17.24423085726225</v>
+        <v>17.24500010563777</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>5.310581827221345</v>
+        <v>5.421862532968831</v>
       </c>
       <c r="S11" t="n">
-        <v>17.74534042358398</v>
+        <v>17.75594043731689</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2.336722846280449</v>
+        <v>2.388270389596816</v>
       </c>
       <c r="V11" t="n">
-        <v>18.57984681447347</v>
+        <v>18.60491348266602</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.259690143054919</v>
+        <v>-2.283876127057095</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.7796351146698</v>
+        <v>18.79143511772156</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.299506425306747</v>
+        <v>-3.253795192944865</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2596523096062765</v>
+        <v>0.2660461202149554</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3764,13 +3764,13 @@
         <v>4</v>
       </c>
       <c r="CM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN11" t="n">
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -3783,13 +3783,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40.90000152587891</v>
+        <v>40.72999954223633</v>
       </c>
       <c r="D12" t="n">
-        <v>40.90000152587891</v>
+        <v>40.72999954223633</v>
       </c>
       <c r="E12" t="n">
-        <v>40.90000152587891</v>
+        <v>41.04999923706055</v>
       </c>
       <c r="F12" t="n">
         <v>40.06000137329102</v>
@@ -3798,67 +3798,67 @@
         <v>40.63000106811523</v>
       </c>
       <c r="H12" t="n">
-        <v>2157200</v>
+        <v>3781800</v>
       </c>
       <c r="I12" t="n">
-        <v>0.007637382905288037</v>
+        <v>0.003449110350385531</v>
       </c>
       <c r="J12" t="n">
-        <v>40.83777787950304</v>
+        <v>40.81888877020942</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1523678554682096</v>
+        <v>-0.217764938368348</v>
       </c>
       <c r="M12" t="n">
-        <v>40.92299995422363</v>
+        <v>40.90599975585938</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.05619927270838885</v>
+        <v>-0.4302552551544422</v>
       </c>
       <c r="P12" t="n">
-        <v>39.40115385789137</v>
+        <v>39.39461532005897</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>3.804070493451653</v>
+        <v>3.3897633250842</v>
       </c>
       <c r="S12" t="n">
-        <v>40.03059982299805</v>
+        <v>40.03759979248047</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2.171842807065249</v>
+        <v>1.729373772015919</v>
       </c>
       <c r="V12" t="n">
-        <v>37.05439989725749</v>
+        <v>37.05319989522298</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>10.37825909820237</v>
+        <v>9.923028665298544</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.75659996032715</v>
+        <v>36.73759994506836</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.27253763956376</v>
+        <v>10.86733919237396</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3157654630269242</v>
+        <v>0.3187609881538432</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4028,13 +4028,13 @@
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="n">
-        <v>8.65</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>6.28</v>
+        <v>6.26</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4065,13 +4065,13 @@
         <v>4</v>
       </c>
       <c r="CM12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN12" t="n">
         <v>0</v>
       </c>
       <c r="CO12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -4084,82 +4084,82 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.910000085830688</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="D13" t="n">
-        <v>3.910000085830688</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="E13" t="n">
         <v>4.050000190734863</v>
       </c>
       <c r="F13" t="n">
-        <v>3.880000114440918</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="G13" t="n">
         <v>4.010000228881836</v>
       </c>
       <c r="H13" t="n">
-        <v>10475300</v>
+        <v>24561100</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.02249997854232788</v>
+        <v>-0.03750002384185791</v>
       </c>
       <c r="J13" t="n">
-        <v>4.000000026490953</v>
+        <v>3.993333339691162</v>
       </c>
       <c r="K13" t="n">
         <v>-1</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.249998501605472</v>
+        <v>-3.589318067539008</v>
       </c>
       <c r="M13" t="n">
-        <v>3.97900002002716</v>
+        <v>3.973000001907349</v>
       </c>
       <c r="N13" t="n">
         <v>-1</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.73410238374417</v>
+        <v>-3.095899753730955</v>
       </c>
       <c r="P13" t="n">
-        <v>3.803076927478497</v>
+        <v>3.800769228201646</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.811490811022939</v>
+        <v>1.295281914661687</v>
       </c>
       <c r="S13" t="n">
-        <v>3.684000000953674</v>
+        <v>3.68579999923706</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6.134638567277682</v>
+        <v>4.454932590740038</v>
       </c>
       <c r="V13" t="n">
-        <v>4.009533338546753</v>
+        <v>4.026466671625773</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.482414892505665</v>
+        <v>-4.382670499590954</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.468550004959106</v>
+        <v>4.4832000041008</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-12.49957857713465</v>
+        <v>-14.12384231997325</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5409863184781729</v>
+        <v>0.5545722783748754</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4311,13 +4311,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>5.51</v>
+        <v>5.42</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CC13" t="n">
         <v>8</v>
@@ -4349,16 +4349,16 @@
         <v>1</v>
       </c>
       <c r="CL13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN13" t="n">
         <v>0</v>
       </c>
       <c r="CO13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>61.2599983215332</v>
+        <v>61.22999954223633</v>
       </c>
       <c r="D14" t="n">
-        <v>61.2599983215332</v>
+        <v>61.22999954223633</v>
       </c>
       <c r="E14" t="n">
         <v>61.66999816894531</v>
@@ -4386,67 +4386,67 @@
         <v>60.83000183105469</v>
       </c>
       <c r="H14" t="n">
-        <v>3400400</v>
+        <v>5823900</v>
       </c>
       <c r="I14" t="n">
-        <v>0.007068822579896716</v>
+        <v>0.006575664953825999</v>
       </c>
       <c r="J14" t="n">
-        <v>60.31888919406467</v>
+        <v>60.31555599636502</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.560222908682378</v>
+        <v>1.516099007570149</v>
       </c>
       <c r="M14" t="n">
-        <v>60.16800041198731</v>
+        <v>60.16500053405762</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.81491474216972</v>
+        <v>1.770130472409528</v>
       </c>
       <c r="P14" t="n">
-        <v>55.44269253657414</v>
+        <v>55.44153873737041</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>10.49246621837771</v>
+        <v>10.4406568372609</v>
       </c>
       <c r="S14" t="n">
-        <v>55.69300010681152</v>
+        <v>55.69240013122558</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9.99586699234184</v>
+        <v>9.943186858463166</v>
       </c>
       <c r="V14" t="n">
-        <v>56.30239992777506</v>
+        <v>56.30219993591309</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>8.805305635492919</v>
+        <v>8.752410406578056</v>
       </c>
       <c r="Y14" t="n">
-        <v>56.13259994506836</v>
+        <v>56.13244995117188</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.134439490567949</v>
+        <v>9.081288266410379</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.354308179906879</v>
+        <v>0.3542589608536341</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>3510880000</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.77</v>
+        <v>13.76</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.20000076293945</v>
+        <v>21.29000091552734</v>
       </c>
       <c r="D15" t="n">
-        <v>21.20000076293945</v>
+        <v>21.29000091552734</v>
       </c>
       <c r="E15" t="n">
-        <v>21.26000022888184</v>
+        <v>21.32999992370605</v>
       </c>
       <c r="F15" t="n">
         <v>20.80999946594238</v>
@@ -4691,67 +4691,67 @@
         <v>21.04999923706055</v>
       </c>
       <c r="H15" t="n">
-        <v>1385800</v>
+        <v>2867400</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01678658873218941</v>
+        <v>0.02110314273416813</v>
       </c>
       <c r="J15" t="n">
-        <v>22.00444433424208</v>
+        <v>22.01444435119629</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.65582315591945</v>
+        <v>-3.290764118829909</v>
       </c>
       <c r="M15" t="n">
-        <v>22.0579999923706</v>
+        <v>22.0670000076294</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.889741725124285</v>
+        <v>-3.521090732013478</v>
       </c>
       <c r="P15" t="n">
-        <v>21.60192306225116</v>
+        <v>21.60538460658147</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.86058573652667</v>
+        <v>-1.459745784659859</v>
       </c>
       <c r="S15" t="n">
-        <v>21.5673999786377</v>
+        <v>21.55479999542236</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.703493309634669</v>
+        <v>-1.228492400538424</v>
       </c>
       <c r="V15" t="n">
-        <v>22.59586669921875</v>
+        <v>22.61413336435954</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.17752775257591</v>
+        <v>-5.855331387224691</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.39904998779297</v>
+        <v>22.38699998855591</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-5.35312535802622</v>
+        <v>-4.90016113632618</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2910091495753193</v>
+        <v>0.2826588723596244</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       <c r="BX15" t="inlineStr"/>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
-        <v>10.65</v>
+        <v>10.7</v>
       </c>
       <c r="CA15" t="n">
         <v>-0.03</v>
@@ -4967,13 +4967,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.63999938964844</v>
+        <v>17.65999984741211</v>
       </c>
       <c r="D16" t="n">
-        <v>17.63999938964844</v>
+        <v>17.65999984741211</v>
       </c>
       <c r="E16" t="n">
-        <v>17.75</v>
+        <v>17.79000091552734</v>
       </c>
       <c r="F16" t="n">
         <v>17.5</v>
@@ -4982,67 +4982,67 @@
         <v>17.61000061035156</v>
       </c>
       <c r="H16" t="n">
-        <v>977100</v>
+        <v>2064700</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.00507615086923674</v>
+        <v>-0.003948093436633493</v>
       </c>
       <c r="J16" t="n">
-        <v>18.07555537753635</v>
+        <v>18.0777776506212</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.409640969755242</v>
+        <v>-2.311002000816928</v>
       </c>
       <c r="M16" t="n">
-        <v>18.13399982452393</v>
+        <v>18.13599987030029</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.724166977256808</v>
+        <v>-2.6246141723219</v>
       </c>
       <c r="P16" t="n">
-        <v>18.19153829721304</v>
+        <v>18.19230754558857</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.031843149015597</v>
+        <v>-2.926004284187331</v>
       </c>
       <c r="S16" t="n">
-        <v>18.91319988250732</v>
+        <v>18.92119987487793</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.731809005182993</v>
+        <v>-6.665539372798129</v>
       </c>
       <c r="V16" t="n">
-        <v>19.18266656239827</v>
+        <v>19.18166656494141</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.04198502711694</v>
+        <v>-7.932922368228772</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.44184990406036</v>
+        <v>18.41779990673065</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-4.347993930019896</v>
+        <v>-4.114498274257004</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.3735607025109533</v>
+        <v>0.385396307071586</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>35.28</v>
+        <v>35.32</v>
       </c>
       <c r="CA16" t="n">
         <v>1.3</v>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.539999961853027</v>
+        <v>4.579999923706055</v>
       </c>
       <c r="D17" t="n">
-        <v>4.539999961853027</v>
+        <v>4.579999923706055</v>
       </c>
       <c r="E17" t="n">
         <v>4.619999885559082</v>
@@ -5261,67 +5261,67 @@
         <v>4.400000095367432</v>
       </c>
       <c r="H17" t="n">
-        <v>2637100</v>
+        <v>3422700</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002207450680250744</v>
+        <v>0.01103746392537586</v>
       </c>
       <c r="J17" t="n">
-        <v>4.982222292158339</v>
+        <v>4.986666732364231</v>
       </c>
       <c r="K17" t="n">
         <v>-1</v>
       </c>
       <c r="L17" t="n">
-        <v>-8.876005613024082</v>
+        <v>-8.155082953886742</v>
       </c>
       <c r="M17" t="n">
-        <v>4.978000068664551</v>
+        <v>4.982000064849854</v>
       </c>
       <c r="N17" t="n">
         <v>-1</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.798716367415119</v>
+        <v>-8.069051302911101</v>
       </c>
       <c r="P17" t="n">
-        <v>4.813461542129517</v>
+        <v>4.815000002200787</v>
       </c>
       <c r="Q17" t="n">
         <v>-1</v>
       </c>
       <c r="R17" t="n">
-        <v>-5.681183445282239</v>
+        <v>-4.880583144077273</v>
       </c>
       <c r="S17" t="n">
-        <v>5.425999994277954</v>
+        <v>5.426799993515015</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-16.32878793511367</v>
+        <v>-15.60404051781676</v>
       </c>
       <c r="V17" t="n">
-        <v>8.22793330192566</v>
+        <v>8.228199968338012</v>
       </c>
       <c r="W17" t="n">
         <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>-44.82211030088821</v>
+        <v>-44.33776595938571</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.255749979019164</v>
+        <v>8.255949978828431</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>-45.00802503236165</v>
+        <v>-44.52485861165568</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.167358127012114</v>
+        <v>1.168172935807859</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>-0.4</v>
       </c>
       <c r="CA17" t="n">
-        <v>11.89</v>
+        <v>11.78</v>
       </c>
       <c r="CB17" t="n">
         <v>-0.23</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.869999885559082</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="D18" t="n">
-        <v>8.869999885559082</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="E18" t="n">
         <v>9.300000190734863</v>
@@ -5548,67 +5548,67 @@
         <v>9.279999732971191</v>
       </c>
       <c r="H18" t="n">
-        <v>6148300</v>
+        <v>10952900</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03796099472158865</v>
+        <v>-0.03687637123002574</v>
       </c>
       <c r="J18" t="n">
-        <v>9.228888935512966</v>
+        <v>9.230000072055393</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.888756842363454</v>
+        <v>-3.791982176404633</v>
       </c>
       <c r="M18" t="n">
-        <v>9.238000011444091</v>
+        <v>9.239000034332275</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.983547579877988</v>
+        <v>-3.885701034281926</v>
       </c>
       <c r="P18" t="n">
-        <v>8.489615440368652</v>
+        <v>8.490000064556416</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>4.480585108504184</v>
+        <v>4.593640128610283</v>
       </c>
       <c r="S18" t="n">
-        <v>9.039400024414062</v>
+        <v>9.064000034332276</v>
       </c>
       <c r="T18" t="n">
         <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.874019718094741</v>
+        <v>-2.030007934624999</v>
       </c>
       <c r="V18" t="n">
-        <v>10.7793333307902</v>
+        <v>10.80400000254313</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-17.71290845768058</v>
+        <v>-17.80821813818334</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.24710001468658</v>
+        <v>11.29510001659393</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-21.13522708985835</v>
+        <v>-21.38183724451246</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5103819283015502</v>
+        <v>0.5337314517472893</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5627,13 +5627,13 @@
         <v>7.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AH18" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
@@ -5835,7 +5835,7 @@
         <v>11.38000011444092</v>
       </c>
       <c r="H19" t="n">
-        <v>12223700</v>
+        <v>15077400</v>
       </c>
       <c r="I19" t="n">
         <v>-0.007936521285438536</v>
@@ -5868,34 +5868,34 @@
         <v>4.733600429981175</v>
       </c>
       <c r="S19" t="n">
-        <v>10.91279996871948</v>
+        <v>10.91519996643066</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.089949712695818</v>
+        <v>3.067282638879743</v>
       </c>
       <c r="V19" t="n">
-        <v>11.51446672439575</v>
+        <v>11.51960005442301</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.296821300767894</v>
+        <v>-2.340359501626098</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43690003395081</v>
+        <v>11.44075003147125</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.634184380347712</v>
+        <v>-1.667286069064843</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.27082870330567</v>
+        <v>0.2880065176051267</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.630000114440918</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="D20" t="n">
-        <v>5.630000114440918</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="E20" t="n">
         <v>6.130000114440918</v>
@@ -6118,67 +6118,67 @@
         <v>6.110000133514404</v>
       </c>
       <c r="H20" t="n">
-        <v>7980500</v>
+        <v>11588700</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07401312745261357</v>
+        <v>-0.06085524509900797</v>
       </c>
       <c r="J20" t="n">
-        <v>6.461111068725586</v>
+        <v>6.46999994913737</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-12.86328226591838</v>
+        <v>-11.74652112774323</v>
       </c>
       <c r="M20" t="n">
-        <v>6.480999946594238</v>
+        <v>6.488999938964843</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-13.13068722675303</v>
+        <v>-12.00493000685928</v>
       </c>
       <c r="P20" t="n">
-        <v>6.110769216830914</v>
+        <v>6.113846136973454</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-7.867570928154373</v>
+        <v>-6.605434447952893</v>
       </c>
       <c r="S20" t="n">
-        <v>5.855599975585937</v>
+        <v>5.841199970245361</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.852719825220722</v>
+        <v>-2.246112661211926</v>
       </c>
       <c r="V20" t="n">
-        <v>5.141066656112671</v>
+        <v>5.143533322016398</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>9.510350497924595</v>
+        <v>11.01318258610027</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.269499990940094</v>
+        <v>5.269699990749359</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.84125864162891</v>
+        <v>8.355315258373983</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5513351538363728</v>
+        <v>0.5379470353524929</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6328,13 +6328,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>13.73</v>
+        <v>13.93</v>
       </c>
       <c r="CA20" t="n">
         <v>0.01</v>
       </c>
       <c r="CB20" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="CC20" t="n">
         <v>3</v>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM20" t="n">
         <v>1</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.299999952316284</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="D21" t="n">
-        <v>2.299999952316284</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="E21" t="n">
         <v>2.380000114440918</v>
@@ -6403,67 +6403,67 @@
         <v>2.369999885559082</v>
       </c>
       <c r="H21" t="n">
-        <v>15535100</v>
+        <v>19564100</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.02127657631718149</v>
+        <v>-0.01702126105374524</v>
       </c>
       <c r="J21" t="n">
-        <v>2.372222211625841</v>
+        <v>2.373333321677314</v>
       </c>
       <c r="K21" t="n">
         <v>-1</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.044498064119307</v>
+        <v>-2.668541258798532</v>
       </c>
       <c r="M21" t="n">
-        <v>2.375</v>
+        <v>2.375999999046326</v>
       </c>
       <c r="N21" t="n">
         <v>-1</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.157896744577508</v>
+        <v>-2.777780147023393</v>
       </c>
       <c r="P21" t="n">
-        <v>2.252307690106905</v>
+        <v>2.252692305124723</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.117484321474524</v>
+        <v>2.543962063724684</v>
       </c>
       <c r="S21" t="n">
-        <v>2.236000003814697</v>
+        <v>2.237200002670288</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2.862251717012555</v>
+        <v>3.254064903556233</v>
       </c>
       <c r="V21" t="n">
-        <v>2.637866667111715</v>
+        <v>2.648333333333333</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-12.8083317859796</v>
+        <v>-12.77533255709726</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.896404507160187</v>
+        <v>2.903440866470337</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-20.59120379662212</v>
+        <v>-20.43922886613606</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4130981368841616</v>
+        <v>0.4499278926330462</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="CA21" t="n">
         <v>1.12</v>
@@ -6653,16 +6653,16 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN21" t="n">
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.25</v>
+        <v>45.18999862670898</v>
       </c>
       <c r="D22" t="n">
-        <v>45.25</v>
+        <v>45.18999862670898</v>
       </c>
       <c r="E22" t="n">
         <v>45.7599983215332</v>
@@ -6690,88 +6690,88 @@
         <v>45.63999938964844</v>
       </c>
       <c r="H22" t="n">
-        <v>1303900</v>
+        <v>1721800</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002436876646852326</v>
+        <v>0.001107648155440843</v>
       </c>
       <c r="J22" t="n">
-        <v>45.77444458007812</v>
+        <v>45.76777776082357</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.145714786687708</v>
+        <v>-1.262414655861126</v>
       </c>
       <c r="M22" t="n">
-        <v>45.87000007629395</v>
+        <v>45.86399993896485</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.35164612004082</v>
+        <v>-1.469565046992875</v>
       </c>
       <c r="P22" t="n">
-        <v>44.28807713435246</v>
+        <v>44.28576938922588</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.171968005586345</v>
+        <v>2.041805415043974</v>
       </c>
       <c r="S22" t="n">
-        <v>45.1260001373291</v>
+        <v>45.14600006103515</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0.274785849163539</v>
+        <v>0.09745839191588991</v>
       </c>
       <c r="V22" t="n">
-        <v>46.80519983927409</v>
+        <v>46.84226648966472</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.322707401345449</v>
+        <v>-3.527301274630442</v>
       </c>
       <c r="Y22" t="n">
-        <v>47.96529993057251</v>
+        <v>47.9881999206543</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.660967271137219</v>
+        <v>-5.831019497651454</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.2674119976425559</v>
+        <v>0.2724443720974341</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="AE22" t="n">
         <v>45</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>45.1</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
         <v>45.2</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>46.7</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>47.2</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>48.3</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
@@ -6898,13 +6898,13 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="CA22" t="n">
         <v>0.5</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CC22" t="n">
         <v>3</v>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.11000061035156</v>
+        <v>16.06999969482422</v>
       </c>
       <c r="D23" t="n">
-        <v>16.11000061035156</v>
+        <v>16.06999969482422</v>
       </c>
       <c r="E23" t="n">
         <v>16.18000030517578</v>
@@ -6973,67 +6973,67 @@
         <v>16.15999984741211</v>
       </c>
       <c r="H23" t="n">
-        <v>6568200</v>
+        <v>9971600</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001865714352478287</v>
+        <v>-0.000621904784159466</v>
       </c>
       <c r="J23" t="n">
-        <v>15.99777772691515</v>
+        <v>15.99333318074544</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7014904529371447</v>
+        <v>0.479365453169419</v>
       </c>
       <c r="M23" t="n">
-        <v>15.97599992752075</v>
+        <v>15.97199983596802</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8387624151147947</v>
+        <v>0.6135728766757929</v>
       </c>
       <c r="P23" t="n">
-        <v>14.96961531272301</v>
+        <v>14.96807681597196</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7.618000020744089</v>
+        <v>7.361820041412599</v>
       </c>
       <c r="S23" t="n">
-        <v>14.89619997024536</v>
+        <v>14.90559995651245</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>8.148391150298238</v>
+        <v>7.811827378360743</v>
       </c>
       <c r="V23" t="n">
-        <v>15.04253327051799</v>
+        <v>15.04019992828369</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>7.096326932683055</v>
+        <v>6.846981898185731</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.55864995956421</v>
+        <v>14.55544995307922</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.6558688827339</v>
+        <v>10.40537906163863</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1972394537908417</v>
+        <v>0.2232766526579484</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7185,13 +7185,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>17.7</v>
+        <v>17.66</v>
       </c>
       <c r="CA23" t="n">
         <v>0.38</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.680000066757202</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="D24" t="n">
-        <v>3.680000066757202</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="E24" t="n">
         <v>3.720000028610229</v>
@@ -7256,67 +7256,67 @@
         <v>3.670000076293945</v>
       </c>
       <c r="H24" t="n">
-        <v>17399600</v>
+        <v>24039400</v>
       </c>
       <c r="I24" t="n">
-        <v>0.008219170029021727</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.725555552376641</v>
+        <v>3.722222222222222</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.222783689009225</v>
+        <v>-1.940295945352585</v>
       </c>
       <c r="M24" t="n">
-        <v>3.734999990463257</v>
+        <v>3.73199999332428</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.472554855327672</v>
+        <v>-2.197210560115964</v>
       </c>
       <c r="P24" t="n">
-        <v>3.616923084625831</v>
+        <v>3.615769239572378</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.743940378480465</v>
+        <v>0.9467101888145332</v>
       </c>
       <c r="S24" t="n">
-        <v>3.735600023269653</v>
+        <v>3.741000022888183</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.48838088034345</v>
+        <v>-2.432502725581292</v>
       </c>
       <c r="V24" t="n">
-        <v>4.489200003941854</v>
+        <v>4.506666669845581</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-18.02548196725728</v>
+        <v>-19.00887368063329</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.773150012493134</v>
+        <v>4.786150012016297</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-22.90206557252016</v>
+        <v>-23.73828471310766</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.5938767755717701</v>
+        <v>0.6378833155576562</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7468,13 +7468,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>-1.53</v>
+        <v>-1.52</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CB24" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CC24" t="n">
         <v>5</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="CL24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM24" t="n">
         <v>3</v>
@@ -7515,7 +7515,7 @@
         <v>-1</v>
       </c>
       <c r="CO24" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>55.90999984741211</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="D25" t="n">
-        <v>55.90999984741211</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="E25" t="n">
         <v>57.04999923706055</v>
@@ -7543,88 +7543,88 @@
         <v>56.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1705400</v>
+        <v>2510500</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01393299655903546</v>
+        <v>-0.008465600278264374</v>
       </c>
       <c r="J25" t="n">
-        <v>56.39222208658854</v>
+        <v>56.42666668362088</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8551218968388803</v>
+        <v>-0.3662549554389046</v>
       </c>
       <c r="M25" t="n">
-        <v>56.44099998474121</v>
+        <v>56.47200012207031</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9408056864206111</v>
+        <v>-0.4462368976173408</v>
       </c>
       <c r="P25" t="n">
-        <v>55.72307704045222</v>
+        <v>55.73500017019418</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3354495424295896</v>
+        <v>0.8701911707686854</v>
       </c>
       <c r="S25" t="n">
-        <v>59.51879981994629</v>
+        <v>59.56959983825683</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.063294259043134</v>
+        <v>-5.623000031305445</v>
       </c>
       <c r="V25" t="n">
-        <v>57.22846649169922</v>
+        <v>57.19853317260742</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.303865060718244</v>
+        <v>-1.71076406618923</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.40309989929199</v>
+        <v>54.29949991226196</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.769878832106267</v>
+        <v>3.536867395729865</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2926605778993859</v>
+        <v>0.3173954147183974</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>54.9</v>
+        <v>55.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="AG25" t="n">
-        <v>56.2</v>
+        <v>57.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="AI25" t="n">
-        <v>58</v>
+        <v>58.7</v>
       </c>
       <c r="AJ25" t="n">
         <v>1</v>
@@ -7751,13 +7751,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>15.71</v>
+        <v>15.79</v>
       </c>
       <c r="CA25" t="n">
         <v>0.32</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CC25" t="n">
         <v>6</v>
@@ -7792,13 +7792,13 @@
         <v>2</v>
       </c>
       <c r="CM25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN25" t="n">
         <v>0</v>
       </c>
       <c r="CO25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.230000019073486</v>
+        <v>6.25</v>
       </c>
       <c r="D26" t="n">
-        <v>6.230000019073486</v>
+        <v>6.25</v>
       </c>
       <c r="E26" t="n">
         <v>6.550000190734863</v>
@@ -7826,67 +7826,67 @@
         <v>6.510000228881836</v>
       </c>
       <c r="H26" t="n">
-        <v>18216300</v>
+        <v>24969100</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.03560371791258699</v>
+        <v>-0.03250774565122305</v>
       </c>
       <c r="J26" t="n">
-        <v>6.576666673024495</v>
+        <v>6.578888893127441</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.271160470591143</v>
+        <v>-4.999155609255102</v>
       </c>
       <c r="M26" t="n">
-        <v>6.557000017166137</v>
+        <v>6.559000015258789</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.987036712468651</v>
+        <v>-4.711084228387477</v>
       </c>
       <c r="P26" t="n">
-        <v>5.571153824145977</v>
+        <v>5.571923054181612</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>11.82602770851523</v>
+        <v>12.16953176174078</v>
       </c>
       <c r="S26" t="n">
-        <v>5.308199987411499</v>
+        <v>5.312799987792968</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>17.36558595848035</v>
+        <v>17.64041587035844</v>
       </c>
       <c r="V26" t="n">
-        <v>6.108266655604044</v>
+        <v>6.141266657511394</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.992928114193531</v>
+        <v>1.770536088929055</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.961800000667572</v>
+        <v>6.982800002098084</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-10.51164902071178</v>
+        <v>-10.49435759119412</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6738502968231719</v>
+        <v>0.6839338399045892</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8038,10 +8038,10 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>-4.13</v>
+        <v>-4.14</v>
       </c>
       <c r="CA26" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="CB26" t="n">
         <v>0.64</v>
@@ -8094,91 +8094,91 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.71999931335449</v>
+        <v>28.84000015258789</v>
       </c>
       <c r="D27" t="n">
-        <v>28.71999931335449</v>
+        <v>28.84000015258789</v>
       </c>
       <c r="E27" t="n">
         <v>31.11000061035156</v>
       </c>
       <c r="F27" t="n">
-        <v>28.67000007629395</v>
+        <v>28.36000061035156</v>
       </c>
       <c r="G27" t="n">
         <v>30.77000045776367</v>
       </c>
       <c r="H27" t="n">
-        <v>3994500</v>
+        <v>7629400</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.05743354248232635</v>
+        <v>-0.05349521488345421</v>
       </c>
       <c r="J27" t="n">
-        <v>31.6011110941569</v>
+        <v>31.61444452073839</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-9.117121775300909</v>
+        <v>-8.775875743540338</v>
       </c>
       <c r="M27" t="n">
-        <v>31.72099990844726</v>
+        <v>31.7329999923706</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-9.46061159406772</v>
+        <v>-9.116691899531284</v>
       </c>
       <c r="P27" t="n">
-        <v>31.76576922490047</v>
+        <v>31.77038464179406</v>
       </c>
       <c r="Q27" t="n">
         <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-9.588213935516677</v>
+        <v>-9.223635540601032</v>
       </c>
       <c r="S27" t="n">
-        <v>31.49340007781982</v>
+        <v>31.48860008239746</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.806291977405715</v>
+        <v>-8.411297812157018</v>
       </c>
       <c r="V27" t="n">
-        <v>33.23833340962728</v>
+        <v>33.2880667368571</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-13.59374442932834</v>
+        <v>-13.36234579025352</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.55454999923706</v>
+        <v>33.5910000038147</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-14.40803314600402</v>
+        <v>-14.14366899076321</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4575302339044061</v>
+        <v>0.4536276302129889</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>17.4</v>
+        <v>22.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>22.4</v>
+        <v>28.4</v>
       </c>
       <c r="AF27" t="n">
         <v>28.6</v>
@@ -8317,13 +8317,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="CA27" t="n">
         <v>-0.05</v>
       </c>
       <c r="CB27" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="CC27" t="n">
         <v>9</v>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20.63999938964844</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="D28" t="n">
-        <v>20.63999938964844</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="E28" t="n">
         <v>20.75</v>
@@ -8392,67 +8392,67 @@
         <v>20.55999946594238</v>
       </c>
       <c r="H28" t="n">
-        <v>1161700</v>
+        <v>1723300</v>
       </c>
       <c r="I28" t="n">
-        <v>0.003891046973934831</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>20.16666645473904</v>
+        <v>20.15777757432726</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>2.347105487025928</v>
+        <v>1.995368240035515</v>
       </c>
       <c r="M28" t="n">
-        <v>20.1269998550415</v>
+        <v>20.1189998626709</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.548812730668526</v>
+        <v>2.191955893840047</v>
       </c>
       <c r="P28" t="n">
-        <v>19.23923066946177</v>
+        <v>19.23615374931922</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>7.280793833456648</v>
+        <v>6.882070781275663</v>
       </c>
       <c r="S28" t="n">
-        <v>20.04560001373291</v>
+        <v>20.08760002136231</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>2.96523613914433</v>
+        <v>2.351696788455069</v>
       </c>
       <c r="V28" t="n">
-        <v>18.91353340148926</v>
+        <v>18.90966673533122</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>9.128204400047418</v>
+        <v>8.727455399981475</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.34530007839203</v>
+        <v>18.33165008068085</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.50837708541609</v>
+        <v>12.15574907580154</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2419966212092179</v>
+        <v>0.2636369904981123</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8612,13 +8612,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>14.14</v>
+        <v>14.08</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB28" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="CC28" t="n">
         <v>2</v>
@@ -8650,16 +8650,16 @@
         <v>0</v>
       </c>
       <c r="CL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN28" t="n">
         <v>0</v>
       </c>
       <c r="CO28" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
@@ -8672,82 +8672,82 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.30999946594238</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="D29" t="n">
-        <v>26.30999946594238</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="E29" t="n">
         <v>27.10000038146973</v>
       </c>
       <c r="F29" t="n">
-        <v>25.92000007629395</v>
+        <v>25.86000061035156</v>
       </c>
       <c r="G29" t="n">
         <v>26.85000038146973</v>
       </c>
       <c r="H29" t="n">
-        <v>4937800</v>
+        <v>8131900</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01164543063552892</v>
+        <v>-0.02817430414557409</v>
       </c>
       <c r="J29" t="n">
-        <v>25.83888901604546</v>
+        <v>25.79000027974446</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.823261246272502</v>
+        <v>0.3101999171041736</v>
       </c>
       <c r="M29" t="n">
-        <v>25.78900012969971</v>
+        <v>25.74500026702881</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>2.020238604142971</v>
+        <v>0.4855333886505234</v>
       </c>
       <c r="P29" t="n">
-        <v>24.02423081031213</v>
+        <v>24.00730778620793</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>9.514430133801065</v>
+        <v>7.758858550959944</v>
       </c>
       <c r="S29" t="n">
-        <v>22.84600006103516</v>
+        <v>22.83400009155273</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>15.16238902062873</v>
+        <v>13.2959653827969</v>
       </c>
       <c r="V29" t="n">
-        <v>24.43546667734782</v>
+        <v>24.49700002034505</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>7.671360704284378</v>
+        <v>5.604771268922941</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.79125</v>
+        <v>25.85665000915527</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.011338984897519</v>
+        <v>0.0516340286672759</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.3955686964764187</v>
+        <v>0.413323142945506</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8899,13 +8899,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>6.08</v>
+        <v>5.97</v>
       </c>
       <c r="CA29" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="CB29" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="CC29" t="n">
         <v>8</v>
@@ -8936,13 +8936,13 @@
         <v>10</v>
       </c>
       <c r="CM29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.859999656677246</v>
+        <v>9.970000267028809</v>
       </c>
       <c r="D30" t="n">
-        <v>9.859999656677246</v>
+        <v>9.970000267028809</v>
       </c>
       <c r="E30" t="n">
         <v>10.22000026702881</v>
@@ -8970,90 +8970,88 @@
         <v>10.21000003814697</v>
       </c>
       <c r="H30" t="n">
-        <v>6498100</v>
+        <v>11247800</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.02182542348154326</v>
+        <v>-0.01091266443549765</v>
       </c>
       <c r="J30" t="n">
-        <v>10.61888896094428</v>
+        <v>10.63111125098334</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.146597982690952</v>
+        <v>-6.218644207052067</v>
       </c>
       <c r="M30" t="n">
-        <v>10.70400009155273</v>
+        <v>10.71500015258789</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-7.884906835357251</v>
+        <v>-6.952868641622459</v>
       </c>
       <c r="P30" t="n">
-        <v>10.74653852902926</v>
+        <v>10.75076932173509</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-8.249529557422006</v>
+        <v>-7.262448215010811</v>
       </c>
       <c r="S30" t="n">
-        <v>11.29420001983643</v>
+        <v>11.32160003662109</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-12.69855643286147</v>
+        <v>-11.93823987086959</v>
       </c>
       <c r="V30" t="n">
-        <v>13.06373335520427</v>
+        <v>13.09486669540405</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-24.52387546053771</v>
+        <v>-23.86329315954005</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.56370001792908</v>
+        <v>13.59945002555847</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-27.30597371186418</v>
+        <v>-26.68820982987227</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3888809381824739</v>
+        <v>0.4015225003069193</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AD30" t="n">
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
@@ -9180,13 +9178,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>6.12</v>
+        <v>6.19</v>
       </c>
       <c r="CA30" t="n">
         <v>0.14</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CC30" t="n">
         <v>9</v>
@@ -9198,7 +9196,7 @@
         <v>7</v>
       </c>
       <c r="CF30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CG30" t="n">
         <v>3</v>
@@ -9207,7 +9205,7 @@
         <v>8</v>
       </c>
       <c r="CI30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CJ30" t="inlineStr"/>
       <c r="CK30" t="n">
@@ -9223,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -9236,13 +9234,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30.95000076293945</v>
+        <v>30.92000007629395</v>
       </c>
       <c r="D31" t="n">
-        <v>30.95000076293945</v>
+        <v>30.92000007629395</v>
       </c>
       <c r="E31" t="n">
-        <v>31.01000022888184</v>
+        <v>31.04000091552734</v>
       </c>
       <c r="F31" t="n">
         <v>30.39999961853027</v>
@@ -9251,67 +9249,67 @@
         <v>30.84000015258789</v>
       </c>
       <c r="H31" t="n">
-        <v>785500</v>
+        <v>1336100</v>
       </c>
       <c r="I31" t="n">
-        <v>0.009787965681663735</v>
+        <v>0.008809150444505587</v>
       </c>
       <c r="J31" t="n">
-        <v>30.67666647169325</v>
+        <v>30.67333306206597</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8910169281216346</v>
+        <v>0.8041741460859678</v>
       </c>
       <c r="M31" t="n">
-        <v>30.64499988555908</v>
+        <v>30.64199981689453</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9952712629119599</v>
+        <v>0.9072523368600002</v>
       </c>
       <c r="P31" t="n">
-        <v>29.31307689960186</v>
+        <v>29.31192302703857</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>5.584278542113136</v>
+        <v>5.486085125742217</v>
       </c>
       <c r="S31" t="n">
-        <v>29.83319995880127</v>
+        <v>29.89599990844727</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>3.743483118406509</v>
+        <v>3.425207957527934</v>
       </c>
       <c r="V31" t="n">
-        <v>32.36340003967285</v>
+        <v>32.3934000269572</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-4.367276846687237</v>
+        <v>-4.548457245726332</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.15650003433228</v>
+        <v>32.1685643196106</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-3.751960785858811</v>
+        <v>-3.881317894424965</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2141424679620754</v>
+        <v>0.2197183575017793</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9459,7 +9457,7 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>13.76</v>
+        <v>13.74</v>
       </c>
       <c r="CA31" t="n">
         <v>0.7</v>
@@ -9515,82 +9513,82 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>95.79000091552734</v>
+        <v>95.23000335693359</v>
       </c>
       <c r="D32" t="n">
-        <v>95.79000091552734</v>
+        <v>95.23000335693359</v>
       </c>
       <c r="E32" t="n">
         <v>97.58000183105469</v>
       </c>
       <c r="F32" t="n">
-        <v>95.55999755859375</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="G32" t="n">
         <v>95.91999816894531</v>
       </c>
       <c r="H32" t="n">
-        <v>2112900</v>
+        <v>3253000</v>
       </c>
       <c r="I32" t="n">
-        <v>0.005247140258118455</v>
+        <v>-0.0006296312101721213</v>
       </c>
       <c r="J32" t="n">
-        <v>95.67333390977647</v>
+        <v>95.61111195882161</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1219430754455478</v>
+        <v>-0.3986028340012971</v>
       </c>
       <c r="M32" t="n">
-        <v>95.49900054931641</v>
+        <v>95.44300079345703</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3047156143384587</v>
+        <v>-0.2231671623405613</v>
       </c>
       <c r="P32" t="n">
-        <v>96.46076906644382</v>
+        <v>96.43923069880559</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.6953792276468752</v>
+        <v>-1.253874935656212</v>
       </c>
       <c r="S32" t="n">
-        <v>91.655</v>
+        <v>91.38059997558594</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4.511484278574375</v>
+        <v>4.212495193045457</v>
       </c>
       <c r="V32" t="n">
-        <v>83.92886657714844</v>
+        <v>83.92026657104492</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>14.1323656831181</v>
+        <v>13.47676461002911</v>
       </c>
       <c r="Y32" t="n">
-        <v>86.05864990234375</v>
+        <v>85.99859989166259</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>11.30781278143032</v>
+        <v>10.73436483489305</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2513962610080324</v>
+        <v>0.2445419254701489</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9740,13 +9738,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>41.83</v>
+        <v>41.59</v>
       </c>
       <c r="CA32" t="n">
         <v>0.04</v>
       </c>
       <c r="CB32" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC32" t="n">
         <v>8</v>
@@ -9781,13 +9779,13 @@
         <v>6</v>
       </c>
       <c r="CM32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
@@ -9800,13 +9798,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.29999923706055</v>
+        <v>27.43000030517578</v>
       </c>
       <c r="D33" t="n">
-        <v>27.29999923706055</v>
+        <v>27.43000030517578</v>
       </c>
       <c r="E33" t="n">
-        <v>27.45000076293945</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="F33" t="n">
         <v>26.51000022888184</v>
@@ -9815,67 +9813,67 @@
         <v>27.29000091552734</v>
       </c>
       <c r="H33" t="n">
-        <v>4748600</v>
+        <v>8087500</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01111108285409435</v>
+        <v>0.01592593722873259</v>
       </c>
       <c r="J33" t="n">
-        <v>27.31888898213704</v>
+        <v>27.33333354526096</v>
       </c>
       <c r="K33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.06914536344742137</v>
+        <v>0.353658874995076</v>
       </c>
       <c r="M33" t="n">
-        <v>27.35100002288818</v>
+        <v>27.36400012969971</v>
       </c>
       <c r="N33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.1864677188583852</v>
+        <v>0.2411934481919541</v>
       </c>
       <c r="P33" t="n">
-        <v>26.25961545797495</v>
+        <v>26.2646154990563</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>3.961915515292275</v>
+        <v>4.437090678755045</v>
       </c>
       <c r="S33" t="n">
-        <v>26.19920001983643</v>
+        <v>26.20540004730224</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4.201652021400134</v>
+        <v>4.673083622700141</v>
       </c>
       <c r="V33" t="n">
-        <v>25.13646663665772</v>
+        <v>25.10066664377848</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>8.607146866249085</v>
+        <v>9.279967319014034</v>
       </c>
       <c r="Y33" t="n">
-        <v>24.02</v>
+        <v>23.99505001068115</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>13.65528408434866</v>
+        <v>14.31524540672179</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2543712173211172</v>
+        <v>0.2872223248309069</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10027,13 +10025,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>40.75</v>
+        <v>40.94</v>
       </c>
       <c r="CA33" t="n">
         <v>0.35</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CC33" t="n">
         <v>10</v>
@@ -10064,13 +10062,13 @@
         <v>6</v>
       </c>
       <c r="CM33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
@@ -10083,10 +10081,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>52.4900016784668</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="D34" t="n">
-        <v>52.4900016784668</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="E34" t="n">
         <v>52.70000076293945</v>
@@ -10098,67 +10096,67 @@
         <v>52.5</v>
       </c>
       <c r="H34" t="n">
-        <v>3225800</v>
+        <v>4910000</v>
       </c>
       <c r="I34" t="n">
-        <v>0.005363007065775083</v>
+        <v>-0.0001915020438331139</v>
       </c>
       <c r="J34" t="n">
-        <v>51.59777789645725</v>
+        <v>51.56555557250977</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.729190322498002</v>
+        <v>1.230366246200047</v>
       </c>
       <c r="M34" t="n">
-        <v>51.575</v>
+        <v>51.54599990844726</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.774118620391263</v>
+        <v>1.268771302630241</v>
       </c>
       <c r="P34" t="n">
-        <v>48.12076906057504</v>
+        <v>48.10961517920861</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>9.079723169826542</v>
+        <v>8.502220540518007</v>
       </c>
       <c r="S34" t="n">
-        <v>48.80719985961914</v>
+        <v>48.80139984130859</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>7.545611773345434</v>
+        <v>6.964146382444686</v>
       </c>
       <c r="V34" t="n">
-        <v>50.30033330281576</v>
+        <v>50.29839996337891</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>4.35318860109514</v>
+        <v>3.780638749831126</v>
       </c>
       <c r="Y34" t="n">
-        <v>49.92934995651245</v>
+        <v>49.92789995193481</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.128550089645918</v>
+        <v>4.550763827823671</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3100844329913451</v>
+        <v>0.3099236631506216</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10310,13 +10308,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>13.89</v>
+        <v>13.81</v>
       </c>
       <c r="CA34" t="n">
         <v>0.26</v>
       </c>
       <c r="CB34" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CC34" t="n">
         <v>5</v>
@@ -10344,16 +10342,16 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
+        <v>7</v>
+      </c>
+      <c r="CM34" t="n">
         <v>8</v>
       </c>
-      <c r="CM34" t="n">
-        <v>9</v>
-      </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -10366,10 +10364,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.4900016784668</v>
+        <v>39.45000076293945</v>
       </c>
       <c r="D35" t="n">
-        <v>39.4900016784668</v>
+        <v>39.45000076293945</v>
       </c>
       <c r="E35" t="n">
         <v>39.90000152587891</v>
@@ -10381,67 +10379,67 @@
         <v>39.77000045776367</v>
       </c>
       <c r="H35" t="n">
-        <v>3000700</v>
+        <v>4922400</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.001769456329480334</v>
+        <v>-0.002780601782936931</v>
       </c>
       <c r="J35" t="n">
-        <v>39.4488894144694</v>
+        <v>39.4444448682997</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1042165308266415</v>
+        <v>0.01408536654098146</v>
       </c>
       <c r="M35" t="n">
-        <v>39.39600028991699</v>
+        <v>39.39200019836426</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2386064266881042</v>
+        <v>0.1472394503531805</v>
       </c>
       <c r="P35" t="n">
-        <v>37.28423118591309</v>
+        <v>37.28269268916203</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>5.916094880849001</v>
+        <v>5.813174739944279</v>
       </c>
       <c r="S35" t="n">
-        <v>38.07640022277832</v>
+        <v>38.11320022583008</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>3.71253965032867</v>
+        <v>3.507447627563427</v>
       </c>
       <c r="V35" t="n">
-        <v>39.75266677856445</v>
+        <v>39.78313344319661</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.6607483758530927</v>
+        <v>-0.8373716482961646</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.65640007019043</v>
+        <v>39.67085006713867</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.4196003455409794</v>
+        <v>-0.5567042395750432</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2543171577676074</v>
+        <v>0.2658809074456946</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10589,13 +10587,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>32.11</v>
+        <v>32.07</v>
       </c>
       <c r="CA35" t="n">
         <v>0.92</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CC35" t="n">
         <v>8</v>
@@ -10645,10 +10643,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21.54000091552734</v>
+        <v>21.5</v>
       </c>
       <c r="D36" t="n">
-        <v>21.54000091552734</v>
+        <v>21.5</v>
       </c>
       <c r="E36" t="n">
         <v>21.60000038146973</v>
@@ -10660,67 +10658,67 @@
         <v>21.48999977111816</v>
       </c>
       <c r="H36" t="n">
-        <v>1778200</v>
+        <v>2632400</v>
       </c>
       <c r="I36" t="n">
-        <v>0.008899322279287913</v>
+        <v>0.007025743131155338</v>
       </c>
       <c r="J36" t="n">
-        <v>20.98777792188856</v>
+        <v>20.98333337571886</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>2.631164650655345</v>
+        <v>2.462271437192199</v>
       </c>
       <c r="M36" t="n">
-        <v>20.89900016784668</v>
+        <v>20.89500007629395</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>3.067135951636816</v>
+        <v>2.895429152893113</v>
       </c>
       <c r="P36" t="n">
-        <v>19.50423071934627</v>
+        <v>19.50269222259521</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>10.43758262232713</v>
+        <v>10.24119006036903</v>
       </c>
       <c r="S36" t="n">
-        <v>18.28479995727539</v>
+        <v>18.2157999420166</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>17.80277042055761</v>
+        <v>18.02940342141141</v>
       </c>
       <c r="V36" t="n">
-        <v>16.75053329467773</v>
+        <v>16.73746662139893</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>28.59292618684207</v>
+        <v>28.45432637046848</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.47264999866486</v>
+        <v>16.45594999790192</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>30.76220837128943</v>
+        <v>30.65183111726265</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.3708056513767023</v>
+        <v>0.3745929747139501</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10872,7 +10870,7 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>18.57</v>
+        <v>18.53</v>
       </c>
       <c r="CA36" t="n">
         <v>0.27</v>
@@ -10928,10 +10926,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26.22999954223633</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="D37" t="n">
-        <v>26.22999954223633</v>
+        <v>26.1200008392334</v>
       </c>
       <c r="E37" t="n">
         <v>26.28000068664551</v>
@@ -10943,67 +10941,67 @@
         <v>25.80999946594238</v>
       </c>
       <c r="H37" t="n">
-        <v>3047500</v>
+        <v>5522400</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0246093418507376</v>
+        <v>0.02031251757871333</v>
       </c>
       <c r="J37" t="n">
-        <v>25.70000012715657</v>
+        <v>25.68777804904514</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2.062254523180784</v>
+        <v>1.682600921586231</v>
       </c>
       <c r="M37" t="n">
-        <v>25.64400005340576</v>
+        <v>25.63300018310547</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>2.285132926260232</v>
+        <v>1.89989721315926</v>
       </c>
       <c r="P37" t="n">
-        <v>24.44346149151142</v>
+        <v>24.43923077216515</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>7.308858654676749</v>
+        <v>6.877344392453397</v>
       </c>
       <c r="S37" t="n">
-        <v>24.42179992675781</v>
+        <v>24.35739994049072</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>7.404039099908257</v>
+        <v>7.236408249850188</v>
       </c>
       <c r="V37" t="n">
-        <v>22.45279998779297</v>
+        <v>22.43139999389648</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>16.82284417309614</v>
+        <v>16.44391721578043</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.12574999809265</v>
+        <v>22.09460000038147</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>18.54965162535726</v>
+        <v>18.21893511890883</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.4044542639354456</v>
+        <v>0.398185265709632</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11155,13 +11153,13 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>31.6</v>
+        <v>31.47</v>
       </c>
       <c r="CA37" t="n">
         <v>0.16</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="CC37" t="n">
         <v>1</v>
@@ -11176,7 +11174,7 @@
         <v>3</v>
       </c>
       <c r="CG37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CH37" t="n">
         <v>6</v>
@@ -11189,16 +11187,16 @@
         <v>0</v>
       </c>
       <c r="CL37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -11211,13 +11209,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11.72999954223633</v>
+        <v>11.6899995803833</v>
       </c>
       <c r="D38" t="n">
-        <v>11.72999954223633</v>
+        <v>11.6899995803833</v>
       </c>
       <c r="E38" t="n">
-        <v>11.75</v>
+        <v>11.77999973297119</v>
       </c>
       <c r="F38" t="n">
         <v>11.35000038146973</v>
@@ -11226,67 +11224,67 @@
         <v>11.47999954223633</v>
       </c>
       <c r="H38" t="n">
-        <v>13700000</v>
+        <v>17106700</v>
       </c>
       <c r="I38" t="n">
-        <v>0.02445412555768089</v>
+        <v>0.02096067904944077</v>
       </c>
       <c r="J38" t="n">
-        <v>11.41555553012424</v>
+        <v>11.41111108991835</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>2.754522206845811</v>
+        <v>2.444008197513289</v>
       </c>
       <c r="M38" t="n">
-        <v>11.38400001525879</v>
+        <v>11.38000001907349</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>3.039349319340934</v>
+        <v>2.724073469158509</v>
       </c>
       <c r="P38" t="n">
-        <v>10.82115382414598</v>
+        <v>10.81961536407471</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>8.398787530978275</v>
+        <v>8.0445023877522</v>
       </c>
       <c r="S38" t="n">
-        <v>10.75539999008179</v>
+        <v>10.72539999008179</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>9.061490535482438</v>
+        <v>8.993600156577083</v>
       </c>
       <c r="V38" t="n">
-        <v>9.909399995803833</v>
+        <v>9.900933332443238</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>18.37244986783694</v>
+        <v>18.06967270527594</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.75300453901291</v>
+        <v>9.738568074703217</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>20.27062527568051</v>
+        <v>20.03817697541282</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3997725893759658</v>
+        <v>0.3876218720345502</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11438,7 +11436,7 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>27.28</v>
+        <v>27.19</v>
       </c>
       <c r="CA38" t="n">
         <v>0.53</v>
@@ -11498,10 +11496,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.409999847412109</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="D39" t="n">
-        <v>6.409999847412109</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E39" t="n">
         <v>6.599999904632568</v>
@@ -11513,67 +11511,67 @@
         <v>6.570000171661377</v>
       </c>
       <c r="H39" t="n">
-        <v>2744600</v>
+        <v>8038800</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.01232664507355929</v>
+        <v>-0.004622455166284678</v>
       </c>
       <c r="J39" t="n">
-        <v>6.861111111111111</v>
+        <v>6.866666687859429</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.574901009378157</v>
+        <v>-5.922329831903175</v>
       </c>
       <c r="M39" t="n">
-        <v>6.907999992370605</v>
+        <v>6.913000011444092</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-7.20903511158804</v>
+        <v>-6.552871004588498</v>
       </c>
       <c r="P39" t="n">
-        <v>6.793461542863112</v>
+        <v>6.795384627122146</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-5.644570047707854</v>
+        <v>-4.93547617064332</v>
       </c>
       <c r="S39" t="n">
-        <v>8.745200004577637</v>
+        <v>8.739400005340576</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-26.70265009311596</v>
+        <v>-26.08188166007598</v>
       </c>
       <c r="V39" t="n">
-        <v>10.28599998474121</v>
+        <v>10.29319998423258</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-37.68228799415675</v>
+        <v>-37.24011922392857</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.21134999275207</v>
+        <v>11.23929999351502</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-42.8257983957681</v>
+        <v>-42.52311049732332</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.112085518248382</v>
+        <v>1.133430021984146</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11725,10 +11723,10 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>-7.54</v>
+        <v>-7.6</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CB39" t="n">
         <v>0.07000000000000001</v>
@@ -11785,10 +11783,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.42000007629395</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="D40" t="n">
-        <v>23.42000007629395</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="E40" t="n">
         <v>23.86000061035156</v>
@@ -11800,67 +11798,67 @@
         <v>23.56999969482422</v>
       </c>
       <c r="H40" t="n">
-        <v>656900</v>
+        <v>1332600</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.005520134393975806</v>
+        <v>-0.0008491953742217895</v>
       </c>
       <c r="J40" t="n">
-        <v>23.14555549621582</v>
+        <v>23.15777778625488</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.185733391116905</v>
+        <v>1.607334278039212</v>
       </c>
       <c r="M40" t="n">
-        <v>23.10399990081787</v>
+        <v>23.11499996185303</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.367729297232585</v>
+        <v>1.79537410978742</v>
       </c>
       <c r="P40" t="n">
-        <v>22.08076917208158</v>
+        <v>22.08499996478741</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>6.065146072473133</v>
+        <v>6.542905701435471</v>
       </c>
       <c r="S40" t="n">
-        <v>21.59140003204346</v>
+        <v>21.56300006866455</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>8.469112894655709</v>
+        <v>9.122110150337623</v>
       </c>
       <c r="V40" t="n">
-        <v>22.0682666905721</v>
+        <v>22.08386669158936</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>6.12523586321949</v>
+        <v>6.548373141588068</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.61440001487732</v>
+        <v>22.63685002326965</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.562332234711719</v>
+        <v>3.945560722705401</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2617711014856148</v>
+        <v>0.2597023581100836</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12008,7 +12006,7 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="CA40" t="n">
         <v>0.38</v>
@@ -12042,16 +12040,16 @@
         <v>0</v>
       </c>
       <c r="CL40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
       </c>
       <c r="CO40" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41">
@@ -12064,10 +12062,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.77000045776367</v>
+        <v>25.71999931335449</v>
       </c>
       <c r="D41" t="n">
-        <v>25.77000045776367</v>
+        <v>25.71999931335449</v>
       </c>
       <c r="E41" t="n">
         <v>26.10000038146973</v>
@@ -12079,67 +12077,67 @@
         <v>26.04000091552734</v>
       </c>
       <c r="H41" t="n">
-        <v>610400</v>
+        <v>878400</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.003480284240668707</v>
+        <v>-0.005413816461436127</v>
       </c>
       <c r="J41" t="n">
-        <v>26.07666693793403</v>
+        <v>26.0711112552219</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.176018702467858</v>
+        <v>-1.346747127232941</v>
       </c>
       <c r="M41" t="n">
-        <v>26.12600021362305</v>
+        <v>26.12100009918213</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-1.362626322240266</v>
+        <v>-1.535166281172339</v>
       </c>
       <c r="P41" t="n">
-        <v>24.82192310920129</v>
+        <v>24.81999998826247</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>3.819516096280796</v>
+        <v>3.626105259942132</v>
       </c>
       <c r="S41" t="n">
-        <v>24.96460006713867</v>
+        <v>24.96360004425049</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>3.226169810287335</v>
+        <v>3.030008763812956</v>
       </c>
       <c r="V41" t="n">
-        <v>26.3435999806722</v>
+        <v>26.34326663970947</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-2.177377136493744</v>
+        <v>-2.365945480031987</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.4208499622345</v>
+        <v>26.42059995651245</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-2.46339351459601</v>
+        <v>-2.651721173293291</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3123950299784418</v>
+        <v>0.3126974897027314</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12287,7 +12285,7 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>10.74</v>
+        <v>10.72</v>
       </c>
       <c r="CA41" t="n">
         <v>0.04</v>
@@ -12321,16 +12319,16 @@
         <v>0</v>
       </c>
       <c r="CL41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN41" t="n">
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
@@ -12343,10 +12341,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.35000038146973</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="D42" t="n">
-        <v>27.35000038146973</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="E42" t="n">
         <v>27.51000022888184</v>
@@ -12358,67 +12356,67 @@
         <v>27.42000007629395</v>
       </c>
       <c r="H42" t="n">
-        <v>968300</v>
+        <v>2063100</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.002559403796997595</v>
       </c>
       <c r="J42" t="n">
-        <v>27.60666677686903</v>
+        <v>27.61444452073839</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.9297261327266129</v>
+        <v>-0.7041403432845282</v>
       </c>
       <c r="M42" t="n">
-        <v>27.61000003814697</v>
+        <v>27.61700000762939</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.9416865495038746</v>
+        <v>-0.7133284979578708</v>
       </c>
       <c r="P42" t="n">
-        <v>26.72653836470384</v>
+        <v>26.72923066065862</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.332745109966271</v>
+        <v>2.584322101915332</v>
       </c>
       <c r="S42" t="n">
-        <v>27.08540004730225</v>
+        <v>27.14520004272461</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0.9769113016805296</v>
+        <v>1.012333794323929</v>
       </c>
       <c r="V42" t="n">
-        <v>28.15133336385091</v>
+        <v>28.17580001831055</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.846518749304348</v>
+        <v>-2.682443591754027</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.9795500087738</v>
+        <v>27.98820000648498</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-2.250034854408533</v>
+        <v>-2.030141023929315</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1761399536090522</v>
+        <v>0.1898242798043679</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12566,7 +12564,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>7.68</v>
+        <v>7.7</v>
       </c>
       <c r="CA42" t="n">
         <v>0.83</v>
@@ -12622,13 +12620,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14.23999977111816</v>
+        <v>14.25</v>
       </c>
       <c r="D43" t="n">
-        <v>14.23999977111816</v>
+        <v>14.25</v>
       </c>
       <c r="E43" t="n">
-        <v>14.27000045776367</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="F43" t="n">
         <v>13.92000007629395</v>
@@ -12637,67 +12635,67 @@
         <v>14.22000026702881</v>
       </c>
       <c r="H43" t="n">
-        <v>9682400</v>
+        <v>14736200</v>
       </c>
       <c r="I43" t="n">
-        <v>0.002816898759880893</v>
+        <v>0.003521140239892029</v>
       </c>
       <c r="J43" t="n">
-        <v>14.11777761247423</v>
+        <v>14.11888874901666</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8657322844917236</v>
+        <v>0.9286230192335536</v>
       </c>
       <c r="M43" t="n">
-        <v>14.07999982833862</v>
+        <v>14.08099985122681</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.136363243822709</v>
+        <v>1.200199918747029</v>
       </c>
       <c r="P43" t="n">
-        <v>13.23384600419265</v>
+        <v>13.23423062838041</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>7.60288253775022</v>
+        <v>7.675318650117098</v>
       </c>
       <c r="S43" t="n">
-        <v>13.42919988632202</v>
+        <v>13.4335998916626</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>6.037588923089628</v>
+        <v>6.077299569150424</v>
       </c>
       <c r="V43" t="n">
-        <v>13.54679996490479</v>
+        <v>13.55686663309733</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>5.117074202093681</v>
+        <v>5.112784433612958</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.26902150630951</v>
+        <v>13.26278523445129</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>7.317632760991072</v>
+        <v>7.443495073601332</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2422210023703982</v>
+        <v>0.2511269024870494</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12849,7 +12847,7 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>9.43</v>
+        <v>9.44</v>
       </c>
       <c r="CA43" t="n">
         <v>0.03</v>
@@ -12909,10 +12907,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>42.90999984741211</v>
+        <v>42.86000061035156</v>
       </c>
       <c r="D44" t="n">
-        <v>42.90999984741211</v>
+        <v>42.86000061035156</v>
       </c>
       <c r="E44" t="n">
         <v>43.08000183105469</v>
@@ -12924,88 +12922,88 @@
         <v>42.79000091552734</v>
       </c>
       <c r="H44" t="n">
-        <v>12279400</v>
+        <v>17991800</v>
       </c>
       <c r="I44" t="n">
-        <v>0.006804338873654725</v>
+        <v>0.005631198603509358</v>
       </c>
       <c r="J44" t="n">
-        <v>42.39666578504774</v>
+        <v>42.39111031426324</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.210788756283295</v>
+        <v>1.106105248511406</v>
       </c>
       <c r="M44" t="n">
-        <v>42.3489990234375</v>
+        <v>42.34399909973145</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.324708580866648</v>
+        <v>1.21859418475046</v>
       </c>
       <c r="P44" t="n">
-        <v>40.26923018235426</v>
+        <v>40.26730713477502</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>6.55778531921133</v>
+        <v>6.438705888374355</v>
       </c>
       <c r="S44" t="n">
-        <v>41.274599609375</v>
+        <v>41.30299964904785</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>3.962243737103743</v>
+        <v>3.769704318169559</v>
       </c>
       <c r="V44" t="n">
-        <v>42.31519983927409</v>
+        <v>42.36819984436035</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.405641496193455</v>
+        <v>1.160778054762389</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.05012891769409</v>
+        <v>42.04607990264893</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.044871090409902</v>
+        <v>1.93578262132199</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2581177737445653</v>
+        <v>0.2674880238448354</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
       </c>
       <c r="AD44" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AE44" t="n">
         <v>42.2</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AF44" t="n">
         <v>42.3</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AG44" t="n">
         <v>42.9</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AH44" t="n">
         <v>43.5</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AI44" t="n">
         <v>43.6</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>44</v>
       </c>
       <c r="AJ44" t="n">
         <v>3</v>
@@ -13152,7 +13150,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ44" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="CA44" t="n">
         <v>0</v>
@@ -13212,13 +13210,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19.64999961853027</v>
+        <v>19.65999984741211</v>
       </c>
       <c r="D45" t="n">
-        <v>19.64999961853027</v>
+        <v>19.65999984741211</v>
       </c>
       <c r="E45" t="n">
-        <v>19.65999984741211</v>
+        <v>19.80999946594238</v>
       </c>
       <c r="F45" t="n">
         <v>19.19000053405762</v>
@@ -13227,67 +13225,67 @@
         <v>19.39999961853027</v>
       </c>
       <c r="H45" t="n">
-        <v>1474000</v>
+        <v>3298900</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01288659819153848</v>
+        <v>0.01340207391723314</v>
       </c>
       <c r="J45" t="n">
-        <v>19.48999998304579</v>
+        <v>19.49111111958821</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8209319426560515</v>
+        <v>0.8664910214080319</v>
       </c>
       <c r="M45" t="n">
-        <v>19.49699993133545</v>
+        <v>19.49799995422363</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.7847345116359407</v>
+        <v>0.8308539007529521</v>
       </c>
       <c r="P45" t="n">
-        <v>18.78192300062913</v>
+        <v>18.78230762481689</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.621872945981433</v>
+        <v>4.672973311519655</v>
       </c>
       <c r="S45" t="n">
-        <v>18.30379997253418</v>
+        <v>18.30399997711181</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>7.354755012708498</v>
+        <v>7.40821608389369</v>
       </c>
       <c r="V45" t="n">
-        <v>18.21926666259766</v>
+        <v>18.2193333307902</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>7.852856991603114</v>
+        <v>7.907350342985477</v>
       </c>
       <c r="Y45" t="n">
-        <v>18.34667272567749</v>
+        <v>18.3467227268219</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>7.103886968173166</v>
+        <v>7.158101968098489</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.1944346921429701</v>
+        <v>0.1946949053955537</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13302,23 +13300,21 @@
         <v>19.1</v>
       </c>
       <c r="AG45" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AH45" t="n">
         <v>23.5</v>
       </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>Foguete</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ45" t="n">
         <v>1</v>
       </c>
       <c r="AK45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -13439,7 +13435,7 @@
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
-        <v>32.75</v>
+        <v>32.77</v>
       </c>
       <c r="CA45" t="n">
         <v>0.2</v>
@@ -13499,10 +13495,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11.23999977111816</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="D46" t="n">
-        <v>11.23999977111816</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="E46" t="n">
         <v>11.55000019073486</v>
@@ -13514,67 +13510,67 @@
         <v>11.5</v>
       </c>
       <c r="H46" t="n">
-        <v>17521000</v>
+        <v>27516200</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.02260871555494226</v>
+        <v>-0.02434780286706018</v>
       </c>
       <c r="J46" t="n">
-        <v>11.35444439782037</v>
+        <v>11.35222223069933</v>
       </c>
       <c r="K46" t="n">
         <v>-1</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.007928020891723</v>
+        <v>-1.164723179158321</v>
       </c>
       <c r="M46" t="n">
-        <v>11.35899991989136</v>
+        <v>11.35699996948242</v>
       </c>
       <c r="N46" t="n">
         <v>-1</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.047628749119058</v>
+        <v>-1.206301865120604</v>
       </c>
       <c r="P46" t="n">
-        <v>11.11884612303514</v>
+        <v>11.11807691133939</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.089624289628673</v>
+        <v>0.9167354795455928</v>
       </c>
       <c r="S46" t="n">
-        <v>12.27099998474121</v>
+        <v>12.30239999771118</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-8.401924984965193</v>
+        <v>-8.798281074292417</v>
       </c>
       <c r="V46" t="n">
-        <v>13.98640004475912</v>
+        <v>14.00593338012695</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-19.63621993402128</v>
+        <v>-19.89109213564524</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.06395003795624</v>
+        <v>14.08050004005432</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-20.07935366107464</v>
+        <v>-20.31532804153507</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.4138143046258857</v>
+        <v>0.4177468147614161</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13726,7 +13722,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="CA46" t="n">
         <v>-0.13</v>
@@ -13786,103 +13782,103 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.75</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="D47" t="n">
-        <v>16.75</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="E47" t="n">
         <v>17.21999931335449</v>
       </c>
       <c r="F47" t="n">
-        <v>16.64999961853027</v>
+        <v>16.54000091552734</v>
       </c>
       <c r="G47" t="n">
         <v>17.21999931335449</v>
       </c>
       <c r="H47" t="n">
-        <v>2224600</v>
+        <v>3495800</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.01528513964628719</v>
+        <v>-0.02410345925310198</v>
       </c>
       <c r="J47" t="n">
-        <v>17.1966667175293</v>
+        <v>17.18000009324815</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.597402885490538</v>
+        <v>-3.37601693032802</v>
       </c>
       <c r="M47" t="n">
-        <v>17.31400012969971</v>
+        <v>17.29900016784668</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-3.25748022106252</v>
+        <v>-4.040694719895831</v>
       </c>
       <c r="P47" t="n">
-        <v>17.58153849381667</v>
+        <v>17.57576927771935</v>
       </c>
       <c r="Q47" t="n">
         <v>-1</v>
       </c>
       <c r="R47" t="n">
-        <v>-4.729611655482351</v>
+        <v>-5.551784851241758</v>
       </c>
       <c r="S47" t="n">
-        <v>16.84160001754761</v>
+        <v>16.82740003585815</v>
       </c>
       <c r="T47" t="n">
         <v>-1</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.5438914203648454</v>
+        <v>-1.351365355930526</v>
       </c>
       <c r="V47" t="n">
-        <v>17.54020003636678</v>
+        <v>17.55746671040853</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-4.5050799576312</v>
+        <v>-5.45332845980105</v>
       </c>
       <c r="Y47" t="n">
-        <v>17.99800006389618</v>
+        <v>18.01780006408691</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-6.934104119710806</v>
+        <v>-7.868883424026585</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.45035308822742</v>
+        <v>0.4524073291200647</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>15.7</v>
+        <v>15</v>
       </c>
       <c r="AE47" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AF47" t="n">
         <v>15.9</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
         <v>16.7</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>16.8</v>
       </c>
-      <c r="AH47" t="n">
-        <v>17.1</v>
-      </c>
       <c r="AI47" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="AJ47" t="n">
         <v>2</v>
@@ -14009,13 +14005,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>62.04</v>
+        <v>61.48</v>
       </c>
       <c r="CA47" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CC47" t="n">
         <v>7</v>
@@ -14069,10 +14065,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.789999961853027</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="D48" t="n">
-        <v>5.789999961853027</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="E48" t="n">
         <v>6.050000190734863</v>
@@ -14084,67 +14080,67 @@
         <v>5.980000019073486</v>
       </c>
       <c r="H48" t="n">
-        <v>17861100</v>
+        <v>25241200</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.02525254106438879</v>
+        <v>-0.01010100037063255</v>
       </c>
       <c r="J48" t="n">
-        <v>5.751111189524333</v>
+        <v>5.761111206478542</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6761958002051914</v>
+        <v>2.063645427095409</v>
       </c>
       <c r="M48" t="n">
-        <v>5.732000064849854</v>
+        <v>5.741000080108643</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1.011861415683583</v>
+        <v>2.421181543157975</v>
       </c>
       <c r="P48" t="n">
-        <v>4.913461565971375</v>
+        <v>4.916923110301678</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>17.83952889653598</v>
+        <v>19.58698524533467</v>
       </c>
       <c r="S48" t="n">
-        <v>4.873000044822692</v>
+        <v>4.87860004901886</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>18.81797473005565</v>
+        <v>20.52638165375846</v>
       </c>
       <c r="V48" t="n">
-        <v>6.688666656812032</v>
+        <v>6.731133325894674</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-13.43566275714702</v>
+        <v>-12.64472370766221</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.357247549295425</v>
+        <v>7.384240401983261</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-21.30209126363414</v>
+        <v>-20.37095497511611</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.8516094962170774</v>
+        <v>0.8557653861071457</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14296,10 +14292,10 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>32.17</v>
+        <v>32.67</v>
       </c>
       <c r="CA48" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="CB48" t="n">
         <v>0.4</v>
@@ -14337,13 +14333,13 @@
         <v>10</v>
       </c>
       <c r="CM48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CN48" t="n">
         <v>-1</v>
       </c>
       <c r="CO48" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49">
@@ -14356,10 +14352,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.06999969482422</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="D49" t="n">
-        <v>16.06999969482422</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="E49" t="n">
         <v>16.32999992370605</v>
@@ -14371,67 +14367,67 @@
         <v>16.32999992370605</v>
       </c>
       <c r="H49" t="n">
-        <v>3637100</v>
+        <v>5371100</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.009858277999067799</v>
+        <v>-0.00554529606446863</v>
       </c>
       <c r="J49" t="n">
-        <v>16.41000005933974</v>
+        <v>16.41777780320909</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.071909587361684</v>
+        <v>-1.691936734010117</v>
       </c>
       <c r="M49" t="n">
-        <v>16.41499996185303</v>
+        <v>16.42199993133545</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-2.101737848495632</v>
+        <v>-1.717211928304272</v>
       </c>
       <c r="P49" t="n">
-        <v>15.3007692190317</v>
+        <v>15.30346151498648</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>5.027397412384467</v>
+        <v>5.466331090144202</v>
       </c>
       <c r="S49" t="n">
-        <v>15.00399997711182</v>
+        <v>15.00719997406006</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>7.104770190206318</v>
+        <v>7.548372897985112</v>
       </c>
       <c r="V49" t="n">
-        <v>15.26266668955485</v>
+        <v>15.28060002009074</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>5.289593369826223</v>
+        <v>5.624120573981195</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.41560001373291</v>
+        <v>15.42485001087189</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.245048395835003</v>
+        <v>4.636345755534036</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3060324362376945</v>
+        <v>0.3100689116167886</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14581,13 +14577,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>9.68</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="CA49" t="n">
         <v>0.95</v>
       </c>
       <c r="CB49" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CC49" t="n">
         <v>5</v>
@@ -14619,7 +14615,7 @@
         <v>0</v>
       </c>
       <c r="CL49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM49" t="n">
         <v>3</v>
@@ -14628,7 +14624,7 @@
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -14641,10 +14637,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5.449999809265137</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="D50" t="n">
-        <v>5.449999809265137</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="E50" t="n">
         <v>5.829999923706055</v>
@@ -14656,67 +14652,67 @@
         <v>5.78000020980835</v>
       </c>
       <c r="H50" t="n">
-        <v>14159300</v>
+        <v>18557000</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.04553419039314266</v>
+        <v>-0.0490368139996048</v>
       </c>
       <c r="J50" t="n">
-        <v>5.651111072964138</v>
+        <v>5.648888852861193</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-3.558791556250793</v>
+        <v>-3.874904078024144</v>
       </c>
       <c r="M50" t="n">
-        <v>5.646999979019165</v>
+        <v>5.644999980926514</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-3.48858102507459</v>
+        <v>-3.808682963938693</v>
       </c>
       <c r="P50" t="n">
-        <v>5.317307710647583</v>
+        <v>5.316538480611948</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>2.495475263766396</v>
+        <v>2.134120690378514</v>
       </c>
       <c r="S50" t="n">
-        <v>4.996400022506714</v>
+        <v>5.005200023651123</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>9.078532237513874</v>
+        <v>8.487169397430453</v>
       </c>
       <c r="V50" t="n">
-        <v>6.416533339818319</v>
+        <v>6.450400002797445</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-15.06317320219128</v>
+        <v>-15.81917670247255</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.870500013828278</v>
+        <v>6.892950015068054</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-20.67535407472667</v>
+        <v>-21.2238618230425</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.6128981647061601</v>
+        <v>0.6220813067491711</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14864,10 +14860,10 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>-4.04</v>
+        <v>-4.02</v>
       </c>
       <c r="CA50" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CB50" t="n">
         <v>0.59</v>
@@ -14902,7 +14898,7 @@
         <v>0</v>
       </c>
       <c r="CL50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM50" t="n">
         <v>2</v>
@@ -14911,7 +14907,7 @@
         <v>-1</v>
       </c>
       <c r="CO50" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
@@ -14924,10 +14920,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>29.67000007629395</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="D51" t="n">
-        <v>29.67000007629395</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="E51" t="n">
         <v>30.3799991607666</v>
@@ -14939,67 +14935,67 @@
         <v>30.20999908447266</v>
       </c>
       <c r="H51" t="n">
-        <v>2053200</v>
+        <v>2960300</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.01297403182226609</v>
+        <v>-0.01197600497002016</v>
       </c>
       <c r="J51" t="n">
-        <v>30.06666670905219</v>
+        <v>30.07000011867947</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.319290350994653</v>
+        <v>-1.230460107348565</v>
       </c>
       <c r="M51" t="n">
-        <v>30.09500007629395</v>
+        <v>30.0980001449585</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.412194713150296</v>
+        <v>-1.322344940202648</v>
       </c>
       <c r="P51" t="n">
-        <v>28.36538468874418</v>
+        <v>28.36653856130747</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>4.599322032348315</v>
+        <v>4.700828050451154</v>
       </c>
       <c r="S51" t="n">
-        <v>28.48620006561279</v>
+        <v>28.4868000793457</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>4.155696470411936</v>
+        <v>4.258816996695181</v>
       </c>
       <c r="V51" t="n">
-        <v>30.26040000915527</v>
+        <v>30.26060001373291</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-1.951064535441376</v>
+        <v>-1.852571497389499</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.10990003585815</v>
+        <v>30.11005003929138</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-1.460981135906553</v>
+        <v>-1.361835253733697</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.2589350047305436</v>
+        <v>0.258474785101611</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15149,7 +15145,7 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>12.47</v>
+        <v>12.48</v>
       </c>
       <c r="CA51" t="n">
         <v>0.3</v>
@@ -15187,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="CL51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM51" t="n">
         <v>4</v>
@@ -15196,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
@@ -15224,7 +15220,7 @@
         <v>7.960000038146973</v>
       </c>
       <c r="H52" t="n">
-        <v>1906200</v>
+        <v>3712200</v>
       </c>
       <c r="I52" t="n">
         <v>-0.003787905242342848</v>
@@ -15257,34 +15253,34 @@
         <v>-5.548138161753499</v>
       </c>
       <c r="S52" t="n">
-        <v>8.399800014495849</v>
+        <v>8.408200016021729</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.069193875216934</v>
+        <v>-6.163033093274525</v>
       </c>
       <c r="V52" t="n">
-        <v>9.088266642888387</v>
+        <v>9.097599973678589</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-13.18476694717624</v>
+        <v>-13.27383167744079</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.813849971294403</v>
+        <v>8.813449971675873</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-10.48179975626622</v>
+        <v>-10.47773696064543</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4422346642140232</v>
+        <v>0.4367655293926458</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15496,13 +15492,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.2400016784668</v>
+        <v>54.06999969482422</v>
       </c>
       <c r="D53" t="n">
-        <v>54.2400016784668</v>
+        <v>54.06999969482422</v>
       </c>
       <c r="E53" t="n">
-        <v>54.31999969482422</v>
+        <v>54.41999816894531</v>
       </c>
       <c r="F53" t="n">
         <v>53.11000061035156</v>
@@ -15511,67 +15507,67 @@
         <v>53.29000091552734</v>
       </c>
       <c r="H53" t="n">
-        <v>3319600</v>
+        <v>4889700</v>
       </c>
       <c r="I53" t="n">
-        <v>0.007616567591784529</v>
+        <v>0.00445844056485023</v>
       </c>
       <c r="J53" t="n">
-        <v>54.07333331637912</v>
+        <v>54.0544442070855</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3082265358277663</v>
+        <v>0.02877744460589059</v>
       </c>
       <c r="M53" t="n">
-        <v>53.92400016784668</v>
+        <v>53.90699996948242</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.5860127394787399</v>
+        <v>0.3023720953384068</v>
       </c>
       <c r="P53" t="n">
-        <v>50.44653848501352</v>
+        <v>50.43999994718111</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>7.519769061221567</v>
+        <v>7.196668817296402</v>
       </c>
       <c r="S53" t="n">
-        <v>48.63559982299805</v>
+        <v>48.57119979858398</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>11.52325020327729</v>
+        <v>11.32111193267362</v>
       </c>
       <c r="V53" t="n">
-        <v>48.17686663309733</v>
+        <v>48.12673329671224</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>12.58515853997883</v>
+        <v>12.34919968797881</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.82564999580384</v>
+        <v>44.75849999427795</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>21.002153194754</v>
+        <v>20.80386898965933</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3682261364474688</v>
+        <v>0.3639335056604686</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15723,10 +15719,10 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="CB53" t="n">
         <v>1.57</v>
@@ -15779,13 +15775,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>49.04999923706055</v>
+        <v>48.88999938964844</v>
       </c>
       <c r="D54" t="n">
-        <v>49.04999923706055</v>
+        <v>48.88999938964844</v>
       </c>
       <c r="E54" t="n">
-        <v>49.13000106811523</v>
+        <v>49.20000076293945</v>
       </c>
       <c r="F54" t="n">
         <v>47.95999908447266</v>
@@ -15794,67 +15790,67 @@
         <v>48.02999877929688</v>
       </c>
       <c r="H54" t="n">
-        <v>19461700</v>
+        <v>26856700</v>
       </c>
       <c r="I54" t="n">
-        <v>0.008221946529001878</v>
+        <v>0.004933152235192972</v>
       </c>
       <c r="J54" t="n">
-        <v>48.75444412231445</v>
+        <v>48.73666636149088</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.6062116388910297</v>
+        <v>0.3146153391375781</v>
       </c>
       <c r="M54" t="n">
-        <v>48.63499984741211</v>
+        <v>48.6189998626709</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8532936999084176</v>
+        <v>0.5573942856558239</v>
       </c>
       <c r="P54" t="n">
-        <v>45.37846154433031</v>
+        <v>45.37230770404522</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>8.090925888140804</v>
+        <v>7.752948579447269</v>
       </c>
       <c r="S54" t="n">
-        <v>43.53599998474121</v>
+        <v>43.48120002746582</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>12.66537866191639</v>
+        <v>12.43939762188265</v>
       </c>
       <c r="V54" t="n">
-        <v>43.48159996032715</v>
+        <v>43.44799995422363</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>12.80633482165799</v>
+        <v>12.52531633483346</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.81735003471375</v>
+        <v>40.76655003547668</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>20.16948477876495</v>
+        <v>19.92675207272238</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3417461613402756</v>
+        <v>0.3340106001749314</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16006,7 +16002,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="CA54" t="n">
         <v>0.51</v>
@@ -16035,11 +16031,7 @@
       <c r="CI54" t="n">
         <v>30</v>
       </c>
-      <c r="CJ54" t="inlineStr">
-        <is>
-          <t>melhor</t>
-        </is>
-      </c>
+      <c r="CJ54" t="inlineStr"/>
       <c r="CK54" t="n">
         <v>0</v>
       </c>
@@ -16066,10 +16058,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.300000190734863</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="D55" t="n">
-        <v>4.300000190734863</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="E55" t="n">
         <v>4.510000228881836</v>
@@ -16081,67 +16073,67 @@
         <v>4.449999809265137</v>
       </c>
       <c r="H55" t="n">
-        <v>27943500</v>
+        <v>33731600</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.05077262879049993</v>
+        <v>-0.04635762216793737</v>
       </c>
       <c r="J55" t="n">
-        <v>4.48888889948527</v>
+        <v>4.491111119588216</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.207916769160105</v>
+        <v>-3.809991411268574</v>
       </c>
       <c r="M55" t="n">
-        <v>4.496000003814697</v>
+        <v>4.498000001907348</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-4.359426443806388</v>
+        <v>-3.957310586271491</v>
       </c>
       <c r="P55" t="n">
-        <v>4.4092307640956</v>
+        <v>4.409999994131235</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-2.47731586766114</v>
+        <v>-2.040812303619697</v>
       </c>
       <c r="S55" t="n">
-        <v>4.771599988937378</v>
+        <v>4.794999990463257</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-9.883473034116152</v>
+        <v>-9.906148482723754</v>
       </c>
       <c r="V55" t="n">
-        <v>5.734733324050904</v>
+        <v>5.748599990208944</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-25.01830603524163</v>
+        <v>-24.85126502071406</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.804054486751556</v>
+        <v>5.811377213001252</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-25.91385555476565</v>
+        <v>-25.66305690849591</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.3768368733494906</v>
+        <v>0.3920198275035645</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16293,13 +16285,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="CA55" t="n">
         <v>0.29</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CC55" t="n">
         <v>9</v>
@@ -16353,13 +16345,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>62.88000106811523</v>
+        <v>63.20000076293945</v>
       </c>
       <c r="D56" t="n">
-        <v>62.88000106811523</v>
+        <v>63.20000076293945</v>
       </c>
       <c r="E56" t="n">
-        <v>62.95000076293945</v>
+        <v>63.27000045776367</v>
       </c>
       <c r="F56" t="n">
         <v>61.34999847412109</v>
@@ -16368,67 +16360,67 @@
         <v>62.04999923706055</v>
       </c>
       <c r="H56" t="n">
-        <v>7438200</v>
+        <v>8491400</v>
       </c>
       <c r="I56" t="n">
-        <v>0.004793851522574943</v>
+        <v>0.009907301274272307</v>
       </c>
       <c r="J56" t="n">
-        <v>63.12666744656033</v>
+        <v>63.16222296820747</v>
       </c>
       <c r="K56" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.3907482977046321</v>
+        <v>0.05981074280904016</v>
       </c>
       <c r="M56" t="n">
-        <v>62.9640007019043</v>
+        <v>62.99600067138672</v>
       </c>
       <c r="N56" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.1334089842650707</v>
+        <v>0.3238302263295807</v>
       </c>
       <c r="P56" t="n">
-        <v>61.99807739257812</v>
+        <v>62.01038507314829</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>1.422501652676548</v>
+        <v>1.918413646984906</v>
       </c>
       <c r="S56" t="n">
-        <v>60.18640029907227</v>
+        <v>60.09640022277832</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>4.475430920703338</v>
+        <v>5.164370126423604</v>
       </c>
       <c r="V56" t="n">
-        <v>60.99066670735677</v>
+        <v>60.92766670227051</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>3.097743413469798</v>
+        <v>3.729560286253776</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.5754999923706</v>
+        <v>56.46084999084473</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>11.14351808926977</v>
+        <v>11.93597116087961</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3972730802915704</v>
+        <v>0.3474749461347816</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16580,13 +16572,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>21.17</v>
+        <v>21.28</v>
       </c>
       <c r="CA56" t="n">
         <v>0.44</v>
       </c>
       <c r="CB56" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CC56" t="n">
         <v>10</v>
@@ -16617,13 +16609,13 @@
         <v>6</v>
       </c>
       <c r="CM56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57">
@@ -16636,10 +16628,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>49.97999954223633</v>
+        <v>49.59999847412109</v>
       </c>
       <c r="D57" t="n">
-        <v>49.97999954223633</v>
+        <v>49.59999847412109</v>
       </c>
       <c r="E57" t="n">
         <v>50.16999816894531</v>
@@ -16651,88 +16643,88 @@
         <v>50</v>
       </c>
       <c r="H57" t="n">
-        <v>336700</v>
+        <v>1448900</v>
       </c>
       <c r="I57" t="n">
-        <v>0.002205747196862839</v>
+        <v>-0.005414085894255849</v>
       </c>
       <c r="J57" t="n">
-        <v>50.65777757432726</v>
+        <v>50.61555523342557</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.337954534417666</v>
+        <v>-2.006412365963377</v>
       </c>
       <c r="M57" t="n">
-        <v>50.71599998474121</v>
+        <v>50.67799987792969</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.451219423310829</v>
+        <v>-2.127158542967799</v>
       </c>
       <c r="P57" t="n">
-        <v>49.02038471515362</v>
+        <v>49.00576928945688</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>1.957583223099564</v>
+        <v>1.212569853060255</v>
       </c>
       <c r="S57" t="n">
-        <v>51.2960001373291</v>
+        <v>51.28840011596679</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.565503336653133</v>
+        <v>-3.29197564756963</v>
       </c>
       <c r="V57" t="n">
-        <v>50.86133344014485</v>
+        <v>50.85880009969075</v>
       </c>
       <c r="W57" t="n">
         <v>-1</v>
       </c>
       <c r="X57" t="n">
-        <v>-1.732817129039108</v>
+        <v>-2.475091081783729</v>
       </c>
       <c r="Y57" t="n">
-        <v>50.28335008621216</v>
+        <v>50.28145008087158</v>
       </c>
       <c r="Z57" t="n">
         <v>-1</v>
       </c>
       <c r="AA57" t="n">
-        <v>-0.6032822861955872</v>
+        <v>-1.355274371869653</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.2558817556906951</v>
+        <v>0.2557134791696691</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
       <c r="AD57" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="AF57" t="n">
         <v>49.5</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AG57" t="n">
         <v>49.6</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AH57" t="n">
         <v>49.7</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>50.1</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>50.4</v>
       </c>
       <c r="AJ57" t="n">
         <v>1</v>
@@ -16859,13 +16851,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>8.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="CA57" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CC57" t="n">
         <v>7</v>
@@ -16919,10 +16911,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20.18000030517578</v>
+        <v>20.38999938964844</v>
       </c>
       <c r="D58" t="n">
-        <v>20.18000030517578</v>
+        <v>20.38999938964844</v>
       </c>
       <c r="E58" t="n">
         <v>20.56999969482422</v>
@@ -16934,67 +16926,67 @@
         <v>20.22999954223633</v>
       </c>
       <c r="H58" t="n">
-        <v>2603600</v>
+        <v>4841500</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.002471539208696361</v>
+        <v>0.007909038607641028</v>
       </c>
       <c r="J58" t="n">
-        <v>19.85888904995388</v>
+        <v>19.88222228156196</v>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1.61696484840698</v>
+        <v>2.553925315267062</v>
       </c>
       <c r="M58" t="n">
-        <v>19.90000019073486</v>
+        <v>19.92100009918213</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>1.407035737473411</v>
+        <v>2.354295909498852</v>
       </c>
       <c r="P58" t="n">
-        <v>19.09192312680758</v>
+        <v>19.10000001467191</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>5.69914916973659</v>
+        <v>6.753923424008349</v>
       </c>
       <c r="S58" t="n">
-        <v>18.89560005187988</v>
+        <v>18.85860004425049</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>6.797350969376162</v>
+        <v>8.120429627886592</v>
       </c>
       <c r="V58" t="n">
-        <v>20.45586673736572</v>
+        <v>20.50606674194336</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.348593221357037</v>
+        <v>-0.56601470070083</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.39409119606018</v>
+        <v>21.41382943153381</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-5.674888826817659</v>
+        <v>-4.781162776881432</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.4358317874940653</v>
+        <v>0.5061982268561603</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17015,7 +17007,7 @@
         <v>20.7</v>
       </c>
       <c r="AI58" t="n">
-        <v>24</v>
+        <v>21.3</v>
       </c>
       <c r="AJ58" t="n">
         <v>1</v>
@@ -17142,13 +17134,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>27.27</v>
+        <v>27.55</v>
       </c>
       <c r="CA58" t="n">
         <v>0.09</v>
       </c>
       <c r="CB58" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17180,16 +17172,16 @@
         <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -17202,10 +17194,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14.8100004196167</v>
+        <v>14.90999984741211</v>
       </c>
       <c r="D59" t="n">
-        <v>14.8100004196167</v>
+        <v>14.90999984741211</v>
       </c>
       <c r="E59" t="n">
         <v>14.97999954223633</v>
@@ -17217,67 +17209,67 @@
         <v>14.97999954223633</v>
       </c>
       <c r="H59" t="n">
-        <v>3220100</v>
+        <v>5381700</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.002693600055589274</v>
+        <v>0.004040367973138448</v>
       </c>
       <c r="J59" t="n">
-        <v>14.69777785407172</v>
+        <v>14.70888890160455</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.7635342339446662</v>
+        <v>1.367274898552162</v>
       </c>
       <c r="M59" t="n">
-        <v>14.70900011062622</v>
+        <v>14.71900005340576</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6866565247865685</v>
+        <v>1.297641098670652</v>
       </c>
       <c r="P59" t="n">
-        <v>14.39000008656428</v>
+        <v>14.39384621840257</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>2.918695834092201</v>
+        <v>3.585932635223216</v>
       </c>
       <c r="S59" t="n">
-        <v>14.12940000534058</v>
+        <v>14.13139999389649</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>4.816909522123177</v>
+        <v>5.509714917502233</v>
       </c>
       <c r="V59" t="n">
-        <v>14.86500002543132</v>
+        <v>14.86566668828328</v>
       </c>
       <c r="W59" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X59" t="n">
-        <v>-0.3699939839927506</v>
+        <v>0.2982251658028081</v>
       </c>
       <c r="Y59" t="n">
-        <v>14.91655002593994</v>
+        <v>14.91705002307892</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.7143046223017482</v>
+        <v>-0.04726253284597809</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3147949037797609</v>
+        <v>0.3145105435314079</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17425,13 +17417,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>26.45</v>
+        <v>26.62</v>
       </c>
       <c r="CA59" t="n">
         <v>0.63</v>
       </c>
       <c r="CB59" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CC59" t="n">
         <v>8</v>
@@ -17463,16 +17455,16 @@
         <v>0</v>
       </c>
       <c r="CL59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60">
@@ -17485,10 +17477,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37.29000091552734</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="D60" t="n">
-        <v>37.29000091552734</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="E60" t="n">
         <v>37.93999862670898</v>
@@ -17500,67 +17492,67 @@
         <v>37.59999847412109</v>
       </c>
       <c r="H60" t="n">
-        <v>5474100</v>
+        <v>6878800</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0002682976544523541</v>
+        <v>-0.002145869607749207</v>
       </c>
       <c r="J60" t="n">
-        <v>37.30555555555556</v>
+        <v>37.29555553860135</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.04169523760355039</v>
+        <v>-0.2562095517333028</v>
       </c>
       <c r="M60" t="n">
-        <v>37.31399993896484</v>
+        <v>37.30499992370606</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.06431640530833675</v>
+        <v>-0.2814613616977374</v>
       </c>
       <c r="P60" t="n">
-        <v>35.61576945965107</v>
+        <v>35.61230791532076</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>4.70081506388063</v>
+        <v>4.458270021122808</v>
       </c>
       <c r="S60" t="n">
-        <v>35.12440002441407</v>
+        <v>35.12480003356934</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>6.165517103802557</v>
+        <v>5.908078415782621</v>
       </c>
       <c r="V60" t="n">
-        <v>36.63106669108073</v>
+        <v>36.67933334350586</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1.798839848163803</v>
+        <v>1.419511675846143</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.19409997940063</v>
+        <v>38.25834997177124</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-2.367117079237108</v>
+        <v>-2.766322148270074</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3357490512520276</v>
+        <v>0.3350287784590856</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17708,13 +17700,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>18.46</v>
+        <v>18.42</v>
       </c>
       <c r="CA60" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="CB60" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="CC60" t="n">
         <v>9</v>
@@ -17768,13 +17760,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.23999977111816</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="D61" t="n">
-        <v>11.23999977111816</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="E61" t="n">
-        <v>11.25</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="F61" t="n">
         <v>10.86999988555908</v>
@@ -17783,67 +17775,67 @@
         <v>11.03999996185303</v>
       </c>
       <c r="H61" t="n">
-        <v>627600</v>
+        <v>964300</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01811592481487367</v>
+        <v>0.01449273985189881</v>
       </c>
       <c r="J61" t="n">
-        <v>11.32444434695774</v>
+        <v>11.31999990675184</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.7456840552380705</v>
+        <v>-1.060071541300396</v>
       </c>
       <c r="M61" t="n">
-        <v>11.33599987030029</v>
+        <v>11.33199987411499</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.8468604470757303</v>
+        <v>-1.164843507908723</v>
       </c>
       <c r="P61" t="n">
-        <v>10.92499993397639</v>
+        <v>10.92346147390512</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>2.883293721239595</v>
+        <v>2.531599859812129</v>
       </c>
       <c r="S61" t="n">
-        <v>10.65539995193481</v>
+        <v>10.65459995269775</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>5.486418358957961</v>
+        <v>5.118914449991023</v>
       </c>
       <c r="V61" t="n">
-        <v>11.59533334732056</v>
+        <v>11.5950666809082</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-3.064453306851266</v>
+        <v>-3.407197927490682</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.4080999994278</v>
+        <v>11.40789999961853</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-1.473516434095626</v>
+        <v>-1.822422973205813</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3663958369808143</v>
+        <v>0.3653142304954091</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17991,13 +17983,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="CA61" t="n">
         <v>0.46</v>
       </c>
       <c r="CB61" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="CC61" t="n">
         <v>8</v>
@@ -18009,7 +18001,7 @@
         <v>4</v>
       </c>
       <c r="CF61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CG61" t="n">
         <v>9</v>
@@ -18018,7 +18010,7 @@
         <v>8</v>
       </c>
       <c r="CI61" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CJ61" t="inlineStr">
         <is>
@@ -18038,7 +18030,7 @@
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
@@ -18051,10 +18043,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36.5099983215332</v>
+        <v>36.81000137329102</v>
       </c>
       <c r="D62" t="n">
-        <v>36.5099983215332</v>
+        <v>36.81000137329102</v>
       </c>
       <c r="E62" t="n">
         <v>36.95000076293945</v>
@@ -18066,67 +18058,67 @@
         <v>36.59999847412109</v>
       </c>
       <c r="H62" t="n">
-        <v>15025600</v>
+        <v>18001800</v>
       </c>
       <c r="I62" t="n">
-        <v>0.001920957669106826</v>
+        <v>0.01015375303309796</v>
       </c>
       <c r="J62" t="n">
-        <v>36.22666634453667</v>
+        <v>36.26000001695421</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.7821088871437317</v>
+        <v>1.516826685272038</v>
       </c>
       <c r="M62" t="n">
-        <v>36.27899971008301</v>
+        <v>36.30900001525879</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.6367281713833896</v>
+        <v>1.379826923962879</v>
       </c>
       <c r="P62" t="n">
-        <v>34.98115378159743</v>
+        <v>34.99269236051119</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>4.370480600728659</v>
+        <v>5.193395792633074</v>
       </c>
       <c r="S62" t="n">
-        <v>36.52299987792968</v>
+        <v>36.57979995727539</v>
       </c>
       <c r="T62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.03559827078809719</v>
+        <v>0.6293129439868348</v>
       </c>
       <c r="V62" t="n">
-        <v>42.56499997456869</v>
+        <v>42.66160001118978</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-14.22530637061709</v>
+        <v>-13.71631311616052</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.31450000762939</v>
+        <v>43.35830001831054</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-15.70952379664465</v>
+        <v>-15.10275689372999</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.4044690519440947</v>
+        <v>0.439306288405663</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18274,13 +18266,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>18.25</v>
+        <v>18.41</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="CB62" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CC62" t="n">
         <v>10</v>
@@ -18311,13 +18303,13 @@
         <v>3</v>
       </c>
       <c r="CM62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN62" t="n">
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
@@ -18330,10 +18322,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>30.53000068664551</v>
+        <v>30.45000076293945</v>
       </c>
       <c r="D63" t="n">
-        <v>30.53000068664551</v>
+        <v>30.45000076293945</v>
       </c>
       <c r="E63" t="n">
         <v>30.60000038146973</v>
@@ -18345,67 +18337,67 @@
         <v>30.06999969482422</v>
       </c>
       <c r="H63" t="n">
-        <v>2252100</v>
+        <v>2785400</v>
       </c>
       <c r="I63" t="n">
-        <v>0.02518468712918231</v>
+        <v>0.02249832306398836</v>
       </c>
       <c r="J63" t="n">
-        <v>30.23000017801921</v>
+        <v>30.22111129760742</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.9923933405876618</v>
+        <v>0.7573826888032149</v>
       </c>
       <c r="M63" t="n">
-        <v>30.25100021362305</v>
+        <v>30.24300022125244</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9222851180200544</v>
+        <v>0.6844576932600372</v>
       </c>
       <c r="P63" t="n">
-        <v>29.8203846858098</v>
+        <v>29.81730776566726</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>2.379633959495457</v>
+        <v>2.121898469990989</v>
       </c>
       <c r="S63" t="n">
-        <v>28.75760009765625</v>
+        <v>28.75600009918213</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>6.163242353223027</v>
+        <v>5.890946786460423</v>
       </c>
       <c r="V63" t="n">
-        <v>29.30660002390544</v>
+        <v>29.30606669108073</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>4.174488551186909</v>
+        <v>3.903403632828279</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.49974999427796</v>
+        <v>30.49934999465943</v>
       </c>
       <c r="Z63" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.09918341092378662</v>
+        <v>-0.1618042080523476</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.1935430581985494</v>
+        <v>0.1907919513932991</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18577,13 +18569,13 @@
         <v>18881600000</v>
       </c>
       <c r="BZ63" t="n">
-        <v>7.39</v>
+        <v>7.37</v>
       </c>
       <c r="CA63" t="n">
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CC63" t="n">
         <v>4</v>
@@ -18621,7 +18613,7 @@
         <v>7</v>
       </c>
       <c r="CN63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO63" t="n">
         <v>46</v>
@@ -18637,10 +18629,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.13999938964844</v>
+        <v>27.17000007629395</v>
       </c>
       <c r="D64" t="n">
-        <v>27.13999938964844</v>
+        <v>27.17000007629395</v>
       </c>
       <c r="E64" t="n">
         <v>27.54000091552734</v>
@@ -18652,67 +18644,67 @@
         <v>27.36000061035156</v>
       </c>
       <c r="H64" t="n">
-        <v>7461500</v>
+        <v>11544300</v>
       </c>
       <c r="I64" t="n">
-        <v>0.001845671346582423</v>
+        <v>0.002953116399241118</v>
       </c>
       <c r="J64" t="n">
-        <v>26.93222257826064</v>
+        <v>26.93555598788791</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.7714803736826279</v>
+        <v>0.8703888960430402</v>
       </c>
       <c r="M64" t="n">
-        <v>26.86400032043457</v>
+        <v>26.86700038909912</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.027393783210774</v>
+        <v>1.127776390392137</v>
       </c>
       <c r="P64" t="n">
-        <v>25.44923092768742</v>
+        <v>25.45038480025071</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>6.643691775068718</v>
+        <v>6.756735858965449</v>
       </c>
       <c r="S64" t="n">
-        <v>26.89940006256104</v>
+        <v>26.90000007629395</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0.8944412385697464</v>
+        <v>1.003717469272208</v>
       </c>
       <c r="V64" t="n">
-        <v>29.12029062906901</v>
+        <v>29.12049063364665</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-6.800382814324557</v>
+        <v>-6.698000325238507</v>
       </c>
       <c r="Y64" t="n">
-        <v>28.56994188308716</v>
+        <v>28.57009188652039</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-5.005059160744102</v>
+        <v>-4.900550603013697</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.3198964191283928</v>
+        <v>0.319982873874586</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18860,7 +18852,7 @@
       <c r="BX64" t="inlineStr"/>
       <c r="BY64" t="inlineStr"/>
       <c r="BZ64" t="n">
-        <v>10.94</v>
+        <v>10.96</v>
       </c>
       <c r="CA64" t="n">
         <v>0.34</v>
@@ -18920,10 +18912,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.93000030517578</v>
+        <v>17.90999984741211</v>
       </c>
       <c r="D65" t="n">
-        <v>17.93000030517578</v>
+        <v>17.90999984741211</v>
       </c>
       <c r="E65" t="n">
         <v>17.95999908447266</v>
@@ -18935,67 +18927,67 @@
         <v>17.75</v>
       </c>
       <c r="H65" t="n">
-        <v>569700</v>
+        <v>1113200</v>
       </c>
       <c r="I65" t="n">
-        <v>0.01014086226342426</v>
+        <v>0.009014075910541264</v>
       </c>
       <c r="J65" t="n">
-        <v>17.61222224765354</v>
+        <v>17.60999997456868</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1.804304153410174</v>
+        <v>1.703576793166767</v>
       </c>
       <c r="M65" t="n">
-        <v>17.5</v>
+        <v>17.49799995422363</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>2.457144601004464</v>
+        <v>2.354554202001973</v>
       </c>
       <c r="P65" t="n">
-        <v>16.00961531125582</v>
+        <v>16.00884606288029</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>11.99519761458479</v>
+        <v>11.87564535922435</v>
       </c>
       <c r="S65" t="n">
-        <v>14.81739999771118</v>
+        <v>14.81379999160767</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>21.00638646419344</v>
+        <v>20.90078074200074</v>
       </c>
       <c r="V65" t="n">
-        <v>15.83719997406006</v>
+        <v>15.85319997151693</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>13.21445921339343</v>
+        <v>12.97403602799804</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.64582215309143</v>
+        <v>15.65193881511688</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>14.59928490643762</v>
+        <v>14.42671773106063</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.3830509082315401</v>
+        <v>0.382901257184312</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19147,7 +19139,7 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>27.58</v>
+        <v>27.55</v>
       </c>
       <c r="CA65" t="n">
         <v>0.71</v>
@@ -19207,10 +19199,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>16.96999931335449</v>
+        <v>17</v>
       </c>
       <c r="D66" t="n">
-        <v>16.96999931335449</v>
+        <v>17</v>
       </c>
       <c r="E66" t="n">
         <v>17.29999923706055</v>
@@ -19222,67 +19214,67 @@
         <v>17.29999923706055</v>
       </c>
       <c r="H66" t="n">
-        <v>1905800</v>
+        <v>3095300</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.008761770941923763</v>
+        <v>-0.007009394471429897</v>
       </c>
       <c r="J66" t="n">
-        <v>17.44333351982964</v>
+        <v>17.44666692945692</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.713553610249229</v>
+        <v>-2.560184883811662</v>
       </c>
       <c r="M66" t="n">
-        <v>17.4730001449585</v>
+        <v>17.47600021362305</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-2.878731914559828</v>
+        <v>-2.723736597645436</v>
       </c>
       <c r="P66" t="n">
-        <v>17.25769241039569</v>
+        <v>17.25884628295898</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-1.667042674070966</v>
+        <v>-1.499789028276842</v>
       </c>
       <c r="S66" t="n">
-        <v>18.5034001159668</v>
+        <v>18.53460014343262</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-8.287129895057053</v>
+        <v>-8.279650661772559</v>
       </c>
       <c r="V66" t="n">
-        <v>18.88386670430501</v>
+        <v>18.91026671091716</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-10.13493380841441</v>
+        <v>-10.10174388399468</v>
       </c>
       <c r="Y66" t="n">
-        <v>19.96629096984863</v>
+        <v>20.00484097480774</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-15.00675143429934</v>
+        <v>-15.0205691641926</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3303446252837296</v>
+        <v>0.3366721628250758</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19434,13 +19426,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>15.15</v>
+        <v>15.18</v>
       </c>
       <c r="CA66" t="n">
         <v>0.39</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CC66" t="n">
         <v>10</v>
@@ -19494,13 +19486,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>47.59999847412109</v>
+        <v>47.54999923706055</v>
       </c>
       <c r="D67" t="n">
-        <v>47.59999847412109</v>
+        <v>47.54999923706055</v>
       </c>
       <c r="E67" t="n">
-        <v>47.66999816894531</v>
+        <v>47.7599983215332</v>
       </c>
       <c r="F67" t="n">
         <v>46.59000015258789</v>
@@ -19509,67 +19501,67 @@
         <v>46.93999862670898</v>
       </c>
       <c r="H67" t="n">
-        <v>1614600</v>
+        <v>2254600</v>
       </c>
       <c r="I67" t="n">
-        <v>0.01927189928219164</v>
+        <v>0.01820125182515286</v>
       </c>
       <c r="J67" t="n">
-        <v>47.35777748955621</v>
+        <v>47.3522220187717</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5114703379361601</v>
+        <v>0.4176725185366051</v>
       </c>
       <c r="M67" t="n">
-        <v>47.30099983215332</v>
+        <v>47.29599990844726</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.6321190736533296</v>
+        <v>0.5370418832564259</v>
       </c>
       <c r="P67" t="n">
-        <v>45.42076932466947</v>
+        <v>45.41884627709022</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>4.797869304842473</v>
+        <v>4.692221697945918</v>
       </c>
       <c r="S67" t="n">
-        <v>43.78600006103515</v>
+        <v>43.77580009460449</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>8.710543113710882</v>
+        <v>8.621656564356519</v>
       </c>
       <c r="V67" t="n">
-        <v>46.08060010274252</v>
+        <v>46.14580009460449</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>3.297262552985178</v>
+        <v>3.042961958785587</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.19430004119873</v>
+        <v>47.22690004348755</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.8596343892550697</v>
+        <v>0.6841422860181033</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.2811432577010795</v>
+        <v>0.2877590586480834</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19717,7 +19709,7 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="CA67" t="n">
         <v>1.14</v>
@@ -19758,13 +19750,13 @@
         <v>8</v>
       </c>
       <c r="CM67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN67" t="n">
         <v>0</v>
       </c>
       <c r="CO67" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68">
@@ -19777,10 +19769,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.61000061035156</v>
+        <v>41.4900016784668</v>
       </c>
       <c r="D68" t="n">
-        <v>41.61000061035156</v>
+        <v>41.4900016784668</v>
       </c>
       <c r="E68" t="n">
         <v>41.72999954223633</v>
@@ -19792,67 +19784,67 @@
         <v>41.34999847412109</v>
       </c>
       <c r="H68" t="n">
-        <v>659900</v>
+        <v>891000</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01364193382945156</v>
+        <v>0.01071869548316595</v>
       </c>
       <c r="J68" t="n">
-        <v>41.13555526733398</v>
+        <v>41.12222205268012</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1.15337046001744</v>
+        <v>0.8943573752301761</v>
       </c>
       <c r="M68" t="n">
-        <v>41.17699966430664</v>
+        <v>41.16499977111816</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>1.051560214622091</v>
+        <v>0.7895102858148459</v>
       </c>
       <c r="P68" t="n">
-        <v>39.40961500314566</v>
+        <v>39.40499965961163</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>5.583372501939611</v>
+        <v>5.291211868711689</v>
       </c>
       <c r="S68" t="n">
-        <v>39.83279968261719</v>
+        <v>39.8303997039795</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>4.461652060349495</v>
+        <v>4.166671654870411</v>
       </c>
       <c r="V68" t="n">
-        <v>41.0369999440511</v>
+        <v>41.03619995117187</v>
       </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
       <c r="X68" t="n">
-        <v>1.396302524750042</v>
+        <v>1.105857091628593</v>
       </c>
       <c r="Y68" t="n">
-        <v>41.17535005569458</v>
+        <v>41.17475006103516</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.055608644660133</v>
+        <v>0.7656430627127799</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2109875803307966</v>
+        <v>0.2096738710033172</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20002,10 +19994,10 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>9.15</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="CA68" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="CB68" t="n">
         <v>1.8</v>
@@ -20036,16 +20028,16 @@
         <v>0</v>
       </c>
       <c r="CL68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN68" t="n">
         <v>0</v>
       </c>
       <c r="CO68" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
@@ -20058,10 +20050,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.67000007629395</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="D69" t="n">
-        <v>19.67000007629395</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="E69" t="n">
         <v>19.71999931335449</v>
@@ -20073,88 +20065,88 @@
         <v>19.70000076293945</v>
       </c>
       <c r="H69" t="n">
-        <v>1107500</v>
+        <v>2077600</v>
       </c>
       <c r="I69" t="n">
-        <v>0.004596534879396152</v>
+        <v>-0.001532210764167874</v>
       </c>
       <c r="J69" t="n">
-        <v>19.43222236633301</v>
+        <v>19.41888893975152</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.22362592130942</v>
+        <v>0.6751688920813522</v>
       </c>
       <c r="M69" t="n">
-        <v>19.38600006103515</v>
+        <v>19.37399997711181</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1.464974798125662</v>
+        <v>0.9084301649460879</v>
       </c>
       <c r="P69" t="n">
-        <v>18.79500000293438</v>
+        <v>18.79038458604079</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>4.655493871896526</v>
+        <v>4.042571068950165</v>
       </c>
       <c r="S69" t="n">
-        <v>19.78220001220703</v>
+        <v>19.8496000289917</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-0.5671762283459408</v>
+        <v>-1.509354301817488</v>
       </c>
       <c r="V69" t="n">
-        <v>23.16760000864665</v>
+        <v>23.21473333994548</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-15.09694543693487</v>
+        <v>-15.78624250910106</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.25255001068115</v>
+        <v>23.2833000087738</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-15.40712710107729</v>
+        <v>-16.03424244117648</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2012641681688223</v>
+        <v>0.2024139069239809</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
       </c>
       <c r="AD69" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AE69" t="n">
         <v>19.4</v>
       </c>
-      <c r="AE69" t="n">
+      <c r="AF69" t="n">
         <v>19.5</v>
       </c>
-      <c r="AF69" t="n">
+      <c r="AG69" t="n">
         <v>19.6</v>
       </c>
-      <c r="AG69" t="n">
+      <c r="AH69" t="n">
         <v>21.9</v>
       </c>
-      <c r="AH69" t="n">
+      <c r="AI69" t="n">
         <v>22.2</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>22.3</v>
       </c>
       <c r="AJ69" t="n">
         <v>1</v>
@@ -20281,13 +20273,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>1967</v>
+        <v>1955</v>
       </c>
       <c r="CA69" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CC69" t="n">
         <v>1</v>
@@ -20341,10 +20333,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>34.7599983215332</v>
+        <v>34.65000152587891</v>
       </c>
       <c r="D70" t="n">
-        <v>34.7599983215332</v>
+        <v>34.65000152587891</v>
       </c>
       <c r="E70" t="n">
         <v>34.97999954223633</v>
@@ -20356,88 +20348,88 @@
         <v>34.47999954223633</v>
       </c>
       <c r="H70" t="n">
-        <v>2078500</v>
+        <v>3572200</v>
       </c>
       <c r="I70" t="n">
-        <v>0.01518681710209813</v>
+        <v>0.01197429402201089</v>
       </c>
       <c r="J70" t="n">
-        <v>33.8999998304579</v>
+        <v>33.88777796427409</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>2.536868717924374</v>
+        <v>2.249258013931713</v>
       </c>
       <c r="M70" t="n">
-        <v>33.99199981689453</v>
+        <v>33.9810001373291</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>2.259350755400282</v>
+        <v>1.968751319402411</v>
       </c>
       <c r="P70" t="n">
-        <v>32.99192311213567</v>
+        <v>32.98769246614896</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>5.359115330707026</v>
+        <v>5.039179571095362</v>
       </c>
       <c r="S70" t="n">
-        <v>31.57279987335205</v>
+        <v>31.51259994506836</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>10.09476023971887</v>
+        <v>9.956022626757404</v>
       </c>
       <c r="V70" t="n">
-        <v>32.69446664174398</v>
+        <v>32.74373332977295</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>6.317679693089024</v>
+        <v>5.821780237785652</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.44609997749328</v>
+        <v>35.50104998588562</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-1.935619592552423</v>
+        <v>-2.397248702066763</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3770563484577566</v>
+        <v>0.3902977945402182</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
       </c>
       <c r="AD70" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AE70" t="n">
         <v>33.3</v>
       </c>
-      <c r="AE70" t="n">
+      <c r="AF70" t="n">
         <v>33.4</v>
       </c>
-      <c r="AF70" t="n">
+      <c r="AG70" t="n">
         <v>34.7</v>
       </c>
-      <c r="AG70" t="n">
+      <c r="AH70" t="n">
         <v>35.2</v>
       </c>
-      <c r="AH70" t="n">
+      <c r="AI70" t="n">
         <v>35.5</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>35.9</v>
       </c>
       <c r="AJ70" t="n">
         <v>3</v>
@@ -20564,13 +20556,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>22.57</v>
+        <v>22.5</v>
       </c>
       <c r="CA70" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="CB70" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CC70" t="n">
         <v>7</v>
@@ -20624,10 +20616,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38.93000030517578</v>
+        <v>38.72999954223633</v>
       </c>
       <c r="D71" t="n">
-        <v>38.93000030517578</v>
+        <v>38.72999954223633</v>
       </c>
       <c r="E71" t="n">
         <v>39.02000045776367</v>
@@ -20639,67 +20631,67 @@
         <v>38.68000030517578</v>
       </c>
       <c r="H71" t="n">
-        <v>6055900</v>
+        <v>8052900</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>-0.005137445706951738</v>
       </c>
       <c r="J71" t="n">
-        <v>38.34111107720269</v>
+        <v>38.31888877020942</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1.535921133812003</v>
+        <v>1.07286715565333</v>
       </c>
       <c r="M71" t="n">
-        <v>38.15200004577637</v>
+        <v>38.13199996948242</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2.039212252217276</v>
+        <v>1.568235532446485</v>
       </c>
       <c r="P71" t="n">
-        <v>35.44961540515606</v>
+        <v>35.44192306811993</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>9.817835427104544</v>
+        <v>9.277364740611471</v>
       </c>
       <c r="S71" t="n">
-        <v>33.7557999420166</v>
+        <v>33.71899993896484</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>15.32832986345181</v>
+        <v>14.86105641431227</v>
       </c>
       <c r="V71" t="n">
-        <v>29.60820003509522</v>
+        <v>29.57920003255208</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>31.48384656625949</v>
+        <v>30.93660240849562</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.86110001564026</v>
+        <v>27.81535000801086</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>39.72887030060488</v>
+        <v>39.23966274406768</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.3365747423486343</v>
+        <v>0.3391618862195365</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20851,13 +20843,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>14.47</v>
+        <v>14.4</v>
       </c>
       <c r="CA71" t="n">
         <v>0.32</v>
       </c>
       <c r="CB71" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CC71" t="n">
         <v>4</v>
@@ -20907,10 +20899,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7.050000190734863</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="D72" t="n">
-        <v>7.050000190734863</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="E72" t="n">
         <v>7.159999847412109</v>
@@ -20922,67 +20914,67 @@
         <v>7.090000152587891</v>
       </c>
       <c r="H72" t="n">
-        <v>6751400</v>
+        <v>8908100</v>
       </c>
       <c r="I72" t="n">
-        <v>0.002844947415308718</v>
+        <v>0.01280222945444076</v>
       </c>
       <c r="J72" t="n">
-        <v>7.357777913411458</v>
+        <v>7.365555657280816</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-4.18302545005592</v>
+        <v>-3.333839063166991</v>
       </c>
       <c r="M72" t="n">
-        <v>7.403000116348267</v>
+        <v>7.410000085830688</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-4.768336080852722</v>
+        <v>-3.91363288680848</v>
       </c>
       <c r="P72" t="n">
-        <v>7.046153875497671</v>
+        <v>7.048846171452449</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0.05458744309526561</v>
+        <v>1.009437748759548</v>
       </c>
       <c r="S72" t="n">
-        <v>7.487399959564209</v>
+        <v>7.512599964141845</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-5.84181119202298</v>
+        <v>-5.22588824716703</v>
       </c>
       <c r="V72" t="n">
-        <v>7.917800006866455</v>
+        <v>7.911733338038126</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-10.96011285178989</v>
+        <v>-10.00707959496737</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.480100004673004</v>
+        <v>7.472000002861023</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-5.749920638353058</v>
+        <v>-4.710922338960925</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.5279439882668993</v>
+        <v>0.5281833157634217</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21134,7 +21126,7 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>-3.39</v>
+        <v>-3.42</v>
       </c>
       <c r="CA72" t="n">
         <v>-0.06</v>
@@ -21194,10 +21186,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74.73999786376953</v>
+        <v>74.76000213623047</v>
       </c>
       <c r="D73" t="n">
-        <v>74.73999786376953</v>
+        <v>74.76000213623047</v>
       </c>
       <c r="E73" t="n">
         <v>74.91000366210938</v>
@@ -21209,67 +21201,67 @@
         <v>73.69999694824219</v>
       </c>
       <c r="H73" t="n">
-        <v>10743100</v>
+        <v>14803500</v>
       </c>
       <c r="I73" t="n">
-        <v>0.02383558717492518</v>
+        <v>0.02410961830452707</v>
       </c>
       <c r="J73" t="n">
-        <v>76.77666642930772</v>
+        <v>76.77888912624783</v>
       </c>
       <c r="K73" t="n">
         <v>-1</v>
       </c>
       <c r="L73" t="n">
-        <v>-2.65271815026439</v>
+        <v>-2.629481896641797</v>
       </c>
       <c r="M73" t="n">
-        <v>76.94399948120117</v>
+        <v>76.94599990844726</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
       </c>
       <c r="O73" t="n">
-        <v>-2.8644229989242</v>
+        <v>-2.840950504012895</v>
       </c>
       <c r="P73" t="n">
-        <v>76.11076912513145</v>
+        <v>76.11153852022611</v>
       </c>
       <c r="Q73" t="n">
         <v>-1</v>
       </c>
       <c r="R73" t="n">
-        <v>-1.801021428529095</v>
+        <v>-1.775731262660622</v>
       </c>
       <c r="S73" t="n">
-        <v>75.41840026855469</v>
+        <v>75.35420028686524</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-0.899518423049894</v>
+        <v>-0.7885401853814648</v>
       </c>
       <c r="V73" t="n">
-        <v>79.85546681722005</v>
+        <v>79.92973353068034</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-6.405909522962573</v>
+        <v>-6.46784515109826</v>
       </c>
       <c r="Y73" t="n">
-        <v>79.02705009460449</v>
+        <v>78.9804001235962</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-5.424790911090397</v>
+        <v>-5.343601679354929</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2683128579776553</v>
+        <v>0.2605540553906802</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21417,7 +21409,7 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>21.29</v>
+        <v>21.3</v>
       </c>
       <c r="CA73" t="n">
         <v>0.21</v>
@@ -21473,10 +21465,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.339999914169312</v>
+        <v>3.359999895095825</v>
       </c>
       <c r="D74" t="n">
-        <v>3.339999914169312</v>
+        <v>3.359999895095825</v>
       </c>
       <c r="E74" t="n">
         <v>3.450000047683716</v>
@@ -21488,67 +21480,67 @@
         <v>3.369999885559082</v>
       </c>
       <c r="H74" t="n">
-        <v>11106000</v>
+        <v>13862100</v>
       </c>
       <c r="I74" t="n">
-        <v>0.003003000207918216</v>
+        <v>0.009009000623754648</v>
       </c>
       <c r="J74" t="n">
-        <v>3.369999965031942</v>
+        <v>3.372222185134888</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.8902092336474552</v>
+        <v>-0.3624402357869433</v>
       </c>
       <c r="M74" t="n">
-        <v>3.370999979972839</v>
+        <v>3.372999978065491</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.9196103823108722</v>
+        <v>-0.3854160407413229</v>
       </c>
       <c r="P74" t="n">
-        <v>3.072692293387193</v>
+        <v>3.073461523422828</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>8.699459472638939</v>
+        <v>9.322985483608308</v>
       </c>
       <c r="S74" t="n">
-        <v>3.113599987030029</v>
+        <v>3.111999983787537</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>7.271323486715395</v>
+        <v>7.969148862476986</v>
       </c>
       <c r="V74" t="n">
-        <v>3.442661458651225</v>
+        <v>3.452594792048136</v>
       </c>
       <c r="W74" t="n">
         <v>-1</v>
       </c>
       <c r="X74" t="n">
-        <v>-2.982040079018814</v>
+        <v>-2.681892968313908</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.513646091222763</v>
+        <v>3.518496090173721</v>
       </c>
       <c r="Z74" t="n">
         <v>-1</v>
       </c>
       <c r="AA74" t="n">
-        <v>-4.942050865260083</v>
+        <v>-4.504657416574548</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.7613649858046246</v>
+        <v>0.7830632292911719</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21696,13 +21688,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>13.36</v>
+        <v>13.44</v>
       </c>
       <c r="CA74" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CC74" t="n">
         <v>6</v>
@@ -21733,13 +21725,13 @@
         <v>8</v>
       </c>
       <c r="CM74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN74" t="n">
         <v>-1</v>
       </c>
       <c r="CO74" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75">
@@ -21752,10 +21744,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38.95000076293945</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="D75" t="n">
-        <v>38.95000076293945</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="E75" t="n">
         <v>39.29000091552734</v>
@@ -21767,73 +21759,73 @@
         <v>39.22999954223633</v>
       </c>
       <c r="H75" t="n">
-        <v>8024100</v>
+        <v>13704800</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0028161957625219</v>
+        <v>-0.003072266829567738</v>
       </c>
       <c r="J75" t="n">
-        <v>38.07777828640408</v>
+        <v>38.07666693793403</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>2.290633844167328</v>
+        <v>2.267351000501723</v>
       </c>
       <c r="M75" t="n">
-        <v>37.95700035095215</v>
+        <v>37.9560001373291</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>2.616119300276567</v>
+        <v>2.59247150864071</v>
       </c>
       <c r="P75" t="n">
-        <v>35.62115405156062</v>
+        <v>35.6207693540133</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>9.345139987773607</v>
+        <v>9.318241388072988</v>
       </c>
       <c r="S75" t="n">
-        <v>35.05219985961914</v>
+        <v>35.01619983673096</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>11.11998938420597</v>
+        <v>11.20566711485945</v>
       </c>
       <c r="V75" t="n">
-        <v>32.47899987538656</v>
+        <v>32.46499987284342</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>19.9236457784428</v>
+        <v>19.9445519150666</v>
       </c>
       <c r="Y75" t="n">
-        <v>30.99449990272522</v>
+        <v>30.94759989738465</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>25.66745998542386</v>
+        <v>25.82558503995578</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.2801716648907971</v>
+        <v>0.287060617693478</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>31</v>
+        <v>32.7</v>
       </c>
       <c r="AE75" t="n">
         <v>33</v>
@@ -21979,7 +21971,7 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>15.52</v>
+        <v>15.51</v>
       </c>
       <c r="CA75" t="n">
         <v>0.39</v>
@@ -22035,10 +22027,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>22.70000076293945</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="D76" t="n">
-        <v>22.70000076293945</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="E76" t="n">
         <v>22.98999977111816</v>
@@ -22050,67 +22042,67 @@
         <v>22.93000030517578</v>
       </c>
       <c r="H76" t="n">
-        <v>508000</v>
+        <v>846900</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0008802179145879219</v>
+        <v>-0.01056337052691259</v>
       </c>
       <c r="J76" t="n">
-        <v>22.62777752346463</v>
+        <v>22.6033329433865</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3191795544212528</v>
+        <v>-0.5456425451020013</v>
       </c>
       <c r="M76" t="n">
-        <v>22.69199981689453</v>
+        <v>22.66999969482422</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.03525888467073966</v>
+        <v>-0.8381127267119943</v>
       </c>
       <c r="P76" t="n">
-        <v>22.08807703164907</v>
+        <v>22.07961544623742</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>2.770380284411263</v>
+        <v>1.813365350378593</v>
       </c>
       <c r="S76" t="n">
-        <v>22.18100009918213</v>
+        <v>22.17660007476807</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>2.339843385945712</v>
+        <v>1.368106321281683</v>
       </c>
       <c r="V76" t="n">
-        <v>24.27920001983643</v>
+        <v>24.27773334503174</v>
       </c>
       <c r="W76" t="n">
         <v>-1</v>
       </c>
       <c r="X76" t="n">
-        <v>-6.504329860978728</v>
+        <v>-7.40486674454435</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.00585001945496</v>
+        <v>26.00475001335144</v>
       </c>
       <c r="Z76" t="n">
         <v>-1</v>
       </c>
       <c r="AA76" t="n">
-        <v>-12.71194463569697</v>
+        <v>-13.55425631588623</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.3007428423860834</v>
+        <v>0.3025115745867232</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22258,13 +22250,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>9.15</v>
+        <v>9.06</v>
       </c>
       <c r="CA76" t="n">
         <v>0.04</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CC76" t="n">
         <v>8</v>
@@ -22299,13 +22291,13 @@
         <v>4</v>
       </c>
       <c r="CM76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
@@ -22318,13 +22310,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>31.06999969482422</v>
+        <v>30.95999908447266</v>
       </c>
       <c r="D77" t="n">
-        <v>31.06999969482422</v>
+        <v>30.95999908447266</v>
       </c>
       <c r="E77" t="n">
-        <v>31.10000038146973</v>
+        <v>31.19000053405762</v>
       </c>
       <c r="F77" t="n">
         <v>30.48999977111816</v>
@@ -22333,67 +22325,67 @@
         <v>30.79000091552734</v>
       </c>
       <c r="H77" t="n">
-        <v>2509700</v>
+        <v>3429900</v>
       </c>
       <c r="I77" t="n">
-        <v>0.01172258616359212</v>
+        <v>0.008140671033963098</v>
       </c>
       <c r="J77" t="n">
-        <v>30.45333332485623</v>
+        <v>30.44111103481717</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>2.024955243453312</v>
+        <v>1.704563440743047</v>
       </c>
       <c r="M77" t="n">
-        <v>30.43899993896484</v>
+        <v>30.42799987792969</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>2.07299765801975</v>
+        <v>1.748387040479926</v>
       </c>
       <c r="P77" t="n">
-        <v>29.98346160008357</v>
+        <v>29.97923080737774</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>3.623791372833409</v>
+        <v>3.271492465555691</v>
       </c>
       <c r="S77" t="n">
-        <v>31.77220012664795</v>
+        <v>31.84520015716553</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-2.210109558118958</v>
+        <v>-2.779700137930182</v>
       </c>
       <c r="V77" t="n">
-        <v>35.9650667699178</v>
+        <v>36.03066677093506</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-13.61061584122501</v>
+        <v>-14.07319969596779</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.65735011100769</v>
+        <v>35.67960011482239</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-12.86509065284501</v>
+        <v>-13.22772961345232</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1615275554152103</v>
+        <v>0.1651035390668993</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22541,7 +22533,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>15.77</v>
+        <v>15.72</v>
       </c>
       <c r="CA77" t="n">
         <v>0.11</v>
@@ -22601,10 +22593,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.5099983215332</v>
+        <v>51.13000106811523</v>
       </c>
       <c r="D78" t="n">
-        <v>51.5099983215332</v>
+        <v>51.13000106811523</v>
       </c>
       <c r="E78" t="n">
         <v>51.84000015258789</v>
@@ -22616,88 +22608,88 @@
         <v>51.70999908447266</v>
       </c>
       <c r="H78" t="n">
-        <v>2253500</v>
+        <v>4917100</v>
       </c>
       <c r="I78" t="n">
-        <v>0.004485170587195553</v>
+        <v>-0.002925072440567167</v>
       </c>
       <c r="J78" t="n">
-        <v>51.57222239176432</v>
+        <v>51.53000047471788</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.1206542346739242</v>
+        <v>-0.7762456877889946</v>
       </c>
       <c r="M78" t="n">
-        <v>51.62100028991699</v>
+        <v>51.58300056457519</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.2150325792998452</v>
+        <v>-0.8781953191979657</v>
       </c>
       <c r="P78" t="n">
-        <v>50.05692335275504</v>
+        <v>50.04230807377742</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2.90284514399384</v>
+        <v>2.173546817093703</v>
       </c>
       <c r="S78" t="n">
-        <v>48.16280029296875</v>
+        <v>48.10960029602051</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>6.949757921474328</v>
+        <v>6.27816642314645</v>
       </c>
       <c r="V78" t="n">
-        <v>47.20606676737467</v>
+        <v>47.23533345540365</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>9.117327176118577</v>
+        <v>8.245242126614102</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.56885005950928</v>
+        <v>47.55080007553101</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>8.285145125630518</v>
+        <v>7.527109926434307</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.176736852740758</v>
+        <v>0.1817480607228171</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="AE78" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AF78" t="n">
         <v>50</v>
       </c>
-      <c r="AF78" t="n">
+      <c r="AG78" t="n">
         <v>51.5</v>
       </c>
-      <c r="AG78" t="n">
+      <c r="AH78" t="n">
         <v>51.7</v>
       </c>
-      <c r="AH78" t="n">
+      <c r="AI78" t="n">
         <v>52.6</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>53.5</v>
       </c>
       <c r="AJ78" t="n">
         <v>1</v>
@@ -22824,13 +22816,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>34.34</v>
+        <v>34.09</v>
       </c>
       <c r="CA78" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB78" t="n">
-        <v>12.18</v>
+        <v>12.09</v>
       </c>
       <c r="CC78" t="n">
         <v>6</v>
@@ -22865,13 +22857,13 @@
         <v>7</v>
       </c>
       <c r="CM78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN78" t="n">
         <v>1</v>
       </c>
       <c r="CO78" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79">
@@ -22884,13 +22876,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10.27000045776367</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="D79" t="n">
-        <v>10.27000045776367</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="E79" t="n">
-        <v>10.36999988555908</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="F79" t="n">
         <v>10.0600004196167</v>
@@ -22899,67 +22891,67 @@
         <v>10.11999988555908</v>
       </c>
       <c r="H79" t="n">
-        <v>3229300</v>
+        <v>7835900</v>
       </c>
       <c r="I79" t="n">
-        <v>0.01683169008645202</v>
+        <v>0.03069301527068591</v>
       </c>
       <c r="J79" t="n">
-        <v>10.02555561065674</v>
+        <v>10.04111109839545</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.438217457465391</v>
+        <v>3.67378415995818</v>
       </c>
       <c r="M79" t="n">
-        <v>9.972000026702881</v>
+        <v>9.985999965667725</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.988371743509921</v>
+        <v>4.245943152434541</v>
       </c>
       <c r="P79" t="n">
-        <v>8.86038459264315</v>
+        <v>8.865769184552706</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>15.90919502851983</v>
+        <v>17.41789833137092</v>
       </c>
       <c r="S79" t="n">
-        <v>8.564200010299682</v>
+        <v>8.581600008010865</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>19.9178025432909</v>
+        <v>21.30604826249704</v>
       </c>
       <c r="V79" t="n">
-        <v>9.882199974060059</v>
+        <v>9.922533302307128</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>3.924232303753782</v>
+        <v>4.912722691408234</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.6700999879837</v>
+        <v>10.69924998283386</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-3.749726156930212</v>
+        <v>-2.703461792983928</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.5474566491412182</v>
+        <v>0.5529876693757008</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23107,13 +23099,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>23.88</v>
+        <v>24.21</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="CC79" t="n">
         <v>5</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -1579,52 +1579,52 @@
         <v>14.08209144757732</v>
       </c>
       <c r="S4" t="n">
-        <v>8.678199977874756</v>
+        <v>8.661999988555909</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>17.7663604559114</v>
+        <v>17.9866114122755</v>
       </c>
       <c r="V4" t="n">
-        <v>8.734066616694133</v>
+        <v>8.72313328742981</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>17.01307896478016</v>
+        <v>17.15973985810821</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.563549942970276</v>
+        <v>8.556599946022034</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.34303338089707</v>
+        <v>19.4399683460729</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7069617938877713</v>
+        <v>0.7071225803735093</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8153604812868268</v>
+        <v>0.8153646249935039</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.614155579213359</v>
+        <v>1.612041789769327</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.988342550747323</v>
+        <v>2.010205933945145</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.757262260834908</v>
+        <v>1.776414123003708</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.03050859771193</v>
+        <v>2.059659859630363</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5166896705999432</v>
+        <v>0.5066241794147291</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1884,52 +1884,52 @@
         <v>12.46183593503045</v>
       </c>
       <c r="S5" t="n">
-        <v>11.27759998321533</v>
+        <v>11.23099998474121</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>11.81456759811441</v>
+        <v>12.27851192066235</v>
       </c>
       <c r="V5" t="n">
-        <v>11.99119998296102</v>
+        <v>11.98373331705729</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>5.160448283704006</v>
+        <v>5.225970263611805</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.94769998073578</v>
+        <v>11.93984997749329</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.543323627219844</v>
+        <v>5.612714401329972</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.700686981383859</v>
+        <v>1.707789142994273</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.545004254750252</v>
+        <v>1.551439261903555</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.139603558078712</v>
+        <v>2.14044510305754</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.658417126012883</v>
+        <v>1.724938713531761</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5302169172185434</v>
+        <v>0.5359115712072205</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.490944922849459</v>
+        <v>0.4951258014620016</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3109942922226176</v>
+        <v>0.3011760306308049</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -2185,52 +2185,52 @@
         <v>2.882196705517484</v>
       </c>
       <c r="S6" t="n">
-        <v>52.68099983215332</v>
+        <v>52.6373998260498</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.686702419453051</v>
+        <v>4.773415305718881</v>
       </c>
       <c r="V6" t="n">
-        <v>55.88979998270671</v>
+        <v>55.84286664326986</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.323673473615411</v>
+        <v>-1.240740597750913</v>
       </c>
       <c r="Y6" t="n">
-        <v>56.01345001220703</v>
+        <v>55.96020000457764</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.541502060915642</v>
+        <v>-1.4478119782139</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.06498040872604094</v>
+        <v>0.06514358679538819</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.009227911956636366</v>
+        <v>0.009249012148952265</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4099718346441723</v>
+        <v>0.4106580117960624</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.5026897438108178</v>
+        <v>0.513408277992725</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.08983609482338756</v>
+        <v>-0.08408202680471873</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.09417636003945652</v>
+        <v>-0.08825241983783125</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2989323242545208</v>
+        <v>0.2687009672598509</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
         <v>-1</v>
       </c>
       <c r="CR6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CS6" t="n">
         <v>5</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -2482,52 +2482,52 @@
         <v>-3.357240029952202</v>
       </c>
       <c r="S7" t="n">
-        <v>16.29400001525879</v>
+        <v>16.2470000076294</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.064321049416613</v>
+        <v>-7.798365635490241</v>
       </c>
       <c r="V7" t="n">
-        <v>20.0546000289917</v>
+        <v>19.99946669260661</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-25.303922688158</v>
+        <v>-25.09800499943267</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.38095000267029</v>
+        <v>21.31990000724792</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-29.93763354591138</v>
+        <v>-29.73700844214222</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.7809541585182227</v>
+        <v>-0.7799390014648356</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.9148354937223899</v>
+        <v>-0.9137041286097022</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.4675789960701248</v>
+        <v>-0.4692195279366319</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.043458969909811</v>
+        <v>-1.009080324623076</v>
       </c>
       <c r="AF7" t="n">
-        <v>-3.26949804251822</v>
+        <v>-3.283265729321781</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.778046540825671</v>
+        <v>-3.816742754196376</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.5516777701443534</v>
+        <v>0.5224675257968191</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
         <v>17.78000068664551</v>
       </c>
       <c r="H8" t="n">
-        <v>48908100</v>
+        <v>48904800</v>
       </c>
       <c r="I8" t="n">
         <v>0.0363842742522249</v>
@@ -2783,52 +2783,52 @@
         <v>11.15071254810317</v>
       </c>
       <c r="S8" t="n">
-        <v>15.89820003509521</v>
+        <v>15.88320003509521</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>14.66706609549304</v>
+        <v>14.77535699327384</v>
       </c>
       <c r="V8" t="n">
-        <v>16.64500003178915</v>
+        <v>16.62706669489543</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>9.522376133494149</v>
+        <v>9.640502902613658</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.22040006160736</v>
+        <v>16.2189500617981</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.38933363539879</v>
+        <v>12.39938141973216</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.191437623305937</v>
+        <v>1.193725520994601</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.097389706487728</v>
+        <v>1.09932880653644</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.771946383565993</v>
+        <v>1.765835477307085</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.778103602293216</v>
+        <v>1.790166037007823</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.761339104249397</v>
+        <v>0.7678593192754091</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.070019958120548</v>
+        <v>1.066055331578221</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.3364927189838927</v>
+        <v>0.3099568723762658</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="H9" t="n">
-        <v>57700000</v>
+        <v>57695000</v>
       </c>
       <c r="I9" t="n">
         <v>-0.009051766591178456</v>
@@ -3088,52 +3088,52 @@
         <v>10.365581891249</v>
       </c>
       <c r="S9" t="n">
-        <v>20.66040004730225</v>
+        <v>20.64940006256104</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>11.2756757782147</v>
+        <v>11.33495259652031</v>
       </c>
       <c r="V9" t="n">
-        <v>21.8500666809082</v>
+        <v>21.8100666809082</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.217069159820888</v>
+        <v>5.410038893841778</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.05975001335144</v>
+        <v>22.04755002021789</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.21695512054171</v>
+        <v>4.274623484405437</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5088799220633571</v>
+        <v>0.5122791899992875</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4716314912990656</v>
+        <v>0.4745514670028538</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.725529627443019</v>
+        <v>1.724260476401822</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.528600572112677</v>
+        <v>1.539250719963127</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.5137766387258136</v>
+        <v>0.5326258371913618</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4307414207770699</v>
+        <v>0.436728873802495</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3568672640383925</v>
+        <v>0.3528897833327714</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -3405,73 +3405,73 @@
         <v>4.774364578207249</v>
       </c>
       <c r="S10" t="n">
-        <v>15.57981781005859</v>
+        <v>15.55201782226563</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2.825338865136726</v>
+        <v>3.009144156381055</v>
       </c>
       <c r="V10" t="n">
-        <v>16.15920596440633</v>
+        <v>16.13740596135457</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8614625430809338</v>
+        <v>-0.7275364074750404</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.28800447463989</v>
+        <v>16.27965447425842</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.645407313667528</v>
+        <v>-1.594960242585724</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.1025193587764494</v>
+        <v>-0.1031111563218686</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.08985715577551669</v>
+        <v>-0.09038820843414407</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9525586338393571</v>
+        <v>0.9519257216493052</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4924536622052197</v>
+        <v>0.5242621959210253</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.08891965910287317</v>
+        <v>-0.0749954274992921</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.1472928406305677</v>
+        <v>-0.1424339494302178</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2256646070356176</v>
+        <v>0.2122067579082601</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AK10" t="n">
         <v>15.8</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>15.9</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>16</v>
       </c>
       <c r="AM10" t="n">
         <v>16.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AO10" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="AP10" t="n">
         <v>1</v>
@@ -3689,7 +3689,7 @@
         <v>18.14999961853027</v>
       </c>
       <c r="H11" t="n">
-        <v>54921800</v>
+        <v>54915600</v>
       </c>
       <c r="I11" t="n">
         <v>0.009449698635731529</v>
@@ -3722,52 +3722,52 @@
         <v>4.670906886998297</v>
       </c>
       <c r="S11" t="n">
-        <v>17.76454040527344</v>
+        <v>17.73094039916992</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2.226116933603755</v>
+        <v>2.419834699022931</v>
       </c>
       <c r="V11" t="n">
-        <v>18.56264680226644</v>
+        <v>18.5356468073527</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.16912468972457</v>
+        <v>-2.026619107737752</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.77703511238098</v>
+        <v>18.76468511581421</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.286116584838357</v>
+        <v>-3.222464244244062</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.1012769240229781</v>
+        <v>-0.101910714912627</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.0956850974985856</v>
+        <v>-0.09629602077602181</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9154076106898713</v>
+        <v>0.9148422964407825</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.3797189271431901</v>
+        <v>0.412619069231688</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.2093968224688127</v>
+        <v>-0.1955428344778047</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.2639452438843499</v>
+        <v>-0.2584415405620585</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2613062642375066</v>
+        <v>0.2463238688055936</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -4039,52 +4039,52 @@
         <v>0.5291923387609399</v>
       </c>
       <c r="S12" t="n">
-        <v>40.08419982910156</v>
+        <v>40.04179985046387</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6591129058425991</v>
+        <v>-0.5539215431573046</v>
       </c>
       <c r="V12" t="n">
-        <v>37.07446655273438</v>
+        <v>37.07759989420573</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>7.405455553041119</v>
+        <v>7.396378968550928</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.79394994735718</v>
+        <v>36.8145499420166</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.224313377053978</v>
+        <v>8.163755247697544</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.5582269127467404</v>
+        <v>-0.5619068183644437</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.7167109997947677</v>
+        <v>-0.7213922731079423</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1440643621004984</v>
+        <v>0.143253075042449</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.1461943108314532</v>
+        <v>-0.1227797088027453</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.049410492216106</v>
+        <v>1.057405284877721</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.02782429329942</v>
+        <v>1.026982831314627</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3242466690268508</v>
+        <v>0.2620005195241231</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -4356,52 +4356,52 @@
         <v>1.564525997362585</v>
       </c>
       <c r="S13" t="n">
-        <v>3.702200002670288</v>
+        <v>3.695</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>5.882990477731203</v>
+        <v>6.089311943002585</v>
       </c>
       <c r="V13" t="n">
-        <v>4.000533339182536</v>
+        <v>3.984333338737488</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.013063160849621</v>
+        <v>-1.614655626778648</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.459850006103515</v>
+        <v>4.445200005769729</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-12.10466560693207</v>
+        <v>-11.81498984959262</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.38065893089573</v>
+        <v>-0.3805653772265725</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.3474723434477559</v>
+        <v>-0.3467356002372466</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2084651907806959</v>
+        <v>0.2090060032810451</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5597250842380479</v>
+        <v>0.5836253423228204</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.113757338059997</v>
+        <v>-0.09161885060097356</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.6031600498651667</v>
+        <v>-0.590801498086851</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.5681964762456391</v>
+        <v>0.5593014524086044</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="CT13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CU13" t="n">
         <v>26</v>
@@ -4953,7 +4953,7 @@
         <v>21.35000038146973</v>
       </c>
       <c r="H15" t="n">
-        <v>1383800</v>
+        <v>1383300</v>
       </c>
       <c r="I15" t="n">
         <v>-0.01367928797598472</v>
@@ -4986,52 +4986,52 @@
         <v>-3.332148577262897</v>
       </c>
       <c r="S15" t="n">
-        <v>21.55540000915527</v>
+        <v>21.55439998626709</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.994146067663058</v>
+        <v>-2.989645451812834</v>
       </c>
       <c r="V15" t="n">
-        <v>22.56733337402344</v>
+        <v>22.54733337402344</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.343949323312756</v>
+        <v>-7.261761288799165</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.40684999465942</v>
+        <v>22.41794999122619</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-6.680323863479617</v>
+        <v>-6.726530054729615</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.212239616837981</v>
+        <v>-1.213347482043761</v>
       </c>
       <c r="AC15" t="n">
-        <v>-1.319201228483687</v>
+        <v>-1.32061745828844</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.7116010213544036</v>
+        <v>-0.7117348085547446</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.473058822158187</v>
+        <v>-0.4721409321161645</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.6176450666702652</v>
+        <v>-0.6094976074881746</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.5527082467061245</v>
+        <v>-0.5553497119546661</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.2843051239713725</v>
+        <v>0.2931230703788119</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>-1</v>
       </c>
       <c r="CR15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CS15" t="n">
         <v>1</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -5262,7 +5262,7 @@
         <v>17.30999946594238</v>
       </c>
       <c r="H16" t="n">
-        <v>2110400</v>
+        <v>2109400</v>
       </c>
       <c r="I16" t="n">
         <v>0.002881800343586649</v>
@@ -5295,52 +5295,52 @@
         <v>-3.859232773139793</v>
       </c>
       <c r="S16" t="n">
-        <v>18.8581999206543</v>
+        <v>18.84939990997314</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.732446936926046</v>
+        <v>-7.689371005789942</v>
       </c>
       <c r="V16" t="n">
-        <v>19.16919990539551</v>
+        <v>19.17526657104492</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.229390353257585</v>
+        <v>-9.258108334177431</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.45449990749359</v>
+        <v>18.47879990577698</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>-5.714055077347992</v>
+        <v>-5.838043015496053</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.7133705066438036</v>
+        <v>-0.713457882330935</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.708430454361353</v>
+        <v>-0.7083836129570611</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.5327926418563206</v>
+        <v>-0.5331579132068953</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.7868198688279323</v>
+        <v>-0.7824010965899697</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.692842203426925</v>
+        <v>-0.6948723933685953</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.4238934840183581</v>
+        <v>-0.4331523766260491</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3532921715278936</v>
+        <v>0.3489947756643143</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
         <v>4.510000228881836</v>
       </c>
       <c r="H17" t="n">
-        <v>3920800</v>
+        <v>3876200</v>
       </c>
       <c r="I17" t="n">
         <v>0.009070286448309206</v>
@@ -5868,7 +5868,7 @@
         <v>9.050000190734863</v>
       </c>
       <c r="H18" t="n">
-        <v>8740800</v>
+        <v>8736200</v>
       </c>
       <c r="I18" t="n">
         <v>0.0659955458926984</v>
@@ -5901,58 +5901,58 @@
         <v>11.27177638607244</v>
       </c>
       <c r="S18" t="n">
-        <v>9.024600028991699</v>
+        <v>8.989200019836426</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>5.6002449123051</v>
+        <v>6.016105014254717</v>
       </c>
       <c r="V18" t="n">
-        <v>10.75739999771118</v>
+        <v>10.73199999491374</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-11.40982268021214</v>
+        <v>-11.20015153291292</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.20150001049042</v>
+        <v>11.15725000858307</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-14.92211110970704</v>
+        <v>-14.58468954590122</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.610209467957791</v>
+        <v>0.6146323033914157</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5457837500345228</v>
+        <v>0.5495812137905436</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.244101484906464</v>
+        <v>1.250817300544677</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.5720255404621105</v>
+        <v>0.6175547816969432</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.929863271118886</v>
+        <v>-0.9298525233835715</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.8522573126897927</v>
+        <v>-0.8469695129722851</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.5562400903078466</v>
+        <v>0.5377602951828039</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK18" t="n">
         <v>9.300000000000001</v>
@@ -6132,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="CR18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CS18" t="n">
         <v>7</v>
@@ -6141,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -6169,7 +6169,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="H19" t="n">
-        <v>13489500</v>
+        <v>13470900</v>
       </c>
       <c r="I19" t="n">
         <v>0.007136478450831429</v>
@@ -6202,52 +6202,52 @@
         <v>4.395760256628541</v>
       </c>
       <c r="S19" t="n">
-        <v>10.92819995880127</v>
+        <v>10.91419996261597</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>3.310700796249384</v>
+        <v>3.443220763081809</v>
       </c>
       <c r="V19" t="n">
-        <v>11.51400005340576</v>
+        <v>11.50620005289714</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.945458489784147</v>
+        <v>-1.878987763555103</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43880002975464</v>
+        <v>11.43470003128052</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.300836342226037</v>
+        <v>-1.265447008068873</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.02736578641389116</v>
+        <v>-0.02753825566012564</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.1561986898219107</v>
+        <v>-0.157125474691837</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.9584634267675202</v>
+        <v>0.9573906902996971</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5914582888233946</v>
+        <v>0.61542037101418</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.2802181741520689</v>
+        <v>-0.2698946624573584</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.1841676410341563</v>
+        <v>-0.17861179075939</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.2861635592788674</v>
+        <v>0.2636959585858982</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -6470,7 +6470,7 @@
         <v>5.460000038146973</v>
       </c>
       <c r="H20" t="n">
-        <v>7186300</v>
+        <v>7185800</v>
       </c>
       <c r="I20" t="n">
         <v>-0.0146520005763966</v>
@@ -6503,52 +6503,52 @@
         <v>-11.77546311707582</v>
       </c>
       <c r="S20" t="n">
-        <v>5.86879997253418</v>
+        <v>5.873399972915649</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.328787152072506</v>
+        <v>-8.40058332056347</v>
       </c>
       <c r="V20" t="n">
-        <v>5.138466653823852</v>
+        <v>5.137799987792969</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>4.700496799708251</v>
+        <v>4.714082432624839</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.269949989318848</v>
+        <v>5.270249989032745</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.08825748527254</v>
+        <v>2.082446290717896</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.184606611980631</v>
+        <v>-3.174869197863879</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.181847512360867</v>
+        <v>-3.172288194899889</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.639223927590573</v>
+        <v>-1.636139972393222</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.8407531763173134</v>
+        <v>-0.8522537685908957</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.3957297526218312</v>
+        <v>0.3963500720581584</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.1906701064916206</v>
+        <v>0.1900144674420327</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.548339409172746</v>
+        <v>0.5263622856108116</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -6806,52 +6806,52 @@
         <v>4.511528551294189</v>
       </c>
       <c r="S21" t="n">
-        <v>2.240799999237061</v>
+        <v>2.23539999961853</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>5.765792858176138</v>
+        <v>6.021288626801518</v>
       </c>
       <c r="V21" t="n">
-        <v>2.63013333161672</v>
+        <v>2.620599999427796</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-9.890504140249648</v>
+        <v>-9.562699913127974</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.891127235889435</v>
+        <v>2.884049966335297</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-18.02505762670219</v>
+        <v>-17.82389649196708</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.2445218304788228</v>
+        <v>0.2447642026313371</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.1390316686135555</v>
+        <v>0.1391193458679484</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.5178765454369489</v>
+        <v>0.5179475274724914</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.5009147757557445</v>
+        <v>0.5235816093121592</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.4399753648902315</v>
+        <v>-0.4254585538045975</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.657097917970952</v>
+        <v>-0.6499790594689727</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.471537260986635</v>
+        <v>0.438103912372576</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -7076,7 +7076,7 @@
         <v>45.45000076293945</v>
       </c>
       <c r="H22" t="n">
-        <v>1367800</v>
+        <v>1367600</v>
       </c>
       <c r="I22" t="n">
         <v>-0.0048405108253049</v>
@@ -7109,52 +7109,52 @@
         <v>1.750377176437433</v>
       </c>
       <c r="S22" t="n">
-        <v>45.1242000579834</v>
+        <v>45.05480010986328</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2344628472459951</v>
+        <v>0.3888585277169932</v>
       </c>
       <c r="V22" t="n">
-        <v>46.77919982910156</v>
+        <v>46.73846651713053</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.311728914827379</v>
+        <v>-3.227463559039369</v>
       </c>
       <c r="Y22" t="n">
-        <v>47.94999992370605</v>
+        <v>47.92814992904663</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-5.672576404165915</v>
+        <v>-5.629573415215644</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.1122812098983095</v>
+        <v>-0.1127329399800997</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.2386153337766168</v>
+        <v>-0.2394068883721539</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.3092836600162032</v>
+        <v>0.3093124411717253</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.03014264227132549</v>
+        <v>0.04996990975566783</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.2712751324775842</v>
+        <v>-0.2641084358332368</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.4601400749133259</v>
+        <v>-0.455342233195577</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.2726732444992066</v>
+        <v>0.2592538383478873</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -7377,7 +7377,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="H23" t="n">
-        <v>10887500</v>
+        <v>10848600</v>
       </c>
       <c r="I23" t="n">
         <v>0.006879337831527055</v>
@@ -7410,52 +7410,52 @@
         <v>6.324615735075466</v>
       </c>
       <c r="S23" t="n">
-        <v>14.95099996566772</v>
+        <v>14.926399974823</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.685107474018286</v>
+        <v>7.862581792168852</v>
       </c>
       <c r="V23" t="n">
-        <v>15.06673327128092</v>
+        <v>15.06899993896484</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>6.857937228890476</v>
+        <v>6.841863738010654</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.579249958992</v>
+        <v>14.58264996051788</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.43092358492539</v>
+        <v>10.40517618581003</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1837448503463775</v>
+        <v>0.1845153381445589</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.178298327315342</v>
+        <v>0.1789347037715471</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33272275661206</v>
+        <v>1.330459828503542</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.275627255267227</v>
+        <v>1.301917725888533</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.9519083898669893</v>
+        <v>0.943437372039337</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.319161328282433</v>
+        <v>1.307509507173027</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.224367202566961</v>
+        <v>0.1924425071210879</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
         <v>3.690000057220459</v>
       </c>
       <c r="H24" t="n">
-        <v>21611300</v>
+        <v>21603500</v>
       </c>
       <c r="I24" t="n">
         <v>0.0273972334300725</v>
@@ -7711,52 +7711,52 @@
         <v>2.739725666037057</v>
       </c>
       <c r="S24" t="n">
-        <v>3.737200026512146</v>
+        <v>3.724800024032593</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3425016963782929</v>
+        <v>0.6765457421825494</v>
       </c>
       <c r="V24" t="n">
-        <v>4.472600005467733</v>
+        <v>4.454866671562195</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-16.15615088727715</v>
+        <v>-15.822396572758</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.762300012111663</v>
+        <v>4.748750013113022</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-21.25653590779966</v>
+        <v>-21.03185070502997</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.3230633976555563</v>
+        <v>0.325234866158715</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.1910855497940493</v>
+        <v>0.1921896333117528</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.3134746401215354</v>
+        <v>0.3181335004943182</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.03492353742401648</v>
+        <v>0.07032541270725834</v>
       </c>
       <c r="AF24" t="n">
-        <v>-1.522758032136386</v>
+        <v>-1.504096362001155</v>
       </c>
       <c r="AG24" t="n">
-        <v>-2.07251744793016</v>
+        <v>-2.06576336037912</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.6302354068756053</v>
+        <v>0.5850108321424783</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>56.79000091552734</v>
       </c>
       <c r="H25" t="n">
-        <v>4384300</v>
+        <v>4381800</v>
       </c>
       <c r="I25" t="n">
         <v>0.00654524596801398</v>
@@ -8016,52 +8016,52 @@
         <v>2.185447690911127</v>
       </c>
       <c r="S25" t="n">
-        <v>59.28919982910156</v>
+        <v>59.1515998840332</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.029736124132914</v>
+        <v>-3.806487673314938</v>
       </c>
       <c r="V25" t="n">
-        <v>57.20099983215332</v>
+        <v>57.22839983622233</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5262116172053709</v>
+        <v>-0.5738380092458331</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.46119989395142</v>
+        <v>54.55589988708496</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.478053433777445</v>
+        <v>4.29669686256768</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.2351075870185702</v>
+        <v>0.2372189942330831</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2057031564946487</v>
+        <v>0.2075044625296247</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.3578473112754739</v>
+        <v>0.36001199767248</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.4731165284346543</v>
+        <v>-0.4473646770042607</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.0352617738922367</v>
+        <v>-0.03829314629863563</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.2758414904589374</v>
+        <v>0.2631379184201178</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.321145894208229</v>
+        <v>0.2900253742811123</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -8247,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="CR25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CS25" t="n">
         <v>6</v>
@@ -8256,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="CU25" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -8284,7 +8284,7 @@
         <v>5.889999866485596</v>
       </c>
       <c r="H26" t="n">
-        <v>20610300</v>
+        <v>20597400</v>
       </c>
       <c r="I26" t="n">
         <v>0.0649572855787568</v>
@@ -8317,52 +8317,52 @@
         <v>9.394206356039376</v>
       </c>
       <c r="S26" t="n">
-        <v>5.364999980926513</v>
+        <v>5.350599985122681</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>16.12302033964949</v>
+        <v>16.43554061966832</v>
       </c>
       <c r="V26" t="n">
-        <v>6.095066655476888</v>
+        <v>6.0667999903361</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>2.21381276405485</v>
+        <v>2.690051246082784</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.957600002288818</v>
+        <v>6.937700004577636</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-10.45762882281212</v>
+        <v>-10.20078678866476</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.6487629548414408</v>
+        <v>-0.6493167425968289</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.6415469119985115</v>
+        <v>-0.6423258481884627</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.8852632379457148</v>
+        <v>0.8807453168770116</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.194173514497263</v>
+        <v>1.215176795684967</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.1221283010242489</v>
+        <v>0.1478184626132261</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.5885491245913647</v>
+        <v>-0.5716752310867564</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.7253931916733978</v>
+        <v>0.701928189522034</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         <v>29.31999969482422</v>
       </c>
       <c r="H27" t="n">
-        <v>6082200</v>
+        <v>6081200</v>
       </c>
       <c r="I27" t="n">
         <v>-0.0003441763096656558</v>
@@ -8618,52 +8618,52 @@
         <v>-8.024018991319664</v>
       </c>
       <c r="S27" t="n">
-        <v>31.37100006103516</v>
+        <v>31.32060009002685</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-7.430426639165604</v>
+        <v>-7.281467047068814</v>
       </c>
       <c r="V27" t="n">
-        <v>33.15466673533122</v>
+        <v>33.1031334177653</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-12.41051780930462</v>
+        <v>-12.27416284422614</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.49314999580383</v>
+        <v>33.4597500038147</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-13.29570100403933</v>
+        <v>-13.20915155607398</v>
       </c>
       <c r="AB27" t="n">
-        <v>-1.360437033680623</v>
+        <v>-1.360444452603744</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.484791663921764</v>
+        <v>-1.48442823818384</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.170974099679917</v>
+        <v>-1.171864958637126</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.9671954553538898</v>
+        <v>-0.9485342047415117</v>
       </c>
       <c r="AF27" t="n">
-        <v>-1.184302520116191</v>
+        <v>-1.175466358058443</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.007962087393677</v>
+        <v>-1.005373729319348</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.4494808268785201</v>
+        <v>0.4506621016709072</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -8886,7 +8886,7 @@
         <v>20.69000053405762</v>
       </c>
       <c r="H28" t="n">
-        <v>3091700</v>
+        <v>3090500</v>
       </c>
       <c r="I28" t="n">
         <v>-0.002422443727669088</v>
@@ -8919,52 +8919,52 @@
         <v>6.058325887043142</v>
       </c>
       <c r="S28" t="n">
-        <v>20.05780002593994</v>
+        <v>19.99540004730225</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>2.653332498876634</v>
+        <v>2.973684466822486</v>
       </c>
       <c r="V28" t="n">
-        <v>18.93820007324219</v>
+        <v>18.94260007222493</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>8.722054223513753</v>
+        <v>8.696800196814051</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.37435008525848</v>
+        <v>18.38805008411407</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.05838604929485</v>
+        <v>11.97489705760667</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.6456847079037762</v>
+        <v>0.6496753423466032</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.586896286810208</v>
+        <v>0.590244854669137</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.260497231103547</v>
+        <v>1.25847201167288</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.4898067160263702</v>
+        <v>0.5458186459304782</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.302580143665146</v>
+        <v>1.305013932186879</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.624332600004869</v>
+        <v>1.624373509040338</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.2586108286549333</v>
+        <v>0.2363157937110793</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -9162,7 +9162,7 @@
         <v>0</v>
       </c>
       <c r="CR28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CS28" t="n">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>0</v>
       </c>
       <c r="CU28" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -9199,7 +9199,7 @@
         <v>26.81999969482422</v>
       </c>
       <c r="H29" t="n">
-        <v>8545400</v>
+        <v>8543600</v>
       </c>
       <c r="I29" t="n">
         <v>0.03674538955503848</v>
@@ -9232,52 +9232,52 @@
         <v>12.88904058809547</v>
       </c>
       <c r="S29" t="n">
-        <v>23.04720008850098</v>
+        <v>23.01520008087158</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>19.97118744296315</v>
+        <v>20.13799367971069</v>
       </c>
       <c r="V29" t="n">
-        <v>24.44180001576742</v>
+        <v>24.37933334350586</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>13.12587289272167</v>
+        <v>13.41573302657864</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.77855000495911</v>
+        <v>25.70720000267029</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.259716365781428</v>
+        <v>7.557414326173919</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.317492144194036</v>
+        <v>1.319109228421315</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.273385601568258</v>
+        <v>1.275148202413399</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.451327875148598</v>
+        <v>1.457279120036153</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.90132099119185</v>
+        <v>1.925486340823989</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.8097201133772939</v>
+        <v>0.8303361228125413</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.3805709742167397</v>
+        <v>0.3977031532128437</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.437301222272269</v>
+        <v>0.4276857659531279</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -9500,7 +9500,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="H30" t="n">
-        <v>12755100</v>
+        <v>12755000</v>
       </c>
       <c r="I30" t="n">
         <v>0.01293533452474604</v>
@@ -9533,52 +9533,52 @@
         <v>-5.05434383577899</v>
       </c>
       <c r="S30" t="n">
-        <v>11.22280004501343</v>
+        <v>11.18360004425049</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-9.291796482652188</v>
+        <v>-8.973852204153701</v>
       </c>
       <c r="V30" t="n">
-        <v>13.01906669616699</v>
+        <v>12.98886669158936</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.80698860562006</v>
+        <v>-21.62518449921726</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.51765002250671</v>
+        <v>13.48170001983643</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-24.6910499367404</v>
+        <v>-24.49023275849973</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.3782266435402135</v>
+        <v>-0.3788294478975667</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.5779707861475664</v>
+        <v>-0.5785728006493669</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.6532510661195582</v>
+        <v>-0.6546198790889782</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.9997202248002918</v>
+        <v>-0.9692752995463314</v>
       </c>
       <c r="AF30" t="n">
-        <v>-1.435061324121438</v>
+        <v>-1.428500649086624</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.272319476748295</v>
+        <v>-1.266089822432565</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.4022796022317656</v>
+        <v>0.3884211844162983</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -9797,7 +9797,7 @@
         <v>30.70000076293945</v>
       </c>
       <c r="H31" t="n">
-        <v>4371500</v>
+        <v>4357000</v>
       </c>
       <c r="I31" t="n">
         <v>-0.002303379277067807</v>
@@ -9830,52 +9830,52 @@
         <v>2.905777163740402</v>
       </c>
       <c r="S31" t="n">
-        <v>29.80859992980957</v>
+        <v>29.72199989318848</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.715611488694011</v>
+        <v>2.011976999477706</v>
       </c>
       <c r="V31" t="n">
-        <v>32.3395333480835</v>
+        <v>32.3070000076294</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-6.244782914837458</v>
+        <v>-6.150370855653397</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.15485002517701</v>
+        <v>32.14790002822876</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-5.706294163761026</v>
+        <v>-5.685908976323433</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.3940992271186826</v>
+        <v>-0.3952105717209055</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.3966560036684417</v>
+        <v>-0.3976480478929525</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.6154393947408086</v>
+        <v>0.616186799004663</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.3249779815272001</v>
+        <v>0.3806755857422457</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.8184712946363601</v>
+        <v>-0.8021556130684159</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.7611847111323091</v>
+        <v>-0.7537636312045319</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.2226221093685613</v>
+        <v>0.218351664051616</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
         <v>97.44999694824219</v>
       </c>
       <c r="H32" t="n">
-        <v>4893500</v>
+        <v>4893200</v>
       </c>
       <c r="I32" t="n">
         <v>0.01411202195454897</v>
@@ -10127,52 +10127,52 @@
         <v>1.960578256370206</v>
       </c>
       <c r="S32" t="n">
-        <v>91.99159988403321</v>
+        <v>92.19279998779297</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>7.020637832531003</v>
+        <v>6.787077690749952</v>
       </c>
       <c r="V32" t="n">
-        <v>83.9776665242513</v>
+        <v>83.98606653849284</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>17.23354675473332</v>
+        <v>17.22182143524984</v>
       </c>
       <c r="Y32" t="n">
-        <v>86.14489986419677</v>
+        <v>86.19799987792969</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>14.28418525466255</v>
+        <v>14.213783484145</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.6082682429979285</v>
+        <v>0.6119087868949853</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.6269960369836266</v>
+        <v>0.63066354385363</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.3065002358212469</v>
+        <v>0.3071178543061867</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.835227003873132</v>
+        <v>0.8085632105528936</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.471484773520246</v>
+        <v>1.469178626801859</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.153269577006925</v>
+        <v>1.147899749773983</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.2332956120462439</v>
+        <v>0.2515251104678772</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -10399,7 +10399,7 @@
         <v>27.5</v>
       </c>
       <c r="H33" t="n">
-        <v>11720900</v>
+        <v>11715900</v>
       </c>
       <c r="I33" t="n">
         <v>0.03096204123008728</v>
@@ -10432,52 +10432,52 @@
         <v>5.446159311561476</v>
       </c>
       <c r="S33" t="n">
-        <v>26.27599998474121</v>
+        <v>26.23139999389648</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>6.44694523366192</v>
+        <v>6.627931867390015</v>
       </c>
       <c r="V33" t="n">
-        <v>25.20199996948242</v>
+        <v>25.238533299764</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>10.98325270702283</v>
+        <v>10.82260201553011</v>
       </c>
       <c r="Y33" t="n">
-        <v>24.06999999046326</v>
+        <v>24.09724998474121</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>16.2027391958307</v>
+        <v>16.07133316484484</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.716408361448278</v>
+        <v>0.7176648681562425</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.6446978625751144</v>
+        <v>0.6453879520024316</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.055433824333248</v>
+        <v>1.054848809654884</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.9769270849338925</v>
+        <v>1.002765693496409</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.213089934247925</v>
+        <v>1.186257255471388</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.634283772540166</v>
+        <v>1.60781436152567</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.3025533065011078</v>
+        <v>0.2693705593677044</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
         <v>52.61000061035156</v>
       </c>
       <c r="H34" t="n">
-        <v>2547200</v>
+        <v>2546200</v>
       </c>
       <c r="I34" t="n">
         <v>0.01401688779897547</v>
@@ -11001,7 +11001,7 @@
         <v>39.79999923706055</v>
       </c>
       <c r="H35" t="n">
-        <v>7565100</v>
+        <v>7563400</v>
       </c>
       <c r="I35" t="n">
         <v>0.01592117950401795</v>
@@ -11034,52 +11034,52 @@
         <v>6.814373870557414</v>
       </c>
       <c r="S35" t="n">
-        <v>38.13980018615722</v>
+        <v>38.05700019836426</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>5.401707839911483</v>
+        <v>5.631028597643661</v>
       </c>
       <c r="V35" t="n">
-        <v>39.75686676025391</v>
+        <v>39.72620010375977</v>
       </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.114609975071176</v>
+        <v>1.19266543979082</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.67150005340577</v>
+        <v>39.65655006408691</v>
       </c>
       <c r="Z35" t="n">
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.332192402158276</v>
+        <v>1.370393284272827</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.620968372743018</v>
+        <v>0.6254755153505412</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.6161381729656148</v>
+        <v>0.6198812151271786</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.608877297989849</v>
+        <v>1.606759193047761</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.167880677709681</v>
+        <v>1.215091291177712</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.1694605681697188</v>
+        <v>0.1804380990089677</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.1914384219146938</v>
+        <v>0.1958393117946745</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.2659328512079474</v>
+        <v>0.2363949384737131</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -11300,7 +11300,7 @@
         <v>21.57999992370605</v>
       </c>
       <c r="H36" t="n">
-        <v>3443900</v>
+        <v>3439800</v>
       </c>
       <c r="I36" t="n">
         <v>0.02806362979521348</v>
@@ -11333,52 +11333,52 @@
         <v>11.22399151701486</v>
       </c>
       <c r="S36" t="n">
-        <v>18.45879993438721</v>
+        <v>18.50679992675781</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>19.07599421612137</v>
+        <v>18.76715385276758</v>
       </c>
       <c r="V36" t="n">
-        <v>16.79919995625814</v>
+        <v>16.80906661987305</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>30.83956140451918</v>
+        <v>30.76276059403432</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.5166999912262</v>
+        <v>16.53054999351501</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>33.07742802080488</v>
+        <v>32.96593005592162</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.247954195121343</v>
+        <v>1.239688370204287</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.253346416760127</v>
+        <v>1.245115415187782</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.165563766021403</v>
+        <v>2.172565944389386</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.788584895101424</v>
+        <v>2.758945315307165</v>
       </c>
       <c r="AF36" t="n">
-        <v>3.748944719440733</v>
+        <v>3.756160749134813</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.790820910946816</v>
+        <v>3.792375637909082</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.3762719158109005</v>
+        <v>0.263202233473645</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -11601,7 +11601,7 @@
         <v>25.51000022888184</v>
       </c>
       <c r="H37" t="n">
-        <v>6936600</v>
+        <v>6935900</v>
       </c>
       <c r="I37" t="n">
         <v>0.007103405844194555</v>
@@ -11634,52 +11634,52 @@
         <v>4.250005910362389</v>
       </c>
       <c r="S37" t="n">
-        <v>24.47939994812012</v>
+        <v>24.52419994354248</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>4.250923273646117</v>
+        <v>4.060481143171389</v>
       </c>
       <c r="V37" t="n">
-        <v>22.47086666107178</v>
+        <v>22.49126665751139</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>13.56927546534808</v>
+        <v>13.46626602393145</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.15699999809265</v>
+        <v>22.18804999351502</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>15.17804964553197</v>
+        <v>15.01686928424309</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.1645539909283379</v>
+        <v>-0.164699573349243</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.157314357018857</v>
+        <v>-0.1575712008929012</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.6891895390451314</v>
+        <v>0.6876097153773777</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.5662507518312996</v>
+        <v>0.5408330878462497</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.76187811875646</v>
+        <v>1.751457238329065</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.782173841402898</v>
+        <v>1.772005649759915</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.3933296352723151</v>
+        <v>0.3943548858774911</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -11902,7 +11902,7 @@
         <v>11.53999996185303</v>
       </c>
       <c r="H38" t="n">
-        <v>9315900</v>
+        <v>9306100</v>
       </c>
       <c r="I38" t="n">
         <v>0.003502623606462141</v>
@@ -11935,52 +11935,52 @@
         <v>5.569727971463942</v>
       </c>
       <c r="S38" t="n">
-        <v>10.79140001296997</v>
+        <v>10.81020000457764</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>6.195674559125083</v>
+        <v>6.010989928902104</v>
       </c>
       <c r="V38" t="n">
-        <v>9.919066667556763</v>
+        <v>9.926399997075398</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>15.53506415709744</v>
+        <v>15.44971028291643</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.770178511142731</v>
+        <v>9.784677479267121</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>17.29570780182805</v>
+        <v>17.12189862598655</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.02224103155842221</v>
+        <v>-0.02222843460062321</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.04780192084853826</v>
+        <v>0.04781093075119294</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.9595876869364452</v>
+        <v>0.956849240689816</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.8716516459180718</v>
+        <v>0.8454657162098207</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.932335556671461</v>
+        <v>1.92431257498133</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.981886377130276</v>
+        <v>1.971994809309103</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.3841959478051145</v>
+        <v>0.3920930477106866</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
         <v>6.269999980926514</v>
       </c>
       <c r="H39" t="n">
-        <v>9973000</v>
+        <v>9929400</v>
       </c>
       <c r="I39" t="n">
         <v>0.08051529741201047</v>
@@ -12240,52 +12240,52 @@
         <v>0.5301374615681963</v>
       </c>
       <c r="S39" t="n">
-        <v>8.595800008773804</v>
+        <v>8.589800004959107</v>
       </c>
       <c r="T39" t="n">
         <v>-1</v>
       </c>
       <c r="U39" t="n">
-        <v>-21.93862082298308</v>
+        <v>-21.88409469052689</v>
       </c>
       <c r="V39" t="n">
-        <v>10.22873332023621</v>
+        <v>10.22593331972758</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-34.40047923752085</v>
+        <v>-34.38251719085405</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.14934999227524</v>
+        <v>11.13034999132156</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-39.81711899979858</v>
+        <v>-39.71438415342895</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.03820570549494683</v>
+        <v>0.03850496617564706</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.04915731854717931</v>
+        <v>-0.04948962575026658</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.03722383394726755</v>
+        <v>0.03726064190840229</v>
       </c>
       <c r="AE39" t="n">
-        <v>-1.21212165522608</v>
+        <v>-1.211475177367677</v>
       </c>
       <c r="AF39" t="n">
-        <v>-1.63160419472359</v>
+        <v>-1.637949966599985</v>
       </c>
       <c r="AG39" t="n">
-        <v>-2.03377361319278</v>
+        <v>-2.050427501506079</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.160713286698636</v>
+        <v>1.144973230333448</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -12512,7 +12512,7 @@
         <v>23.95000076293945</v>
       </c>
       <c r="H40" t="n">
-        <v>5146800</v>
+        <v>5145900</v>
       </c>
       <c r="I40" t="n">
         <v>0.01344544590045849</v>
@@ -12545,52 +12545,52 @@
         <v>8.352054864149636</v>
       </c>
       <c r="S40" t="n">
-        <v>21.71320003509522</v>
+        <v>21.72400001525879</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>11.08450527903787</v>
+        <v>11.02928016153414</v>
       </c>
       <c r="V40" t="n">
-        <v>22.08686669667562</v>
+        <v>22.07473336537679</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>9.205172333764283</v>
+        <v>9.265196729689686</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.61440001487732</v>
+        <v>22.58865001678467</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>6.657708466134812</v>
+        <v>6.77929323492483</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.10263691351542</v>
+        <v>1.102426454404388</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.078342170220248</v>
+        <v>1.07817854708279</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.701412869977219</v>
+        <v>1.701946534338219</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.996043714075441</v>
+        <v>1.991801932138089</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.750094784006003</v>
+        <v>1.759760690111139</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.012009202647645</v>
+        <v>1.031731577422822</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.2590011598630133</v>
+        <v>0.2597363229629378</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -12809,7 +12809,7 @@
         <v>26.39999961853027</v>
       </c>
       <c r="H41" t="n">
-        <v>3922600</v>
+        <v>3918500</v>
       </c>
       <c r="I41" t="n">
         <v>0.02784139850122558</v>
@@ -13106,7 +13106,7 @@
         <v>27.65999984741211</v>
       </c>
       <c r="H42" t="n">
-        <v>1326900</v>
+        <v>1324900</v>
       </c>
       <c r="I42" t="n">
         <v>-0.0007301405936721572</v>
@@ -13139,52 +13139,52 @@
         <v>1.923548492498498</v>
       </c>
       <c r="S42" t="n">
-        <v>27.07520004272461</v>
+        <v>26.99260005950928</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.088822228621001</v>
+        <v>1.398163863029432</v>
       </c>
       <c r="V42" t="n">
-        <v>28.14280002593994</v>
+        <v>28.11320003509521</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.745992530928813</v>
+        <v>-2.643595161468779</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98550001144409</v>
+        <v>27.97560001373291</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-2.199350277675931</v>
+        <v>-2.164740610397029</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.2148616253255731</v>
+        <v>-0.2151480605539819</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.2602106654821314</v>
+        <v>-0.2605272615590754</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.4689759450087688</v>
+        <v>0.4683237698948549</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.224042536104468</v>
+        <v>0.2867825815607853</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.3542685568832149</v>
+        <v>-0.3390830765342459</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.2775416727202476</v>
+        <v>-0.2715235420336072</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.1899243496435677</v>
+        <v>0.1705193944045834</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
         <v>14.14999961853027</v>
       </c>
       <c r="H43" t="n">
-        <v>25940600</v>
+        <v>25938100</v>
       </c>
       <c r="I43" t="n">
         <v>0.02209553995130764</v>
@@ -13436,52 +13436,52 @@
         <v>7.295176057614297</v>
       </c>
       <c r="S43" t="n">
-        <v>13.46099988937378</v>
+        <v>13.43999988555908</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>6.529977493781878</v>
+        <v>6.696430615269828</v>
       </c>
       <c r="V43" t="n">
-        <v>13.54773330052694</v>
+        <v>13.53739996592204</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>5.84796610980036</v>
+        <v>5.928761717067189</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.285950922966</v>
+        <v>13.29110974788666</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>7.933562570970095</v>
+        <v>7.891669127688984</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.5371765579269737</v>
+        <v>0.5401657167920711</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.4856791336937922</v>
+        <v>0.4881122750970288</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.435844258578199</v>
+        <v>1.434297360392608</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.123526124466749</v>
+        <v>1.150049131086902</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.7085521674196077</v>
+        <v>0.7158053845409473</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.9863381218213474</v>
+        <v>0.9767703399785741</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.2549955990630993</v>
+        <v>0.2357205194957963</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -13704,7 +13704,7 @@
         <v>42.70000076293945</v>
       </c>
       <c r="H44" t="n">
-        <v>15617100</v>
+        <v>15599600</v>
       </c>
       <c r="I44" t="n">
         <v>0.01771792977929376</v>
@@ -13737,52 +13737,52 @@
         <v>6.134521537287086</v>
       </c>
       <c r="S44" t="n">
-        <v>41.31599975585937</v>
+        <v>41.23839973449707</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>4.269537432517645</v>
+        <v>4.465745781636293</v>
       </c>
       <c r="V44" t="n">
-        <v>42.28379989624023</v>
+        <v>42.23166653951009</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.882995229303531</v>
+        <v>2.008765841032885</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.0758076095581</v>
+        <v>42.07577167510986</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.386630889690793</v>
+        <v>2.386718332105795</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.5212883866575155</v>
+        <v>0.5241581709775137</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.4874919773967288</v>
+        <v>0.4899911877143477</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.180012504095202</v>
+        <v>1.179683491314194</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.7193335145618122</v>
+        <v>0.7514301010256084</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.2246099782394237</v>
+        <v>0.2390260240967221</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.2759722515712182</v>
+        <v>0.2750583955252236</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.268839009198555</v>
+        <v>0.247111566516859</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -14021,7 +14021,7 @@
         <v>19.23999977111816</v>
       </c>
       <c r="H45" t="n">
-        <v>3742600</v>
+        <v>3738600</v>
       </c>
       <c r="I45" t="n">
         <v>0.002612390073336357</v>
@@ -14293,7 +14293,7 @@
         <v>3</v>
       </c>
       <c r="CT45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU45" t="n">
         <v>58</v>
@@ -14324,7 +14324,7 @@
         <v>11.32999992370605</v>
       </c>
       <c r="H46" t="n">
-        <v>12994000</v>
+        <v>12988700</v>
       </c>
       <c r="I46" t="n">
         <v>0.03760072277755033</v>
@@ -14357,52 +14357,52 @@
         <v>4.450607960930725</v>
       </c>
       <c r="S46" t="n">
-        <v>12.19880001068115</v>
+        <v>12.14880001068115</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-4.990653650852562</v>
+        <v>-4.599630067183322</v>
       </c>
       <c r="V46" t="n">
-        <v>13.95486671447754</v>
+        <v>13.93506671269735</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-16.94653636093999</v>
+        <v>-16.82852768815724</v>
       </c>
       <c r="Y46" t="n">
-        <v>14.03725004196167</v>
+        <v>14.01910004138947</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-17.43396948874028</v>
+        <v>-17.32707436019425</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.642962770077437</v>
+        <v>0.6538725660316383</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.5415236046173959</v>
+        <v>0.550454094254042</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.7475578042040817</v>
+        <v>0.7529051374884176</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.7139024327900569</v>
+        <v>-0.6607950276559758</v>
       </c>
       <c r="AF46" t="n">
-        <v>-2.015418488432256</v>
+        <v>-2.011626734618257</v>
       </c>
       <c r="AG46" t="n">
-        <v>-2.285032090259118</v>
+        <v>-2.296199473255405</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.4393281141776098</v>
+        <v>0.3716126672431861</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -14629,7 +14629,7 @@
         <v>16.89999961853027</v>
       </c>
       <c r="H47" t="n">
-        <v>5292400</v>
+        <v>5292300</v>
       </c>
       <c r="I47" t="n">
         <v>-0.0005934853801448092</v>
@@ -14662,52 +14662,52 @@
         <v>-4.359981897603321</v>
       </c>
       <c r="S47" t="n">
-        <v>16.88680004119873</v>
+        <v>16.8946000289917</v>
       </c>
       <c r="T47" t="n">
         <v>-1</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.2771388806444121</v>
+        <v>-0.3231794556255512</v>
       </c>
       <c r="V47" t="n">
-        <v>17.53086671193441</v>
+        <v>17.51100004196167</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-3.940857977524861</v>
+        <v>-3.831876464884124</v>
       </c>
       <c r="Y47" t="n">
-        <v>17.98830006599426</v>
+        <v>17.97135006427765</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-6.383593275593398</v>
+        <v>-6.295297279521504</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1609192882235565</v>
+        <v>-0.1618246096471876</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.2000573356627818</v>
+        <v>-0.2011595492366524</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.4379907107850664</v>
+        <v>-0.4410997288371403</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.02671456003247998</v>
+        <v>-0.03141540284716896</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.4257490212343493</v>
+        <v>-0.4283797653144042</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.7078786332101932</v>
+        <v>-0.7360100611100862</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.4472670236266433</v>
+        <v>0.4432672308593432</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -14731,7 +14731,7 @@
         <v>17.2</v>
       </c>
       <c r="AP47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ47" t="n">
         <v>0</v>
@@ -14930,7 +14930,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="H48" t="n">
-        <v>22045000</v>
+        <v>22044900</v>
       </c>
       <c r="I48" t="n">
         <v>0.02222224214704216</v>
@@ -14963,52 +14963,52 @@
         <v>18.36175357132416</v>
       </c>
       <c r="S48" t="n">
-        <v>4.926000037193298</v>
+        <v>4.908000044822693</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>21.39667019736217</v>
+        <v>21.84189006643583</v>
       </c>
       <c r="V48" t="n">
-        <v>6.664733319282532</v>
+        <v>6.625866656303406</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-10.27397897869315</v>
+        <v>-9.747655223569661</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.346607073545456</v>
+        <v>7.319254695177078</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-18.60188030734639</v>
+        <v>-18.29769193557474</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.5731221137260867</v>
+        <v>0.5796184061520501</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.5165696245879772</v>
+        <v>0.5226344849700656</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.471293580814566</v>
+        <v>1.490068957903808</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.358345347071243</v>
+        <v>1.404597267809298</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.4658259696110706</v>
+        <v>-0.4424510155980234</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.8010779405007998</v>
+        <v>-0.7890206621238132</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.8390912807059802</v>
+        <v>0.8251000449830916</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -15235,7 +15235,7 @@
         <v>16.34000015258789</v>
       </c>
       <c r="H49" t="n">
-        <v>13518000</v>
+        <v>13517900</v>
       </c>
       <c r="I49" t="n">
         <v>0.02230487137331938</v>
@@ -15268,52 +15268,52 @@
         <v>6.597092857079846</v>
       </c>
       <c r="S49" t="n">
-        <v>15.07659997940064</v>
+        <v>15.06099998474121</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>9.441120826606635</v>
+        <v>9.554478565279116</v>
       </c>
       <c r="V49" t="n">
-        <v>15.27033336003621</v>
+        <v>15.25513336181641</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>8.052650921046224</v>
+        <v>8.160313047799987</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.42635001659393</v>
+        <v>15.41835001468658</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>6.959844566285319</v>
+        <v>7.015342006655064</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.2820549973568594</v>
+        <v>0.2826345923857537</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.280555315173779</v>
+        <v>0.2809613084867227</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.257099875445642</v>
+        <v>1.257086646952862</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.589860536148671</v>
+        <v>1.615007957821614</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.90116128567502</v>
+        <v>0.9129911223935947</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.6850195782567495</v>
+        <v>0.690294801661564</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.306540447913865</v>
+        <v>0.2983282139687472</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -15540,7 +15540,7 @@
         <v>5.309999942779541</v>
       </c>
       <c r="H50" t="n">
-        <v>16567300</v>
+        <v>16567000</v>
       </c>
       <c r="I50" t="n">
         <v>0.005736177762703853</v>
@@ -15573,52 +15573,52 @@
         <v>-2.118519021742986</v>
       </c>
       <c r="S50" t="n">
-        <v>5.019000024795532</v>
+        <v>5.006400022506714</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>4.801757379870146</v>
+        <v>5.065520238795138</v>
       </c>
       <c r="V50" t="n">
-        <v>6.391466671625773</v>
+        <v>6.355000003178914</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-17.70276684328122</v>
+        <v>-17.23052358378182</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.855950014591217</v>
+        <v>6.831350014209748</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-23.27831711597651</v>
+        <v>-23.00203886580808</v>
       </c>
       <c r="AB50" t="n">
-        <v>-1.047126467055435</v>
+        <v>-1.043687830590389</v>
       </c>
       <c r="AC50" t="n">
-        <v>-1.053491951592909</v>
+        <v>-1.049753676828963</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2128572507118078</v>
+        <v>-0.212286932826452</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.373795022333221</v>
+        <v>0.3939472757786474</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.7696440162783574</v>
+        <v>-0.7493211276971526</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.8867117593975332</v>
+        <v>-0.8751654272500515</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.6246395507191262</v>
+        <v>0.6131238660108328</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>30.92000007629395</v>
       </c>
       <c r="H51" t="n">
-        <v>6271400</v>
+        <v>6269400</v>
       </c>
       <c r="I51" t="n">
         <v>0.02838501957786055</v>
@@ -16146,7 +16146,7 @@
         <v>8.020000457763672</v>
       </c>
       <c r="H52" t="n">
-        <v>5634600</v>
+        <v>5633700</v>
       </c>
       <c r="I52" t="n">
         <v>0.001259414606122666</v>
@@ -16179,48 +16179,48 @@
         <v>-4.764100005610048</v>
       </c>
       <c r="S52" t="n">
-        <v>8.388400011062622</v>
+        <v>8.376400003433227</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-5.226267240705294</v>
+        <v>-5.090494651560603</v>
       </c>
       <c r="V52" t="n">
-        <v>9.077266642252605</v>
+        <v>9.07006664276123</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-12.41857133225875</v>
+        <v>-12.34904745038464</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.813649971485138</v>
+        <v>8.812599971294404</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-9.799006824802143</v>
+        <v>-9.788259592390954</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.5415513144114891</v>
+        <v>-0.5422696509481557</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.6938973125277728</v>
+        <v>-0.6945868689915646</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.6641537462086581</v>
+        <v>-0.6634383096600078</v>
       </c>
       <c r="AE52" t="n">
-        <v>-0.5847879270405927</v>
+        <v>-0.5699917633924008</v>
       </c>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>0.4339350253315741</v>
+        <v>0.4393318765980768</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -16447,7 +16447,7 @@
         <v>53.09999847412109</v>
       </c>
       <c r="H53" t="n">
-        <v>8866100</v>
+        <v>8866000</v>
       </c>
       <c r="I53" t="n">
         <v>-0.009923212522206293</v>
@@ -16480,52 +16480,52 @@
         <v>3.795081355076683</v>
       </c>
       <c r="S53" t="n">
-        <v>48.94179985046387</v>
+        <v>49.00219985961914</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>8.046702879101497</v>
+        <v>7.913524738899823</v>
       </c>
       <c r="V53" t="n">
-        <v>48.29539995829264</v>
+        <v>48.34486661275228</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>9.49283185102888</v>
+        <v>9.380798362088544</v>
       </c>
       <c r="Y53" t="n">
-        <v>44.94874999046326</v>
+        <v>45.01789998054505</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>17.64509820481047</v>
+        <v>17.46438881193454</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0.7404330370198067</v>
+        <v>-0.7410149574778326</v>
       </c>
       <c r="AC53" t="n">
-        <v>-0.6409398604732842</v>
+        <v>-0.6410601951776985</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.5643926342361434</v>
+        <v>0.564169361530822</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.7904244696470886</v>
+        <v>0.7783614862818163</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.6062494588362448</v>
+        <v>0.599568567188176</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.015787020998282</v>
+        <v>1.008189454817693</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.3615830265705866</v>
+        <v>0.3553763210383464</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -16748,7 +16748,7 @@
         <v>48.20999908447266</v>
       </c>
       <c r="H54" t="n">
-        <v>28539400</v>
+        <v>28538400</v>
       </c>
       <c r="I54" t="n">
         <v>-0.01030927835051543</v>
@@ -16781,52 +16781,52 @@
         <v>4.649700289163042</v>
       </c>
       <c r="S54" t="n">
-        <v>43.82840003967285</v>
+        <v>43.88</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>9.518029306456718</v>
+        <v>9.38924339106654</v>
       </c>
       <c r="V54" t="n">
-        <v>43.58659996032715</v>
+        <v>43.62073328653971</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>10.12558915742444</v>
+        <v>10.0394156253481</v>
       </c>
       <c r="Y54" t="n">
-        <v>40.92450003623962</v>
+        <v>40.97670002937317</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>17.28915431464002</v>
+        <v>17.13974030508153</v>
       </c>
       <c r="AB54" t="n">
-        <v>-0.589852879907408</v>
+        <v>-0.5903510682865798</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.4993838772662721</v>
+        <v>-0.4995288037097482</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.7342244126645718</v>
+        <v>0.734206693623596</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.9924615599945612</v>
+        <v>0.9805306990608778</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.7082714055386972</v>
+        <v>0.7027377149501161</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.094150992613131</v>
+        <v>1.087774693276895</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.3337087256241969</v>
+        <v>0.3299524117289683</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -17049,7 +17049,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="H55" t="n">
-        <v>28682400</v>
+        <v>28681400</v>
       </c>
       <c r="I55" t="n">
         <v>-0.01168228698220142</v>
@@ -17082,52 +17082,52 @@
         <v>-4.014661747999956</v>
       </c>
       <c r="S55" t="n">
-        <v>4.739799995422363</v>
+        <v>4.711799993515014</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-10.75572760119065</v>
+        <v>-10.22539104173868</v>
       </c>
       <c r="V55" t="n">
-        <v>5.718599993387858</v>
+        <v>5.70559999148051</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-26.03084629167224</v>
+        <v>-25.86231026728758</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.795599944591523</v>
+        <v>5.788240854740143</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-27.01359549461416</v>
+        <v>-26.92080158327503</v>
       </c>
       <c r="AB55" t="n">
-        <v>-1.049494455448156</v>
+        <v>-1.05854354345148</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.075565668678847</v>
+        <v>-1.084642823479867</v>
       </c>
       <c r="AD55" t="n">
-        <v>-0.6207558190449566</v>
+        <v>-0.6217417805399321</v>
       </c>
       <c r="AE55" t="n">
-        <v>-1.243708971188215</v>
+        <v>-1.188879360193344</v>
       </c>
       <c r="AF55" t="n">
-        <v>-2.207943157764212</v>
+        <v>-2.225606375209817</v>
       </c>
       <c r="AG55" t="n">
-        <v>-2.398413411152185</v>
+        <v>-2.427522753469594</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.3835268593561886</v>
+        <v>0.3724033644612716</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -17354,7 +17354,7 @@
         <v>62.68000030517578</v>
       </c>
       <c r="H56" t="n">
-        <v>8063900</v>
+        <v>8062900</v>
       </c>
       <c r="I56" t="n">
         <v>-0.03463001871095683</v>
@@ -17387,52 +17387,52 @@
         <v>-1.924077102318042</v>
       </c>
       <c r="S56" t="n">
-        <v>60.34340026855469</v>
+        <v>60.45920028686523</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>1.170963129954862</v>
+        <v>0.9771861807501695</v>
       </c>
       <c r="V56" t="n">
-        <v>61.05640004475912</v>
+        <v>61.11646672566732</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.01048343448659987</v>
+        <v>-0.1087554503193393</v>
       </c>
       <c r="Y56" t="n">
-        <v>56.70424999237061</v>
+        <v>56.82440000534058</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>7.663886296485094</v>
+        <v>7.436240824932301</v>
       </c>
       <c r="AB56" t="n">
-        <v>-1.094765974287978</v>
+        <v>-1.095565540864456</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.9705925338516852</v>
+        <v>-0.9712909633719909</v>
       </c>
       <c r="AD56" t="n">
-        <v>-0.296901426614513</v>
+        <v>-0.2969517090118702</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.1162503412507521</v>
+        <v>0.09716124415747399</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.000570044509114999</v>
+        <v>-0.005915872321825531</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.4111127827367154</v>
+        <v>0.3996810730582303</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.3613337880074251</v>
+        <v>0.4060395817914721</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -17956,7 +17956,7 @@
         <v>20.51000022888184</v>
       </c>
       <c r="H58" t="n">
-        <v>7289600</v>
+        <v>7283200</v>
       </c>
       <c r="I58" t="n">
         <v>0.01878403740553058</v>
@@ -17989,52 +17989,52 @@
         <v>6.938875983609266</v>
       </c>
       <c r="S58" t="n">
-        <v>18.96540008544922</v>
+        <v>18.97760005950928</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>8.671583607477533</v>
+        <v>8.601722798053817</v>
       </c>
       <c r="V58" t="n">
-        <v>20.42000007629395</v>
+        <v>20.37286673227946</v>
       </c>
       <c r="W58" t="n">
         <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>0.9304629448958388</v>
+        <v>1.163969122206945</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.38621081352234</v>
+        <v>21.36541473388672</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-3.62948915980939</v>
+        <v>-3.535686683100184</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.003675692125687</v>
+        <v>1.001806863008637</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.8828577146360491</v>
+        <v>0.8793303568806569</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.108207374718214</v>
+        <v>1.107937829796529</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.8804896359554717</v>
+        <v>0.8742603190041747</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.04568243940783245</v>
+        <v>0.05711412602533134</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.178232719901966</v>
+        <v>-0.17349931211286</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.4756902177034589</v>
+        <v>0.4349823110816991</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -18052,10 +18052,10 @@
         <v>20.7</v>
       </c>
       <c r="AN58" t="n">
-        <v>21.3</v>
+        <v>24</v>
       </c>
       <c r="AO58" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="AP58" t="n">
         <v>1</v>
@@ -18257,7 +18257,7 @@
         <v>15.15999984741211</v>
       </c>
       <c r="H59" t="n">
-        <v>11381600</v>
+        <v>11380300</v>
       </c>
       <c r="I59" t="n">
         <v>0.02939208901367851</v>
@@ -18558,7 +18558,7 @@
         <v>37.65000152587891</v>
       </c>
       <c r="H60" t="n">
-        <v>6170100</v>
+        <v>6167500</v>
       </c>
       <c r="I60" t="n">
         <v>0.0239054364918474</v>
@@ -18591,52 +18591,52 @@
         <v>6.09631760005482</v>
       </c>
       <c r="S60" t="n">
-        <v>35.2457999420166</v>
+        <v>35.20479995727539</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>8.154727640162942</v>
+        <v>8.280686094360046</v>
       </c>
       <c r="V60" t="n">
-        <v>36.62486666361491</v>
+        <v>36.5686666615804</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>4.082287266741642</v>
+        <v>4.242244555047497</v>
       </c>
       <c r="Y60" t="n">
-        <v>38.16994997024536</v>
+        <v>38.1066499710083</v>
       </c>
       <c r="Z60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-0.1308648253391343</v>
+        <v>0.03503052849468365</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.6580884605737058</v>
+        <v>0.6591647589960741</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.6182250129598996</v>
+        <v>0.6190968144837903</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.188622737985305</v>
+        <v>1.190606521841161</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.237111290075744</v>
+        <v>1.263964449547337</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.3060329317351072</v>
+        <v>0.3191619663271015</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.008002496408052865</v>
+        <v>0.002147455289455937</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.3379320874829665</v>
+        <v>0.3381565574675869</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -18859,7 +18859,7 @@
         <v>11.02000045776367</v>
       </c>
       <c r="H61" t="n">
-        <v>2080500</v>
+        <v>2080400</v>
       </c>
       <c r="I61" t="n">
         <v>-0.01542650356009545</v>
@@ -19160,7 +19160,7 @@
         <v>36.70000076293945</v>
       </c>
       <c r="H62" t="n">
-        <v>8602500</v>
+        <v>8596900</v>
       </c>
       <c r="I62" t="n">
         <v>0.03425408391258955</v>
@@ -19193,52 +19193,52 @@
         <v>6.365956857648817</v>
       </c>
       <c r="S62" t="n">
-        <v>36.48559989929199</v>
+        <v>36.38959991455078</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>2.615823037174493</v>
+        <v>2.886535478886077</v>
       </c>
       <c r="V62" t="n">
-        <v>42.47459999084472</v>
+        <v>42.37259999593099</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-11.85320489238494</v>
+        <v>-11.64101652883156</v>
       </c>
       <c r="Y62" t="n">
-        <v>43.27865001678467</v>
+        <v>43.23390001296997</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-13.49083529133023</v>
+        <v>-13.40129246846304</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.8620882629341431</v>
+        <v>0.8686107452535479</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.767523397028067</v>
+        <v>0.7727567638532783</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.9490984358212008</v>
+        <v>0.9536656010551818</v>
       </c>
       <c r="AE62" t="n">
-        <v>0.3223405221605142</v>
+        <v>0.3566606571547346</v>
       </c>
       <c r="AF62" t="n">
-        <v>-0.8659968241957638</v>
+        <v>-0.8482369509506178</v>
       </c>
       <c r="AG62" t="n">
-        <v>-0.9738260723747308</v>
+        <v>-0.9633639007984824</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.4459104088084396</v>
+        <v>0.4124450850995018</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -19457,7 +19457,7 @@
         <v>29.82999992370605</v>
       </c>
       <c r="H63" t="n">
-        <v>1463300</v>
+        <v>1461800</v>
       </c>
       <c r="I63" t="n">
         <v>0.01526979210805512</v>
@@ -19778,7 +19778,7 @@
         <v>27.70000076293945</v>
       </c>
       <c r="H64" t="n">
-        <v>18045300</v>
+        <v>18045100</v>
       </c>
       <c r="I64" t="n">
         <v>0.02306851264866894</v>
@@ -20042,7 +20042,7 @@
         <v>0</v>
       </c>
       <c r="CR64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CS64" t="n">
         <v>9</v>
@@ -20051,7 +20051,7 @@
         <v>0</v>
       </c>
       <c r="CU64" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -20079,7 +20079,7 @@
         <v>17.68000030517578</v>
       </c>
       <c r="H65" t="n">
-        <v>1305300</v>
+        <v>1305200</v>
       </c>
       <c r="I65" t="n">
         <v>-0.006787377667537009</v>
@@ -20112,52 +20112,52 @@
         <v>7.435991422083664</v>
       </c>
       <c r="S65" t="n">
-        <v>14.97959997177124</v>
+        <v>14.96659996032715</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>17.2260908103945</v>
+        <v>17.32791357081576</v>
       </c>
       <c r="V65" t="n">
-        <v>15.87619997024536</v>
+        <v>15.85946663538615</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>10.6058093174232</v>
+        <v>10.722509587819</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.68198881626129</v>
+        <v>15.67532770633698</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>11.975589778088</v>
+        <v>12.02317294357745</v>
       </c>
       <c r="AB65" t="n">
-        <v>-0.4969009020694493</v>
+        <v>-0.497196611594253</v>
       </c>
       <c r="AC65" t="n">
-        <v>-0.2986698743053018</v>
+        <v>-0.2988798208750769</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.140166388302344</v>
+        <v>1.139058519568545</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.796146407420906</v>
+        <v>1.807160608382142</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.9172090949000057</v>
+        <v>0.9247560034852752</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.094221035289296</v>
+        <v>1.096240844040385</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.3794621180122025</v>
+        <v>0.3809776304382758</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -20384,7 +20384,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="H66" t="n">
-        <v>8949000</v>
+        <v>8944300</v>
       </c>
       <c r="I66" t="n">
         <v>0.02705876967486209</v>
@@ -20417,52 +20417,52 @@
         <v>1.160997051096631</v>
       </c>
       <c r="S66" t="n">
-        <v>18.43440010070801</v>
+        <v>18.36940010070801</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-5.285775565855964</v>
+        <v>-4.950629913060139</v>
       </c>
       <c r="V66" t="n">
-        <v>18.84873336791992</v>
+        <v>18.82926670074463</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-7.367785709202393</v>
+        <v>-7.272017747870252</v>
       </c>
       <c r="Y66" t="n">
-        <v>19.91974097251892</v>
+        <v>19.87809097290039</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-12.34826241686425</v>
+        <v>-12.16460821979483</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.3236744261172498</v>
+        <v>0.32705757143765</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.1956101602459487</v>
+        <v>0.1977035249815763</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.2392296312400447</v>
+        <v>0.241315053160397</v>
       </c>
       <c r="AE66" t="n">
-        <v>-0.8048653456230281</v>
+        <v>-0.7619119907878285</v>
       </c>
       <c r="AF66" t="n">
-        <v>-0.7364074191964337</v>
+        <v>-0.7339760923537826</v>
       </c>
       <c r="AG66" t="n">
-        <v>-0.9937618230291824</v>
+        <v>-0.9887948106548365</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.2713563144624239</v>
+        <v>0.2608668725027553</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -20479,13 +20479,13 @@
         <v>17.4</v>
       </c>
       <c r="AM66" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="AN66" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="AO66" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="AP66" t="n">
         <v>1</v>
@@ -20687,7 +20687,7 @@
         <v>48</v>
       </c>
       <c r="H67" t="n">
-        <v>6306000</v>
+        <v>6303400</v>
       </c>
       <c r="I67" t="n">
         <v>-0.01541991357751582</v>
@@ -20720,58 +20720,58 @@
         <v>2.973101548223572</v>
       </c>
       <c r="S67" t="n">
-        <v>44.04040016174316</v>
+        <v>44.0352001953125</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>7.287853485593297</v>
+        <v>7.300522741871658</v>
       </c>
       <c r="V67" t="n">
-        <v>46.05273345947266</v>
+        <v>45.93966679890951</v>
       </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>2.599773022335284</v>
+        <v>2.852291477920771</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.22205005645752</v>
+        <v>47.19060005187988</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.05918833152958157</v>
+        <v>0.1258724153852974</v>
       </c>
       <c r="AB67" t="n">
-        <v>-0.177099309636248</v>
+        <v>-0.1770014459870431</v>
       </c>
       <c r="AC67" t="n">
-        <v>-0.1345637157924768</v>
+        <v>-0.1344192173661944</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.6152676749349301</v>
+        <v>0.6142196695729834</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.05399064837158</v>
+        <v>1.055690724454875</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.3273337733629897</v>
+        <v>0.3582062193702068</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.007459055769755384</v>
+        <v>0.01583436900606781</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.2834509787038798</v>
+        <v>0.2754688793886823</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="AK67" t="n">
         <v>42.7</v>
@@ -20988,7 +20988,7 @@
         <v>42</v>
       </c>
       <c r="H68" t="n">
-        <v>1482900</v>
+        <v>1482600</v>
       </c>
       <c r="I68" t="n">
         <v>-0.006442387467112898</v>
@@ -21287,7 +21287,7 @@
         <v>19.60000038146973</v>
       </c>
       <c r="H69" t="n">
-        <v>10242300</v>
+        <v>10240000</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -21320,52 +21320,52 @@
         <v>3.109838871602128</v>
       </c>
       <c r="S69" t="n">
-        <v>19.73499996185303</v>
+        <v>19.65539993286133</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-1.393467838418734</v>
+        <v>-0.9941331596208688</v>
       </c>
       <c r="V69" t="n">
-        <v>23.11359999338786</v>
+        <v>23.05033331553141</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-15.807147782952</v>
+        <v>-15.57606209815446</v>
       </c>
       <c r="Y69" t="n">
-        <v>23.22699999809265</v>
+        <v>23.19434999465942</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-16.21819827756203</v>
+        <v>-16.1002611025815</v>
       </c>
       <c r="AB69" t="n">
-        <v>-0.07593342117834684</v>
+        <v>-0.07601987894790664</v>
       </c>
       <c r="AC69" t="n">
-        <v>-0.005034079975814611</v>
+        <v>-0.005040527381650548</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.5326785593263149</v>
+        <v>0.5333151368187247</v>
       </c>
       <c r="AE69" t="n">
-        <v>-0.1752330052397618</v>
+        <v>-0.125063671067691</v>
       </c>
       <c r="AF69" t="n">
-        <v>-1.204968324498722</v>
+        <v>-1.184806610135888</v>
       </c>
       <c r="AG69" t="n">
-        <v>-1.067369409193783</v>
+        <v>-1.057481265483897</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.1998809672110239</v>
+        <v>0.1986503501350698</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -21386,7 +21386,7 @@
         <v>19.6</v>
       </c>
       <c r="AO69" t="n">
-        <v>21.9</v>
+        <v>20.2</v>
       </c>
       <c r="AP69" t="n">
         <v>1</v>
@@ -21588,7 +21588,7 @@
         <v>34.77999877929688</v>
       </c>
       <c r="H70" t="n">
-        <v>4134000</v>
+        <v>4132900</v>
       </c>
       <c r="I70" t="n">
         <v>0.01865887474880545</v>
@@ -21621,52 +21621,52 @@
         <v>4.650542308540901</v>
       </c>
       <c r="S70" t="n">
-        <v>31.72679988861084</v>
+        <v>31.76539989471436</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>10.127711428128</v>
+        <v>9.993888767390803</v>
       </c>
       <c r="V70" t="n">
-        <v>32.6853999710083</v>
+        <v>32.6478666305542</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>6.8978769043686</v>
+        <v>7.02077113366313</v>
       </c>
       <c r="Y70" t="n">
-        <v>35.4199499797821</v>
+        <v>35.36514998435974</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-1.355031143034018</v>
+        <v>-1.20217603442592</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.736496626224549</v>
+        <v>0.7365331739113455</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.6753437619102637</v>
+        <v>0.6749875526722509</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.8057496992441823</v>
+        <v>0.8093930405484804</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.33903956092389</v>
+        <v>1.326186844757304</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.5612661881116895</v>
+        <v>0.5737108741284304</v>
       </c>
       <c r="AG70" t="n">
-        <v>-0.08906965203183143</v>
+        <v>-0.07952443129092131</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.3889829228232862</v>
+        <v>0.3793278632261399</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -21889,7 +21889,7 @@
         <v>39.29999923706055</v>
       </c>
       <c r="H71" t="n">
-        <v>8193200</v>
+        <v>8192600</v>
       </c>
       <c r="I71" t="n">
         <v>-0.007922345127243546</v>
@@ -21922,52 +21922,52 @@
         <v>7.711351523513893</v>
       </c>
       <c r="S71" t="n">
-        <v>34.09179996490479</v>
+        <v>34.09759998321533</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>13.86902344489524</v>
+        <v>13.84965426872714</v>
       </c>
       <c r="V71" t="n">
-        <v>29.73860004425049</v>
+        <v>29.76453337351481</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>30.53741479780748</v>
+        <v>30.42367977912657</v>
       </c>
       <c r="Y71" t="n">
-        <v>27.98410002708435</v>
+        <v>28.02915002822876</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>38.72162998721547</v>
+        <v>38.49866890622</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.1686787365174574</v>
+        <v>0.1677087768956232</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.200220091008265</v>
+        <v>0.1990059473589244</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.141468789668899</v>
+        <v>1.140135956750387</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.611205535054441</v>
+        <v>1.619962531535647</v>
       </c>
       <c r="AF71" t="n">
-        <v>3.488431806972447</v>
+        <v>3.478510372194823</v>
       </c>
       <c r="AG71" t="n">
-        <v>3.906368634597555</v>
+        <v>3.891210602834344</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.3386836127763044</v>
+        <v>0.3032526924755134</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -22190,7 +22190,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="H72" t="n">
-        <v>9972100</v>
+        <v>9969700</v>
       </c>
       <c r="I72" t="n">
         <v>0.00144923940673447</v>
@@ -22223,52 +22223,52 @@
         <v>-2.37992005054536</v>
       </c>
       <c r="S72" t="n">
-        <v>7.454199953079224</v>
+        <v>7.428399953842163</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-7.300583685608177</v>
+        <v>-6.978624059706474</v>
       </c>
       <c r="V72" t="n">
-        <v>7.920333340962728</v>
+        <v>7.927866671880087</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-12.75619914032319</v>
+        <v>-12.83910119324183</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.486800005435944</v>
+        <v>7.495550005435944</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-7.70422820971626</v>
+        <v>-7.811970537174459</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.8253251093933792</v>
+        <v>-0.828805022288999</v>
       </c>
       <c r="AC72" t="n">
-        <v>-0.8505477403946484</v>
+        <v>-0.8548304744734395</v>
       </c>
       <c r="AD72" t="n">
-        <v>-0.2544222623556142</v>
+        <v>-0.2542899545582633</v>
       </c>
       <c r="AE72" t="n">
-        <v>-0.5393792521529621</v>
+        <v>-0.5152760124877923</v>
       </c>
       <c r="AF72" t="n">
-        <v>-0.6444029637620107</v>
+        <v>-0.6483806760940317</v>
       </c>
       <c r="AG72" t="n">
-        <v>-0.3346688062872922</v>
+        <v>-0.3397885886960947</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.5222780575542083</v>
+        <v>0.5237107088654149</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -22495,7 +22495,7 @@
         <v>73.98000335693359</v>
       </c>
       <c r="H73" t="n">
-        <v>13413700</v>
+        <v>13413600</v>
       </c>
       <c r="I73" t="n">
         <v>-0.01117622548899821</v>
@@ -22528,52 +22528,52 @@
         <v>-4.707774522167594</v>
       </c>
       <c r="S73" t="n">
-        <v>75.35060043334961</v>
+        <v>75.38560043334961</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-3.716755228870448</v>
+        <v>-3.76145757981834</v>
       </c>
       <c r="V73" t="n">
-        <v>79.71993357340494</v>
+        <v>79.63126688639323</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-8.993899267421195</v>
+        <v>-8.892567092694858</v>
       </c>
       <c r="Y73" t="n">
-        <v>79.04420013427735</v>
+        <v>79.08685012817382</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-8.215905874798446</v>
+        <v>-8.265403244435612</v>
       </c>
       <c r="AB73" t="n">
-        <v>-1.407327173439258</v>
+        <v>-1.407823706553072</v>
       </c>
       <c r="AC73" t="n">
-        <v>-1.476894984277544</v>
+        <v>-1.477568818787731</v>
       </c>
       <c r="AD73" t="n">
-        <v>-0.9761074012572862</v>
+        <v>-0.9765214438958196</v>
       </c>
       <c r="AE73" t="n">
-        <v>-0.5352169748703757</v>
+        <v>-0.5414622593190159</v>
       </c>
       <c r="AF73" t="n">
-        <v>-0.675172583845314</v>
+        <v>-0.6658832344833043</v>
       </c>
       <c r="AG73" t="n">
-        <v>-0.5972156753985206</v>
+        <v>-0.5990399674786701</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.2585376787080518</v>
+        <v>0.2667012787113113</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -22792,7 +22792,7 @@
         <v>3.5</v>
       </c>
       <c r="H74" t="n">
-        <v>19153100</v>
+        <v>19148100</v>
       </c>
       <c r="I74" t="n">
         <v>0.06086957543318405</v>
@@ -22825,52 +22825,52 @@
         <v>16.87546354836872</v>
       </c>
       <c r="S74" t="n">
-        <v>3.138599987030029</v>
+        <v>3.135599989891052</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>16.61250560617142</v>
+        <v>16.72407506155965</v>
       </c>
       <c r="V74" t="n">
-        <v>3.440394790967305</v>
+        <v>3.430061457951864</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>6.383142290528775</v>
+        <v>6.703629969829292</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.515496091842651</v>
+        <v>3.510896092653275</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>4.110486549063268</v>
+        <v>4.246892794390053</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.433004719933332</v>
+        <v>1.438230606281094</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.25774184339271</v>
+        <v>1.261907179293711</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.550602734916499</v>
+        <v>1.546840348100518</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.381749355481497</v>
+        <v>1.391498687081526</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.4609221497190075</v>
+        <v>0.4834265197151125</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.3289399641360935</v>
+        <v>0.3395073988650311</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.7792101069744427</v>
+        <v>0.7566727469590204</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -23089,7 +23089,7 @@
         <v>40.09999847412109</v>
       </c>
       <c r="H75" t="n">
-        <v>8030500</v>
+        <v>8030300</v>
       </c>
       <c r="I75" t="n">
         <v>-0.000504552423603033</v>
@@ -23122,58 +23122,58 @@
         <v>9.687583184001799</v>
       </c>
       <c r="S75" t="n">
-        <v>35.33619987487793</v>
+        <v>35.34499984741211</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>12.1229760760222</v>
+        <v>12.09506041286816</v>
       </c>
       <c r="V75" t="n">
-        <v>32.57459987640381</v>
+        <v>32.58539986928304</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>21.62850528391128</v>
+        <v>21.58819315037151</v>
       </c>
       <c r="Y75" t="n">
-        <v>31.10319990158081</v>
+        <v>31.14599989891052</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>27.38238849138828</v>
+        <v>27.20734303113724</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.900158001326254</v>
+        <v>0.8977939265352357</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.9480686317452284</v>
+        <v>0.9454701484226499</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.797002255961742</v>
+        <v>1.793646260182877</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.919149493871239</v>
+        <v>1.919446807447887</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.631636649208314</v>
+        <v>2.619884917032528</v>
       </c>
       <c r="AG75" t="n">
-        <v>3.226010450857966</v>
+        <v>3.194164137481156</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.2839534232921242</v>
+        <v>0.2674984149656044</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
       </c>
       <c r="AJ75" t="n">
-        <v>32.7</v>
+        <v>31</v>
       </c>
       <c r="AK75" t="n">
         <v>33</v>
@@ -23390,7 +23390,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="H76" t="n">
-        <v>4976600</v>
+        <v>4976500</v>
       </c>
       <c r="I76" t="n">
         <v>0.05491584478777289</v>
@@ -23691,7 +23691,7 @@
         <v>31.17000007629395</v>
       </c>
       <c r="H77" t="n">
-        <v>3632000</v>
+        <v>3630000</v>
       </c>
       <c r="I77" t="n">
         <v>-0.00710827836122585</v>
@@ -23724,52 +23724,52 @@
         <v>2.204027649345366</v>
       </c>
       <c r="S77" t="n">
-        <v>31.70140014648437</v>
+        <v>31.59740013122559</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-3.064219875965866</v>
+        <v>-2.745164429310326</v>
       </c>
       <c r="V77" t="n">
-        <v>35.89940010070801</v>
+        <v>35.82620010375977</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-14.39968507543314</v>
+        <v>-14.22478673921274</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.6359001159668</v>
+        <v>35.61150011062622</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-13.76673679566287</v>
+        <v>-13.70765217198275</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1490918424127068</v>
+        <v>0.1496240729560274</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.2069216096217148</v>
+        <v>0.2076633893199595</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.3998802367073053</v>
+        <v>0.4005306007886981</v>
       </c>
       <c r="AE77" t="n">
-        <v>-0.3975778747663939</v>
+        <v>-0.356197289095033</v>
       </c>
       <c r="AF77" t="n">
-        <v>-1.183360926785859</v>
+        <v>-1.166252392626518</v>
       </c>
       <c r="AG77" t="n">
-        <v>-1.044700244029223</v>
+        <v>-1.037067985520416</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.1581202249371812</v>
+        <v>0.1545768069512445</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -23992,7 +23992,7 @@
         <v>52</v>
       </c>
       <c r="H78" t="n">
-        <v>8467600</v>
+        <v>8466300</v>
       </c>
       <c r="I78" t="n">
         <v>-0.01351867448328459</v>
@@ -24025,52 +24025,52 @@
         <v>1.475433844752124</v>
       </c>
       <c r="S78" t="n">
-        <v>48.34400032043457</v>
+        <v>48.36640037536621</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>5.65944376238066</v>
+        <v>5.610509433467282</v>
       </c>
       <c r="V78" t="n">
-        <v>47.21413345336914</v>
+        <v>47.17146680196127</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>8.187947326204036</v>
+        <v>8.285803461449529</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.62260007858276</v>
+        <v>47.63950008392334</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>7.260002072055734</v>
+        <v>7.221951827937839</v>
       </c>
       <c r="AB78" t="n">
-        <v>-0.1818511118095568</v>
+        <v>-0.1818132294022624</v>
       </c>
       <c r="AC78" t="n">
-        <v>-0.247795009883588</v>
+        <v>-0.247765172204221</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.2663306068918387</v>
+        <v>0.2666997363458074</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.7996480984046068</v>
+        <v>0.794373903093723</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.7386793550365482</v>
+        <v>0.7517660131542834</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.6575773167850548</v>
+        <v>0.6606841374115127</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.1865877716784098</v>
+        <v>0.1825972129090706</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -24262,7 +24262,7 @@
         <v>4</v>
       </c>
       <c r="CT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU78" t="n">
         <v>47</v>
@@ -24293,7 +24293,7 @@
         <v>10.68000030517578</v>
       </c>
       <c r="H79" t="n">
-        <v>9232700</v>
+        <v>9231900</v>
       </c>
       <c r="I79" t="n">
         <v>0.05094339079430821</v>
@@ -24326,52 +24326,52 @@
         <v>22.16458278396784</v>
       </c>
       <c r="S79" t="n">
-        <v>8.677400007247925</v>
+        <v>8.649200010299683</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>28.37947235367628</v>
+        <v>28.79804294104615</v>
       </c>
       <c r="V79" t="n">
-        <v>9.88846664428711</v>
+        <v>9.852599976857503</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>12.65649917278829</v>
+        <v>13.06660545936291</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.67559998989105</v>
+        <v>10.64524999141693</v>
       </c>
       <c r="Z79" t="n">
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>4.350110100335827</v>
+        <v>4.64761609454669</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.648750816267988</v>
+        <v>1.65081181694938</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.626371304274793</v>
+        <v>1.627539689182087</v>
       </c>
       <c r="AD79" t="n">
-        <v>2.761243783575936</v>
+        <v>2.750678124165601</v>
       </c>
       <c r="AE79" t="n">
-        <v>3.154709885654782</v>
+        <v>3.18637558915682</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.217329820207972</v>
+        <v>1.252733282985192</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.3789958828512645</v>
+        <v>0.4061863166127686</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.5644308851665147</v>
+        <v>0.5473837509355137</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -933,16 +933,16 @@
         <v>15.19999980926514</v>
       </c>
       <c r="E2" t="n">
-        <v>15.35999965667725</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15.14000034332275</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>15.18000030517578</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>17923800</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0.007832890858321839</v>
@@ -1234,16 +1234,16 @@
         <v>28.56999969482422</v>
       </c>
       <c r="E3" t="n">
-        <v>28.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>28.39999961853027</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>28.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3406600</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>-0.01414768301892355</v>
@@ -1535,16 +1535,16 @@
         <v>10.19999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>10.47999954223633</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10.1899995803833</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>10.35000038146973</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>12184800</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0.02764537351578178</v>
@@ -1838,16 +1838,16 @@
         <v>12.51000022888184</v>
       </c>
       <c r="E5" t="n">
-        <v>12.80000019073486</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12.42000007629395</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>12.80000019073486</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3412600</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>-0.02494151962019531</v>
@@ -2139,16 +2139,16 @@
         <v>54.43999862670898</v>
       </c>
       <c r="E6" t="n">
-        <v>54.7599983215332</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>53.75</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>54.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>17895000</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>-0.002016509842163838</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="AK6" t="n">
         <v>54.1</v>
@@ -2250,7 +2250,7 @@
         <v>54.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -2436,16 +2436,16 @@
         <v>15.52000045776367</v>
       </c>
       <c r="E7" t="n">
-        <v>16.21999931335449</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>15.4399995803833</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>16.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3802400</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>-0.05250297601130527</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="AL7" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>16.7</v>
@@ -2737,16 +2737,16 @@
         <v>17.65999984741211</v>
       </c>
       <c r="E8" t="n">
-        <v>17.97999954223633</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>17.6200008392334</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>17.72999954223633</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>46611700</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>-0.01670374456310031</v>
@@ -3042,16 +3042,16 @@
         <v>21.48999977111816</v>
       </c>
       <c r="E9" t="n">
-        <v>21.80999946594238</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>21.18000030517578</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>21.38999938964844</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>44512000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>-0.004631791605510527</v>
@@ -3359,16 +3359,16 @@
         <v>15.60999965667725</v>
       </c>
       <c r="E10" t="n">
-        <v>15.77999973297119</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>15.46000003814697</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>15.64000034332275</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6937500</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>-0.01014589704768565</v>
@@ -3676,16 +3676,16 @@
         <v>17.65999984741211</v>
       </c>
       <c r="E11" t="n">
-        <v>17.8799991607666</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>17.54000091552734</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>17.81999969482422</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>28131600</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>-0.01230421273381421</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>17.5</v>
@@ -3993,16 +3993,16 @@
         <v>38.38000106811523</v>
       </c>
       <c r="E12" t="n">
-        <v>38.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>38.36000061035156</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>38.81000137329102</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6345300</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>-0.01564505216957846</v>
@@ -4310,16 +4310,16 @@
         <v>4.010000228881836</v>
       </c>
       <c r="E13" t="n">
-        <v>4.170000076293945</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3.990000009536743</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.070000171661377</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>22046600</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>-0.01955988281698129</v>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="AL13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
         <v>4.1</v>
@@ -4615,16 +4615,16 @@
         <v>62.25</v>
       </c>
       <c r="E14" t="n">
-        <v>63.16999816894531</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>61.72000122070312</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>62.09999847412109</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>9374000</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>-0.007177045573585339</v>
@@ -4936,16 +4936,16 @@
         <v>20.59000015258789</v>
       </c>
       <c r="E15" t="n">
-        <v>20.63999938964844</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>20.02000045776367</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>20.14999961853027</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2528700</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0.01729250916144598</v>
@@ -5245,16 +5245,16 @@
         <v>17.95999908447266</v>
       </c>
       <c r="E16" t="n">
-        <v>18.03000068664551</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>17.3799991607666</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>17.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2466000</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0.03159099608736082</v>
@@ -5542,16 +5542,16 @@
         <v>3.900000095367432</v>
       </c>
       <c r="E17" t="n">
-        <v>4.059999942779541</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3.839999914169312</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4.050000190734863</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5475800</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>-0.03703705884028974</v>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="AL17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
         <v>7.4</v>
@@ -5847,16 +5847,16 @@
         <v>9.420000076293945</v>
       </c>
       <c r="E18" t="n">
-        <v>9.619999885559082</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>9.069999694824219</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9.189999580383301</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>7090800</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0.01727860080532961</v>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>9.300000000000001</v>
@@ -6150,16 +6150,16 @@
         <v>10.84000015258789</v>
       </c>
       <c r="E19" t="n">
-        <v>10.88000011444092</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>10.72999954223633</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>10.85000038146973</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>11968500</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>-0.004591385597661701</v>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>10.7</v>
@@ -6447,16 +6447,16 @@
         <v>5.050000190734863</v>
       </c>
       <c r="E20" t="n">
-        <v>5.050000190734863</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.840000152587891</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4.949999809265137</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7643300</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0.02020209804504458</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="AL20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>5.3</v>
@@ -6752,16 +6752,16 @@
         <v>2.109999895095825</v>
       </c>
       <c r="E21" t="n">
-        <v>2.150000095367432</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.079999923706055</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.099999904632568</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>39671200</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>-0.004716976888241464</v>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="AL21" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>2.3</v>
@@ -7057,16 +7057,16 @@
         <v>43.90000152587891</v>
       </c>
       <c r="E22" t="n">
-        <v>44.18999862670898</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>43.47000122070312</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>44.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1553500</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>-0.009029293861635312</v>
@@ -7358,16 +7358,16 @@
         <v>15.68000030517578</v>
       </c>
       <c r="E23" t="n">
-        <v>15.77999973297119</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>15.55000019073486</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>15.57999992370605</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>8536600</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>-0.006337099460557605</v>
@@ -7659,16 +7659,16 @@
         <v>3.740000009536743</v>
       </c>
       <c r="E24" t="n">
-        <v>3.859999895095825</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3.720000028610229</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.799999952316284</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>20252700</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>-0.02094238877070942</v>
@@ -7752,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
         <v>3.6</v>
@@ -7767,7 +7767,7 @@
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AP24" t="n">
         <v>1</v>
@@ -7960,16 +7960,16 @@
         <v>56.38000106811523</v>
       </c>
       <c r="E25" t="n">
-        <v>57.84999847412109</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>56.38000106811523</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>57.56000137329102</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3809100</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>-0.02557897557248812</v>
@@ -8053,7 +8053,7 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>54.1</v>
+        <v>53</v>
       </c>
       <c r="AK25" t="n">
         <v>55.9</v>
@@ -8261,16 +8261,16 @@
         <v>5.989999771118164</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5.699999809265137</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.920000076293945</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>13467100</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0.006722682879878539</v>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="AL26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>7.8</v>
@@ -8562,16 +8562,16 @@
         <v>27.59000015258789</v>
       </c>
       <c r="E27" t="n">
-        <v>27.85000038146973</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>27.10000038146973</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>27.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2245700</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0.001451938897825134</v>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="AL27" t="n">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
         <v>28.4</v>
@@ -8867,16 +8867,16 @@
         <v>20.11000061035156</v>
       </c>
       <c r="E28" t="n">
-        <v>20.54000091552734</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>20.07999992370605</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>20.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3500500</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>-0.0233122651131209</v>
@@ -9180,16 +9180,16 @@
         <v>26.53000068664551</v>
       </c>
       <c r="E29" t="n">
-        <v>27.06999969482422</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>26.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>26.84000015258789</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5367200</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>-0.01740738197609226</v>
@@ -9479,16 +9479,16 @@
         <v>9.699999809265137</v>
       </c>
       <c r="E30" t="n">
-        <v>9.770000457763672</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>9.590000152587891</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9.770000457763672</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>7700800</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>-0.01020412035953522</v>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>9.6</v>
@@ -9778,16 +9778,16 @@
         <v>28.8700008392334</v>
       </c>
       <c r="E31" t="n">
-        <v>29.07999992370605</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>28.73999977111816</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>29.04999923706055</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3395900</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>-0.007903764234408306</v>
@@ -9871,13 +9871,13 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK31" t="n">
         <v>28.1</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>28.5</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>28.7</v>
       </c>
       <c r="AM31" t="n">
         <v>29.1</v>
@@ -10075,16 +10075,16 @@
         <v>100.4400024414062</v>
       </c>
       <c r="E32" t="n">
-        <v>101.8899993896484</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>99.08999633789062</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>5071300</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>-0.01063824110886546</v>
@@ -10380,16 +10380,16 @@
         <v>26.75</v>
       </c>
       <c r="E33" t="n">
-        <v>27.17000007629395</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>26.54000091552734</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>27.02000045776367</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>6896000</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>-0.02372261414524568</v>
@@ -10681,16 +10681,16 @@
         <v>50.90000152587891</v>
       </c>
       <c r="E34" t="n">
-        <v>51.47000122070312</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>50.5099983215332</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>50.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2582400</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>-0.01107440608715093</v>
@@ -10774,13 +10774,13 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>49.8</v>
+        <v>50.8</v>
       </c>
       <c r="AL34" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="AM34" t="n">
         <v>51.6</v>
@@ -10978,16 +10978,16 @@
         <v>39.11999893188477</v>
       </c>
       <c r="E35" t="n">
-        <v>39.65999984741211</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>39.09000015258789</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>39.40000152587891</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>6907400</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>-0.01683845107380033</v>
@@ -11275,16 +11275,16 @@
         <v>21.44000053405762</v>
       </c>
       <c r="E36" t="n">
-        <v>21.80999946594238</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>21.3799991607666</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>21.6200008392334</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3176500</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>-0.01379941307355026</v>
@@ -11576,16 +11576,16 @@
         <v>25.09000015258789</v>
       </c>
       <c r="E37" t="n">
-        <v>25.1299991607666</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>24.63999938964844</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5433300</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0.004001615941801706</v>
@@ -11877,16 +11877,16 @@
         <v>11.19999980926514</v>
       </c>
       <c r="E38" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>10.96000003814697</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>11.09000015258789</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>4604900</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0.00268574151891543</v>
@@ -12182,16 +12182,16 @@
         <v>6.230000019073486</v>
       </c>
       <c r="E39" t="n">
-        <v>6.409999847412109</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>6.110000133514404</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>6.239999771118164</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>9186300</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>-0.004792365608860094</v>
@@ -12279,11 +12279,13 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AK39" t="n">
-        <v>6</v>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
       </c>
       <c r="AL39" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
         <v>6.3</v>
@@ -12292,13 +12294,13 @@
         <v>6.4</v>
       </c>
       <c r="AO39" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="AP39" t="n">
         <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
@@ -12485,16 +12487,16 @@
         <v>24.6299991607666</v>
       </c>
       <c r="E40" t="n">
-        <v>24.67000007629395</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>24.1200008392334</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>24.44000053405762</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1873000</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0.004076578529226715</v>
@@ -12578,7 +12580,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="AK40" t="n">
         <v>24.3</v>
@@ -12587,13 +12589,13 @@
         <v>24.5</v>
       </c>
       <c r="AM40" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="AN40" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="AP40" t="n">
         <v>1</v>
@@ -12782,16 +12784,16 @@
         <v>25.94000053405762</v>
       </c>
       <c r="E41" t="n">
-        <v>26.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>25.94000053405762</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>26.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3897300</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>-0.03208950475691341</v>
@@ -13079,16 +13081,16 @@
         <v>26.79000091552734</v>
       </c>
       <c r="E42" t="n">
-        <v>26.94000053405762</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>26.57999992370605</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>26.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1407400</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>-0.004459269140289712</v>
@@ -13376,16 +13378,16 @@
         <v>13.94999980926514</v>
       </c>
       <c r="E43" t="n">
-        <v>14.01000022888184</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>13.78999996185303</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>13.85999965667725</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>25529100</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>-0.002859182452283227</v>
@@ -13677,16 +13679,16 @@
         <v>41.70999908447266</v>
       </c>
       <c r="E44" t="n">
-        <v>42.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>41.52999877929688</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>41.84000015258789</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>18076100</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>-0.009969189959514235</v>
@@ -13998,16 +14000,16 @@
         <v>18.30999946594238</v>
       </c>
       <c r="E45" t="n">
-        <v>18.42000007629395</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>17.85000038146973</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>18.10000038146973</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>7212600</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0.008815418775477868</v>
@@ -14299,16 +14301,16 @@
         <v>11.15999984741211</v>
       </c>
       <c r="E46" t="n">
-        <v>11.36999988555908</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>10.97000026702881</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>11.01000022888184</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>11544200</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0.003597118908694741</v>
@@ -14402,7 +14404,7 @@
         </is>
       </c>
       <c r="AL46" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
         <v>13.4</v>
@@ -14604,16 +14606,16 @@
         <v>17.20000076293945</v>
       </c>
       <c r="E47" t="n">
-        <v>17.20999908447266</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>16.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>5798800</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0.02198460136130076</v>
@@ -14905,16 +14907,16 @@
         <v>6.599999904632568</v>
       </c>
       <c r="E48" t="n">
-        <v>7.150000095367432</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>6.53000020980835</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>6.650000095367432</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>46408900</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>-0.02366868621774187</v>
@@ -15008,7 +15010,7 @@
         </is>
       </c>
       <c r="AL48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
         <v>8.4</v>
@@ -15210,16 +15212,16 @@
         <v>16.48999977111816</v>
       </c>
       <c r="E49" t="n">
-        <v>16.76000022888184</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>16.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>6448700</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>-0.009014400482705964</v>
@@ -15515,16 +15517,16 @@
         <v>5.210000038146973</v>
       </c>
       <c r="E50" t="n">
-        <v>5.320000171661377</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>5.070000171661377</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>5.130000114440918</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>8441700</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0.007736936414457718</v>
@@ -15816,16 +15818,16 @@
         <v>30.27000045776367</v>
       </c>
       <c r="E51" t="n">
-        <v>30.95000076293945</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>30.27000045776367</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>30.80999946594238</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>4837100</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>-0.02668810011335543</v>
@@ -16119,16 +16121,16 @@
         <v>6.710000038146973</v>
       </c>
       <c r="E52" t="n">
-        <v>7.150000095367432</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>6.679999828338623</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>7.099999904632568</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>12534600</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>-0.05758424915759885</v>
@@ -16218,7 +16220,7 @@
         </is>
       </c>
       <c r="AL52" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
         <v>8.1</v>
@@ -16420,16 +16422,16 @@
         <v>54.0099983215332</v>
       </c>
       <c r="E53" t="n">
-        <v>54.61000061035156</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>53.38999938964844</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>53.58000183105469</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>8688200</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0.01828803524250877</v>
@@ -16721,16 +16723,16 @@
         <v>48.72000122070312</v>
       </c>
       <c r="E54" t="n">
-        <v>49.27000045776367</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>48.27999877929688</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>48.56000137329102</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>46839600</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0.01352197898908858</v>
@@ -17022,16 +17024,16 @@
         <v>4.190000057220459</v>
       </c>
       <c r="E55" t="n">
-        <v>4.210000038146973</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>4.03000020980835</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>4.090000152587891</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>16757500</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0.02195125723934765</v>
@@ -17125,7 +17127,7 @@
         </is>
       </c>
       <c r="AL55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
         <v>5.9</v>
@@ -17327,16 +17329,16 @@
         <v>61.63000106811523</v>
       </c>
       <c r="E56" t="n">
-        <v>62.09999847412109</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>60.15000152587891</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>60.18999862670898</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>9182900</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0.03841621992607647</v>
@@ -17628,16 +17630,16 @@
         <v>47</v>
       </c>
       <c r="E57" t="n">
-        <v>47.33000183105469</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>46.70000076293945</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1568900</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>-0.001911237041755331</v>
@@ -17731,7 +17733,7 @@
         </is>
       </c>
       <c r="AL57" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
         <v>47.5</v>
@@ -17933,16 +17935,16 @@
         <v>17.67000007629395</v>
       </c>
       <c r="E58" t="n">
-        <v>18.15999984741211</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>17.54999923706055</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>18.05999946594238</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>9791500</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>-0.02698236647771735</v>
@@ -18234,16 +18236,16 @@
         <v>15.76000022888184</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03000068664551</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>15.90999984741211</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>10950100</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>-0.02050962837641601</v>
@@ -18342,7 +18344,7 @@
         <v>16</v>
       </c>
       <c r="AO59" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="AP59" t="n">
         <v>1</v>
@@ -18535,16 +18537,16 @@
         <v>37.47000122070312</v>
       </c>
       <c r="E60" t="n">
-        <v>37.88000106811523</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>36.7400016784668</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>36.91999816894531</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>4908400</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0.002139658527965604</v>
@@ -18628,7 +18630,7 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="AK60" t="n">
         <v>36.8</v>
@@ -18836,16 +18838,16 @@
         <v>10.89000034332275</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>10.52000045776367</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>10.53999996185303</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2529400</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0.04011461944433492</v>
@@ -18934,7 +18936,7 @@
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AL61" t="n">
         <v>10.2</v>
@@ -18946,7 +18948,7 @@
         <v>12.3</v>
       </c>
       <c r="AO61" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="AP61" t="n">
         <v>1</v>
@@ -19139,16 +19141,16 @@
         <v>38.02999877929688</v>
       </c>
       <c r="E62" t="n">
-        <v>38.02999877929688</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>37.15000152587891</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>37.47999954223633</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>9163800</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>-0.008344190549059771</v>
@@ -19232,13 +19234,13 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="AK62" t="n">
         <v>36.3</v>
       </c>
-      <c r="AK62" t="n">
-        <v>37.2</v>
-      </c>
       <c r="AL62" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="AM62" t="n">
         <v>38.7</v>
@@ -19436,16 +19438,16 @@
         <v>29.69000053405762</v>
       </c>
       <c r="E63" t="n">
-        <v>29.84000015258789</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>29.3700008392334</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2062700</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>-0.002016788771172506</v>
@@ -19753,16 +19755,16 @@
         <v>26.75</v>
       </c>
       <c r="E64" t="n">
-        <v>27.03000068664551</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>26.44000053405762</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>26.73999977111816</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>15771000</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>-0.006684006800445008</v>
@@ -20054,16 +20056,16 @@
         <v>16.86000061035156</v>
       </c>
       <c r="E65" t="n">
-        <v>17.32999992370605</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>16.80999946594238</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>17.30999946594238</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1410100</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>-0.02486988330865947</v>
@@ -20355,16 +20357,16 @@
         <v>16.82999992370605</v>
       </c>
       <c r="E66" t="n">
-        <v>17.19000053405762</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>16.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>17.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>5446200</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>-0.02885170237745005</v>
@@ -20458,7 +20460,7 @@
         </is>
       </c>
       <c r="AL66" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="AM66" t="n">
         <v>17.4</v>
@@ -20660,16 +20662,16 @@
         <v>44.68999862670898</v>
       </c>
       <c r="E67" t="n">
-        <v>45.04999923706055</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>44.45999908447266</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>44.86000061035156</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>6572000</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>-0.006888919406466965</v>
@@ -20961,16 +20963,16 @@
         <v>40.22000122070312</v>
       </c>
       <c r="E68" t="n">
-        <v>40.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>40.13000106811523</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>40.59000015258789</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2914800</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>-0.01397400544326144</v>
@@ -21258,16 +21260,16 @@
         <v>18.47999954223633</v>
       </c>
       <c r="E69" t="n">
-        <v>18.63999938964844</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>18.35000038146973</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>18.55999946594238</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>5092900</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>-0.006985548836732636</v>
@@ -21356,7 +21358,7 @@
         </is>
       </c>
       <c r="AK69" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AL69" t="n">
         <v>17.3</v>
@@ -21365,10 +21367,10 @@
         <v>18.5</v>
       </c>
       <c r="AN69" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="AO69" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="AP69" t="n">
         <v>1</v>
@@ -21561,16 +21563,16 @@
         <v>33.97999954223633</v>
       </c>
       <c r="E70" t="n">
-        <v>34.59000015258789</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>33.79000091552734</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>34.56999969482422</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3330700</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>-0.02636108720397567</v>
@@ -21862,16 +21864,16 @@
         <v>37.34000015258789</v>
       </c>
       <c r="E71" t="n">
-        <v>37.70000076293945</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>36.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>36.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>8655500</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0.02133475793211281</v>
@@ -22163,16 +22165,16 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>7.010000228881836</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>6.679999828338623</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>6.900000095367432</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>8642900</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0.01010103512198191</v>
@@ -22468,16 +22470,16 @@
         <v>71.16000366210938</v>
       </c>
       <c r="E73" t="n">
-        <v>71.44000244140625</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>69.80000305175781</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>70.27999877929688</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>14379700</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0.005510909107570017</v>
@@ -22765,16 +22767,16 @@
         <v>3.849999904632568</v>
       </c>
       <c r="E74" t="n">
-        <v>3.890000104904175</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>3.720000028610229</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3.809999942779541</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>16312700</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>-0.005167953880604426</v>
@@ -23064,16 +23066,16 @@
         <v>38.06000137329102</v>
       </c>
       <c r="E75" t="n">
-        <v>38.06000137329102</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>36.93999862670898</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>36.93999862670898</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>6273000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0.0228433837606048</v>
@@ -23365,16 +23367,16 @@
         <v>22.26000022888184</v>
       </c>
       <c r="E76" t="n">
-        <v>22.3799991607666</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>21.85000038146973</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>22.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2340400</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>-0.0008976865865026884</v>
@@ -23666,16 +23668,16 @@
         <v>29.51000022888184</v>
       </c>
       <c r="E77" t="n">
-        <v>29.82999992370605</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>29.48999977111816</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>29.6299991607666</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>3088400</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>-0.0199269468385016</v>
@@ -23967,16 +23969,16 @@
         <v>50.11999893188477</v>
       </c>
       <c r="E78" t="n">
-        <v>51.36000061035156</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>50.04999923706055</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>50.66999816894531</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>8191300</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>-0.01860193398504628</v>
@@ -24268,16 +24270,16 @@
         <v>10.85999965667725</v>
       </c>
       <c r="E79" t="n">
-        <v>11.15999984741211</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>10.71000003814697</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>4257900</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>-0.02162168617517668</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -933,16 +933,16 @@
         <v>15.27000045776367</v>
       </c>
       <c r="E2" t="n">
-        <v>15.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15.07999992370605</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>15.11999988555908</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>21981500</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0.004605305880061028</v>
@@ -1234,16 +1234,16 @@
         <v>28.77000045776367</v>
       </c>
       <c r="E3" t="n">
-        <v>28.8799991607666</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>28.3700008392334</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>28.56999969482422</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2651900</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0.007000376796492791</v>
@@ -1327,22 +1327,22 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AK3" t="n">
         <v>27.8</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>28.2</v>
       </c>
-      <c r="AL3" t="n">
-        <v>28.4</v>
-      </c>
       <c r="AM3" t="n">
-        <v>28.9</v>
+        <v>29.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="AP3" t="n">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>10.53999996185303</v>
       </c>
       <c r="E4" t="n">
-        <v>10.55000019073486</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10.1899995803833</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>10.19999980926514</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>26239800</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0.03333334891624729</v>
@@ -1840,16 +1840,16 @@
         <v>12.6899995803833</v>
       </c>
       <c r="E5" t="n">
-        <v>12.77000045776367</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12.40999984741211</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>12.53999996185303</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3611400</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0.01438843710697135</v>
@@ -2141,16 +2141,16 @@
         <v>54.79999923706055</v>
       </c>
       <c r="E6" t="n">
-        <v>54.95000076293945</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>54.06000137329102</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>54.43999862670898</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12532900</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0.006612796095386786</v>
@@ -2438,16 +2438,16 @@
         <v>17.14999961853027</v>
       </c>
       <c r="E7" t="n">
-        <v>17.19000053405762</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>15.39999961853027</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>15.52000045776367</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6483100</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0.1050257160238173</v>
@@ -2540,13 +2540,13 @@
         <v>17.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.6</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>1</v>
@@ -2735,16 +2735,16 @@
         <v>17.89999961853027</v>
       </c>
       <c r="E8" t="n">
-        <v>18.04999923706055</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>17.53000068664551</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>17.69000053405762</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>56291000</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0.01359002113204055</v>
@@ -3040,16 +3040,16 @@
         <v>22.04000091552734</v>
       </c>
       <c r="E9" t="n">
-        <v>22.18000030517578</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>21.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>21.46999931335449</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>37152800</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0.02559335273462238</v>
@@ -3151,7 +3151,7 @@
         <v>22.3</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -3357,16 +3357,16 @@
         <v>15.64999961853027</v>
       </c>
       <c r="E10" t="n">
-        <v>15.67000007629395</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>15.44999980926514</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>15.60999965667725</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8430900</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0.002562457574168953</v>
@@ -3674,16 +3674,16 @@
         <v>17.78000068664551</v>
       </c>
       <c r="E11" t="n">
-        <v>17.78000068664551</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>17.48999977111816</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>17.6299991607666</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>41736700</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0.006795064567963971</v>
@@ -3991,16 +3991,16 @@
         <v>38.7599983215332</v>
       </c>
       <c r="E12" t="n">
-        <v>38.97000122070312</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>38.2400016784668</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>38.43999862670898</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4566300</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0.009900918260621339</v>
@@ -4308,16 +4308,16 @@
         <v>3.920000076293945</v>
       </c>
       <c r="E13" t="n">
-        <v>4.019999980926514</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3.900000095367432</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.019999980926514</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>15027200</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>-0.02244392704510811</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="AL13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
         <v>4.1</v>
@@ -4613,16 +4613,16 @@
         <v>62.84999847412109</v>
       </c>
       <c r="E14" t="n">
-        <v>63.0099983215332</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>61.79000091552734</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>62.13000106811523</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>11405400</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0.009638529704756538</v>
@@ -4938,16 +4938,16 @@
         <v>20.23999977111816</v>
       </c>
       <c r="E15" t="n">
-        <v>20.6200008392334</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>20.09000015258789</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>20.53000068664551</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1784600</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0.01699856138299916</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AK15" t="n">
         <v>19.8</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>20.1</v>
       </c>
       <c r="AL15" t="n">
         <v>20.2</v>
@@ -5247,16 +5247,16 @@
         <v>18.22999954223633</v>
       </c>
       <c r="E16" t="n">
-        <v>18.42000007629395</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>17.6200008392334</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3498500</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0.0150334338266811</v>
@@ -5544,16 +5544,16 @@
         <v>3.720000028610229</v>
       </c>
       <c r="E17" t="n">
-        <v>3.940000057220459</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3.650000095367432</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.920000076293945</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4409400</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>-0.04615386214246842</v>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="AL17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
         <v>7.4</v>
@@ -5849,16 +5849,16 @@
         <v>9.510000228881836</v>
       </c>
       <c r="E18" t="n">
-        <v>9.609999656677246</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>9.270000457763672</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9.449999809265137</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>7461200</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0.009554156248297918</v>
@@ -5942,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>9.300000000000001</v>
@@ -6150,16 +6150,16 @@
         <v>10.96000003814697</v>
       </c>
       <c r="E19" t="n">
-        <v>10.96000003814697</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>10.76000022888184</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>10.81999969482422</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>9187400</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0.01107009998799979</v>
@@ -6447,16 +6447,16 @@
         <v>4.760000228881836</v>
       </c>
       <c r="E20" t="n">
-        <v>4.920000076293945</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.699999809265137</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4.920000076293945</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>15223000</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>-0.0574257328514729</v>
@@ -6550,16 +6550,16 @@
         </is>
       </c>
       <c r="AL20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AN20" t="n">
         <v>5.5</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>7.4</v>
       </c>
       <c r="AP20" t="n">
         <v>1</v>
@@ -6752,16 +6752,16 @@
         <v>2.200000047683716</v>
       </c>
       <c r="E21" t="n">
-        <v>2.210000038146973</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.099999904632568</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.099999904632568</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>38505700</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0.04265410287321525</v>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="AL21" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>2.3</v>
@@ -7057,16 +7057,16 @@
         <v>44.5</v>
       </c>
       <c r="E22" t="n">
-        <v>44.83000183105469</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>43.52999877929688</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>43.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1729100</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0.01366739073499579</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="AK22" t="n">
         <v>41.9</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>43.5</v>
       </c>
       <c r="AL22" t="n">
         <v>43.9</v>
@@ -7168,7 +7168,7 @@
         <v>45.1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -7358,16 +7358,16 @@
         <v>15.75</v>
       </c>
       <c r="E23" t="n">
-        <v>15.81999969482422</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>15.55000019073486</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>15.61999988555908</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>13416500</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0.004464266164657671</v>
@@ -7659,16 +7659,16 @@
         <v>3.720000028610229</v>
       </c>
       <c r="E24" t="n">
-        <v>3.759999990463257</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3.650000095367432</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.740000009536743</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>32506000</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>-0.005347588469389097</v>
@@ -7751,13 +7751,11 @@
       <c r="AI24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AJ24" t="n">
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AL24" t="n">
         <v>3.7</v>
@@ -7962,16 +7960,16 @@
         <v>56.93000030517578</v>
       </c>
       <c r="E25" t="n">
-        <v>57.16999816894531</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>56.02999877929688</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>56.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2743000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0.009755218634992069</v>
@@ -8070,7 +8068,7 @@
         <v>57.9</v>
       </c>
       <c r="AO25" t="n">
-        <v>58.6</v>
+        <v>60.3</v>
       </c>
       <c r="AP25" t="n">
         <v>1</v>
@@ -8263,16 +8261,16 @@
         <v>5.400000095367432</v>
       </c>
       <c r="E26" t="n">
-        <v>6.019999980926514</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>43531600</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>-0.09849744545826522</v>
@@ -8366,7 +8364,7 @@
         </is>
       </c>
       <c r="AL26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>7.8</v>
@@ -8564,16 +8562,16 @@
         <v>28.71999931335449</v>
       </c>
       <c r="E27" t="n">
-        <v>28.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>27.14999961853027</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4378300</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0.04095683778604875</v>
@@ -8865,16 +8863,16 @@
         <v>20.11000061035156</v>
       </c>
       <c r="E28" t="n">
-        <v>20.15999984741211</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>19.8799991607666</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>20.10000038146973</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>5676700</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -9178,16 +9176,16 @@
         <v>27.1299991607666</v>
       </c>
       <c r="E29" t="n">
-        <v>27.27000045776367</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>26.23999977111816</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>26.32999992370605</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4617700</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0.02261584842035513</v>
@@ -9479,16 +9477,16 @@
         <v>10.15999984741211</v>
       </c>
       <c r="E30" t="n">
-        <v>10.22000026702881</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>9.560000419616699</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9.689999580383301</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>12961600</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0.04742268527753946</v>
@@ -9572,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>9.6</v>
@@ -9776,16 +9774,16 @@
         <v>29.13999938964844</v>
       </c>
       <c r="E31" t="n">
-        <v>29.25</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>28.73999977111816</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>28.86000061035156</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1651500</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0.009352218308498195</v>
@@ -10073,16 +10071,16 @@
         <v>100.4599990844727</v>
       </c>
       <c r="E32" t="n">
-        <v>101.4300003051758</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>99.65000152587891</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4392400</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0.0001990904279205452</v>
@@ -10378,16 +10376,16 @@
         <v>27.10000038146973</v>
       </c>
       <c r="E33" t="n">
-        <v>27.20999908447266</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>26.57999992370605</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>26.75</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>5204300</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0.01308412641008316</v>
@@ -10420,52 +10418,52 @@
         <v>0.002839989001817065</v>
       </c>
       <c r="S33" t="n">
-        <v>26.34440002441406</v>
+        <v>26.35100002288818</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2.868163087242174</v>
+        <v>2.842398231304202</v>
       </c>
       <c r="V33" t="n">
-        <v>25.45993330637614</v>
+        <v>25.43826663970947</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>6.441757153711205</v>
+        <v>6.532417343115142</v>
       </c>
       <c r="Y33" t="n">
-        <v>24.30454998970032</v>
+        <v>24.27659998893738</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>11.50175746086249</v>
+        <v>11.63013104725928</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.3340118262558422</v>
+        <v>-0.3335504381499687</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.2769506568169987</v>
+        <v>-0.2767649301800118</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.0005565027042568741</v>
+        <v>0.000556718905630391</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.4405043108288179</v>
+        <v>0.4367610884661595</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.6928638057667478</v>
+        <v>0.7077845487157719</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.125306984710527</v>
+        <v>1.147135458076788</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.2472975955847271</v>
+        <v>0.2472975955847272</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -10679,16 +10677,16 @@
         <v>51.88000106811523</v>
       </c>
       <c r="E34" t="n">
-        <v>51.88000106811523</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>50.52000045776367</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2417400</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0.01925342854337786</v>
@@ -10980,16 +10978,16 @@
         <v>39.77000045776367</v>
       </c>
       <c r="E35" t="n">
-        <v>40.02000045776367</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>38.90999984741211</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>39.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10756200</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0.01661558138103936</v>
@@ -11277,16 +11275,16 @@
         <v>22.03000068664551</v>
       </c>
       <c r="E36" t="n">
-        <v>22.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>21.30999946594238</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>21.39999961853027</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>4639100</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0.02751866314791696</v>
@@ -11578,16 +11576,16 @@
         <v>24.20000076293945</v>
       </c>
       <c r="E37" t="n">
-        <v>24.95000076293945</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>24.10000038146973</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>24.95000076293945</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9388600</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>-0.03547227517878826</v>
@@ -11879,16 +11877,16 @@
         <v>10.81999969482422</v>
       </c>
       <c r="E38" t="n">
-        <v>11.21000003814697</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>10.77000045776367</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>11.21000003814697</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>6538400</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>-0.03392858222431083</v>
@@ -12184,16 +12182,16 @@
         <v>6.28000020980835</v>
       </c>
       <c r="E39" t="n">
-        <v>6.289999961853027</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>6.170000076293945</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>6.239999771118164</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5982600</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0.008025712773962246</v>
@@ -12276,14 +12274,16 @@
       <c r="AI39" t="n">
         <v>0</v>
       </c>
-      <c r="AJ39" t="n">
-        <v>6</v>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
       </c>
       <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
         <v>6.1</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>6.2</v>
       </c>
       <c r="AM39" t="n">
         <v>6.3</v>
@@ -12485,16 +12485,16 @@
         <v>23.72999954223633</v>
       </c>
       <c r="E40" t="n">
-        <v>24.44000053405762</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>23.70000076293945</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>24.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3157800</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>-0.03654078965475127</v>
@@ -12782,16 +12782,16 @@
         <v>26.13999938964844</v>
       </c>
       <c r="E41" t="n">
-        <v>26.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>25.72999954223633</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>25.98999977111816</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2181000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0.007710055955019612</v>
@@ -12875,10 +12875,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AK41" t="n">
         <v>25.8</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>25.9</v>
       </c>
       <c r="AL41" t="n">
         <v>26</v>
@@ -12887,10 +12887,10 @@
         <v>26.2</v>
       </c>
       <c r="AN41" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AO41" t="n">
         <v>26.6</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>26.7</v>
       </c>
       <c r="AP41" t="n">
         <v>2</v>
@@ -13079,16 +13079,16 @@
         <v>26.70999908447266</v>
       </c>
       <c r="E42" t="n">
-        <v>26.85000038146973</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>26.51000022888184</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>26.80999946594238</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2389700</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>-0.002986257122832625</v>
@@ -13181,13 +13181,13 @@
         <v>24.6</v>
       </c>
       <c r="AM42" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AN42" t="n">
         <v>27.6</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>28.5</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>28.6</v>
       </c>
       <c r="AP42" t="n">
         <v>1</v>
@@ -13376,16 +13376,16 @@
         <v>14.15999984741211</v>
       </c>
       <c r="E43" t="n">
-        <v>14.1899995803833</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>13.86999988555908</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>13.93000030517578</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>35863900</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0.01505376638123668</v>
@@ -13679,16 +13679,16 @@
         <v>42.29999923706055</v>
       </c>
       <c r="E44" t="n">
-        <v>42.36000061035156</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>41.5099983215332</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>41.70999908447266</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>17654200</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0.01414529286833588</v>
@@ -13784,10 +13784,10 @@
         <v>42.3</v>
       </c>
       <c r="AN44" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="AO44" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="AP44" t="n">
         <v>3</v>
@@ -14000,16 +14000,16 @@
         <v>18.27000045776367</v>
       </c>
       <c r="E45" t="n">
-        <v>18.30999946594238</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>17.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>18.30999946594238</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>6421200</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>-0.00218454447544425</v>
@@ -14301,16 +14301,16 @@
         <v>11.35000038146973</v>
       </c>
       <c r="E46" t="n">
-        <v>11.40999984741211</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>11.09000015258789</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>11.19999980926514</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>20426900</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0.01702513769314051</v>
@@ -14404,7 +14404,7 @@
         </is>
       </c>
       <c r="AL46" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
         <v>13.4</v>
@@ -14606,16 +14606,16 @@
         <v>16.85000038146973</v>
       </c>
       <c r="E47" t="n">
-        <v>17.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>16.81999969482422</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>17.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>4112400</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>-0.02034885848516166</v>
@@ -14907,16 +14907,16 @@
         <v>6.630000114440918</v>
       </c>
       <c r="E48" t="n">
-        <v>6.760000228881836</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>6.519999980926514</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>6.639999866485596</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>35252600</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0.004545486400278964</v>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="AL48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
         <v>8.4</v>
@@ -15212,16 +15212,16 @@
         <v>16.60000038146973</v>
       </c>
       <c r="E49" t="n">
-        <v>16.61000061035156</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>16.31999969482422</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>16.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>12801500</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0.006670746626948221</v>
@@ -15517,16 +15517,16 @@
         <v>5.380000114440918</v>
       </c>
       <c r="E50" t="n">
-        <v>5.380000114440918</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>5.199999809265137</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>5.210000038146973</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>8513200</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0.03262957294610858</v>
@@ -15818,16 +15818,16 @@
         <v>30.65999984741211</v>
       </c>
       <c r="E51" t="n">
-        <v>30.65999984741211</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>30.15999984741211</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>30.21999931335449</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>5607900</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0.01288402324911142</v>
@@ -16123,16 +16123,16 @@
         <v>6.550000190734863</v>
       </c>
       <c r="E52" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>6.420000076293945</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>25485500</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>-0.02384498457563267</v>
@@ -16221,21 +16221,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AL52" t="n">
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="AN52" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO52" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AP52" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ52" t="n">
         <v>-1</v>
       </c>
@@ -16424,16 +16424,16 @@
         <v>54.06000137329102</v>
       </c>
       <c r="E53" t="n">
-        <v>54.06000137329102</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>52.90999984741211</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>53.59999847412109</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>9863000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0.0009258110222505334</v>
@@ -16725,16 +16725,16 @@
         <v>49.09999847412109</v>
       </c>
       <c r="E54" t="n">
-        <v>49.09999847412109</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>47.88999938964844</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>48.11999893188477</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>23881500</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0.007799615022515471</v>
@@ -17340,7 +17340,7 @@
         <v>60.75</v>
       </c>
       <c r="H56" t="n">
-        <v>6811200</v>
+        <v>6821000</v>
       </c>
       <c r="I56" t="n">
         <v>-0.0004868180021768698</v>
@@ -17946,7 +17946,7 @@
         <v>17.79999923706055</v>
       </c>
       <c r="H58" t="n">
-        <v>19738600</v>
+        <v>19749900</v>
       </c>
       <c r="I58" t="n">
         <v>0.02659871597765551</v>
@@ -18247,7 +18247,7 @@
         <v>15.72999954223633</v>
       </c>
       <c r="H59" t="n">
-        <v>7655500</v>
+        <v>7661900</v>
       </c>
       <c r="I59" t="n">
         <v>0.01269034304318195</v>
@@ -18548,7 +18548,7 @@
         <v>37.54999923706055</v>
       </c>
       <c r="H60" t="n">
-        <v>8933000</v>
+        <v>8950500</v>
       </c>
       <c r="I60" t="n">
         <v>0.0008006079081817052</v>
@@ -19152,7 +19152,7 @@
         <v>37.68000030517578</v>
       </c>
       <c r="H62" t="n">
-        <v>12849600</v>
+        <v>12867400</v>
       </c>
       <c r="I62" t="n">
         <v>0.01314751554165694</v>
@@ -19770,7 +19770,7 @@
         <v>26.75</v>
       </c>
       <c r="H64" t="n">
-        <v>16228800</v>
+        <v>16274700</v>
       </c>
       <c r="I64" t="n">
         <v>0.01158876508195816</v>
@@ -20372,7 +20372,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="H66" t="n">
-        <v>8696100</v>
+        <v>8698200</v>
       </c>
       <c r="I66" t="n">
         <v>-0.004159221339366748</v>
@@ -20677,7 +20677,7 @@
         <v>44.61000061035156</v>
       </c>
       <c r="H67" t="n">
-        <v>3336000</v>
+        <v>3340600</v>
       </c>
       <c r="I67" t="n">
         <v>-0.007160431968171288</v>
@@ -21576,7 +21576,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="H70" t="n">
-        <v>5650500</v>
+        <v>5660200</v>
       </c>
       <c r="I70" t="n">
         <v>0.01942318588297054</v>
@@ -21877,7 +21877,7 @@
         <v>37</v>
       </c>
       <c r="H71" t="n">
-        <v>13508600</v>
+        <v>13516200</v>
       </c>
       <c r="I71" t="n">
         <v>0.02704869623475892</v>
@@ -22178,7 +22178,7 @@
         <v>6.949999809265137</v>
       </c>
       <c r="H72" t="n">
-        <v>9786600</v>
+        <v>9841300</v>
       </c>
       <c r="I72" t="n">
         <v>-0.00714288439069477</v>
@@ -22483,7 +22483,7 @@
         <v>70.98999786376953</v>
       </c>
       <c r="H73" t="n">
-        <v>29050900</v>
+        <v>29094800</v>
       </c>
       <c r="I73" t="n">
         <v>-0.02178194170868408</v>
@@ -23984,7 +23984,7 @@
         <v>50.34000015258789</v>
       </c>
       <c r="H78" t="n">
-        <v>13007000</v>
+        <v>13012200</v>
       </c>
       <c r="I78" t="n">
         <v>0.003391899187261016</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -1005,19 +1005,19 @@
         <v>1.117441734621751</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.037769122079782</v>
+        <v>1.037769122079783</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5680223922099696</v>
+        <v>0.56802239220997</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5389173030911808</v>
+        <v>0.5389173030911819</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1678397311923873</v>
+        <v>0.1678397311923872</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3767299459438371</v>
+        <v>0.3767299459438373</v>
       </c>
       <c r="AH2" t="n">
         <v>0.183877482932149</v>
@@ -1308,7 +1308,7 @@
         <v>1.482143254178956</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.345785936116726</v>
+        <v>1.345785936116727</v>
       </c>
       <c r="AD3" t="n">
         <v>1.357134928290587</v>
@@ -1317,13 +1317,13 @@
         <v>1.782718647365071</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5533491184064683</v>
+        <v>0.5533491184064684</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4089255248069094</v>
+        <v>0.4089255248069097</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2598746505714941</v>
+        <v>0.2598746505714942</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1581,49 +1581,49 @@
         <v>14.11588423158032</v>
       </c>
       <c r="S4" t="n">
-        <v>9.049999961853027</v>
+        <v>9.050799961090087</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>23.20441619369092</v>
+        <v>23.19352616856816</v>
       </c>
       <c r="V4" t="n">
-        <v>8.795866613388062</v>
+        <v>8.78733328183492</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>26.76408259260116</v>
+        <v>26.88718250370031</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.642249941825867</v>
+        <v>8.643199944496155</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.01732411796678</v>
+        <v>29.00314339749141</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.093158117421933</v>
+        <v>1.09488064663975</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.092664426595361</v>
+        <v>1.094164370342352</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.566309053401028</v>
+        <v>1.565861868681723</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.390782817581205</v>
+        <v>2.38591476437816</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.52462030673516</v>
+        <v>2.532198525694908</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.846467779067128</v>
+        <v>2.84871463753693</v>
       </c>
       <c r="AH4" t="n">
         <v>0.5026143628794456</v>
@@ -1886,52 +1886,52 @@
         <v>14.12055912381107</v>
       </c>
       <c r="S5" t="n">
-        <v>11.45159997940064</v>
+        <v>11.43779996871948</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.68182367253404</v>
+        <v>20.82742951109186</v>
       </c>
       <c r="V5" t="n">
-        <v>12.05453331629435</v>
+        <v>12.04679998397827</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>14.64566343803166</v>
+        <v>14.71925916595467</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.9674499797821</v>
+        <v>11.9592999792099</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.47990355649554</v>
+        <v>15.55860057736629</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.255291798531089</v>
+        <v>2.266588419987757</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.173033947585371</v>
+        <v>2.183564485461038</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.3246183729773</v>
+        <v>2.325289575894004</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.777212720204536</v>
+        <v>2.786380568014423</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.529543060542095</v>
+        <v>1.52950363436611</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.383062267728382</v>
+        <v>1.382321677108845</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3295757111364941</v>
+        <v>0.3295757111364939</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -2187,52 +2187,52 @@
         <v>3.648799424309228</v>
       </c>
       <c r="S6" t="n">
-        <v>53.38039978027344</v>
+        <v>53.38959976196289</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>6.593434594145038</v>
+        <v>6.57506664138168</v>
       </c>
       <c r="V6" t="n">
-        <v>55.56793329874674</v>
+        <v>55.50513328552246</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>2.397188716684204</v>
+        <v>2.51304367324215</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.61959997177124</v>
+        <v>55.5646499633789</v>
       </c>
       <c r="Z6" t="n">
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.302068973450933</v>
+        <v>2.403239403793768</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8516261939450975</v>
+        <v>0.8546199318310106</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.7985414808241237</v>
+        <v>0.8012896676235417</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.5338565587700824</v>
+        <v>0.5367794071020036</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.7379965736998469</v>
+        <v>0.7415126040125374</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1636188919900236</v>
+        <v>0.1717356008351789</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1406518346797157</v>
+        <v>0.1468850727008536</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2338193696120586</v>
+        <v>0.2338193696120587</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -2484,52 +2484,52 @@
         <v>21.80877171245388</v>
       </c>
       <c r="S7" t="n">
-        <v>15.94280000686646</v>
+        <v>15.93680002212524</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>22.56316899861755</v>
+        <v>22.60931233622644</v>
       </c>
       <c r="V7" t="n">
-        <v>19.50526669184367</v>
+        <v>19.44246669133504</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1780761280141788</v>
+        <v>0.5016556064656644</v>
       </c>
       <c r="Y7" t="n">
-        <v>20.9014000082016</v>
+        <v>20.86085000514984</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-6.513434947611398</v>
+        <v>-6.331712702485399</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.374823595892837</v>
+        <v>3.369008775261449</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.406636616647534</v>
+        <v>3.401656468643951</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.878044665238835</v>
+        <v>2.885892443904195</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.742656071648707</v>
+        <v>2.745681648393913</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02383334917000557</v>
+        <v>0.06750537190326113</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.8949401367648341</v>
+        <v>-0.8798791135562546</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.7395874625743636</v>
+        <v>0.7395874625743637</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2781,52 +2781,52 @@
         <v>8.373734933758785</v>
       </c>
       <c r="S8" t="n">
-        <v>16.40020004272461</v>
+        <v>16.38060005187988</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>15.85224540251083</v>
+        <v>15.99086687803912</v>
       </c>
       <c r="V8" t="n">
-        <v>16.66600002924601</v>
+        <v>16.64446669896444</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>14.00455998234856</v>
+        <v>14.15205030980126</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.38105005264282</v>
+        <v>16.38290005207062</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.98768051462397</v>
+        <v>15.97458288588295</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.415752854138487</v>
+        <v>1.417598913870871</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.310269849424369</v>
+        <v>1.311818732157197</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.317494573513383</v>
+        <v>1.312397339501384</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.874967147959138</v>
+        <v>1.889120497212674</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.119796394896102</v>
+        <v>1.127244448212267</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.380384942234415</v>
+        <v>1.373020447868911</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2856990230040565</v>
+        <v>0.2856990230040567</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -3086,52 +3086,52 @@
         <v>6.958026309251104</v>
       </c>
       <c r="S9" t="n">
-        <v>20.98080009460449</v>
+        <v>20.96280010223389</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>13.05574242354286</v>
+        <v>13.1528192687712</v>
       </c>
       <c r="V9" t="n">
-        <v>21.59560001373291</v>
+        <v>21.54946667989095</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>9.837185807621234</v>
+        <v>10.0723264557122</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.07515002250672</v>
+        <v>22.06745002746582</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.451135277317576</v>
+        <v>7.488628200502815</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.701059416000045</v>
+        <v>1.711590981969224</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.509495606856978</v>
+        <v>1.517773170636018</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.156097492463378</v>
+        <v>1.153928468370479</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.762774334114171</v>
+        <v>1.77809469531281</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.9724278580475842</v>
+        <v>0.9944526195888395</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.764908243170794</v>
+        <v>0.7686190784165683</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3386870446202586</v>
+        <v>0.3386870446202587</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -3407,64 +3407,64 @@
         <v>6.116014494295443</v>
       </c>
       <c r="S10" t="n">
-        <v>15.54341781616211</v>
+        <v>15.51821781158447</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>8.27734364964539</v>
+        <v>8.453175023373667</v>
       </c>
       <c r="V10" t="n">
-        <v>16.01913928985596</v>
+        <v>15.99713928222656</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>5.061823979291892</v>
+        <v>5.206309870695645</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.28170446395874</v>
+        <v>16.27785446166992</v>
       </c>
       <c r="Z10" t="n">
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.367555657093671</v>
+        <v>3.392003923712987</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.859484328500814</v>
+        <v>1.870595243849852</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.726539321349437</v>
+        <v>1.737271487406263</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.228992803996025</v>
+        <v>1.229118177052025</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.470820305567899</v>
+        <v>1.504239573339923</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5328773217437925</v>
+        <v>0.5485117937815541</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.3047099565328528</v>
+        <v>0.30686199840862</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.243004415677737</v>
+        <v>0.2430044156777369</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AL10" t="n">
         <v>16.6</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>16.7</v>
       </c>
       <c r="AM10" t="n">
         <v>16.9</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -3726,52 +3726,52 @@
         <v>6.835613219287648</v>
       </c>
       <c r="S11" t="n">
-        <v>17.69134044647217</v>
+        <v>17.66054046630859</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>8.697244284115195</v>
+        <v>8.886812263315653</v>
       </c>
       <c r="V11" t="n">
-        <v>18.38164683024089</v>
+        <v>18.35518016815185</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>4.615216034940679</v>
+        <v>4.766062583261245</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.74858510971069</v>
+        <v>18.74178510665893</v>
       </c>
       <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.567737403695016</v>
+        <v>2.604951624399598</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.025396044388794</v>
+        <v>2.038341496692606</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.891048141915106</v>
+        <v>1.903698783793803</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.348992209675996</v>
+        <v>1.349285347274868</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.516084931593397</v>
+        <v>1.551813186192003</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4582179230801216</v>
+        <v>0.4741128780598127</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.21004270174057</v>
+        <v>0.2133015402357188</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2719977019374989</v>
+        <v>0.271997701937499</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -4043,52 +4043,52 @@
         <v>0.7626437757639044</v>
       </c>
       <c r="S12" t="n">
-        <v>39.74119995117187</v>
+        <v>39.65779991149903</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.783541545394833</v>
+        <v>1.997591528547511</v>
       </c>
       <c r="V12" t="n">
-        <v>37.34306655883789</v>
+        <v>37.3667332204183</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>8.319976076968036</v>
+        <v>8.251370341457537</v>
       </c>
       <c r="Y12" t="n">
-        <v>36.98339996337891</v>
+        <v>36.99869997024536</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.373396721213261</v>
+        <v>9.328167734189725</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.406164493350245</v>
+        <v>1.415462233398593</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.251810554239312</v>
+        <v>1.259928899391059</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2048706890228887</v>
+        <v>0.2036342951144773</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.3936632877400021</v>
+        <v>0.4402601943037937</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.260337311203485</v>
+        <v>1.260740647215273</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.227635897572389</v>
+        <v>1.23018678702424</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2648415560292979</v>
+        <v>0.2648415560292978</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -4360,49 +4360,49 @@
         <v>-1.86770225058903</v>
       </c>
       <c r="S13" t="n">
-        <v>3.76360002040863</v>
+        <v>3.758400020599365</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>3.092785986850158</v>
+        <v>3.235421806488834</v>
       </c>
       <c r="V13" t="n">
-        <v>3.906200014750163</v>
+        <v>3.893400015830994</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6707260306771643</v>
+        <v>-0.3441696546871668</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.362900011539459</v>
+        <v>4.348700011968613</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-11.06832372553385</v>
+        <v>-10.77793124928659</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.5816644888549142</v>
+        <v>-0.5806205782083358</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.520898637442344</v>
+        <v>-0.5187802022531025</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.2558171894493598</v>
+        <v>-0.2548338394934332</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3088241059127128</v>
+        <v>0.3242891793317066</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.03942286204554044</v>
+        <v>-0.02029163770708006</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.5769276426970003</v>
+        <v>-0.5640619711779972</v>
       </c>
       <c r="AH13" t="n">
         <v>0.3653798124603019</v>
@@ -4701,13 +4701,13 @@
         <v>1.556981664749986</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.377826504765573</v>
+        <v>2.377826504765575</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.555768193408861</v>
+        <v>1.555768193408865</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.342148733061707</v>
+        <v>1.342148733061706</v>
       </c>
       <c r="AH14" t="n">
         <v>0.2570939874438469</v>
@@ -4992,73 +4992,73 @@
         <v>-3.500552857964356</v>
       </c>
       <c r="S15" t="n">
-        <v>21.40659999847412</v>
+        <v>21.40259998321533</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.0205626752421</v>
+        <v>-3.002437810534444</v>
       </c>
       <c r="V15" t="n">
-        <v>22.34540002187093</v>
+        <v>22.32420001983643</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.094971633702496</v>
+        <v>-7.006745099778275</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.42435000419617</v>
+        <v>22.42875</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-7.422064742134729</v>
+        <v>-7.440226366240495</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4141259618046725</v>
+        <v>0.4144773108239388</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.3248334855478541</v>
+        <v>0.3251313670643313</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.7247081420941704</v>
+        <v>-0.7244863061382024</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.466926389153756</v>
+        <v>-0.4638571435504508</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.5759759636244147</v>
+        <v>-0.5679615075669434</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.5889213896304092</v>
+        <v>-0.589134320393386</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.3020926240872248</v>
+        <v>0.3020926240872247</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AK15" t="n">
         <v>19.8</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>20.2</v>
       </c>
       <c r="AL15" t="n">
         <v>20.5</v>
       </c>
       <c r="AM15" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AN15" t="n">
         <v>22.3</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>22.4</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>22.5</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -5231,7 +5231,7 @@
         <v>-1</v>
       </c>
       <c r="CR15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CS15" t="n">
         <v>3</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -5301,58 +5301,58 @@
         <v>5.369241242426846</v>
       </c>
       <c r="S16" t="n">
-        <v>18.54459991455078</v>
+        <v>18.50299991607666</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.916459269097705</v>
+        <v>2.14559641276695</v>
       </c>
       <c r="V16" t="n">
-        <v>19.1449332300822</v>
+        <v>19.14399990081787</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.279365190822711</v>
+        <v>-1.274552254240104</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.6503999042511</v>
+        <v>18.67574990272522</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.338307572816611</v>
+        <v>1.200753474281274</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.275567964564878</v>
+        <v>1.276110817356636</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.268579279835404</v>
+        <v>1.269095841318217</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.7406573397469496</v>
+        <v>0.7415112012743801</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1945658206352129</v>
+        <v>0.2179642528605256</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.09564622336133149</v>
+        <v>-0.09528785041312589</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.09945766724865011</v>
+        <v>0.0892774880250209</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.3817646087687524</v>
+        <v>0.3817646087687523</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AK16" t="n">
         <v>18.5</v>
@@ -5625,22 +5625,22 @@
         <v>-49.95311713416201</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.003516087471444692</v>
+        <v>-0.00351608747144469</v>
       </c>
       <c r="AC17" t="n">
         <v>-0.127021599367817</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.7723597449664806</v>
+        <v>-0.7723597449664804</v>
       </c>
       <c r="AE17" t="n">
         <v>-1.059482574693821</v>
       </c>
       <c r="AF17" t="n">
-        <v>-1.812744240873288</v>
+        <v>-1.812744240873289</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.950042578578796</v>
+        <v>-1.950042578578795</v>
       </c>
       <c r="AH17" t="n">
         <v>1.215915413961654</v>
@@ -5903,49 +5903,49 @@
         <v>11.48114334155592</v>
       </c>
       <c r="S18" t="n">
-        <v>8.9532000541687</v>
+        <v>8.942600059509278</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>15.04266774357487</v>
+        <v>15.17903207336404</v>
       </c>
       <c r="V18" t="n">
-        <v>10.5568666712443</v>
+        <v>10.53000000635783</v>
       </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.433169694272218</v>
+        <v>-2.184233765281064</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.93130001544952</v>
+        <v>10.90835001468658</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>-5.7751577929654</v>
+        <v>-5.576918811118663</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.298390712051078</v>
+        <v>1.304875037517943</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.232451027944498</v>
+        <v>1.238366265812817</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.250248698321863</v>
+        <v>1.251324210516027</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.514763309673276</v>
+        <v>1.528177633737851</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.223979504379862</v>
+        <v>-0.20299058082927</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.3738927694130237</v>
+        <v>-0.3652914478602585</v>
       </c>
       <c r="AH18" t="n">
         <v>0.4788591673696178</v>
@@ -5972,7 +5972,7 @@
         <v>10.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -6204,49 +6204,49 @@
         <v>2.675387020861253</v>
       </c>
       <c r="S19" t="n">
-        <v>10.917799949646</v>
+        <v>10.90759996414184</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>4.508233344045406</v>
+        <v>4.605961759891062</v>
       </c>
       <c r="V19" t="n">
-        <v>11.46053337732951</v>
+        <v>11.45126671473185</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4409352362025379</v>
+        <v>-0.3603694538583604</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43165003299713</v>
+        <v>11.43030003547668</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.1893881069008371</v>
+        <v>-0.1775997830465327</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.169705277719697</v>
+        <v>1.176720456068453</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.015777678635765</v>
+        <v>1.021414061690184</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.5849032278664782</v>
+        <v>0.5840961167980332</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.8136703528507664</v>
+        <v>0.8314681788314903</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.06334942315824177</v>
+        <v>-0.05167247894013056</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.02660717018577308</v>
+        <v>-0.02488757246163284</v>
       </c>
       <c r="AH19" t="n">
         <v>0.2558935783628294</v>
@@ -6505,52 +6505,52 @@
         <v>-14.53138772165918</v>
       </c>
       <c r="S20" t="n">
-        <v>5.796999988555908</v>
+        <v>5.789599990844726</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-14.26600310500038</v>
+        <v>-14.15642189355284</v>
       </c>
       <c r="V20" t="n">
-        <v>5.113666655222575</v>
+        <v>5.113799988428751</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.809468718188702</v>
+        <v>-2.812002787799385</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.248099987506866</v>
+        <v>5.246899988651275</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-5.299064384772302</v>
+        <v>-5.27740568828343</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.1455067252069277</v>
+        <v>-0.1453746746409427</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.293436002419844</v>
+        <v>-0.2931953477180765</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.852291571726506</v>
+        <v>-1.851499888982379</v>
       </c>
       <c r="AE20" t="n">
-        <v>-1.377594511113835</v>
+        <v>-1.374732168145546</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.2363769656802364</v>
+        <v>-0.2362161567723928</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.482053813970006</v>
+        <v>-0.4797717921566819</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.5186694655011158</v>
+        <v>0.518669465501116</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -6569,13 +6569,13 @@
         <v>4.1</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AP20" t="n">
         <v>1</v>
@@ -6810,52 +6810,52 @@
         <v>4.793501452164506</v>
       </c>
       <c r="S21" t="n">
-        <v>2.24239999294281</v>
+        <v>2.242799997329712</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>8.36603970767033</v>
+        <v>8.346712575814674</v>
       </c>
       <c r="V21" t="n">
-        <v>2.551599998474121</v>
+        <v>2.542466665903727</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.765634573978553</v>
+        <v>-4.423523055573617</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.837172714471817</v>
+        <v>2.830913624763489</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-14.35135216258473</v>
+        <v>-14.16198482706378</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.47086756479077</v>
+        <v>1.472871970352245</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.282900025036134</v>
+        <v>1.284099130569213</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.5546001951148781</v>
+        <v>0.5552752223239752</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.7377618974963798</v>
+        <v>0.7377215630682439</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.2149461967395295</v>
+        <v>-0.1998090673177439</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.5314685391586997</v>
+        <v>-0.525520711565018</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.4236705178977769</v>
+        <v>0.4236705178977765</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -7111,49 +7111,49 @@
         <v>5.783515830741864</v>
       </c>
       <c r="S22" t="n">
-        <v>44.84340011596679</v>
+        <v>44.80700012207031</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>7.239861447225815</v>
+        <v>7.326980207497733</v>
       </c>
       <c r="V22" t="n">
-        <v>46.4713331858317</v>
+        <v>46.43166653951009</v>
       </c>
       <c r="W22" t="n">
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>3.483151559873239</v>
+        <v>3.571557380277693</v>
       </c>
       <c r="Y22" t="n">
-        <v>47.7810499382019</v>
+        <v>47.7587999534607</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.6465957001480112</v>
+        <v>0.6934851785428837</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.027861710756844</v>
+        <v>2.035676607121343</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.899628374849948</v>
+        <v>1.905659495014955</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.019030002089153</v>
+        <v>1.018950538365087</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.9287558448009663</v>
+        <v>0.939488660113713</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.2836554473538114</v>
+        <v>0.2905834779969984</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.05145780003503854</v>
+        <v>0.05504620652987849</v>
       </c>
       <c r="AH22" t="n">
         <v>0.2429696558184775</v>
@@ -7412,52 +7412,52 @@
         <v>5.249565508401945</v>
       </c>
       <c r="S23" t="n">
-        <v>15.12639993667602</v>
+        <v>15.11479993820191</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>9.808022264956415</v>
+        <v>9.892295486959188</v>
       </c>
       <c r="V23" t="n">
-        <v>15.15733327229818</v>
+        <v>15.15493327458699</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>9.583924242850211</v>
+        <v>9.601278404864647</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.68764995574951</v>
+        <v>14.6923499584198</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>13.08821125499074</v>
+        <v>13.05203495260339</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.637780323327997</v>
+        <v>1.642802279993286</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.503268896531114</v>
+        <v>1.50670674283819</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.112939585691165</v>
+        <v>1.110965210145191</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.626708408308669</v>
+        <v>1.636555398788276</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.325605011523347</v>
+        <v>1.319766520795003</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.653974668024959</v>
+        <v>1.639606908377181</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.1834865298867226</v>
+        <v>0.1834865298867225</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -7713,52 +7713,52 @@
         <v>8.574900599377203</v>
       </c>
       <c r="S24" t="n">
-        <v>3.732200016975403</v>
+        <v>3.723200016021729</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>10.39065073736199</v>
+        <v>10.6574953757477</v>
       </c>
       <c r="V24" t="n">
-        <v>4.317800002098084</v>
+        <v>4.298866669336955</v>
       </c>
       <c r="W24" t="n">
         <v>-1</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.581039335839722</v>
+        <v>-4.160789285550485</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.657050009965896</v>
+        <v>4.64450001001358</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>-11.53198104502956</v>
+        <v>-11.29292977335927</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.385115775039602</v>
+        <v>1.397680338874798</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.356124660536477</v>
+        <v>1.367074183201185</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.038256838372487</v>
+        <v>1.035465935846983</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.138946627788712</v>
+        <v>1.167298953214355</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.4515913684880666</v>
+        <v>-0.4093218865644171</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.175632990692219</v>
+        <v>-1.149160434799572</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.5080534153449564</v>
+        <v>0.5080534153449562</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -8014,52 +8014,52 @@
         <v>-0.2550743175868578</v>
       </c>
       <c r="S25" t="n">
-        <v>57.82620002746582</v>
+        <v>57.75860000610351</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.725754116156989</v>
+        <v>-2.611905423511123</v>
       </c>
       <c r="V25" t="n">
-        <v>57.17199984232585</v>
+        <v>57.21113316853841</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.612677263115898</v>
+        <v>-1.679975758751371</v>
       </c>
       <c r="Y25" t="n">
-        <v>55.08789989471435</v>
+        <v>55.17499988555908</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.109537861321064</v>
+        <v>1.948346382728815</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.2848467402616797</v>
+        <v>-0.2872442556853326</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.2734579448140687</v>
+        <v>-0.2756336358409601</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.04278093414625331</v>
+        <v>-0.04292534460206681</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.3239333791823263</v>
+        <v>-0.3110436348522304</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.1031470961709494</v>
+        <v>-0.1071243362938473</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.1218407301852701</v>
+        <v>0.1119499382773583</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.2213078459724424</v>
+        <v>0.2213078459724423</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -8315,49 +8315,49 @@
         <v>1.013791349060602</v>
       </c>
       <c r="S26" t="n">
-        <v>5.504999990463257</v>
+        <v>5.488199987411499</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>12.0799289188505</v>
+        <v>12.42301830192628</v>
       </c>
       <c r="V26" t="n">
-        <v>5.935599997838338</v>
+        <v>5.907866665522257</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.949054493917591</v>
+        <v>4.437023135634959</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.82440000295639</v>
+        <v>6.797850000858307</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-9.589120309169354</v>
+        <v>-9.236007332981577</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6299096870252072</v>
+        <v>0.6300493804231883</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.513115948452322</v>
+        <v>0.5133461298483243</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.09586343753857535</v>
+        <v>0.09525861942059055</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.8853159988425701</v>
+        <v>0.9082039618144029</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.2171461394302067</v>
+        <v>0.2429192736231671</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.5398249818666295</v>
+        <v>-0.517876076900562</v>
       </c>
       <c r="AH26" t="n">
         <v>0.7708941800256122</v>
@@ -8616,52 +8616,52 @@
         <v>-7.392121019880789</v>
       </c>
       <c r="S27" t="n">
-        <v>30.65499996185303</v>
+        <v>30.69639995574951</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.236831851993236</v>
+        <v>-8.360592117259724</v>
       </c>
       <c r="V27" t="n">
-        <v>32.40086675008138</v>
+        <v>32.35306674957275</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-13.18133746932572</v>
+        <v>-13.05306733823594</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.07609998703003</v>
+        <v>33.05704998970032</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-14.95370018896701</v>
+        <v>-14.90469001459251</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.3036617230383237</v>
+        <v>0.303696227865927</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.1779820471334128</v>
+        <v>0.1779571774401867</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.041505969653493</v>
+        <v>-1.042261089946044</v>
       </c>
       <c r="AE27" t="n">
-        <v>-1.05005152967364</v>
+        <v>-1.066378057086903</v>
       </c>
       <c r="AF27" t="n">
-        <v>-1.245470293873776</v>
+        <v>-1.238961849002135</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.132549758738735</v>
+        <v>-1.134227253754584</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.4346243559676437</v>
+        <v>0.4346243559676436</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -8921,49 +8921,49 @@
         <v>1.777939096246211</v>
       </c>
       <c r="S28" t="n">
-        <v>19.707200050354</v>
+        <v>19.63700004577637</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>3.566208265316112</v>
+        <v>3.936445484716502</v>
       </c>
       <c r="V28" t="n">
-        <v>19.0654000600179</v>
+        <v>19.07300005594889</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>7.052565291897382</v>
+        <v>7.009908181939135</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.55730009555817</v>
+        <v>18.57115009784699</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.983670805094121</v>
+        <v>9.901647124042729</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.3772566050101022</v>
+        <v>0.3797417306643875</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.2813166101984144</v>
+        <v>0.283072052799369</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.3696230012123142</v>
+        <v>0.3691606610938671</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.6576676071715039</v>
+        <v>0.7224846496832843</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.107822669138254</v>
+        <v>1.100949290427208</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.43041627418636</v>
+        <v>1.422392029926317</v>
       </c>
       <c r="AH28" t="n">
         <v>0.2348941449330692</v>
@@ -9234,52 +9234,52 @@
         <v>7.636330388858652</v>
       </c>
       <c r="S29" t="n">
-        <v>23.95340007781983</v>
+        <v>23.96940006256104</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>16.85188607957213</v>
+        <v>16.77388544587354</v>
       </c>
       <c r="V29" t="n">
-        <v>24.17626667022705</v>
+        <v>24.11460000356038</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>15.77469819022019</v>
+        <v>16.070761144641</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.38699999809265</v>
+        <v>25.33005000114441</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>10.25327834411738</v>
+        <v>10.50116272906519</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.7997387264127522</v>
+        <v>0.7994258129431635</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.6938004261336377</v>
+        <v>0.693425824887595</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.8658475375458089</v>
+        <v>0.8667164322836487</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.594508159309033</v>
+        <v>1.59079710952683</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.995860537142889</v>
+        <v>1.016665893611566</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.5616108565513535</v>
+        <v>0.57711586147512</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.4020542244199047</v>
+        <v>0.4020542244199046</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -9535,49 +9535,49 @@
         <v>-0.007316574819789336</v>
       </c>
       <c r="S30" t="n">
-        <v>10.80360004425049</v>
+        <v>10.79740003585815</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.717610927525055</v>
+        <v>-2.661750106709607</v>
       </c>
       <c r="V30" t="n">
-        <v>12.63360001881917</v>
+        <v>12.60026668548584</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-16.80914218254492</v>
+        <v>-16.58906520614971</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.16300001144409</v>
+        <v>13.13235000610351</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-20.15497819840235</v>
+        <v>-19.96862538694819</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.117432816074079</v>
+        <v>1.120619787295006</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.011898034659101</v>
+        <v>1.014323657242914</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.000945455208758717</v>
+        <v>-0.0009480566790743055</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.2985031570421562</v>
+        <v>-0.2942372609913997</v>
       </c>
       <c r="AF30" t="n">
-        <v>-1.129647267633705</v>
+        <v>-1.122817820114672</v>
       </c>
       <c r="AG30" t="n">
-        <v>-1.059339729596519</v>
+        <v>-1.056119644309193</v>
       </c>
       <c r="AH30" t="n">
         <v>0.3931660867948943</v>
@@ -9832,49 +9832,49 @@
         <v>2.479172202901462</v>
       </c>
       <c r="S31" t="n">
-        <v>29.51659992218018</v>
+        <v>29.49859992980957</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>4.009272219291127</v>
+        <v>4.072738489245435</v>
       </c>
       <c r="V31" t="n">
-        <v>32.08666665395101</v>
+        <v>32.05713331858317</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-4.321626506007926</v>
+        <v>-4.233480711318006</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.11140003204346</v>
+        <v>32.10610003471375</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-4.39532149858178</v>
+        <v>-4.379539309520598</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.527389560108991</v>
+        <v>1.531327634983034</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.323951486765806</v>
+        <v>1.326864306618019</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.5250509631122704</v>
+        <v>0.5257758363386965</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.7579499728561255</v>
+        <v>0.7692259912037502</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.5473152631028552</v>
+        <v>-0.5340687411145034</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.5599724855686363</v>
+        <v>-0.555069554260377</v>
       </c>
       <c r="AH31" t="n">
         <v>0.2747111824957685</v>
@@ -9898,7 +9898,7 @@
         <v>31.1</v>
       </c>
       <c r="AO31" t="n">
-        <v>31.6</v>
+        <v>39.4</v>
       </c>
       <c r="AP31" t="n">
         <v>1</v>
@@ -10129,52 +10129,52 @@
         <v>1.699976298091221</v>
       </c>
       <c r="S32" t="n">
-        <v>94.88679977416992</v>
+        <v>95.11199981689452</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>3.54443424568484</v>
+        <v>3.299268430005275</v>
       </c>
       <c r="V32" t="n">
-        <v>84.27679977416992</v>
+        <v>84.29173314412435</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>16.58012675288217</v>
+        <v>16.55947307668881</v>
       </c>
       <c r="Y32" t="n">
-        <v>86.74084980010986</v>
+        <v>86.77879981994629</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>13.26843145578171</v>
+        <v>13.21889701615467</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.1969202826513392</v>
+        <v>-0.1974807405581988</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.1706780949952318</v>
+        <v>-0.1712448526911969</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.2660832004196223</v>
+        <v>0.2664279681102634</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.4206083257766076</v>
+        <v>0.3921938389122805</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.392851461971276</v>
+        <v>1.390370591318039</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.073260068778335</v>
+        <v>1.070167366597522</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.2107783505929836</v>
+        <v>0.2107783505929834</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -10432,52 +10432,52 @@
         <v>5.11744174492543</v>
       </c>
       <c r="S33" t="n">
-        <v>26.50440002441406</v>
+        <v>26.49680000305176</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>8.321633608106364</v>
+        <v>8.352703274229324</v>
       </c>
       <c r="V33" t="n">
-        <v>25.56819997151693</v>
+        <v>25.59433330535889</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>12.28791669517489</v>
+        <v>12.17326406568839</v>
       </c>
       <c r="Y33" t="n">
-        <v>24.40169998168945</v>
+        <v>24.4271999835968</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>17.65573343667065</v>
+        <v>17.53291045945427</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.19672527585751</v>
+        <v>1.198373715947922</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.107226754294822</v>
+        <v>1.107949300607298</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.005890418798953</v>
+        <v>1.005275355920703</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.28651011490054</v>
+        <v>1.291064454388393</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.324805999802385</v>
+        <v>1.303091733192684</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.730374172391929</v>
+        <v>1.704631399891429</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.2569322823071294</v>
+        <v>0.2569322823071292</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -10766,7 +10766,7 @@
         <v>1.622550124967579</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.481290476310992</v>
+        <v>1.481290476310991</v>
       </c>
       <c r="AE34" t="n">
         <v>2.12167150497591</v>
@@ -10775,7 +10775,7 @@
         <v>1.255234128368573</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.178632280524772</v>
+        <v>1.178632280524773</v>
       </c>
       <c r="AH34" t="n">
         <v>0.2565553721148922</v>
@@ -11034,49 +11034,49 @@
         <v>6.680894628707805</v>
       </c>
       <c r="S35" t="n">
-        <v>38.20360023498535</v>
+        <v>38.15860023498535</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>9.701702430213849</v>
+        <v>9.831072390824556</v>
       </c>
       <c r="V35" t="n">
-        <v>39.67153345743815</v>
+        <v>39.6359334564209</v>
       </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>5.642500288967932</v>
+        <v>5.737385732296452</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.70410007476806</v>
+        <v>39.69355007171631</v>
       </c>
       <c r="Z35" t="n">
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.555848812817932</v>
+        <v>5.583904114626256</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.565758060882264</v>
+        <v>1.576944587616959</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.485949940150765</v>
+        <v>1.494919793646047</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.552598528588299</v>
+        <v>1.550801754700138</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.066731772351481</v>
+        <v>2.088399989314734</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.8588206408105604</v>
+        <v>0.8694182890649329</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.8023991907892227</v>
+        <v>0.8028049605107276</v>
       </c>
       <c r="AH35" t="n">
         <v>0.2209262787037864</v>
@@ -11335,52 +11335,52 @@
         <v>11.12525652751501</v>
       </c>
       <c r="S36" t="n">
-        <v>19.52159999847412</v>
+        <v>19.56639999389649</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>20.37947710145094</v>
+        <v>20.10385153799654</v>
       </c>
       <c r="V36" t="n">
-        <v>17.08593329111735</v>
+        <v>17.09926662445069</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>37.54004302602071</v>
+        <v>37.43279472814782</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.83935000419617</v>
+        <v>16.8594000005722</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>39.55408014052846</v>
+        <v>39.38811582382775</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.776951226474342</v>
+        <v>1.765385785157492</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.736583200989001</v>
+        <v>1.725540454341069</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.079511913303732</v>
+        <v>2.084685257369994</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.786184882891739</v>
+        <v>2.769091986494741</v>
       </c>
       <c r="AF36" t="n">
-        <v>4.12142368637319</v>
+        <v>4.131946551877424</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.153292331322032</v>
+        <v>4.161230281141509</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.2950131196969971</v>
+        <v>0.2950131196969972</v>
       </c>
       <c r="AI36" t="n">
         <v>1</v>
@@ -11636,52 +11636,52 @@
         <v>3.861519663831148</v>
       </c>
       <c r="S37" t="n">
-        <v>24.73479991912842</v>
+        <v>24.75859992980957</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>5.519351144156802</v>
+        <v>5.417917230631037</v>
       </c>
       <c r="V37" t="n">
-        <v>22.68013332366943</v>
+        <v>22.70853332519531</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>15.07869027485501</v>
+        <v>14.93476926804231</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.41644999504089</v>
+        <v>22.44339999198914</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>16.43235386175658</v>
+        <v>16.29254208714261</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.352225762378501</v>
+        <v>1.352707852588639</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.189266304569052</v>
+        <v>1.190696918727626</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.6255008249143057</v>
+        <v>0.6242141808060482</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.7352236327584748</v>
+        <v>0.7215648739137108</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.996657739762323</v>
+        <v>1.981281321545296</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.030356315110625</v>
+        <v>2.022950263254896</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.3556521246556742</v>
+        <v>0.3556521246556744</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -11937,52 +11937,52 @@
         <v>5.105621743748184</v>
       </c>
       <c r="S38" t="n">
-        <v>10.95020000457764</v>
+        <v>10.96279998779297</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>7.303976138225912</v>
+        <v>7.180647399237186</v>
       </c>
       <c r="V38" t="n">
-        <v>10.0113999970754</v>
+        <v>10.02346666018168</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>17.36620256340265</v>
+        <v>17.22491228186541</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.897694084644318</v>
+        <v>9.910205504894257</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>18.7145197610161</v>
+        <v>18.56464524572312</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.508776016117267</v>
+        <v>1.507307460354059</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.334131681721372</v>
+        <v>1.333968288045903</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.8777946024703103</v>
+        <v>0.8753677214969707</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.026564936379198</v>
+        <v>1.008748493067321</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.188710164005153</v>
+        <v>2.172904288732979</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.248488214259697</v>
+        <v>2.239205222853043</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.3519338025806106</v>
+        <v>0.3519338025806109</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -12242,52 +12242,52 @@
         <v>15.76003412802918</v>
       </c>
       <c r="S39" t="n">
-        <v>7.802600030899048</v>
+        <v>7.799200029373169</v>
       </c>
       <c r="T39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.03332017729844983</v>
+        <v>0.01025953121706118</v>
       </c>
       <c r="V39" t="n">
-        <v>10.00266666094462</v>
+        <v>10.0013999970754</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-22.02079250336375</v>
+        <v>-22.01091654152686</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.8097499871254</v>
+        <v>10.79154999017715</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-27.84291773607344</v>
+        <v>-27.72122449662286</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.007026828477134</v>
+        <v>2.022173538466572</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.889155956481095</v>
+        <v>1.901493755807878</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.098133549992292</v>
+        <v>1.098938505681459</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.001865023362964374</v>
+        <v>0.000574668294968693</v>
       </c>
       <c r="AF39" t="n">
-        <v>-1.111150012863667</v>
+        <v>-1.114203362281154</v>
       </c>
       <c r="AG39" t="n">
-        <v>-1.596986855886831</v>
+        <v>-1.607639745333717</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.6730432153400968</v>
+        <v>0.6730432153400963</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -12543,52 +12543,52 @@
         <v>7.447192669427773</v>
       </c>
       <c r="S40" t="n">
-        <v>22.37499996185303</v>
+        <v>22.40599994659424</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>12.44692688405456</v>
+        <v>12.29135011774596</v>
       </c>
       <c r="V40" t="n">
-        <v>22.13973335266113</v>
+        <v>22.13020001729329</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>13.64183771611662</v>
+        <v>13.69079279785644</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.56065000534058</v>
+        <v>22.54985000610352</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>11.5216088253495</v>
+        <v>11.57502085646739</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.7905192563398504</v>
+        <v>0.7907749068894796</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.8039152225323287</v>
+        <v>0.8040904503102947</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.459863273407383</v>
+        <v>1.460692451322047</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.090085238983271</v>
+        <v>2.069402345714681</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.315820358115355</v>
+        <v>2.319886742818884</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.702722155234557</v>
+        <v>1.710141870731813</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.2902287736062515</v>
+        <v>0.2902287736062516</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -12869,22 +12869,22 @@
         <v>7.632775899651765</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.29560900664296</v>
+        <v>2.295609006642958</v>
       </c>
       <c r="AC41" t="n">
         <v>2.152637851660328</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.919217576551338</v>
+        <v>1.919217576551339</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.366595412793216</v>
+        <v>2.366595412793218</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.9374095284079392</v>
+        <v>0.9374095284079405</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.7277302407121089</v>
+        <v>0.7277302407121086</v>
       </c>
       <c r="AH41" t="n">
         <v>0.3115397901584969</v>
@@ -13143,52 +13143,52 @@
         <v>3.130762400172161</v>
       </c>
       <c r="S42" t="n">
-        <v>26.8353999710083</v>
+        <v>26.78279998779297</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>5.047812085949021</v>
+        <v>5.254120356743953</v>
       </c>
       <c r="V42" t="n">
-        <v>28.00546671549479</v>
+        <v>27.98820006052653</v>
       </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>0.6589207044377807</v>
+        <v>0.7210198336966239</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.98445000648498</v>
+        <v>27.97865000724792</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.7345169461075703</v>
+        <v>0.7553993018067042</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.484630669389062</v>
+        <v>1.494918197101896</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.378483031143162</v>
+        <v>1.387645733035332</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.7679026043838734</v>
+        <v>0.7696637428627021</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.048394672518029</v>
+        <v>1.093743496849712</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.08319688966492689</v>
+        <v>0.09057813359432913</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.09041786546664853</v>
+        <v>0.09236687742495661</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.177431263788284</v>
+        <v>0.1774312637882841</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -13440,83 +13440,81 @@
         <v>5.042550287187135</v>
       </c>
       <c r="S43" t="n">
-        <v>13.54079990386963</v>
+        <v>13.52859991073608</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>8.339242736329172</v>
+        <v>8.436942278498934</v>
       </c>
       <c r="V43" t="n">
-        <v>13.52006663004557</v>
+        <v>13.51239995956421</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>8.505382981566683</v>
+        <v>8.566946805851279</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.38161564350128</v>
+        <v>13.38986270427704</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>9.628018522698794</v>
+        <v>9.560496625615137</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.081638413094953</v>
+        <v>1.087645118980482</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.9840937626284151</v>
+        <v>0.9890471500452338</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.9869366654978078</v>
+        <v>0.9859724536461181</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.428343609539787</v>
+        <v>1.442344916701256</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.028831310747132</v>
+        <v>1.032888500804648</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.191187570061245</v>
+        <v>1.177842674633135</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.2177608177960519</v>
+        <v>0.2177608177960522</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="AL43" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="AM43" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AN43" t="n">
         <v>15.2</v>
       </c>
-      <c r="AN43" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>Foguete</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AP43" t="n">
         <v>1</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
@@ -13741,49 +13739,49 @@
         <v>6.496240791968903</v>
       </c>
       <c r="S44" t="n">
-        <v>41.3155997467041</v>
+        <v>41.27279968261719</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>8.506235189363172</v>
+        <v>8.618756604330089</v>
       </c>
       <c r="V44" t="n">
-        <v>41.97679987589518</v>
+        <v>41.93439987182617</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>6.797092593039548</v>
+        <v>6.905075470446731</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.19349838256836</v>
+        <v>42.20428770065308</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>6.248601205287978</v>
+        <v>6.221439274192467</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.567155729383328</v>
+        <v>1.575580326670323</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.44733894071348</v>
+        <v>1.4546477213352</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.239855838414523</v>
+        <v>1.239612381487488</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.430691370571006</v>
+        <v>1.447683734553498</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.8127136166063221</v>
+        <v>0.8241723492637696</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.7225070245231705</v>
+        <v>0.7176157970435486</v>
       </c>
       <c r="AH44" t="n">
         <v>0.2407353512612255</v>
@@ -14093,7 +14091,7 @@
         <v>1.372171625339919</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.5635902466336111</v>
+        <v>0.5635902466336107</v>
       </c>
       <c r="AC45" t="n">
         <v>0.330707366289912</v>
@@ -14105,10 +14103,10 @@
         <v>0.09795230949363913</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.5071831739717897</v>
+        <v>0.5071831739717892</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.2307033767826986</v>
+        <v>0.2307033767826988</v>
       </c>
       <c r="AH45" t="n">
         <v>0.2073708645724055</v>
@@ -14369,52 +14367,52 @@
         <v>4.362074011233128</v>
       </c>
       <c r="S46" t="n">
-        <v>11.75380002975464</v>
+        <v>11.72880002975464</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0.05275059224678231</v>
+        <v>0.2660135653097099</v>
       </c>
       <c r="V46" t="n">
-        <v>13.69973339080811</v>
+        <v>13.67666672388713</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-14.15891175829555</v>
+        <v>-14.01413468427739</v>
       </c>
       <c r="Y46" t="n">
-        <v>13.87815004825592</v>
+        <v>13.86835004806519</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-15.26247959568843</v>
+        <v>-15.2026002507594</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.001426787249574</v>
+        <v>1.01542485338246</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.8917571153918499</v>
+        <v>0.9040925491253886</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.7363831928426037</v>
+        <v>0.7396700790568111</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.007550668513899374</v>
+        <v>0.03822740052535164</v>
       </c>
       <c r="AF46" t="n">
-        <v>-1.6902724484432</v>
+        <v>-1.675538304064089</v>
       </c>
       <c r="AG46" t="n">
-        <v>-2.077622861340886</v>
+        <v>-2.079127476220697</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.3535732126196817</v>
+        <v>0.3535732126196819</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -14674,52 +14672,52 @@
         <v>-2.169436083865124</v>
       </c>
       <c r="S47" t="n">
-        <v>17.16120004653931</v>
+        <v>17.16820003509521</v>
       </c>
       <c r="T47" t="n">
         <v>-1</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.055873154625449</v>
+        <v>-1.096215633987064</v>
       </c>
       <c r="V47" t="n">
-        <v>17.38513338724772</v>
+        <v>17.35353338241577</v>
       </c>
       <c r="W47" t="n">
         <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.330346486202769</v>
+        <v>-2.152494434118782</v>
       </c>
       <c r="Y47" t="n">
-        <v>17.88290006637573</v>
+        <v>17.864350066185</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-5.048960296082404</v>
+        <v>-4.950364948471508</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.04087292677920182</v>
+        <v>0.0410640468236178</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.04791682031951463</v>
+        <v>0.04823446662819364</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.2260180265821971</v>
+        <v>-0.2273397032300807</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.1050970137871436</v>
+        <v>-0.1094422266485587</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.277135792974627</v>
+        <v>-0.2554578379123356</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.6695243340534325</v>
+        <v>-0.6560778210131799</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.3521258285573435</v>
+        <v>0.3521258285573438</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -14905,7 +14903,7 @@
         <v>0</v>
       </c>
       <c r="CR47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CS47" t="n">
         <v>2</v>
@@ -14914,7 +14912,7 @@
         <v>0</v>
       </c>
       <c r="CU47" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48">
@@ -14975,52 +14973,52 @@
         <v>28.10618445007706</v>
       </c>
       <c r="S48" t="n">
-        <v>5.250400042533874</v>
+        <v>5.242600045204163</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>44.94133917159145</v>
+        <v>45.15698447139597</v>
       </c>
       <c r="V48" t="n">
-        <v>6.460733332633972</v>
+        <v>6.427199997901917</v>
       </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>17.78848842244179</v>
+        <v>18.40303920834265</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.198514233827591</v>
+        <v>7.174495190382004</v>
       </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>5.716261527318226</v>
+        <v>6.070182383232069</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.927681739318783</v>
+        <v>1.933481361427631</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.988659736142064</v>
+        <v>1.993514517256766</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.313531960372713</v>
+        <v>2.311211024577755</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.893238824575233</v>
+        <v>2.923247115441544</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.8342521341456304</v>
+        <v>0.8627780808096781</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.2601503054242478</v>
+        <v>0.2766014305557372</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.800127145335697</v>
+        <v>0.8001271453356966</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -15280,52 +15278,52 @@
         <v>7.0278652623302</v>
       </c>
       <c r="S49" t="n">
-        <v>15.42079999923706</v>
+        <v>15.41819999694824</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>13.41823882018752</v>
+        <v>13.43736476748257</v>
       </c>
       <c r="V49" t="n">
-        <v>15.28073334376017</v>
+        <v>15.26553334554036</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>14.45785603123647</v>
+        <v>14.57182251825908</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.46110001564026</v>
+        <v>15.45545001506805</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>13.12260934490751</v>
+        <v>13.16396322375962</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.561584555367663</v>
+        <v>1.564774206658464</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.504042547672795</v>
+        <v>1.506231972166637</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.336660985329192</v>
+        <v>1.335222331977251</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.265715019418458</v>
+        <v>2.274541092984242</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.647103726555028</v>
+        <v>1.659813470844752</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.33232119597032</v>
+        <v>1.336935995040607</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.2791624007392077</v>
+        <v>0.2791624007392078</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -15585,52 +15583,52 @@
         <v>2.794946185109175</v>
       </c>
       <c r="S50" t="n">
-        <v>5.127000007629395</v>
+        <v>5.126800012588501</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>9.810807608016736</v>
+        <v>9.815091297043848</v>
       </c>
       <c r="V50" t="n">
-        <v>6.104133329391479</v>
+        <v>6.065066665013632</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-7.76741249519574</v>
+        <v>-7.173318523972659</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.696650006771088</v>
+        <v>6.677450006008148</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-15.92811168646507</v>
+        <v>-15.6863756467629</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.071359800220525</v>
+        <v>1.069788468730795</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.024072285429126</v>
+        <v>1.021981651265185</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.2812805303572734</v>
+        <v>0.2806045624372497</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.7739799984594312</v>
+        <v>0.7716785802721073</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.348534376809259</v>
+        <v>-0.321680748351396</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.6164894890495998</v>
+        <v>-0.6061096768449178</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.4518452087199722</v>
+        <v>0.4518452087199717</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -15913,13 +15911,13 @@
         <v>9.117811049205423</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.79618369869289</v>
+        <v>1.796183698692889</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.664302933340609</v>
+        <v>1.66430293334061</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.693179778105155</v>
+        <v>1.693179778105156</v>
       </c>
       <c r="AE51" t="n">
         <v>2.261599448389921</v>
@@ -15928,7 +15926,7 @@
         <v>1.131807736902745</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.9955092775011217</v>
+        <v>0.9955092775011215</v>
       </c>
       <c r="AH51" t="n">
         <v>0.2739723001042189</v>
@@ -16191,48 +16189,48 @@
         <v>-7.2406875737026</v>
       </c>
       <c r="S52" t="n">
-        <v>8.116399974822999</v>
+        <v>8.106799964904786</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-8.210538756407145</v>
+        <v>-8.101842385195246</v>
       </c>
       <c r="V52" t="n">
-        <v>8.93559998512268</v>
+        <v>8.928733320236207</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-16.62563429798774</v>
+        <v>-16.56151503169713</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.766349973678588</v>
+        <v>8.767199974060059</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-15.01594356107</v>
+        <v>-15.02418296254433</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.011091692819718</v>
+        <v>1.012399985793423</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.7083425314905467</v>
+        <v>0.7090886658085156</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.9625480387608082</v>
+        <v>-0.9624075859329129</v>
       </c>
       <c r="AE52" t="n">
-        <v>-0.8895120320022813</v>
+        <v>-0.8792883899710638</v>
       </c>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>0.5645144932666259</v>
+        <v>0.5645144932666261</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -16492,49 +16490,49 @@
         <v>6.243457508284824</v>
       </c>
       <c r="S53" t="n">
-        <v>50.46979988098145</v>
+        <v>50.43999984741211</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>12.18589941986455</v>
+        <v>12.25217903086439</v>
       </c>
       <c r="V53" t="n">
-        <v>49.07413327534994</v>
+        <v>49.10399993896485</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>15.37646241085044</v>
+        <v>15.30628666149832</v>
       </c>
       <c r="Y53" t="n">
-        <v>45.87914996147155</v>
+        <v>45.95079995155334</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>23.41117692771809</v>
+        <v>23.21874481310473</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.344301594652531</v>
+        <v>1.345992951288616</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.329710536189115</v>
+        <v>1.330487061955575</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.9278455148974848</v>
+        <v>0.9275389896998107</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.194106051849822</v>
+        <v>1.202140734715504</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.9938615304138891</v>
+        <v>0.9898005978525557</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.374256621586535</v>
+        <v>1.366797783442</v>
       </c>
       <c r="AH53" t="n">
         <v>0.3610514439141015</v>
@@ -16793,49 +16791,49 @@
         <v>6.260180148137885</v>
       </c>
       <c r="S54" t="n">
-        <v>45.33939979553222</v>
+        <v>45.32499977111816</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>12.85989316071105</v>
+        <v>12.89574942601914</v>
       </c>
       <c r="V54" t="n">
-        <v>44.24646657307942</v>
+        <v>44.26579989115397</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>15.64764857422158</v>
+        <v>15.59713886288785</v>
       </c>
       <c r="Y54" t="n">
-        <v>41.70409997940064</v>
+        <v>41.75819997787475</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>22.69776399495558</v>
+        <v>22.53880242936076</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.316304873217715</v>
+        <v>1.317532180601257</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.304819007424552</v>
+        <v>1.305313032852943</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.985952189207515</v>
+        <v>0.9859359933201177</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.332810625751386</v>
+        <v>1.338509503490396</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.109015294487113</v>
+        <v>1.105724702752938</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.466094098181502</v>
+        <v>1.45975980457143</v>
       </c>
       <c r="AH54" t="n">
         <v>0.3325941578774697</v>
@@ -17094,52 +17092,52 @@
         <v>-0.758111395633856</v>
       </c>
       <c r="S55" t="n">
-        <v>4.52119999885559</v>
+        <v>4.504199991226196</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-4.228967424531815</v>
+        <v>-3.867502949679599</v>
       </c>
       <c r="V55" t="n">
-        <v>5.573133319218954</v>
+        <v>5.556666650772095</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-22.30582554388126</v>
+        <v>-22.07558603314085</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.722136330604553</v>
+        <v>5.715322694778442</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-24.32896258435382</v>
+        <v>-24.23874984938345</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.925193388716794</v>
+        <v>0.9327336117772176</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.8383963130787007</v>
+        <v>0.8449590907718207</v>
       </c>
       <c r="AD55" t="n">
-        <v>-0.1187207506228024</v>
+        <v>-0.1185671065882322</v>
       </c>
       <c r="AE55" t="n">
-        <v>-0.5055383042517244</v>
+        <v>-0.4629187645145892</v>
       </c>
       <c r="AF55" t="n">
-        <v>-2.129730332225189</v>
+        <v>-2.13270808100775</v>
       </c>
       <c r="AG55" t="n">
-        <v>-2.457813088657576</v>
+        <v>-2.481142030606022</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.3036122784380052</v>
+        <v>0.3036122784380049</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -17329,7 +17327,7 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CS55" t="n">
         <v>4</v>
@@ -17338,7 +17336,7 @@
         <v>0</v>
       </c>
       <c r="CU55" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -17399,52 +17397,52 @@
         <v>1.312897472666064</v>
       </c>
       <c r="S56" t="n">
-        <v>60.98300018310547</v>
+        <v>60.99700019836425</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>3.323874083501206</v>
+        <v>3.300159215408319</v>
       </c>
       <c r="V56" t="n">
-        <v>61.50546666463216</v>
+        <v>61.55046666463216</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>2.446175500309151</v>
+        <v>2.371276346048748</v>
       </c>
       <c r="Y56" t="n">
-        <v>57.70774997711182</v>
+        <v>57.81929998397827</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>9.188104451350775</v>
+        <v>8.977449292871546</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.9050825041002102</v>
+        <v>0.905314867061865</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.8538665782644204</v>
+        <v>0.8541743649196574</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.2008912306737164</v>
+        <v>0.2009211706556286</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.3317019825582462</v>
+        <v>0.3295399383624045</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.1331724171284628</v>
+        <v>0.1291011589200895</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.5002033016882129</v>
+        <v>0.4894670012324381</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.3490495169693836</v>
+        <v>0.3490495169693837</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -17733,16 +17731,16 @@
         <v>1.185552068562806</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.09387405561740257</v>
+        <v>0.09387405561740256</v>
       </c>
       <c r="AE57" t="n">
-        <v>-0.1458442333367194</v>
+        <v>-0.1458442333367192</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.4119858862421656</v>
+        <v>-0.411985886242167</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.3557014117302106</v>
+        <v>-0.3557014117302104</v>
       </c>
       <c r="AH57" t="n">
         <v>0.2147783541287801</v>
@@ -18001,52 +17999,52 @@
         <v>-0.001972769016057207</v>
       </c>
       <c r="S58" t="n">
-        <v>19.01240005493164</v>
+        <v>19.03620002746582</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>2.564641726765485</v>
+        <v>2.43641048037423</v>
       </c>
       <c r="V58" t="n">
-        <v>19.98340006510417</v>
+        <v>19.9454000600179</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-2.419008094364782</v>
+        <v>-2.233096647235178</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.18280592918396</v>
+        <v>21.15877455711365</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-7.944206895015387</v>
+        <v>-7.839653249464599</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.120977421958578</v>
+        <v>1.119044863377494</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.7955916533518534</v>
+        <v>0.7926356442395635</v>
       </c>
       <c r="AD58" t="n">
-        <v>-0.0003103234544352226</v>
+        <v>-0.0003102155543501138</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.262202688111467</v>
+        <v>0.2492640715919845</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.1178306662288582</v>
+        <v>-0.1087356508192806</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.3848436307646254</v>
+        <v>-0.3793940880459387</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.4261493290622446</v>
+        <v>0.4261493290622447</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -18344,7 +18342,7 @@
         <v>1.95631991207986</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.981015432919118</v>
+        <v>1.981015432919116</v>
       </c>
       <c r="AH59" t="n">
         <v>0.2546859762278432</v>
@@ -18603,52 +18601,52 @@
         <v>6.727417953503044</v>
       </c>
       <c r="S60" t="n">
-        <v>35.7226000213623</v>
+        <v>35.72860008239746</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>11.47004885145999</v>
+        <v>11.45132919563361</v>
       </c>
       <c r="V60" t="n">
-        <v>36.31333330790202</v>
+        <v>36.2711333211263</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>9.656690993330333</v>
+        <v>9.784272088434756</v>
       </c>
       <c r="Y60" t="n">
-        <v>37.84029998779297</v>
+        <v>37.78879999160767</v>
       </c>
       <c r="Z60" t="n">
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>5.231723077433027</v>
+        <v>5.375136822729618</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.492643031824</v>
+        <v>1.494286862512302</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.419799923627178</v>
+        <v>1.421399879015555</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.328787998104019</v>
+        <v>1.332631371252363</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.821041183866717</v>
+        <v>1.832322442481242</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.7612355809560721</v>
+        <v>0.7759979547463409</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.335184802763705</v>
+        <v>0.3460890706261845</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.2683300840789917</v>
+        <v>0.2683300840789916</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -18931,13 +18929,13 @@
         <v>-1.881769243444045</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.048810661667427</v>
+        <v>1.048810661667426</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.9813709642764035</v>
+        <v>0.9813709642764041</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.1953108883725845</v>
+        <v>0.1953108883725844</v>
       </c>
       <c r="AE61" t="n">
         <v>0.4626050969406534</v>
@@ -19205,49 +19203,49 @@
         <v>11.8233176675826</v>
       </c>
       <c r="S62" t="n">
-        <v>36.51419990539551</v>
+        <v>36.49739990234375</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>13.59963972839797</v>
+        <v>13.65193042031635</v>
       </c>
       <c r="V62" t="n">
-        <v>41.72593332926432</v>
+        <v>41.62953333536784</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.5894027224922711</v>
+        <v>-0.3592012236285841</v>
       </c>
       <c r="Y62" t="n">
-        <v>42.94829999923706</v>
+        <v>42.89604999542237</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-3.418762691484443</v>
+        <v>-3.301120856902096</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.601283405568632</v>
+        <v>1.610794729979033</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.614297551064849</v>
+        <v>1.622430542765163</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.771379417790862</v>
+        <v>1.776039906431723</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.698095416851102</v>
+        <v>1.709669187411636</v>
       </c>
       <c r="AF62" t="n">
-        <v>-0.04284622315254365</v>
+        <v>-0.02605977855814427</v>
       </c>
       <c r="AG62" t="n">
-        <v>-0.243814787059475</v>
+        <v>-0.2346844849529174</v>
       </c>
       <c r="AH62" t="n">
         <v>0.3772380988729792</v>
@@ -19529,10 +19527,10 @@
         <v>-7.195564473215632</v>
       </c>
       <c r="AB63" t="n">
-        <v>-1.322762195310417</v>
+        <v>-1.322762195310418</v>
       </c>
       <c r="AC63" t="n">
-        <v>-1.325738786076624</v>
+        <v>-1.325738786076623</v>
       </c>
       <c r="AD63" t="n">
         <v>-1.06552433637422</v>
@@ -19544,7 +19542,7 @@
         <v>-0.2406746324926294</v>
       </c>
       <c r="AG63" t="n">
-        <v>-0.6270671940869069</v>
+        <v>-0.6270671940869067</v>
       </c>
       <c r="AH63" t="n">
         <v>0.2477149371825346</v>
@@ -19850,19 +19848,19 @@
         <v>-1.245881983587564</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.178997682474475</v>
+        <v>1.178997682474474</v>
       </c>
       <c r="AC64" t="n">
         <v>1.01503476996555</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.9227496677003332</v>
+        <v>0.9227496677003333</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.9908171648377657</v>
+        <v>0.9908171648377656</v>
       </c>
       <c r="AF64" t="n">
-        <v>-0.2026456071655098</v>
+        <v>-0.2026456071655097</v>
       </c>
       <c r="AG64" t="n">
         <v>-0.1036671595223949</v>
@@ -20124,52 +20122,52 @@
         <v>0.4650369023304322</v>
       </c>
       <c r="S65" t="n">
-        <v>15.59360004425049</v>
+        <v>15.5856000328064</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>10.30166680003609</v>
+        <v>10.3582841002905</v>
       </c>
       <c r="V65" t="n">
-        <v>15.93426664352417</v>
+        <v>15.91353331247966</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>7.94347269147582</v>
+        <v>8.084109450733537</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.78554440498352</v>
+        <v>15.77572773933411</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>8.960453448215487</v>
+        <v>9.028255603411326</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.09905789580573628</v>
+        <v>0.09911388104082525</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.02069383669401594</v>
+        <v>0.02070893934639458</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.07120731561808527</v>
+        <v>0.07116282005956515</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.051746421263287</v>
+        <v>1.057757308221205</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.6854172207886498</v>
+        <v>0.6956461360140129</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.8121795733424996</v>
+        <v>0.8167524470640996</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.378615325158926</v>
+        <v>0.3786153251589256</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -20429,49 +20427,49 @@
         <v>1.952842467884472</v>
       </c>
       <c r="S66" t="n">
-        <v>17.80800006866455</v>
+        <v>17.76400005340576</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-0.9995558581065201</v>
+        <v>-0.7543396320440234</v>
       </c>
       <c r="V66" t="n">
-        <v>18.62333335876465</v>
+        <v>18.60813335418701</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-5.333815267450793</v>
+        <v>-5.256487444509418</v>
       </c>
       <c r="Y66" t="n">
-        <v>19.54884999275207</v>
+        <v>19.51779999732971</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-9.815671165807226</v>
+        <v>-9.672200948987001</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.759945236676461</v>
+        <v>0.766757205216531</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.6856143581698599</v>
+        <v>0.6918286625347575</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.4216718497240543</v>
+        <v>0.4253645508100123</v>
       </c>
       <c r="AE66" t="n">
-        <v>-0.1674191975593637</v>
+        <v>-0.1283037582851364</v>
       </c>
       <c r="AF66" t="n">
-        <v>-0.5855071084932069</v>
+        <v>-0.585564311747556</v>
       </c>
       <c r="AG66" t="n">
-        <v>-0.8708207992446947</v>
+        <v>-0.8715709560279828</v>
       </c>
       <c r="AH66" t="n">
         <v>0.3052458951727157</v>
@@ -20498,7 +20496,7 @@
         <v>18.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
         <v>0</v>
@@ -20730,49 +20728,49 @@
         <v>-4.368166711618655</v>
       </c>
       <c r="S67" t="n">
-        <v>44.68200012207031</v>
+        <v>44.65920013427734</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-0.7430321987426656</v>
+        <v>-0.6923582581563652</v>
       </c>
       <c r="V67" t="n">
-        <v>45.29460009256999</v>
+        <v>45.1832000986735</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-2.085461879602382</v>
+        <v>-1.844051821767423</v>
       </c>
       <c r="Y67" t="n">
-        <v>47.03585004806519</v>
+        <v>46.99495004653931</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-5.710222247922516</v>
+        <v>-5.628161259452149</v>
       </c>
       <c r="AB67" t="n">
-        <v>-0.7230054838404495</v>
+        <v>-0.7230261918515726</v>
       </c>
       <c r="AC67" t="n">
-        <v>-0.8230098114438918</v>
+        <v>-0.8225841436157124</v>
       </c>
       <c r="AD67" t="n">
-        <v>-0.8961153730925068</v>
+        <v>-0.895069865908783</v>
       </c>
       <c r="AE67" t="n">
-        <v>-0.1066705811836341</v>
+        <v>-0.09945086801746139</v>
       </c>
       <c r="AF67" t="n">
-        <v>-0.2607703045642973</v>
+        <v>-0.2298754152465613</v>
       </c>
       <c r="AG67" t="n">
-        <v>-0.7176891227469986</v>
+        <v>-0.7062727480208025</v>
       </c>
       <c r="AH67" t="n">
         <v>0.2624751804227321</v>
@@ -20781,10 +20779,10 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>39.2</v>
+        <v>41.9</v>
       </c>
       <c r="AK67" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="AL67" t="n">
         <v>42.7</v>
@@ -20961,7 +20959,7 @@
         <v>0</v>
       </c>
       <c r="CR67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CS67" t="n">
         <v>1</v>
@@ -20970,7 +20968,7 @@
         <v>0</v>
       </c>
       <c r="CU67" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68">
@@ -21070,10 +21068,10 @@
         <v>1.325203385111286</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.5672726709428054</v>
+        <v>0.5672726709428056</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.46228948565662</v>
+        <v>0.4622894856566201</v>
       </c>
       <c r="AH68" t="n">
         <v>0.2086674604302148</v>
@@ -21330,52 +21328,52 @@
         <v>-2.132671302750895</v>
       </c>
       <c r="S69" t="n">
-        <v>19.01419994354248</v>
+        <v>18.96519992828369</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-2.441337042106693</v>
+        <v>-2.189276637173419</v>
       </c>
       <c r="V69" t="n">
-        <v>22.57239999135335</v>
+        <v>22.51173332214356</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-17.81999590576828</v>
+        <v>-17.59852974620159</v>
       </c>
       <c r="Y69" t="n">
-        <v>22.9860000038147</v>
+        <v>22.96284999847412</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-19.29870689122929</v>
+        <v>-19.21734785406344</v>
       </c>
       <c r="AB69" t="n">
-        <v>-0.09954128528432213</v>
+        <v>-0.0996540963115755</v>
       </c>
       <c r="AC69" t="n">
-        <v>-0.2404277884326264</v>
+        <v>-0.2407434376932747</v>
       </c>
       <c r="AD69" t="n">
-        <v>-0.3653005042731449</v>
+        <v>-0.3657747576639453</v>
       </c>
       <c r="AE69" t="n">
-        <v>-0.3101186308299047</v>
+        <v>-0.2783504880859468</v>
       </c>
       <c r="AF69" t="n">
-        <v>-1.339147828497215</v>
+        <v>-1.321853440213399</v>
       </c>
       <c r="AG69" t="n">
-        <v>-1.251895325252159</v>
+        <v>-1.245732930229476</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.1830085644106418</v>
+        <v>0.1830085644106419</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -21631,49 +21629,49 @@
         <v>2.495757770093165</v>
       </c>
       <c r="S70" t="n">
-        <v>32.73159992218017</v>
+        <v>32.82739994049072</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>7.999604535574793</v>
+        <v>7.684429891503199</v>
       </c>
       <c r="V70" t="n">
-        <v>32.47413326263428</v>
+        <v>32.43413326263428</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>8.855864414388778</v>
+        <v>8.990112940203147</v>
       </c>
       <c r="Y70" t="n">
-        <v>34.9681999874115</v>
+        <v>34.90009999275208</v>
       </c>
       <c r="Z70" t="n">
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.091844838587741</v>
+        <v>1.289103703033664</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3811651779597571</v>
+        <v>0.3805439003143026</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.3546517858264982</v>
+        <v>0.3538588379664784</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.4397733180168726</v>
+        <v>0.4419495488453085</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.043669276284832</v>
+        <v>1.008213276964727</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.7443645240195804</v>
+        <v>0.7595240619359818</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.07687523873847403</v>
+        <v>0.09151410017228546</v>
       </c>
       <c r="AH70" t="n">
         <v>0.3656985219818046</v>
@@ -21932,49 +21930,49 @@
         <v>2.667268015909267</v>
       </c>
       <c r="S71" t="n">
-        <v>35.32099994659424</v>
+        <v>35.27319995880127</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>9.311742783982128</v>
+        <v>9.459875076396923</v>
       </c>
       <c r="V71" t="n">
-        <v>30.40360004425049</v>
+        <v>30.43826671600342</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>26.99154229813964</v>
+        <v>26.84690942027826</v>
       </c>
       <c r="Y71" t="n">
-        <v>28.72840003967285</v>
+        <v>28.77800004005432</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>34.39662688152695</v>
+        <v>34.16498907711684</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.248214472660303</v>
+        <v>0.2469276330615779</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.1918618290996495</v>
+        <v>0.190783002344631</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.3962875069736997</v>
+        <v>0.3953865117807087</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.098886142124252</v>
+        <v>1.123970842169238</v>
       </c>
       <c r="AF71" t="n">
-        <v>3.023370973616206</v>
+        <v>3.012552928078797</v>
       </c>
       <c r="AG71" t="n">
-        <v>3.382414027672974</v>
+        <v>3.368215372172736</v>
       </c>
       <c r="AH71" t="n">
         <v>0.3189360389019097</v>
@@ -22233,52 +22231,52 @@
         <v>3.123176920885469</v>
       </c>
       <c r="S72" t="n">
-        <v>7.230799989700317</v>
+        <v>7.204199991226196</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>3.446368724458344</v>
+        <v>3.82832275871269</v>
       </c>
       <c r="V72" t="n">
-        <v>7.959133342107137</v>
+        <v>7.959733339945475</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-6.019918280534832</v>
+        <v>-6.027002418089488</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.547850008010864</v>
+        <v>7.553750007152558</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.8989313362794155</v>
+        <v>-0.9763360980868878</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.200481625809112</v>
+        <v>1.205922040629755</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.15208755550269</v>
+        <v>1.158289092240461</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.3325274410163427</v>
+        <v>0.3323367219041801</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.2525461719018395</v>
+        <v>0.2805547451754849</v>
       </c>
       <c r="AF72" t="n">
-        <v>-0.3035259194351878</v>
+        <v>-0.3039477101452556</v>
       </c>
       <c r="AG72" t="n">
-        <v>-0.03956455379721214</v>
+        <v>-0.04305090009240865</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.4844648111797626</v>
+        <v>0.4844648111797627</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -22538,49 +22536,49 @@
         <v>-3.801057127660769</v>
       </c>
       <c r="S73" t="n">
-        <v>74.91120040893554</v>
+        <v>74.91620040893555</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-3.752712437483679</v>
+        <v>-3.759136100659156</v>
       </c>
       <c r="V73" t="n">
-        <v>78.74760030110677</v>
+        <v>78.66400029500325</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-8.441656382629157</v>
+        <v>-8.344352939420881</v>
       </c>
       <c r="Y73" t="n">
-        <v>79.10265018463134</v>
+        <v>79.12230018615723</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-8.852613274227288</v>
+        <v>-8.87524970269345</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.563648753143559</v>
+        <v>0.5637731800627901</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.4523685818023133</v>
+        <v>0.4524927788845054</v>
       </c>
       <c r="AD73" t="n">
-        <v>-0.7553594453082476</v>
+        <v>-0.7552747299606064</v>
       </c>
       <c r="AE73" t="n">
-        <v>-0.5263909382815328</v>
+        <v>-0.5269192456088201</v>
       </c>
       <c r="AF73" t="n">
-        <v>-0.6079079705387078</v>
+        <v>-0.5998434365087555</v>
       </c>
       <c r="AG73" t="n">
-        <v>-0.6119253415647585</v>
+        <v>-0.6119116747813119</v>
       </c>
       <c r="AH73" t="n">
         <v>0.2617057195393629</v>
@@ -22589,13 +22587,13 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AK73" t="n">
         <v>63.7</v>
       </c>
-      <c r="AK73" t="n">
+      <c r="AL73" t="n">
         <v>63.8</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>65.3</v>
       </c>
       <c r="AM73" t="n">
         <v>73.5</v>
@@ -22835,52 +22833,52 @@
         <v>32.74450107279502</v>
       </c>
       <c r="S74" t="n">
-        <v>3.307999978065491</v>
+        <v>3.301999979019165</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>43.28899040350366</v>
+        <v>43.54935800230217</v>
       </c>
       <c r="V74" t="n">
-        <v>3.410861455599467</v>
+        <v>3.400928122202555</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>38.96781891673457</v>
+        <v>39.37371213974323</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.5215460896492</v>
+        <v>3.518096090555191</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>34.59996406266942</v>
+        <v>34.7319586819513</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.750639077631547</v>
+        <v>2.763742005955114</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.73670982331955</v>
+        <v>2.749311214075701</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.821708320208583</v>
+        <v>2.819944041562162</v>
       </c>
       <c r="AE74" t="n">
-        <v>3.284678715172712</v>
+        <v>3.303898513815987</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.637170793848957</v>
+        <v>2.659165570519377</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.5794103509788</v>
+        <v>2.587596354611061</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.6785654253886005</v>
+        <v>0.6785654253886004</v>
       </c>
       <c r="AI74" t="n">
         <v>1</v>
@@ -23136,52 +23134,52 @@
         <v>1.545867790122601</v>
       </c>
       <c r="S75" t="n">
-        <v>36.1366000366211</v>
+        <v>36.09340003967285</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>5.571640628109488</v>
+        <v>5.697998758624837</v>
       </c>
       <c r="V75" t="n">
-        <v>33.00053324381511</v>
+        <v>33.02399990081787</v>
       </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>15.60419719287082</v>
+        <v>15.52204954110991</v>
       </c>
       <c r="Y75" t="n">
-        <v>31.70079993247986</v>
+        <v>31.74269992828369</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>20.34397115257447</v>
+        <v>20.18511850621162</v>
       </c>
       <c r="AB75" t="n">
-        <v>-0.1874478540462949</v>
+        <v>-0.1870381265301168</v>
       </c>
       <c r="AC75" t="n">
-        <v>-0.2856634190163107</v>
+        <v>-0.2849441148450318</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.2851831762931051</v>
+        <v>0.2843527936147632</v>
       </c>
       <c r="AE75" t="n">
-        <v>0.8806062419713307</v>
+        <v>0.9020911594967673</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.898746566287512</v>
+        <v>1.883087667513452</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.389856331785084</v>
+        <v>2.362739330926526</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.289474629265653</v>
+        <v>0.2894746292656529</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -23464,10 +23462,10 @@
         <v>-1.480356263002716</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.215699895140186</v>
+        <v>2.215699895140185</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.021668699684158</v>
+        <v>2.021668699684157</v>
       </c>
       <c r="AD76" t="n">
         <v>1.434222789339517</v>
@@ -23476,10 +23474,10 @@
         <v>1.505876684873994</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.3517517697425355</v>
+        <v>0.3517517697425356</v>
       </c>
       <c r="AG76" t="n">
-        <v>-0.07503593853789794</v>
+        <v>-0.07503593853789788</v>
       </c>
       <c r="AH76" t="n">
         <v>0.3928316961237687</v>
@@ -23738,73 +23736,73 @@
         <v>-0.1656200864401676</v>
       </c>
       <c r="S77" t="n">
-        <v>30.71520015716553</v>
+        <v>30.63220012664795</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-1.872690930138381</v>
+        <v>-1.606808309440788</v>
       </c>
       <c r="V77" t="n">
-        <v>35.2052001063029</v>
+        <v>35.12100009918213</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-14.3876492715848</v>
+        <v>-14.1823999757048</v>
       </c>
       <c r="Y77" t="n">
-        <v>35.43995011329651</v>
+        <v>35.42630011558533</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-14.95473528237168</v>
+        <v>-14.92196675545932</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.1782368396593348</v>
+        <v>0.1788642136923759</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.07919275325620903</v>
+        <v>0.0794741653048236</v>
       </c>
       <c r="AD77" t="n">
-        <v>-0.0300320720612539</v>
+        <v>-0.03008024065870619</v>
       </c>
       <c r="AE77" t="n">
-        <v>-0.2428512285065842</v>
+        <v>-0.2084760882161694</v>
       </c>
       <c r="AF77" t="n">
-        <v>-1.157172175381697</v>
+        <v>-1.139414744842073</v>
       </c>
       <c r="AG77" t="n">
-        <v>-1.102229333557453</v>
+        <v>-1.097487367378061</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.1582126915011279</v>
+        <v>0.1582126915011277</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>27.8</v>
+        <v>23.2</v>
       </c>
       <c r="AK77" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL77" t="n">
         <v>27.9</v>
       </c>
-      <c r="AL77" t="n">
-        <v>29.4</v>
-      </c>
       <c r="AM77" t="n">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="AN77" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="AO77" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AP77" t="n">
         <v>1</v>
@@ -24039,49 +24037,49 @@
         <v>0.9363996718823299</v>
       </c>
       <c r="S78" t="n">
-        <v>49.48220024108887</v>
+        <v>49.52140029907227</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>3.976784605904748</v>
+        <v>3.894478856049865</v>
       </c>
       <c r="V78" t="n">
-        <v>47.13486679077148</v>
+        <v>47.12106679280599</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>9.154866165894902</v>
+        <v>9.18683354340858</v>
       </c>
       <c r="Y78" t="n">
-        <v>47.82030006408691</v>
+        <v>47.81570007324219</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AA78" t="n">
-        <v>7.59029260374392</v>
+        <v>7.600643061024695</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.5443228834173682</v>
+        <v>0.5441400248402649</v>
       </c>
       <c r="AC78" t="n">
-        <v>0.477485608008205</v>
+        <v>0.4773229039953611</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.169185271698238</v>
+        <v>0.1695097249430943</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.5671603852030362</v>
+        <v>0.5564286321898992</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.8722042296210564</v>
+        <v>0.8805402493885042</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.7587264724877114</v>
+        <v>0.7692411144591388</v>
       </c>
       <c r="AH78" t="n">
         <v>0.2258272066371025</v>
@@ -24340,52 +24338,52 @@
         <v>8.693026734764752</v>
       </c>
       <c r="S79" t="n">
-        <v>9.119600009918212</v>
+        <v>9.119400005340577</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>21.4965558978</v>
+        <v>21.49922053224221</v>
       </c>
       <c r="V79" t="n">
-        <v>9.746799983978271</v>
+        <v>9.708599980672201</v>
       </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>13.6783348577922</v>
+        <v>14.12562002517382</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.57129999160767</v>
+        <v>10.54694999217987</v>
       </c>
       <c r="Z79" t="n">
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>4.812084913891708</v>
+        <v>5.054067118185057</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.1663020452334736</v>
+        <v>0.1665606007081852</v>
       </c>
       <c r="AC79" t="n">
-        <v>0.1313028525134495</v>
+        <v>0.1314329964418804</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.028921267057851</v>
+        <v>1.024257849415722</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.092206881927044</v>
+        <v>2.077952428092376</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.223134393343195</v>
+        <v>1.252633455566665</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.4261473568302085</v>
+        <v>0.4460604221074795</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.5502743156813046</v>
+        <v>0.5502743156813045</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -933,16 +933,16 @@
         <v>16.5</v>
       </c>
       <c r="E2" t="n">
-        <v>16.86000061035156</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>16.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>16.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>72309500</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0.0416666566322148</v>
@@ -1238,16 +1238,16 @@
         <v>33.06000137329102</v>
       </c>
       <c r="E3" t="n">
-        <v>33.93000030517578</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>31.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>32.40999984741211</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>22387700</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0.08357919125792934</v>
@@ -1543,16 +1543,16 @@
         <v>12.97999954223633</v>
       </c>
       <c r="E4" t="n">
-        <v>13.44999980926514</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.61999988555908</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>12.81999969482422</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>52188000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0.1641255593107611</v>
@@ -1585,67 +1585,69 @@
         <v>30.391774585849</v>
       </c>
       <c r="S4" t="n">
-        <v>9.149199943542481</v>
+        <v>9.153399953842163</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>41.87032333245303</v>
+        <v>41.80522655724161</v>
       </c>
       <c r="V4" t="n">
-        <v>8.820133275985718</v>
+        <v>8.812199945449828</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>47.16330395569576</v>
+        <v>47.29579018390906</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.667799940109253</v>
+        <v>8.667099943161011</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>49.7496438764451</v>
+        <v>49.76173838261225</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.886678971016154</v>
+        <v>3.888936998018534</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.749665968554399</v>
+        <v>3.752146099728539</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.303378591171774</v>
+        <v>3.301792661040941</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.162794653997566</v>
+        <v>4.150296353809944</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.262148992937018</v>
+        <v>4.267052877872684</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.64966649780979</v>
+        <v>4.656919112118035</v>
       </c>
       <c r="AH4" t="n">
         <v>0.6591214355602542</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>13.4</v>
+        <v>12</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1848,16 +1850,16 @@
         <v>15.53999996185303</v>
       </c>
       <c r="E5" t="n">
-        <v>15.89999961853027</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>14.02000045776367</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>14.4399995803833</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17551300</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0.1244573303191152</v>
@@ -1890,67 +1892,69 @@
         <v>26.44426333367134</v>
       </c>
       <c r="S5" t="n">
-        <v>11.53459997177124</v>
+        <v>11.52479997634888</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>34.72508799511253</v>
+        <v>34.83965009149069</v>
       </c>
       <c r="V5" t="n">
-        <v>12.07906665166219</v>
+        <v>12.07273331960042</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>28.65232397500332</v>
+        <v>28.7198147301357</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.98349997997284</v>
+        <v>11.97569997787476</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>29.67830757144332</v>
+        <v>29.76276952965887</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.177352443674319</v>
+        <v>5.199340944362248</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.97103968664926</v>
+        <v>4.992503289974946</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.211337669205499</v>
+        <v>4.213173411006315</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.487034036855149</v>
+        <v>4.485353829149907</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.960416054815736</v>
+        <v>2.952037200471838</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.635074958675798</v>
+        <v>2.627527966174515</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.4662577686351305</v>
+        <v>0.4662577686351304</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>15.9</v>
+        <v>14.7</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1963,7 +1967,7 @@
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -2149,16 +2153,16 @@
         <v>61.38000106811523</v>
       </c>
       <c r="E6" t="n">
-        <v>61.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>59.72999954223633</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>60.90000152587891</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>52616400</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0.0787346119876422</v>
@@ -2191,52 +2195,52 @@
         <v>11.12596821019733</v>
       </c>
       <c r="S6" t="n">
-        <v>53.58019981384277</v>
+        <v>53.61199981689453</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>14.55724555222232</v>
+        <v>14.48929582509773</v>
       </c>
       <c r="V6" t="n">
-        <v>55.56866663614909</v>
+        <v>55.49859995524088</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>10.45793391088081</v>
+        <v>10.59738645230266</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.61229997634888</v>
+        <v>55.55209997177124</v>
       </c>
       <c r="Z6" t="n">
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.37126875568764</v>
+        <v>10.49087451114438</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.733247342627152</v>
+        <v>2.738854225631296</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.557997769663795</v>
+        <v>2.562911719490862</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.629293041325683</v>
+        <v>1.636449304849954</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.635702947414084</v>
+        <v>1.638984972756181</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.7158757535246124</v>
+        <v>0.7261646711000138</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.635396445688478</v>
+        <v>0.6428615636912233</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.3184973086206187</v>
+        <v>0.3184973086206188</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -2448,16 +2452,16 @@
         <v>22.17000007629395</v>
       </c>
       <c r="E7" t="n">
-        <v>22.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>21.59000015258789</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8306800</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0.1345956518700411</v>
@@ -2490,52 +2494,52 @@
         <v>35.80078293053195</v>
       </c>
       <c r="S7" t="n">
-        <v>16.04520002365112</v>
+        <v>16.04720003128052</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>38.17216390954726</v>
+        <v>38.15494312452243</v>
       </c>
       <c r="V7" t="n">
-        <v>19.478600025177</v>
+        <v>19.41400002161662</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>13.8172150341307</v>
+        <v>14.19594133928425</v>
       </c>
       <c r="Y7" t="n">
-        <v>20.88795000553131</v>
+        <v>20.84485000133514</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.137749613643918</v>
+        <v>6.357206095865045</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.899121731801618</v>
+        <v>4.894108170640371</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.959314088493796</v>
+        <v>4.956022456295514</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.494290229827891</v>
+        <v>4.508033883821938</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.387431994477053</v>
+        <v>4.383717262273159</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.788296284351774</v>
+        <v>1.841727583127437</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.8259360136101617</v>
+        <v>0.8619139125539712</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.8231841978491294</v>
+        <v>0.8231841978491296</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2745,16 +2749,16 @@
         <v>23.29999923706055</v>
       </c>
       <c r="E8" t="n">
-        <v>24.28000068664551</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>22.03000068664551</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>22.10000038146973</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>200101300</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0.2263157493189762</v>
@@ -2787,67 +2791,69 @@
         <v>30.72938620529497</v>
       </c>
       <c r="S8" t="n">
-        <v>16.55320003509522</v>
+        <v>16.53780004501343</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>40.75827747904409</v>
+        <v>40.88935150770612</v>
       </c>
       <c r="V8" t="n">
-        <v>16.70200002670288</v>
+        <v>16.67653336207072</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>39.50424619691591</v>
+        <v>39.71728255018699</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.42605004787445</v>
+        <v>16.42775004863739</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>41.84785246088784</v>
+        <v>41.83317355131771</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.91481025378406</v>
+        <v>6.921871106104113</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.567687048779065</v>
+        <v>6.574119744812427</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.645138375931153</v>
+        <v>4.628440109245979</v>
       </c>
       <c r="AE8" t="n">
-        <v>4.638665309573692</v>
+        <v>4.647115709564392</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.116486007230883</v>
+        <v>3.120950385396652</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.558981134991931</v>
+        <v>3.541982421024321</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.6820477207536789</v>
+        <v>0.682047720753679</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>24.3</v>
+        <v>20.3</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -3050,16 +3056,16 @@
         <v>26.32999992370605</v>
       </c>
       <c r="E9" t="n">
-        <v>27.19000053405762</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>25.19000053405762</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.19000053405762</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>147487200</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0.1100337557295845</v>
@@ -3092,49 +3098,49 @@
         <v>17.4317268100405</v>
       </c>
       <c r="S9" t="n">
-        <v>21.0888000869751</v>
+        <v>21.08240009307861</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>24.85300166493605</v>
+        <v>24.89090334809762</v>
       </c>
       <c r="V9" t="n">
-        <v>21.59146667480469</v>
+        <v>21.54533334096273</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>21.94632407455122</v>
+        <v>22.20743818173634</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.09895002365112</v>
+        <v>22.09060002326965</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.14593180004798</v>
+        <v>19.19096763315948</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.247800013845235</v>
+        <v>4.271955669560398</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.993014236861855</v>
+        <v>4.013339096643812</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.851932926785101</v>
+        <v>2.846270753117111</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.290844102510718</v>
+        <v>3.298858551406521</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.148417714873024</v>
+        <v>2.17087050521331</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.947796602071539</v>
+        <v>1.952003863424538</v>
       </c>
       <c r="AH9" t="n">
         <v>0.4462896961095754</v>
@@ -3346,13 +3352,13 @@
         <v>8</v>
       </c>
       <c r="CS9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -3371,16 +3377,16 @@
         <v>19.36000061035156</v>
       </c>
       <c r="E10" t="n">
-        <v>19.54000091552734</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>18.04000091552734</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>18.04000091552734</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>43642800</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0.1503268388659855</v>
@@ -3413,55 +3419,55 @@
         <v>20.77934889165394</v>
       </c>
       <c r="S10" t="n">
-        <v>15.60401782989502</v>
+        <v>15.58361782073975</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>24.07061323180898</v>
+        <v>24.2330300515067</v>
       </c>
       <c r="V10" t="n">
-        <v>16.02573928833008</v>
+        <v>16.00427261352539</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>20.80566307758099</v>
+        <v>20.96770080003641</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.29930446624756</v>
+        <v>16.29450446128845</v>
       </c>
       <c r="Z10" t="n">
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>18.77807823298266</v>
+        <v>18.81306765938137</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.230192771962771</v>
+        <v>6.260621063373724</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.858143919230953</v>
+        <v>5.887889360275587</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.048488386875645</v>
+        <v>4.04721330589552</v>
       </c>
       <c r="AE10" t="n">
-        <v>4.152262474892886</v>
+        <v>4.181643398662528</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.184046460823281</v>
+        <v>2.20169966808799</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.701232559250076</v>
+        <v>1.70360273216204</v>
       </c>
       <c r="AH10" t="n">
         <v>0.4799680446503717</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>16.7</v>
@@ -3694,16 +3700,16 @@
         <v>21.84000015258789</v>
       </c>
       <c r="E11" t="n">
-        <v>22.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>20.76000022888184</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>20.76000022888184</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>160291100</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0.1357254639876104</v>
@@ -3736,55 +3742,55 @@
         <v>20.07612648235755</v>
       </c>
       <c r="S11" t="n">
-        <v>17.75374046325684</v>
+        <v>17.72774047851562</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>23.01633110942442</v>
+        <v>23.19675019529953</v>
       </c>
       <c r="V11" t="n">
-        <v>18.38624683380127</v>
+        <v>18.35924683888753</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>18.78443898858816</v>
+        <v>18.95912912030585</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.765085105896</v>
+        <v>18.75768510818482</v>
       </c>
       <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.38636344753777</v>
+        <v>16.43227843215111</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.856766068044897</v>
+        <v>5.888112160451934</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.522273891469558</v>
+        <v>5.553032337054362</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.851959075885054</v>
+        <v>3.850311942052294</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.908563535528625</v>
+        <v>3.939807925963378</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.864645916313357</v>
+        <v>1.884061573228021</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.344690162809077</v>
+        <v>1.349047398611362</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.458348654875829</v>
+        <v>0.4583486548758291</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>19.5</v>
@@ -4015,16 +4021,16 @@
         <v>40.9900016784668</v>
       </c>
       <c r="E12" t="n">
-        <v>42.41999816894531</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>40.88000106811523</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>41.90000152587891</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>10004700</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0.01334983696766945</v>
@@ -4057,49 +4063,49 @@
         <v>1.957374195944466</v>
       </c>
       <c r="S12" t="n">
-        <v>39.71299995422363</v>
+        <v>39.64779991149902</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>3.215576072608812</v>
+        <v>3.385312097931815</v>
       </c>
       <c r="V12" t="n">
-        <v>37.38513323465983</v>
+        <v>37.40833323160808</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>9.642518648201268</v>
+        <v>9.574520267137697</v>
       </c>
       <c r="Y12" t="n">
-        <v>37.01249998092651</v>
+        <v>37.02559997558594</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.74637406170886</v>
+        <v>10.70719098541257</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.766373774149095</v>
+        <v>1.777903477507385</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.658905567748167</v>
+        <v>1.669693153911255</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.525769369704293</v>
+        <v>0.5226764569534194</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.7102744299378019</v>
+        <v>0.7460578322788315</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.470250290675132</v>
+        <v>1.469826753618769</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.413443545909188</v>
+        <v>1.416152135428421</v>
       </c>
       <c r="AH12" t="n">
         <v>0.263201321283092</v>
@@ -4308,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="CR12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS12" t="n">
         <v>4</v>
@@ -4317,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -4336,16 +4342,16 @@
         <v>4.190000057220459</v>
       </c>
       <c r="E13" t="n">
-        <v>4.239999771118164</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4.050000190734863</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.070000171661377</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>51944600</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0.07989689011238865</v>
@@ -4378,49 +4384,49 @@
         <v>5.746457483425221</v>
       </c>
       <c r="S13" t="n">
-        <v>3.776200022697449</v>
+        <v>3.773800020217895</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>10.95810688088024</v>
+        <v>11.02867228715878</v>
       </c>
       <c r="V13" t="n">
-        <v>3.899333349863688</v>
+        <v>3.88733335018158</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>7.454266698355807</v>
+        <v>7.785972536282271</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.353150012493134</v>
+        <v>4.339500011205673</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3.747859706291992</v>
+        <v>-3.445096292180384</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.049279024358224</v>
+        <v>1.049239522092174</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.9897054418737358</v>
+        <v>0.9873846623826139</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.7865289820459525</v>
+        <v>0.7847653798909259</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.097022817535901</v>
+        <v>1.11097717316023</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.4395840223828456</v>
+        <v>0.4612070487752531</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.1964301085618773</v>
+        <v>-0.1815703880860696</v>
       </c>
       <c r="AH13" t="n">
         <v>0.4134296865086579</v>
@@ -4429,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>4</v>
@@ -4637,16 +4643,16 @@
         <v>80.88999938964844</v>
       </c>
       <c r="E14" t="n">
-        <v>84.58999633789062</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>75.40000152587891</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>61921800</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0.2252348303950378</v>
@@ -4730,16 +4736,18 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>61.7</v>
+        <v>62.6</v>
       </c>
       <c r="AK14" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>84.59999999999999</v>
+        <v>65.5</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -4962,16 +4970,16 @@
         <v>21.19000053405762</v>
       </c>
       <c r="E15" t="n">
-        <v>21.69000053405762</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>20.47999954223633</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>21.38999938964844</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7529200</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0.02071292391305257</v>
@@ -5004,52 +5012,52 @@
         <v>-1.297069857950906</v>
       </c>
       <c r="S15" t="n">
-        <v>21.39340000152588</v>
+        <v>21.39439998626709</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9507580256235801</v>
+        <v>-0.9553876357396077</v>
       </c>
       <c r="V15" t="n">
-        <v>22.32113335927328</v>
+        <v>22.29993335723877</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.067542077766993</v>
+        <v>-4.977292108457621</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.42645000457764</v>
+        <v>22.43020000457764</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-5.513353519026135</v>
+        <v>-5.529150298556918</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.162135618479089</v>
+        <v>1.16320105534428</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9562283470481239</v>
+        <v>0.957188224909282</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2683963484502686</v>
+        <v>-0.2683117283713717</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1468912160578697</v>
+        <v>-0.1475194188235043</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.4105267307834995</v>
+        <v>-0.4026448482959571</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.436254046722903</v>
+        <v>-0.4366194524865821</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.2955078131425599</v>
+        <v>0.2955078131425598</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -5271,16 +5279,16 @@
         <v>19.10000038146973</v>
       </c>
       <c r="E16" t="n">
-        <v>19.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18.86000061035156</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5131700</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0.01058205116276123</v>
@@ -5313,49 +5321,49 @@
         <v>6.120183971675801</v>
       </c>
       <c r="S16" t="n">
-        <v>18.51499992370605</v>
+        <v>18.47219993591309</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3.159602809474798</v>
+        <v>3.398623053749492</v>
       </c>
       <c r="V16" t="n">
-        <v>19.147999903361</v>
+        <v>19.14353323618571</v>
       </c>
       <c r="W16" t="n">
         <v>-1</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2506764264337207</v>
+        <v>-0.2274024036153208</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.67874990463257</v>
+        <v>18.70399990558624</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.255239129962778</v>
+        <v>2.117196738036825</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.352593049715601</v>
+        <v>1.3537256923486</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.291870227334021</v>
+        <v>1.292840814079643</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.8435526196544866</v>
+        <v>0.8447181008039505</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3208834802868105</v>
+        <v>0.3454345351563421</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.01874473564534675</v>
+        <v>-0.01700633514309672</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1677027117910723</v>
+        <v>0.1575382488280837</v>
       </c>
       <c r="AH16" t="n">
         <v>0.3828853766858881</v>
@@ -5568,16 +5576,16 @@
         <v>4.090000152587891</v>
       </c>
       <c r="E17" t="n">
-        <v>4.400000095367432</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4.03000020980835</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4.150000095367432</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6129300</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0.01488832249524741</v>
@@ -5671,7 +5679,7 @@
         </is>
       </c>
       <c r="AL17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
         <v>7.4</v>
@@ -5873,16 +5881,16 @@
         <v>12.32999992370605</v>
       </c>
       <c r="E18" t="n">
-        <v>12.86999988555908</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>11.39000034332275</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>11.39999961853027</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>24198800</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0.1970873490659963</v>
@@ -5915,49 +5923,49 @@
         <v>31.16484420225367</v>
       </c>
       <c r="S18" t="n">
-        <v>9.011000061035157</v>
+        <v>9.003800048828126</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>36.83275818654941</v>
+        <v>36.94217837845972</v>
       </c>
       <c r="V18" t="n">
-        <v>10.55280000686646</v>
+        <v>10.52706666946411</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>16.84102717461923</v>
+        <v>17.1266442101266</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.92545001506805</v>
+        <v>10.90230001449585</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.8557625242062</v>
+        <v>13.09540103750507</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.189382468107261</v>
+        <v>4.211571084789981</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.044084782048497</v>
+        <v>4.064598648367394</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.305182505540832</v>
+        <v>3.308295486526791</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.582389945398968</v>
+        <v>3.590118763927002</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.539879699224156</v>
+        <v>1.576385249440243</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.8364976786057142</v>
+        <v>0.860280734594645</v>
       </c>
       <c r="AH18" t="n">
         <v>0.7129686766320239</v>
@@ -5966,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="AL18" t="n">
         <v>12.2</v>
@@ -6174,16 +6182,16 @@
         <v>11.97999954223633</v>
       </c>
       <c r="E19" t="n">
-        <v>12.32999992370605</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>11.89999961853027</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>11.89999961853027</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>48702000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0.04995615271226317</v>
@@ -6216,49 +6224,49 @@
         <v>7.218335979051055</v>
       </c>
       <c r="S19" t="n">
-        <v>10.93359994888306</v>
+        <v>10.92759996414185</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>9.570494606034753</v>
+        <v>9.6306561509193</v>
       </c>
       <c r="V19" t="n">
-        <v>11.45993337631226</v>
+        <v>11.45160004297892</v>
       </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.538125561873267</v>
+        <v>4.614197992195614</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.43680003166199</v>
+        <v>11.43460003376007</v>
       </c>
       <c r="Z19" t="n">
         <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.749576009640209</v>
+        <v>4.769729652685657</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.890484201609733</v>
+        <v>2.908553246656869</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.62037534279779</v>
+        <v>2.635760003566225</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.570662435784871</v>
+        <v>1.568275167972942</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.718758008957601</v>
+        <v>1.728818135376388</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.6521300195728243</v>
+        <v>0.661507252701815</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.6672355776658218</v>
+        <v>0.6682339029513337</v>
       </c>
       <c r="AH19" t="n">
         <v>0.2874547504402187</v>
@@ -6475,16 +6483,16 @@
         <v>5.039999961853027</v>
       </c>
       <c r="E20" t="n">
-        <v>5.300000190734863</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.960000038146973</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5.300000190734863</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>15935300</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0.01408454217634447</v>
@@ -6517,13 +6525,13 @@
         <v>-12.76794061566122</v>
       </c>
       <c r="S20" t="n">
-        <v>5.781199989318847</v>
+        <v>5.776599988937378</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-12.82086813871232</v>
+        <v>-12.75144598024781</v>
       </c>
       <c r="V20" t="n">
         <v>5.110999987920125</v>
@@ -6535,31 +6543,31 @@
         <v>-1.389161147229632</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.244799988269806</v>
+        <v>5.24339998960495</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.904820524611456</v>
+        <v>-3.879162912521717</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.287936996177967</v>
+        <v>0.2875586226802243</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1437451335590101</v>
+        <v>0.1435719649502968</v>
       </c>
       <c r="AD20" t="n">
-        <v>-1.620491624825432</v>
+        <v>-1.61972817447954</v>
       </c>
       <c r="AE20" t="n">
-        <v>-1.234668534056311</v>
+        <v>-1.235001810316793</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.1168776293264514</v>
+        <v>-0.1166935453452374</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.3552068761913316</v>
+        <v>-0.3526525672676781</v>
       </c>
       <c r="AH20" t="n">
         <v>0.4982848389919968</v>
@@ -6578,16 +6586,16 @@
         </is>
       </c>
       <c r="AL20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AP20" t="n">
         <v>1</v>
@@ -6780,16 +6788,16 @@
         <v>2.690000057220459</v>
       </c>
       <c r="E21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.589999914169312</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.609999895095825</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>87698200</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0.1069958779096756</v>
@@ -6822,52 +6830,52 @@
         <v>15.1275749172304</v>
       </c>
       <c r="S21" t="n">
-        <v>2.253999996185303</v>
+        <v>2.255</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>19.34339227032158</v>
+        <v>19.29046816942169</v>
       </c>
       <c r="V21" t="n">
-        <v>2.546199998855591</v>
+        <v>2.53733333269755</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>5.647634059755724</v>
+        <v>6.016817836094167</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.833713624477387</v>
+        <v>2.827090899944305</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-5.0715628430319</v>
+        <v>-4.849184111007791</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.39196763138119</v>
+        <v>3.398569963819484</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.090071616686192</v>
+        <v>3.094568252033712</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.741873258137365</v>
+        <v>1.74520922015555</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.699296098619959</v>
+        <v>1.699583584998678</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.2553608312309839</v>
+        <v>0.2725595210944966</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.1885618201449314</v>
+        <v>-0.1807546993722815</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.5093066287985811</v>
+        <v>0.509306628798581</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -7083,16 +7091,16 @@
         <v>50.04000091552734</v>
       </c>
       <c r="E22" t="n">
-        <v>52.29999923706055</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>50.04000091552734</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>50.58000183105469</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3511800</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0.04054898641613991</v>
@@ -7125,49 +7133,49 @@
         <v>9.518840754619154</v>
       </c>
       <c r="S22" t="n">
-        <v>44.91980010986328</v>
+        <v>44.9060001373291</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>11.39853871375485</v>
+        <v>11.43277237451058</v>
       </c>
       <c r="V22" t="n">
-        <v>46.46926653544108</v>
+        <v>46.43546653747558</v>
       </c>
       <c r="W22" t="n">
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>7.68407734037064</v>
+        <v>7.762459703387997</v>
       </c>
       <c r="Y22" t="n">
-        <v>47.78699995040893</v>
+        <v>47.75834995269776</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.714673378652074</v>
+        <v>4.777491192826905</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.037367235915576</v>
+        <v>3.048699817512753</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.840953341719519</v>
+        <v>2.849755570281852</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.669516451847465</v>
+        <v>1.669443104339562</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.457683386808786</v>
+        <v>1.461328845476774</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.6258353668445328</v>
+        <v>0.6315859371410255</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.3752050717125255</v>
+        <v>0.3792058726184194</v>
       </c>
       <c r="AH22" t="n">
         <v>0.2643110674516133</v>
@@ -7386,16 +7394,16 @@
         <v>17.25</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>16.69000053405762</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>16.70000076293945</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>81666100</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0.03853096725653238</v>
@@ -7428,49 +7436,49 @@
         <v>8.595641897251506</v>
       </c>
       <c r="S23" t="n">
-        <v>15.17379993438721</v>
+        <v>15.16899993896484</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>13.68279583618117</v>
+        <v>13.71876899867117</v>
       </c>
       <c r="V23" t="n">
-        <v>15.1745999399821</v>
+        <v>15.17173327763875</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>13.67680247404501</v>
+        <v>13.69828143119517</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.70709995746613</v>
+        <v>14.7110999584198</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>17.29028870333447</v>
+        <v>17.25839705226854</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.839991906355892</v>
+        <v>2.84837519411885</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.659791335927388</v>
+        <v>2.665695615409291</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.815154704129001</v>
+        <v>1.811989933298833</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.256118738015813</v>
+        <v>2.256370172368114</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.890454176542384</v>
+        <v>1.881703161517462</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.185001794160128</v>
+        <v>2.168147875022674</v>
       </c>
       <c r="AH23" t="n">
         <v>0.2066373460917492</v>
@@ -7689,16 +7697,16 @@
         <v>5.099999904632568</v>
       </c>
       <c r="E24" t="n">
-        <v>5.179999828338623</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4.639999866485596</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>4.650000095367432</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>145981500</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0.237864088906522</v>
@@ -7731,49 +7739,49 @@
         <v>32.53373071828464</v>
       </c>
       <c r="S24" t="n">
-        <v>3.756200013160706</v>
+        <v>3.749200015068054</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>35.77551479589885</v>
+        <v>36.02901643378968</v>
       </c>
       <c r="V24" t="n">
-        <v>4.309866668383281</v>
+        <v>4.291800003051758</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>18.33312482832985</v>
+        <v>18.83125730477016</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.652750009298325</v>
+        <v>4.640850009918213</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>9.612592433301453</v>
+        <v>9.893659431636033</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.331829579355201</v>
+        <v>5.369131619953408</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.166563510072277</v>
+        <v>5.202110632788787</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.80525493513277</v>
+        <v>3.798015908070801</v>
       </c>
       <c r="AE24" t="n">
-        <v>3.776169562552789</v>
+        <v>3.796933932650411</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.770000832572767</v>
+        <v>1.812968059779406</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.9646917707539001</v>
+        <v>0.9905740973715476</v>
       </c>
       <c r="AH24" t="n">
         <v>0.8167170718628636</v>
@@ -7990,16 +7998,16 @@
         <v>61.02999877929688</v>
       </c>
       <c r="E25" t="n">
-        <v>62.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>56.88000106811523</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>57.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>11336800</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0.08497775607638891</v>
@@ -8032,55 +8040,55 @@
         <v>7.792426215511158</v>
       </c>
       <c r="S25" t="n">
-        <v>57.76779998779297</v>
+        <v>57.73979995727539</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>5.647088502925934</v>
+        <v>5.698320438339019</v>
       </c>
       <c r="V25" t="n">
-        <v>57.21419982910156</v>
+        <v>57.24906649271647</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>6.669321534851631</v>
+        <v>6.60435622485029</v>
       </c>
       <c r="Y25" t="n">
-        <v>55.17729988098144</v>
+        <v>55.26174987792969</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>10.60707738678736</v>
+        <v>10.43804967108162</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.159009383846973</v>
+        <v>2.177380269734772</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.063692351261475</v>
+        <v>2.080196766830273</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.307058203791916</v>
+        <v>1.311457340581911</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.6737600040647137</v>
+        <v>0.6814258615487661</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.4258404591399851</v>
+        <v>0.4204766420623895</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.6103733971932535</v>
+        <v>0.5975979588588944</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.3230207718245605</v>
+        <v>0.3230207718245604</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
         <v>57.9</v>
@@ -8295,16 +8303,16 @@
         <v>6.429999828338623</v>
       </c>
       <c r="E26" t="n">
-        <v>6.829999923706055</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>6.300000190734863</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>6.599999904632568</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>38538800</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0.04213934340837944</v>
@@ -8337,49 +8345,49 @@
         <v>4.572462411007622</v>
       </c>
       <c r="S26" t="n">
-        <v>5.527599983215332</v>
+        <v>5.509599981307983</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>16.32534640465024</v>
+        <v>16.70538424120106</v>
       </c>
       <c r="V26" t="n">
-        <v>5.920999997456868</v>
+        <v>5.894599997202556</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>8.596518005410834</v>
+        <v>9.082886563806809</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.807699999809265</v>
+        <v>6.781500000953674</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-5.548131843078048</v>
+        <v>-5.183221596484846</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.307674116604528</v>
+        <v>1.307923107098224</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.137556569861508</v>
+        <v>1.138047174278241</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.4322845797452728</v>
+        <v>0.4294483229232567</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.192722249091493</v>
+        <v>1.217021672134889</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.4718812685131117</v>
+        <v>0.4963227643135723</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.3123444855031604</v>
+        <v>-0.2906020220824868</v>
       </c>
       <c r="AH26" t="n">
         <v>0.7522260739693396</v>
@@ -8398,7 +8406,7 @@
         </is>
       </c>
       <c r="AL26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>7.8</v>
@@ -8596,16 +8604,16 @@
         <v>30.04000091552734</v>
       </c>
       <c r="E27" t="n">
-        <v>31.80999946594238</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>29.1200008392334</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>29.15999984741211</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>7987100</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0.06789910457674853</v>
@@ -8638,52 +8646,52 @@
         <v>-0.7509970486594305</v>
       </c>
       <c r="S27" t="n">
-        <v>30.66339996337891</v>
+        <v>30.71019996643066</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.033039547460767</v>
+        <v>-2.18233372506827</v>
       </c>
       <c r="V27" t="n">
-        <v>32.34206675211588</v>
+        <v>32.29640008290609</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.117868670028435</v>
+        <v>-6.986534603195659</v>
       </c>
       <c r="Y27" t="n">
-        <v>33.04879999160767</v>
+        <v>33.02574999809265</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-9.10410991274833</v>
+        <v>-9.040670030923577</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.840038653390118</v>
+        <v>1.842858647774888</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.688671562877914</v>
+        <v>1.690530057878695</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.1058140892915711</v>
+        <v>-0.1059341542315593</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.2593903954637863</v>
+        <v>-0.2788477691078141</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.6746136785484861</v>
+        <v>-0.6663444079700578</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.6919588434023609</v>
+        <v>-0.6916152041088048</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.4791905948345205</v>
+        <v>0.4791905948345204</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -8897,16 +8905,16 @@
         <v>20.6200008392334</v>
       </c>
       <c r="E28" t="n">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>20.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>20.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>21833900</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0.01028912265513404</v>
@@ -8939,49 +8947,49 @@
         <v>2.567442325911777</v>
       </c>
       <c r="S28" t="n">
-        <v>19.67080005645752</v>
+        <v>19.62400005340576</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>4.825430486058323</v>
+        <v>5.075421846295702</v>
       </c>
       <c r="V28" t="n">
-        <v>19.08426672617594</v>
+        <v>19.09066673278809</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>8.047121406823793</v>
+        <v>8.010899398388695</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.57960010051727</v>
+        <v>18.59230010509491</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>10.98194109495026</v>
+        <v>10.90613169256466</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.7450580504856456</v>
+        <v>0.7515830166546219</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.6546894356026057</v>
+        <v>0.6601466474772917</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.5339376184955575</v>
+        <v>0.5338531273629177</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.8902140434560407</v>
+        <v>0.9328980345057092</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.268979294252752</v>
+        <v>1.2607830501442</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.581654893097639</v>
+        <v>1.571824146247038</v>
       </c>
       <c r="AH28" t="n">
         <v>0.2356058561444916</v>
@@ -9210,16 +9218,16 @@
         <v>33.13999938964844</v>
       </c>
       <c r="E29" t="n">
-        <v>35.31999969482422</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>32.06000137329102</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>32.18999862670898</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>25511700</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0.1839942715485252</v>
@@ -9252,52 +9260,52 @@
         <v>25.70427940357602</v>
       </c>
       <c r="S29" t="n">
-        <v>24.20300006866455</v>
+        <v>24.21820003509522</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>36.92517165487495</v>
+        <v>36.83923388866395</v>
       </c>
       <c r="V29" t="n">
-        <v>24.19246667226156</v>
+        <v>24.1312000020345</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>36.98478885431673</v>
+        <v>37.33257934480839</v>
       </c>
       <c r="Y29" t="n">
-        <v>25.38845000267029</v>
+        <v>25.33005000114441</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>30.53179452137827</v>
+        <v>30.83274367066458</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.263995996681689</v>
+        <v>4.262544753331574</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.029720252472226</v>
+        <v>4.027749135548424</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.867322011047388</v>
+        <v>2.869771041323303</v>
       </c>
       <c r="AE29" t="n">
-        <v>3.419278827404445</v>
+        <v>3.418804087870243</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.315377303863952</v>
+        <v>2.341324281975792</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.670919169774535</v>
+        <v>1.692783795556625</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.6500343194356141</v>
+        <v>0.650034319435614</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -9511,16 +9519,16 @@
         <v>11.35000038146973</v>
       </c>
       <c r="E30" t="n">
-        <v>12.23999977111816</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>11.26000022888184</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>11.35999965667725</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>27097600</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0.07992389479493456</v>
@@ -9553,49 +9561,49 @@
         <v>7.834542517856109</v>
       </c>
       <c r="S30" t="n">
-        <v>10.79800004959106</v>
+        <v>10.79540004730225</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>5.112060838521369</v>
+        <v>5.13737639862706</v>
       </c>
       <c r="V30" t="n">
-        <v>12.60046669006348</v>
+        <v>12.56926668802897</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.923968209684235</v>
+        <v>-9.700377411201561</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.13250000953674</v>
+        <v>13.10105000495911</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-13.57319342678527</v>
+        <v>-13.36571971579804</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.711406901710193</v>
+        <v>2.719164181362972</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.525465236273352</v>
+        <v>2.531595361783488</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.010410325886205</v>
+        <v>1.013342297588002</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.5631862119339791</v>
+        <v>0.569757089518792</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.6714726404069599</v>
+        <v>-0.6613606492021876</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.7177679645549222</v>
+        <v>-0.7115623914874081</v>
       </c>
       <c r="AH30" t="n">
         <v>0.455371094942885</v>
@@ -9808,16 +9816,16 @@
         <v>31.63999938964844</v>
       </c>
       <c r="E31" t="n">
-        <v>33.09999847412109</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>31.09000015258789</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>31.14999961853027</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>7815600</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0.03061884701461426</v>
@@ -9850,64 +9858,64 @@
         <v>5.239994605410548</v>
       </c>
       <c r="S31" t="n">
-        <v>29.54639991760254</v>
+        <v>29.54359992980957</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>7.085802256398139</v>
+        <v>7.09595128833164</v>
       </c>
       <c r="V31" t="n">
-        <v>32.07306664784749</v>
+        <v>32.04599997202556</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-1.350252107021755</v>
+        <v>-1.266930608286634</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.11805003166199</v>
+        <v>32.11205002784729</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1.488417390041696</v>
+        <v>-1.470010908022045</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.550024399443406</v>
+        <v>2.556516213320525</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.255718497064136</v>
+        <v>2.260582092352074</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.107704500647444</v>
+        <v>1.10888670690462</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.335544014787099</v>
+        <v>1.335989080191405</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.1709384826304639</v>
+        <v>-0.1597799182048964</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.1894591394864349</v>
+        <v>-0.1861489037170927</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.283843532415534</v>
+        <v>0.2838435324155341</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="AK31" t="n">
         <v>31</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>31.1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>31.6</v>
       </c>
       <c r="AM31" t="n">
         <v>39.4</v>
@@ -10109,16 +10117,16 @@
         <v>95</v>
       </c>
       <c r="E32" t="n">
-        <v>98.93000030517578</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>93.05000305175781</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>98.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>15201700</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>-0.0330788804071247</v>
@@ -10151,52 +10159,52 @@
         <v>-1.561858404227691</v>
       </c>
       <c r="S32" t="n">
-        <v>95.11879974365235</v>
+        <v>95.36199981689452</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.1248961761213498</v>
+        <v>-0.3796059411396612</v>
       </c>
       <c r="V32" t="n">
-        <v>84.29399978637696</v>
+        <v>84.30573313395182</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>12.70078563213852</v>
+        <v>12.68510037040572</v>
       </c>
       <c r="Y32" t="n">
-        <v>86.78049980163574</v>
+        <v>86.81599983215332</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.471598132244599</v>
+        <v>9.426833974923175</v>
       </c>
       <c r="AB32" t="n">
-        <v>-1.017976454592475</v>
+        <v>-1.021018888025251</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.9454144440597148</v>
+        <v>-0.948791653029504</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.2443758225248386</v>
+        <v>-0.2447129426238092</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.0148188297942358</v>
+        <v>-0.04512013933807584</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.066478777958292</v>
+        <v>1.064847605017027</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.7666909919621777</v>
+        <v>0.7640014710793246</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.2300723895259849</v>
+        <v>0.2300723895259848</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -10410,16 +10418,16 @@
         <v>30.26000022888184</v>
       </c>
       <c r="E33" t="n">
-        <v>31.69000053405762</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>29.96999931335449</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>30.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>30353000</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0.05398819901904739</v>
@@ -10452,49 +10460,49 @@
         <v>10.15499299317829</v>
       </c>
       <c r="S33" t="n">
-        <v>26.59560001373291</v>
+        <v>26.60400001525879</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>13.77821975536095</v>
+        <v>13.74229518691226</v>
       </c>
       <c r="V33" t="n">
-        <v>25.6272666422526</v>
+        <v>25.6541999689738</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>18.07736131714912</v>
+        <v>17.95339658020245</v>
       </c>
       <c r="Y33" t="n">
-        <v>24.45189998626709</v>
+        <v>24.4756999874115</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>23.7531653813272</v>
+        <v>23.63282866044835</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.541820065083497</v>
+        <v>2.545154540996572</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.457891964561738</v>
+        <v>2.459175617798248</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.990118908164741</v>
+        <v>1.987250813521095</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.129178052902667</v>
+        <v>2.120808415940645</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.949364613668196</v>
+        <v>1.921857403032454</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.327776865773452</v>
+        <v>2.297402417739922</v>
       </c>
       <c r="AH33" t="n">
         <v>0.2918637906149286</v>
@@ -10503,16 +10511,18 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="AL33" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>31.7</v>
+        <v>28.9</v>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -10711,16 +10721,16 @@
         <v>62.84999847412109</v>
       </c>
       <c r="E34" t="n">
-        <v>65.51000213623047</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>58.93000030517578</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>10700000</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0.1396191611097055</v>
@@ -10804,16 +10814,18 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="AK34" t="n">
-        <v>51.8</v>
+        <v>53.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>65.5</v>
+        <v>59.2</v>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
@@ -11012,16 +11024,16 @@
         <v>47.65999984741211</v>
       </c>
       <c r="E35" t="n">
-        <v>48.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>46.31999969482422</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>46.70000076293945</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>40583600</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0.1371987597455231</v>
@@ -11054,49 +11066,49 @@
         <v>20.0306084771909</v>
       </c>
       <c r="S35" t="n">
-        <v>38.37640022277832</v>
+        <v>38.34500022888184</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>24.19090787760626</v>
+        <v>24.29260545815337</v>
       </c>
       <c r="V35" t="n">
-        <v>39.70853345235189</v>
+        <v>39.67566678365072</v>
       </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>20.02457835568659</v>
+        <v>20.12400473897397</v>
       </c>
       <c r="Y35" t="n">
-        <v>39.74800006866455</v>
+        <v>39.7327000617981</v>
       </c>
       <c r="Z35" t="n">
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>19.90540345446211</v>
+        <v>19.95157583875326</v>
       </c>
       <c r="AB35" t="n">
-        <v>5.760798432098825</v>
+        <v>5.796427930901505</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.526726486686369</v>
+        <v>5.555822717634685</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.475741966807401</v>
+        <v>4.470608231442138</v>
       </c>
       <c r="AE35" t="n">
-        <v>4.918889800314195</v>
+        <v>4.923877782875866</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.008257255804203</v>
+        <v>3.009338531795637</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.851806330031712</v>
+        <v>2.845015333705722</v>
       </c>
       <c r="AH35" t="n">
         <v>0.4379892801520445</v>
@@ -11105,16 +11117,18 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="AK35" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="AL35" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>48.7</v>
+        <v>46.3</v>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -11313,16 +11327,16 @@
         <v>24.28000068664551</v>
       </c>
       <c r="E36" t="n">
-        <v>25.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>24.10000038146973</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>24.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>7521400</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0.03319151858065994</v>
@@ -11355,67 +11369,69 @@
         <v>13.66836788641595</v>
       </c>
       <c r="S36" t="n">
-        <v>19.67560001373291</v>
+        <v>19.72680000305176</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>23.40157692623798</v>
+        <v>23.08129388897016</v>
       </c>
       <c r="V36" t="n">
-        <v>17.13566663106283</v>
+        <v>17.14846663157145</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>41.69276987818921</v>
+        <v>41.58700721348714</v>
       </c>
       <c r="Y36" t="n">
-        <v>16.88670000553131</v>
+        <v>16.9054000043869</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>43.78179679092121</v>
+        <v>43.6227517854941</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.573141818743146</v>
+        <v>2.556565237642482</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.506132991932527</v>
+        <v>2.490301560377853</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.530905970349945</v>
+        <v>2.536642040727368</v>
       </c>
       <c r="AE36" t="n">
-        <v>3.154554542247749</v>
+        <v>3.135125178695794</v>
       </c>
       <c r="AF36" t="n">
-        <v>4.47591879714007</v>
+        <v>4.487518666557712</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.508720496828315</v>
+        <v>4.519319187701393</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.2969298092590092</v>
+        <v>0.2969298092590094</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>25.1</v>
+        <v>24</v>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
@@ -11614,16 +11630,16 @@
         <v>25.79000091552734</v>
       </c>
       <c r="E37" t="n">
-        <v>27.1299991607666</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>25.21999931335449</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>26.36000061035156</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>21769300</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>-0.01187737400044153</v>
@@ -11656,52 +11672,52 @@
         <v>2.342835399981869</v>
       </c>
       <c r="S37" t="n">
-        <v>24.76939994812012</v>
+        <v>24.78919994354248</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>4.120410545047076</v>
+        <v>4.037245954948894</v>
       </c>
       <c r="V37" t="n">
-        <v>22.71213333129883</v>
+        <v>22.74180000305176</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>13.5516445739908</v>
+        <v>13.40351648535535</v>
       </c>
       <c r="Y37" t="n">
-        <v>22.44609999656677</v>
+        <v>22.47269999504089</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>14.89746958033705</v>
+        <v>14.76147023374355</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.9391319163949022</v>
+        <v>0.9397445267192103</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.7965609601111423</v>
+        <v>0.7977608136279353</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.3796289781852066</v>
+        <v>0.3789518068231054</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.5491072325647767</v>
+        <v>0.5380431373101576</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.798626868382068</v>
+        <v>1.78342675197105</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.851729360534102</v>
+        <v>1.845282987470214</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.3589642899717148</v>
+        <v>0.358964289971715</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -11915,16 +11931,16 @@
         <v>11.77999973297119</v>
       </c>
       <c r="E38" t="n">
-        <v>12.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>11.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>11.88000011444092</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>26879800</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0.002553168763505642</v>
@@ -11957,52 +11973,52 @@
         <v>4.89400092377625</v>
       </c>
       <c r="S38" t="n">
-        <v>10.97539999008179</v>
+        <v>10.98799997329712</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>7.330937766427673</v>
+        <v>7.207860953756627</v>
       </c>
       <c r="V38" t="n">
-        <v>10.02766666094462</v>
+        <v>10.04019998868307</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>17.47498327653324</v>
+        <v>17.32833754555848</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.913355505466461</v>
+        <v>9.925866925716401</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>18.82959030850269</v>
+        <v>18.67980722621837</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.483500346634159</v>
+        <v>1.482516703694655</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.322015321805964</v>
+        <v>1.322255704988507</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.8411952893249055</v>
+        <v>0.8390890414748172</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.030171480249264</v>
+        <v>1.012624365305701</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.204290166503441</v>
+        <v>2.189123286891026</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.273627731919023</v>
+        <v>2.266301556796386</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.3496238296663606</v>
+        <v>0.3496238296663607</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -12017,7 +12033,7 @@
         <v>8.1</v>
       </c>
       <c r="AM38" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -12220,16 +12236,16 @@
         <v>8.760000228881836</v>
       </c>
       <c r="E39" t="n">
-        <v>9.270000457763672</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>8.590000152587891</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>8.899999618530273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>17852900</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0.1230769249579375</v>
@@ -12262,52 +12278,52 @@
         <v>28.38782672158164</v>
       </c>
       <c r="S39" t="n">
-        <v>7.768400030136108</v>
+        <v>7.776000032424927</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>12.76453574608662</v>
+        <v>12.65432346133943</v>
       </c>
       <c r="V39" t="n">
-        <v>9.991133330663045</v>
+        <v>9.99073333422343</v>
       </c>
       <c r="W39" t="n">
         <v>-1</v>
       </c>
       <c r="X39" t="n">
-        <v>-12.32225675542563</v>
+        <v>-12.3187464240057</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.78384999036789</v>
+        <v>10.76184999227524</v>
       </c>
       <c r="Z39" t="n">
         <v>-1</v>
       </c>
       <c r="AA39" t="n">
-        <v>-18.76741389479408</v>
+        <v>-18.60135352964697</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.151084414135401</v>
+        <v>3.173902879181875</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.000981571957616</v>
+        <v>3.019897646442981</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.953436497338836</v>
+        <v>1.954885747008464</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.7117888465537653</v>
+        <v>0.7060139592447767</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.6240410634633845</v>
+        <v>-0.625561871708526</v>
       </c>
       <c r="AG39" t="n">
-        <v>-1.086124797700767</v>
+        <v>-1.087748071466075</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.7270950150542104</v>
+        <v>0.7270950150542097</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -12521,16 +12537,16 @@
         <v>26.95000076293945</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>25.89999961853027</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>25.95999908447266</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>8512600</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0.07114471090553121</v>
@@ -12563,52 +12579,52 @@
         <v>14.02395715180953</v>
       </c>
       <c r="S40" t="n">
-        <v>22.51199996948242</v>
+        <v>22.5403999710083</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>19.7139338995791</v>
+        <v>19.56309913578652</v>
       </c>
       <c r="V40" t="n">
-        <v>22.16553335825602</v>
+        <v>22.15820002237956</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>21.58516705803225</v>
+        <v>21.62540610573163</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.57635001182556</v>
+        <v>22.56630001068115</v>
       </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>19.37270971092741</v>
+        <v>19.42587287319318</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.844543633142419</v>
+        <v>2.847533563084837</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.657707212333813</v>
+        <v>2.660654633432347</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.711060511381791</v>
+        <v>2.713746558101699</v>
       </c>
       <c r="AE40" t="n">
-        <v>3.242690998328064</v>
+        <v>3.228471508810089</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.544016206602149</v>
+        <v>3.544472000109225</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.808159623197698</v>
+        <v>2.813419391871525</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.3432492695972137</v>
+        <v>0.3432492695972136</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -12623,7 +12639,7 @@
         <v>25.6</v>
       </c>
       <c r="AM40" t="n">
-        <v>30</v>
+        <v>28.9</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -12822,16 +12838,16 @@
         <v>30.76000022888184</v>
       </c>
       <c r="E41" t="n">
-        <v>31.97999954223633</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>29.88999938964844</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>8326600</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0.08043558028654973</v>
@@ -12915,16 +12931,18 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="AK41" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="AL41" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>32</v>
+        <v>30.6</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -13123,16 +13141,16 @@
         <v>29.29999923706055</v>
       </c>
       <c r="E42" t="n">
-        <v>30.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>29.31999969482422</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>9405200</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0.03937561837439096</v>
@@ -13165,52 +13183,52 @@
         <v>6.793391936179487</v>
       </c>
       <c r="S42" t="n">
-        <v>26.85139995574951</v>
+        <v>26.83959999084473</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>9.119074928481464</v>
+        <v>9.167048864569853</v>
       </c>
       <c r="V42" t="n">
-        <v>28.01106671651204</v>
+        <v>27.99306672414144</v>
       </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>4.601511729607568</v>
+        <v>4.668772184906769</v>
       </c>
       <c r="Y42" t="n">
-        <v>27.99579999923706</v>
+        <v>27.98930000305176</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.658553203905686</v>
+        <v>4.682858213195332</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.865693347409658</v>
+        <v>2.874488373773548</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.70960190220367</v>
+        <v>2.71733181482614</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.666249041600165</v>
+        <v>1.666750087448691</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.896072601021088</v>
+        <v>1.906618689963476</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.581153378673289</v>
+        <v>0.5865634814824706</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.5732825316774407</v>
+        <v>0.5724440680717781</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.2002804019608585</v>
+        <v>0.2002804019608586</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -13424,16 +13442,16 @@
         <v>16.36000061035156</v>
       </c>
       <c r="E43" t="n">
-        <v>16.42000007629395</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>15.71000003814697</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>15.92000007629395</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>84984800</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0.1152011264668349</v>
@@ -13466,67 +13484,69 @@
         <v>16.01887951047433</v>
       </c>
       <c r="S43" t="n">
-        <v>13.59339992523193</v>
+        <v>13.58679992675781</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>20.35252917104493</v>
+        <v>20.41099227590902</v>
       </c>
       <c r="V43" t="n">
-        <v>13.53399996439616</v>
+        <v>13.5271999613444</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>20.88074961866227</v>
+        <v>20.94151529586485</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.406062707901</v>
+        <v>13.41386859416962</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>22.03434346692731</v>
+        <v>21.9633284424934</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.627339916487461</v>
+        <v>4.650872350553493</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.34927867463319</v>
+        <v>4.369418307279807</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.085251776480579</v>
+        <v>3.082227167189954</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.423157303882924</v>
+        <v>3.426089807447255</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.512816724890896</v>
+        <v>2.511758202360743</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.716149567401135</v>
+        <v>2.696092723133437</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.380771904897576</v>
+        <v>0.3807719048975759</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="AK43" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="AL43" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>16.4</v>
+        <v>15.2</v>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -13725,16 +13745,16 @@
         <v>49.47999954223633</v>
       </c>
       <c r="E44" t="n">
-        <v>50.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>48.08000183105469</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>48.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>105299300</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0.1037251287364545</v>
@@ -13767,49 +13787,49 @@
         <v>16.4382814357473</v>
       </c>
       <c r="S44" t="n">
-        <v>41.45399971008301</v>
+        <v>41.42039970397949</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>19.36121939567902</v>
+        <v>19.45804457672219</v>
       </c>
       <c r="V44" t="n">
-        <v>41.99479988098145</v>
+        <v>41.95813321431478</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>17.82411080054883</v>
+        <v>17.92707575787793</v>
       </c>
       <c r="Y44" t="n">
-        <v>42.24958770751953</v>
+        <v>42.25867799758911</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>17.11356779330166</v>
+        <v>17.08837542210667</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.630366817895673</v>
+        <v>4.653368312851526</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.365107039469258</v>
+        <v>4.385611628390686</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.083255339854937</v>
+        <v>3.082767487084579</v>
       </c>
       <c r="AE44" t="n">
-        <v>3.200000955221982</v>
+        <v>3.211433947279968</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.122529397084165</v>
+        <v>2.13105016839335</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.976689009838195</v>
+        <v>1.969269448643491</v>
       </c>
       <c r="AH44" t="n">
         <v>0.3669000273298496</v>
@@ -13827,7 +13847,7 @@
         <v>44.3</v>
       </c>
       <c r="AM44" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -14046,16 +14066,16 @@
         <v>18.45999908447266</v>
       </c>
       <c r="E45" t="n">
-        <v>19.21999931335449</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>18.02000045776367</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>18.56999969482422</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>16978800</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>-0.008593004701890727</v>
@@ -14347,16 +14367,16 @@
         <v>13.56999969482422</v>
       </c>
       <c r="E46" t="n">
-        <v>14.28999996185303</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>12.40999984741211</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>12.40999984741211</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>77137200</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0.1539115162172477</v>
@@ -14389,49 +14409,49 @@
         <v>19.22816667931109</v>
       </c>
       <c r="S46" t="n">
-        <v>11.75780002593994</v>
+        <v>11.73480001449585</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>15.41274443251476</v>
+        <v>15.63895147817918</v>
       </c>
       <c r="V46" t="n">
-        <v>13.68633338928223</v>
+        <v>13.66366671880086</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-0.8499989818245214</v>
+        <v>-0.6855189452752176</v>
       </c>
       <c r="Y46" t="n">
-        <v>13.87560004711151</v>
+        <v>13.86520004749298</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-2.202429813843688</v>
+        <v>-2.129073880345053</v>
       </c>
       <c r="AB46" t="n">
-        <v>4.514600785169598</v>
+        <v>4.586413670590389</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.314346860648553</v>
+        <v>4.38370702743286</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.168702563484078</v>
+        <v>3.185716511162968</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.175332375420445</v>
+        <v>2.216386309812932</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.1014847755417857</v>
+        <v>-0.08187281002315971</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.3009719473771856</v>
+        <v>-0.2914466045950569</v>
       </c>
       <c r="AH46" t="n">
         <v>0.5487317438383513</v>
@@ -14445,7 +14465,7 @@
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>13.4</v>
@@ -14618,16 +14638,16 @@
         <v>1</v>
       </c>
       <c r="CR46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CS46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CT46" t="n">
         <v>0</v>
       </c>
       <c r="CU46" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -14646,16 +14666,16 @@
         <v>17.79000091552734</v>
       </c>
       <c r="E47" t="n">
-        <v>19.29999923706055</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>17.79000091552734</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>18.96999931335449</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>16759700</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0.04770326237501976</v>
@@ -14688,52 +14708,52 @@
         <v>2.718192464801339</v>
       </c>
       <c r="S47" t="n">
-        <v>17.2052000617981</v>
+        <v>17.227200050354</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>3.39897735352536</v>
+        <v>3.266931733121513</v>
       </c>
       <c r="V47" t="n">
-        <v>17.36586672465006</v>
+        <v>17.33533338546753</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>2.442343924448295</v>
+        <v>2.622779267925531</v>
       </c>
       <c r="Y47" t="n">
-        <v>17.87360007286072</v>
+        <v>17.85400006771088</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.4677242245131763</v>
+        <v>-0.358458339536344</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.808085187906691</v>
+        <v>0.8090098031721781</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.7340341416565329</v>
+        <v>0.7361867676561925</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.2845645750783706</v>
+        <v>0.2861622757790837</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.339154194396469</v>
+        <v>0.326941459709635</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.2894931800758118</v>
+        <v>0.3102171440879342</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.06192044686859711</v>
+        <v>-0.04742598364362066</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.3174994490962353</v>
+        <v>0.3174994490962356</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -14754,10 +14774,10 @@
         <v>18.2</v>
       </c>
       <c r="AO47" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="AP47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ47" t="n">
         <v>0</v>
@@ -14947,16 +14967,16 @@
         <v>9.449999809265137</v>
       </c>
       <c r="E48" t="n">
-        <v>9.789999961853027</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>8.430000305175781</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>8.430000305175781</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>65166500</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0.2417870753572504</v>
@@ -14989,49 +15009,49 @@
         <v>54.4700073281411</v>
       </c>
       <c r="S48" t="n">
-        <v>5.345200037956237</v>
+        <v>5.338600039482117</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>76.79412823020164</v>
+        <v>77.01269507692612</v>
       </c>
       <c r="V48" t="n">
-        <v>6.461399995485942</v>
+        <v>6.428933332761129</v>
       </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>46.2531311459914</v>
+        <v>46.99172195656455</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.200145188570023</v>
+        <v>7.174745191335678</v>
       </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>31.24735073768622</v>
+        <v>31.71199195585494</v>
       </c>
       <c r="AB48" t="n">
-        <v>4.75564582219554</v>
+        <v>4.792753888481994</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.753793436526647</v>
+        <v>4.786830311086462</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.313928198465431</v>
+        <v>4.300501594421038</v>
       </c>
       <c r="AE48" t="n">
-        <v>4.733950803933385</v>
+        <v>4.747651580229344</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.146908465537261</v>
+        <v>2.174713395920571</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.41935868747447</v>
+        <v>1.437729675127435</v>
       </c>
       <c r="AH48" t="n">
         <v>1.012043439721475</v>
@@ -15248,16 +15268,16 @@
         <v>19.32999992370605</v>
       </c>
       <c r="E49" t="n">
-        <v>20.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>18.32999992370605</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>18.32999992370605</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>46176300</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0.1052029832285273</v>
@@ -15290,49 +15310,49 @@
         <v>17.11602495335418</v>
       </c>
       <c r="S49" t="n">
-        <v>15.51739999771118</v>
+        <v>15.51619998931885</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>24.56983725725464</v>
+        <v>24.57947137193758</v>
       </c>
       <c r="V49" t="n">
-        <v>15.29860001246134</v>
+        <v>15.28433334350586</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>26.35143024826434</v>
+        <v>26.46936892356613</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.48025001525879</v>
+        <v>15.47200001239777</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>24.86878380292689</v>
+        <v>24.93536652156709</v>
       </c>
       <c r="AB49" t="n">
-        <v>4.487389528235302</v>
+        <v>4.496282507702079</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.27360747001567</v>
+        <v>4.279640346972332</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.194330710491697</v>
+        <v>3.190349495588261</v>
       </c>
       <c r="AE49" t="n">
-        <v>4.038851572145385</v>
+        <v>4.045289622627014</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.971259148245307</v>
+        <v>2.981768767729459</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.515921546008617</v>
+        <v>2.521638255960926</v>
       </c>
       <c r="AH49" t="n">
         <v>0.3777186876436248</v>
@@ -15341,16 +15361,18 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="AK49" t="n">
-        <v>15.8</v>
+        <v>16.3</v>
       </c>
       <c r="AL49" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>20.1</v>
+        <v>17.8</v>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
@@ -15553,16 +15575,16 @@
         <v>6.269999980926514</v>
       </c>
       <c r="E50" t="n">
-        <v>6.690000057220459</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>6.099999904632568</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>6.170000076293945</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>32706700</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0.113676705768442</v>
@@ -15595,49 +15617,49 @@
         <v>13.84078192822863</v>
       </c>
       <c r="S50" t="n">
-        <v>5.164600009918213</v>
+        <v>5.163000011444092</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>21.40339946724753</v>
+        <v>21.4410220226359</v>
       </c>
       <c r="V50" t="n">
-        <v>6.077666664123536</v>
+        <v>6.040133330027262</v>
       </c>
       <c r="W50" t="n">
         <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>3.164591403775427</v>
+        <v>3.805655245332371</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.686900005340576</v>
+        <v>6.667300004959106</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-6.234578415724782</v>
+        <v>-5.958934257301793</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.940967254256534</v>
+        <v>2.931366470420787</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.786927970210081</v>
+        <v>2.777363627204835</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.387005043212792</v>
+        <v>1.383185641978969</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.676698193447798</v>
+        <v>1.674593649937192</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.1422852836370888</v>
+        <v>0.1711244869748958</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.2416881386747161</v>
+        <v>-0.230751932138158</v>
       </c>
       <c r="AH50" t="n">
         <v>0.5444421952684086</v>
@@ -15856,16 +15878,16 @@
         <v>36.18999862670898</v>
       </c>
       <c r="E51" t="n">
-        <v>37.90000152587891</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>36.18999862670898</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>36.27000045776367</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>17114200</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0.09766446123101447</v>
@@ -15949,16 +15971,18 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="AK51" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="AL51" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>36.2</v>
+        <v>36</v>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
@@ -16136,13 +16160,13 @@
         <v>9</v>
       </c>
       <c r="CS51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CT51" t="n">
         <v>0</v>
       </c>
       <c r="CU51" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
@@ -16161,16 +16185,16 @@
         <v>7.900000095367432</v>
       </c>
       <c r="E52" t="n">
-        <v>8.260000228881836</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>7.769999980926514</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>8.090000152587891</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>14832400</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0.06040272451318129</v>
@@ -16203,48 +16227,48 @@
         <v>-1.159711525564436</v>
       </c>
       <c r="S52" t="n">
-        <v>8.103199968338012</v>
+        <v>8.097199964523316</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-2.507649740405674</v>
+        <v>-2.435408166031301</v>
       </c>
       <c r="V52" t="n">
-        <v>8.927533321380615</v>
+        <v>8.921466655731201</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-11.50971034241157</v>
+        <v>-11.44953626775676</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.766299974918365</v>
+        <v>8.766849975585938</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-9.882161026083304</v>
+        <v>-9.887814695500932</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.296178470299973</v>
+        <v>2.299143333336517</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.971999777050502</v>
+        <v>1.97382208269938</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.1543008902212289</v>
+        <v>-0.1542412845558835</v>
       </c>
       <c r="AE52" t="n">
-        <v>-0.2718539007659935</v>
+        <v>-0.2644534330649854</v>
       </c>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="n">
-        <v>0.5427062499120597</v>
+        <v>0.5427062499120598</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -16260,7 +16284,7 @@
         </is>
       </c>
       <c r="AL52" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
         <v>8.1</v>
@@ -16462,16 +16486,16 @@
         <v>60.40000152587891</v>
       </c>
       <c r="E53" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>58.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>58.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>33909500</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0.06676090895977538</v>
@@ -16504,67 +16528,69 @@
         <v>12.27568733940488</v>
       </c>
       <c r="S53" t="n">
-        <v>50.70379989624023</v>
+        <v>50.69699989318848</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>19.1232247868619</v>
+        <v>19.13920281897016</v>
       </c>
       <c r="V53" t="n">
-        <v>49.19193328857422</v>
+        <v>49.20859995524089</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>22.78436216677009</v>
+        <v>22.74277581727073</v>
       </c>
       <c r="Y53" t="n">
-        <v>46.01674996376038</v>
+        <v>46.08639996528625</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>31.25655673954764</v>
+        <v>31.05818977263165</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.971279752313804</v>
+        <v>2.978518174435711</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.87611819189003</v>
+        <v>2.881007432526735</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.816692056663328</v>
+        <v>1.816669872049435</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.866782249827313</v>
+        <v>1.871198700744585</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.473223236666332</v>
+        <v>1.471727482038929</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.835906964955699</v>
+        <v>1.830223887212215</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.4025366414822068</v>
+        <v>0.4025366414822067</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="AK53" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="AL53" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>62</v>
+        <v>56.7</v>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
@@ -16763,16 +16789,16 @@
         <v>55.36000061035156</v>
       </c>
       <c r="E54" t="n">
-        <v>56.75</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>53.15999984741211</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>122802400</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0.08188396699902811</v>
@@ -16805,49 +16831,49 @@
         <v>13.81039168845419</v>
       </c>
       <c r="S54" t="n">
-        <v>45.58759979248047</v>
+        <v>45.58799980163574</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>21.43653287814249</v>
+        <v>21.43546734060746</v>
       </c>
       <c r="V54" t="n">
-        <v>44.35333323160808</v>
+        <v>44.36066655476888</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>24.81587420108409</v>
+        <v>24.79524071623812</v>
       </c>
       <c r="Y54" t="n">
-        <v>41.82384998321533</v>
+        <v>41.87704998016358</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>32.36466904067543</v>
+        <v>32.19651488482265</v>
       </c>
       <c r="AB54" t="n">
-        <v>3.525686236533454</v>
+        <v>3.530924809044787</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.392974029094617</v>
+        <v>3.396102439483952</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.161097720114357</v>
+        <v>2.161399326330189</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.208223223869823</v>
+        <v>2.211697217716166</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.757748840292617</v>
+        <v>1.757169684353366</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.089540737370707</v>
+        <v>2.085043645712627</v>
       </c>
       <c r="AH54" t="n">
         <v>0.3996769838717206</v>
@@ -16856,16 +16882,18 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="AK54" t="n">
-        <v>39.3</v>
+        <v>39.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>56.8</v>
+        <v>51.3</v>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
@@ -17036,7 +17064,7 @@
         <v>0</v>
       </c>
       <c r="CR54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CS54" t="n">
         <v>7</v>
@@ -17045,7 +17073,7 @@
         <v>0</v>
       </c>
       <c r="CU54" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -17064,16 +17092,16 @@
         <v>4.679999828338623</v>
       </c>
       <c r="E55" t="n">
-        <v>4.789999961853027</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>4.550000190734863</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>4.550000190734863</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>29222800</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0.08083138817540747</v>
@@ -17106,52 +17134,52 @@
         <v>7.093818139435373</v>
       </c>
       <c r="S55" t="n">
-        <v>4.509599990844727</v>
+        <v>4.493199987411499</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>3.778602045410625</v>
+        <v>4.157389865807824</v>
       </c>
       <c r="V55" t="n">
-        <v>5.558466650644938</v>
+        <v>5.543333317438761</v>
       </c>
       <c r="W55" t="n">
         <v>-1</v>
       </c>
       <c r="X55" t="n">
-        <v>-15.80412148743194</v>
+        <v>-15.57426623407579</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.716672694683075</v>
+        <v>5.70990451335907</v>
       </c>
       <c r="Z55" t="n">
         <v>-1</v>
       </c>
       <c r="AA55" t="n">
-        <v>-18.13420011449376</v>
+        <v>-18.0371612626945</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.626803706682081</v>
+        <v>2.64867668619593</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.491297669513774</v>
+        <v>2.511605656685731</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.105093419432873</v>
+        <v>1.10381269204561</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.4508690651182782</v>
+        <v>0.4963710202537039</v>
       </c>
       <c r="AF55" t="n">
-        <v>-1.528563112492665</v>
+        <v>-1.5223058387125</v>
       </c>
       <c r="AG55" t="n">
-        <v>-1.859084467982124</v>
+        <v>-1.871246561495095</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.3847930000902879</v>
+        <v>0.3847930000902878</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -17167,7 +17195,7 @@
         </is>
       </c>
       <c r="AL55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
         <v>5.9</v>
@@ -17341,7 +17369,7 @@
         <v>1</v>
       </c>
       <c r="CR55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CS55" t="n">
         <v>5</v>
@@ -17350,7 +17378,7 @@
         <v>0</v>
       </c>
       <c r="CU55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
@@ -17369,16 +17397,16 @@
         <v>64.15000152587891</v>
       </c>
       <c r="E56" t="n">
-        <v>65.33000183105469</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>15591500</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0.01809241762757052</v>
@@ -17411,52 +17439,52 @@
         <v>2.951072331410326</v>
       </c>
       <c r="S56" t="n">
-        <v>61.0552001953125</v>
+        <v>61.10360023498535</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>5.068857887069884</v>
+        <v>4.985633054644978</v>
       </c>
       <c r="V56" t="n">
-        <v>61.56986666361491</v>
+        <v>61.59626668294271</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>4.190580558441818</v>
+        <v>4.145924713394008</v>
       </c>
       <c r="Y56" t="n">
-        <v>57.83384998321533</v>
+        <v>57.9429999923706</v>
       </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>10.9212019336369</v>
+        <v>10.71225434362319</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.241698897527975</v>
+        <v>1.242991983272573</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.216978410878553</v>
+        <v>1.218246021544489</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.4515527031320825</v>
+        <v>0.4517360187724838</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.5061148620338721</v>
+        <v>0.498331086490417</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.2282882118783769</v>
+        <v>0.225947836710429</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.5957274102562569</v>
+        <v>0.5854807497025362</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.350892550384668</v>
+        <v>0.3508925503846681</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -17670,16 +17698,16 @@
         <v>51.54000091552734</v>
       </c>
       <c r="E57" t="n">
-        <v>52.4900016784668</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>49.11999893188477</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>50.90999984741211</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>5340000</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0.04184353433890609</v>
@@ -17943,7 +17971,7 @@
         <v>0</v>
       </c>
       <c r="CR57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CS57" t="n">
         <v>5</v>
@@ -17952,7 +17980,7 @@
         <v>0</v>
       </c>
       <c r="CU57" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
@@ -17971,16 +17999,16 @@
         <v>21.29000091552734</v>
       </c>
       <c r="E58" t="n">
-        <v>23.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>20.22999954223633</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>20.29999923706055</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>24847500</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0.09179491874499202</v>
@@ -18013,52 +18041,52 @@
         <v>8.771864820067847</v>
       </c>
       <c r="S58" t="n">
-        <v>19.07440006256104</v>
+        <v>19.10240005493164</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>11.61557294436252</v>
+        <v>11.45196862334026</v>
       </c>
       <c r="V58" t="n">
-        <v>19.95813340504964</v>
+        <v>19.92413340250651</v>
       </c>
       <c r="W58" t="n">
         <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>6.67330698441331</v>
+        <v>6.855342139242074</v>
       </c>
       <c r="Y58" t="n">
-        <v>21.16832456588745</v>
+        <v>21.14267554283142</v>
       </c>
       <c r="Z58" t="n">
         <v>1</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.5748038738784808</v>
+        <v>0.6968151802616865</v>
       </c>
       <c r="AB58" t="n">
-        <v>3.517109243895889</v>
+        <v>3.513283393795197</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.158772774904565</v>
+        <v>3.148558927778403</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.375410033635089</v>
+        <v>1.375379278136077</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.185662333312183</v>
+        <v>1.170235138027183</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.3250589739468072</v>
+        <v>0.3338156806322533</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.02784592664837569</v>
+        <v>0.0337187841089293</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.4802343766822484</v>
+        <v>0.4802343766822486</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -18272,16 +18300,16 @@
         <v>18.92000007629395</v>
       </c>
       <c r="E59" t="n">
-        <v>19.3700008392334</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>17.64999961853027</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>17.68000030517578</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>37123500</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0.1208531408146527</v>
@@ -18365,7 +18393,7 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="AK59" t="n">
         <v>17</v>
@@ -18577,16 +18605,16 @@
         <v>43.72999954223633</v>
       </c>
       <c r="E60" t="n">
-        <v>45.09999847412109</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>43.65999984741211</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>44.93000030517578</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>22212400</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0.09819186030582339</v>
@@ -18619,49 +18647,49 @@
         <v>16.19859257522478</v>
       </c>
       <c r="S60" t="n">
-        <v>35.92380004882813</v>
+        <v>35.93560005187988</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>21.72988236989936</v>
+        <v>21.68991050407882</v>
       </c>
       <c r="V60" t="n">
-        <v>36.33619997660319</v>
+        <v>36.29799997965495</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>20.34830161214984</v>
+        <v>20.47495610432262</v>
       </c>
       <c r="Y60" t="n">
-        <v>37.83759998321533</v>
+        <v>37.78244998931885</v>
       </c>
       <c r="Z60" t="n">
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>15.5728681566348</v>
+        <v>15.74156666547262</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.171680587050566</v>
+        <v>4.173499047103554</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.0085164394557</v>
+        <v>4.010003947168494</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.143802116593718</v>
+        <v>3.149644726859782</v>
       </c>
       <c r="AE60" t="n">
-        <v>3.395970491589793</v>
+        <v>3.410727131227328</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.6075170986173</v>
+        <v>1.626397498463753</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.002812501918557</v>
+        <v>1.018323253690738</v>
       </c>
       <c r="AH60" t="n">
         <v>0.3790183127357107</v>
@@ -18857,13 +18885,13 @@
         <v>8</v>
       </c>
       <c r="CS60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CT60" t="n">
         <v>0</v>
       </c>
       <c r="CU60" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61">
@@ -18882,16 +18910,16 @@
         <v>11.60000038146973</v>
       </c>
       <c r="E61" t="n">
-        <v>11.84000015258789</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>11.52000045776367</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>11.69999980926514</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2862400</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0.03571433741219288</v>
@@ -18975,13 +19003,13 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="n">
         <v>10.2</v>
       </c>
-      <c r="AK61" t="n">
+      <c r="AL61" t="n">
         <v>10.7</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>11.5</v>
       </c>
       <c r="AM61" t="n">
         <v>12.3</v>
@@ -19183,16 +19211,16 @@
         <v>50.06000137329102</v>
       </c>
       <c r="E62" t="n">
-        <v>51.54999923706055</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>47.27999877929688</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>39196300</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0.2068467195212536</v>
@@ -19225,49 +19253,49 @@
         <v>32.8868277800521</v>
       </c>
       <c r="S62" t="n">
-        <v>36.77259994506836</v>
+        <v>36.7607999420166</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>36.1339732520182</v>
+        <v>36.1776714659405</v>
       </c>
       <c r="V62" t="n">
-        <v>41.72126668294271</v>
+        <v>41.61840001424154</v>
       </c>
       <c r="W62" t="n">
         <v>1</v>
       </c>
       <c r="X62" t="n">
-        <v>19.98677258223685</v>
+        <v>20.28333947523408</v>
       </c>
       <c r="Y62" t="n">
-        <v>42.96485000610352</v>
+        <v>42.90889999389648</v>
       </c>
       <c r="Z62" t="n">
         <v>1</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.51385112756025</v>
+        <v>16.66577651818558</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.813459836212046</v>
+        <v>5.844681496989009</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.658834078621979</v>
+        <v>5.684880993734921</v>
       </c>
       <c r="AD62" t="n">
-        <v>4.711597997637175</v>
+        <v>4.718944484995123</v>
       </c>
       <c r="AE62" t="n">
-        <v>4.352043259312615</v>
+        <v>4.364334681034808</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.447921323646943</v>
+        <v>1.466064781049059</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.176343210284187</v>
+        <v>1.183104704107753</v>
       </c>
       <c r="AH62" t="n">
         <v>0.6742306412267967</v>
@@ -19484,16 +19512,16 @@
         <v>28.82999992370605</v>
       </c>
       <c r="E63" t="n">
-        <v>28.86000061035156</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>27.89999961853027</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>28.3700008392334</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>28144800</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0.02634388633315798</v>
@@ -19592,7 +19620,7 @@
         <v>29.1</v>
       </c>
       <c r="AO63" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="AP63" t="n">
         <v>2</v>
@@ -19805,16 +19833,16 @@
         <v>31.5</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>30.93000030517578</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>64903300</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0.1158342370098611</v>
@@ -20110,16 +20138,16 @@
         <v>16.92000007629395</v>
       </c>
       <c r="E65" t="n">
-        <v>17.79999923706055</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>16.89999961853027</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>17.25</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>7462400</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>-0.01627910896660079</v>
@@ -20152,49 +20180,49 @@
         <v>-1.37207401114767</v>
       </c>
       <c r="S65" t="n">
-        <v>15.65660003662109</v>
+        <v>15.65120002746582</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>8.069440598327446</v>
+        <v>8.10672693851938</v>
       </c>
       <c r="V65" t="n">
-        <v>15.93719998041789</v>
+        <v>15.91539998372396</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>6.166704923597806</v>
+        <v>6.312125950949089</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.79347774028778</v>
+        <v>15.78254996299744</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>7.132832644785416</v>
+        <v>7.2070110087615</v>
       </c>
       <c r="AB65" t="n">
-        <v>-0.2015560833182188</v>
+        <v>-0.2017302862363238</v>
       </c>
       <c r="AC65" t="n">
-        <v>-0.3529998533188213</v>
+        <v>-0.353380715905479</v>
       </c>
       <c r="AD65" t="n">
-        <v>-0.2101425525677469</v>
+        <v>-0.2100819003068996</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.8234494568415286</v>
+        <v>0.8276203204702475</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.5323202552265851</v>
+        <v>0.5435167316913534</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.6465258108343039</v>
+        <v>0.6521649699533139</v>
       </c>
       <c r="AH65" t="n">
         <v>0.3588837990063</v>
@@ -20413,16 +20441,16 @@
         <v>20.90999984741211</v>
       </c>
       <c r="E66" t="n">
-        <v>21.1299991607666</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>19.20000076293945</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>19.30999946594238</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>31460400</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>0.1860465594317637</v>
@@ -20455,49 +20483,49 @@
         <v>19.88621303434735</v>
       </c>
       <c r="S66" t="n">
-        <v>17.82380004882813</v>
+        <v>17.7892000579834</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>17.31504948512309</v>
+        <v>17.54322723481974</v>
       </c>
       <c r="V66" t="n">
-        <v>18.62806668599447</v>
+        <v>18.61413335164388</v>
       </c>
       <c r="W66" t="n">
         <v>1</v>
       </c>
       <c r="X66" t="n">
-        <v>12.24997311789376</v>
+        <v>12.33399617589757</v>
       </c>
       <c r="Y66" t="n">
-        <v>19.5327499961853</v>
+        <v>19.49884999275207</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>7.05097772456915</v>
+        <v>7.237092726927867</v>
       </c>
       <c r="AB66" t="n">
-        <v>5.402319912717814</v>
+        <v>5.442375886273336</v>
       </c>
       <c r="AC66" t="n">
-        <v>5.27908984058111</v>
+        <v>5.318781778369997</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.140175568768966</v>
+        <v>4.169764168750907</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.872403291170232</v>
+        <v>2.949040974245972</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.351496274972336</v>
+        <v>1.380232846187108</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.6328143067721669</v>
+        <v>0.6596446151817602</v>
       </c>
       <c r="AH66" t="n">
         <v>0.6088717142845692</v>
@@ -20714,16 +20742,16 @@
         <v>41.95999908447266</v>
       </c>
       <c r="E67" t="n">
-        <v>45.13999938964844</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>40.59999847412109</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>45.09999847412109</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>28517200</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>-0.05388950331177667</v>
@@ -20756,49 +20784,49 @@
         <v>-9.187319509755083</v>
       </c>
       <c r="S67" t="n">
-        <v>44.67260009765625</v>
+        <v>44.66160011291504</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-6.072180726561091</v>
+        <v>-6.049046656662769</v>
       </c>
       <c r="V67" t="n">
-        <v>45.18766675313314</v>
+        <v>45.07586675008138</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-7.142806656280137</v>
+        <v>-6.912496398315179</v>
       </c>
       <c r="Y67" t="n">
-        <v>46.99830003738403</v>
+        <v>46.95945003509522</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-10.72017700406981</v>
+        <v>-10.64631495233912</v>
       </c>
       <c r="AB67" t="n">
-        <v>-2.028230949243131</v>
+        <v>-2.026697271531326</v>
       </c>
       <c r="AC67" t="n">
-        <v>-2.189482620738107</v>
+        <v>-2.186721541750836</v>
       </c>
       <c r="AD67" t="n">
-        <v>-1.874908321387764</v>
+        <v>-1.871232426767193</v>
       </c>
       <c r="AE67" t="n">
-        <v>-0.8714768315957749</v>
+        <v>-0.8682798679909679</v>
       </c>
       <c r="AF67" t="n">
-        <v>-0.8930324579831065</v>
+        <v>-0.8615698781047036</v>
       </c>
       <c r="AG67" t="n">
-        <v>-1.347031239469507</v>
+        <v>-1.335310994613474</v>
       </c>
       <c r="AH67" t="n">
         <v>0.300065955656146</v>
@@ -20812,19 +20840,19 @@
         </is>
       </c>
       <c r="AK67" t="n">
-        <v>39.2</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="n">
         <v>41.9</v>
       </c>
       <c r="AM67" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN67" t="n">
         <v>42.7</v>
       </c>
-      <c r="AN67" t="n">
+      <c r="AO67" t="n">
         <v>47.1</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>47.3</v>
       </c>
       <c r="AP67" t="n">
         <v>1</v>
@@ -21017,16 +21045,16 @@
         <v>43.88999938964844</v>
       </c>
       <c r="E68" t="n">
-        <v>46.45000076293945</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>43.40000152587891</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>43.40000152587891</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>7747600</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0.02427073401543867</v>
@@ -21316,16 +21344,16 @@
         <v>19.27000045776367</v>
       </c>
       <c r="E69" t="n">
-        <v>20.04999923706055</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>19.27000045776367</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>19.34000015258789</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>16775300</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0.03881408357498217</v>
@@ -21358,49 +21386,49 @@
         <v>1.472407865779866</v>
       </c>
       <c r="S69" t="n">
-        <v>18.97459995269775</v>
+        <v>18.92119995117188</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>1.556820727721945</v>
+        <v>1.843437559414375</v>
       </c>
       <c r="V69" t="n">
-        <v>22.51486666361491</v>
+        <v>22.45819999694824</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-14.41210491863625</v>
+        <v>-14.19614902181743</v>
       </c>
       <c r="Y69" t="n">
-        <v>22.96520000457764</v>
+        <v>22.94210000038147</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-16.09043050388154</v>
+        <v>-16.00594340778193</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.254721051599826</v>
+        <v>1.25738292753499</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.036254213137028</v>
+        <v>1.038487331658629</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.2521839005950507</v>
+        <v>0.2526433335081886</v>
       </c>
       <c r="AE69" t="n">
-        <v>0.1979239032588091</v>
+        <v>0.2347042470302936</v>
       </c>
       <c r="AF69" t="n">
-        <v>-1.083321627362119</v>
+        <v>-1.067371891447549</v>
       </c>
       <c r="AG69" t="n">
-        <v>-1.043759170464431</v>
+        <v>-1.038305690121427</v>
       </c>
       <c r="AH69" t="n">
         <v>0.212530543714433</v>
@@ -21617,16 +21645,16 @@
         <v>36.81999969482422</v>
       </c>
       <c r="E70" t="n">
-        <v>38.31000137329102</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>36.25</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>37.11999893188477</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>8766200</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>0.04158419474273178</v>
@@ -21659,52 +21687,52 @@
         <v>6.504977429796329</v>
       </c>
       <c r="S70" t="n">
-        <v>32.92699993133545</v>
+        <v>33.01439994812011</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>11.82312318646418</v>
+        <v>11.5270904595702</v>
       </c>
       <c r="V70" t="n">
-        <v>32.46733325958252</v>
+        <v>32.43073324839274</v>
       </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>13.40629487627242</v>
+        <v>13.53428062453386</v>
       </c>
       <c r="Y70" t="n">
-        <v>34.92499999046326</v>
+        <v>34.85299998283386</v>
       </c>
       <c r="Z70" t="n">
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>5.425911824991891</v>
+        <v>5.643702731355004</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.358201720433916</v>
+        <v>1.355987392951198</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.223416829141946</v>
+        <v>1.22063832096075</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.144878387005581</v>
+        <v>1.150391253014784</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.535891483071223</v>
+        <v>1.506209731140809</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.12764141346446</v>
+        <v>1.144153318371262</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.3847601716034346</v>
+        <v>0.4035364592469232</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.3750909058215391</v>
+        <v>0.3750909058215392</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -21918,16 +21946,16 @@
         <v>39.04999923706055</v>
       </c>
       <c r="E71" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>38.38000106811523</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>38.43000030517578</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>20571100</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0.01139597564758965</v>
@@ -21960,52 +21988,52 @@
         <v>3.216556166121528</v>
       </c>
       <c r="S71" t="n">
-        <v>35.43419994354248</v>
+        <v>35.39999996185303</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>10.20426395764301</v>
+        <v>10.31073242695128</v>
       </c>
       <c r="V71" t="n">
-        <v>30.49193337758382</v>
+        <v>30.52586671193441</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>28.06665537898687</v>
+        <v>27.92429320866273</v>
       </c>
       <c r="Y71" t="n">
-        <v>28.81825003623963</v>
+        <v>28.86575003623962</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>35.50440844934809</v>
+        <v>35.28142933419386</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.6425202212090279</v>
+        <v>0.6394044174308883</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.504241152498742</v>
+        <v>0.5015633849397442</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.4781712711164886</v>
+        <v>0.4771277375462445</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.206780089116938</v>
+        <v>1.227976060954138</v>
       </c>
       <c r="AF71" t="n">
-        <v>3.138558389731407</v>
+        <v>3.129349777064299</v>
       </c>
       <c r="AG71" t="n">
-        <v>3.482351198271703</v>
+        <v>3.469956190516286</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.319486333973434</v>
+        <v>0.3194863339734341</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -22020,7 +22048,7 @@
         <v>22.7</v>
       </c>
       <c r="AM71" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
@@ -22219,16 +22247,16 @@
         <v>7.460000038146973</v>
       </c>
       <c r="E72" t="n">
-        <v>7.829999923706055</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>7.269999980926514</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>7.730000019073486</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>17568000</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>-0.002673794234694493</v>
@@ -22261,49 +22289,49 @@
         <v>2.689538275613446</v>
       </c>
       <c r="S72" t="n">
-        <v>7.210199995040893</v>
+        <v>7.183800001144409</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>3.464536951511598</v>
+        <v>3.844762339688802</v>
       </c>
       <c r="V72" t="n">
-        <v>7.961733341217041</v>
+        <v>7.963466672897339</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-6.3018099397106</v>
+        <v>-6.322204329225764</v>
       </c>
       <c r="Y72" t="n">
-        <v>7.555250008106231</v>
+        <v>7.56135000705719</v>
       </c>
       <c r="Z72" t="n">
         <v>-1</v>
       </c>
       <c r="AA72" t="n">
-        <v>-1.26071235044588</v>
+        <v>-1.340368701562876</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.01775006911536</v>
+        <v>1.023863346971476</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.9475827384864958</v>
+        <v>0.9541526308532758</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.2864319258926376</v>
+        <v>0.2865148518958277</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.2539113387715611</v>
+        <v>0.2819292285496051</v>
       </c>
       <c r="AF72" t="n">
-        <v>-0.3181542481529731</v>
+        <v>-0.3195499027944631</v>
       </c>
       <c r="AG72" t="n">
-        <v>-0.05563744867042205</v>
+        <v>-0.05931257474993702</v>
       </c>
       <c r="AH72" t="n">
         <v>0.4347960637929446</v>
@@ -22524,16 +22552,16 @@
         <v>71.40000152587891</v>
       </c>
       <c r="E73" t="n">
-        <v>74.26999664306641</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>69.51000213623047</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>73.37999725341797</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>71199700</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>-0.009708695742808304</v>
@@ -22566,52 +22594,52 @@
         <v>-4.356606078566405</v>
       </c>
       <c r="S73" t="n">
-        <v>74.82560043334961</v>
+        <v>74.83940048217774</v>
       </c>
       <c r="T73" t="n">
         <v>-1</v>
       </c>
       <c r="U73" t="n">
-        <v>-4.578110817195552</v>
+        <v>-4.595706184361926</v>
       </c>
       <c r="V73" t="n">
-        <v>78.63380030314127</v>
+        <v>78.55226694742838</v>
       </c>
       <c r="W73" t="n">
         <v>-1</v>
       </c>
       <c r="X73" t="n">
-        <v>-9.199350342187886</v>
+        <v>-9.105103772926341</v>
       </c>
       <c r="Y73" t="n">
-        <v>79.09965019226074</v>
+        <v>79.13625019073487</v>
       </c>
       <c r="Z73" t="n">
         <v>-1</v>
       </c>
       <c r="AA73" t="n">
-        <v>-9.734112158103049</v>
+        <v>-9.775859541246888</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.2898789034586381</v>
+        <v>0.2898727498529467</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.175600116853444</v>
+        <v>0.1756103733435349</v>
       </c>
       <c r="AD73" t="n">
-        <v>-0.8636212144800783</v>
+        <v>-0.863529407880674</v>
       </c>
       <c r="AE73" t="n">
-        <v>-0.6407819185453847</v>
+        <v>-0.6427992512024672</v>
       </c>
       <c r="AF73" t="n">
-        <v>-0.6600272466011007</v>
+        <v>-0.6521134538891734</v>
       </c>
       <c r="AG73" t="n">
-        <v>-0.6696470351508418</v>
+        <v>-0.6707288059756299</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.2592894913477306</v>
+        <v>0.2592894913477305</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -22821,16 +22849,16 @@
         <v>5.75</v>
       </c>
       <c r="E74" t="n">
-        <v>5.800000190734863</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>5.440000057220459</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>5.449999809265137</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>57645700</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>0.2130802273527488</v>
@@ -22863,55 +22891,55 @@
         <v>56.44621267843545</v>
       </c>
       <c r="S74" t="n">
-        <v>3.358799977302551</v>
+        <v>3.353999977111816</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>71.19209357080616</v>
+        <v>71.43709121165284</v>
       </c>
       <c r="V74" t="n">
-        <v>3.419861454963684</v>
+        <v>3.410116723378499</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>68.13546617961049</v>
+        <v>68.61592920207471</v>
       </c>
       <c r="Y74" t="n">
-        <v>3.532296090126037</v>
+      